--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -53,19 +53,19 @@
     <t xml:space="preserve">1.20654845237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23177230358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2499897480011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26330244541168</t>
+    <t xml:space="preserve">1.23177254199982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24998962879181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26330232620239</t>
   </si>
   <si>
     <t xml:space="preserve">1.27311182022095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26120030879974</t>
+    <t xml:space="preserve">1.26120042800903</t>
   </si>
   <si>
     <t xml:space="preserve">1.24718713760376</t>
@@ -77,40 +77,40 @@
     <t xml:space="preserve">1.19323575496674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501842975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814038276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24578583240509</t>
+    <t xml:space="preserve">1.17501854896545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19814050197601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2457857131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.23457515239716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495640277863</t>
+    <t xml:space="preserve">1.21495628356934</t>
   </si>
   <si>
     <t xml:space="preserve">1.18272566795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17992305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641985416412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12457048892975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12807357311249</t>
+    <t xml:space="preserve">1.17992317676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641961574554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12457036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12807369232178</t>
   </si>
   <si>
     <t xml:space="preserve">1.10284984111786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08603382110596</t>
+    <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
     <t xml:space="preserve">1.01596701145172</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">1.02507567405701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02017080783844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195372104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297377586365</t>
+    <t xml:space="preserve">1.02017092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297365665436</t>
   </si>
   <si>
     <t xml:space="preserve">1.04329299926758</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">1.1105569601059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09304022789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106716632843</t>
+    <t xml:space="preserve">1.0930403470993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106704711914</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017582893372</t>
@@ -155,85 +155,85 @@
     <t xml:space="preserve">1.10004711151123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1315770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705387592316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227760791779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1182644367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14909362792969</t>
+    <t xml:space="preserve">1.13157713413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705363750458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227772712708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11826455593109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1490935087204</t>
   </si>
   <si>
     <t xml:space="preserve">1.17852175235748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17011368274689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412709236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16310703754425</t>
+    <t xml:space="preserve">1.1701135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412721157074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16310715675354</t>
   </si>
   <si>
     <t xml:space="preserve">1.22616708278656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2450852394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24088132381439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20514702796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1911336183548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22686779499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22196316719055</t>
+    <t xml:space="preserve">1.24508512020111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2408812046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20514714717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113373756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22686767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22196304798126</t>
   </si>
   <si>
     <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17221558094025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183433055878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19743978977203</t>
+    <t xml:space="preserve">1.17221570014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183456897736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19743967056274</t>
   </si>
   <si>
     <t xml:space="preserve">1.20374584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20304501056671</t>
+    <t xml:space="preserve">1.203045129776</t>
   </si>
   <si>
     <t xml:space="preserve">1.23807835578918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23317384719849</t>
+    <t xml:space="preserve">1.23317360877991</t>
   </si>
   <si>
     <t xml:space="preserve">1.19954168796539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22476577758789</t>
+    <t xml:space="preserve">1.2247656583786</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845972537994</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">1.21916043758392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22896981239319</t>
+    <t xml:space="preserve">1.22896957397461</t>
   </si>
   <si>
     <t xml:space="preserve">1.21215379238129</t>
@@ -251,31 +251,31 @@
     <t xml:space="preserve">1.22266376018524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2920298576355</t>
+    <t xml:space="preserve">1.29202973842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.2962338924408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27521395683289</t>
+    <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
     <t xml:space="preserve">1.28712511062622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28151977062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788773059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737788200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865023136139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469908714294</t>
+    <t xml:space="preserve">1.28151965141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788784980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737776279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865046977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469920635223</t>
   </si>
   <si>
     <t xml:space="preserve">1.14138638973236</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13648164272308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14629113674164</t>
+    <t xml:space="preserve">1.13648176193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14629125595093</t>
   </si>
   <si>
     <t xml:space="preserve">1.14208710193634</t>
@@ -302,49 +302,49 @@
     <t xml:space="preserve">1.084632396698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501376628876</t>
+    <t xml:space="preserve">1.06501364707947</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253037929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902705669403</t>
+    <t xml:space="preserve">1.08253026008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">1.05800724029541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1014484167099</t>
+    <t xml:space="preserve">1.10144853591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.10355031490326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09514236450195</t>
+    <t xml:space="preserve">1.09514248371124</t>
   </si>
   <si>
     <t xml:space="preserve">1.11966574192047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09934628009796</t>
+    <t xml:space="preserve">1.09934651851654</t>
   </si>
   <si>
     <t xml:space="preserve">1.11265921592712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1568009853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528017044067</t>
+    <t xml:space="preserve">1.15680122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528040885925</t>
   </si>
   <si>
     <t xml:space="preserve">1.48681509494781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48821640014648</t>
+    <t xml:space="preserve">1.48821651935577</t>
   </si>
   <si>
     <t xml:space="preserve">1.45178186893463</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">1.40133380889893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4699991941452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375540733337</t>
+    <t xml:space="preserve">1.46999931335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776834011078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375528812408</t>
   </si>
   <si>
     <t xml:space="preserve">1.43636703491211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936062812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674876213074</t>
+    <t xml:space="preserve">1.42936050891876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674852371216</t>
   </si>
   <si>
     <t xml:space="preserve">1.42235386371613</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">1.41814982891083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41114318370819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42795944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48120999336243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69421255588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338348388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071425437927</t>
+    <t xml:space="preserve">1.4111430644989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42795932292938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48120975494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69421243667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338336467743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80071401596069</t>
   </si>
   <si>
     <t xml:space="preserve">1.84555673599243</t>
@@ -407,103 +407,103 @@
     <t xml:space="preserve">1.7923059463501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79090440273285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268707752228</t>
+    <t xml:space="preserve">1.79090452194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268731594086</t>
   </si>
   <si>
     <t xml:space="preserve">1.73064720630646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71663391590118</t>
+    <t xml:space="preserve">1.71663403511047</t>
   </si>
   <si>
     <t xml:space="preserve">1.78670072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84275424480438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593810558319</t>
+    <t xml:space="preserve">1.84275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593774795532</t>
   </si>
   <si>
     <t xml:space="preserve">1.82313549518585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83995127677917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83854997158051</t>
+    <t xml:space="preserve">1.8399510383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854973316193</t>
   </si>
   <si>
     <t xml:space="preserve">1.84415531158447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8301420211792</t>
+    <t xml:space="preserve">1.83014178276062</t>
   </si>
   <si>
     <t xml:space="preserve">1.81472730636597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82874059677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192457675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294475078583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937916278839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99549925327301</t>
+    <t xml:space="preserve">1.82874071598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192469596863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294463157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835886955261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8693790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549949169159</t>
   </si>
   <si>
     <t xml:space="preserve">2.07257270812988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02913093566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798742294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04034161567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830210208893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03053259849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01932191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9997034072876</t>
+    <t xml:space="preserve">2.02913117408752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798718452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04034185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830222129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03053283691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01932215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970328807831</t>
   </si>
   <si>
     <t xml:space="preserve">2.01231551170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09359288215637</t>
+    <t xml:space="preserve">2.09359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066645622253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15945553779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989403247833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339257240295</t>
+    <t xml:space="preserve">2.15945506095886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989415168762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339269161224</t>
   </si>
   <si>
     <t xml:space="preserve">1.97167646884918</t>
@@ -512,31 +512,31 @@
     <t xml:space="preserve">1.95345938205719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01651906967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250601768494</t>
+    <t xml:space="preserve">2.01651930809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250625610352</t>
   </si>
   <si>
     <t xml:space="preserve">1.98428869247437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9786833524704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944585323334</t>
+    <t xml:space="preserve">1.97868311405182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944561481476</t>
   </si>
   <si>
     <t xml:space="preserve">1.91982746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.863774061203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86797785758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918865680695</t>
+    <t xml:space="preserve">1.86377418041229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8679780960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918889522552</t>
   </si>
   <si>
     <t xml:space="preserve">1.85676729679108</t>
@@ -545,64 +545,64 @@
     <t xml:space="preserve">1.78950321674347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80631947517395</t>
+    <t xml:space="preserve">1.80631911754608</t>
   </si>
   <si>
     <t xml:space="preserve">1.90301120281219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89880752563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91001784801483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690043926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849260807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569011688232</t>
+    <t xml:space="preserve">1.89880728721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001772880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849284648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98568999767303</t>
   </si>
   <si>
     <t xml:space="preserve">1.94224858283997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95766353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186697483063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326839923859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9702752828598</t>
+    <t xml:space="preserve">1.95766317844391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9618673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326851844788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027564048767</t>
   </si>
   <si>
     <t xml:space="preserve">1.96607136726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0039074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397389411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18888354301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1650607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13283014297485</t>
+    <t xml:space="preserve">2.00390720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18888306617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16506052017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13282990455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.06416487693787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09639549255371</t>
+    <t xml:space="preserve">2.09639525413513</t>
   </si>
   <si>
     <t xml:space="preserve">2.11601448059082</t>
@@ -617,40 +617,40 @@
     <t xml:space="preserve">2.14404058456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13002753257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14824509620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13423132896423</t>
+    <t xml:space="preserve">2.13002729415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14824485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13423156738281</t>
   </si>
   <si>
     <t xml:space="preserve">2.14123797416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15244841575623</t>
+    <t xml:space="preserve">2.15244889259338</t>
   </si>
   <si>
     <t xml:space="preserve">2.13703417778015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11180996894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09779667854309</t>
+    <t xml:space="preserve">2.11181020736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09779644012451</t>
   </si>
   <si>
     <t xml:space="preserve">2.118816614151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10200095176697</t>
+    <t xml:space="preserve">2.10200071334839</t>
   </si>
   <si>
     <t xml:space="preserve">2.11741542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24213433265686</t>
+    <t xml:space="preserve">2.24213409423828</t>
   </si>
   <si>
     <t xml:space="preserve">2.48876881599426</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">2.48316359519958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46494626998901</t>
+    <t xml:space="preserve">2.46494603157043</t>
   </si>
   <si>
     <t xml:space="preserve">2.40328741073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099919319153</t>
+    <t xml:space="preserve">2.52099895477295</t>
   </si>
   <si>
     <t xml:space="preserve">2.48036098480225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46634769439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4439263343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43972229957581</t>
+    <t xml:space="preserve">2.46634721755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44392609596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43972253799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.47615671157837</t>
@@ -698,100 +698,100 @@
     <t xml:space="preserve">2.47335457801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65552759170532</t>
+    <t xml:space="preserve">2.65552735328674</t>
   </si>
   <si>
     <t xml:space="preserve">2.71858763694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70457410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751081466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11096096038818</t>
+    <t xml:space="preserve">2.7045738697052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751057624817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865456581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11096119880676</t>
   </si>
   <si>
     <t xml:space="preserve">3.23988389968872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38422107696533</t>
+    <t xml:space="preserve">3.38422083854675</t>
   </si>
   <si>
     <t xml:space="preserve">3.46129441261292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71003079414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5804078578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251465797424</t>
+    <t xml:space="preserve">3.71003150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040809631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251489639282</t>
   </si>
   <si>
     <t xml:space="preserve">3.6609845161438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69601798057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78360176086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176076889038</t>
+    <t xml:space="preserve">3.69601821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7836012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95176100730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.06386804580688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19349145889282</t>
+    <t xml:space="preserve">4.19349098205566</t>
   </si>
   <si>
     <t xml:space="preserve">4.16896820068359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11291408538818</t>
+    <t xml:space="preserve">4.11291456222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.03233814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30910205841064</t>
+    <t xml:space="preserve">4.30910158157349</t>
   </si>
   <si>
     <t xml:space="preserve">4.30559825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6979718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50023555755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10085582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01677513122559</t>
+    <t xml:space="preserve">4.55433464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69797134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50023508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256200790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10085535049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01677465438843</t>
   </si>
   <si>
     <t xml:space="preserve">5.44768524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4441819190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77349519729614</t>
+    <t xml:space="preserve">5.44418144226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7734956741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.3970890045166</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">6.76143550872803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49518299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238851547241</t>
+    <t xml:space="preserve">6.49518203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238946914673</t>
   </si>
   <si>
     <t xml:space="preserve">7.09369373321533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97858142852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626554489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5325288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35266828536987</t>
+    <t xml:space="preserve">6.97858190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3562650680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53252840042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35266780853271</t>
   </si>
   <si>
     <t xml:space="preserve">6.07208585739136</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">6.32389116287231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43900156021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4030294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798803329468</t>
+    <t xml:space="preserve">6.43900108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40302896499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15842008590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798851013184</t>
   </si>
   <si>
     <t xml:space="preserve">6.37425088882446</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">5.6943793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70157384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3670334815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87421560287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1799783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97853517532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96414613723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84543895721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8778133392334</t>
+    <t xml:space="preserve">5.70157432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36703300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87421655654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17997789382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97853565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96414709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8454384803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87781286239624</t>
   </si>
   <si>
     <t xml:space="preserve">4.9101881980896</t>
@@ -911,91 +911,91 @@
     <t xml:space="preserve">4.70155000686646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92457675933838</t>
+    <t xml:space="preserve">4.92457723617554</t>
   </si>
   <si>
     <t xml:space="preserve">4.7698974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.690758228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6583833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68716096878052</t>
+    <t xml:space="preserve">4.69075870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65838432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68716144561768</t>
   </si>
   <si>
     <t xml:space="preserve">4.82385540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55046701431274</t>
+    <t xml:space="preserve">4.5504674911499</t>
   </si>
   <si>
     <t xml:space="preserve">4.51089811325073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49291276931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43895387649536</t>
+    <t xml:space="preserve">4.49291181564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4389533996582</t>
   </si>
   <si>
     <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38499593734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46413469314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03609085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85622978210449</t>
+    <t xml:space="preserve">4.38499641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46413421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0360894203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85623025894165</t>
   </si>
   <si>
     <t xml:space="preserve">4.80946636199951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76629972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68356466293335</t>
+    <t xml:space="preserve">4.76630020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68356418609619</t>
   </si>
   <si>
     <t xml:space="preserve">4.67636966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60442590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59003639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62960577011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66198062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67277193069458</t>
+    <t xml:space="preserve">4.60442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59003686904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62960624694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66198110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277240753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.74831390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75910520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95335388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486845016479</t>
+    <t xml:space="preserve">4.75910472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9533543586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486749649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.14400672912598</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">5.11522960662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19436740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10803413391113</t>
+    <t xml:space="preserve">5.1943678855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10803461074829</t>
   </si>
   <si>
     <t xml:space="preserve">4.93536853790283</t>
@@ -1016,37 +1016,37 @@
     <t xml:space="preserve">4.75550842285156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99652099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90659046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097949981689</t>
+    <t xml:space="preserve">4.99652147293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90659093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92098045349121</t>
   </si>
   <si>
     <t xml:space="preserve">4.82025766372681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89220190048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05407619476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0181040763855</t>
+    <t xml:space="preserve">4.89220237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05407667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01810455322266</t>
   </si>
   <si>
     <t xml:space="preserve">4.95695209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616079330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839529037476</t>
+    <t xml:space="preserve">4.94616031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839576721191</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393678665161</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">5.89942026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77711486816406</t>
+    <t xml:space="preserve">5.77711534500122</t>
   </si>
   <si>
     <t xml:space="preserve">6.03611373901367</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">5.94978141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18000173568726</t>
+    <t xml:space="preserve">6.18000268936157</t>
   </si>
   <si>
     <t xml:space="preserve">6.20878028869629</t>
@@ -1076,40 +1076,40 @@
     <t xml:space="preserve">6.52533388137817</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03613710403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89584732055664</t>
+    <t xml:space="preserve">7.03613758087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89584684371948</t>
   </si>
   <si>
     <t xml:space="preserve">7.11527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802331924438</t>
+    <t xml:space="preserve">7.13685894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802379608154</t>
   </si>
   <si>
     <t xml:space="preserve">8.12968921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43904685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704650878906</t>
+    <t xml:space="preserve">8.43904781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704746246338</t>
   </si>
   <si>
     <t xml:space="preserve">9.29518413543701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160682678223</t>
+    <t xml:space="preserve">10.2160692214966</t>
   </si>
   <si>
     <t xml:space="preserve">8.42465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61890888214111</t>
+    <t xml:space="preserve">8.61890983581543</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321605682373</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">8.01457977294922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80593967437744</t>
+    <t xml:space="preserve">7.80594062805176</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">7.99299383163452</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10091209411621</t>
+    <t xml:space="preserve">8.10091018676758</t>
   </si>
   <si>
     <t xml:space="preserve">7.98580026626587</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">7.8850793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73399543762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41024684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54694175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499656677246</t>
+    <t xml:space="preserve">7.73399591445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41024780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54694128036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499752044678</t>
   </si>
   <si>
     <t xml:space="preserve">7.45341396331787</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">7.52535820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38866424560547</t>
+    <t xml:space="preserve">7.38866472244263</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760509490967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84191179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910726547241</t>
+    <t xml:space="preserve">7.84191226959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910774230957</t>
   </si>
   <si>
     <t xml:space="preserve">8.04335689544678</t>
@@ -1178,91 +1178,91 @@
     <t xml:space="preserve">7.85630178451538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74838638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463636398315</t>
+    <t xml:space="preserve">7.74838542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571840286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.424635887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.19441509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96419382095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599864959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498512268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20880317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20160961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413675308228</t>
+    <t xml:space="preserve">6.96419429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498655319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2088041305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20161056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">7.65485763549805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25196981430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00735998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944410324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91742897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85627746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89224910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78793001174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95699977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98217916488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16204023361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045763015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02174997329712</t>
+    <t xml:space="preserve">7.2519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00736045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9534010887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844297409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91742992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.856276512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.892249584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78793096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95699882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541669845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217964172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16204071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02174949645996</t>
   </si>
   <si>
     <t xml:space="preserve">7.338303565979</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">7.82752323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25918865203857</t>
+    <t xml:space="preserve">8.25918769836426</t>
   </si>
   <si>
     <t xml:space="preserve">8.15846633911133</t>
@@ -1280,46 +1280,46 @@
     <t xml:space="preserve">7.9138560295105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89946746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313514709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76996850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48219203948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79152679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850099563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64044523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48936223983765</t>
+    <t xml:space="preserve">7.8994665145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313467025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76996803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48219156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836015701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850147247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6404447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4893627166748</t>
   </si>
   <si>
     <t xml:space="preserve">6.63325119018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62605571746826</t>
+    <t xml:space="preserve">6.62605667114258</t>
   </si>
   <si>
     <t xml:space="preserve">6.56130647659302</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">6.55411195755005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28791809082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19439172744751</t>
+    <t xml:space="preserve">6.28791904449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19439125061035</t>
   </si>
   <si>
     <t xml:space="preserve">6.02172517776489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87783670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86344766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25914144515991</t>
+    <t xml:space="preserve">5.87783718109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86344718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914096832275</t>
   </si>
   <si>
     <t xml:space="preserve">6.26633548736572</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">6.44619560241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46777868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641735076904</t>
+    <t xml:space="preserve">6.46777820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641687393188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51814031600952</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">6.46058368682861</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29511260986328</t>
+    <t xml:space="preserve">6.2951135635376</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086297988892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13683557510376</t>
+    <t xml:space="preserve">6.1368350982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.92819786071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93539142608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89222526550293</t>
+    <t xml:space="preserve">5.93539237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89222574234009</t>
   </si>
   <si>
     <t xml:space="preserve">5.79869890213013</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99294757843018</t>
+    <t xml:space="preserve">5.99294805526733</t>
   </si>
   <si>
     <t xml:space="preserve">6.17280769348145</t>
@@ -1403,19 +1403,19 @@
     <t xml:space="preserve">6.1871976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25194692611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22316884994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12244701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27353000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950212478638</t>
+    <t xml:space="preserve">6.25194644927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12244749069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27353048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950164794922</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230760574341</t>
@@ -1424,25 +1424,25 @@
     <t xml:space="preserve">6.33828020095825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58551788330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38323163986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46564483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326290130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30831098556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59300947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41320037841797</t>
+    <t xml:space="preserve">6.58551740646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38323211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326242446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3083119392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41320085525513</t>
   </si>
   <si>
     <t xml:space="preserve">6.17345428466797</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">6.09853410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90373992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618391036987</t>
+    <t xml:space="preserve">5.90374040603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
   </si>
   <si>
     <t xml:space="preserve">5.9411997795105</t>
@@ -1463,46 +1463,46 @@
     <t xml:space="preserve">5.86628007888794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94869232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84380340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48418569564819</t>
+    <t xml:space="preserve">5.9486927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84380388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48418521881104</t>
   </si>
   <si>
     <t xml:space="preserve">5.60405826568604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55910539627075</t>
+    <t xml:space="preserve">5.55910587310791</t>
   </si>
   <si>
     <t xml:space="preserve">5.888756275177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8063440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64151859283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79135894775391</t>
+    <t xml:space="preserve">5.80634355545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64151811599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79135942459106</t>
   </si>
   <si>
     <t xml:space="preserve">5.76139163970947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88126420974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621612548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078670501709</t>
+    <t xml:space="preserve">5.88126468658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621660232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078718185425</t>
   </si>
   <si>
     <t xml:space="preserve">6.55554866790771</t>
@@ -1517,34 +1517,34 @@
     <t xml:space="preserve">6.30081939697266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12850284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06107378005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77637577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76888275146484</t>
+    <t xml:space="preserve">6.12850189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06107330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77637529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.768883228302</t>
   </si>
   <si>
     <t xml:space="preserve">5.70145463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66399383544922</t>
+    <t xml:space="preserve">5.66399478912354</t>
   </si>
   <si>
     <t xml:space="preserve">5.57409000396729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75389814376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78386688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67897891998291</t>
+    <t xml:space="preserve">5.75389862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78386735916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
     <t xml:space="preserve">5.6265344619751</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">5.61904191970825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65650320053101</t>
+    <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.54412174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58158111572266</t>
+    <t xml:space="preserve">5.58158159255981</t>
   </si>
   <si>
     <t xml:space="preserve">5.50666093826294</t>
@@ -1571,40 +1571,40 @@
     <t xml:space="preserve">5.43174028396606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46920108795166</t>
+    <t xml:space="preserve">5.46920156478882</t>
   </si>
   <si>
     <t xml:space="preserve">5.31935930252075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189897537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49167680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51415348052979</t>
+    <t xml:space="preserve">5.28189945220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49167728424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51415300369263</t>
   </si>
   <si>
     <t xml:space="preserve">5.36431217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27440786361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450307846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2069787979126</t>
+    <t xml:space="preserve">5.27440738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20697927474976</t>
   </si>
   <si>
     <t xml:space="preserve">5.5890736579895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7464075088501</t>
+    <t xml:space="preserve">5.74640655517578</t>
   </si>
   <si>
     <t xml:space="preserve">5.47669267654419</t>
@@ -1616,79 +1616,79 @@
     <t xml:space="preserve">5.13955020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09459781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10958194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07212209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713748931885</t>
+    <t xml:space="preserve">5.0945987701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10958242416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07212162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05713796615601</t>
   </si>
   <si>
     <t xml:space="preserve">5.01967716217041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03466176986694</t>
+    <t xml:space="preserve">5.03466129302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.92977285385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87732887268066</t>
+    <t xml:space="preserve">4.87732839584351</t>
   </si>
   <si>
     <t xml:space="preserve">4.86983633041382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73498010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77243947982788</t>
+    <t xml:space="preserve">4.7349796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77243995666504</t>
   </si>
   <si>
     <t xml:space="preserve">4.82488393783569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88482046127319</t>
+    <t xml:space="preserve">4.88482093811035</t>
   </si>
   <si>
     <t xml:space="preserve">4.75745534896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86234474182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478824615479</t>
+    <t xml:space="preserve">4.86234426498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91478872299194</t>
   </si>
   <si>
     <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85485219955444</t>
+    <t xml:space="preserve">4.8548526763916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95224905014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16951847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13205862045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840667724609</t>
+    <t xml:space="preserve">5.16951894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08710622787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13205814361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840620040894</t>
   </si>
   <si>
     <t xml:space="preserve">6.25586700439453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01612091064453</t>
+    <t xml:space="preserve">6.01612043380737</t>
   </si>
   <si>
     <t xml:space="preserve">6.10602521896362</t>
@@ -1700,19 +1700,19 @@
     <t xml:space="preserve">5.04215335845947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98221731185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94475698471069</t>
+    <t xml:space="preserve">4.98221778869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94475650787354</t>
   </si>
   <si>
     <t xml:space="preserve">4.99720144271851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02716970443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89231300354004</t>
+    <t xml:space="preserve">5.0271692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8923134803772</t>
   </si>
   <si>
     <t xml:space="preserve">5.04964590072632</t>
@@ -1727,25 +1727,25 @@
     <t xml:space="preserve">4.7949161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78742361068726</t>
+    <t xml:space="preserve">4.78742408752441</t>
   </si>
   <si>
     <t xml:space="preserve">4.83237600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97472524642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729761123657</t>
+    <t xml:space="preserve">4.97472476959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729665756226</t>
   </si>
   <si>
     <t xml:space="preserve">4.76494789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47275733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047157287598</t>
+    <t xml:space="preserve">4.4727578163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047204971313</t>
   </si>
   <si>
     <t xml:space="preserve">4.38285303115845</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">4.32291603088379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18056678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30044031143188</t>
+    <t xml:space="preserve">4.18056774139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30043935775757</t>
   </si>
   <si>
     <t xml:space="preserve">4.31542444229126</t>
@@ -1772,16 +1772,16 @@
     <t xml:space="preserve">4.45777320861816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10209035873413</t>
+    <t xml:space="preserve">4.71250295639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10208988189697</t>
   </si>
   <si>
     <t xml:space="preserve">5.07961416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93726491928101</t>
+    <t xml:space="preserve">4.93726539611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.01218605041504</t>
@@ -1796,34 +1796,34 @@
     <t xml:space="preserve">5.25942325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19948673248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11707448959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28939247131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202688217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31186819076538</t>
+    <t xml:space="preserve">5.19948720932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11707401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28939151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31186771392822</t>
   </si>
   <si>
     <t xml:space="preserve">5.41675662994385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44672441482544</t>
+    <t xml:space="preserve">5.37180471420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4467248916626</t>
   </si>
   <si>
     <t xml:space="preserve">5.39427995681763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45421743392944</t>
+    <t xml:space="preserve">5.45421695709229</t>
   </si>
   <si>
     <t xml:space="preserve">5.40926456451416</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">5.89624834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85878753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.121009349823</t>
+    <t xml:space="preserve">5.85878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12100982666016</t>
   </si>
   <si>
     <t xml:space="preserve">6.22589874267578</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">6.00113725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79885101318359</t>
+    <t xml:space="preserve">5.79885149002075</t>
   </si>
   <si>
     <t xml:space="preserve">5.82132768630981</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">6.21091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09104156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
+    <t xml:space="preserve">6.09104204177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097761154175</t>
   </si>
   <si>
     <t xml:space="preserve">6.14348602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04608964920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361345291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859758377075</t>
+    <t xml:space="preserve">6.04608917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859710693359</t>
   </si>
   <si>
     <t xml:space="preserve">5.73142290115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396305084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393131256104</t>
+    <t xml:space="preserve">5.97866153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396257400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393083572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.7089467048645</t>
@@ -1913,31 +1913,31 @@
     <t xml:space="preserve">5.49916934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46170854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73891448974609</t>
+    <t xml:space="preserve">5.46170902252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73891496658325</t>
   </si>
   <si>
     <t xml:space="preserve">5.55161333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47268581390381</t>
+    <t xml:space="preserve">5.47268533706665</t>
   </si>
   <si>
     <t xml:space="preserve">5.30019426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33155632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484470367432</t>
+    <t xml:space="preserve">5.33155584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484518051147</t>
   </si>
   <si>
     <t xml:space="preserve">5.35507774353027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30803489685059</t>
+    <t xml:space="preserve">5.30803394317627</t>
   </si>
   <si>
     <t xml:space="preserve">5.37859916687012</t>
@@ -1949,25 +1949,25 @@
     <t xml:space="preserve">5.24531078338623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26883220672607</t>
+    <t xml:space="preserve">5.26883172988892</t>
   </si>
   <si>
     <t xml:space="preserve">5.28451299667358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25315093994141</t>
+    <t xml:space="preserve">5.25315141677856</t>
   </si>
   <si>
     <t xml:space="preserve">5.14338302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06497812271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00225400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690540313721</t>
+    <t xml:space="preserve">5.06497764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690492630005</t>
   </si>
   <si>
     <t xml:space="preserve">5.20610761642456</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">5.33939695358276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235315322876</t>
+    <t xml:space="preserve">5.29235363006592</t>
   </si>
   <si>
     <t xml:space="preserve">5.11986207962036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13554382324219</t>
+    <t xml:space="preserve">5.13554334640503</t>
   </si>
   <si>
     <t xml:space="preserve">5.09634017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11202144622803</t>
+    <t xml:space="preserve">5.11202192306519</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474555969238</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">5.45700454711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61381483078003</t>
+    <t xml:space="preserve">5.61381435394287</t>
   </si>
   <si>
     <t xml:space="preserve">5.70790195465088</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55893182754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51188850402832</t>
+    <t xml:space="preserve">5.63733673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55893087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51188802719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.48836660385132</t>
@@ -2027,10 +2027,10 @@
     <t xml:space="preserve">5.36291837692261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31587505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32371616363525</t>
+    <t xml:space="preserve">5.31587553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3237156867981</t>
   </si>
   <si>
     <t xml:space="preserve">5.19826745986938</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71999549865723</t>
+    <t xml:space="preserve">4.71999502182007</t>
   </si>
   <si>
     <t xml:space="preserve">4.51614189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97089195251465</t>
+    <t xml:space="preserve">4.97089242935181</t>
   </si>
   <si>
     <t xml:space="preserve">4.82192230224609</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">4.67295217514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63374948501587</t>
+    <t xml:space="preserve">4.63374900817871</t>
   </si>
   <si>
     <t xml:space="preserve">4.64943027496338</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">4.59454727172852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62590885162354</t>
+    <t xml:space="preserve">4.62590932846069</t>
   </si>
   <si>
     <t xml:space="preserve">4.68079233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90032720565796</t>
+    <t xml:space="preserve">4.9003267288208</t>
   </si>
   <si>
     <t xml:space="preserve">5.2296290397644</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">5.15122413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22178888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21394824981689</t>
+    <t xml:space="preserve">5.22178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21394920349121</t>
   </si>
   <si>
     <t xml:space="preserve">5.15906476974487</t>
@@ -2105,46 +2105,46 @@
     <t xml:space="preserve">5.08065938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1277027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01793575286865</t>
+    <t xml:space="preserve">5.12770223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01793527603149</t>
   </si>
   <si>
     <t xml:space="preserve">5.07281923294067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08850002288818</t>
+    <t xml:space="preserve">5.08849954605103</t>
   </si>
   <si>
     <t xml:space="preserve">5.19042682647705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18258619308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52756881713867</t>
+    <t xml:space="preserve">5.18258571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52756929397583</t>
   </si>
   <si>
     <t xml:space="preserve">5.5197286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40212106704712</t>
+    <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
     <t xml:space="preserve">5.56677150726318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43348217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50404739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53541040420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41780185699463</t>
+    <t xml:space="preserve">5.43348264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50404787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53540992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41780233383179</t>
   </si>
   <si>
     <t xml:space="preserve">5.42564296722412</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">5.76278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64517641067505</t>
+    <t xml:space="preserve">5.64517688751221</t>
   </si>
   <si>
     <t xml:space="preserve">5.44132375717163</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">5.40996122360229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38643980026245</t>
+    <t xml:space="preserve">5.38643932342529</t>
   </si>
   <si>
     <t xml:space="preserve">5.34723711013794</t>
@@ -2174,28 +2174,28 @@
     <t xml:space="preserve">5.37075853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23746967315674</t>
+    <t xml:space="preserve">5.2374701499939</t>
   </si>
   <si>
     <t xml:space="preserve">4.97873258590698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83760356903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89248609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92384910583496</t>
+    <t xml:space="preserve">4.8376030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89248657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896562576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9238486289978</t>
   </si>
   <si>
     <t xml:space="preserve">4.87680578231812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98657321929932</t>
+    <t xml:space="preserve">4.98657274246216</t>
   </si>
   <si>
     <t xml:space="preserve">4.57102537155151</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">4.2260422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11627578735352</t>
+    <t xml:space="preserve">4.11627531051636</t>
   </si>
   <si>
     <t xml:space="preserve">3.84185671806335</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">3.29301977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32438158988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099406242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09700679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05780434608459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94803667068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00292062759399</t>
+    <t xml:space="preserve">3.32438182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099382400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09700655937195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05780458450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94803690910339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00292038917542</t>
   </si>
   <si>
     <t xml:space="preserve">3.13620924949646</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">3.25381731987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22245502471924</t>
+    <t xml:space="preserve">3.22245526313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.24205660820007</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">3.24597692489624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23813629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36750459671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34006309509277</t>
+    <t xml:space="preserve">3.23813605308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36750507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34006285667419</t>
   </si>
   <si>
     <t xml:space="preserve">3.45767092704773</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">3.59880065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37142562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52039456367493</t>
+    <t xml:space="preserve">3.37142539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52039480209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.54391670227051</t>
@@ -2297,97 +2297,97 @@
     <t xml:space="preserve">3.7242488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81049489974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92026209831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33580923080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32796907424927</t>
+    <t xml:space="preserve">3.81049466133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9202618598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3358097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32796955108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.32012891769409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23388338088989</t>
+    <t xml:space="preserve">4.23388242721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.16331815719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07707262039185</t>
+    <t xml:space="preserve">4.07707214355469</t>
   </si>
   <si>
     <t xml:space="preserve">4.21820163726807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21036148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740432739258</t>
+    <t xml:space="preserve">4.21036100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740385055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208904266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401560783386</t>
+    <t xml:space="preserve">3.73208928108215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481339454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8340163230896</t>
   </si>
   <si>
     <t xml:space="preserve">3.84577679634094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70072674751282</t>
+    <t xml:space="preserve">3.70072722434998</t>
   </si>
   <si>
     <t xml:space="preserve">3.83009624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265355110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145830154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169014930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74385070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298621177673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660749435425</t>
+    <t xml:space="preserve">3.87321877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265378952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8222553730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145853996277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169062614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385023117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660701751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.10059404373169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91634130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946502685547</t>
+    <t xml:space="preserve">3.91634178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946478843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13979625701904</t>
+    <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
     <t xml:space="preserve">4.14763736724854</t>
@@ -2396,76 +2396,76 @@
     <t xml:space="preserve">4.01434755325317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9516236782074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94378399848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88889956474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05355072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03002977371216</t>
+    <t xml:space="preserve">3.95162415504456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9437837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88890027999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05355024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.030029296875</t>
   </si>
   <si>
     <t xml:space="preserve">3.89281988143921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92810225486755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242122650146</t>
+    <t xml:space="preserve">3.92810249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242146492004</t>
   </si>
   <si>
     <t xml:space="preserve">3.85753726959229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86537861824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617616653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105916976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90850138664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913308143616</t>
+    <t xml:space="preserve">3.86537837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617592811584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458154678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085009098053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.779132604599</t>
   </si>
   <si>
     <t xml:space="preserve">3.755610704422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7477707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657386779785</t>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657410621643</t>
   </si>
   <si>
     <t xml:space="preserve">3.88497948646545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96730470657349</t>
+    <t xml:space="preserve">3.96730518341064</t>
   </si>
   <si>
     <t xml:space="preserve">4.02218866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345181465149</t>
+    <t xml:space="preserve">3.93594288825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345157623291</t>
   </si>
   <si>
     <t xml:space="preserve">3.75953149795532</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">3.6458432674408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6693651676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544532775879</t>
+    <t xml:space="preserve">3.66936492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544461250305</t>
   </si>
   <si>
     <t xml:space="preserve">3.63016247749329</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">3.56351804733276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56743860244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59095978736877</t>
+    <t xml:space="preserve">3.56743836402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5909595489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.48903322219849</t>
@@ -2501,31 +2501,31 @@
     <t xml:space="preserve">3.44199013710022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38710641860962</t>
+    <t xml:space="preserve">3.3871066570282</t>
   </si>
   <si>
     <t xml:space="preserve">3.31654167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3322229385376</t>
+    <t xml:space="preserve">3.33222246170044</t>
   </si>
   <si>
     <t xml:space="preserve">3.40278768539429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42238879203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43806958198547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49295330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55175757408142</t>
+    <t xml:space="preserve">3.42238831520081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43806982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49295353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55175733566284</t>
   </si>
   <si>
     <t xml:space="preserve">3.55567717552185</t>
@@ -2540,19 +2540,19 @@
     <t xml:space="preserve">3.37926554679871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43414950370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630863189697</t>
+    <t xml:space="preserve">3.43414902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630910873413</t>
   </si>
   <si>
     <t xml:space="preserve">3.4615912437439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44983077049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189051628113</t>
+    <t xml:space="preserve">3.44983053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189075469971</t>
   </si>
   <si>
     <t xml:space="preserve">3.20677447319031</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">3.17541241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52823567390442</t>
+    <t xml:space="preserve">3.52823615074158</t>
   </si>
   <si>
     <t xml:space="preserve">3.53215646743774</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">3.53607630729675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10843420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866724014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252084732056</t>
+    <t xml:space="preserve">4.10843467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866652488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252132415771</t>
   </si>
   <si>
     <t xml:space="preserve">4.13195610046387</t>
@@ -2585,22 +2585,22 @@
     <t xml:space="preserve">4.09275341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06139135360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28876638412476</t>
+    <t xml:space="preserve">4.06139087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2887659072876</t>
   </si>
   <si>
     <t xml:space="preserve">4.2495641708374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24172306060791</t>
+    <t xml:space="preserve">4.24172353744507</t>
   </si>
   <si>
     <t xml:space="preserve">4.39853382110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35933065414429</t>
+    <t xml:space="preserve">4.35933113098145</t>
   </si>
   <si>
     <t xml:space="preserve">4.69647359848022</t>
@@ -2612,37 +2612,37 @@
     <t xml:space="preserve">4.82976245880127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72783613204956</t>
+    <t xml:space="preserve">4.7278356552124</t>
   </si>
   <si>
     <t xml:space="preserve">4.74351692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487897872925</t>
+    <t xml:space="preserve">4.76703882217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487945556641</t>
   </si>
   <si>
     <t xml:space="preserve">4.73567628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68863248825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80624103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.010094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99441337585449</t>
+    <t xml:space="preserve">4.68863296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80624151229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01009511947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99441385269165</t>
   </si>
   <si>
     <t xml:space="preserve">4.9473705291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86112499237061</t>
+    <t xml:space="preserve">4.86112451553345</t>
   </si>
   <si>
     <t xml:space="preserve">4.84544372558594</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">4.93952941894531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04929733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68437957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59813404083252</t>
+    <t xml:space="preserve">5.04929780960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59813356399536</t>
   </si>
   <si>
     <t xml:space="preserve">5.6294960975647</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">5.7157416343689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69222068786621</t>
+    <t xml:space="preserve">5.69222021102905</t>
   </si>
   <si>
     <t xml:space="preserve">5.66869878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66085767745972</t>
+    <t xml:space="preserve">5.66085863113403</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358226776123</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">5.78630685806274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08424663543701</t>
+    <t xml:space="preserve">6.08424711227417</t>
   </si>
   <si>
     <t xml:space="preserve">6.17833280563354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14697122573853</t>
+    <t xml:space="preserve">6.14697074890137</t>
   </si>
   <si>
     <t xml:space="preserve">6.05288410186768</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">6.03720283508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15080690383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00474548339844</t>
+    <t xml:space="preserve">6.15080642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00474500656128</t>
   </si>
   <si>
     <t xml:space="preserve">6.11834859848022</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">6.45915842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42670059204102</t>
+    <t xml:space="preserve">6.42670011520386</t>
   </si>
   <si>
     <t xml:space="preserve">6.26440954208374</t>
@@ -2729,19 +2729,19 @@
     <t xml:space="preserve">6.41047048568726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39424180984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44292974472046</t>
+    <t xml:space="preserve">6.39424228668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4429292678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.96225833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14077854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43290042877197</t>
+    <t xml:space="preserve">7.14077806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43289995193481</t>
   </si>
   <si>
     <t xml:space="preserve">8.00091743469238</t>
@@ -2750,37 +2750,37 @@
     <t xml:space="preserve">7.83862686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87108373641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78994035720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977310180664</t>
+    <t xml:space="preserve">7.87108421325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78993988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977262496948</t>
   </si>
   <si>
     <t xml:space="preserve">7.95222997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90354347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60139274597168</t>
+    <t xml:space="preserve">7.90354299545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60139179229736</t>
   </si>
   <si>
     <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56081962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43910217285156</t>
+    <t xml:space="preserve">8.56081867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43910026550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.19566631317139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23623657226562</t>
+    <t xml:space="preserve">8.23623752593994</t>
   </si>
   <si>
     <t xml:space="preserve">8.01714611053467</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">8.06583213806152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96845960617065</t>
+    <t xml:space="preserve">7.96845865249634</t>
   </si>
   <si>
     <t xml:space="preserve">7.40044260025024</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">7.25438070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48158836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64387845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56273317337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69256448745728</t>
+    <t xml:space="preserve">7.4815878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6438775062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5627326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69256496429443</t>
   </si>
   <si>
     <t xml:space="preserve">7.72502326965332</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62764835357666</t>
+    <t xml:space="preserve">7.6276478767395</t>
   </si>
   <si>
     <t xml:space="preserve">7.46535778045654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3030686378479</t>
+    <t xml:space="preserve">7.30306911468506</t>
   </si>
   <si>
     <t xml:space="preserve">7.22192335128784</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">7.3842134475708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70879411697388</t>
+    <t xml:space="preserve">7.70879459381104</t>
   </si>
   <si>
     <t xml:space="preserve">7.61142015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66010665893555</t>
+    <t xml:space="preserve">7.66010713577271</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">7.74125289916992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3579568862915</t>
+    <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
     <t xml:space="preserve">8.1550931930542</t>
@@ -2864,34 +2864,34 @@
     <t xml:space="preserve">8.96654605865479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84482765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368236541748</t>
+    <t xml:space="preserve">8.84482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368141174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.52024745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39852809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47967338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3173828125</t>
+    <t xml:space="preserve">8.39852905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47967433929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31738376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.08206367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11452102661133</t>
+    <t xml:space="preserve">8.11452007293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.03337574005127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04960346221924</t>
+    <t xml:space="preserve">8.04960536956787</t>
   </si>
   <si>
     <t xml:space="preserve">9.04768943786621</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4034481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23627662658691</t>
+    <t xml:space="preserve">9.40344905853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23627758026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.48703575134277</t>
@@ -2924,34 +2924,34 @@
     <t xml:space="preserve">9.57062149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52882862091064</t>
+    <t xml:space="preserve">9.52882766723633</t>
   </si>
   <si>
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779392242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420818328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90496730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31986331939697</t>
+    <t xml:space="preserve">9.73779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90496635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31986236572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02731037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15269088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013889312744</t>
+    <t xml:space="preserve">9.02731132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15268993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.7765531539917</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">8.35862159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60937976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19448280334473</t>
+    <t xml:space="preserve">8.6093807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19448375701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11089706420898</t>
+    <t xml:space="preserve">9.11089611053467</t>
   </si>
   <si>
     <t xml:space="preserve">9.36165618896484</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">9.06910514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9437255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90193176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81834506988525</t>
+    <t xml:space="preserve">8.94372463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.901930809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81834602355957</t>
   </si>
   <si>
     <t xml:space="preserve">8.56758785247803</t>
@@ -2993,34 +2993,34 @@
     <t xml:space="preserve">8.52579307556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73475933074951</t>
+    <t xml:space="preserve">8.7347583770752</t>
   </si>
   <si>
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846977233887</t>
+    <t xml:space="preserve">8.30846881866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.32518768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65649700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82366943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154579162598</t>
+    <t xml:space="preserve">7.65649747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82366991043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321443557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154626846313</t>
   </si>
   <si>
     <t xml:space="preserve">7.07139444351196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10482835769653</t>
+    <t xml:space="preserve">7.10482788085938</t>
   </si>
   <si>
     <t xml:space="preserve">7.68993234634399</t>
@@ -3029,19 +3029,19 @@
     <t xml:space="preserve">7.45589065551758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89053773880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80695295333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62306308746338</t>
+    <t xml:space="preserve">7.89053869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80695247650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62306261062622</t>
   </si>
   <si>
     <t xml:space="preserve">7.99084186553955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09114646911621</t>
+    <t xml:space="preserve">8.09114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.04099369049072</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">8.30011177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35026264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24995994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87382221221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69828987121582</t>
+    <t xml:space="preserve">8.35026359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24996089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8738226890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69829034805298</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
@@ -3080,37 +3080,37 @@
     <t xml:space="preserve">7.81531190872192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77351808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91561508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7818775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60634613037109</t>
+    <t xml:space="preserve">7.77351856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91561412811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78187656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60634660720825</t>
   </si>
   <si>
     <t xml:space="preserve">7.89889764785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79859352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023456573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978004455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41302871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64850187301636</t>
+    <t xml:space="preserve">7.79859447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978052139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41302824020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64850234985352</t>
   </si>
   <si>
     <t xml:space="preserve">8.24154376983643</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">8.28514957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32003498077393</t>
+    <t xml:space="preserve">8.32003402709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">8.19793701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49445915222168</t>
+    <t xml:space="preserve">8.49445819854736</t>
   </si>
   <si>
     <t xml:space="preserve">8.69504642486572</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678726196289</t>
+    <t xml:space="preserve">8.54678630828857</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">8.17177391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12816715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93630170822144</t>
+    <t xml:space="preserve">8.1281681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93630218505859</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">7.71827077865601</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77931976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95374393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14561080932617</t>
+    <t xml:space="preserve">7.77931928634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95374345779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14560985565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
@@ -3194,40 +3194,40 @@
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804111480713</t>
+    <t xml:space="preserve">7.78804063796997</t>
   </si>
   <si>
     <t xml:space="preserve">7.65722274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76187658309937</t>
+    <t xml:space="preserve">7.76187705993652</t>
   </si>
   <si>
     <t xml:space="preserve">7.6921067237854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70082855224609</t>
+    <t xml:space="preserve">7.70082807540894</t>
   </si>
   <si>
     <t xml:space="preserve">7.5961742401123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46535634994507</t>
+    <t xml:space="preserve">7.46535587310791</t>
   </si>
   <si>
     <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50024127960205</t>
+    <t xml:space="preserve">7.73571395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50024080276489</t>
   </si>
   <si>
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256795883179</t>
+    <t xml:space="preserve">7.55256748199463</t>
   </si>
   <si>
     <t xml:space="preserve">7.447913646698</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">8.61655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77353763580322</t>
+    <t xml:space="preserve">8.77353858947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.72121047973633</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596698760986</t>
+    <t xml:space="preserve">8.41596794128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.34619808197021</t>
@@ -3281,22 +3281,22 @@
     <t xml:space="preserve">8.37236213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89269542694092</t>
+    <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
     <t xml:space="preserve">7.83164644241333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66594314575195</t>
+    <t xml:space="preserve">7.66594362258911</t>
   </si>
   <si>
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97118616104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68338632583618</t>
+    <t xml:space="preserve">7.9711856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338680267334</t>
   </si>
   <si>
     <t xml:space="preserve">7.33453750610352</t>
@@ -3314,10 +3314,10 @@
     <t xml:space="preserve">7.28221082687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13395023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12522888183594</t>
+    <t xml:space="preserve">7.13395071029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12522840499878</t>
   </si>
   <si>
     <t xml:space="preserve">6.78510189056396</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63684129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87231349945068</t>
+    <t xml:space="preserve">6.6368408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
     <t xml:space="preserve">7.75315618515015</t>
@@ -3344,22 +3344,22 @@
     <t xml:space="preserve">7.43047142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49151992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27348947525024</t>
+    <t xml:space="preserve">7.49152040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2734899520874</t>
   </si>
   <si>
     <t xml:space="preserve">7.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38686513900757</t>
+    <t xml:space="preserve">7.38686466217041</t>
   </si>
   <si>
     <t xml:space="preserve">7.3519811630249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31709575653076</t>
+    <t xml:space="preserve">7.31709623336792</t>
   </si>
   <si>
     <t xml:space="preserve">7.47407674789429</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">7.32581663131714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30837392807007</t>
+    <t xml:space="preserve">7.30837440490723</t>
   </si>
   <si>
     <t xml:space="preserve">7.42175006866455</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98862838745117</t>
+    <t xml:space="preserve">7.97990751266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.90141725540161</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885852813721</t>
+    <t xml:space="preserve">7.91885900497437</t>
   </si>
   <si>
     <t xml:space="preserve">7.82292652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11944770812988</t>
+    <t xml:space="preserve">8.11944675445557</t>
   </si>
   <si>
     <t xml:space="preserve">8.2589864730835</t>
@@ -3443,16 +3443,16 @@
     <t xml:space="preserve">8.27642822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52934265136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94796085357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87819194793701</t>
+    <t xml:space="preserve">8.337477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5293436050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94796180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87819290161133</t>
   </si>
   <si>
     <t xml:space="preserve">8.89563369750977</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">8.79098033905029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70376682281494</t>
+    <t xml:space="preserve">8.70376777648926</t>
   </si>
   <si>
     <t xml:space="preserve">8.71248912811279</t>
@@ -3479,19 +3479,19 @@
     <t xml:space="preserve">8.93051910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62527656555176</t>
+    <t xml:space="preserve">8.62527751922607</t>
   </si>
   <si>
     <t xml:space="preserve">8.56422805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46829605102539</t>
+    <t xml:space="preserve">8.46829509735107</t>
   </si>
   <si>
     <t xml:space="preserve">8.6863260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15727138519287</t>
+    <t xml:space="preserve">9.15727043151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -69414,7 +69414,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6496064815</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>25397</v>
@@ -69435,6 +69435,32 @@
         <v>1418</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6494907407</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>9638</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>12.5500001907349</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355509757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546637058258</t>
+    <t xml:space="preserve">1.21355497837067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546625137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.20654845237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23177254199982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24998962879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26330232620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27311182022095</t>
+    <t xml:space="preserve">1.23177242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2499897480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26330256462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27311170101166</t>
   </si>
   <si>
     <t xml:space="preserve">1.26120042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24718713760376</t>
+    <t xml:space="preserve">1.24718701839447</t>
   </si>
   <si>
     <t xml:space="preserve">1.20794975757599</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">1.19323575496674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501854896545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814050197601</t>
+    <t xml:space="preserve">1.17501842975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19814038276672</t>
   </si>
   <si>
     <t xml:space="preserve">1.2457857131958</t>
@@ -89,58 +89,58 @@
     <t xml:space="preserve">1.23457515239716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18272566795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17992317676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641961574554</t>
+    <t xml:space="preserve">1.21495640277863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18272578716278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17992305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641985416412</t>
   </si>
   <si>
     <t xml:space="preserve">1.12457036972046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12807369232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10284984111786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08603370189667</t>
+    <t xml:space="preserve">1.12807381153107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10284972190857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08603358268738</t>
   </si>
   <si>
     <t xml:space="preserve">1.01596701145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507567405701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02017092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297365665436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04329299926758</t>
+    <t xml:space="preserve">1.0250757932663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02017104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195372104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297389507294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04329311847687</t>
   </si>
   <si>
     <t xml:space="preserve">1.09654378890991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11335980892181</t>
+    <t xml:space="preserve">1.11335968971252</t>
   </si>
   <si>
     <t xml:space="preserve">1.1105569601059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0930403470993</t>
+    <t xml:space="preserve">1.09304022789001</t>
   </si>
   <si>
     <t xml:space="preserve">1.12106704711914</t>
@@ -149,58 +149,58 @@
     <t xml:space="preserve">1.13017582893372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15610039234161</t>
+    <t xml:space="preserve">1.1561005115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.10004711151123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13157713413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705363750458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227772712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11826455593109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1490935087204</t>
+    <t xml:space="preserve">1.1315770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227784633636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11826431751251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14909374713898</t>
   </si>
   <si>
     <t xml:space="preserve">1.17852175235748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1701135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412721157074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081451416016</t>
+    <t xml:space="preserve">1.17011368274689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412709236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081427574158</t>
   </si>
   <si>
     <t xml:space="preserve">1.16310715675354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22616708278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508512020111</t>
+    <t xml:space="preserve">1.22616696357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508500099182</t>
   </si>
   <si>
     <t xml:space="preserve">1.2408812046051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20514714717865</t>
+    <t xml:space="preserve">1.20514702796936</t>
   </si>
   <si>
     <t xml:space="preserve">1.19113373756409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22686767578125</t>
+    <t xml:space="preserve">1.22686791419983</t>
   </si>
   <si>
     <t xml:space="preserve">1.22196304798126</t>
@@ -209,40 +209,40 @@
     <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17221570014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183456897736</t>
+    <t xml:space="preserve">1.17221581935883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183444976807</t>
   </si>
   <si>
     <t xml:space="preserve">1.19743967056274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20374584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.203045129776</t>
+    <t xml:space="preserve">1.20374572277069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20304501056671</t>
   </si>
   <si>
     <t xml:space="preserve">1.23807835578918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23317360877991</t>
+    <t xml:space="preserve">1.23317384719849</t>
   </si>
   <si>
     <t xml:space="preserve">1.19954168796539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2247656583786</t>
+    <t xml:space="preserve">1.22476589679718</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845972537994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21916043758392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896957397461</t>
+    <t xml:space="preserve">1.21916031837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22896981239319</t>
   </si>
   <si>
     <t xml:space="preserve">1.21215379238129</t>
@@ -260,28 +260,28 @@
     <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28712511062622</t>
+    <t xml:space="preserve">1.28712499141693</t>
   </si>
   <si>
     <t xml:space="preserve">1.28151965141296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24788784980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737776279449</t>
+    <t xml:space="preserve">1.24788773059845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737788200378</t>
   </si>
   <si>
     <t xml:space="preserve">1.20865046977997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15469920635223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138638973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11896514892578</t>
+    <t xml:space="preserve">1.15469908714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138627052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1189649105072</t>
   </si>
   <si>
     <t xml:space="preserve">1.12036645412445</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">1.13648176193237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14629125595093</t>
+    <t xml:space="preserve">1.14629113674164</t>
   </si>
   <si>
     <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0720202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084632396698</t>
+    <t xml:space="preserve">1.07202041149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08463227748871</t>
   </si>
   <si>
     <t xml:space="preserve">1.06501364707947</t>
@@ -308,19 +308,19 @@
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253026008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05800724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10144853591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355031490326</t>
+    <t xml:space="preserve">1.08253037929535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902693748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05800700187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10144829750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355043411255</t>
   </si>
   <si>
     <t xml:space="preserve">1.09514248371124</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">1.11966574192047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09934651851654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11265921592712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15680122375488</t>
+    <t xml:space="preserve">1.09934639930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11265897750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15680110454559</t>
   </si>
   <si>
     <t xml:space="preserve">1.34528040885925</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">1.48821651935577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45178186893463</t>
+    <t xml:space="preserve">1.45178174972534</t>
   </si>
   <si>
     <t xml:space="preserve">1.4153470993042</t>
@@ -356,28 +356,28 @@
     <t xml:space="preserve">1.45738708972931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40133380889893</t>
+    <t xml:space="preserve">1.40133392810822</t>
   </si>
   <si>
     <t xml:space="preserve">1.46999931335449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43776834011078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375528812408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43636703491211</t>
+    <t xml:space="preserve">1.43776845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375516891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4363671541214</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936050891876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41674852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42235386371613</t>
+    <t xml:space="preserve">1.41674864292145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42235374450684</t>
   </si>
   <si>
     <t xml:space="preserve">1.41814982891083</t>
@@ -389,103 +389,103 @@
     <t xml:space="preserve">1.42795932292938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48120975494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69421243667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338336467743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071401596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84555673599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7923059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268731594086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064720630646</t>
+    <t xml:space="preserve">1.48120999336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6942126750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8007138967514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84555661678314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79230558872223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090440273285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268707752228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064708709717</t>
   </si>
   <si>
     <t xml:space="preserve">1.71663403511047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670072555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84275412559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313549518585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8399510383606</t>
+    <t xml:space="preserve">1.78670048713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8427540063858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593786716461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995139598846</t>
   </si>
   <si>
     <t xml:space="preserve">1.83854973316193</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84415531158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83014178276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874071598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192469596863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294463157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835886955261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8693790435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99549949169159</t>
+    <t xml:space="preserve">1.84415543079376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014214038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472718715668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874035835266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192445755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294451236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835922718048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937928199768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549901485443</t>
   </si>
   <si>
     <t xml:space="preserve">2.07257270812988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02913117408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798718452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04034185409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830222129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03053283691406</t>
+    <t xml:space="preserve">2.02913165092468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798766136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04034209251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830234050751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03053307533264</t>
   </si>
   <si>
     <t xml:space="preserve">2.01932215690613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99970328807831</t>
+    <t xml:space="preserve">1.9997034072876</t>
   </si>
   <si>
     <t xml:space="preserve">2.01231551170349</t>
@@ -494,127 +494,127 @@
     <t xml:space="preserve">2.09359264373779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066645622253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15945506095886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989415168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339269161224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167646884918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345938205719</t>
+    <t xml:space="preserve">2.17066550254822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15945529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989403247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339257240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167670726776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345914363861</t>
   </si>
   <si>
     <t xml:space="preserve">2.01651930809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97868311405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944561481476</t>
+    <t xml:space="preserve">2.00250601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428893089294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9786833524704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944585323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.91982746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377418041229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8679780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918889522552</t>
+    <t xml:space="preserve">1.86377394199371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86797797679901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918865680695</t>
   </si>
   <si>
     <t xml:space="preserve">1.85676729679108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78950321674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631911754608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301120281219</t>
+    <t xml:space="preserve">1.78950297832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631947517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301108360291</t>
   </si>
   <si>
     <t xml:space="preserve">1.89880728721619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91001772880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690055847168</t>
+    <t xml:space="preserve">1.91001796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690067768097</t>
   </si>
   <si>
     <t xml:space="preserve">1.98849284648895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98568999767303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224858283997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766317844391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9618673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326851844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97027564048767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00390720367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18888306617737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16506052017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13282990455627</t>
+    <t xml:space="preserve">1.98569011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224882125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766305923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186721324921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326887607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027552127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607160568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0039074420929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397389411926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18888354301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1650607585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13283014297485</t>
   </si>
   <si>
     <t xml:space="preserve">2.06416487693787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09639525413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499382972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1132116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14404058456421</t>
+    <t xml:space="preserve">2.09639549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601400375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11321115493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14404082298279</t>
   </si>
   <si>
     <t xml:space="preserve">2.13002729415894</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">2.11181020736694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09779644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.118816614151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10200071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741542816162</t>
+    <t xml:space="preserve">2.09779691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11881637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10200095176697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11741518974304</t>
   </si>
   <si>
     <t xml:space="preserve">2.24213409423828</t>
@@ -656,28 +656,28 @@
     <t xml:space="preserve">2.48876881599426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4873673915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316359519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46494603157043</t>
+    <t xml:space="preserve">2.48736763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316383361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46494626998901</t>
   </si>
   <si>
     <t xml:space="preserve">2.40328741073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099895477295</t>
+    <t xml:space="preserve">2.52099943161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.48036098480225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46634721755981</t>
+    <t xml:space="preserve">2.46634769439697</t>
   </si>
   <si>
     <t xml:space="preserve">2.44392609596252</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">2.47615671157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45513653755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437427520752</t>
+    <t xml:space="preserve">2.45513677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437403678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.47335457801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65552735328674</t>
+    <t xml:space="preserve">2.65552759170532</t>
   </si>
   <si>
     <t xml:space="preserve">2.71858763694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7045738697052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751057624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865456581116</t>
+    <t xml:space="preserve">2.70457434654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.788654088974</t>
   </si>
   <si>
     <t xml:space="preserve">3.11096119880676</t>
@@ -722,37 +722,37 @@
     <t xml:space="preserve">3.38422083854675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46129441261292</t>
+    <t xml:space="preserve">3.46129417419434</t>
   </si>
   <si>
     <t xml:space="preserve">3.71003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58040809631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6609845161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7836012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176100730896</t>
+    <t xml:space="preserve">3.5804078578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66098499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601798057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78360176086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9517617225647</t>
   </si>
   <si>
     <t xml:space="preserve">4.06386804580688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16896820068359</t>
+    <t xml:space="preserve">4.19349193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16896867752075</t>
   </si>
   <si>
     <t xml:space="preserve">4.11291456222534</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">4.03233814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30910158157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30559825897217</t>
+    <t xml:space="preserve">4.30910110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30559873580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.55433464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69797134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50023508071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256200790405</t>
+    <t xml:space="preserve">4.6979718208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50023555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256153106689</t>
   </si>
   <si>
     <t xml:space="preserve">5.10085535049438</t>
@@ -788,85 +788,85 @@
     <t xml:space="preserve">5.44768524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44418144226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7734956741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143550872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518203735352</t>
+    <t xml:space="preserve">5.44418239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77349519729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39708852767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143598556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518251419067</t>
   </si>
   <si>
     <t xml:space="preserve">6.71238946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09369373321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78433418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3562650680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53252840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35266780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07208585739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32389116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094627380371</t>
+    <t xml:space="preserve">7.09369230270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7843337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626649856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5325288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35266828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0720853805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.323890209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900156021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094436645508</t>
   </si>
   <si>
     <t xml:space="preserve">6.40302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15842008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37425088882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47137641906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32748746871948</t>
+    <t xml:space="preserve">6.15841913223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798898696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37425136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47137689590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32748889923096</t>
   </si>
   <si>
     <t xml:space="preserve">6.15122509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11165523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93898916244507</t>
+    <t xml:space="preserve">6.11165571212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">5.96057271957397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85265684127808</t>
+    <t xml:space="preserve">5.85265636444092</t>
   </si>
   <si>
     <t xml:space="preserve">5.90661478042603</t>
@@ -881,64 +881,64 @@
     <t xml:space="preserve">5.6943793296814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70157432556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36703300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87421655654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17997789382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97853565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96414709091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8454384803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87781286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9101881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92457723617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69075870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65838432312012</t>
+    <t xml:space="preserve">5.70157384872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3670334815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87421607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1799783706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97853517532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96414661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84543895721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87781381607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155096054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92457675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76989698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.690758228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65838384628296</t>
   </si>
   <si>
     <t xml:space="preserve">4.68716144561768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82385540008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5504674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51089811325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49291181564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4389533996582</t>
+    <t xml:space="preserve">4.82385492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55046701431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51089763641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49291229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43895387649536</t>
   </si>
   <si>
     <t xml:space="preserve">4.38139867782593</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">4.38499641418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46413421630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0360894203186</t>
+    <t xml:space="preserve">4.46413469314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03609037399292</t>
   </si>
   <si>
     <t xml:space="preserve">4.85623025894165</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">4.76630020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68356418609619</t>
+    <t xml:space="preserve">4.68356466293335</t>
   </si>
   <si>
     <t xml:space="preserve">4.67636966705322</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">4.60442543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59003686904907</t>
+    <t xml:space="preserve">4.59003639221191</t>
   </si>
   <si>
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198110580444</t>
+    <t xml:space="preserve">4.66198062896729</t>
   </si>
   <si>
     <t xml:space="preserve">4.67277240753174</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">4.74831390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75910472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9533543586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486749649048</t>
+    <t xml:space="preserve">4.75910568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486845016479</t>
   </si>
   <si>
     <t xml:space="preserve">5.14400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11522960662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1943678855896</t>
+    <t xml:space="preserve">5.11522912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19436740875244</t>
   </si>
   <si>
     <t xml:space="preserve">5.10803461074829</t>
@@ -1022,55 +1022,55 @@
     <t xml:space="preserve">4.90659093856812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92098045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82025766372681</t>
+    <t xml:space="preserve">4.92097997665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82025814056396</t>
   </si>
   <si>
     <t xml:space="preserve">4.89220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05407667160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01810455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95695209503174</t>
+    <t xml:space="preserve">5.05407619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0181040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.94616031646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15839576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23393678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60804653167725</t>
+    <t xml:space="preserve">5.15839529037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23393726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60804605484009</t>
   </si>
   <si>
     <t xml:space="preserve">5.89942026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77711534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611373901367</t>
+    <t xml:space="preserve">5.7771143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611421585083</t>
   </si>
   <si>
     <t xml:space="preserve">5.94978141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18000268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20878028869629</t>
+    <t xml:space="preserve">6.18000221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20877933502197</t>
   </si>
   <si>
     <t xml:space="preserve">6.52533388137817</t>
@@ -1085,19 +1085,19 @@
     <t xml:space="preserve">7.11527681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13685894012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802379608154</t>
+    <t xml:space="preserve">7.13685846328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802331924438</t>
   </si>
   <si>
     <t xml:space="preserve">8.12968921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43904781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704746246338</t>
+    <t xml:space="preserve">8.43904685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.29518413543701</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">8.61890983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22321605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01457977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80594062805176</t>
+    <t xml:space="preserve">8.22321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0145788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80594158172607</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299383163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10091018676758</t>
+    <t xml:space="preserve">7.99299478530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10091209411621</t>
   </si>
   <si>
     <t xml:space="preserve">7.98580026626587</t>
@@ -1136,49 +1136,49 @@
     <t xml:space="preserve">7.8850793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73399591445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41024780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54694128036499</t>
+    <t xml:space="preserve">7.73399543762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41024732589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54694080352783</t>
   </si>
   <si>
     <t xml:space="preserve">7.47499752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45341396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535820007324</t>
+    <t xml:space="preserve">7.45341300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535676956177</t>
   </si>
   <si>
     <t xml:space="preserve">7.38866472244263</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23760509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84191226959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702409744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04335689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824602127075</t>
+    <t xml:space="preserve">8.23760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84191274642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910726547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04335594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824697494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.85630178451538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74838542938232</t>
+    <t xml:space="preserve">7.74838638305664</t>
   </si>
   <si>
     <t xml:space="preserve">7.57571840286255</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">6.96419429779053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21599721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498655319214</t>
+    <t xml:space="preserve">7.21599864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498464584351</t>
   </si>
   <si>
     <t xml:space="preserve">7.2088041305542</t>
@@ -1211,61 +1211,61 @@
     <t xml:space="preserve">7.65485763549805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2519702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448551177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00736045837402</t>
+    <t xml:space="preserve">7.25197076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722105026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00735998153687</t>
   </si>
   <si>
     <t xml:space="preserve">6.89944362640381</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9534010887146</t>
+    <t xml:space="preserve">6.95340204238892</t>
   </si>
   <si>
     <t xml:space="preserve">7.15844297409058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91742992401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.856276512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.892249584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78793096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95699882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98217964172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16204071044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045715332031</t>
+    <t xml:space="preserve">6.91742897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85627698898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89225006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78793048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95699977874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217916488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16204023361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045763015747</t>
   </si>
   <si>
     <t xml:space="preserve">7.02174949645996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.338303565979</t>
+    <t xml:space="preserve">7.33830261230469</t>
   </si>
   <si>
     <t xml:space="preserve">7.82752323150635</t>
@@ -1280,97 +1280,97 @@
     <t xml:space="preserve">7.9138560295105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8994665145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313467025757</t>
+    <t xml:space="preserve">7.89946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313323974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.66924571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76996803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435707092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48219156265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79152774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836015701294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850147247314</t>
+    <t xml:space="preserve">7.76996850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48219060897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79152727127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850099563599</t>
   </si>
   <si>
     <t xml:space="preserve">6.6404447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325119018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62605667114258</t>
+    <t xml:space="preserve">6.48936319351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605619430542</t>
   </si>
   <si>
     <t xml:space="preserve">6.56130647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60447359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411195755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791904449463</t>
+    <t xml:space="preserve">6.60447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791809082031</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02172517776489</t>
+    <t xml:space="preserve">6.02172565460205</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25914096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619560241699</t>
+    <t xml:space="preserve">5.86344766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2591404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633596420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.46777820587158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67641687393188</t>
+    <t xml:space="preserve">6.67641735076904</t>
   </si>
   <si>
     <t xml:space="preserve">6.51814031600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46058368682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2951135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10086297988892</t>
+    <t xml:space="preserve">6.46058464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29511213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10086393356323</t>
   </si>
   <si>
     <t xml:space="preserve">6.1368350982666</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">5.93539237976074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89222574234009</t>
+    <t xml:space="preserve">5.89222526550293</t>
   </si>
   <si>
     <t xml:space="preserve">5.79869890213013</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99294805526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17280769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1871976852417</t>
+    <t xml:space="preserve">5.99294757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17280721664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18719625473022</t>
   </si>
   <si>
     <t xml:space="preserve">6.25194644927979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22316837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12244749069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27353048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950164794922</t>
+    <t xml:space="preserve">6.22316789627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12244701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27352952957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950212478638</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230760574341</t>
@@ -1424,25 +1424,25 @@
     <t xml:space="preserve">6.33828020095825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58551740646362</t>
+    <t xml:space="preserve">6.58551692962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.38323211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46564435958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326242446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3083119392395</t>
+    <t xml:space="preserve">6.46564388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326385498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30831098556519</t>
   </si>
   <si>
     <t xml:space="preserve">6.59300994873047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41320085525513</t>
+    <t xml:space="preserve">6.41319990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.17345428466797</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">5.90374040603638</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95618438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9411997795105</t>
+    <t xml:space="preserve">5.95618391036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94120025634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.86628007888794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9486927986145</t>
+    <t xml:space="preserve">5.94869232177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.84380388259888</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">5.59656524658203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48418521881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60405826568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55910587310791</t>
+    <t xml:space="preserve">5.48418474197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60405731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55910539627075</t>
   </si>
   <si>
     <t xml:space="preserve">5.888756275177</t>
@@ -1487,34 +1487,34 @@
     <t xml:space="preserve">5.80634355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64151811599731</t>
+    <t xml:space="preserve">5.64151859283447</t>
   </si>
   <si>
     <t xml:space="preserve">5.79135942459106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76139163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88126468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621660232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078718185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55554866790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815181732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33827972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30081939697266</t>
+    <t xml:space="preserve">5.76139116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88126420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621612548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078765869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55554819107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815229415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33827924728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3008189201355</t>
   </si>
   <si>
     <t xml:space="preserve">6.12850189208984</t>
@@ -1523,22 +1523,22 @@
     <t xml:space="preserve">6.06107330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77637529373169</t>
+    <t xml:space="preserve">5.77637577056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.768883228302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70145463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66399478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57409000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75389862060547</t>
+    <t xml:space="preserve">5.70145416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57408952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75389909744263</t>
   </si>
   <si>
     <t xml:space="preserve">5.78386735916138</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">5.54412174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58158159255981</t>
+    <t xml:space="preserve">5.58158111572266</t>
   </si>
   <si>
     <t xml:space="preserve">5.50666093826294</t>
@@ -1568,46 +1568,46 @@
     <t xml:space="preserve">5.53662919998169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43174028396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46920156478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31935930252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28189945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49167728424072</t>
+    <t xml:space="preserve">5.43174076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4692006111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31935977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28189992904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49167633056641</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415300369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36431217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27440738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20697927474976</t>
+    <t xml:space="preserve">5.36431169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27440786361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450307846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2069787979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.5890736579895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74640655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47669267654419</t>
+    <t xml:space="preserve">5.74640703201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47669315338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.21447086334229</t>
@@ -1616,28 +1616,28 @@
     <t xml:space="preserve">5.13955020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0945987701416</t>
+    <t xml:space="preserve">5.09459829330444</t>
   </si>
   <si>
     <t xml:space="preserve">5.10958242416382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07212162017822</t>
+    <t xml:space="preserve">5.07212209701538</t>
   </si>
   <si>
     <t xml:space="preserve">5.05713796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01967716217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732839584351</t>
+    <t xml:space="preserve">5.01967763900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466176986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732887268066</t>
   </si>
   <si>
     <t xml:space="preserve">4.86983633041382</t>
@@ -1646,28 +1646,28 @@
     <t xml:space="preserve">4.7349796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77243995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82488393783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88482093811035</t>
+    <t xml:space="preserve">4.77243947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82488441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
     <t xml:space="preserve">4.75745534896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86234426498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478872299194</t>
+    <t xml:space="preserve">4.86234378814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9147891998291</t>
   </si>
   <si>
     <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8548526763916</t>
+    <t xml:space="preserve">4.85485219955444</t>
   </si>
   <si>
     <t xml:space="preserve">4.95224905014038</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">5.13205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21840620040894</t>
+    <t xml:space="preserve">6.21840667724609</t>
   </si>
   <si>
     <t xml:space="preserve">6.25586700439453</t>
@@ -1694,52 +1694,52 @@
     <t xml:space="preserve">6.10602521896362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99364471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04215335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94475650787354</t>
+    <t xml:space="preserve">5.99364519119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04215383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94475698471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.99720144271851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0271692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8923134803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964590072632</t>
+    <t xml:space="preserve">5.02716970443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89231300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964542388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95974111557007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81739187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7949161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78742408752441</t>
+    <t xml:space="preserve">4.81739139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79491567611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7874231338501</t>
   </si>
   <si>
     <t xml:space="preserve">4.83237600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97472476959229</t>
+    <t xml:space="preserve">4.97472524642944</t>
   </si>
   <si>
     <t xml:space="preserve">4.90729665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76494789123535</t>
+    <t xml:space="preserve">4.76494741439819</t>
   </si>
   <si>
     <t xml:space="preserve">4.4727578163147</t>
@@ -1751,49 +1751,49 @@
     <t xml:space="preserve">4.38285303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32291603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30043935775757</t>
+    <t xml:space="preserve">4.32291650772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30043983459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.31542444229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46526527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777320861816</t>
+    <t xml:space="preserve">4.46526575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777368545532</t>
   </si>
   <si>
     <t xml:space="preserve">4.71250295639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10208988189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07961416244507</t>
+    <t xml:space="preserve">5.10209035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07961463928223</t>
   </si>
   <si>
     <t xml:space="preserve">4.93726539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01218605041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443960189819</t>
+    <t xml:space="preserve">5.01218557357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443912506104</t>
   </si>
   <si>
     <t xml:space="preserve">5.22196292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25942325592041</t>
+    <t xml:space="preserve">5.25942277908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.19948720932007</t>
@@ -1802,22 +1802,22 @@
     <t xml:space="preserve">5.11707401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28939151763916</t>
+    <t xml:space="preserve">5.28939199447632</t>
   </si>
   <si>
     <t xml:space="preserve">5.16202640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31186771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41675662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180471420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4467248916626</t>
+    <t xml:space="preserve">5.31186819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41675615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44672441482544</t>
   </si>
   <si>
     <t xml:space="preserve">5.39427995681763</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">5.45421695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40926456451416</t>
+    <t xml:space="preserve">5.409264087677</t>
   </si>
   <si>
     <t xml:space="preserve">5.89624834060669</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">6.12100982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22589874267578</t>
+    <t xml:space="preserve">6.22589921951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.81383562088013</t>
@@ -1850,70 +1850,70 @@
     <t xml:space="preserve">5.79885149002075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82132768630981</t>
+    <t xml:space="preserve">5.82132816314697</t>
   </si>
   <si>
     <t xml:space="preserve">5.91123199462891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03110504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00862884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872406005859</t>
+    <t xml:space="preserve">6.03110551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00862979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872453689575</t>
   </si>
   <si>
     <t xml:space="preserve">5.83631134033203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87377214431763</t>
+    <t xml:space="preserve">5.87377262115479</t>
   </si>
   <si>
     <t xml:space="preserve">5.97116851806641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21091461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09104204177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097761154175</t>
+    <t xml:space="preserve">6.21091413497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09104156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097808837891</t>
   </si>
   <si>
     <t xml:space="preserve">6.14348602294922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04608917236328</t>
+    <t xml:space="preserve">6.04608869552612</t>
   </si>
   <si>
     <t xml:space="preserve">6.02361297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03859710693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396257400513</t>
+    <t xml:space="preserve">6.03859758377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396209716797</t>
   </si>
   <si>
     <t xml:space="preserve">5.72393083572388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7089467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170902252197</t>
+    <t xml:space="preserve">5.70894622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916887283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170854568481</t>
   </si>
   <si>
     <t xml:space="preserve">5.73891496658325</t>
@@ -1922,25 +1922,25 @@
     <t xml:space="preserve">5.55161333084106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47268533706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33155584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484518051147</t>
+    <t xml:space="preserve">5.47268581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33155632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484470367432</t>
   </si>
   <si>
     <t xml:space="preserve">5.35507774353027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30803394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859916687012</t>
+    <t xml:space="preserve">5.30803489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859964370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.39428043365479</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">5.26883172988892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28451299667358</t>
+    <t xml:space="preserve">5.28451251983643</t>
   </si>
   <si>
     <t xml:space="preserve">5.25315141677856</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">5.14338302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06497764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00225448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690492630005</t>
+    <t xml:space="preserve">5.06497859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00225400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690540313721</t>
   </si>
   <si>
     <t xml:space="preserve">5.20610761642456</t>
@@ -1976,46 +1976,46 @@
     <t xml:space="preserve">5.33939695358276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11986207962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13554334640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09634017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11202192306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17474555969238</t>
+    <t xml:space="preserve">5.29235315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11986255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13554286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09634065628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11202144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17474508285522</t>
   </si>
   <si>
     <t xml:space="preserve">5.44916391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45700454711914</t>
+    <t xml:space="preserve">5.45700407028198</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381435394287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70790195465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67653942108154</t>
+    <t xml:space="preserve">5.70790147781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67653894424438</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733673095703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55893087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51188802719116</t>
+    <t xml:space="preserve">5.55893135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51188850402832</t>
   </si>
   <si>
     <t xml:space="preserve">5.48836660385132</t>
@@ -2033,70 +2033,70 @@
     <t xml:space="preserve">5.3237156867981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19826745986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79840040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70431423187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71999502182007</t>
+    <t xml:space="preserve">5.19826698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79840087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70431470870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71999454498291</t>
   </si>
   <si>
     <t xml:space="preserve">4.51614189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97089242935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82192230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6415901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71215486526489</t>
+    <t xml:space="preserve">4.97089195251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82192134857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64159059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71215438842773</t>
   </si>
   <si>
     <t xml:space="preserve">4.67295217514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63374900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64943027496338</t>
+    <t xml:space="preserve">4.63374948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64943075180054</t>
   </si>
   <si>
     <t xml:space="preserve">4.59454727172852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62590932846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68079233169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9003267288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2296290397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02577495574951</t>
+    <t xml:space="preserve">4.62590885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68079280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90032720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22962951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02577543258667</t>
   </si>
   <si>
     <t xml:space="preserve">5.04145622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15122413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21394920349121</t>
+    <t xml:space="preserve">5.1512246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22178888320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21394872665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.15906476974487</t>
@@ -2111,28 +2111,28 @@
     <t xml:space="preserve">5.01793527603149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07281923294067</t>
+    <t xml:space="preserve">5.07281875610352</t>
   </si>
   <si>
     <t xml:space="preserve">5.08849954605103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19042682647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18258571624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52756929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5197286605835</t>
+    <t xml:space="preserve">5.19042634963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18258619308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52756977081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51972913742065</t>
   </si>
   <si>
     <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56677150726318</t>
+    <t xml:space="preserve">5.56677198410034</t>
   </si>
   <si>
     <t xml:space="preserve">5.43348264694214</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">5.50404787063599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53540992736816</t>
+    <t xml:space="preserve">5.53541040420532</t>
   </si>
   <si>
     <t xml:space="preserve">5.41780233383179</t>
@@ -2153,49 +2153,49 @@
     <t xml:space="preserve">5.84118986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76278495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517688751221</t>
+    <t xml:space="preserve">5.76278448104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517641067505</t>
   </si>
   <si>
     <t xml:space="preserve">5.44132375717163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40996122360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38643932342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34723711013794</t>
+    <t xml:space="preserve">5.40996170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38643980026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3472375869751</t>
   </si>
   <si>
     <t xml:space="preserve">5.37075853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2374701499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97873258590698</t>
+    <t xml:space="preserve">5.23746967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97873210906982</t>
   </si>
   <si>
     <t xml:space="preserve">4.8376030921936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89248657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896562576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9238486289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87680578231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98657274246216</t>
+    <t xml:space="preserve">4.89248704910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92384910583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87680530548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
     <t xml:space="preserve">4.57102537155151</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">4.57886648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39069271087646</t>
+    <t xml:space="preserve">4.39069318771362</t>
   </si>
   <si>
     <t xml:space="preserve">4.15547752380371</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">4.2260422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11627531051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84185671806335</t>
+    <t xml:space="preserve">4.1162748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84185695648193</t>
   </si>
   <si>
     <t xml:space="preserve">3.63800311088562</t>
@@ -2228,28 +2228,28 @@
     <t xml:space="preserve">3.26165771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29301977157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32438182830811</t>
+    <t xml:space="preserve">3.29301953315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32438206672668</t>
   </si>
   <si>
     <t xml:space="preserve">2.90099382400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09700655937195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05780458450317</t>
+    <t xml:space="preserve">3.09700679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05780434608459</t>
   </si>
   <si>
     <t xml:space="preserve">2.94803690910339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00292038917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13620924949646</t>
+    <t xml:space="preserve">3.00292062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13620972633362</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036236763</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">3.21461462974548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25381731987</t>
+    <t xml:space="preserve">3.25381708145142</t>
   </si>
   <si>
     <t xml:space="preserve">3.22245526313782</t>
@@ -2267,40 +2267,40 @@
     <t xml:space="preserve">3.24205660820007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23813605308533</t>
+    <t xml:space="preserve">3.24597668647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23813652992249</t>
   </si>
   <si>
     <t xml:space="preserve">3.36750507354736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34006285667419</t>
+    <t xml:space="preserve">3.34006309509277</t>
   </si>
   <si>
     <t xml:space="preserve">3.45767092704773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59880065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37142539024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52039480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54391670227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7242488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81049466133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9202618598938</t>
+    <t xml:space="preserve">3.59880042076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37142515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52039504051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54391694068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72424864768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81049489974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92026162147522</t>
   </si>
   <si>
     <t xml:space="preserve">4.3358097076416</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">4.32796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32012891769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23388242721558</t>
+    <t xml:space="preserve">4.32012939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23388290405273</t>
   </si>
   <si>
     <t xml:space="preserve">4.16331815719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07707214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21820163726807</t>
+    <t xml:space="preserve">4.07707166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21820211410522</t>
   </si>
   <si>
     <t xml:space="preserve">4.21036100387573</t>
@@ -2333,49 +2333,49 @@
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208928108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481339454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8340163230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84577679634094</t>
+    <t xml:space="preserve">3.73208951950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481387138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401608467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577703475952</t>
   </si>
   <si>
     <t xml:space="preserve">3.70072722434998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83009624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321877479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8222553730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145853996277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169062614441</t>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265402793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145806312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169038772583</t>
   </si>
   <si>
     <t xml:space="preserve">3.74385023117065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98298597335815</t>
+    <t xml:space="preserve">3.98298573493958</t>
   </si>
   <si>
     <t xml:space="preserve">4.29660701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10059404373169</t>
+    <t xml:space="preserve">4.10059356689453</t>
   </si>
   <si>
     <t xml:space="preserve">3.91634178161621</t>
@@ -2390,160 +2390,160 @@
     <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763736724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01434755325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95162415504456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9437837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88890027999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05355024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923198699951</t>
+    <t xml:space="preserve">4.14763689041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01434803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95162391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94378328323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88889956474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05355072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923151016235</t>
   </si>
   <si>
     <t xml:space="preserve">4.030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89281988143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242146492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85753726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86537837982178</t>
+    <t xml:space="preserve">3.89282059669495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810225486755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242074966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753798484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8653781414032</t>
   </si>
   <si>
     <t xml:space="preserve">3.82617592811584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88105964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458154678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9085009098053</t>
+    <t xml:space="preserve">3.88105869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458059310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850162506104</t>
   </si>
   <si>
     <t xml:space="preserve">3.779132604599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.755610704422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657410621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497948646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96730518341064</t>
+    <t xml:space="preserve">3.75561118125916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74777102470398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497972488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96730470657349</t>
   </si>
   <si>
     <t xml:space="preserve">4.02218866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93594288825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75953149795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6458432674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544461250305</t>
+    <t xml:space="preserve">3.93594264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64584374427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6693651676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544508934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.63016247749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56351804733276</t>
+    <t xml:space="preserve">3.56351780891418</t>
   </si>
   <si>
     <t xml:space="preserve">3.56743836402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5909595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903322219849</t>
+    <t xml:space="preserve">3.59095978736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903298377991</t>
   </si>
   <si>
     <t xml:space="preserve">3.48119258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44199013710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3871066570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33222246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238831520081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43806982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49295353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55175733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55567717552185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50079393386841</t>
+    <t xml:space="preserve">3.44198989868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38710641860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654143333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33222270011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43806934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551156044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49295282363892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55175757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55567741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50079345703125</t>
   </si>
   <si>
     <t xml:space="preserve">3.51255464553833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37926554679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43414902687073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630910873413</t>
+    <t xml:space="preserve">3.37926578521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43414950370789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630887031555</t>
   </si>
   <si>
     <t xml:space="preserve">3.4615912437439</t>
@@ -2555,46 +2555,46 @@
     <t xml:space="preserve">3.15189075469971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20677447319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17541241645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52823615074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215646743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607630729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10843467712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866652488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252132415771</t>
+    <t xml:space="preserve">3.20677423477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17541217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.528235912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215575218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607654571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10843420028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866700172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252084732056</t>
   </si>
   <si>
     <t xml:space="preserve">4.13195610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09275341033936</t>
+    <t xml:space="preserve">4.0927529335022</t>
   </si>
   <si>
     <t xml:space="preserve">4.06139087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2887659072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2495641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24172353744507</t>
+    <t xml:space="preserve">4.28876638412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24956369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.39853382110596</t>
@@ -2609,34 +2609,34 @@
     <t xml:space="preserve">4.75919771194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82976245880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7278356552124</t>
+    <t xml:space="preserve">4.82976198196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72783517837524</t>
   </si>
   <si>
     <t xml:space="preserve">4.74351692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703882217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487945556641</t>
+    <t xml:space="preserve">4.76703834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487897872925</t>
   </si>
   <si>
     <t xml:space="preserve">4.73567628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80624151229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01009511947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99441385269165</t>
+    <t xml:space="preserve">4.68863344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80624103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.010094165802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99441337585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.9473705291748</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">4.86112451553345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84544372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91600847244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93952941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04929780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68438005447388</t>
+    <t xml:space="preserve">4.84544324874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91600799560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93952989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04929733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68437957763672</t>
   </si>
   <si>
     <t xml:space="preserve">5.59813356399536</t>
@@ -2672,40 +2672,40 @@
     <t xml:space="preserve">5.7157416343689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69222021102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66869878768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66085863113403</t>
+    <t xml:space="preserve">5.69222068786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66869831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66085767745972</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358226776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78630685806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08424711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17833280563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14697074890137</t>
+    <t xml:space="preserve">5.78630638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08424663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1783332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14697122573853</t>
   </si>
   <si>
     <t xml:space="preserve">6.05288410186768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97447919845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720283508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15080642700195</t>
+    <t xml:space="preserve">5.97447872161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720331192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15080690383911</t>
   </si>
   <si>
     <t xml:space="preserve">6.00474500656128</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">6.11834859848022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49161577224731</t>
+    <t xml:space="preserve">6.49161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">6.45915842056274</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">6.26440954208374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41047048568726</t>
+    <t xml:space="preserve">6.41047143936157</t>
   </si>
   <si>
     <t xml:space="preserve">6.39424228668213</t>
@@ -2738,16 +2738,16 @@
     <t xml:space="preserve">6.96225833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14077806472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43289995193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00091743469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83862686157227</t>
+    <t xml:space="preserve">7.14077854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43290090560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00091648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83862543106079</t>
   </si>
   <si>
     <t xml:space="preserve">7.87108421325684</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">7.78993988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91977262496948</t>
+    <t xml:space="preserve">7.91977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">7.95222997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90354299545288</t>
+    <t xml:space="preserve">7.90354251861572</t>
   </si>
   <si>
     <t xml:space="preserve">8.60139179229736</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56081867218018</t>
+    <t xml:space="preserve">8.56081962585449</t>
   </si>
   <si>
     <t xml:space="preserve">8.43910026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19566631317139</t>
+    <t xml:space="preserve">8.1956672668457</t>
   </si>
   <si>
     <t xml:space="preserve">8.23623752593994</t>
@@ -2786,10 +2786,10 @@
     <t xml:space="preserve">8.01714611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06583213806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96845865249634</t>
+    <t xml:space="preserve">8.06583404541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96845960617065</t>
   </si>
   <si>
     <t xml:space="preserve">7.40044260025024</t>
@@ -2801,31 +2801,31 @@
     <t xml:space="preserve">7.4815878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6438775062561</t>
+    <t xml:space="preserve">7.64387893676758</t>
   </si>
   <si>
     <t xml:space="preserve">7.5627326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69256496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502326965332</t>
+    <t xml:space="preserve">7.69256544113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502374649048</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6276478767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535778045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306911468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192335128784</t>
+    <t xml:space="preserve">7.62765026092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46535873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3030686378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192239761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.81619691848755</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">7.15700674057007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23815250396729</t>
+    <t xml:space="preserve">7.23815155029297</t>
   </si>
   <si>
     <t xml:space="preserve">7.3842134475708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70879459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61142015457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53027486801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74125289916992</t>
+    <t xml:space="preserve">7.70879411697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61142063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010761260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53027534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74125194549561</t>
   </si>
   <si>
     <t xml:space="preserve">8.35795593261719</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">8.1550931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96654605865479</t>
+    <t xml:space="preserve">8.96654415130615</t>
   </si>
   <si>
     <t xml:space="preserve">8.84482669830322</t>
@@ -2870,88 +2870,88 @@
     <t xml:space="preserve">8.76368141174316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52024745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39852905273438</t>
+    <t xml:space="preserve">8.5202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39852809906006</t>
   </si>
   <si>
     <t xml:space="preserve">8.47967433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31738376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08206367492676</t>
+    <t xml:space="preserve">8.3173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08206272125244</t>
   </si>
   <si>
     <t xml:space="preserve">8.11452007293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03337574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04960536956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04768943786621</t>
+    <t xml:space="preserve">8.03337478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04960441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04769039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940784454346</t>
+    <t xml:space="preserve">9.16940879821777</t>
   </si>
   <si>
     <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40344905853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23627758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48703575134277</t>
+    <t xml:space="preserve">9.40345001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23627662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48703670501709</t>
   </si>
   <si>
     <t xml:space="preserve">9.77958679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6124153137207</t>
+    <t xml:space="preserve">9.61241436004639</t>
   </si>
   <si>
     <t xml:space="preserve">9.57062149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52882766723633</t>
+    <t xml:space="preserve">9.52882862091064</t>
   </si>
   <si>
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90496635437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31986236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2780704498291</t>
+    <t xml:space="preserve">9.73779392242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420818328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90496730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31986331939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27806949615479</t>
   </si>
   <si>
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15268993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013984680176</t>
+    <t xml:space="preserve">9.15269088745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013889312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.7765531539917</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">8.35862159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6093807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19448375701904</t>
+    <t xml:space="preserve">8.60937976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19448280334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11089611053467</t>
+    <t xml:space="preserve">9.11089706420898</t>
   </si>
   <si>
     <t xml:space="preserve">9.36165618896484</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">8.94372463226318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.901930809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81834602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52579307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7347583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20816612243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30846881866455</t>
+    <t xml:space="preserve">8.90193176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81834697723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758689880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52579402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73476028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20816707611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30846977233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.32518768310547</t>
@@ -3008,28 +3008,28 @@
     <t xml:space="preserve">7.65649747848511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82366991043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321443557739</t>
+    <t xml:space="preserve">7.82366943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321538925171</t>
   </si>
   <si>
     <t xml:space="preserve">7.12154626846313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07139444351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10482788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68993234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589065551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053869247437</t>
+    <t xml:space="preserve">7.07139348983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10482835769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68993186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053916931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.80695247650146</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">7.62306261062622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99084186553955</t>
+    <t xml:space="preserve">7.99084281921387</t>
   </si>
   <si>
     <t xml:space="preserve">8.09114551544189</t>
@@ -3056,22 +3056,22 @@
     <t xml:space="preserve">8.10786247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48400020599365</t>
+    <t xml:space="preserve">8.48400115966797</t>
   </si>
   <si>
     <t xml:space="preserve">8.30011177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35026359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24996089935303</t>
+    <t xml:space="preserve">8.35026264190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.8738226890564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69829034805298</t>
+    <t xml:space="preserve">7.69829082489014</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
@@ -3083,34 +3083,34 @@
     <t xml:space="preserve">7.77351856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91561412811279</t>
+    <t xml:space="preserve">7.91561508178711</t>
   </si>
   <si>
     <t xml:space="preserve">7.78187656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60634660720825</t>
+    <t xml:space="preserve">7.60634565353394</t>
   </si>
   <si>
     <t xml:space="preserve">7.89889764785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79859447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978052139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41302824020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64850234985352</t>
+    <t xml:space="preserve">7.79859352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023504257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41302871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64850187301636</t>
   </si>
   <si>
     <t xml:space="preserve">8.24154376983643</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">8.21538066864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28514957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32003402709961</t>
+    <t xml:space="preserve">8.28514862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32003498077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19793701171875</t>
+    <t xml:space="preserve">8.19793796539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.49445819854736</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678630828857</t>
+    <t xml:space="preserve">8.54678535461426</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">8.45957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177391052246</t>
+    <t xml:space="preserve">8.17177486419678</t>
   </si>
   <si>
     <t xml:space="preserve">8.1281681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93630218505859</t>
+    <t xml:space="preserve">7.93630123138428</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827077865601</t>
+    <t xml:space="preserve">7.71827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.77931928634644</t>
@@ -3182,43 +3182,43 @@
     <t xml:space="preserve">7.95374345779419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14560985565186</t>
+    <t xml:space="preserve">8.14561080932617</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86653184890747</t>
+    <t xml:space="preserve">7.86653232574463</t>
   </si>
   <si>
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804063796997</t>
+    <t xml:space="preserve">7.78804016113281</t>
   </si>
   <si>
     <t xml:space="preserve">7.65722274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76187705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6921067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70082807540894</t>
+    <t xml:space="preserve">7.76187658309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69210767745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70082855224609</t>
   </si>
   <si>
     <t xml:space="preserve">7.5961742401123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46535587310791</t>
+    <t xml:space="preserve">7.46535634994507</t>
   </si>
   <si>
     <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571395874023</t>
+    <t xml:space="preserve">7.73571300506592</t>
   </si>
   <si>
     <t xml:space="preserve">7.50024080276489</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256748199463</t>
+    <t xml:space="preserve">7.55256843566895</t>
   </si>
   <si>
     <t xml:space="preserve">7.447913646698</t>
@@ -3242,19 +3242,19 @@
     <t xml:space="preserve">7.50896167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57001113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80548334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74443435668945</t>
+    <t xml:space="preserve">7.57001066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80548286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74443483352661</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77353858947754</t>
+    <t xml:space="preserve">8.77353763580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.72121047973633</t>
@@ -3263,16 +3263,16 @@
     <t xml:space="preserve">8.48573684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5031795501709</t>
+    <t xml:space="preserve">8.50318050384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619808197021</t>
+    <t xml:space="preserve">8.41596698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3461971282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.02351379394531</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83164644241333</t>
+    <t xml:space="preserve">7.83164596557617</t>
   </si>
   <si>
     <t xml:space="preserve">7.66594362258911</t>
@@ -3293,31 +3293,31 @@
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9711856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68338680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33453750610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1688346862793</t>
+    <t xml:space="preserve">7.97118711471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33453798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16883516311646</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418085098267</t>
+    <t xml:space="preserve">7.06418037414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13395071029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12522840499878</t>
+    <t xml:space="preserve">7.13395023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12522888183594</t>
   </si>
   <si>
     <t xml:space="preserve">6.78510189056396</t>
@@ -3329,46 +3329,46 @@
     <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6368408203125</t>
+    <t xml:space="preserve">6.63684129714966</t>
   </si>
   <si>
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75315618515015</t>
+    <t xml:space="preserve">7.75315570831299</t>
   </si>
   <si>
     <t xml:space="preserve">7.4391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43047142028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49152040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2734899520874</t>
+    <t xml:space="preserve">7.43047189712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49151992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27348899841309</t>
   </si>
   <si>
     <t xml:space="preserve">7.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38686466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3519811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31709623336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47407674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29093170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581663131714</t>
+    <t xml:space="preserve">7.38686513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35198068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31709575653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47407722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.290931224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581615447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.30837440490723</t>
@@ -3377,28 +3377,28 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663499832153</t>
+    <t xml:space="preserve">7.45663547515869</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03223419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10200500488281</t>
+    <t xml:space="preserve">7.85781049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03223514556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">8.15433216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09328269958496</t>
+    <t xml:space="preserve">8.05839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09328365325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.00607109069824</t>
@@ -3407,31 +3407,31 @@
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584190368652</t>
+    <t xml:space="preserve">8.11072635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584095001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990751266479</t>
+    <t xml:space="preserve">7.97990703582764</t>
   </si>
   <si>
     <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90141725540161</t>
+    <t xml:space="preserve">7.90141677856445</t>
   </si>
   <si>
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885900497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82292652130127</t>
+    <t xml:space="preserve">7.91885852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82292556762695</t>
   </si>
   <si>
     <t xml:space="preserve">8.11944675445557</t>
@@ -3446,16 +3446,16 @@
     <t xml:space="preserve">8.337477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5293436050415</t>
+    <t xml:space="preserve">8.52934265136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.94796180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87819290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563369750977</t>
+    <t xml:space="preserve">8.87819194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563465118408</t>
   </si>
   <si>
     <t xml:space="preserve">8.65144062042236</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">8.71248912811279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86075019836426</t>
+    <t xml:space="preserve">8.86074924468994</t>
   </si>
   <si>
     <t xml:space="preserve">8.93051910400391</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">8.6863260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15727043151855</t>
+    <t xml:space="preserve">9.15727138519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">8.91307735443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96540451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00028896331787</t>
+    <t xml:space="preserve">8.96540355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00028800964355</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3518,22 +3518,22 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66888236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91124534606934</t>
+    <t xml:space="preserve">8.80842304229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66888332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91124629974365</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8567419052124</t>
+    <t xml:space="preserve">8.82040691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85674285888672</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422756195068</t>
+    <t xml:space="preserve">8.58422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498817443848</t>
+    <t xml:space="preserve">8.77498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38438320159912</t>
+    <t xml:space="preserve">8.49339008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3843822479248</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453788757324</t>
+    <t xml:space="preserve">8.18453884124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896350860596</t>
+    <t xml:space="preserve">8.33896446228027</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09370040893555</t>
+    <t xml:space="preserve">8.09369945526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04828071594238</t>
+    <t xml:space="preserve">8.04827976226807</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644821166992</t>
+    <t xml:space="preserve">8.06644916534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3659,40 +3659,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919696807861</t>
+    <t xml:space="preserve">8.03919792175293</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94835901260376</t>
+    <t xml:space="preserve">8.00286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9483585357666</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9029393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385461807251</t>
+    <t xml:space="preserve">7.95744276046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90293884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385557174683</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85752010345459</t>
+    <t xml:space="preserve">7.85751962661743</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210136413574</t>
+    <t xml:space="preserve">7.81210088729858</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126245498657</t>
+    <t xml:space="preserve">7.72126293182373</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568807601929</t>
+    <t xml:space="preserve">7.87568855285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950777053833</t>
+    <t xml:space="preserve">7.63950824737549</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49416637420654</t>
+    <t xml:space="preserve">7.4941668510437</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41241216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4487476348877</t>
+    <t xml:space="preserve">7.4124116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44874715805054</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112440109253</t>
+    <t xml:space="preserve">6.73112392425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7220401763916</t>
+    <t xml:space="preserve">6.72204065322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486675262451</t>
+    <t xml:space="preserve">6.59486722946167</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3806,22 +3806,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699247360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31248998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790967941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775308609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767669677734</t>
+    <t xml:space="preserve">7.01272296905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31249046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767621994019</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393339157104</t>
+    <t xml:space="preserve">7.79393291473389</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3842,31 +3842,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96652698516846</t>
+    <t xml:space="preserve">7.76668262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9665265083313</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.475998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607717514038</t>
+    <t xml:space="preserve">7.63042402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47599840164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607669830322</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523921966553</t>
+    <t xml:space="preserve">7.28523874282837</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264562606812</t>
+    <t xml:space="preserve">7.11264514923096</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225652694702</t>
+    <t xml:space="preserve">7.61225700378418</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890279769897</t>
+    <t xml:space="preserve">7.24890327453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -69440,7 +69440,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6494907407</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>9638</v>
@@ -69461,6 +69461,32 @@
         <v>1412</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495949074</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>10381</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1426">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19253528118134</t>
+    <t xml:space="preserve">1.19253516197205</t>
   </si>
   <si>
     <t xml:space="preserve">GE.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.21355509757996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22546637058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20654845237732</t>
+    <t xml:space="preserve">1.22546648979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20654833316803</t>
   </si>
   <si>
     <t xml:space="preserve">1.23177242279053</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">1.26330244541168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27311170101166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26120042800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718713760376</t>
+    <t xml:space="preserve">1.27311182022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26120054721832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718701839447</t>
   </si>
   <si>
     <t xml:space="preserve">1.2079496383667</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">1.19323563575745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814026355743</t>
+    <t xml:space="preserve">1.17501842975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1981406211853</t>
   </si>
   <si>
     <t xml:space="preserve">1.2457857131958</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495628356934</t>
+    <t xml:space="preserve">1.21495652198792</t>
   </si>
   <si>
     <t xml:space="preserve">1.18272566795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17992317676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641997337341</t>
+    <t xml:space="preserve">1.17992293834686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641985416412</t>
   </si>
   <si>
     <t xml:space="preserve">1.12457048892975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12807369232178</t>
+    <t xml:space="preserve">1.12807381153107</t>
   </si>
   <si>
     <t xml:space="preserve">1.10284984111786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08603358268738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01596701145172</t>
+    <t xml:space="preserve">1.08603382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01596713066101</t>
   </si>
   <si>
     <t xml:space="preserve">1.0250757932663</t>
@@ -122,61 +122,61 @@
     <t xml:space="preserve">1.02017104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00195384025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297353744507</t>
+    <t xml:space="preserve">1.00195372104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297377586365</t>
   </si>
   <si>
     <t xml:space="preserve">1.04329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09654366970062</t>
+    <t xml:space="preserve">1.09654378890991</t>
   </si>
   <si>
     <t xml:space="preserve">1.11335968971252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11055707931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09304022789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106704711914</t>
+    <t xml:space="preserve">1.11055731773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09304046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106716632843</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017559051514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15610039234161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10004687309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13157725334167</t>
+    <t xml:space="preserve">1.15610015392303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10004711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1315770149231</t>
   </si>
   <si>
     <t xml:space="preserve">1.10705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13227796554565</t>
+    <t xml:space="preserve">1.13227784633636</t>
   </si>
   <si>
     <t xml:space="preserve">1.1182644367218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14909362792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17852175235748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17011368274689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412697315216</t>
+    <t xml:space="preserve">1.14909374713898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1701135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412709236145</t>
   </si>
   <si>
     <t xml:space="preserve">1.17081451416016</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">1.16310703754425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22616708278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508500099182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24088108539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20514714717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19113385677338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22686767578125</t>
+    <t xml:space="preserve">1.22616720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508512020111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2408812046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20514702796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113373756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22686779499054</t>
   </si>
   <si>
     <t xml:space="preserve">1.22196304798126</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17221581935883</t>
+    <t xml:space="preserve">1.17221570014954</t>
   </si>
   <si>
     <t xml:space="preserve">1.19183421134949</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">1.20374584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.203045129776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2380782365799</t>
+    <t xml:space="preserve">1.20304501056671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23807859420776</t>
   </si>
   <si>
     <t xml:space="preserve">1.2331737279892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19954168796539</t>
+    <t xml:space="preserve">1.19954180717468</t>
   </si>
   <si>
     <t xml:space="preserve">1.22476577758789</t>
@@ -239,61 +239,61 @@
     <t xml:space="preserve">1.21845960617065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21916055679321</t>
+    <t xml:space="preserve">1.21916031837463</t>
   </si>
   <si>
     <t xml:space="preserve">1.2289696931839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.212153673172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22266387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2920298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29623365402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521371841431</t>
+    <t xml:space="preserve">1.21215391159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22266376018524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29202961921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29623377323151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
     <t xml:space="preserve">1.28712522983551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28151977062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788773059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737788200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865046977997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469908714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138615131378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11896526813507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036645412445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13648164272308</t>
+    <t xml:space="preserve">1.28151965141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788784980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737800121307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865035057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469896793365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138638973236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11896502971649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036633491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13648188114166</t>
   </si>
   <si>
     <t xml:space="preserve">1.14629113674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14208722114563</t>
+    <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
     <t xml:space="preserve">1.07202041149139</t>
@@ -302,49 +302,49 @@
     <t xml:space="preserve">1.084632396698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501376628876</t>
+    <t xml:space="preserve">1.06501352787018</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253026008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902705669403</t>
+    <t xml:space="preserve">1.08253037929535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902681827545</t>
   </si>
   <si>
     <t xml:space="preserve">1.05800712108612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1014484167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355031490326</t>
+    <t xml:space="preserve">1.10144853591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355043411255</t>
   </si>
   <si>
     <t xml:space="preserve">1.09514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11966562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934639930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11265909671783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15680110454559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528028964996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681509494781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48821651935577</t>
+    <t xml:space="preserve">1.11966574192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934651851654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11265921592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1568009853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528040885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4868152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48821663856506</t>
   </si>
   <si>
     <t xml:space="preserve">1.45178186893463</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">1.4153470993042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4573872089386</t>
+    <t xml:space="preserve">1.45738697052002</t>
   </si>
   <si>
     <t xml:space="preserve">1.40133380889893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4699991941452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776845932007</t>
+    <t xml:space="preserve">1.46999931335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776857852936</t>
   </si>
   <si>
     <t xml:space="preserve">1.42375516891479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4363671541214</t>
+    <t xml:space="preserve">1.43636703491211</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936038970947</t>
@@ -380,88 +380,88 @@
     <t xml:space="preserve">1.42235386371613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41814982891083</t>
+    <t xml:space="preserve">1.41814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42795920372009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48120999336243</t>
+    <t xml:space="preserve">1.42795932292938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48121011257172</t>
   </si>
   <si>
     <t xml:space="preserve">1.6942126750946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338324546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071413516998</t>
+    <t xml:space="preserve">1.66338312625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8007138967514</t>
   </si>
   <si>
     <t xml:space="preserve">1.84555673599243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79230618476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090476036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268719673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064720630646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71663391590118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78670060634613</t>
+    <t xml:space="preserve">1.79230582714081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090440273285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268707752228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064744472504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71663415431976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78670048713684</t>
   </si>
   <si>
     <t xml:space="preserve">1.84275412559509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82593786716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313477993011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995127677917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83855009078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84415531158447</t>
+    <t xml:space="preserve">1.82593810558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313501834869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995115756989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854997158051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84415543079376</t>
   </si>
   <si>
     <t xml:space="preserve">1.83014190196991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81472706794739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874071598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192469596863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294475078583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835922718048</t>
+    <t xml:space="preserve">1.81472730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874047756195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192445755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294451236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835970401764</t>
   </si>
   <si>
     <t xml:space="preserve">1.86937928199768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99549901485443</t>
+    <t xml:space="preserve">1.99549973011017</t>
   </si>
   <si>
     <t xml:space="preserve">2.07257270812988</t>
@@ -470,82 +470,82 @@
     <t xml:space="preserve">2.0291314125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08798742294312</t>
+    <t xml:space="preserve">2.08798718452454</t>
   </si>
   <si>
     <t xml:space="preserve">2.04034209251404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99830222129822</t>
+    <t xml:space="preserve">1.99830210208893</t>
   </si>
   <si>
     <t xml:space="preserve">2.03053259849548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01932191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970316886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231551170349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066597938538</t>
+    <t xml:space="preserve">2.01932215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970364570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359288215637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066645622253</t>
   </si>
   <si>
     <t xml:space="preserve">2.15945529937744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989379405975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339257240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167658805847</t>
+    <t xml:space="preserve">1.98989403247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339269161224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167682647705</t>
   </si>
   <si>
     <t xml:space="preserve">1.95345962047577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01651930809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97868323326111</t>
+    <t xml:space="preserve">2.01651954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428881168365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97868311405182</t>
   </si>
   <si>
     <t xml:space="preserve">1.93944597244263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91982710361481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377382278442</t>
+    <t xml:space="preserve">1.91982746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377394199371</t>
   </si>
   <si>
     <t xml:space="preserve">1.86797797679901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87918853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85676729679108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78950309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631959438324</t>
+    <t xml:space="preserve">1.87918841838837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85676717758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7895028591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631923675537</t>
   </si>
   <si>
     <t xml:space="preserve">1.90301132202148</t>
@@ -554,37 +554,37 @@
     <t xml:space="preserve">1.89880740642548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91001808643341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690043926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849284648895</t>
+    <t xml:space="preserve">1.91001796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690079689026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849272727966</t>
   </si>
   <si>
     <t xml:space="preserve">1.98569011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94224870204926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766341686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9618673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326851844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97027492523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9660712480545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00390768051147</t>
+    <t xml:space="preserve">1.94224882125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766305923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186721324921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326875686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027552127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607136726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0039074420929</t>
   </si>
   <si>
     <t xml:space="preserve">2.07397389411926</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">2.18888354301453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16506052017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13283014297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06416487693787</t>
+    <t xml:space="preserve">2.1650607585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13282990455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06416463851929</t>
   </si>
   <si>
     <t xml:space="preserve">2.09639549255371</t>
@@ -611,28 +611,28 @@
     <t xml:space="preserve">2.09499430656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11321091651917</t>
+    <t xml:space="preserve">2.11321115493774</t>
   </si>
   <si>
     <t xml:space="preserve">2.14404082298279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13002753257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14824509620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13423132896423</t>
+    <t xml:space="preserve">2.13002705574036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14824485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13423109054565</t>
   </si>
   <si>
     <t xml:space="preserve">2.14123797416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15244889259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13703441619873</t>
+    <t xml:space="preserve">2.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13703393936157</t>
   </si>
   <si>
     <t xml:space="preserve">2.11180996894836</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">2.118816614151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10200119018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24213409423828</t>
+    <t xml:space="preserve">2.10200047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11741590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213433265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.48876881599426</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">2.48736763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316311836243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46494626998901</t>
+    <t xml:space="preserve">2.49297308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316335678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46494603157043</t>
   </si>
   <si>
     <t xml:space="preserve">2.40328741073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099990844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48036098480225</t>
+    <t xml:space="preserve">2.52099967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48036074638367</t>
   </si>
   <si>
     <t xml:space="preserve">2.46634745597839</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">2.44392609596252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43972229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47615647315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45513677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47335433959961</t>
+    <t xml:space="preserve">2.43972206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47615718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45513701438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437403678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47335457801819</t>
   </si>
   <si>
     <t xml:space="preserve">2.65552759170532</t>
@@ -704,64 +704,64 @@
     <t xml:space="preserve">2.71858763694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70457434654236</t>
+    <t xml:space="preserve">2.70457410812378</t>
   </si>
   <si>
     <t xml:space="preserve">2.84751033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865432739258</t>
+    <t xml:space="preserve">2.788654088974</t>
   </si>
   <si>
     <t xml:space="preserve">3.11096096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23988366127014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38422107696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129441261292</t>
+    <t xml:space="preserve">3.23988389968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38422131538391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129488945007</t>
   </si>
   <si>
     <t xml:space="preserve">3.71003127098083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58040833473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66098475456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601798057556</t>
+    <t xml:space="preserve">3.58040761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66098499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601774215698</t>
   </si>
   <si>
     <t xml:space="preserve">3.78360104560852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95176219940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386804580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19349193572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16896820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11291408538818</t>
+    <t xml:space="preserve">3.95176148414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19349241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16896772384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1129150390625</t>
   </si>
   <si>
     <t xml:space="preserve">4.03233814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30910158157349</t>
+    <t xml:space="preserve">4.30910110473633</t>
   </si>
   <si>
     <t xml:space="preserve">4.30559825897217</t>
@@ -770,22 +770,22 @@
     <t xml:space="preserve">4.55433511734009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6979718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50023555755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256105422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10085487365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01677560806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44768571853638</t>
+    <t xml:space="preserve">4.69797229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50023603439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10085535049438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01677513122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44768524169922</t>
   </si>
   <si>
     <t xml:space="preserve">5.44418239593506</t>
@@ -794,127 +794,127 @@
     <t xml:space="preserve">5.77349519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369325637817</t>
+    <t xml:space="preserve">6.39708852767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518251419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936918258667</t>
   </si>
   <si>
     <t xml:space="preserve">6.97858238220215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78433275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626554489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53252840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35266780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0720853805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.323890209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900108337402</t>
+    <t xml:space="preserve">6.78433322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626602172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53252935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35266828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07208585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32389068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900156021118</t>
   </si>
   <si>
     <t xml:space="preserve">6.51094532012939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40302991867065</t>
+    <t xml:space="preserve">6.40302848815918</t>
   </si>
   <si>
     <t xml:space="preserve">6.15841913223267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19798755645752</t>
+    <t xml:space="preserve">6.19798851013184</t>
   </si>
   <si>
     <t xml:space="preserve">6.37425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47137594223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3274884223938</t>
+    <t xml:space="preserve">6.47137546539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32748794555664</t>
   </si>
   <si>
     <t xml:space="preserve">6.15122509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11165571212769</t>
+    <t xml:space="preserve">6.11165523529053</t>
   </si>
   <si>
     <t xml:space="preserve">5.93898963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057319641113</t>
+    <t xml:space="preserve">5.96057271957397</t>
   </si>
   <si>
     <t xml:space="preserve">5.85265731811523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90661478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89582300186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75193452835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69437885284424</t>
+    <t xml:space="preserve">5.90661525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89582347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75193500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6943793296814</t>
   </si>
   <si>
     <t xml:space="preserve">5.70157384872437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3670334815979</t>
+    <t xml:space="preserve">5.36703300476074</t>
   </si>
   <si>
     <t xml:space="preserve">4.87421607971191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17997884750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97853517532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96414661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8454384803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8778133392334</t>
+    <t xml:space="preserve">5.17997932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97853565216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96414613723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84543895721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87781381607056</t>
   </si>
   <si>
     <t xml:space="preserve">4.9101881980896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70155048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92457675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76989698410034</t>
+    <t xml:space="preserve">4.70155000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92457723617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76989793777466</t>
   </si>
   <si>
     <t xml:space="preserve">4.69075870513916</t>
@@ -923,37 +923,37 @@
     <t xml:space="preserve">4.6583833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68716096878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82385540008545</t>
+    <t xml:space="preserve">4.68716144561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82385587692261</t>
   </si>
   <si>
     <t xml:space="preserve">4.55046701431274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51089811325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49291181564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4389533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38139915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38499593734741</t>
+    <t xml:space="preserve">4.51089859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49291133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43895387649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38139867782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38499546051025</t>
   </si>
   <si>
     <t xml:space="preserve">4.46413469314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03609037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85623025894165</t>
+    <t xml:space="preserve">5.03609085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85622930526733</t>
   </si>
   <si>
     <t xml:space="preserve">4.80946636199951</t>
@@ -962,94 +962,94 @@
     <t xml:space="preserve">4.76629972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68356466293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67637014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59003686904907</t>
+    <t xml:space="preserve">4.68356418609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67636966705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60442590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59003639221191</t>
   </si>
   <si>
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67277240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74831390380859</t>
+    <t xml:space="preserve">4.6619815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74831295013428</t>
   </si>
   <si>
     <t xml:space="preserve">4.75910520553589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95335578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104944229126</t>
+    <t xml:space="preserve">4.95335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8310489654541</t>
   </si>
   <si>
     <t xml:space="preserve">5.06486797332764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14400625228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11522960662842</t>
+    <t xml:space="preserve">5.14400720596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.19436740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10803413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93536806106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550842285156</t>
+    <t xml:space="preserve">5.10803461074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93536853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
     <t xml:space="preserve">4.99652099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90659141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82025718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89220237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05407667160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0181040763855</t>
+    <t xml:space="preserve">4.90659093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92098045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82025814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89220190048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05407619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925748825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01810455322266</t>
   </si>
   <si>
     <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94615983963013</t>
+    <t xml:space="preserve">4.94616031646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.15839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393678665161</t>
+    <t xml:space="preserve">5.23393726348877</t>
   </si>
   <si>
     <t xml:space="preserve">5.60804605484009</t>
@@ -1058,37 +1058,37 @@
     <t xml:space="preserve">5.8994197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77711486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611469268799</t>
+    <t xml:space="preserve">5.7771143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611421585083</t>
   </si>
   <si>
     <t xml:space="preserve">5.94978141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18000316619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20877981185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52533435821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03613662719727</t>
+    <t xml:space="preserve">6.18000221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20877933502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52533388137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03613758087158</t>
   </si>
   <si>
     <t xml:space="preserve">6.89584636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11527633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13685894012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802474975586</t>
+    <t xml:space="preserve">7.11527585983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13685989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802284240723</t>
   </si>
   <si>
     <t xml:space="preserve">8.12968921661377</t>
@@ -1097,55 +1097,55 @@
     <t xml:space="preserve">8.43904781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95704555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29518222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42465877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61890983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321701049805</t>
+    <t xml:space="preserve">8.95704650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2951831817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160692214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42465972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61890888214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321605682373</t>
   </si>
   <si>
     <t xml:space="preserve">8.0145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80594062805176</t>
+    <t xml:space="preserve">7.8059401512146</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299478530884</t>
+    <t xml:space="preserve">7.99299573898315</t>
   </si>
   <si>
     <t xml:space="preserve">8.10091209411621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98580026626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88507699966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73399543762207</t>
+    <t xml:space="preserve">7.98580121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8850793838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73399639129639</t>
   </si>
   <si>
     <t xml:space="preserve">7.41024732589722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54694175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499704360962</t>
+    <t xml:space="preserve">7.54694080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499799728394</t>
   </si>
   <si>
     <t xml:space="preserve">7.45341396331787</t>
@@ -1154,136 +1154,136 @@
     <t xml:space="preserve">7.52535820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38866424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84191131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910726547241</t>
+    <t xml:space="preserve">7.38866376876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702314376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910774230957</t>
   </si>
   <si>
     <t xml:space="preserve">8.04335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92824554443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630178451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74838590621948</t>
+    <t xml:space="preserve">7.92824459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85629987716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74838542938232</t>
   </si>
   <si>
     <t xml:space="preserve">7.57571935653687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42463636398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19441556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419382095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498512268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20880460739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20160913467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413579940796</t>
+    <t xml:space="preserve">7.42463493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1944146156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498464584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880365371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20160865783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55413436889648</t>
   </si>
   <si>
     <t xml:space="preserve">7.65485715866089</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722009658813</t>
+    <t xml:space="preserve">7.25196981430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18721914291382</t>
   </si>
   <si>
     <t xml:space="preserve">7.10448360443115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00735998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1584415435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91743040084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85627746582031</t>
+    <t xml:space="preserve">7.00735950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91742992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85627794265747</t>
   </si>
   <si>
     <t xml:space="preserve">6.892249584198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78793096542358</t>
+    <t xml:space="preserve">6.78793048858643</t>
   </si>
   <si>
     <t xml:space="preserve">6.95700025558472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93541622161865</t>
+    <t xml:space="preserve">6.93541574478149</t>
   </si>
   <si>
     <t xml:space="preserve">6.98217964172363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16203927993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02174949645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33830213546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82752418518066</t>
+    <t xml:space="preserve">7.16204071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045667648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02174854278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33830261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82752323150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.25918769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15846729278564</t>
+    <t xml:space="preserve">8.15846633911133</t>
   </si>
   <si>
     <t xml:space="preserve">7.91385650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89946699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313514709473</t>
+    <t xml:space="preserve">7.89946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313419342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.66924619674683</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">7.76996755599976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48219060897827</t>
+    <t xml:space="preserve">7.64046716690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4821925163269</t>
   </si>
   <si>
     <t xml:space="preserve">6.79152774810791</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">6.74836206436157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56850099563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64044523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48936223983765</t>
+    <t xml:space="preserve">6.56850051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64044570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4893627166748</t>
   </si>
   <si>
     <t xml:space="preserve">6.63325071334839</t>
@@ -1322,37 +1322,37 @@
     <t xml:space="preserve">6.62605619430542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56130599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791856765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19439077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02172517776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87783670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86344814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25914096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619607925415</t>
+    <t xml:space="preserve">6.56130647659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447263717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791904449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19439029693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87783718109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86344766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2591404914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619655609131</t>
   </si>
   <si>
     <t xml:space="preserve">6.46777868270874</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">6.67641687393188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51814126968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46058416366577</t>
+    <t xml:space="preserve">6.51814031600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46058368682861</t>
   </si>
   <si>
     <t xml:space="preserve">6.29511260986328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10086393356323</t>
+    <t xml:space="preserve">6.10086345672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.13683557510376</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">5.93539190292358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89222574234009</t>
+    <t xml:space="preserve">5.89222526550293</t>
   </si>
   <si>
     <t xml:space="preserve">5.79869890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97136402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01453065872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99294710159302</t>
+    <t xml:space="preserve">5.97136449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01453113555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99294757843018</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728081703186</t>
@@ -1403,40 +1403,40 @@
     <t xml:space="preserve">6.18719720840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25194597244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22316837310791</t>
+    <t xml:space="preserve">6.25194692611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316789627075</t>
   </si>
   <si>
     <t xml:space="preserve">6.12244701385498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27352905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30230760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33828020095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58551692962646</t>
+    <t xml:space="preserve">6.27353000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950212478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30230665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33827972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58551740646362</t>
   </si>
   <si>
     <t xml:space="preserve">6.38323259353638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46564435958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326290130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30831098556519</t>
+    <t xml:space="preserve">6.46564388275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3083119392395</t>
   </si>
   <si>
     <t xml:space="preserve">6.59300947189331</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">6.41319990158081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17345476150513</t>
+    <t xml:space="preserve">6.17345428466797</t>
   </si>
   <si>
     <t xml:space="preserve">6.09853410720825</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">5.90373992919922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95618438720703</t>
+    <t xml:space="preserve">5.95618391036987</t>
   </si>
   <si>
     <t xml:space="preserve">5.94120025634766</t>
@@ -1466,76 +1466,76 @@
     <t xml:space="preserve">5.94869232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84380340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48418426513672</t>
+    <t xml:space="preserve">5.84380388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656572341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48418521881104</t>
   </si>
   <si>
     <t xml:space="preserve">5.60405826568604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55910539627075</t>
+    <t xml:space="preserve">5.55910587310791</t>
   </si>
   <si>
     <t xml:space="preserve">5.888756275177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8063440322876</t>
+    <t xml:space="preserve">5.80634355545044</t>
   </si>
   <si>
     <t xml:space="preserve">5.64151859283447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88126373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621612548828</t>
+    <t xml:space="preserve">5.79135894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139211654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88126420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621660232544</t>
   </si>
   <si>
     <t xml:space="preserve">6.33078765869141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55554914474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815181732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33827972412109</t>
+    <t xml:space="preserve">6.55554866790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815277099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33827924728394</t>
   </si>
   <si>
     <t xml:space="preserve">6.3008189201355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12850284576416</t>
+    <t xml:space="preserve">6.12850189208984</t>
   </si>
   <si>
     <t xml:space="preserve">6.06107330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77637481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76888370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70145463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66399478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57409000396729</t>
+    <t xml:space="preserve">5.77637529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.768883228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70145416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66399431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57408952713013</t>
   </si>
   <si>
     <t xml:space="preserve">5.75389909744263</t>
@@ -1544,58 +1544,58 @@
     <t xml:space="preserve">5.78386688232422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67897891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6265344619751</t>
+    <t xml:space="preserve">5.67897844314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62653350830078</t>
   </si>
   <si>
     <t xml:space="preserve">5.61904191970825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65650224685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54412126541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58158111572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50666093826294</t>
+    <t xml:space="preserve">5.65650272369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54412174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58158159255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5066614151001</t>
   </si>
   <si>
     <t xml:space="preserve">5.53662919998169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43174028396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46920156478882</t>
+    <t xml:space="preserve">5.43174076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46920108795166</t>
   </si>
   <si>
     <t xml:space="preserve">5.31935977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424917221069</t>
+    <t xml:space="preserve">5.28189992904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424869537354</t>
   </si>
   <si>
     <t xml:space="preserve">5.49167680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51415348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36431264877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27440786361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450260162354</t>
+    <t xml:space="preserve">5.51415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36431217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27440738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450307846069</t>
   </si>
   <si>
     <t xml:space="preserve">5.2069787979126</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">5.74640655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47669267654419</t>
+    <t xml:space="preserve">5.47669315338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.21447086334229</t>
@@ -1616,52 +1616,52 @@
     <t xml:space="preserve">5.13955020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09459829330444</t>
+    <t xml:space="preserve">5.09459781646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.10958242416382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07212162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01967716217041</t>
+    <t xml:space="preserve">5.07212209701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05713748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967763900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.03466176986694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92977333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86983728408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73497915267944</t>
+    <t xml:space="preserve">4.92977237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86983633041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7349796295166</t>
   </si>
   <si>
     <t xml:space="preserve">4.77243947982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82488393783569</t>
+    <t xml:space="preserve">4.82488441467285</t>
   </si>
   <si>
     <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75745487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478824615479</t>
+    <t xml:space="preserve">4.75745582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234474182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9147891998291</t>
   </si>
   <si>
     <t xml:space="preserve">4.89980459213257</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">4.8548526763916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95224905014038</t>
+    <t xml:space="preserve">4.95224857330322</t>
   </si>
   <si>
     <t xml:space="preserve">5.16951894760132</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">5.08710622787476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13205909729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840620040894</t>
+    <t xml:space="preserve">5.13205862045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840667724609</t>
   </si>
   <si>
     <t xml:space="preserve">6.25586748123169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01612091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602569580078</t>
+    <t xml:space="preserve">6.01612043380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602521896362</t>
   </si>
   <si>
     <t xml:space="preserve">5.99364471435547</t>
@@ -1700,37 +1700,37 @@
     <t xml:space="preserve">5.04215383529663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94475698471069</t>
+    <t xml:space="preserve">4.98221731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94475650787354</t>
   </si>
   <si>
     <t xml:space="preserve">4.99720144271851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02717018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89231300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964590072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95974063873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81739234924316</t>
+    <t xml:space="preserve">5.0271692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89231252670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.049644947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95974111557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81739139556885</t>
   </si>
   <si>
     <t xml:space="preserve">4.79491567611694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78742408752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83237648010254</t>
+    <t xml:space="preserve">4.78742361068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83237552642822</t>
   </si>
   <si>
     <t xml:space="preserve">4.97472524642944</t>
@@ -1739,10 +1739,10 @@
     <t xml:space="preserve">4.90729713439941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76494789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47275686264038</t>
+    <t xml:space="preserve">4.76494741439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4727578163147</t>
   </si>
   <si>
     <t xml:space="preserve">4.27047204971313</t>
@@ -1751,22 +1751,22 @@
     <t xml:space="preserve">4.38285255432129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32291650772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30044031143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31542444229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46526575088501</t>
+    <t xml:space="preserve">4.32291698455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30043983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31542491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46526527404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.45777320861816</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">5.07961463928223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93726491928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218509674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196245193481</t>
+    <t xml:space="preserve">4.93726539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218557357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196340560913</t>
   </si>
   <si>
     <t xml:space="preserve">5.25942325592041</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">5.11707401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28939151763916</t>
+    <t xml:space="preserve">5.28939199447632</t>
   </si>
   <si>
     <t xml:space="preserve">5.16202640533447</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">5.31186819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41675662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44672536849976</t>
+    <t xml:space="preserve">5.41675615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180376052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4467248916626</t>
   </si>
   <si>
     <t xml:space="preserve">5.39428043365479</t>
@@ -1832,43 +1832,43 @@
     <t xml:space="preserve">5.89624786376953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85878801345825</t>
+    <t xml:space="preserve">5.85878753662109</t>
   </si>
   <si>
     <t xml:space="preserve">6.12100982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22589921951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383609771729</t>
+    <t xml:space="preserve">6.22589874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383562088013</t>
   </si>
   <si>
     <t xml:space="preserve">6.00113677978516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79885053634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8213267326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91123247146606</t>
+    <t xml:space="preserve">5.79885149002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91123199462891</t>
   </si>
   <si>
     <t xml:space="preserve">6.03110551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.008629322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631181716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377214431763</t>
+    <t xml:space="preserve">6.00862979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872406005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377262115479</t>
   </si>
   <si>
     <t xml:space="preserve">5.97116851806641</t>
@@ -1880,34 +1880,34 @@
     <t xml:space="preserve">6.09104156494141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361345291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859710693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142337799072</t>
+    <t xml:space="preserve">6.15097856521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608964920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142290115356</t>
   </si>
   <si>
     <t xml:space="preserve">5.97866106033325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69396257400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7089467048645</t>
+    <t xml:space="preserve">5.69396209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70894718170166</t>
   </si>
   <si>
     <t xml:space="preserve">5.49916982650757</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">5.46170854568481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73891448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161380767822</t>
+    <t xml:space="preserve">5.73891401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161333084106</t>
   </si>
   <si>
     <t xml:space="preserve">5.47268581390381</t>
@@ -1931,49 +1931,52 @@
     <t xml:space="preserve">5.33155584335327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46484470367432</t>
+    <t xml:space="preserve">5.46484518051147</t>
   </si>
   <si>
     <t xml:space="preserve">5.35507774353027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30803442001343</t>
+    <t xml:space="preserve">5.30803489685059</t>
   </si>
   <si>
     <t xml:space="preserve">5.37859916687012</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24531030654907</t>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531078338623</t>
   </si>
   <si>
     <t xml:space="preserve">5.26883172988892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28451347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315046310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14338302612305</t>
+    <t xml:space="preserve">5.28451251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14338350296021</t>
   </si>
   <si>
     <t xml:space="preserve">5.06497812271118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00225448608398</t>
+    <t xml:space="preserve">5.00225400924683</t>
   </si>
   <si>
     <t xml:space="preserve">5.16690540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20610809326172</t>
+    <t xml:space="preserve">5.20610761642456</t>
   </si>
   <si>
     <t xml:space="preserve">5.33939647674561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235363006592</t>
+    <t xml:space="preserve">5.29235315322876</t>
   </si>
   <si>
     <t xml:space="preserve">5.11986207962036</t>
@@ -1982,22 +1985,19 @@
     <t xml:space="preserve">5.13554334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09634065628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713748931885</t>
+    <t xml:space="preserve">5.09634017944336</t>
   </si>
   <si>
     <t xml:space="preserve">5.11202144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17474555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44916439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45700454711914</t>
+    <t xml:space="preserve">5.17474508285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44916391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45700407028198</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">5.70790147781372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67653942108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55893182754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51188898086548</t>
+    <t xml:space="preserve">5.67653894424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733720779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55893135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51188802719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48052597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36291837692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31587505340576</t>
+    <t xml:space="preserve">5.48052644729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36291885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31587553024292</t>
   </si>
   <si>
     <t xml:space="preserve">5.3237156867981</t>
@@ -2036,22 +2036,22 @@
     <t xml:space="preserve">5.19826793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79840040206909</t>
+    <t xml:space="preserve">4.79840087890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71999549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51614189147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97089242935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82192277908325</t>
+    <t xml:space="preserve">4.71999502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51614236831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97089290618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82192182540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.6415901184082</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">4.71215486526489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67295169830322</t>
+    <t xml:space="preserve">4.67295217514038</t>
   </si>
   <si>
     <t xml:space="preserve">4.63374948501587</t>
@@ -2069,37 +2069,37 @@
     <t xml:space="preserve">4.64943027496338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59454727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62590885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68079233169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90032720565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2296290397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0414571762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15122413635254</t>
+    <t xml:space="preserve">4.59454679489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62590932846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68079280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90032768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22962951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02577590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04145622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1512246131897</t>
   </si>
   <si>
     <t xml:space="preserve">5.22178840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21394872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15906476974487</t>
+    <t xml:space="preserve">5.21394824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15906429290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.08065938949585</t>
@@ -2108,61 +2108,61 @@
     <t xml:space="preserve">5.1277027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01793575286865</t>
+    <t xml:space="preserve">5.01793527603149</t>
   </si>
   <si>
     <t xml:space="preserve">5.07281875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08849954605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19042682647705</t>
+    <t xml:space="preserve">5.08850049972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19042730331421</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52756881713867</t>
+    <t xml:space="preserve">5.52756977081299</t>
   </si>
   <si>
     <t xml:space="preserve">5.5197286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40212106704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56677150726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4334831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50404739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53540992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41780138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42564249038696</t>
+    <t xml:space="preserve">5.40212059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56677198410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43348264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50404787063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53541040420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41780185699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42564296722412</t>
   </si>
   <si>
     <t xml:space="preserve">5.84118986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76278495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44132328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40996122360229</t>
+    <t xml:space="preserve">5.7627854347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44132375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40996170043945</t>
   </si>
   <si>
     <t xml:space="preserve">5.38643980026245</t>
@@ -2171,22 +2171,22 @@
     <t xml:space="preserve">5.3472375869751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37075901031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2374701499939</t>
+    <t xml:space="preserve">5.37075853347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23746967315674</t>
   </si>
   <si>
     <t xml:space="preserve">4.97873258590698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83760261535645</t>
+    <t xml:space="preserve">4.8376030921936</t>
   </si>
   <si>
     <t xml:space="preserve">4.89248704910278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86896514892578</t>
+    <t xml:space="preserve">4.86896467208862</t>
   </si>
   <si>
     <t xml:space="preserve">4.92384910583496</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">4.57102537155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54750347137451</t>
+    <t xml:space="preserve">4.54750394821167</t>
   </si>
   <si>
     <t xml:space="preserve">4.57886648178101</t>
@@ -2210,34 +2210,34 @@
     <t xml:space="preserve">4.39069318771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15547800064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2260422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11627531051636</t>
+    <t xml:space="preserve">4.15547752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22604274749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11627435684204</t>
   </si>
   <si>
     <t xml:space="preserve">3.84185719490051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63800311088562</t>
+    <t xml:space="preserve">3.63800287246704</t>
   </si>
   <si>
     <t xml:space="preserve">3.26165771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29302000999451</t>
+    <t xml:space="preserve">3.29301977157593</t>
   </si>
   <si>
     <t xml:space="preserve">3.32438182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90099334716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09700703620911</t>
+    <t xml:space="preserve">2.90099382400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09700679779053</t>
   </si>
   <si>
     <t xml:space="preserve">3.05780434608459</t>
@@ -2246,13 +2246,13 @@
     <t xml:space="preserve">2.94803690910339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00292038917542</t>
+    <t xml:space="preserve">3.00292015075684</t>
   </si>
   <si>
     <t xml:space="preserve">3.13620948791504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03036260604858</t>
+    <t xml:space="preserve">3.03036236763</t>
   </si>
   <si>
     <t xml:space="preserve">3.21461486816406</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">3.22245526313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24205636978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23813629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36750555038452</t>
+    <t xml:space="preserve">3.24205684661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24597668647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23813652992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36750483512878</t>
   </si>
   <si>
     <t xml:space="preserve">3.34006333351135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45767068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59880089759827</t>
+    <t xml:space="preserve">3.45767116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59880018234253</t>
   </si>
   <si>
     <t xml:space="preserve">3.37142539024353</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">3.52039480209351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54391694068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72424864768982</t>
+    <t xml:space="preserve">3.54391670227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7242488861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.81049466133118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92026233673096</t>
+    <t xml:space="preserve">3.9202618598938</t>
   </si>
   <si>
     <t xml:space="preserve">4.3358097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32796859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32012891769409</t>
+    <t xml:space="preserve">4.32796907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32012844085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.23388290405273</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">4.16331768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07707166671753</t>
+    <t xml:space="preserve">4.07707262039185</t>
   </si>
   <si>
     <t xml:space="preserve">4.21820211410522</t>
@@ -2330,109 +2330,109 @@
     <t xml:space="preserve">4.25740432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19468069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208928108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481339454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84577703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321925163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225489616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169062614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74384999275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10059356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91634154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946455001831</t>
+    <t xml:space="preserve">4.19467973709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481410980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401608467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70072722434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265402793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145806312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385023117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298573493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660749435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10059404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91634082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946526527405</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13979721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14763736724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01434755325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95162415504456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9437837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88889956474304</t>
+    <t xml:space="preserve">4.1397967338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14763689041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01434850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95162391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94378328323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8889000415802</t>
   </si>
   <si>
     <t xml:space="preserve">4.05355072021484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06923198699951</t>
+    <t xml:space="preserve">4.06923246383667</t>
   </si>
   <si>
     <t xml:space="preserve">4.030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89282035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810273170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242098808289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85753726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86537861824036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617568969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105893135071</t>
+    <t xml:space="preserve">3.89282011985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810225486755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753750801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86537766456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617545127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105916976929</t>
   </si>
   <si>
     <t xml:space="preserve">3.90458106994629</t>
@@ -2441,49 +2441,49 @@
     <t xml:space="preserve">3.90850114822388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.779132604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75561118125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777054786682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657410621643</t>
+    <t xml:space="preserve">3.77913236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.755610704422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657386779785</t>
   </si>
   <si>
     <t xml:space="preserve">3.88497924804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96730518341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02218866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594264984131</t>
+    <t xml:space="preserve">3.96730470657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02218818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594288825989</t>
   </si>
   <si>
     <t xml:space="preserve">3.76345181465149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75953149795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64584374427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544461250305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016295433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56351804733276</t>
+    <t xml:space="preserve">3.75953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6458432674408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66936469078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016247749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56351852416992</t>
   </si>
   <si>
     <t xml:space="preserve">3.56743860244751</t>
@@ -2492,115 +2492,115 @@
     <t xml:space="preserve">3.59095978736877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48903322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44199013710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38710641860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33222246170044</t>
+    <t xml:space="preserve">3.48903274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119235038757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44198966026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3871066570282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654143333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3322229385376</t>
   </si>
   <si>
     <t xml:space="preserve">3.40278744697571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42238855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43807005882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49295353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55175757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55567765235901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50079393386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51255488395691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37926554679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43414926528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630887031555</t>
+    <t xml:space="preserve">3.42238831520081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43806982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551179885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49295330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55175733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55567741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50079369544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51255512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37926602363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43414902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630910873413</t>
   </si>
   <si>
     <t xml:space="preserve">3.4615912437439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44983077049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20677447319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17541265487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52823567390442</t>
+    <t xml:space="preserve">3.44983053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189051628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20677423477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17541217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52823543548584</t>
   </si>
   <si>
     <t xml:space="preserve">3.53215599060059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53607630729675</t>
+    <t xml:space="preserve">3.53607654571533</t>
   </si>
   <si>
     <t xml:space="preserve">4.10843420028687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99866652488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252084732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0927529335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06139183044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2887659072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24956369400024</t>
+    <t xml:space="preserve">3.99866700172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2025203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13195657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09275341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06139135360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28876686096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2495641708374</t>
   </si>
   <si>
     <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3985333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3593316078186</t>
+    <t xml:space="preserve">4.39853382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35933113098145</t>
   </si>
   <si>
     <t xml:space="preserve">4.69647359848022</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">4.75919771194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82976293563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72783613204956</t>
+    <t xml:space="preserve">4.82976245880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7278356552124</t>
   </si>
   <si>
     <t xml:space="preserve">4.74351739883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703882217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487897872925</t>
+    <t xml:space="preserve">4.76703834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487945556641</t>
   </si>
   <si>
     <t xml:space="preserve">4.73567676544189</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">4.99441337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94737005233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86112451553345</t>
+    <t xml:space="preserve">4.94736957550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86112546920776</t>
   </si>
   <si>
     <t xml:space="preserve">4.84544324874878</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">4.91600847244263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93952989578247</t>
+    <t xml:space="preserve">4.93953037261963</t>
   </si>
   <si>
     <t xml:space="preserve">5.04929733276367</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">5.58245277404785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68438005447388</t>
+    <t xml:space="preserve">5.68437957763672</t>
   </si>
   <si>
     <t xml:space="preserve">5.59813404083252</t>
@@ -2669,34 +2669,34 @@
     <t xml:space="preserve">5.62949562072754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71574115753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69222021102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66869926452637</t>
+    <t xml:space="preserve">5.7157416343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69222068786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66869831085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.66085815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72358274459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78630685806274</t>
+    <t xml:space="preserve">5.72358226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78630638122559</t>
   </si>
   <si>
     <t xml:space="preserve">6.08424663543701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17833232879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14697074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288457870483</t>
+    <t xml:space="preserve">6.17833280563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14697122573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288410186768</t>
   </si>
   <si>
     <t xml:space="preserve">5.97447919845581</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">6.03720331192017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15080690383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00474452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11834812164307</t>
+    <t xml:space="preserve">6.15080642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11834859848022</t>
   </si>
   <si>
     <t xml:space="preserve">6.49161624908447</t>
@@ -2723,103 +2723,103 @@
     <t xml:space="preserve">6.4266996383667</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2644100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41047096252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39424180984497</t>
+    <t xml:space="preserve">6.26440954208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41047143936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39424228668213</t>
   </si>
   <si>
     <t xml:space="preserve">6.4429292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96225881576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077854156494</t>
+    <t xml:space="preserve">6.96225786209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077806472778</t>
   </si>
   <si>
     <t xml:space="preserve">7.43290090560913</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0009183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83862686157227</t>
+    <t xml:space="preserve">8.00091648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83862638473511</t>
   </si>
   <si>
     <t xml:space="preserve">7.87108421325684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78994035720825</t>
+    <t xml:space="preserve">7.78994083404541</t>
   </si>
   <si>
     <t xml:space="preserve">7.91977214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95223093032837</t>
+    <t xml:space="preserve">7.95222997665405</t>
   </si>
   <si>
     <t xml:space="preserve">7.90354251861572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60139274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64196395874023</t>
+    <t xml:space="preserve">8.60139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.56081867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43910026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19566631317139</t>
+    <t xml:space="preserve">8.43910121917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19566535949707</t>
   </si>
   <si>
     <t xml:space="preserve">8.23623752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01714706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06583213806152</t>
+    <t xml:space="preserve">8.01714611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06583309173584</t>
   </si>
   <si>
     <t xml:space="preserve">7.96845865249634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40044212341309</t>
+    <t xml:space="preserve">7.40044260025024</t>
   </si>
   <si>
     <t xml:space="preserve">7.25438117980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48158740997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64387845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56273317337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69256496429443</t>
+    <t xml:space="preserve">7.4815878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64387798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5627326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69256544113159</t>
   </si>
   <si>
     <t xml:space="preserve">7.72502374649048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75748205184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62764883041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535921096802</t>
+    <t xml:space="preserve">7.75748157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62764835357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46535873413086</t>
   </si>
   <si>
     <t xml:space="preserve">7.30306816101074</t>
@@ -2831,97 +2831,97 @@
     <t xml:space="preserve">6.81619691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15700626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23815202713013</t>
+    <t xml:space="preserve">7.15700674057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23815250396729</t>
   </si>
   <si>
     <t xml:space="preserve">7.38421392440796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70879364013672</t>
+    <t xml:space="preserve">7.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">7.61142063140869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66010713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53027486801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74125242233276</t>
+    <t xml:space="preserve">7.66010665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53027534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74125289916992</t>
   </si>
   <si>
     <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15509223937988</t>
+    <t xml:space="preserve">8.1550931930542</t>
   </si>
   <si>
     <t xml:space="preserve">8.96654605865479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84482574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5202465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39853000640869</t>
+    <t xml:space="preserve">8.84482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368141174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52024555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39852809906006</t>
   </si>
   <si>
     <t xml:space="preserve">8.47967338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3173828125</t>
+    <t xml:space="preserve">8.31738376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.08206272125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11452102661133</t>
+    <t xml:space="preserve">8.11452007293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.03337478637695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04960346221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04768943786621</t>
+    <t xml:space="preserve">8.04960441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04769039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4452428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40344905853271</t>
+    <t xml:space="preserve">9.16940784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44524192810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40345001220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.23627758026123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48703575134277</t>
+    <t xml:space="preserve">9.48703670501709</t>
   </si>
   <si>
     <t xml:space="preserve">9.77958679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6124153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5706205368042</t>
+    <t xml:space="preserve">9.61241436004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57062149047852</t>
   </si>
   <si>
     <t xml:space="preserve">9.52882862091064</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779296875</t>
+    <t xml:space="preserve">9.73779392242432</t>
   </si>
   <si>
     <t xml:space="preserve">9.65420818328857</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">9.90496635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31986236572266</t>
+    <t xml:space="preserve">9.31986331939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
@@ -2948,49 +2948,49 @@
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15268993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7765531539917</t>
+    <t xml:space="preserve">9.15269184112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77655220031738</t>
   </si>
   <si>
     <t xml:space="preserve">8.35862255096436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6093807220459</t>
+    <t xml:space="preserve">8.60937976837158</t>
   </si>
   <si>
     <t xml:space="preserve">9.19448375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98551750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11089611053467</t>
+    <t xml:space="preserve">8.98551845550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11089706420898</t>
   </si>
   <si>
     <t xml:space="preserve">9.36165618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06910514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9437255859375</t>
+    <t xml:space="preserve">9.06910419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94372463226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.90193176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81834506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52579307556152</t>
+    <t xml:space="preserve">8.81834602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52579402923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.73475933074951</t>
@@ -3011,31 +3011,31 @@
     <t xml:space="preserve">7.82366991043091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67321538925171</t>
+    <t xml:space="preserve">7.67321443557739</t>
   </si>
   <si>
     <t xml:space="preserve">7.12154626846313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07139444351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10482788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68993234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589017868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053869247437</t>
+    <t xml:space="preserve">7.0713939666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10482835769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68993091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589113235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053821563721</t>
   </si>
   <si>
     <t xml:space="preserve">7.80695247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62306261062622</t>
+    <t xml:space="preserve">7.62306308746338</t>
   </si>
   <si>
     <t xml:space="preserve">7.99084281921387</t>
@@ -3050,28 +3050,28 @@
     <t xml:space="preserve">8.27503490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40041446685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10786247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48400020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30011177062988</t>
+    <t xml:space="preserve">8.40041542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1078634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48400115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30011081695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.35026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24996089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69829034805298</t>
+    <t xml:space="preserve">8.24995994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87382078170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69829082489014</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">7.91561508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7818775177002</t>
+    <t xml:space="preserve">7.78187656402588</t>
   </si>
   <si>
     <t xml:space="preserve">7.60634613037109</t>
@@ -3095,34 +3095,34 @@
     <t xml:space="preserve">7.89889764785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79859352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202886581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63977956771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41302824020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64850234985352</t>
+    <t xml:space="preserve">7.79859447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023504257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41302871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64850187301636</t>
   </si>
   <si>
     <t xml:space="preserve">8.24154376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21538066864014</t>
+    <t xml:space="preserve">8.21537971496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.28514957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32003402709961</t>
+    <t xml:space="preserve">8.32003498077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">8.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59039211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64271926879883</t>
+    <t xml:space="preserve">8.59039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64271831512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.63399791717529</t>
@@ -3164,16 +3164,16 @@
     <t xml:space="preserve">8.17177391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1281681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93630218505859</t>
+    <t xml:space="preserve">8.12816715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93630123138428</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827077865601</t>
+    <t xml:space="preserve">7.71827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.77931928634644</t>
@@ -3182,40 +3182,40 @@
     <t xml:space="preserve">7.95374345779419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14560985565186</t>
+    <t xml:space="preserve">8.14561080932617</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86653184890747</t>
+    <t xml:space="preserve">7.86653232574463</t>
   </si>
   <si>
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804063796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65722274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76187705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978052139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6921067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70082807540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5961742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535587310791</t>
+    <t xml:space="preserve">7.78804016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65722179412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76187658309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978004455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69210767745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59617376327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46535634994507</t>
   </si>
   <si>
     <t xml:space="preserve">7.54384660720825</t>
@@ -3224,70 +3224,70 @@
     <t xml:space="preserve">7.73571395874023</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50024080276489</t>
+    <t xml:space="preserve">7.50024127960205</t>
   </si>
   <si>
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.447913646698</t>
+    <t xml:space="preserve">7.55256795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44791316986084</t>
   </si>
   <si>
     <t xml:space="preserve">7.53512620925903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51768350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50896167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57001113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80548334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74443435668945</t>
+    <t xml:space="preserve">7.5176830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50896120071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57001066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80548286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74443483352661</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77353858947754</t>
+    <t xml:space="preserve">8.77353763580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.72121047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48573684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5031795501709</t>
+    <t xml:space="preserve">8.48573780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50318050384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619808197021</t>
+    <t xml:space="preserve">8.41596698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3461971282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.02351379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37236213684082</t>
+    <t xml:space="preserve">8.37236309051514</t>
   </si>
   <si>
     <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83164644241333</t>
+    <t xml:space="preserve">7.83164596557617</t>
   </si>
   <si>
     <t xml:space="preserve">7.66594362258911</t>
@@ -3296,16 +3296,16 @@
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9711856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68338680267334</t>
+    <t xml:space="preserve">7.97118711471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338632583618</t>
   </si>
   <si>
     <t xml:space="preserve">7.33453750610352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1688346862793</t>
+    <t xml:space="preserve">7.16883516311646</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">7.28221082687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13395071029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12522840499878</t>
+    <t xml:space="preserve">7.13395023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12522888183594</t>
   </si>
   <si>
     <t xml:space="preserve">6.78510189056396</t>
@@ -3332,40 +3332,40 @@
     <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6368408203125</t>
+    <t xml:space="preserve">6.63684129714966</t>
   </si>
   <si>
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75315618515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43047142028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49152040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2734899520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39558601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38686466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3519811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31709623336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47407674789429</t>
+    <t xml:space="preserve">7.7531566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43919229507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43047189712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49151945114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27348899841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39558553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38686561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35198068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3170952796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47407722473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.29093170166016</t>
@@ -3386,25 +3386,25 @@
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03223419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10200500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15433216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05839729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09328269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00607109069824</t>
+    <t xml:space="preserve">7.85781145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03223514556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1020040512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15433120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09328365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
@@ -3419,22 +3419,22 @@
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990751266479</t>
+    <t xml:space="preserve">7.97990703582764</t>
   </si>
   <si>
     <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90141725540161</t>
+    <t xml:space="preserve">7.90141677856445</t>
   </si>
   <si>
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885900497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82292652130127</t>
+    <t xml:space="preserve">7.91885852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82292556762695</t>
   </si>
   <si>
     <t xml:space="preserve">8.11944675445557</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">8.337477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5293436050415</t>
+    <t xml:space="preserve">8.52934265136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.94796180725098</t>
@@ -3458,16 +3458,16 @@
     <t xml:space="preserve">8.87819290161133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65144062042236</t>
+    <t xml:space="preserve">8.89563465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65144157409668</t>
   </si>
   <si>
     <t xml:space="preserve">8.6601619720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79098033905029</t>
+    <t xml:space="preserve">8.79097938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.70376777648926</t>
@@ -3476,13 +3476,13 @@
     <t xml:space="preserve">8.71248912811279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86075019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93051910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62527751922607</t>
+    <t xml:space="preserve">8.86074924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93052005767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62527656555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.56422805786133</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">8.46829509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6863260269165</t>
+    <t xml:space="preserve">8.68632507324219</t>
   </si>
   <si>
     <t xml:space="preserve">9.15727043151855</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">8.91307735443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96540451049805</t>
+    <t xml:space="preserve">8.96540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00028896331787</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">8.66888236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91124534606934</t>
+    <t xml:space="preserve">8.91124629974365</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8567419052124</t>
+    <t xml:space="preserve">8.82040691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85674285888672</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422756195068</t>
+    <t xml:space="preserve">8.58422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498817443848</t>
+    <t xml:space="preserve">8.77498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3584,19 +3584,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38438320159912</t>
+    <t xml:space="preserve">8.49339008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3843822479248</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453788757324</t>
+    <t xml:space="preserve">8.18453884124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896350860596</t>
+    <t xml:space="preserve">8.33896446228027</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09370040893555</t>
+    <t xml:space="preserve">8.09369945526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04828071594238</t>
+    <t xml:space="preserve">8.04827976226807</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644821166992</t>
+    <t xml:space="preserve">8.06644916534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3662,40 +3662,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919696807861</t>
+    <t xml:space="preserve">8.03919792175293</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94835901260376</t>
+    <t xml:space="preserve">8.00286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9483585357666</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9029393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385461807251</t>
+    <t xml:space="preserve">7.95744276046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90293884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385557174683</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85752010345459</t>
+    <t xml:space="preserve">7.85751962661743</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210136413574</t>
+    <t xml:space="preserve">7.81210088729858</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126245498657</t>
+    <t xml:space="preserve">7.72126293182373</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568807601929</t>
+    <t xml:space="preserve">7.87568855285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950777053833</t>
+    <t xml:space="preserve">7.63950824737549</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49416637420654</t>
+    <t xml:space="preserve">7.4941668510437</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41241216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4487476348877</t>
+    <t xml:space="preserve">7.4124116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44874715805054</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112440109253</t>
+    <t xml:space="preserve">6.73112392425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7220401763916</t>
+    <t xml:space="preserve">6.72204065322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486675262451</t>
+    <t xml:space="preserve">6.59486722946167</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699247360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31248998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790967941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775308609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767669677734</t>
+    <t xml:space="preserve">7.01272296905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31249046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767621994019</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393339157104</t>
+    <t xml:space="preserve">7.79393291473389</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3845,31 +3845,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96652698516846</t>
+    <t xml:space="preserve">7.76668262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9665265083313</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.475998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607717514038</t>
+    <t xml:space="preserve">7.63042402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47599840164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607669830322</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523921966553</t>
+    <t xml:space="preserve">7.28523874282837</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264562606812</t>
+    <t xml:space="preserve">7.11264514923096</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225652694702</t>
+    <t xml:space="preserve">7.61225700378418</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890279769897</t>
+    <t xml:space="preserve">7.24890327453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -4287,6 +4287,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8000001907349</t>
   </si>
 </sst>
 </file>
@@ -27003,7 +27006,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G861" t="s">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27029,7 +27032,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G862" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27055,7 +27058,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G863" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27081,7 +27084,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G864" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27107,7 +27110,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G865" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27133,7 +27136,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G866" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27159,7 +27162,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G867" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27185,7 +27188,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27211,7 +27214,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G869" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27237,7 +27240,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G870" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27263,7 +27266,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G871" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27289,7 +27292,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G872" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27315,7 +27318,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27367,7 +27370,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G875" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27393,7 +27396,7 @@
         <v>6.75</v>
       </c>
       <c r="G876" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27419,7 +27422,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G877" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27445,7 +27448,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G878" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27471,7 +27474,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G879" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27497,7 +27500,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G880" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27523,7 +27526,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G881" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27549,7 +27552,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G882" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27575,7 +27578,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G883" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27601,7 +27604,7 @@
         <v>6.5</v>
       </c>
       <c r="G884" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27627,7 +27630,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G885" t="s">
-        <v>657</v>
+        <v>537</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27679,7 +27682,7 @@
         <v>6.5</v>
       </c>
       <c r="G887" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28095,7 +28098,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G903" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28173,7 +28176,7 @@
         <v>6.75</v>
       </c>
       <c r="G906" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28277,7 +28280,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28355,7 +28358,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G913" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28381,7 +28384,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G914" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29109,7 +29112,7 @@
         <v>6.75</v>
       </c>
       <c r="G942" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29161,7 +29164,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G944" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29343,7 +29346,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G951" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -29369,7 +29372,7 @@
         <v>6.5</v>
       </c>
       <c r="G952" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -29577,7 +29580,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G960" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29655,7 +29658,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G963" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -29707,7 +29710,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G965" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30747,7 +30750,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1005" t="s">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30903,7 +30906,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1011" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30929,7 +30932,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31111,7 +31114,7 @@
         <v>6.75</v>
       </c>
       <c r="G1019" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31137,7 +31140,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31163,7 +31166,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1021" t="s">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31267,7 +31270,7 @@
         <v>6.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31293,7 +31296,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1026" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31319,7 +31322,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1027" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31345,7 +31348,7 @@
         <v>6.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31423,7 +31426,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1031" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31449,7 +31452,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1032" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31527,7 +31530,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1035" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31839,7 +31842,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31943,7 +31946,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1051" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -38391,7 +38394,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1299" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38417,7 +38420,7 @@
         <v>6.5</v>
       </c>
       <c r="G1300" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38443,7 +38446,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1301" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38469,7 +38472,7 @@
         <v>6.5</v>
       </c>
       <c r="G1302" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38937,7 +38940,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1320" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38963,7 +38966,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1321" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -69521,13 +69524,13 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.649525463</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>14622</v>
       </c>
       <c r="C2497" t="n">
-        <v>12.8000001907349</v>
+        <v>12.8500003814697</v>
       </c>
       <c r="D2497" t="n">
         <v>12.4499998092651</v>
@@ -69542,6 +69545,32 @@
         <v>1414</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6911458333</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>6607</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="1430">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19253504276276</t>
+    <t xml:space="preserve">1.19253516197205</t>
   </si>
   <si>
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355509757996</t>
+    <t xml:space="preserve">1.21355521678925</t>
   </si>
   <si>
     <t xml:space="preserve">1.22546637058258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20654857158661</t>
+    <t xml:space="preserve">1.20654833316803</t>
   </si>
   <si>
     <t xml:space="preserve">1.23177242279053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24998986721039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26330244541168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27311170101166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26120030879974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718701839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20794975757599</t>
+    <t xml:space="preserve">1.24998962879181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26330232620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27311158180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26120042800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718713760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2079496383667</t>
   </si>
   <si>
     <t xml:space="preserve">1.19323563575745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501842975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814050197601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24578583240509</t>
+    <t xml:space="preserve">1.17501831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19814038276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2457857131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.23457515239716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495640277863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1827255487442</t>
+    <t xml:space="preserve">1.21495628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18272578716278</t>
   </si>
   <si>
     <t xml:space="preserve">1.17992305755615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17641973495483</t>
+    <t xml:space="preserve">1.17641961574554</t>
   </si>
   <si>
     <t xml:space="preserve">1.12457048892975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12807381153107</t>
+    <t xml:space="preserve">1.12807369232178</t>
   </si>
   <si>
     <t xml:space="preserve">1.10284972190857</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01596713066101</t>
+    <t xml:space="preserve">1.01596689224243</t>
   </si>
   <si>
     <t xml:space="preserve">1.0250757932663</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">1.02297377586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04329311847687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09654378890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11335968971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1105569601059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09304046630859</t>
+    <t xml:space="preserve">1.04329299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09654366970062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11335980892181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11055707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09304022789001</t>
   </si>
   <si>
     <t xml:space="preserve">1.12106704711914</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">1.13017570972443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15610039234161</t>
+    <t xml:space="preserve">1.1561005115509</t>
   </si>
   <si>
     <t xml:space="preserve">1.10004699230194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1315770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227784633636</t>
+    <t xml:space="preserve">1.13157713413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705363750458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227772712708</t>
   </si>
   <si>
     <t xml:space="preserve">1.1182644367218</t>
@@ -170,37 +170,37 @@
     <t xml:space="preserve">1.14909374713898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17852187156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17011368274689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412721157074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081439495087</t>
+    <t xml:space="preserve">1.17852175235748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17011380195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412697315216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081451416016</t>
   </si>
   <si>
     <t xml:space="preserve">1.16310703754425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22616720199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508512020111</t>
+    <t xml:space="preserve">1.22616732120514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508500099182</t>
   </si>
   <si>
     <t xml:space="preserve">1.24088108539581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20514714717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19113385677338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22686791419983</t>
+    <t xml:space="preserve">1.20514702796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113373756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22686779499054</t>
   </si>
   <si>
     <t xml:space="preserve">1.22196304798126</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17221570014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183444976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19743978977203</t>
+    <t xml:space="preserve">1.17221581935883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183456897736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19743967056274</t>
   </si>
   <si>
     <t xml:space="preserve">1.20374572277069</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">1.20304501056671</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23807847499847</t>
+    <t xml:space="preserve">1.23807835578918</t>
   </si>
   <si>
     <t xml:space="preserve">1.23317384719849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19954180717468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22476601600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845972537994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916043758392</t>
+    <t xml:space="preserve">1.19954192638397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2247656583786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916055679321</t>
   </si>
   <si>
     <t xml:space="preserve">1.22896981239319</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">1.21215379238129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22266364097595</t>
+    <t xml:space="preserve">1.22266376018524</t>
   </si>
   <si>
     <t xml:space="preserve">1.2920298576355</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28712511062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28151965141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788749217987</t>
+    <t xml:space="preserve">1.28712499141693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28151977062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788773059845</t>
   </si>
   <si>
     <t xml:space="preserve">1.23737788200378</t>
@@ -275,55 +275,55 @@
     <t xml:space="preserve">1.20865046977997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15469908714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138638973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11896502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036621570587</t>
+    <t xml:space="preserve">1.15469884872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138627052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1189649105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
     <t xml:space="preserve">1.13648164272308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14629113674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14208698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07202041149139</t>
+    <t xml:space="preserve">1.14629101753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14208710193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0720202922821</t>
   </si>
   <si>
     <t xml:space="preserve">1.08463227748871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501352787018</t>
+    <t xml:space="preserve">1.06501376628876</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253037929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902693748474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05800700187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10144829750061</t>
+    <t xml:space="preserve">1.08253014087677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902681827545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05800688266754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10144853591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.10355031490326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09514236450195</t>
+    <t xml:space="preserve">1.09514248371124</t>
   </si>
   <si>
     <t xml:space="preserve">1.11966574192047</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">1.09934639930725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11265909671783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1568009853363</t>
+    <t xml:space="preserve">1.11265897750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15680122375488</t>
   </si>
   <si>
     <t xml:space="preserve">1.34528040885925</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">1.4868152141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48821675777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45178186893463</t>
+    <t xml:space="preserve">1.48821663856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45178174972534</t>
   </si>
   <si>
     <t xml:space="preserve">1.41534721851349</t>
@@ -356,61 +356,61 @@
     <t xml:space="preserve">1.45738708972931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40133380889893</t>
+    <t xml:space="preserve">1.40133368968964</t>
   </si>
   <si>
     <t xml:space="preserve">1.46999931335449</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43776845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375540733337</t>
+    <t xml:space="preserve">1.43776857852936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375516891479</t>
   </si>
   <si>
     <t xml:space="preserve">1.4363671541214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936038970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674852371216</t>
+    <t xml:space="preserve">1.42936062812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674864292145</t>
   </si>
   <si>
     <t xml:space="preserve">1.42235386371613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41814982891083</t>
+    <t xml:space="preserve">1.41814959049225</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4279590845108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48120999336243</t>
+    <t xml:space="preserve">1.42795944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48120975494385</t>
   </si>
   <si>
     <t xml:space="preserve">1.69421255588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338312625885</t>
+    <t xml:space="preserve">1.66338348388672</t>
   </si>
   <si>
     <t xml:space="preserve">1.80071377754211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84555685520172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79230606555939</t>
+    <t xml:space="preserve">1.84555661678314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79230618476868</t>
   </si>
   <si>
     <t xml:space="preserve">1.79090452194214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77268731594086</t>
+    <t xml:space="preserve">1.77268719673157</t>
   </si>
   <si>
     <t xml:space="preserve">1.73064732551575</t>
@@ -419,55 +419,55 @@
     <t xml:space="preserve">1.71663391590118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670036792755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84275376796722</t>
+    <t xml:space="preserve">1.78670072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275412559509</t>
   </si>
   <si>
     <t xml:space="preserve">1.8259379863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82313525676727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8399510383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83855009078979</t>
+    <t xml:space="preserve">1.82313549518585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995139598846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854997158051</t>
   </si>
   <si>
     <t xml:space="preserve">1.84415519237518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8301420211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874047756195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192457675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294439315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835958480835</t>
+    <t xml:space="preserve">1.83014214038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472718715668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874035835266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192445755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294463157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835910797119</t>
   </si>
   <si>
     <t xml:space="preserve">1.8693790435791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9954993724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07257270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02913165092468</t>
+    <t xml:space="preserve">1.99549925327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0725724697113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02913117408752</t>
   </si>
   <si>
     <t xml:space="preserve">2.08798742294312</t>
@@ -476,46 +476,46 @@
     <t xml:space="preserve">2.04034209251404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99830186367035</t>
+    <t xml:space="preserve">1.99830222129822</t>
   </si>
   <si>
     <t xml:space="preserve">2.03053283691406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01932215690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970364570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066597938538</t>
+    <t xml:space="preserve">2.01932191848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970352649689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359288215637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066621780396</t>
   </si>
   <si>
     <t xml:space="preserve">2.15945553779602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989391326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339269161224</t>
+    <t xml:space="preserve">1.98989379405975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339281082153</t>
   </si>
   <si>
     <t xml:space="preserve">1.97167646884918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95345938205719</t>
+    <t xml:space="preserve">1.95345914363861</t>
   </si>
   <si>
     <t xml:space="preserve">2.01651954650879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250625610352</t>
+    <t xml:space="preserve">2.00250601768494</t>
   </si>
   <si>
     <t xml:space="preserve">1.98428869247437</t>
@@ -524,55 +524,55 @@
     <t xml:space="preserve">1.9786833524704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93944585323334</t>
+    <t xml:space="preserve">1.93944609165192</t>
   </si>
   <si>
     <t xml:space="preserve">1.91982734203339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377382278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8679780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85676729679108</t>
+    <t xml:space="preserve">1.863774061203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86797785758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918865680695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85676753520966</t>
   </si>
   <si>
     <t xml:space="preserve">1.78950309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80631923675537</t>
+    <t xml:space="preserve">1.80631947517395</t>
   </si>
   <si>
     <t xml:space="preserve">1.90301144123077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89880740642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9100182056427</t>
+    <t xml:space="preserve">1.89880728721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001832485199</t>
   </si>
   <si>
     <t xml:space="preserve">1.99690079689026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98849296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224870204926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766341686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186745166779</t>
+    <t xml:space="preserve">1.98849236965179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98569023609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224882125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766317844391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186697483063</t>
   </si>
   <si>
     <t xml:space="preserve">1.96326875686646</t>
@@ -581,49 +581,49 @@
     <t xml:space="preserve">1.97027540206909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96607112884521</t>
+    <t xml:space="preserve">1.96607136726379</t>
   </si>
   <si>
     <t xml:space="preserve">2.00390720367432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07397413253784</t>
+    <t xml:space="preserve">2.07397389411926</t>
   </si>
   <si>
     <t xml:space="preserve">2.18888330459595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1650607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13283014297485</t>
+    <t xml:space="preserve">2.16506028175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1328296661377</t>
   </si>
   <si>
     <t xml:space="preserve">2.06416487693787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09639525413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601400375366</t>
+    <t xml:space="preserve">2.09639549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601376533508</t>
   </si>
   <si>
     <t xml:space="preserve">2.09499430656433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11321139335632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14404082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002705574036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14824461936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13423132896423</t>
+    <t xml:space="preserve">2.1132116317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14404058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002753257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14824485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13423156738281</t>
   </si>
   <si>
     <t xml:space="preserve">2.14123797416687</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">2.13703417778015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11181020736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09779691696167</t>
+    <t xml:space="preserve">2.11180996894836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09779644012451</t>
   </si>
   <si>
     <t xml:space="preserve">2.118816614151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10200095176697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741518974304</t>
+    <t xml:space="preserve">2.10200071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11741542816162</t>
   </si>
   <si>
     <t xml:space="preserve">2.24213409423828</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">2.4873673915863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316383361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46494626998901</t>
+    <t xml:space="preserve">2.49297308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316335678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46494603157043</t>
   </si>
   <si>
     <t xml:space="preserve">2.40328741073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099967002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48036074638367</t>
+    <t xml:space="preserve">2.52099943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48036098480225</t>
   </si>
   <si>
     <t xml:space="preserve">2.46634769439697</t>
@@ -683,34 +683,34 @@
     <t xml:space="preserve">2.44392609596252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43972229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47615694999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45513677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437403678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47335433959961</t>
+    <t xml:space="preserve">2.43972253799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47615671157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45513653755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47335386276245</t>
   </si>
   <si>
     <t xml:space="preserve">2.65552759170532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71858763694763</t>
+    <t xml:space="preserve">2.71858787536621</t>
   </si>
   <si>
     <t xml:space="preserve">2.70457434654236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84751081466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865432739258</t>
+    <t xml:space="preserve">2.84751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865456581116</t>
   </si>
   <si>
     <t xml:space="preserve">3.11096143722534</t>
@@ -728,55 +728,55 @@
     <t xml:space="preserve">3.71003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58040738105774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6925151348114</t>
+    <t xml:space="preserve">3.58040833473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251489639282</t>
   </si>
   <si>
     <t xml:space="preserve">3.66098427772522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69601845741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78360104560852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176148414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19349193572998</t>
+    <t xml:space="preserve">3.69601798057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7836012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95176100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386756896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19349145889282</t>
   </si>
   <si>
     <t xml:space="preserve">4.16896820068359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1129150390625</t>
+    <t xml:space="preserve">4.11291456222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.03233861923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30910110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30559825897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55433464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69797134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50023508071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256200790405</t>
+    <t xml:space="preserve">4.3091025352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30559778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55433511734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6979718208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50023460388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256153106689</t>
   </si>
   <si>
     <t xml:space="preserve">5.10085535049438</t>
@@ -797,64 +797,64 @@
     <t xml:space="preserve">6.3970890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76143550872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518251419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858238220215</t>
+    <t xml:space="preserve">6.76143503189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238851547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0936918258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858285903931</t>
   </si>
   <si>
     <t xml:space="preserve">6.7843337059021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35626554489136</t>
+    <t xml:space="preserve">6.3562650680542</t>
   </si>
   <si>
     <t xml:space="preserve">6.53252840042114</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35266828536987</t>
+    <t xml:space="preserve">6.35266876220703</t>
   </si>
   <si>
     <t xml:space="preserve">6.07208585739136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.323890209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900156021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094484329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4030294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841960906982</t>
+    <t xml:space="preserve">6.32389068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40302848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15841913223267</t>
   </si>
   <si>
     <t xml:space="preserve">6.19798851013184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37425088882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47137689590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15122509002686</t>
+    <t xml:space="preserve">6.37425184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47137641906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32748746871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15122413635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.11165475845337</t>
@@ -863,61 +863,61 @@
     <t xml:space="preserve">5.93898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85265636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90661478042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89582252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75193500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69437885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70157337188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36703300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87421607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1799783706665</t>
+    <t xml:space="preserve">5.96057224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85265684127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90661525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89582300186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75193452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69437980651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70157432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3670334815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87421655654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17997884750366</t>
   </si>
   <si>
     <t xml:space="preserve">4.97853565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96414613723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8454384803772</t>
+    <t xml:space="preserve">4.96414661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84543895721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.8778133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91018867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92457628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76989698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69075775146484</t>
+    <t xml:space="preserve">4.9101881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9245777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7698974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69075870513916</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838432312012</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">4.82385540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55046701431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51089763641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49291229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43895387649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38139820098877</t>
+    <t xml:space="preserve">4.5504674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51089811325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49291181564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43895435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38139915466309</t>
   </si>
   <si>
     <t xml:space="preserve">4.38499593734741</t>
@@ -953,67 +953,67 @@
     <t xml:space="preserve">5.03609037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85622978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80946588516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7662992477417</t>
+    <t xml:space="preserve">4.85623025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80946683883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76630020141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.68356418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67636966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59003639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62960624694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66198062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6727728843689</t>
+    <t xml:space="preserve">4.67636919021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60442590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59003734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62960577011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66198110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277240753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.74831390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75910520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9533543586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486845016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14400672912598</t>
+    <t xml:space="preserve">4.75910568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14400720596313</t>
   </si>
   <si>
     <t xml:space="preserve">5.11522912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19436693191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10803413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93536901473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7555079460144</t>
+    <t xml:space="preserve">5.19436740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10803461074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93536853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550842285156</t>
   </si>
   <si>
     <t xml:space="preserve">4.99652147293091</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">4.92097997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82025861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89220237731934</t>
+    <t xml:space="preserve">4.82025814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89220285415649</t>
   </si>
   <si>
     <t xml:space="preserve">5.05407667160034</t>
@@ -1037,34 +1037,34 @@
     <t xml:space="preserve">5.07925748825073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01810359954834</t>
+    <t xml:space="preserve">5.01810503005981</t>
   </si>
   <si>
     <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839529037476</t>
+    <t xml:space="preserve">4.94615983963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839576721191</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393678665161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60804557800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8994197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77711486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978141784668</t>
+    <t xml:space="preserve">5.60804748535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89942026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77711534500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978094100952</t>
   </si>
   <si>
     <t xml:space="preserve">6.18000221252441</t>
@@ -1073,64 +1073,64 @@
     <t xml:space="preserve">6.20877981185913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52533340454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03613710403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8958477973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527681350708</t>
+    <t xml:space="preserve">6.52533388137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0361385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89584684371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527729034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.13685941696167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69802284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12968921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43904781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704746246338</t>
+    <t xml:space="preserve">7.69802331924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43904876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.29518508911133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42465972900391</t>
+    <t xml:space="preserve">10.2160692214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42466068267822</t>
   </si>
   <si>
     <t xml:space="preserve">8.61890888214111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22321605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80594110488892</t>
+    <t xml:space="preserve">8.22321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0145788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80593967437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10091209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98580121994019</t>
+    <t xml:space="preserve">7.99299573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10091114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98580026626587</t>
   </si>
   <si>
     <t xml:space="preserve">7.88507843017578</t>
@@ -1142,34 +1142,34 @@
     <t xml:space="preserve">7.41024780273438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54694032669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499799728394</t>
+    <t xml:space="preserve">7.54694080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499704360962</t>
   </si>
   <si>
     <t xml:space="preserve">7.45341396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52535629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38866424560547</t>
+    <t xml:space="preserve">7.52535820007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38866472244263</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84191179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8491063117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04335784912109</t>
+    <t xml:space="preserve">7.8419132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910678863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04335594177246</t>
   </si>
   <si>
     <t xml:space="preserve">7.92824602127075</t>
@@ -1178,28 +1178,28 @@
     <t xml:space="preserve">7.85630083084106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74838495254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1944146156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498512268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2088041305542</t>
+    <t xml:space="preserve">7.74838542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571840286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42463636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441556930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419429779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880317687988</t>
   </si>
   <si>
     <t xml:space="preserve">7.20160961151123</t>
@@ -1208,40 +1208,40 @@
     <t xml:space="preserve">7.5541353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65485763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25197076797485</t>
+    <t xml:space="preserve">7.65485811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">7.24477529525757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18721961975098</t>
+    <t xml:space="preserve">7.18722009658813</t>
   </si>
   <si>
     <t xml:space="preserve">7.10448455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00736045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340299606323</t>
+    <t xml:space="preserve">7.00735902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944505691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9534010887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.15844297409058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91742897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.856276512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89225006103516</t>
+    <t xml:space="preserve">6.91742944717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85627698898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89224910736084</t>
   </si>
   <si>
     <t xml:space="preserve">6.78793048858643</t>
@@ -1256,91 +1256,91 @@
     <t xml:space="preserve">6.98217964172363</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16203880310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045763015747</t>
+    <t xml:space="preserve">7.1620397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045715332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.02174949645996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33830261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82752323150635</t>
+    <t xml:space="preserve">7.33830308914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82752418518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.25918769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15846633911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9138560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89946603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76996803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435659408569</t>
+    <t xml:space="preserve">8.15846538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91385698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8994665145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313371658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7699670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435707092285</t>
   </si>
   <si>
     <t xml:space="preserve">7.48219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79152822494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64044523239136</t>
+    <t xml:space="preserve">6.79152631759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836111068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64044380187988</t>
   </si>
   <si>
     <t xml:space="preserve">6.4893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325119018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62605714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56130599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447406768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791856765747</t>
+    <t xml:space="preserve">6.63325071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56130647659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447263717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411195755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791904449463</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439077377319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02172470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87783718109131</t>
+    <t xml:space="preserve">6.02172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87783670425415</t>
   </si>
   <si>
     <t xml:space="preserve">5.86344814300537</t>
@@ -1349,73 +1349,73 @@
     <t xml:space="preserve">6.2591404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26633548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46777868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641687393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51813983917236</t>
+    <t xml:space="preserve">6.26633501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619512557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46777820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51814031600952</t>
   </si>
   <si>
     <t xml:space="preserve">6.46058416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29511260986328</t>
+    <t xml:space="preserve">6.2951135635376</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13683557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92819786071777</t>
+    <t xml:space="preserve">6.13683605194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92819833755493</t>
   </si>
   <si>
     <t xml:space="preserve">5.93539190292358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89222621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79869937896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97136402130127</t>
+    <t xml:space="preserve">5.89222526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79869890213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97136497497559</t>
   </si>
   <si>
     <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99294710159302</t>
+    <t xml:space="preserve">5.99294757843018</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728081703186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18719673156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25194692611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22316837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12244749069214</t>
+    <t xml:space="preserve">6.1871976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25194597244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316884994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12244701385498</t>
   </si>
   <si>
     <t xml:space="preserve">6.27352952957153</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30950164794922</t>
+    <t xml:space="preserve">6.30950212478638</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230760574341</t>
@@ -1427,34 +1427,34 @@
     <t xml:space="preserve">6.58551692962646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38323211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46564388275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326290130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30831098556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41320037841797</t>
+    <t xml:space="preserve">6.38323259353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41319990158081</t>
   </si>
   <si>
     <t xml:space="preserve">6.17345428466797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09853410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90374088287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618438720703</t>
+    <t xml:space="preserve">6.09853363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90374040603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618486404419</t>
   </si>
   <si>
     <t xml:space="preserve">5.94120025634766</t>
@@ -1463,19 +1463,19 @@
     <t xml:space="preserve">5.86628007888794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9486927986145</t>
+    <t xml:space="preserve">5.94869232177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.84380388259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59656524658203</t>
+    <t xml:space="preserve">5.59656572341919</t>
   </si>
   <si>
     <t xml:space="preserve">5.48418521881104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60405731201172</t>
+    <t xml:space="preserve">5.60405778884888</t>
   </si>
   <si>
     <t xml:space="preserve">5.55910539627075</t>
@@ -1487,37 +1487,37 @@
     <t xml:space="preserve">5.80634355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64151859283447</t>
+    <t xml:space="preserve">5.64151811599731</t>
   </si>
   <si>
     <t xml:space="preserve">5.79135990142822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76139116287231</t>
+    <t xml:space="preserve">5.76139068603516</t>
   </si>
   <si>
     <t xml:space="preserve">5.88126420974731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92621660232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078765869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55554866790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815229415894</t>
+    <t xml:space="preserve">5.92621612548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078718185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55554914474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815277099609</t>
   </si>
   <si>
     <t xml:space="preserve">6.33827924728394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12850189208984</t>
+    <t xml:space="preserve">6.30081939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12850141525269</t>
   </si>
   <si>
     <t xml:space="preserve">6.06107330322266</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">5.76888275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70145463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66399383544922</t>
+    <t xml:space="preserve">5.70145511627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66399478912354</t>
   </si>
   <si>
     <t xml:space="preserve">5.57408952713013</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">5.75389909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78386688232422</t>
+    <t xml:space="preserve">5.78386735916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62653493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61904239654541</t>
+    <t xml:space="preserve">5.62653398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61904191970825</t>
   </si>
   <si>
     <t xml:space="preserve">5.65650272369385</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">5.54412174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58158159255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50666093826294</t>
+    <t xml:space="preserve">5.58158206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5066614151001</t>
   </si>
   <si>
     <t xml:space="preserve">5.53662919998169</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">5.43174076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4692006111145</t>
+    <t xml:space="preserve">5.46920108795166</t>
   </si>
   <si>
     <t xml:space="preserve">5.31935930252075</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">5.28189992904663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42424821853638</t>
+    <t xml:space="preserve">5.42424869537354</t>
   </si>
   <si>
     <t xml:space="preserve">5.49167680740356</t>
@@ -1598,25 +1598,25 @@
     <t xml:space="preserve">5.18450307846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20697927474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5890736579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74640655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47669267654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21447086334229</t>
+    <t xml:space="preserve">5.2069787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58907413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74640703201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47669315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21447134017944</t>
   </si>
   <si>
     <t xml:space="preserve">5.13955068588257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09459829330444</t>
+    <t xml:space="preserve">5.0945987701416</t>
   </si>
   <si>
     <t xml:space="preserve">5.10958194732666</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">5.07212209701538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05713748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01967811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466176986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732887268066</t>
+    <t xml:space="preserve">5.05713796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967668533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732839584351</t>
   </si>
   <si>
     <t xml:space="preserve">4.86983633041382</t>
@@ -1652,22 +1652,22 @@
     <t xml:space="preserve">4.82488441467285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88481998443604</t>
+    <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
     <t xml:space="preserve">4.75745582580566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478872299194</t>
+    <t xml:space="preserve">4.86234426498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91478824615479</t>
   </si>
   <si>
     <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85485219955444</t>
+    <t xml:space="preserve">4.8548526763916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95224905014038</t>
@@ -1679,31 +1679,31 @@
     <t xml:space="preserve">5.08710622787476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13205814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840620040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25586748123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01612091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602521896362</t>
+    <t xml:space="preserve">5.13205862045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01612043380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602617263794</t>
   </si>
   <si>
     <t xml:space="preserve">5.99364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04215383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94475746154785</t>
+    <t xml:space="preserve">5.04215335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94475698471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.99720144271851</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">5.02716970443726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89231252670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964542388916</t>
+    <t xml:space="preserve">4.89231300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964590072632</t>
   </si>
   <si>
     <t xml:space="preserve">4.95974111557007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81739139556885</t>
+    <t xml:space="preserve">4.81739234924316</t>
   </si>
   <si>
     <t xml:space="preserve">4.7949161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78742361068726</t>
+    <t xml:space="preserve">4.78742408752441</t>
   </si>
   <si>
     <t xml:space="preserve">4.83237600326538</t>
@@ -1736,28 +1736,28 @@
     <t xml:space="preserve">4.97472524642944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90729713439941</t>
+    <t xml:space="preserve">4.90729665756226</t>
   </si>
   <si>
     <t xml:space="preserve">4.76494789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4727578163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047252655029</t>
+    <t xml:space="preserve">4.47275733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047157287598</t>
   </si>
   <si>
     <t xml:space="preserve">4.38285303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32291698455811</t>
+    <t xml:space="preserve">4.32291603088379</t>
   </si>
   <si>
     <t xml:space="preserve">4.18056726455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16558265686035</t>
+    <t xml:space="preserve">4.16558313369751</t>
   </si>
   <si>
     <t xml:space="preserve">4.30044031143188</t>
@@ -1766,55 +1766,55 @@
     <t xml:space="preserve">4.31542444229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46526575088501</t>
+    <t xml:space="preserve">4.46526527404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.45777320861816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71250295639038</t>
+    <t xml:space="preserve">4.71250343322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.10209035873413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07961416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218605041504</t>
+    <t xml:space="preserve">5.07961463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726491928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218509674072</t>
   </si>
   <si>
     <t xml:space="preserve">5.24443912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22196340560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25942373275757</t>
+    <t xml:space="preserve">5.22196292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25942325592041</t>
   </si>
   <si>
     <t xml:space="preserve">5.19948720932007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11707448959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28939199447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202640533447</t>
+    <t xml:space="preserve">5.11707401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28939151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202688217163</t>
   </si>
   <si>
     <t xml:space="preserve">5.31186771392822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41675615310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180423736572</t>
+    <t xml:space="preserve">5.41675662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180471420288</t>
   </si>
   <si>
     <t xml:space="preserve">5.4467248916626</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">5.45421695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.409264087677</t>
+    <t xml:space="preserve">5.40926456451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.89624834060669</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">5.85878801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12101030349731</t>
+    <t xml:space="preserve">6.121009349823</t>
   </si>
   <si>
     <t xml:space="preserve">6.22589921951294</t>
@@ -1844,43 +1844,43 @@
     <t xml:space="preserve">5.81383562088013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885101318359</t>
+    <t xml:space="preserve">6.00113725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885149002075</t>
   </si>
   <si>
     <t xml:space="preserve">5.82132768630981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91123247146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03110551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.008629322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377262115479</t>
+    <t xml:space="preserve">5.91123199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00862884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872358322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631181716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377214431763</t>
   </si>
   <si>
     <t xml:space="preserve">5.97116899490356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21091413497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09104204177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097856521606</t>
+    <t xml:space="preserve">6.21091461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09104156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097808837891</t>
   </si>
   <si>
     <t xml:space="preserve">6.14348554611206</t>
@@ -1889,43 +1889,43 @@
     <t xml:space="preserve">6.04608869552612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02361297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859758377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866153717041</t>
+    <t xml:space="preserve">6.02361249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859710693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142290115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866106033325</t>
   </si>
   <si>
     <t xml:space="preserve">5.69396257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72393131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7089467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916887283325</t>
+    <t xml:space="preserve">5.72393035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70894622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916934967041</t>
   </si>
   <si>
     <t xml:space="preserve">5.46170902252197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73891496658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161333084106</t>
+    <t xml:space="preserve">5.73891448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161380767822</t>
   </si>
   <si>
     <t xml:space="preserve">5.47268581390381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30019426345825</t>
+    <t xml:space="preserve">5.30019474029541</t>
   </si>
   <si>
     <t xml:space="preserve">5.33155632019043</t>
@@ -1943,25 +1943,25 @@
     <t xml:space="preserve">5.37859964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39428091049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24531078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26883220672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315141677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14338350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06497859954834</t>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26883125305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315046310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14338302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06497812271118</t>
   </si>
   <si>
     <t xml:space="preserve">5.00225400924683</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">5.33939695358276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235315322876</t>
+    <t xml:space="preserve">5.29235410690308</t>
   </si>
   <si>
     <t xml:space="preserve">5.11986207962036</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">5.09634017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11202096939087</t>
+    <t xml:space="preserve">5.11202144622803</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474603652954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44916439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45700454711914</t>
+    <t xml:space="preserve">5.44916343688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4570050239563</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">5.70790147781372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67653894424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55893135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51188850402832</t>
+    <t xml:space="preserve">5.6765398979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55893182754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51188802719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48052644729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36291837692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31587505340576</t>
+    <t xml:space="preserve">5.48052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36291885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31587553024292</t>
   </si>
   <si>
     <t xml:space="preserve">5.3237156867981</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">4.79840040206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70431470870972</t>
+    <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
     <t xml:space="preserve">4.71999502182007</t>
@@ -2048,64 +2048,64 @@
     <t xml:space="preserve">4.51614189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97089195251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82192134857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64159059524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71215486526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67295265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63374996185303</t>
+    <t xml:space="preserve">4.97089242935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82192182540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64158964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71215534210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67295217514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63374900817871</t>
   </si>
   <si>
     <t xml:space="preserve">4.64943075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59454679489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62590885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68079280853271</t>
+    <t xml:space="preserve">4.59454727172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62590932846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6807918548584</t>
   </si>
   <si>
     <t xml:space="preserve">4.90032768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22962951660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02577495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04145622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1512246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22178888320923</t>
+    <t xml:space="preserve">5.2296290397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02577543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0414571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15122413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22178840637207</t>
   </si>
   <si>
     <t xml:space="preserve">5.21394872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15906524658203</t>
+    <t xml:space="preserve">5.15906476974487</t>
   </si>
   <si>
     <t xml:space="preserve">5.08065938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1277027130127</t>
+    <t xml:space="preserve">5.12770223617554</t>
   </si>
   <si>
     <t xml:space="preserve">5.01793527603149</t>
@@ -2114,19 +2114,19 @@
     <t xml:space="preserve">5.07281875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08849906921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19042682647705</t>
+    <t xml:space="preserve">5.08849954605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19042634963989</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52756977081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51972913742065</t>
+    <t xml:space="preserve">5.52756929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5197286605835</t>
   </si>
   <si>
     <t xml:space="preserve">5.40212059020996</t>
@@ -2138,31 +2138,31 @@
     <t xml:space="preserve">5.4334831237793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50404787063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53541040420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41780233383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42564296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84118986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76278448104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44132375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40996170043945</t>
+    <t xml:space="preserve">5.50404739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53540992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41780185699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42564249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84119033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7627854347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517641067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44132328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40996122360229</t>
   </si>
   <si>
     <t xml:space="preserve">5.38643980026245</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">5.34723711013794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37075853347778</t>
+    <t xml:space="preserve">5.37075901031494</t>
   </si>
   <si>
     <t xml:space="preserve">5.23746967315674</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57102489471436</t>
+    <t xml:space="preserve">4.57102584838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750394821167</t>
@@ -2207,22 +2207,22 @@
     <t xml:space="preserve">4.57886648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39069318771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15547752380371</t>
+    <t xml:space="preserve">4.39069271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15547800064087</t>
   </si>
   <si>
     <t xml:space="preserve">4.2260422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1162748336792</t>
+    <t xml:space="preserve">4.11627531051636</t>
   </si>
   <si>
     <t xml:space="preserve">3.84185671806335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63800311088562</t>
+    <t xml:space="preserve">3.63800287246704</t>
   </si>
   <si>
     <t xml:space="preserve">3.26165771484375</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">3.29301977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32438182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099382400513</t>
+    <t xml:space="preserve">3.32438206672668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099406242371</t>
   </si>
   <si>
     <t xml:space="preserve">3.09700679779053</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">3.05780434608459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94803714752197</t>
+    <t xml:space="preserve">2.94803690910339</t>
   </si>
   <si>
     <t xml:space="preserve">3.00292062759399</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">3.21461462974548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25381708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22245526313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24205660820007</t>
+    <t xml:space="preserve">3.25381779670715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2224555015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24205684661865</t>
   </si>
   <si>
     <t xml:space="preserve">3.24597668647766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23813629150391</t>
+    <t xml:space="preserve">3.23813652992249</t>
   </si>
   <si>
     <t xml:space="preserve">3.36750483512878</t>
@@ -2282,37 +2282,37 @@
     <t xml:space="preserve">3.45767092704773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59880089759827</t>
+    <t xml:space="preserve">3.59880042076111</t>
   </si>
   <si>
     <t xml:space="preserve">3.37142515182495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52039504051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54391670227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72424864768982</t>
+    <t xml:space="preserve">3.52039480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54391694068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72424912452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.81049466133118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92026162147522</t>
+    <t xml:space="preserve">3.92026138305664</t>
   </si>
   <si>
     <t xml:space="preserve">4.3358097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32796907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32012891769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23388290405273</t>
+    <t xml:space="preserve">4.32796955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32012844085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23388242721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.1633186340332</t>
@@ -2321,223 +2321,223 @@
     <t xml:space="preserve">4.07707214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21820211410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036148071289</t>
+    <t xml:space="preserve">4.21820163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036100387573</t>
   </si>
   <si>
     <t xml:space="preserve">4.25740432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19467973709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208951950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481410980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401560783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8457772731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70072746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265402793884</t>
+    <t xml:space="preserve">4.19468021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577655792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009576797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265378952026</t>
   </si>
   <si>
     <t xml:space="preserve">3.8222553730011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86145782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169014930725</t>
+    <t xml:space="preserve">3.86145830154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169038772583</t>
   </si>
   <si>
     <t xml:space="preserve">3.74384999275208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98298621177673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10059309005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91634106636047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946455001831</t>
+    <t xml:space="preserve">3.98298597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660654067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10059404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91634130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946478843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1397967338562</t>
+    <t xml:space="preserve">4.13979721069336</t>
   </si>
   <si>
     <t xml:space="preserve">4.14763736724854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01434755325317</t>
+    <t xml:space="preserve">4.01434803009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.95162415504456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94378328323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88889956474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05355072021484</t>
+    <t xml:space="preserve">3.9437837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88889980316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05355024337769</t>
   </si>
   <si>
     <t xml:space="preserve">4.06923151016235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03002882003784</t>
+    <t xml:space="preserve">4.030029296875</t>
   </si>
   <si>
     <t xml:space="preserve">3.89282035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92810273170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85753774642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8653781414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617592811584</t>
+    <t xml:space="preserve">3.92810201644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242098808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8575382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86537837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617568969727</t>
   </si>
   <si>
     <t xml:space="preserve">3.88105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90458059310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9085009098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.779132604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75561118125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777102470398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497996330261</t>
+    <t xml:space="preserve">3.90458106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850138664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.755610704422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657410621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497948646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.96730518341064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02218866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594264984131</t>
+    <t xml:space="preserve">4.02218914031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594288825989</t>
   </si>
   <si>
     <t xml:space="preserve">3.76345157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75953102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64584374427795</t>
+    <t xml:space="preserve">3.75953125953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6458432674408</t>
   </si>
   <si>
     <t xml:space="preserve">3.66936492919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66544532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016223907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56351828575134</t>
+    <t xml:space="preserve">3.66544508934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016247749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56351804733276</t>
   </si>
   <si>
     <t xml:space="preserve">3.56743860244751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59096026420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903322219849</t>
+    <t xml:space="preserve">3.5909595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903298377991</t>
   </si>
   <si>
     <t xml:space="preserve">3.48119282722473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44198989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38710641860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654143333435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33222270011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278744697571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238855361938</t>
+    <t xml:space="preserve">3.44198966026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3871066570282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33222246170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238807678223</t>
   </si>
   <si>
     <t xml:space="preserve">3.43806958198547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46551156044006</t>
+    <t xml:space="preserve">3.46551179885864</t>
   </si>
   <si>
     <t xml:space="preserve">3.4929530620575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55175733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55567717552185</t>
+    <t xml:space="preserve">3.55175757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55567741394043</t>
   </si>
   <si>
     <t xml:space="preserve">3.50079369544983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51255464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37926578521729</t>
+    <t xml:space="preserve">3.51255488395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37926602363586</t>
   </si>
   <si>
     <t xml:space="preserve">3.43414950370789</t>
@@ -2546,10 +2546,10 @@
     <t xml:space="preserve">3.42630887031555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4615912437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44983077049255</t>
+    <t xml:space="preserve">3.46159100532532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44983053207397</t>
   </si>
   <si>
     <t xml:space="preserve">3.15189051628113</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">3.52823567390442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53215551376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607654571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10843420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252084732056</t>
+    <t xml:space="preserve">3.53215599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607678413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10843467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866652488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252132415771</t>
   </si>
   <si>
     <t xml:space="preserve">4.13195610046387</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">4.0927529335022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06139135360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28876638412476</t>
+    <t xml:space="preserve">4.06139087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28876686096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.24956369400024</t>
@@ -2597,37 +2597,37 @@
     <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39853429794312</t>
+    <t xml:space="preserve">4.3985333442688</t>
   </si>
   <si>
     <t xml:space="preserve">4.35933065414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69647407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976198196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7278356552124</t>
+    <t xml:space="preserve">4.69647312164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75919771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976245880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72783660888672</t>
   </si>
   <si>
     <t xml:space="preserve">4.74351692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703786849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487850189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73567581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68863391876221</t>
+    <t xml:space="preserve">4.76703834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487897872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73567676544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68863296508789</t>
   </si>
   <si>
     <t xml:space="preserve">4.80624103546143</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">4.84544324874878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91600799560547</t>
+    <t xml:space="preserve">4.91600894927979</t>
   </si>
   <si>
     <t xml:space="preserve">4.93952989578247</t>
@@ -2663,109 +2663,109 @@
     <t xml:space="preserve">5.68438005447388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59813356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62949657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71574211120605</t>
+    <t xml:space="preserve">5.59813404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6294960975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7157416343689</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66869831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66085767745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72358226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78630638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08424663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1783332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14697122573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97447919845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720283508301</t>
+    <t xml:space="preserve">5.66869878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66085815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72358274459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78630685806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08424711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17833280563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14697074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288457870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97447872161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720235824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00474452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11834859848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49161577224731</t>
+    <t xml:space="preserve">6.00474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11834812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">6.45915842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42670059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26440954208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41047048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39424180984497</t>
+    <t xml:space="preserve">6.42670011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2644100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41047096252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39424228668213</t>
   </si>
   <si>
     <t xml:space="preserve">6.4429292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96225833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43290090560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00091648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87108469009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78994035720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977119445801</t>
+    <t xml:space="preserve">6.96225786209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43289995193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00091743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83862638473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87108421325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78993988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">7.95222997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90354251861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60139179229736</t>
+    <t xml:space="preserve">7.90354347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60139274597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.64196300506592</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">8.56081867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43910121917725</t>
+    <t xml:space="preserve">8.43910026550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.19566631317139</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">8.23623752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01714706420898</t>
+    <t xml:space="preserve">8.01714611053467</t>
   </si>
   <si>
     <t xml:space="preserve">8.06583309173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96845960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40044164657593</t>
+    <t xml:space="preserve">7.96845865249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40044260025024</t>
   </si>
   <si>
     <t xml:space="preserve">7.25438070297241</t>
@@ -2801,40 +2801,40 @@
     <t xml:space="preserve">7.4815878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64387798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5627326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69256448745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502326965332</t>
+    <t xml:space="preserve">7.64387893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56273174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69256544113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502470016479</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62764930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4653582572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306911468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192335128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81619739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15700626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23815202713013</t>
+    <t xml:space="preserve">7.62764835357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46535778045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30306816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192287445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81619644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15700674057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23815250396729</t>
   </si>
   <si>
     <t xml:space="preserve">7.38421392440796</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">7.70879507064819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61142015457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53027486801147</t>
+    <t xml:space="preserve">7.61141967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53027439117432</t>
   </si>
   <si>
     <t xml:space="preserve">7.74125289916992</t>
@@ -2858,40 +2858,40 @@
     <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1550931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96654415130615</t>
+    <t xml:space="preserve">8.15509414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96654605865479</t>
   </si>
   <si>
     <t xml:space="preserve">8.84482765197754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5202465057373</t>
+    <t xml:space="preserve">8.76368141174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52024745941162</t>
   </si>
   <si>
     <t xml:space="preserve">8.39852905273438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47967338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31738185882568</t>
+    <t xml:space="preserve">8.47967433929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31738376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.08206272125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11452102661133</t>
+    <t xml:space="preserve">8.1145191192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.03337478637695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04960346221924</t>
+    <t xml:space="preserve">8.04960441589355</t>
   </si>
   <si>
     <t xml:space="preserve">9.04769039154053</t>
@@ -2900,37 +2900,37 @@
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4452428817749</t>
+    <t xml:space="preserve">9.16940784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44524192810059</t>
   </si>
   <si>
     <t xml:space="preserve">9.40345001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23627662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48703670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7795877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61241436004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57062149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52882957458496</t>
+    <t xml:space="preserve">9.23627758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48703575134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77958679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6124153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57062244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52882862091064</t>
   </si>
   <si>
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779392242432</t>
+    <t xml:space="preserve">9.73779487609863</t>
   </si>
   <si>
     <t xml:space="preserve">9.65420818328857</t>
@@ -2972,79 +2972,79 @@
     <t xml:space="preserve">9.11089706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06910419464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94372463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90193176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81834602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758594512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52579402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73475933074951</t>
+    <t xml:space="preserve">9.36165523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06910514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9437255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90193271636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81834697723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52579307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73476028442383</t>
   </si>
   <si>
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846977233887</t>
+    <t xml:space="preserve">8.30846881866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.32518768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65649747848511</t>
+    <t xml:space="preserve">7.65649652481079</t>
   </si>
   <si>
     <t xml:space="preserve">7.82366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154626846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07139348983765</t>
+    <t xml:space="preserve">7.67321538925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07139444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.10482835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68993234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589017868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80695295333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62306261062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99084281921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09114646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04099369049072</t>
+    <t xml:space="preserve">7.68993091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589113235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80695247650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62306308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99084186553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09114551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04099464416504</t>
   </si>
   <si>
     <t xml:space="preserve">8.27503490447998</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">8.40041542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10786247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48400020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30011177062988</t>
+    <t xml:space="preserve">8.1078634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48400115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30011081695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.35026264190674</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87382221221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69829082489014</t>
+    <t xml:space="preserve">7.87382173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69828987121582</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531190872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77351903915405</t>
+    <t xml:space="preserve">7.81531095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77351856231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.91561508178711</t>
@@ -3089,22 +3089,22 @@
     <t xml:space="preserve">7.78187656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60634565353394</t>
+    <t xml:space="preserve">7.60634613037109</t>
   </si>
   <si>
     <t xml:space="preserve">7.89889764785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79859352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978099822998</t>
+    <t xml:space="preserve">7.79859447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023504257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978004455566</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">8.24154376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21538066864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28514862060547</t>
+    <t xml:space="preserve">8.21537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28514957427979</t>
   </si>
   <si>
     <t xml:space="preserve">8.32003498077393</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">8.38108253479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19793796539307</t>
+    <t xml:space="preserve">8.19793701171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.49445819854736</t>
@@ -3140,16 +3140,16 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678535461426</t>
+    <t xml:space="preserve">8.54678630828857</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59039211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64271926879883</t>
+    <t xml:space="preserve">8.59039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64271831512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.63399791717529</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">8.45957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1281681060791</t>
+    <t xml:space="preserve">8.17177391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12816715240479</t>
   </si>
   <si>
     <t xml:space="preserve">7.93630123138428</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">7.78804016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65722274780273</t>
+    <t xml:space="preserve">7.65722179412842</t>
   </si>
   <si>
     <t xml:space="preserve">7.76187658309937</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">7.70082855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5961742401123</t>
+    <t xml:space="preserve">7.59617376327515</t>
   </si>
   <si>
     <t xml:space="preserve">7.46535634994507</t>
@@ -3218,28 +3218,28 @@
     <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50024080276489</t>
+    <t xml:space="preserve">7.73571395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50024127960205</t>
   </si>
   <si>
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.447913646698</t>
+    <t xml:space="preserve">7.55256795883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44791316986084</t>
   </si>
   <si>
     <t xml:space="preserve">7.53512620925903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51768350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50896167755127</t>
+    <t xml:space="preserve">7.5176830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50896120071411</t>
   </si>
   <si>
     <t xml:space="preserve">7.57001066207886</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">8.72121047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48573684692383</t>
+    <t xml:space="preserve">8.48573780059814</t>
   </si>
   <si>
     <t xml:space="preserve">8.50318050384521</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">8.02351379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37236213684082</t>
+    <t xml:space="preserve">8.37236309051514</t>
   </si>
   <si>
     <t xml:space="preserve">7.89269495010376</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">7.68338632583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33453798294067</t>
+    <t xml:space="preserve">7.33453750610352</t>
   </si>
   <si>
     <t xml:space="preserve">7.16883516311646</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418037414551</t>
+    <t xml:space="preserve">7.06418085098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
@@ -3335,40 +3335,40 @@
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75315570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4391918182373</t>
+    <t xml:space="preserve">7.7531566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43919229507446</t>
   </si>
   <si>
     <t xml:space="preserve">7.43047189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49151992797852</t>
+    <t xml:space="preserve">7.49151945114136</t>
   </si>
   <si>
     <t xml:space="preserve">7.27348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39558601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38686513900757</t>
+    <t xml:space="preserve">7.39558553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">7.35198068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31709575653076</t>
+    <t xml:space="preserve">7.3170952796936</t>
   </si>
   <si>
     <t xml:space="preserve">7.47407722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.290931224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581615447998</t>
+    <t xml:space="preserve">7.29093170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581663131714</t>
   </si>
   <si>
     <t xml:space="preserve">7.30837440490723</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663547515869</t>
+    <t xml:space="preserve">7.45663499832153</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781049728394</t>
+    <t xml:space="preserve">7.85781145095825</t>
   </si>
   <si>
     <t xml:space="preserve">8.03223514556885</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">8.1020040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15433216094971</t>
+    <t xml:space="preserve">8.15433120727539</t>
   </si>
   <si>
     <t xml:space="preserve">8.05839824676514</t>
@@ -3401,16 +3401,16 @@
     <t xml:space="preserve">8.09328365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00607109069824</t>
+    <t xml:space="preserve">8.00607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584095001221</t>
+    <t xml:space="preserve">8.11072540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584190368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
@@ -3452,19 +3452,19 @@
     <t xml:space="preserve">8.94796180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87819194793701</t>
+    <t xml:space="preserve">8.87819290161133</t>
   </si>
   <si>
     <t xml:space="preserve">8.89563465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65144062042236</t>
+    <t xml:space="preserve">8.65144157409668</t>
   </si>
   <si>
     <t xml:space="preserve">8.6601619720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79098033905029</t>
+    <t xml:space="preserve">8.79097938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.70376777648926</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">8.86074924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93051910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62527751922607</t>
+    <t xml:space="preserve">8.93052005767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62527656555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.56422805786133</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">8.46829509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6863260269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15727138519287</t>
+    <t xml:space="preserve">8.68632507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15727043151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">8.96540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00028800964355</t>
+    <t xml:space="preserve">9.00028896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842304229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66888332366943</t>
+    <t xml:space="preserve">8.80842208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66888236999512</t>
   </si>
   <si>
     <t xml:space="preserve">8.91124629974365</t>
@@ -4299,6 +4299,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.6499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -70027,7 +70030,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6909837963</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>5753</v>
@@ -70048,6 +70051,32 @@
         <v>1402</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6911111111</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>4800</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="1431">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355521678925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546637058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20654833316803</t>
+    <t xml:space="preserve">1.21355509757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546648979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20654845237732</t>
   </si>
   <si>
     <t xml:space="preserve">1.23177242279053</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">1.24998962879181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26330232620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27311158180237</t>
+    <t xml:space="preserve">1.26330256462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27311170101166</t>
   </si>
   <si>
     <t xml:space="preserve">1.26120042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24718713760376</t>
+    <t xml:space="preserve">1.24718701839447</t>
   </si>
   <si>
     <t xml:space="preserve">1.2079496383667</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">1.19323563575745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814038276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2457857131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23457515239716</t>
+    <t xml:space="preserve">1.17501842975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19814050197601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24578583240509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
     <t xml:space="preserve">1.21495628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18272578716278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17992305755615</t>
+    <t xml:space="preserve">1.18272566795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17992317676544</t>
   </si>
   <si>
     <t xml:space="preserve">1.17641961574554</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">1.12457048892975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12807369232178</t>
+    <t xml:space="preserve">1.12807381153107</t>
   </si>
   <si>
     <t xml:space="preserve">1.10284972190857</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01596689224243</t>
+    <t xml:space="preserve">1.01596701145172</t>
   </si>
   <si>
     <t xml:space="preserve">1.0250757932663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02017104625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297377586365</t>
+    <t xml:space="preserve">1.02017116546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195372104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297365665436</t>
   </si>
   <si>
     <t xml:space="preserve">1.04329299926758</t>
@@ -140,109 +140,109 @@
     <t xml:space="preserve">1.11055707931519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09304022789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106704711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017570972443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1561005115509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10004699230194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13157713413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705363750458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227772712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1182644367218</t>
+    <t xml:space="preserve">1.09304046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106716632843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017582893372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15610039234161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10004711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1315770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227784633636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11826419830322</t>
   </si>
   <si>
     <t xml:space="preserve">1.14909374713898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17852175235748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17011380195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412697315216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16310703754425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22616732120514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508500099182</t>
+    <t xml:space="preserve">1.17852163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17011368274689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412709236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081439495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16310715675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22616708278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2450852394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.24088108539581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20514702796936</t>
+    <t xml:space="preserve">1.20514714717865</t>
   </si>
   <si>
     <t xml:space="preserve">1.19113373756409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22686779499054</t>
+    <t xml:space="preserve">1.22686791419983</t>
   </si>
   <si>
     <t xml:space="preserve">1.22196304798126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24438440799713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17221581935883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183456897736</t>
+    <t xml:space="preserve">1.24438452720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17221570014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183444976807</t>
   </si>
   <si>
     <t xml:space="preserve">1.19743967056274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20374572277069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20304501056671</t>
+    <t xml:space="preserve">1.20374584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.203045129776</t>
   </si>
   <si>
     <t xml:space="preserve">1.23807835578918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23317384719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19954192638397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247656583786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916055679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896981239319</t>
+    <t xml:space="preserve">1.2331737279892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19954168796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845972537994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916043758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2289696931839</t>
   </si>
   <si>
     <t xml:space="preserve">1.21215379238129</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">1.2920298576355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29623377323151</t>
+    <t xml:space="preserve">1.29623365402222</t>
   </si>
   <si>
     <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28712499141693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28151977062225</t>
+    <t xml:space="preserve">1.28712511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28151988983154</t>
   </si>
   <si>
     <t xml:space="preserve">1.24788773059845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23737788200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865046977997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469884872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138627052307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1189649105072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036645412445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13648164272308</t>
+    <t xml:space="preserve">1.23737776279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865035057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469896793365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138638973236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11896502971649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036633491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13648176193237</t>
   </si>
   <si>
     <t xml:space="preserve">1.14629101753235</t>
@@ -296,127 +296,127 @@
     <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0720202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08463227748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501376628876</t>
+    <t xml:space="preserve">1.07202041149139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084632396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501364707947</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253014087677</t>
+    <t xml:space="preserve">1.08253037929535</t>
   </si>
   <si>
     <t xml:space="preserve">1.07902681827545</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05800688266754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10144853591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355031490326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09514248371124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11966574192047</t>
+    <t xml:space="preserve">1.05800700187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1014484167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355043411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09514236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11966586112976</t>
   </si>
   <si>
     <t xml:space="preserve">1.09934639930725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11265897750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15680122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528040885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4868152141571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48821663856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45178174972534</t>
+    <t xml:space="preserve">1.11265921592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1568009853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528052806854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48681533336639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48821651935577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45178186893463</t>
   </si>
   <si>
     <t xml:space="preserve">1.41534721851349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45738708972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40133368968964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46999931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776857852936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375516891479</t>
+    <t xml:space="preserve">1.4573872089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40133392810822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4699991941452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375528812408</t>
   </si>
   <si>
     <t xml:space="preserve">1.4363671541214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936062812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674864292145</t>
+    <t xml:space="preserve">1.42936050891876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674840450287</t>
   </si>
   <si>
     <t xml:space="preserve">1.42235386371613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41814959049225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4111430644989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42795944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48120975494385</t>
+    <t xml:space="preserve">1.41814970970154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114318370819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42795932292938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48120999336243</t>
   </si>
   <si>
     <t xml:space="preserve">1.69421255588531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338348388672</t>
+    <t xml:space="preserve">1.66338324546814</t>
   </si>
   <si>
     <t xml:space="preserve">1.80071377754211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84555661678314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79230618476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268719673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064732551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71663391590118</t>
+    <t xml:space="preserve">1.84555637836456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7923059463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090464115143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064756393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7166336774826</t>
   </si>
   <si>
     <t xml:space="preserve">1.78670072555542</t>
@@ -428,70 +428,70 @@
     <t xml:space="preserve">1.8259379863739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82313549518585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995139598846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83854997158051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84415519237518</t>
+    <t xml:space="preserve">1.82313513755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995115756989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83855020999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84415543079376</t>
   </si>
   <si>
     <t xml:space="preserve">1.83014214038849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81472718715668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874035835266</t>
+    <t xml:space="preserve">1.81472754478455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874047756195</t>
   </si>
   <si>
     <t xml:space="preserve">1.81192445755005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83294463157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8693790435791</t>
+    <t xml:space="preserve">1.83294451236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835934638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937916278839</t>
   </si>
   <si>
     <t xml:space="preserve">1.99549925327301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0725724697113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02913117408752</t>
+    <t xml:space="preserve">2.07257223129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0291314125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.08798742294312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04034209251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830222129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03053283691406</t>
+    <t xml:space="preserve">2.04034233093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830162525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0305323600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.01932191848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99970352649689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359288215637</t>
+    <t xml:space="preserve">1.99970328807831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231551170349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066621780396</t>
@@ -500,31 +500,31 @@
     <t xml:space="preserve">2.15945553779602</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98989379405975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339281082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167646884918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345914363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01651954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250601768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9786833524704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944609165192</t>
+    <t xml:space="preserve">1.98989403247833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339269161224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345938205719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01651930809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428893089294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97868323326111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944573402405</t>
   </si>
   <si>
     <t xml:space="preserve">1.91982734203339</t>
@@ -539,43 +539,43 @@
     <t xml:space="preserve">1.87918865680695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85676753520966</t>
+    <t xml:space="preserve">1.85676729679108</t>
   </si>
   <si>
     <t xml:space="preserve">1.78950309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80631947517395</t>
+    <t xml:space="preserve">1.80631935596466</t>
   </si>
   <si>
     <t xml:space="preserve">1.90301144123077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89880728721619</t>
+    <t xml:space="preserve">1.8988071680069</t>
   </si>
   <si>
     <t xml:space="preserve">1.91001832485199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99690079689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849236965179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569023609161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224882125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766317844391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186697483063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326875686646</t>
+    <t xml:space="preserve">1.99690091609955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849308490753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98569011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224858283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766341686249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186745166779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326887607574</t>
   </si>
   <si>
     <t xml:space="preserve">1.97027540206909</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">1.96607136726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00390720367432</t>
+    <t xml:space="preserve">2.0039074420929</t>
   </si>
   <si>
     <t xml:space="preserve">2.07397389411926</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">2.18888330459595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16506028175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1328296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06416487693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09639549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601376533508</t>
+    <t xml:space="preserve">2.1650607585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13283014297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06416463851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09639573097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601400375366</t>
   </si>
   <si>
     <t xml:space="preserve">2.09499430656433</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">2.1132116317749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14404058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002753257751</t>
+    <t xml:space="preserve">2.14404082298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002729415894</t>
   </si>
   <si>
     <t xml:space="preserve">2.14824485778809</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">2.1524486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13703417778015</t>
+    <t xml:space="preserve">2.13703393936157</t>
   </si>
   <si>
     <t xml:space="preserve">2.11180996894836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09779644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.118816614151</t>
+    <t xml:space="preserve">2.09779667854309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11881685256958</t>
   </si>
   <si>
     <t xml:space="preserve">2.10200071334839</t>
@@ -650,25 +650,25 @@
     <t xml:space="preserve">2.11741542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24213409423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48876881599426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4873673915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316335678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46494603157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40328741073608</t>
+    <t xml:space="preserve">2.24213433265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48876905441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48736763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316359519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46494626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40328788757324</t>
   </si>
   <si>
     <t xml:space="preserve">2.52099943161011</t>
@@ -677,22 +677,22 @@
     <t xml:space="preserve">2.48036098480225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46634769439697</t>
+    <t xml:space="preserve">2.46634745597839</t>
   </si>
   <si>
     <t xml:space="preserve">2.44392609596252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43972253799438</t>
+    <t xml:space="preserve">2.43972206115723</t>
   </si>
   <si>
     <t xml:space="preserve">2.47615671157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45513653755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437427520752</t>
+    <t xml:space="preserve">2.45513701438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437403678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.47335386276245</t>
@@ -701,70 +701,70 @@
     <t xml:space="preserve">2.65552759170532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71858787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70457434654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865456581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11096143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2398841381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129465103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040833473206</t>
+    <t xml:space="preserve">2.71858763694763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7045738697052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751057624817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.788654088974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11096096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23988366127014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38422083854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129512786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003103256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5804078578949</t>
   </si>
   <si>
     <t xml:space="preserve">3.69251489639282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66098427772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601798057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7836012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386756896973</t>
+    <t xml:space="preserve">3.66098403930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601845741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78360176086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9517617225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386804580688</t>
   </si>
   <si>
     <t xml:space="preserve">4.19349145889282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16896820068359</t>
+    <t xml:space="preserve">4.16896772384644</t>
   </si>
   <si>
     <t xml:space="preserve">4.11291456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3091025352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30559778213501</t>
+    <t xml:space="preserve">4.03233814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30910110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30559825897217</t>
   </si>
   <si>
     <t xml:space="preserve">4.55433511734009</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">4.6979718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50023460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256153106689</t>
+    <t xml:space="preserve">5.50023508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256200790405</t>
   </si>
   <si>
     <t xml:space="preserve">5.10085535049438</t>
@@ -791,34 +791,34 @@
     <t xml:space="preserve">5.44418239593506</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77349519729614</t>
+    <t xml:space="preserve">5.7734956741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.3970890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518203735352</t>
+    <t xml:space="preserve">6.76143455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518346786499</t>
   </si>
   <si>
     <t xml:space="preserve">6.71238851547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0936918258667</t>
+    <t xml:space="preserve">7.09369230270386</t>
   </si>
   <si>
     <t xml:space="preserve">6.97858285903931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3562650680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53252840042114</t>
+    <t xml:space="preserve">6.78433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626602172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53252792358398</t>
   </si>
   <si>
     <t xml:space="preserve">6.35266876220703</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">6.32389068603516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43900203704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094627380371</t>
+    <t xml:space="preserve">6.43900156021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094532012939</t>
   </si>
   <si>
     <t xml:space="preserve">6.40302848815918</t>
@@ -845,34 +845,34 @@
     <t xml:space="preserve">6.19798851013184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37425184249878</t>
+    <t xml:space="preserve">6.3742504119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.47137641906738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32748746871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15122413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11165475845337</t>
+    <t xml:space="preserve">6.32748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15122509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11165523529053</t>
   </si>
   <si>
     <t xml:space="preserve">5.93898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057224273682</t>
+    <t xml:space="preserve">5.96057319641113</t>
   </si>
   <si>
     <t xml:space="preserve">5.85265684127808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90661525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89582300186157</t>
+    <t xml:space="preserve">5.90661430358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89582252502441</t>
   </si>
   <si>
     <t xml:space="preserve">5.75193452835083</t>
@@ -881,58 +881,58 @@
     <t xml:space="preserve">5.69437980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70157432556152</t>
+    <t xml:space="preserve">5.70157384872437</t>
   </si>
   <si>
     <t xml:space="preserve">5.3670334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87421655654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17997884750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97853565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96414661407471</t>
+    <t xml:space="preserve">4.87421560287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1799783706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97853517532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96414613723755</t>
   </si>
   <si>
     <t xml:space="preserve">4.84543895721436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8778133392334</t>
+    <t xml:space="preserve">4.87781381607056</t>
   </si>
   <si>
     <t xml:space="preserve">4.9101881980896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70155000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9245777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7698974609375</t>
+    <t xml:space="preserve">4.70155048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92457723617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76989698410034</t>
   </si>
   <si>
     <t xml:space="preserve">4.69075870513916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65838432312012</t>
+    <t xml:space="preserve">4.65838384628296</t>
   </si>
   <si>
     <t xml:space="preserve">4.68716096878052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82385540008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5504674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51089811325073</t>
+    <t xml:space="preserve">4.82385587692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55046701431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51089859008789</t>
   </si>
   <si>
     <t xml:space="preserve">4.49291181564331</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">4.43895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38139915466309</t>
+    <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
     <t xml:space="preserve">4.38499593734741</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">5.03609037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85623025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80946683883667</t>
+    <t xml:space="preserve">4.85622978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80946636199951</t>
   </si>
   <si>
     <t xml:space="preserve">4.76630020141602</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">4.68356418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67636919021606</t>
+    <t xml:space="preserve">4.67637014389038</t>
   </si>
   <si>
     <t xml:space="preserve">4.60442590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59003734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62960577011108</t>
+    <t xml:space="preserve">4.59003686904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
     <t xml:space="preserve">4.66198110580444</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">4.74831390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75910568237305</t>
+    <t xml:space="preserve">4.75910520553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.95335531234741</t>
@@ -998,67 +998,67 @@
     <t xml:space="preserve">5.06486797332764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14400720596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11522912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19436740875244</t>
+    <t xml:space="preserve">5.14400672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11522960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19436693191528</t>
   </si>
   <si>
     <t xml:space="preserve">5.10803461074829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93536853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550842285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99652147293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90659093856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097997665405</t>
+    <t xml:space="preserve">4.93536901473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7555079460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99652194976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90659046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92098045349121</t>
   </si>
   <si>
     <t xml:space="preserve">4.82025814056396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89220285415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05407667160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01810503005981</t>
+    <t xml:space="preserve">4.89220237731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0540771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0181040763855</t>
   </si>
   <si>
     <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94615983963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839576721191</t>
+    <t xml:space="preserve">4.94616031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839624404907</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393678665161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60804748535156</t>
+    <t xml:space="preserve">5.60804653167725</t>
   </si>
   <si>
     <t xml:space="preserve">5.89942026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77711534500122</t>
+    <t xml:space="preserve">5.7771143913269</t>
   </si>
   <si>
     <t xml:space="preserve">6.03611469268799</t>
@@ -1067,22 +1067,22 @@
     <t xml:space="preserve">5.94978094100952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18000221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20877981185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52533388137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0361385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89584684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527729034424</t>
+    <t xml:space="preserve">6.18000316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20878028869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52533435821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03613662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89584732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527681350708</t>
   </si>
   <si>
     <t xml:space="preserve">7.13685941696167</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">7.69802331924438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12969017028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43904876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29518508911133</t>
+    <t xml:space="preserve">8.12968921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43904781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29518413543701</t>
   </si>
   <si>
     <t xml:space="preserve">10.2160692214966</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42466068267822</t>
+    <t xml:space="preserve">8.42465877532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.61890888214111</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">8.0145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80593967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32393836975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99299573898315</t>
+    <t xml:space="preserve">7.8059401512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32393741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99299383163452</t>
   </si>
   <si>
     <t xml:space="preserve">8.10091114044189</t>
@@ -1136,85 +1136,85 @@
     <t xml:space="preserve">7.88507843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73399591445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41024780273438</t>
+    <t xml:space="preserve">7.73399639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41024732589722</t>
   </si>
   <si>
     <t xml:space="preserve">7.54694080352783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47499704360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535820007324</t>
+    <t xml:space="preserve">7.47499656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341444015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535724639893</t>
   </si>
   <si>
     <t xml:space="preserve">7.38866472244263</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8419132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702409744263</t>
+    <t xml:space="preserve">8.23760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702314376831</t>
   </si>
   <si>
     <t xml:space="preserve">7.84910678863525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04335594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824602127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630083084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74838542938232</t>
+    <t xml:space="preserve">8.04335689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824506759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85630130767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74838590621948</t>
   </si>
   <si>
     <t xml:space="preserve">7.57571840286255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42463636398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19441556930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419429779053</t>
+    <t xml:space="preserve">7.424635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419334411621</t>
   </si>
   <si>
     <t xml:space="preserve">7.21599864959717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97498559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20880317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20160961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5541353225708</t>
+    <t xml:space="preserve">6.97498512268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2088041305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20160913467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55413579940796</t>
   </si>
   <si>
     <t xml:space="preserve">7.65485811233521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2519702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477529525757</t>
+    <t xml:space="preserve">7.25197124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477624893188</t>
   </si>
   <si>
     <t xml:space="preserve">7.18722009658813</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">7.10448455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00735902786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944505691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9534010887146</t>
+    <t xml:space="preserve">7.00735998153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944314956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340251922607</t>
   </si>
   <si>
     <t xml:space="preserve">7.15844297409058</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">6.91742944717407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85627698898315</t>
+    <t xml:space="preserve">6.856276512146</t>
   </si>
   <si>
     <t xml:space="preserve">6.89224910736084</t>
@@ -1247,124 +1247,124 @@
     <t xml:space="preserve">6.78793048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95699882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541622161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98217964172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1620397567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02174949645996</t>
+    <t xml:space="preserve">6.9569993019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98218059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16204071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045667648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02174806594849</t>
   </si>
   <si>
     <t xml:space="preserve">7.33830308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82752418518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25918769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15846538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91385698318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8994665145874</t>
+    <t xml:space="preserve">7.82752323150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25918674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15846824645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91385650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89946699142456</t>
   </si>
   <si>
     <t xml:space="preserve">7.81313371658325</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66924524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435707092285</t>
+    <t xml:space="preserve">7.66924619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76996898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435468673706</t>
   </si>
   <si>
     <t xml:space="preserve">7.48219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79152631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836111068726</t>
+    <t xml:space="preserve">6.79152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836158752441</t>
   </si>
   <si>
     <t xml:space="preserve">6.56850099563599</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64044380187988</t>
+    <t xml:space="preserve">6.6404447555542</t>
   </si>
   <si>
     <t xml:space="preserve">6.4893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62605571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56130647659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447263717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411195755005</t>
+    <t xml:space="preserve">6.63325119018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56130599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411100387573</t>
   </si>
   <si>
     <t xml:space="preserve">6.28791904449463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19439077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02172565460205</t>
+    <t xml:space="preserve">6.19439172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02172517776489</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633501052856</t>
+    <t xml:space="preserve">5.86344718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633596420288</t>
   </si>
   <si>
     <t xml:space="preserve">6.44619512557983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46777820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51814031600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46058416366577</t>
+    <t xml:space="preserve">6.46777868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6764178276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51814079284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46058368682861</t>
   </si>
   <si>
     <t xml:space="preserve">6.2951135635376</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">6.13683605194092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92819833755493</t>
+    <t xml:space="preserve">5.92819786071777</t>
   </si>
   <si>
     <t xml:space="preserve">5.93539190292358</t>
@@ -1388,49 +1388,49 @@
     <t xml:space="preserve">5.79869890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97136497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01453065872192</t>
+    <t xml:space="preserve">5.97136449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01453018188477</t>
   </si>
   <si>
     <t xml:space="preserve">5.99294757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1728081703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1871976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25194597244263</t>
+    <t xml:space="preserve">6.17280769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18719673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25194644927979</t>
   </si>
   <si>
     <t xml:space="preserve">6.22316884994507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12244701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27352952957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950212478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30230760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33828020095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58551692962646</t>
+    <t xml:space="preserve">6.12244749069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27352905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30230808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33827972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58551740646362</t>
   </si>
   <si>
     <t xml:space="preserve">6.38323259353638</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46564435958862</t>
+    <t xml:space="preserve">6.46564483642578</t>
   </si>
   <si>
     <t xml:space="preserve">6.35326337814331</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">6.30831146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59300947189331</t>
+    <t xml:space="preserve">6.59300994873047</t>
   </si>
   <si>
     <t xml:space="preserve">6.41319990158081</t>
@@ -1448,19 +1448,19 @@
     <t xml:space="preserve">6.17345428466797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09853363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90374040603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618486404419</t>
+    <t xml:space="preserve">6.09853410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90374088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
   </si>
   <si>
     <t xml:space="preserve">5.94120025634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86628007888794</t>
+    <t xml:space="preserve">5.86627960205078</t>
   </si>
   <si>
     <t xml:space="preserve">5.94869232177734</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">5.59656572341919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48418521881104</t>
+    <t xml:space="preserve">5.48418569564819</t>
   </si>
   <si>
     <t xml:space="preserve">5.60405778884888</t>
@@ -1484,40 +1484,40 @@
     <t xml:space="preserve">5.888756275177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80634355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64151811599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139068603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88126420974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621612548828</t>
+    <t xml:space="preserve">5.80634260177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64151859283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79135894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88126373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621660232544</t>
   </si>
   <si>
     <t xml:space="preserve">6.33078718185425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55554914474487</t>
+    <t xml:space="preserve">6.55554962158203</t>
   </si>
   <si>
     <t xml:space="preserve">6.45815277099609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33827924728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12850141525269</t>
+    <t xml:space="preserve">6.33827877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.128502368927</t>
   </si>
   <si>
     <t xml:space="preserve">6.06107330322266</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">5.77637529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76888275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70145511627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66399478912354</t>
+    <t xml:space="preserve">5.768883228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70145463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66399383544922</t>
   </si>
   <si>
     <t xml:space="preserve">5.57408952713013</t>
@@ -1541,25 +1541,25 @@
     <t xml:space="preserve">5.75389909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78386735916138</t>
+    <t xml:space="preserve">5.78386640548706</t>
   </si>
   <si>
     <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62653398513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61904191970825</t>
+    <t xml:space="preserve">5.6265344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61904239654541</t>
   </si>
   <si>
     <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54412174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58158206939697</t>
+    <t xml:space="preserve">5.54412126541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58158159255981</t>
   </si>
   <si>
     <t xml:space="preserve">5.5066614151001</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">5.53662919998169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43174076080322</t>
+    <t xml:space="preserve">5.43174123764038</t>
   </si>
   <si>
     <t xml:space="preserve">5.46920108795166</t>
@@ -1577,19 +1577,19 @@
     <t xml:space="preserve">5.31935930252075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49167680740356</t>
+    <t xml:space="preserve">5.28189945220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49167728424072</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415348052979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36431217193604</t>
+    <t xml:space="preserve">5.36431169509888</t>
   </si>
   <si>
     <t xml:space="preserve">5.27440786361694</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">5.2069787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58907413482666</t>
+    <t xml:space="preserve">5.5890736579895</t>
   </si>
   <si>
     <t xml:space="preserve">5.74640703201294</t>
@@ -1613,34 +1613,34 @@
     <t xml:space="preserve">5.21447134017944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13955068588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0945987701416</t>
+    <t xml:space="preserve">5.13955116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09459781646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.10958194732666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07212209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01967668533325</t>
+    <t xml:space="preserve">5.07212162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05713748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967763900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.03466129302979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92977285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732839584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86983633041382</t>
+    <t xml:space="preserve">4.92977333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86983680725098</t>
   </si>
   <si>
     <t xml:space="preserve">4.7349796295166</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75745582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234426498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478824615479</t>
+    <t xml:space="preserve">4.75745534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234378814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91478872299194</t>
   </si>
   <si>
     <t xml:space="preserve">4.89980459213257</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">4.95224905014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16951894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710622787476</t>
+    <t xml:space="preserve">5.16951847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0871057510376</t>
   </si>
   <si>
     <t xml:space="preserve">5.13205862045288</t>
@@ -1685,16 +1685,16 @@
     <t xml:space="preserve">6.21840667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25586700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01612043380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602617263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99364471435547</t>
+    <t xml:space="preserve">6.25586652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01611995697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602521896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99364519119263</t>
   </si>
   <si>
     <t xml:space="preserve">5.04215335845947</t>
@@ -1715,25 +1715,25 @@
     <t xml:space="preserve">4.89231300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04964590072632</t>
+    <t xml:space="preserve">5.04964542388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95974111557007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81739234924316</t>
+    <t xml:space="preserve">4.81739187240601</t>
   </si>
   <si>
     <t xml:space="preserve">4.7949161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78742408752441</t>
+    <t xml:space="preserve">4.78742361068726</t>
   </si>
   <si>
     <t xml:space="preserve">4.83237600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97472524642944</t>
+    <t xml:space="preserve">4.9747257232666</t>
   </si>
   <si>
     <t xml:space="preserve">4.90729665756226</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">4.76494789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47275733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047157287598</t>
+    <t xml:space="preserve">4.4727578163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047204971313</t>
   </si>
   <si>
     <t xml:space="preserve">4.38285303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32291603088379</t>
+    <t xml:space="preserve">4.32291650772095</t>
   </si>
   <si>
     <t xml:space="preserve">4.18056726455688</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">4.16558313369751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30044031143188</t>
+    <t xml:space="preserve">4.30043983459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.31542444229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46526527404785</t>
+    <t xml:space="preserve">4.46526479721069</t>
   </si>
   <si>
     <t xml:space="preserve">4.45777320861816</t>
@@ -1775,22 +1775,22 @@
     <t xml:space="preserve">4.71250343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10209035873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07961463928223</t>
+    <t xml:space="preserve">5.10208988189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07961416244507</t>
   </si>
   <si>
     <t xml:space="preserve">4.93726491928101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01218509674072</t>
+    <t xml:space="preserve">5.01218557357788</t>
   </si>
   <si>
     <t xml:space="preserve">5.24443912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22196292877197</t>
+    <t xml:space="preserve">5.22196340560913</t>
   </si>
   <si>
     <t xml:space="preserve">5.25942325592041</t>
@@ -1799,13 +1799,13 @@
     <t xml:space="preserve">5.19948720932007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11707401275635</t>
+    <t xml:space="preserve">5.11707353591919</t>
   </si>
   <si>
     <t xml:space="preserve">5.28939151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16202688217163</t>
+    <t xml:space="preserve">5.16202592849731</t>
   </si>
   <si>
     <t xml:space="preserve">5.31186771392822</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">5.37180471420288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4467248916626</t>
+    <t xml:space="preserve">5.44672536849976</t>
   </si>
   <si>
     <t xml:space="preserve">5.39427995681763</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">5.40926456451416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89624834060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85878801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.121009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589921951294</t>
+    <t xml:space="preserve">5.89624786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85878753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12100982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589874267578</t>
   </si>
   <si>
     <t xml:space="preserve">5.81383562088013</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">6.00113725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79885149002075</t>
+    <t xml:space="preserve">5.79885101318359</t>
   </si>
   <si>
     <t xml:space="preserve">5.82132768630981</t>
@@ -1859,10 +1859,10 @@
     <t xml:space="preserve">6.03110504150391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00862884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872358322144</t>
+    <t xml:space="preserve">6.008629322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872453689575</t>
   </si>
   <si>
     <t xml:space="preserve">5.83631181716919</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">6.21091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09104156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348554611206</t>
+    <t xml:space="preserve">6.09104108810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097761154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
   </si>
   <si>
     <t xml:space="preserve">6.04608869552612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02361249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859710693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142290115356</t>
+    <t xml:space="preserve">6.02361297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142337799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.97866106033325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69396257400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393035888672</t>
+    <t xml:space="preserve">5.69396305084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393083572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.70894622802734</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">5.49916934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46170902252197</t>
+    <t xml:space="preserve">5.46170854568481</t>
   </si>
   <si>
     <t xml:space="preserve">5.73891448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55161380767822</t>
+    <t xml:space="preserve">5.55161333084106</t>
   </si>
   <si>
     <t xml:space="preserve">5.47268581390381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30019474029541</t>
+    <t xml:space="preserve">5.30019426345825</t>
   </si>
   <si>
     <t xml:space="preserve">5.33155632019043</t>
@@ -1934,34 +1934,34 @@
     <t xml:space="preserve">5.46484518051147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35507774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30803489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859964370728</t>
+    <t xml:space="preserve">5.35507726669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30803442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859916687012</t>
   </si>
   <si>
     <t xml:space="preserve">5.39428043365479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24531030654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26883125305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315046310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14338302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06497812271118</t>
+    <t xml:space="preserve">5.24531078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26883172988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315141677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14338350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06497859954834</t>
   </si>
   <si>
     <t xml:space="preserve">5.00225400924683</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">5.16690540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20610761642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33939695358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235410690308</t>
+    <t xml:space="preserve">5.20610809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2923526763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.11986207962036</t>
@@ -1985,34 +1985,34 @@
     <t xml:space="preserve">5.13554334640503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09634017944336</t>
+    <t xml:space="preserve">5.09634065628052</t>
   </si>
   <si>
     <t xml:space="preserve">5.11202144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17474603652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44916343688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4570050239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61381483078003</t>
+    <t xml:space="preserve">5.17474555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44916391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45700454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61381435394287</t>
   </si>
   <si>
     <t xml:space="preserve">5.70790147781372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6765398979187</t>
+    <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733673095703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55893182754517</t>
+    <t xml:space="preserve">5.55893135070801</t>
   </si>
   <si>
     <t xml:space="preserve">5.51188802719116</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48052597045898</t>
+    <t xml:space="preserve">5.48052644729614</t>
   </si>
   <si>
     <t xml:space="preserve">5.36291885375977</t>
@@ -2030,82 +2030,82 @@
     <t xml:space="preserve">5.31587553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3237156867981</t>
+    <t xml:space="preserve">5.32371520996094</t>
   </si>
   <si>
     <t xml:space="preserve">5.19826698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79840040206909</t>
+    <t xml:space="preserve">4.79839992523193</t>
   </si>
   <si>
     <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71999502182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51614189147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97089242935181</t>
+    <t xml:space="preserve">4.71999549865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51614141464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97089195251465</t>
   </si>
   <si>
     <t xml:space="preserve">4.82192182540894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64158964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71215534210205</t>
+    <t xml:space="preserve">4.6415901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71215486526489</t>
   </si>
   <si>
     <t xml:space="preserve">4.67295217514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63374900817871</t>
+    <t xml:space="preserve">4.63374996185303</t>
   </si>
   <si>
     <t xml:space="preserve">4.64943075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59454727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62590932846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6807918548584</t>
+    <t xml:space="preserve">4.59454679489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62590885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68079233169556</t>
   </si>
   <si>
     <t xml:space="preserve">4.90032768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2296290397644</t>
+    <t xml:space="preserve">5.22962951660156</t>
   </si>
   <si>
     <t xml:space="preserve">5.02577543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0414571762085</t>
+    <t xml:space="preserve">5.04145669937134</t>
   </si>
   <si>
     <t xml:space="preserve">5.15122413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22178840637207</t>
+    <t xml:space="preserve">5.22178888320923</t>
   </si>
   <si>
     <t xml:space="preserve">5.21394872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15906476974487</t>
+    <t xml:space="preserve">5.15906524658203</t>
   </si>
   <si>
     <t xml:space="preserve">5.08065938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12770223617554</t>
+    <t xml:space="preserve">5.1277027130127</t>
   </si>
   <si>
     <t xml:space="preserve">5.01793527603149</t>
@@ -2114,31 +2114,31 @@
     <t xml:space="preserve">5.07281875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08849954605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19042634963989</t>
+    <t xml:space="preserve">5.08849906921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19042682647705</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52756929397583</t>
+    <t xml:space="preserve">5.52756881713867</t>
   </si>
   <si>
     <t xml:space="preserve">5.5197286605835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40212059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56677150726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4334831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50404739379883</t>
+    <t xml:space="preserve">5.4021201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56677198410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43348264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50404787063599</t>
   </si>
   <si>
     <t xml:space="preserve">5.53540992736816</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">5.41780185699463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42564249038696</t>
+    <t xml:space="preserve">5.42564296722412</t>
   </si>
   <si>
     <t xml:space="preserve">5.84119033813477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7627854347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517641067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44132328033447</t>
+    <t xml:space="preserve">5.76278495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44132375717163</t>
   </si>
   <si>
     <t xml:space="preserve">5.40996122360229</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">5.34723711013794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37075901031494</t>
+    <t xml:space="preserve">5.37075853347778</t>
   </si>
   <si>
     <t xml:space="preserve">5.23746967315674</t>
@@ -2180,67 +2180,67 @@
     <t xml:space="preserve">4.97873258590698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8376030921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89248704910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896514892578</t>
+    <t xml:space="preserve">4.83760356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89248657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896562576294</t>
   </si>
   <si>
     <t xml:space="preserve">4.92384910583496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87680578231812</t>
+    <t xml:space="preserve">4.87680530548096</t>
   </si>
   <si>
     <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57102584838867</t>
+    <t xml:space="preserve">4.57102489471436</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750394821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57886648178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39069271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15547800064087</t>
+    <t xml:space="preserve">4.57886600494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39069318771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15547752380371</t>
   </si>
   <si>
     <t xml:space="preserve">4.2260422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11627531051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84185671806335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63800287246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26165771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29301977157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32438206672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099406242371</t>
+    <t xml:space="preserve">4.1162748336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8418562412262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63800311088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26165795326233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29302000999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32438182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099358558655</t>
   </si>
   <si>
     <t xml:space="preserve">3.09700679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05780434608459</t>
+    <t xml:space="preserve">3.05780458450317</t>
   </si>
   <si>
     <t xml:space="preserve">2.94803690910339</t>
@@ -2258,22 +2258,22 @@
     <t xml:space="preserve">3.21461462974548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25381779670715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2224555015564</t>
+    <t xml:space="preserve">3.25381731987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22245526313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.24205684661865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24597668647766</t>
+    <t xml:space="preserve">3.24597692489624</t>
   </si>
   <si>
     <t xml:space="preserve">3.23813652992249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36750483512878</t>
+    <t xml:space="preserve">3.36750507354736</t>
   </si>
   <si>
     <t xml:space="preserve">3.34006333351135</t>
@@ -2282,85 +2282,85 @@
     <t xml:space="preserve">3.45767092704773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59880042076111</t>
+    <t xml:space="preserve">3.59880065917969</t>
   </si>
   <si>
     <t xml:space="preserve">3.37142515182495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52039480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54391694068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72424912452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81049466133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92026138305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3358097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32796955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32012844085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23388242721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1633186340332</t>
+    <t xml:space="preserve">3.52039456367493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54391646385193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72424864768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81049418449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92026209831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33580923080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32796907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32012891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23388290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16331815719604</t>
   </si>
   <si>
     <t xml:space="preserve">4.07707214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21820163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740432739258</t>
+    <t xml:space="preserve">4.21820211410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036195755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740385055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84577655792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009576797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321877479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8222553730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145830154419</t>
+    <t xml:space="preserve">3.732088804245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481387138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401608467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577679634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70072722434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265402793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225584983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145782470703</t>
   </si>
   <si>
     <t xml:space="preserve">3.75169038772583</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">3.74384999275208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98298597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660654067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10059404373169</t>
+    <t xml:space="preserve">3.98298573493958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10059356689453</t>
   </si>
   <si>
     <t xml:space="preserve">3.91634130477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95946478843689</t>
+    <t xml:space="preserve">3.95946502685547</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
@@ -2390,22 +2390,22 @@
     <t xml:space="preserve">4.13979721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763736724854</t>
+    <t xml:space="preserve">4.14763689041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.01434803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95162415504456</t>
+    <t xml:space="preserve">3.95162463188171</t>
   </si>
   <si>
     <t xml:space="preserve">3.9437837600708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88889980316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05355024337769</t>
+    <t xml:space="preserve">3.8889000415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.053551197052</t>
   </si>
   <si>
     <t xml:space="preserve">4.06923151016235</t>
@@ -2414,34 +2414,34 @@
     <t xml:space="preserve">4.030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89282035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810201644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242098808289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8575382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86537837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617568969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105916976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90850138664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913284301758</t>
+    <t xml:space="preserve">3.89281988143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810273170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753774642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86537766456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617521286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458154678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085009098053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913236618042</t>
   </si>
   <si>
     <t xml:space="preserve">3.755610704422</t>
@@ -2450,76 +2450,76 @@
     <t xml:space="preserve">3.74777030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80657410621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497948646545</t>
+    <t xml:space="preserve">3.80657434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497996330261</t>
   </si>
   <si>
     <t xml:space="preserve">3.96730518341064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02218914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594288825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75953125953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6458432674408</t>
+    <t xml:space="preserve">4.02218866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345133781433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75953078269958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64584398269653</t>
   </si>
   <si>
     <t xml:space="preserve">3.66936492919922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66544508934021</t>
+    <t xml:space="preserve">3.66544556617737</t>
   </si>
   <si>
     <t xml:space="preserve">3.63016247749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56351804733276</t>
+    <t xml:space="preserve">3.56351828575134</t>
   </si>
   <si>
     <t xml:space="preserve">3.56743860244751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5909595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903298377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119282722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44198966026306</t>
+    <t xml:space="preserve">3.59096002578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44198989868164</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871066570282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31654167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33222246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238807678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43806958198547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551179885864</t>
+    <t xml:space="preserve">3.31654119491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33222270011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43807005882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551132202148</t>
   </si>
   <si>
     <t xml:space="preserve">3.4929530620575</t>
@@ -2528,28 +2528,28 @@
     <t xml:space="preserve">3.55175757408142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55567741394043</t>
+    <t xml:space="preserve">3.55567717552185</t>
   </si>
   <si>
     <t xml:space="preserve">3.50079369544983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51255488395691</t>
+    <t xml:space="preserve">3.51255416870117</t>
   </si>
   <si>
     <t xml:space="preserve">3.37926602363586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43414950370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630887031555</t>
+    <t xml:space="preserve">3.43414974212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630863189697</t>
   </si>
   <si>
     <t xml:space="preserve">3.46159100532532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44983053207397</t>
+    <t xml:space="preserve">3.44983077049255</t>
   </si>
   <si>
     <t xml:space="preserve">3.15189051628113</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">4.10843467712402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99866652488708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0927529335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28876686096191</t>
+    <t xml:space="preserve">3.99866724014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13195562362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09275341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06139135360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2887659072876</t>
   </si>
   <si>
     <t xml:space="preserve">4.24956369400024</t>
@@ -2597,28 +2597,28 @@
     <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3985333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35933065414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69647312164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919771194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976245880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72783660888672</t>
+    <t xml:space="preserve">4.39853382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35933113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69647359848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75919818878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976198196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72783613204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.74351692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703834533691</t>
+    <t xml:space="preserve">4.76703786849976</t>
   </si>
   <si>
     <t xml:space="preserve">4.77487897872925</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">4.73567676544189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68863296508789</t>
+    <t xml:space="preserve">4.68863344192505</t>
   </si>
   <si>
     <t xml:space="preserve">4.80624103546143</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">5.01009464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99441337585449</t>
+    <t xml:space="preserve">4.99441385269165</t>
   </si>
   <si>
     <t xml:space="preserve">4.9473705291748</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">4.86112451553345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84544324874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91600894927979</t>
+    <t xml:space="preserve">4.84544372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91600847244263</t>
   </si>
   <si>
     <t xml:space="preserve">4.93952989578247</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">5.04929780960083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58245229721069</t>
+    <t xml:space="preserve">5.58245277404785</t>
   </si>
   <si>
     <t xml:space="preserve">5.68438005447388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59813404083252</t>
+    <t xml:space="preserve">5.59813356399536</t>
   </si>
   <si>
     <t xml:space="preserve">5.6294960975647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7157416343689</t>
+    <t xml:space="preserve">5.71574211120605</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222021102905</t>
@@ -2678,40 +2678,40 @@
     <t xml:space="preserve">5.66869878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66085815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72358274459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78630685806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08424711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17833280563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14697074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97447872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720235824585</t>
+    <t xml:space="preserve">5.66085767745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72358226776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78630638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08424663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1783332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14697122573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288362503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97447919845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11834812164307</t>
+    <t xml:space="preserve">6.00474452972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11834859848022</t>
   </si>
   <si>
     <t xml:space="preserve">6.49161624908447</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">6.45915842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42670011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2644100189209</t>
+    <t xml:space="preserve">6.42670059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26440906524658</t>
   </si>
   <si>
     <t xml:space="preserve">6.41047096252441</t>
@@ -2732,49 +2732,49 @@
     <t xml:space="preserve">6.39424228668213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4429292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96225786209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077806472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43289995193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00091743469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83862638473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87108421325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78993988037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95222997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90354347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60139274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64196300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56081867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43910026550293</t>
+    <t xml:space="preserve">6.44292974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96225833892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43290090560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00091648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83862590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87108469009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78993940353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95222902297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90354251861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64196395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56081962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43910121917725</t>
   </si>
   <si>
     <t xml:space="preserve">8.19566631317139</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">8.23623752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01714611053467</t>
+    <t xml:space="preserve">8.01714706420898</t>
   </si>
   <si>
     <t xml:space="preserve">8.06583309173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96845865249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40044260025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25438070297241</t>
+    <t xml:space="preserve">7.96845960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40044164657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25438022613525</t>
   </si>
   <si>
     <t xml:space="preserve">7.4815878868103</t>
@@ -2804,52 +2804,52 @@
     <t xml:space="preserve">7.64387893676758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56273174285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69256544113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502470016479</t>
+    <t xml:space="preserve">7.5627326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69256448745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502279281616</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62764835357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535778045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81619644165039</t>
+    <t xml:space="preserve">7.62764930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4653582572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3030686378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192239761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81619691848755</t>
   </si>
   <si>
     <t xml:space="preserve">7.15700674057007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23815250396729</t>
+    <t xml:space="preserve">7.23815155029297</t>
   </si>
   <si>
     <t xml:space="preserve">7.38421392440796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70879507064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61141967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53027439117432</t>
+    <t xml:space="preserve">7.70879411697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61142015457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010713577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53027486801147</t>
   </si>
   <si>
     <t xml:space="preserve">7.74125289916992</t>
@@ -2858,34 +2858,34 @@
     <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15509414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96654605865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84482765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52024745941162</t>
+    <t xml:space="preserve">8.1550931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96654510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5202465057373</t>
   </si>
   <si>
     <t xml:space="preserve">8.39852905273438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47967433929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31738376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08206272125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1145191192627</t>
+    <t xml:space="preserve">8.47967338562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31738185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08206367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11452102661133</t>
   </si>
   <si>
     <t xml:space="preserve">8.03337478637695</t>
@@ -2894,43 +2894,43 @@
     <t xml:space="preserve">8.04960441589355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04769039154053</t>
+    <t xml:space="preserve">9.04768943786621</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940784454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44524192810059</t>
+    <t xml:space="preserve">9.16940879821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
     <t xml:space="preserve">9.40345001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23627758026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48703575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77958679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6124153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57062244415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52882862091064</t>
+    <t xml:space="preserve">9.23627662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48703670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7795877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61241436004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57062149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52882957458496</t>
   </si>
   <si>
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779487609863</t>
+    <t xml:space="preserve">9.73779392242432</t>
   </si>
   <si>
     <t xml:space="preserve">9.65420818328857</t>
@@ -2972,79 +2972,79 @@
     <t xml:space="preserve">9.11089706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36165523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06910514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9437255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90193271636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81834697723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758785247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52579307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73476028442383</t>
+    <t xml:space="preserve">9.36165618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06910419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94372463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90193176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81834602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758594512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52579402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73475933074951</t>
   </si>
   <si>
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846881866455</t>
+    <t xml:space="preserve">8.30846977233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.32518768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65649652481079</t>
+    <t xml:space="preserve">7.65649747848511</t>
   </si>
   <si>
     <t xml:space="preserve">7.82366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67321538925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07139444351196</t>
+    <t xml:space="preserve">7.67321491241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154626846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07139348983765</t>
   </si>
   <si>
     <t xml:space="preserve">7.10482835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68993091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589113235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053916931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80695247650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62306308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99084186553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04099464416504</t>
+    <t xml:space="preserve">7.68993234634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80695295333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62306261062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99084281921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09114646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04099369049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.27503490447998</t>
@@ -3053,13 +3053,13 @@
     <t xml:space="preserve">8.40041542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1078634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48400115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30011081695557</t>
+    <t xml:space="preserve">8.10786247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48400020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30011177062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.35026264190674</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69828987121582</t>
+    <t xml:space="preserve">7.87382221221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69829082489014</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531095504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77351856231689</t>
+    <t xml:space="preserve">7.81531190872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77351903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.91561508178711</t>
@@ -3089,22 +3089,22 @@
     <t xml:space="preserve">7.78187656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60634613037109</t>
+    <t xml:space="preserve">7.60634565353394</t>
   </si>
   <si>
     <t xml:space="preserve">7.89889764785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79859447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023504257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978004455566</t>
+    <t xml:space="preserve">7.79859352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978099822998</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
@@ -3116,10 +3116,10 @@
     <t xml:space="preserve">8.24154376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21537971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28514957427979</t>
+    <t xml:space="preserve">8.21538066864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28514862060547</t>
   </si>
   <si>
     <t xml:space="preserve">8.32003498077393</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">8.38108253479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19793701171875</t>
+    <t xml:space="preserve">8.19793796539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.49445819854736</t>
@@ -3140,16 +3140,16 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678630828857</t>
+    <t xml:space="preserve">8.54678535461426</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64271831512451</t>
+    <t xml:space="preserve">8.59039211273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64271926879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.63399791717529</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">8.45957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12816715240479</t>
+    <t xml:space="preserve">8.17177486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1281681060791</t>
   </si>
   <si>
     <t xml:space="preserve">7.93630123138428</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">7.78804016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65722179412842</t>
+    <t xml:space="preserve">7.65722274780273</t>
   </si>
   <si>
     <t xml:space="preserve">7.76187658309937</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">7.70082855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59617376327515</t>
+    <t xml:space="preserve">7.5961742401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.46535634994507</t>
@@ -3218,28 +3218,28 @@
     <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50024127960205</t>
+    <t xml:space="preserve">7.73571300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50024080276489</t>
   </si>
   <si>
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44791316986084</t>
+    <t xml:space="preserve">7.55256843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.447913646698</t>
   </si>
   <si>
     <t xml:space="preserve">7.53512620925903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5176830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50896120071411</t>
+    <t xml:space="preserve">7.51768350601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50896167755127</t>
   </si>
   <si>
     <t xml:space="preserve">7.57001066207886</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">8.72121047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48573780059814</t>
+    <t xml:space="preserve">8.48573684692383</t>
   </si>
   <si>
     <t xml:space="preserve">8.50318050384521</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">8.02351379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37236309051514</t>
+    <t xml:space="preserve">8.37236213684082</t>
   </si>
   <si>
     <t xml:space="preserve">7.89269495010376</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">7.68338632583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33453750610352</t>
+    <t xml:space="preserve">7.33453798294067</t>
   </si>
   <si>
     <t xml:space="preserve">7.16883516311646</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418085098267</t>
+    <t xml:space="preserve">7.06418037414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
@@ -3335,40 +3335,40 @@
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7531566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43919229507446</t>
+    <t xml:space="preserve">7.75315570831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4391918182373</t>
   </si>
   <si>
     <t xml:space="preserve">7.43047189712524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49151945114136</t>
+    <t xml:space="preserve">7.49151992797852</t>
   </si>
   <si>
     <t xml:space="preserve">7.27348899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39558553695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38686561584473</t>
+    <t xml:space="preserve">7.39558601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38686513900757</t>
   </si>
   <si>
     <t xml:space="preserve">7.35198068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3170952796936</t>
+    <t xml:space="preserve">7.31709575653076</t>
   </si>
   <si>
     <t xml:space="preserve">7.47407722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29093170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581663131714</t>
+    <t xml:space="preserve">7.290931224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581615447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.30837440490723</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663499832153</t>
+    <t xml:space="preserve">7.45663547515869</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781145095825</t>
+    <t xml:space="preserve">7.85781049728394</t>
   </si>
   <si>
     <t xml:space="preserve">8.03223514556885</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">8.1020040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15433120727539</t>
+    <t xml:space="preserve">8.15433216094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.05839824676514</t>
@@ -3401,16 +3401,16 @@
     <t xml:space="preserve">8.09328365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00607013702393</t>
+    <t xml:space="preserve">8.00607109069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584190368652</t>
+    <t xml:space="preserve">8.11072635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584095001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
@@ -3452,19 +3452,19 @@
     <t xml:space="preserve">8.94796180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87819290161133</t>
+    <t xml:space="preserve">8.87819194793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.89563465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65144157409668</t>
+    <t xml:space="preserve">8.65144062042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.6601619720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79097938537598</t>
+    <t xml:space="preserve">8.79098033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.70376777648926</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">8.86074924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93052005767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62527656555176</t>
+    <t xml:space="preserve">8.93051910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62527751922607</t>
   </si>
   <si>
     <t xml:space="preserve">8.56422805786133</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">8.46829509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68632507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15727043151855</t>
+    <t xml:space="preserve">8.6863260269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15727138519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">8.96540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00028896331787</t>
+    <t xml:space="preserve">9.00028800964355</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66888236999512</t>
+    <t xml:space="preserve">8.80842304229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66888332366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.91124629974365</t>
@@ -4302,6 +4302,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.1000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3000001907349</t>
   </si>
 </sst>
 </file>
@@ -70056,13 +70059,13 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6911111111</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>4800</v>
       </c>
       <c r="C2517" t="n">
-        <v>11.0500001907349</v>
+        <v>11.1000003814697</v>
       </c>
       <c r="D2517" t="n">
         <v>10.8500003814697</v>
@@ -70077,6 +70080,32 @@
         <v>1429</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6910763889</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>8136</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">1.21355497837067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22546637058258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20654833316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23177230358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24998962879181</t>
+    <t xml:space="preserve">1.22546660900116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20654845237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23177242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2499897480011</t>
   </si>
   <si>
     <t xml:space="preserve">1.26330232620239</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">1.27311182022095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26120030879974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718725681305</t>
+    <t xml:space="preserve">1.26120042800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718701839447</t>
   </si>
   <si>
     <t xml:space="preserve">1.20794975757599</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">1.19323563575745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501866817474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814038276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24578595161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23457515239716</t>
+    <t xml:space="preserve">1.17501842975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19814050197601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24578583240509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
     <t xml:space="preserve">1.21495640277863</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">1.17992317676544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17641985416412</t>
+    <t xml:space="preserve">1.17641973495483</t>
   </si>
   <si>
     <t xml:space="preserve">1.12457036972046</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">1.12807381153107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10284984111786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08603370189667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01596701145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02507591247559</t>
+    <t xml:space="preserve">1.10284972190857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08603358268738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01596713066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02507555484772</t>
   </si>
   <si>
     <t xml:space="preserve">1.02017104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00195360183716</t>
+    <t xml:space="preserve">1.00195372104645</t>
   </si>
   <si>
     <t xml:space="preserve">1.02297377586365</t>
@@ -131,64 +131,64 @@
     <t xml:space="preserve">1.04329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09654366970062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11335980892181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1105569601059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09304022789001</t>
+    <t xml:space="preserve">1.0965439081192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1133599281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11055719852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0930403470993</t>
   </si>
   <si>
     <t xml:space="preserve">1.12106716632843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13017582893372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15610027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10004699230194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13157713413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705363750458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227772712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1182644367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14909374713898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17852175235748</t>
+    <t xml:space="preserve">1.13017570972443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15610015392303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10004723072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13157725334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227784633636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11826431751251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14909362792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852187156677</t>
   </si>
   <si>
     <t xml:space="preserve">1.17011380195618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18412721157074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081415653229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16310703754425</t>
+    <t xml:space="preserve">1.18412709236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081439495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16310715675354</t>
   </si>
   <si>
     <t xml:space="preserve">1.22616708278656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24508500099182</t>
+    <t xml:space="preserve">1.24508512020111</t>
   </si>
   <si>
     <t xml:space="preserve">1.24088132381439</t>
@@ -200,52 +200,52 @@
     <t xml:space="preserve">1.19113385677338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22686767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22196304798126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24438428878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17221558094025</t>
+    <t xml:space="preserve">1.22686779499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22196316719055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24438440799713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17221570014954</t>
   </si>
   <si>
     <t xml:space="preserve">1.19183444976807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19743978977203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20374596118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.203045129776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23807835578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23317360877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19954168796539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247656583786</t>
+    <t xml:space="preserve">1.19743955135345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20374572277069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20304501056671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23807847499847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23317384719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19954180717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22476589679718</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845972537994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21916031837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896981239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.212153673172</t>
+    <t xml:space="preserve">1.21916043758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2289696931839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21215379238129</t>
   </si>
   <si>
     <t xml:space="preserve">1.22266376018524</t>
@@ -254,37 +254,37 @@
     <t xml:space="preserve">1.29202973842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2962338924408</t>
+    <t xml:space="preserve">1.29623377323151</t>
   </si>
   <si>
     <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28712522983551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28151977062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788784980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737776279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865035057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469908714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138627052307</t>
+    <t xml:space="preserve">1.28712511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28151965141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788773059845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737788200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865046977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469920635223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138650894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.11896502971649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12036657333374</t>
+    <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
     <t xml:space="preserve">1.13648164272308</t>
@@ -293,34 +293,34 @@
     <t xml:space="preserve">1.14629113674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14208686351776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07202053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084632396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501388549805</t>
+    <t xml:space="preserve">1.14208722114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07202017307281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08463251590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501364707947</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253049850464</t>
+    <t xml:space="preserve">1.08253037929535</t>
   </si>
   <si>
     <t xml:space="preserve">1.07902705669403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05800712108612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1014484167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355031490326</t>
+    <t xml:space="preserve">1.05800700187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10144853591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355043411255</t>
   </si>
   <si>
     <t xml:space="preserve">1.09514236450195</t>
@@ -332,55 +332,55 @@
     <t xml:space="preserve">1.09934639930725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11265897750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15680110454559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528028964996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681509494781</t>
+    <t xml:space="preserve">1.11265921592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1568009853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528052806854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4868152141571</t>
   </si>
   <si>
     <t xml:space="preserve">1.48821651935577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45178210735321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4153470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4573872089386</t>
+    <t xml:space="preserve">1.45178174972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41534721851349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45738708972931</t>
   </si>
   <si>
     <t xml:space="preserve">1.40133380889893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46999931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776834011078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375516891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43636691570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936038970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42235386371613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814970970154</t>
+    <t xml:space="preserve">1.46999907493591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375528812408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4363671541214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936050891876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674864292145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42235362529755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814982891083</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">1.42795920372009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48120975494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69421255588531</t>
+    <t xml:space="preserve">1.48121011257172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69421279430389</t>
   </si>
   <si>
     <t xml:space="preserve">1.66338324546814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80071401596069</t>
+    <t xml:space="preserve">1.8007138967514</t>
   </si>
   <si>
     <t xml:space="preserve">1.84555673599243</t>
@@ -407,76 +407,76 @@
     <t xml:space="preserve">1.79230582714081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79090440273285</t>
+    <t xml:space="preserve">1.79090476036072</t>
   </si>
   <si>
     <t xml:space="preserve">1.77268731594086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73064696788788</t>
+    <t xml:space="preserve">1.73064720630646</t>
   </si>
   <si>
     <t xml:space="preserve">1.71663391590118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670060634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84275388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8259379863739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313501834869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8399510383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83854985237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84415543079376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83014190196991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472730636597</t>
+    <t xml:space="preserve">1.78670072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275424480438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593786716461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313525676727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995091915131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854997158051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84415531158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014214038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472718715668</t>
   </si>
   <si>
     <t xml:space="preserve">1.82874059677124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81192493438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294463157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835934638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99549961090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07257294654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02913117408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798742294312</t>
+    <t xml:space="preserve">1.81192481517792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294439315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835958480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937928199768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549973011017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0725724697113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0291314125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798718452454</t>
   </si>
   <si>
     <t xml:space="preserve">2.04034209251404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99830198287964</t>
+    <t xml:space="preserve">1.99830210208893</t>
   </si>
   <si>
     <t xml:space="preserve">2.03053259849548</t>
@@ -485,106 +485,106 @@
     <t xml:space="preserve">2.01932191848755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99970352649689</t>
+    <t xml:space="preserve">1.9997034072876</t>
   </si>
   <si>
     <t xml:space="preserve">2.01231551170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09359240531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066597938538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15945553779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989427089691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339269161224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167646884918</t>
+    <t xml:space="preserve">2.09359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066621780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15945529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989379405975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339245319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167670726776</t>
   </si>
   <si>
     <t xml:space="preserve">1.95345938205719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01651930809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250649452209</t>
+    <t xml:space="preserve">2.01651954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250601768494</t>
   </si>
   <si>
     <t xml:space="preserve">1.98428869247437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97868311405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944585323334</t>
+    <t xml:space="preserve">1.9786833524704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944561481476</t>
   </si>
   <si>
     <t xml:space="preserve">1.91982746124268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377418041229</t>
+    <t xml:space="preserve">1.86377394199371</t>
   </si>
   <si>
     <t xml:space="preserve">1.86797785758972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87918841838837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85676741600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78950309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631935596466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89880740642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91001808643341</t>
+    <t xml:space="preserve">1.87918865680695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8567670583725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78950333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631947517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301144123077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89880764484406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001796722412</t>
   </si>
   <si>
     <t xml:space="preserve">1.99690043926239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98849296569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569047451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224870204926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766341686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9618673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326899528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97027540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00390720367432</t>
+    <t xml:space="preserve">1.98849308490753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98569011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224858283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186721324921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326887607574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027552127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0039074420929</t>
   </si>
   <si>
     <t xml:space="preserve">2.07397413253784</t>
@@ -593,46 +593,46 @@
     <t xml:space="preserve">2.18888354301453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16506099700928</t>
+    <t xml:space="preserve">2.1650607585907</t>
   </si>
   <si>
     <t xml:space="preserve">2.13283014297485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06416463851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09639525413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601424217224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499406814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11321139335632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14404106140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002777099609</t>
+    <t xml:space="preserve">2.06416487693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09639501571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601400375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499430656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11321115493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14404034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002729415894</t>
   </si>
   <si>
     <t xml:space="preserve">2.14824461936951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13423156738281</t>
+    <t xml:space="preserve">2.13423132896423</t>
   </si>
   <si>
     <t xml:space="preserve">2.14123797416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13703393936157</t>
+    <t xml:space="preserve">2.15244889259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13703417778015</t>
   </si>
   <si>
     <t xml:space="preserve">2.11181020736694</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">2.24213433265686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48876857757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4873673915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297285079956</t>
+    <t xml:space="preserve">2.48876881599426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48736763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297261238098</t>
   </si>
   <si>
     <t xml:space="preserve">2.48316359519958</t>
@@ -671,88 +671,88 @@
     <t xml:space="preserve">2.40328741073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48036098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46634721755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44392609596252</t>
+    <t xml:space="preserve">2.52099967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48036074638367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46634769439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4439263343811</t>
   </si>
   <si>
     <t xml:space="preserve">2.43972229957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47615671157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45513677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4943745136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47335410118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65552735328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71858787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7045738697052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751033782959</t>
+    <t xml:space="preserve">2.47615694999695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45513701438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437403678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47335433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6555278301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71858763694763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70457434654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751057624817</t>
   </si>
   <si>
     <t xml:space="preserve">2.78865432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11096119880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2398841381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38422083854675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129393577576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003127098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040809631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66098403930664</t>
+    <t xml:space="preserve">3.11096167564392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23988389968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38422131538391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129441261292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040738105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251418113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6609845161438</t>
   </si>
   <si>
     <t xml:space="preserve">3.69601821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78360152244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176148414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386804580688</t>
+    <t xml:space="preserve">3.78360104560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9517617225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386852264404</t>
   </si>
   <si>
     <t xml:space="preserve">4.19349145889282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16896820068359</t>
+    <t xml:space="preserve">4.16896772384644</t>
   </si>
   <si>
     <t xml:space="preserve">4.11291456222534</t>
@@ -764,85 +764,85 @@
     <t xml:space="preserve">4.30910158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30559778213501</t>
+    <t xml:space="preserve">4.30559825897217</t>
   </si>
   <si>
     <t xml:space="preserve">4.55433511734009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69797086715698</t>
+    <t xml:space="preserve">4.6979718208313</t>
   </si>
   <si>
     <t xml:space="preserve">5.50023555755615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79256153106689</t>
+    <t xml:space="preserve">4.79256200790405</t>
   </si>
   <si>
     <t xml:space="preserve">5.10085535049438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01677513122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44768476486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4441819190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77349519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39708948135376</t>
+    <t xml:space="preserve">5.0167760848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44768571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44418239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77349472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">6.76143598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49518299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369325637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78433322906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626649856567</t>
+    <t xml:space="preserve">6.49518251419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238851547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369277954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858285903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78433275222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626602172852</t>
   </si>
   <si>
     <t xml:space="preserve">6.5325288772583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35266780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07208585739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32389068603516</t>
+    <t xml:space="preserve">6.35266876220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07208681106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32388973236084</t>
   </si>
   <si>
     <t xml:space="preserve">6.43900108337402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51094532012939</t>
+    <t xml:space="preserve">6.51094579696655</t>
   </si>
   <si>
     <t xml:space="preserve">6.40302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15842008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798803329468</t>
+    <t xml:space="preserve">6.15841865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798898696899</t>
   </si>
   <si>
     <t xml:space="preserve">6.37425184249878</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">6.47137594223022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15122509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11165475845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96057319641113</t>
+    <t xml:space="preserve">6.32748746871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1512246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11165523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96057224273682</t>
   </si>
   <si>
     <t xml:space="preserve">5.85265636444092</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">5.90661478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89582300186157</t>
+    <t xml:space="preserve">5.89582347869873</t>
   </si>
   <si>
     <t xml:space="preserve">5.75193500518799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6943793296814</t>
+    <t xml:space="preserve">5.69437885284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.70157384872437</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">5.3670334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87421655654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1799783706665</t>
+    <t xml:space="preserve">4.87421607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17997884750366</t>
   </si>
   <si>
     <t xml:space="preserve">4.97853517532349</t>
@@ -899,61 +899,61 @@
     <t xml:space="preserve">4.96414613723755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84543895721436</t>
+    <t xml:space="preserve">4.8454384803772</t>
   </si>
   <si>
     <t xml:space="preserve">4.87781381607056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9101881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92457723617554</t>
+    <t xml:space="preserve">4.91018772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92457675933838</t>
   </si>
   <si>
     <t xml:space="preserve">4.76989698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69075775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65838384628296</t>
+    <t xml:space="preserve">4.69075870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65838432312012</t>
   </si>
   <si>
     <t xml:space="preserve">4.68716096878052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82385492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5504674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51089811325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49291181564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43895435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38139915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38499546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46413421630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03609037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85623025894165</t>
+    <t xml:space="preserve">4.82385540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55046701431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51089859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49291229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43895387649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38139867782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38499641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46413373947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03609085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85622978210449</t>
   </si>
   <si>
     <t xml:space="preserve">4.80946683883667</t>
@@ -962,46 +962,46 @@
     <t xml:space="preserve">4.76629972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68356466293335</t>
+    <t xml:space="preserve">4.68356418609619</t>
   </si>
   <si>
     <t xml:space="preserve">4.67636966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59003639221191</t>
+    <t xml:space="preserve">4.60442590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59003686904907</t>
   </si>
   <si>
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67277193069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74831342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75910520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95335483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14400720596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1152286529541</t>
+    <t xml:space="preserve">4.66198110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74831295013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75910472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14400672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.19436740875244</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.10803461074829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93536901473999</t>
+    <t xml:space="preserve">4.93536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">4.7555079460144</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">4.99652147293091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90659141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82025766372681</t>
+    <t xml:space="preserve">4.90659093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92098045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82025814056396</t>
   </si>
   <si>
     <t xml:space="preserve">4.89220237731934</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">5.05407619476318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07925701141357</t>
+    <t xml:space="preserve">5.07925748825073</t>
   </si>
   <si>
     <t xml:space="preserve">5.0181040763855</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">4.94616031646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15839576721191</t>
+    <t xml:space="preserve">5.15839529037476</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393678665161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6080470085144</t>
+    <t xml:space="preserve">5.60804653167725</t>
   </si>
   <si>
     <t xml:space="preserve">5.8994197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77711534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611373901367</t>
+    <t xml:space="preserve">5.7771143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611421585083</t>
   </si>
   <si>
     <t xml:space="preserve">5.94978141784668</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">7.03613758087158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89584589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527633666992</t>
+    <t xml:space="preserve">6.89584636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527681350708</t>
   </si>
   <si>
     <t xml:space="preserve">7.13685894012451</t>
@@ -1091,244 +1091,244 @@
     <t xml:space="preserve">7.69802379608154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12968826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43904781341553</t>
+    <t xml:space="preserve">8.12968921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43904972076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.95704650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29518413543701</t>
+    <t xml:space="preserve">9.29518508911133</t>
   </si>
   <si>
     <t xml:space="preserve">10.2160692214966</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42465877532959</t>
+    <t xml:space="preserve">8.42465972900391</t>
   </si>
   <si>
     <t xml:space="preserve">8.6189079284668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22321605682373</t>
+    <t xml:space="preserve">8.22321701049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.0145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80594062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32393741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99299430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10091114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98580169677734</t>
+    <t xml:space="preserve">7.80594205856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32393836975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99299478530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10091209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98580074310303</t>
   </si>
   <si>
     <t xml:space="preserve">7.8850793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73399591445923</t>
+    <t xml:space="preserve">7.73399543762207</t>
   </si>
   <si>
     <t xml:space="preserve">7.41024732589722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54694080352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499704360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341444015503</t>
+    <t xml:space="preserve">7.54694175720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499799728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341300964355</t>
   </si>
   <si>
     <t xml:space="preserve">7.52535915374756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38866472244263</t>
+    <t xml:space="preserve">7.38866376876831</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760509490967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84191131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910774230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04335689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824506759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630226135254</t>
+    <t xml:space="preserve">7.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702314376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910678863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04335498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824554443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85630178451538</t>
   </si>
   <si>
     <t xml:space="preserve">7.74838447570801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57571887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463636398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1944146156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498559951782</t>
+    <t xml:space="preserve">7.57571935653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.424635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419382095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498464584351</t>
   </si>
   <si>
     <t xml:space="preserve">7.2088041305542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20161008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25196933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722105026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448551177979</t>
+    <t xml:space="preserve">7.20160865783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485715866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448455810547</t>
   </si>
   <si>
     <t xml:space="preserve">7.00735998153687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89944505691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340251922607</t>
+    <t xml:space="preserve">6.89944410324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340204238892</t>
   </si>
   <si>
     <t xml:space="preserve">7.15844249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91743040084839</t>
+    <t xml:space="preserve">6.91742944717407</t>
   </si>
   <si>
     <t xml:space="preserve">6.85627746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89225006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78793001174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95699977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98218011856079</t>
+    <t xml:space="preserve">6.89224910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7879319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95700073242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217964172363</t>
   </si>
   <si>
     <t xml:space="preserve">7.16204023361206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14045667648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02174854278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33830213546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82752370834351</t>
+    <t xml:space="preserve">7.14045763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0217490196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.338303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82752418518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.25918769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15846538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9138560295105</t>
+    <t xml:space="preserve">8.15846729278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91385555267334</t>
   </si>
   <si>
     <t xml:space="preserve">7.8994665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313467025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924524307251</t>
+    <t xml:space="preserve">7.81313419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924619674683</t>
   </si>
   <si>
     <t xml:space="preserve">7.76996755599976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64046764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435659408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48219108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79152631759644</t>
+    <t xml:space="preserve">7.64046812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4821925163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79152822494507</t>
   </si>
   <si>
     <t xml:space="preserve">6.7483606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56850147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6404447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48936176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325119018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62605619430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56130599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447406768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411148071289</t>
+    <t xml:space="preserve">6.56850099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64044570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56130647659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447263717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411100387573</t>
   </si>
   <si>
     <t xml:space="preserve">6.28791809082031</t>
@@ -1340,43 +1340,43 @@
     <t xml:space="preserve">6.02172517776489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87783670425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86344766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25914144515991</t>
+    <t xml:space="preserve">5.87783765792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86344814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2591404914856</t>
   </si>
   <si>
     <t xml:space="preserve">6.26633501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44619560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46777868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51814031600952</t>
+    <t xml:space="preserve">6.44619512557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46777820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641687393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51814126968384</t>
   </si>
   <si>
     <t xml:space="preserve">6.46058416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29511260986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10086297988892</t>
+    <t xml:space="preserve">6.29511213302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10086345672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.13683557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92819786071777</t>
+    <t xml:space="preserve">5.92819738388062</t>
   </si>
   <si>
     <t xml:space="preserve">5.93539190292358</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">5.97136402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01453018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99294805526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17280769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18719720840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25194597244263</t>
+    <t xml:space="preserve">6.01453113555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99294757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1728081703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18719673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25194644927979</t>
   </si>
   <si>
     <t xml:space="preserve">6.22316884994507</t>
@@ -1412,46 +1412,46 @@
     <t xml:space="preserve">6.12244749069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27353096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950307846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30230808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33828020095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58551740646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38323163986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46564435958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326290130615</t>
+    <t xml:space="preserve">6.27353000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30230665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33827924728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58551645278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38323211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46564483642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326337814331</t>
   </si>
   <si>
     <t xml:space="preserve">6.3083119392395</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17345428466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09853410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90373992919922</t>
+    <t xml:space="preserve">6.59300994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41319942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09853363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90374040603638</t>
   </si>
   <si>
     <t xml:space="preserve">5.95618486404419</t>
@@ -1460,109 +1460,109 @@
     <t xml:space="preserve">5.94120025634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86627960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9486927986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84380435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48418521881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60405778884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55910587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88875579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80634307861328</t>
+    <t xml:space="preserve">5.86628007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94869232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84380388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48418474197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60405731201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55910491943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.888756275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8063440322876</t>
   </si>
   <si>
     <t xml:space="preserve">5.64151811599731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79135942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139163970947</t>
+    <t xml:space="preserve">5.79135894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139116287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.88126420974731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92621660232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55554866790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815229415894</t>
+    <t xml:space="preserve">5.92621564865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078765869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55554819107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815277099609</t>
   </si>
   <si>
     <t xml:space="preserve">6.33827972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12850189208984</t>
+    <t xml:space="preserve">6.30081939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.128502368927</t>
   </si>
   <si>
     <t xml:space="preserve">6.06107330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77637529373169</t>
+    <t xml:space="preserve">5.77637481689453</t>
   </si>
   <si>
     <t xml:space="preserve">5.76888275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70145463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66399383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57409000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78386688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67897891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6265344619751</t>
+    <t xml:space="preserve">5.70145416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66399478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57408952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75389909744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78386735916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67897844314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62653398513794</t>
   </si>
   <si>
     <t xml:space="preserve">5.61904191970825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65650320053101</t>
+    <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.54412174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58158111572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5066614151001</t>
+    <t xml:space="preserve">5.58158159255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50666093826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.53662919998169</t>
@@ -1583,34 +1583,34 @@
     <t xml:space="preserve">5.42424869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49167728424072</t>
+    <t xml:space="preserve">5.49167680740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415348052979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36431217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27440690994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450212478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20697832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58907461166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7464075088501</t>
+    <t xml:space="preserve">5.36431264877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27440738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20697927474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58907413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74640703201294</t>
   </si>
   <si>
     <t xml:space="preserve">5.47669363021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21447134017944</t>
+    <t xml:space="preserve">5.21447086334229</t>
   </si>
   <si>
     <t xml:space="preserve">5.13955020904541</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">5.10958242416382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07212162017822</t>
+    <t xml:space="preserve">5.07212209701538</t>
   </si>
   <si>
     <t xml:space="preserve">5.05713796615601</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">5.01967763900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03466176986694</t>
+    <t xml:space="preserve">5.03466129302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.92977237701416</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">4.7349796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77243995666504</t>
+    <t xml:space="preserve">4.77243947982788</t>
   </si>
   <si>
     <t xml:space="preserve">4.82488441467285</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75745487213135</t>
+    <t xml:space="preserve">4.75745534896851</t>
   </si>
   <si>
     <t xml:space="preserve">4.86234426498413</t>
@@ -1664,22 +1664,22 @@
     <t xml:space="preserve">4.91478872299194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89980506896973</t>
+    <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
     <t xml:space="preserve">4.85485219955444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95224857330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16951847076416</t>
+    <t xml:space="preserve">4.95224905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16951894760132</t>
   </si>
   <si>
     <t xml:space="preserve">5.08710622787476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1320595741272</t>
+    <t xml:space="preserve">5.13205814361572</t>
   </si>
   <si>
     <t xml:space="preserve">6.21840620040894</t>
@@ -1688,43 +1688,43 @@
     <t xml:space="preserve">6.25586652755737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01612138748169</t>
+    <t xml:space="preserve">6.01612043380737</t>
   </si>
   <si>
     <t xml:space="preserve">6.10602569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99364471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04215383529663</t>
+    <t xml:space="preserve">5.99364519119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04215335845947</t>
   </si>
   <si>
     <t xml:space="preserve">4.98221731185913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94475698471069</t>
+    <t xml:space="preserve">4.94475650787354</t>
   </si>
   <si>
     <t xml:space="preserve">4.99720144271851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02716970443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89231300354004</t>
+    <t xml:space="preserve">5.0271692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89231252670288</t>
   </si>
   <si>
     <t xml:space="preserve">5.04964590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95974159240723</t>
+    <t xml:space="preserve">4.95974111557007</t>
   </si>
   <si>
     <t xml:space="preserve">4.81739187240601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7949161529541</t>
+    <t xml:space="preserve">4.79491567611694</t>
   </si>
   <si>
     <t xml:space="preserve">4.78742361068726</t>
@@ -1733,55 +1733,55 @@
     <t xml:space="preserve">4.83237648010254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97472476959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729665756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76494836807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47275686264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047204971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38285207748413</t>
+    <t xml:space="preserve">4.97472524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76494789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47275733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38285303115845</t>
   </si>
   <si>
     <t xml:space="preserve">4.32291603088379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18056726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558361053467</t>
+    <t xml:space="preserve">4.18056678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
   </si>
   <si>
     <t xml:space="preserve">4.30043983459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3154239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46526575088501</t>
+    <t xml:space="preserve">4.31542444229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46526527404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.45777320861816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10209035873413</t>
+    <t xml:space="preserve">4.71250295639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10208988189697</t>
   </si>
   <si>
     <t xml:space="preserve">5.07961463928223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93726491928101</t>
+    <t xml:space="preserve">4.93726539611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.01218557357788</t>
@@ -1793,166 +1793,166 @@
     <t xml:space="preserve">5.22196340560913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19948720932007</t>
+    <t xml:space="preserve">5.25942277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19948673248291</t>
   </si>
   <si>
     <t xml:space="preserve">5.11707353591919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28939151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202688217163</t>
+    <t xml:space="preserve">5.28939199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202640533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.31186819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41675662994385</t>
+    <t xml:space="preserve">5.41675615310669</t>
   </si>
   <si>
     <t xml:space="preserve">5.37180376052856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4467248916626</t>
+    <t xml:space="preserve">5.44672441482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89624834060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12101030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383514404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00113725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885149002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91123199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.008629322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631181716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97116851806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21091461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09104156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608869552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866106033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396257400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170854568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73891496658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47268533706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33155584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35507726669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30803489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859964370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.39428043365479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45421695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.409264087677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89624786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85878801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.121009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00113725662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885053634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82132768630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91123247146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03110504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.008629322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377214431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97116804122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21091508865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09104156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859710693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396257400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7089467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73891496658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161285400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47268581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33155632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484565734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35507774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30803442001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859916687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39428091049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24531030654907</t>
+    <t xml:space="preserve">5.24531078338623</t>
   </si>
   <si>
     <t xml:space="preserve">5.26883172988892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28451251983643</t>
+    <t xml:space="preserve">5.28451299667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.25315093994141</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">5.06497859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00225400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690540313721</t>
+    <t xml:space="preserve">5.00225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690587997437</t>
   </si>
   <si>
     <t xml:space="preserve">5.20610761642456</t>
@@ -1976,16 +1976,16 @@
     <t xml:space="preserve">5.33939695358276</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11986255645752</t>
+    <t xml:space="preserve">5.29235363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11986207962036</t>
   </si>
   <si>
     <t xml:space="preserve">5.13554286956787</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09634017944336</t>
+    <t xml:space="preserve">5.09634065628052</t>
   </si>
   <si>
     <t xml:space="preserve">5.11202096939087</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">5.17474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44916391372681</t>
+    <t xml:space="preserve">5.44916439056396</t>
   </si>
   <si>
     <t xml:space="preserve">5.45700454711914</t>
@@ -2006,19 +2006,19 @@
     <t xml:space="preserve">5.70790147781372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67653894424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733720779419</t>
+    <t xml:space="preserve">5.67653942108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733673095703</t>
   </si>
   <si>
     <t xml:space="preserve">5.55893135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51188850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48836660385132</t>
+    <t xml:space="preserve">5.51188802719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48836612701416</t>
   </si>
   <si>
     <t xml:space="preserve">5.48052597045898</t>
@@ -2030,34 +2030,34 @@
     <t xml:space="preserve">5.31587553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32371616363525</t>
+    <t xml:space="preserve">5.3237156867981</t>
   </si>
   <si>
     <t xml:space="preserve">5.19826745986938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79840040206909</t>
+    <t xml:space="preserve">4.79839992523193</t>
   </si>
   <si>
     <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71999549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51614141464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97089147567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82192182540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6415901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71215534210205</t>
+    <t xml:space="preserve">4.71999502182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51614189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97089290618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82192230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64158964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71215486526489</t>
   </si>
   <si>
     <t xml:space="preserve">4.67295265197754</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">4.68079233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90032720565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22962951660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04145622253418</t>
+    <t xml:space="preserve">4.90032768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2296290397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02577590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0414571762085</t>
   </si>
   <si>
     <t xml:space="preserve">5.15122413635254</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">5.22178888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21394824981689</t>
+    <t xml:space="preserve">5.21394872665405</t>
   </si>
   <si>
     <t xml:space="preserve">5.15906476974487</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">5.1277027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01793575286865</t>
+    <t xml:space="preserve">5.01793527603149</t>
   </si>
   <si>
     <t xml:space="preserve">5.07281875610352</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">5.08850002288818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19042682647705</t>
+    <t xml:space="preserve">5.19042634963989</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">5.52756929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51972818374634</t>
+    <t xml:space="preserve">5.51972913742065</t>
   </si>
   <si>
     <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56677198410034</t>
+    <t xml:space="preserve">5.5667724609375</t>
   </si>
   <si>
     <t xml:space="preserve">5.43348264694214</t>
@@ -2144,22 +2144,22 @@
     <t xml:space="preserve">5.53540992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41780138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42564249038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84119033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76278495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44132328033447</t>
+    <t xml:space="preserve">5.41780185699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4256420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84118986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7627854347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44132423400879</t>
   </si>
   <si>
     <t xml:space="preserve">5.40996170043945</t>
@@ -2177,37 +2177,37 @@
     <t xml:space="preserve">5.23746967315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97873210906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83760261535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89248657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896562576294</t>
+    <t xml:space="preserve">4.97873258590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8376030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89248704910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896514892578</t>
   </si>
   <si>
     <t xml:space="preserve">4.92384958267212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87680578231812</t>
+    <t xml:space="preserve">4.87680530548096</t>
   </si>
   <si>
     <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57102537155151</t>
+    <t xml:space="preserve">4.57102584838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750394821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57886695861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39069271087646</t>
+    <t xml:space="preserve">4.57886648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39069366455078</t>
   </si>
   <si>
     <t xml:space="preserve">4.15547752380371</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">4.2260422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11627531051636</t>
+    <t xml:space="preserve">4.1162748336792</t>
   </si>
   <si>
     <t xml:space="preserve">3.84185695648193</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">3.63800311088562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26165795326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29301977157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32438158988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099382400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09700679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05780458450317</t>
+    <t xml:space="preserve">3.26165771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29301953315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32438182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099406242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09700703620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05780434608459</t>
   </si>
   <si>
     <t xml:space="preserve">2.94803690910339</t>
@@ -2249,136 +2249,136 @@
     <t xml:space="preserve">3.00292062759399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13620924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03036260604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21461462974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25381731987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22245502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24205660820007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23813629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34006309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45767092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59880065917969</t>
+    <t xml:space="preserve">3.13620972633362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03036212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25381755828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22245526313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24205684661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24597668647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23813652992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36750483512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34006333351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45767140388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59880042076111</t>
   </si>
   <si>
     <t xml:space="preserve">3.37142515182495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52039504051208</t>
+    <t xml:space="preserve">3.52039480209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.54391694068909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72424912452698</t>
+    <t xml:space="preserve">3.72424840927124</t>
   </si>
   <si>
     <t xml:space="preserve">3.81049466133118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92026209831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3358097076416</t>
+    <t xml:space="preserve">3.92026162147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33581066131592</t>
   </si>
   <si>
     <t xml:space="preserve">4.32796907424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32012844085693</t>
+    <t xml:space="preserve">4.32012891769409</t>
   </si>
   <si>
     <t xml:space="preserve">4.23388290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1633186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07707214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21820163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740480422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19467973709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208928108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401584625244</t>
+    <t xml:space="preserve">4.16331768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07707166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21820211410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19468021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208975791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481387138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401608467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.84577703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009648323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265355110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145806312561</t>
+    <t xml:space="preserve">3.70072746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265402793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145853996277</t>
   </si>
   <si>
     <t xml:space="preserve">3.75169038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74385094642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298621177673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660749435425</t>
+    <t xml:space="preserve">3.74385023117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660701751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.10059404373169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91634178161621</t>
+    <t xml:space="preserve">3.91634130477905</t>
   </si>
   <si>
     <t xml:space="preserve">3.95946478843689</t>
@@ -2387,112 +2387,112 @@
     <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13979625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14763736724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01434755325317</t>
+    <t xml:space="preserve">4.13979721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14763641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01434850692749</t>
   </si>
   <si>
     <t xml:space="preserve">3.9516236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94378304481506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88889956474304</t>
+    <t xml:space="preserve">3.94378423690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8889000415802</t>
   </si>
   <si>
     <t xml:space="preserve">4.05355072021484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06923151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03002977371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89281988143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242098808289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85753750801086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86537837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617592811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105940818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9085009098053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.779132604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.755610704422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777030944824</t>
+    <t xml:space="preserve">4.06923198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89281964302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810225486755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8575382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8653781414032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617545127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458059310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75561022758484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7477707862854</t>
   </si>
   <si>
     <t xml:space="preserve">3.80657410621643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88497972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96730518341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02218914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594312667847</t>
+    <t xml:space="preserve">3.88497924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96730470657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02218866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594336509705</t>
   </si>
   <si>
     <t xml:space="preserve">3.76345133781433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7595317363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6458432674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6693651676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544461250305</t>
+    <t xml:space="preserve">3.75953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64584350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66936492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544508934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.63016247749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56351828575134</t>
+    <t xml:space="preserve">3.56351804733276</t>
   </si>
   <si>
     <t xml:space="preserve">3.56743836402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59095978736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903298377991</t>
+    <t xml:space="preserve">3.59096002578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903322219849</t>
   </si>
   <si>
     <t xml:space="preserve">3.48119282722473</t>
@@ -2501,25 +2501,25 @@
     <t xml:space="preserve">3.44198966026306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38710618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654143333435</t>
+    <t xml:space="preserve">3.3871066570282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654191017151</t>
   </si>
   <si>
     <t xml:space="preserve">3.33222270011902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40278768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238879203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43807005882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551132202148</t>
+    <t xml:space="preserve">3.40278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43806958198547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551179885864</t>
   </si>
   <si>
     <t xml:space="preserve">3.49295353889465</t>
@@ -2528,61 +2528,61 @@
     <t xml:space="preserve">3.55175757408142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55567717552185</t>
+    <t xml:space="preserve">3.55567765235901</t>
   </si>
   <si>
     <t xml:space="preserve">3.50079393386841</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51255464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37926554679871</t>
+    <t xml:space="preserve">3.51255440711975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37926578521729</t>
   </si>
   <si>
     <t xml:space="preserve">3.43414950370789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42630887031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46159100532532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44983053207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189027786255</t>
+    <t xml:space="preserve">3.42630839347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4615912437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4498302936554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189051628113</t>
   </si>
   <si>
     <t xml:space="preserve">3.20677423477173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17541241645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52823615074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215575218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607654571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10843467712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13195657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09275341033936</t>
+    <t xml:space="preserve">3.17541265487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52823543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607678413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10843420028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866700172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2025203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13195610046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09275388717651</t>
   </si>
   <si>
     <t xml:space="preserve">4.06139135360718</t>
@@ -2591,58 +2591,58 @@
     <t xml:space="preserve">4.28876638412476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24956321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24172353744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39853382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35933065414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69647312164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976245880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7278356552124</t>
+    <t xml:space="preserve">4.2495641708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24172306060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3985333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35933113098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69647359848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75919771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976293563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72783613204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.74351739883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487897872925</t>
+    <t xml:space="preserve">4.76703882217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487945556641</t>
   </si>
   <si>
     <t xml:space="preserve">4.73567628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80624103546143</t>
+    <t xml:space="preserve">4.68863344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80624151229858</t>
   </si>
   <si>
     <t xml:space="preserve">5.010094165802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99441385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9473705291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86112499237061</t>
+    <t xml:space="preserve">4.99441337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94737005233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86112451553345</t>
   </si>
   <si>
     <t xml:space="preserve">4.84544372558594</t>
@@ -2651,31 +2651,31 @@
     <t xml:space="preserve">4.91600847244263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93953037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04929780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245277404785</t>
+    <t xml:space="preserve">4.93952989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04929733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245229721069</t>
   </si>
   <si>
     <t xml:space="preserve">5.68437957763672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59813404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6294960975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7157416343689</t>
+    <t xml:space="preserve">5.59813451766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62949562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71574211120605</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222068786621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66869878768921</t>
+    <t xml:space="preserve">5.66869831085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.66085815429688</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">6.08424711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17833232879639</t>
+    <t xml:space="preserve">6.17833280563354</t>
   </si>
   <si>
     <t xml:space="preserve">6.14697074890137</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">6.05288410186768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97447967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720235824585</t>
+    <t xml:space="preserve">5.97447872161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
@@ -2714,55 +2714,55 @@
     <t xml:space="preserve">6.11834812164307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49161624908447</t>
+    <t xml:space="preserve">6.49161577224731</t>
   </si>
   <si>
     <t xml:space="preserve">6.45915842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42670059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26440906524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41047096252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39424180984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44292974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96225833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43290042877197</t>
+    <t xml:space="preserve">6.42670011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26440954208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41047143936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39424276351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4429292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96225786209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43289995193481</t>
   </si>
   <si>
     <t xml:space="preserve">8.00091743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87108373641968</t>
+    <t xml:space="preserve">7.83862733840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87108516693115</t>
   </si>
   <si>
     <t xml:space="preserve">7.78993988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91977262496948</t>
+    <t xml:space="preserve">7.91977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">7.95222997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90354299545288</t>
+    <t xml:space="preserve">7.90354251861572</t>
   </si>
   <si>
     <t xml:space="preserve">8.60139274597168</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56081962585449</t>
+    <t xml:space="preserve">8.56081867218018</t>
   </si>
   <si>
     <t xml:space="preserve">8.43910026550293</t>
@@ -2789,67 +2789,67 @@
     <t xml:space="preserve">8.06583309173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96845960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40044212341309</t>
+    <t xml:space="preserve">7.96845865249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4004430770874</t>
   </si>
   <si>
     <t xml:space="preserve">7.25438070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48158836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64387845993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5627326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69256496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75748062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62764883041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535778045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306911468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192335128784</t>
+    <t xml:space="preserve">7.4815878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64387798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56273174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69256544113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75748157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62764835357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4653582572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30306768417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192287445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.81619691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15700674057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23815250396729</t>
+    <t xml:space="preserve">7.15700721740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23815202713013</t>
   </si>
   <si>
     <t xml:space="preserve">7.38421392440796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70879459381104</t>
+    <t xml:space="preserve">7.70879507064819</t>
   </si>
   <si>
     <t xml:space="preserve">7.61141967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66010713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53027439117432</t>
+    <t xml:space="preserve">7.66010761260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53027486801147</t>
   </si>
   <si>
     <t xml:space="preserve">7.74125289916992</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1550931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96654510498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84482669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52024745941162</t>
+    <t xml:space="preserve">8.15509414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96654605865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84482765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5202465057373</t>
   </si>
   <si>
     <t xml:space="preserve">8.39852905273438</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">8.47967433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08206367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11452102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03337574005127</t>
+    <t xml:space="preserve">8.31738471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08206272125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1145191192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03337478637695</t>
   </si>
   <si>
     <t xml:space="preserve">8.04960441589355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04768943786621</t>
+    <t xml:space="preserve">9.04769039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
@@ -2918,28 +2918,28 @@
     <t xml:space="preserve">9.7795877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6124153137207</t>
+    <t xml:space="preserve">9.61241436004639</t>
   </si>
   <si>
     <t xml:space="preserve">9.57062244415283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52882862091064</t>
+    <t xml:space="preserve">9.52882766723633</t>
   </si>
   <si>
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779392242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420913696289</t>
+    <t xml:space="preserve">9.73779487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420818328857</t>
   </si>
   <si>
     <t xml:space="preserve">9.90496635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31986236572266</t>
+    <t xml:space="preserve">9.31986331939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15268993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013984680176</t>
+    <t xml:space="preserve">9.15269088745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013889312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.7765531539917</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">8.6093807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19448375701904</t>
+    <t xml:space="preserve">9.19448280334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
@@ -2975,19 +2975,19 @@
     <t xml:space="preserve">9.36165523529053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06910514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9437255859375</t>
+    <t xml:space="preserve">9.06910610198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94372463226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.90193176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81834602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758689880371</t>
+    <t xml:space="preserve">8.81834697723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758785247803</t>
   </si>
   <si>
     <t xml:space="preserve">8.52579307556152</t>
@@ -2999,49 +2999,49 @@
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846881866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32518672943115</t>
+    <t xml:space="preserve">8.30846977233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32518768310547</t>
   </si>
   <si>
     <t xml:space="preserve">7.65649747848511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82366895675659</t>
+    <t xml:space="preserve">7.82366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">7.67321538925171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12154579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07139444351196</t>
+    <t xml:space="preserve">7.12154626846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0713939666748</t>
   </si>
   <si>
     <t xml:space="preserve">7.10482835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68993139266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589113235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053964614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80695295333862</t>
+    <t xml:space="preserve">7.68993186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80695247650146</t>
   </si>
   <si>
     <t xml:space="preserve">7.62306308746338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99084186553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09114551544189</t>
+    <t xml:space="preserve">7.99084281921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09114646911621</t>
   </si>
   <si>
     <t xml:space="preserve">8.04099464416504</t>
@@ -3053,82 +3053,82 @@
     <t xml:space="preserve">8.40041542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10786247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48400020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30011081695557</t>
+    <t xml:space="preserve">8.1078634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48400115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30011177062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.35026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24996089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69829034805298</t>
+    <t xml:space="preserve">8.24995994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8738226890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69828987121582</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531095504761</t>
+    <t xml:space="preserve">7.81531190872192</t>
   </si>
   <si>
     <t xml:space="preserve">7.77351856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91561508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7818775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60634565353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89889812469482</t>
+    <t xml:space="preserve">7.91561603546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78187656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60634660720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89889764785767</t>
   </si>
   <si>
     <t xml:space="preserve">7.79859447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79023551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63977956771851</t>
+    <t xml:space="preserve">7.79023504257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978099822998</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64850234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24154472351074</t>
+    <t xml:space="preserve">7.64850187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24154376983643</t>
   </si>
   <si>
     <t xml:space="preserve">8.21538066864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2851505279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32003402709961</t>
+    <t xml:space="preserve">8.28514862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32003498077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19793701171875</t>
+    <t xml:space="preserve">8.19793796539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.49445819854736</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">8.69504642486572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67760467529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54678630828857</t>
+    <t xml:space="preserve">8.67760372161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54678535461426</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59039306640625</t>
+    <t xml:space="preserve">8.59039211273193</t>
   </si>
   <si>
     <t xml:space="preserve">8.64271926879883</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">8.45957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177391052246</t>
+    <t xml:space="preserve">8.17177486419678</t>
   </si>
   <si>
     <t xml:space="preserve">8.1281681060791</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827173233032</t>
+    <t xml:space="preserve">7.71827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.77931928634644</t>
@@ -3182,73 +3182,73 @@
     <t xml:space="preserve">7.95374345779419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14560985565186</t>
+    <t xml:space="preserve">8.14561080932617</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86653184890747</t>
+    <t xml:space="preserve">7.86653232574463</t>
   </si>
   <si>
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804063796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65722179412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76187705993652</t>
+    <t xml:space="preserve">7.78804016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65722274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76187658309937</t>
   </si>
   <si>
     <t xml:space="preserve">7.69210767745972</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70082807540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59617376327515</t>
+    <t xml:space="preserve">7.70082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5961742401123</t>
   </si>
   <si>
     <t xml:space="preserve">7.46535634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54384613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73571395874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50024127960205</t>
+    <t xml:space="preserve">7.54384660720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73571300506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50024080276489</t>
   </si>
   <si>
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44791316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53512668609619</t>
+    <t xml:space="preserve">7.55256843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.447913646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53512620925903</t>
   </si>
   <si>
     <t xml:space="preserve">7.51768350601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50896120071411</t>
+    <t xml:space="preserve">7.50896167755127</t>
   </si>
   <si>
     <t xml:space="preserve">7.57001066207886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80548334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74443435668945</t>
+    <t xml:space="preserve">7.80548286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74443483352661</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596794128418</t>
+    <t xml:space="preserve">8.41596698760986</t>
   </si>
   <si>
     <t xml:space="preserve">8.3461971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.023512840271</t>
+    <t xml:space="preserve">8.02351379394531</t>
   </si>
   <si>
     <t xml:space="preserve">8.37236213684082</t>
@@ -3284,22 +3284,22 @@
     <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83164644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66594457626343</t>
+    <t xml:space="preserve">7.83164596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66594362258911</t>
   </si>
   <si>
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97118663787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68338584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33453750610352</t>
+    <t xml:space="preserve">7.97118711471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33453798294067</t>
   </si>
   <si>
     <t xml:space="preserve">7.16883516311646</t>
@@ -3308,19 +3308,19 @@
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418085098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28221130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13395071029663</t>
+    <t xml:space="preserve">7.06418037414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28221082687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13395023345947</t>
   </si>
   <si>
     <t xml:space="preserve">7.12522888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78510141372681</t>
+    <t xml:space="preserve">6.78510189056396</t>
   </si>
   <si>
     <t xml:space="preserve">6.61939907073975</t>
@@ -3329,31 +3329,31 @@
     <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6368408203125</t>
+    <t xml:space="preserve">6.63684129714966</t>
   </si>
   <si>
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75315618515015</t>
+    <t xml:space="preserve">7.75315570831299</t>
   </si>
   <si>
     <t xml:space="preserve">7.4391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43047142028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49151945114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27348947525024</t>
+    <t xml:space="preserve">7.43047189712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49151992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27348899841309</t>
   </si>
   <si>
     <t xml:space="preserve">7.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38686561584473</t>
+    <t xml:space="preserve">7.38686513900757</t>
   </si>
   <si>
     <t xml:space="preserve">7.35198068618774</t>
@@ -3377,19 +3377,19 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663499832153</t>
+    <t xml:space="preserve">7.45663547515869</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781097412109</t>
+    <t xml:space="preserve">7.85781049728394</t>
   </si>
   <si>
     <t xml:space="preserve">8.03223514556885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10200500488281</t>
+    <t xml:space="preserve">8.1020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">8.15433216094971</t>
@@ -3398,16 +3398,16 @@
     <t xml:space="preserve">8.05839824676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09328269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00607013702393</t>
+    <t xml:space="preserve">8.09328365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00607109069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072540283203</t>
+    <t xml:space="preserve">8.11072635650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.07584095001221</t>
@@ -3416,19 +3416,19 @@
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990655899048</t>
+    <t xml:space="preserve">7.97990703582764</t>
   </si>
   <si>
     <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90141725540161</t>
+    <t xml:space="preserve">7.90141677856445</t>
   </si>
   <si>
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885900497437</t>
+    <t xml:space="preserve">7.91885852813721</t>
   </si>
   <si>
     <t xml:space="preserve">7.82292556762695</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">8.11944675445557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25898551940918</t>
+    <t xml:space="preserve">8.2589864730835</t>
   </si>
   <si>
     <t xml:space="preserve">8.27642822265625</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">8.337477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5293436050415</t>
+    <t xml:space="preserve">8.52934265136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.94796180725098</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">8.87819194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65144157409668</t>
+    <t xml:space="preserve">8.89563465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65144062042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.6601619720459</t>
@@ -3470,28 +3470,28 @@
     <t xml:space="preserve">8.70376777648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71248817443848</t>
+    <t xml:space="preserve">8.71248912811279</t>
   </si>
   <si>
     <t xml:space="preserve">8.86074924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93052005767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62527656555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56422901153564</t>
+    <t xml:space="preserve">8.93051910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62527751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56422805786133</t>
   </si>
   <si>
     <t xml:space="preserve">8.46829509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68632507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15727043151855</t>
+    <t xml:space="preserve">8.6863260269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15727138519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3509,31 +3509,31 @@
     <t xml:space="preserve">8.96540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00028896331787</t>
+    <t xml:space="preserve">9.00028800964355</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8433084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80842208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66888236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91124534606934</t>
+    <t xml:space="preserve">8.84330749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80842304229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66888332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91124629974365</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8567419052124</t>
+    <t xml:space="preserve">8.82040691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85674285888672</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422756195068</t>
+    <t xml:space="preserve">8.58422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498817443848</t>
+    <t xml:space="preserve">8.77498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38438320159912</t>
+    <t xml:space="preserve">8.49339008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3843822479248</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453788757324</t>
+    <t xml:space="preserve">8.18453884124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896350860596</t>
+    <t xml:space="preserve">8.33896446228027</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09370040893555</t>
+    <t xml:space="preserve">8.09369945526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04828071594238</t>
+    <t xml:space="preserve">8.04827976226807</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644821166992</t>
+    <t xml:space="preserve">8.06644916534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3659,40 +3659,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919696807861</t>
+    <t xml:space="preserve">8.03919792175293</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94835901260376</t>
+    <t xml:space="preserve">8.00286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9483585357666</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9029393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385461807251</t>
+    <t xml:space="preserve">7.95744276046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90293884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385557174683</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85752010345459</t>
+    <t xml:space="preserve">7.85751962661743</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210136413574</t>
+    <t xml:space="preserve">7.81210088729858</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126245498657</t>
+    <t xml:space="preserve">7.72126293182373</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568807601929</t>
+    <t xml:space="preserve">7.87568855285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950777053833</t>
+    <t xml:space="preserve">7.63950824737549</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49416637420654</t>
+    <t xml:space="preserve">7.4941668510437</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41241216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4487476348877</t>
+    <t xml:space="preserve">7.4124116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44874715805054</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112440109253</t>
+    <t xml:space="preserve">6.73112392425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7220401763916</t>
+    <t xml:space="preserve">6.72204065322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486675262451</t>
+    <t xml:space="preserve">6.59486722946167</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3806,22 +3806,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699247360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31248998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790967941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775308609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767669677734</t>
+    <t xml:space="preserve">7.01272296905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31249046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767621994019</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393339157104</t>
+    <t xml:space="preserve">7.79393291473389</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3842,31 +3842,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96652698516846</t>
+    <t xml:space="preserve">7.76668262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9665265083313</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.475998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607717514038</t>
+    <t xml:space="preserve">7.63042402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47599840164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607669830322</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523921966553</t>
+    <t xml:space="preserve">7.28523874282837</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264562606812</t>
+    <t xml:space="preserve">7.11264514923096</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225652694702</t>
+    <t xml:space="preserve">7.61225700378418</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890279769897</t>
+    <t xml:space="preserve">7.24890327453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -70250,7 +70250,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6912731481</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>31428</v>
@@ -70271,6 +70271,32 @@
         <v>1415</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6911458333</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>16344</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -44,52 +44,52 @@
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355497837067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546648979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20654845237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23177242279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24998986721039</t>
+    <t xml:space="preserve">1.21355509757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546637058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20654833316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23177254199982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2499897480011</t>
   </si>
   <si>
     <t xml:space="preserve">1.26330256462097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27311193943024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26120054721832</t>
+    <t xml:space="preserve">1.27311182022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26120042800903</t>
   </si>
   <si>
     <t xml:space="preserve">1.24718701839447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2079496383667</t>
+    <t xml:space="preserve">1.20794975757599</t>
   </si>
   <si>
     <t xml:space="preserve">1.19323575496674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501854896545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814038276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2457857131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23457503318787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21495640277863</t>
+    <t xml:space="preserve">1.17501842975616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1981406211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24578583240509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23457515239716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21495628356934</t>
   </si>
   <si>
     <t xml:space="preserve">1.18272578716278</t>
@@ -104,55 +104,55 @@
     <t xml:space="preserve">1.12457036972046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12807357311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10284960269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08603358268738</t>
+    <t xml:space="preserve">1.12807393074036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10284972190857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
     <t xml:space="preserve">1.01596701145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507567405701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02017104625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195360183716</t>
+    <t xml:space="preserve">1.0250757932663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02017092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195384025574</t>
   </si>
   <si>
     <t xml:space="preserve">1.02297377586365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.04329323768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09654378890991</t>
+    <t xml:space="preserve">1.04329311847687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09654366970062</t>
   </si>
   <si>
     <t xml:space="preserve">1.11335980892181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1105569601059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0930403470993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106716632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017570972443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15610039234161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10004711151123</t>
+    <t xml:space="preserve">1.11055707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09304022789001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017582893372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15610027313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10004699230194</t>
   </si>
   <si>
     <t xml:space="preserve">1.13157713413239</t>
@@ -161,79 +161,79 @@
     <t xml:space="preserve">1.10705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13227784633636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11826431751251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14909386634827</t>
+    <t xml:space="preserve">1.13227772712708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11826419830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14909374713898</t>
   </si>
   <si>
     <t xml:space="preserve">1.17852175235748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17011368274689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412697315216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16310715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22616708278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508512020111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2408812046051</t>
+    <t xml:space="preserve">1.17011380195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412709236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081439495087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16310691833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22616696357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508500099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24088096618652</t>
   </si>
   <si>
     <t xml:space="preserve">1.20514702796936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19113373756409</t>
+    <t xml:space="preserve">1.19113385677338</t>
   </si>
   <si>
     <t xml:space="preserve">1.22686779499054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22196280956268</t>
+    <t xml:space="preserve">1.22196316719055</t>
   </si>
   <si>
     <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17221558094025</t>
+    <t xml:space="preserve">1.17221570014954</t>
   </si>
   <si>
     <t xml:space="preserve">1.19183444976807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19743967056274</t>
+    <t xml:space="preserve">1.19743978977203</t>
   </si>
   <si>
     <t xml:space="preserve">1.20374584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.203045129776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23807847499847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2331737279892</t>
+    <t xml:space="preserve">1.20304501056671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23807835578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23317384719849</t>
   </si>
   <si>
     <t xml:space="preserve">1.19954180717468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22476577758789</t>
+    <t xml:space="preserve">1.2247656583786</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845972537994</t>
@@ -242,52 +242,52 @@
     <t xml:space="preserve">1.21916031837463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22896981239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21215391159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22266376018524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29202973842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2962338924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2752138376236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2871253490448</t>
+    <t xml:space="preserve">1.2289696931839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21215379238129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22266387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2920298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29623377323151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521371841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28712522983551</t>
   </si>
   <si>
     <t xml:space="preserve">1.28151965141296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24788761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737788200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865046977997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469920635223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138638973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11896502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036633491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13648164272308</t>
+    <t xml:space="preserve">1.24788773059845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737776279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865035057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469896793365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138615131378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11896514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036645412445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13648176193237</t>
   </si>
   <si>
     <t xml:space="preserve">1.14629113674164</t>
@@ -296,58 +296,58 @@
     <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07202041149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08463263511658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501376628876</t>
+    <t xml:space="preserve">1.0720202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08463251590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501388549805</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253026008606</t>
+    <t xml:space="preserve">1.08253037929535</t>
   </si>
   <si>
     <t xml:space="preserve">1.07902693748474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05800700187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10144853591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09514248371124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11966562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934628009796</t>
+    <t xml:space="preserve">1.05800712108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1014484167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355031490326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09514236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11966574192047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934651851654</t>
   </si>
   <si>
     <t xml:space="preserve">1.11265909671783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15680122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528052806854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681509494781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48821651935577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45178174972534</t>
+    <t xml:space="preserve">1.15680110454559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528040885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4868152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48821663856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45178198814392</t>
   </si>
   <si>
     <t xml:space="preserve">1.41534721851349</t>
@@ -359,148 +359,148 @@
     <t xml:space="preserve">1.40133392810822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46999907493591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776834011078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375528812408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4363671541214</t>
+    <t xml:space="preserve">1.4699991941452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776857852936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375516891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43636703491211</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936038970947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41674840450287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42235374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814970970154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114318370819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42795932292938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48120999336243</t>
+    <t xml:space="preserve">1.41674852371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42235386371613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814959049225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114294528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42795920372009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48120975494385</t>
   </si>
   <si>
     <t xml:space="preserve">1.6942126750946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338324546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8007138967514</t>
+    <t xml:space="preserve">1.66338312625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80071401596069</t>
   </si>
   <si>
     <t xml:space="preserve">1.84555661678314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79230570793152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090487957001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064720630646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71663415431976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78670072555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84275388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593786716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995115756989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83855009078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84415519237518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8301420211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472718715668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874071598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192457675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294463157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835910797119</t>
+    <t xml:space="preserve">1.79230630397797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090464115143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268707752228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064732551575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71663403511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78670048713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8427540063858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313513755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995127677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854997158051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84415543079376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014178276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472730636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874047756195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192469596863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294451236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835934638977</t>
   </si>
   <si>
     <t xml:space="preserve">1.86937940120697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99549949169159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07257223129272</t>
+    <t xml:space="preserve">1.99549961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07257270812988</t>
   </si>
   <si>
     <t xml:space="preserve">2.0291314125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08798718452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04034209251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830186367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03053259849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01932239532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970316886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231551170349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359264373779</t>
+    <t xml:space="preserve">2.08798766136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04034185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830198287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0305323600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01932191848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970328807831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359288215637</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066597938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15945529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989403247833</t>
+    <t xml:space="preserve">2.15945553779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989427089691</t>
   </si>
   <si>
     <t xml:space="preserve">1.88339245319366</t>
@@ -509,40 +509,40 @@
     <t xml:space="preserve">1.97167646884918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9534592628479</t>
+    <t xml:space="preserve">1.95345914363861</t>
   </si>
   <si>
     <t xml:space="preserve">2.01651930809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97868311405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9394463300705</t>
+    <t xml:space="preserve">2.00250601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428916931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9786833524704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944585323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.9198272228241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377382278442</t>
+    <t xml:space="preserve">1.86377429962158</t>
   </si>
   <si>
     <t xml:space="preserve">1.86797785758972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87918901443481</t>
+    <t xml:space="preserve">1.87918853759766</t>
   </si>
   <si>
     <t xml:space="preserve">1.85676765441895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78950309753418</t>
+    <t xml:space="preserve">1.78950333595276</t>
   </si>
   <si>
     <t xml:space="preserve">1.80631947517395</t>
@@ -551,76 +551,76 @@
     <t xml:space="preserve">1.90301144123077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89880740642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91001796722412</t>
+    <t xml:space="preserve">1.89880752563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001784801483</t>
   </si>
   <si>
     <t xml:space="preserve">1.99690067768097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98849308490753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9856903553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224882125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9576632976532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186721324921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326887607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97027552127838</t>
+    <t xml:space="preserve">1.98849248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98568999767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224870204926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766317844391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9618673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326851844788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027540206909</t>
   </si>
   <si>
     <t xml:space="preserve">1.96607136726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00390720367432</t>
+    <t xml:space="preserve">2.00390768051147</t>
   </si>
   <si>
     <t xml:space="preserve">2.07397437095642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18888330459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16506052017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13282990455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06416463851929</t>
+    <t xml:space="preserve">2.18888354301453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1650607585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13283014297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06416511535645</t>
   </si>
   <si>
     <t xml:space="preserve">2.09639525413513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11601400375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499430656433</t>
+    <t xml:space="preserve">2.11601424217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499382972717</t>
   </si>
   <si>
     <t xml:space="preserve">2.11321115493774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14404082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002753257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14824461936951</t>
+    <t xml:space="preserve">2.14404058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002777099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14824485778809</t>
   </si>
   <si>
     <t xml:space="preserve">2.13423156738281</t>
@@ -629,28 +629,28 @@
     <t xml:space="preserve">2.14123797416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15244889259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13703393936157</t>
+    <t xml:space="preserve">2.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13703441619873</t>
   </si>
   <si>
     <t xml:space="preserve">2.11180996894836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09779667854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11881685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10200095176697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24213433265686</t>
+    <t xml:space="preserve">2.09779644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.118816614151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10200047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1174156665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213409423828</t>
   </si>
   <si>
     <t xml:space="preserve">2.48876881599426</t>
@@ -659,76 +659,76 @@
     <t xml:space="preserve">2.48736763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316311836243</t>
+    <t xml:space="preserve">2.49297285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316359519958</t>
   </si>
   <si>
     <t xml:space="preserve">2.46494626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40328741073608</t>
+    <t xml:space="preserve">2.40328764915466</t>
   </si>
   <si>
     <t xml:space="preserve">2.52099967002869</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48036098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46634745597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44392561912537</t>
+    <t xml:space="preserve">2.48036074638367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46634769439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4439263343811</t>
   </si>
   <si>
     <t xml:space="preserve">2.43972229957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47615694999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45513677597046</t>
+    <t xml:space="preserve">2.47615671157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45513701438904</t>
   </si>
   <si>
     <t xml:space="preserve">2.49437403678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47335457801819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65552735328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71858763694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70457410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751057624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865456581116</t>
+    <t xml:space="preserve">2.47335410118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6555278301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71858787536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70457458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865432739258</t>
   </si>
   <si>
     <t xml:space="preserve">3.11096119880676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23988389968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129441261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003103256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5804078578949</t>
+    <t xml:space="preserve">3.2398841381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38422107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129465103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003174781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040738105774</t>
   </si>
   <si>
     <t xml:space="preserve">3.69251465797424</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">3.69601798057556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78360080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176124572754</t>
+    <t xml:space="preserve">3.78360056877136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95176148414612</t>
   </si>
   <si>
     <t xml:space="preserve">4.06386804580688</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">4.19349145889282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16896772384644</t>
+    <t xml:space="preserve">4.16896820068359</t>
   </si>
   <si>
     <t xml:space="preserve">4.11291408538818</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">4.30910158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30559778213501</t>
+    <t xml:space="preserve">4.30559825897217</t>
   </si>
   <si>
     <t xml:space="preserve">4.55433464050293</t>
@@ -773,109 +773,109 @@
     <t xml:space="preserve">4.69797134399414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50023460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10085535049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01677465438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44768571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4441819190979</t>
+    <t xml:space="preserve">5.50023555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10085487365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01677513122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44768524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44418144226074</t>
   </si>
   <si>
     <t xml:space="preserve">5.77349519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39708757400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369325637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858238220215</t>
+    <t xml:space="preserve">6.39708948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518251419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238851547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369277954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858333587646</t>
   </si>
   <si>
     <t xml:space="preserve">6.78433322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35626602172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53252935409546</t>
+    <t xml:space="preserve">6.35626554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5325288772583</t>
   </si>
   <si>
     <t xml:space="preserve">6.35266828536987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07208633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.323890209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900108337402</t>
+    <t xml:space="preserve">6.0720853805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32389068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900060653687</t>
   </si>
   <si>
     <t xml:space="preserve">6.51094579696655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40302991867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798898696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37425184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47137641906738</t>
+    <t xml:space="preserve">6.40302896499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15842008590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37425136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47137546539307</t>
   </si>
   <si>
     <t xml:space="preserve">6.32748746871948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15122413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11165523529053</t>
+    <t xml:space="preserve">6.1512246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11165475845337</t>
   </si>
   <si>
     <t xml:space="preserve">5.93898963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85265636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90661525726318</t>
+    <t xml:space="preserve">5.96057319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85265684127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90661478042603</t>
   </si>
   <si>
     <t xml:space="preserve">5.89582300186157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75193452835083</t>
+    <t xml:space="preserve">5.75193500518799</t>
   </si>
   <si>
     <t xml:space="preserve">5.6943793296814</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">5.70157432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36703395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87421655654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1799783706665</t>
+    <t xml:space="preserve">5.3670334815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87421607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17997884750366</t>
   </si>
   <si>
     <t xml:space="preserve">4.97853517532349</t>
@@ -899,58 +899,58 @@
     <t xml:space="preserve">4.96414613723755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84543895721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87781381607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155048370361</t>
+    <t xml:space="preserve">4.84543800354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87781429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9101881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155000686646</t>
   </si>
   <si>
     <t xml:space="preserve">4.92457675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.690758228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65838432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68716144561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82385492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55046701431274</t>
+    <t xml:space="preserve">4.76989793777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69075775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65838384628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68716096878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82385540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55046796798706</t>
   </si>
   <si>
     <t xml:space="preserve">4.51089811325073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49291229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43895387649536</t>
+    <t xml:space="preserve">4.49291181564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38499641418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46413373947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03609037399292</t>
+    <t xml:space="preserve">4.38499546051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46413421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03609085083008</t>
   </si>
   <si>
     <t xml:space="preserve">4.85622978210449</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">4.76630020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68356466293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67636919021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60442590713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59003639221191</t>
+    <t xml:space="preserve">4.68356418609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67637014389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60442543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59003686904907</t>
   </si>
   <si>
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198062896729</t>
+    <t xml:space="preserve">4.66198110580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.67277193069458</t>
@@ -986,52 +986,52 @@
     <t xml:space="preserve">4.74831390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75910520553589</t>
+    <t xml:space="preserve">4.75910568237305</t>
   </si>
   <si>
     <t xml:space="preserve">4.9533543586731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83104944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486749649048</t>
+    <t xml:space="preserve">4.83104991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486797332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.14400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19436740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10803508758545</t>
+    <t xml:space="preserve">5.11522912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1943678855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10803461074829</t>
   </si>
   <si>
     <t xml:space="preserve">4.93536901473999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7555079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99652147293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90659093856812</t>
+    <t xml:space="preserve">4.75550889968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99652099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90659141540527</t>
   </si>
   <si>
     <t xml:space="preserve">4.92097997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82025766372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89220237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05407667160034</t>
+    <t xml:space="preserve">4.82025814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89220190048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0540771484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.07925748825073</t>
@@ -1043,67 +1043,67 @@
     <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839529037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23393678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60804653167725</t>
+    <t xml:space="preserve">4.94615983963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23393726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60804605484009</t>
   </si>
   <si>
     <t xml:space="preserve">5.8994197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77711582183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18000268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20877885818481</t>
+    <t xml:space="preserve">5.77711486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978189468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18000221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20878028869629</t>
   </si>
   <si>
     <t xml:space="preserve">6.52533435821533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03613805770874</t>
+    <t xml:space="preserve">7.03613758087158</t>
   </si>
   <si>
     <t xml:space="preserve">6.89584636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11527585983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802284240723</t>
+    <t xml:space="preserve">7.11527633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13686037063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802474975586</t>
   </si>
   <si>
     <t xml:space="preserve">8.12968826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43904876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2951831817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160701751709</t>
+    <t xml:space="preserve">8.43904972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29518413543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160692214966</t>
   </si>
   <si>
     <t xml:space="preserve">8.42465972900391</t>
@@ -1115,28 +1115,28 @@
     <t xml:space="preserve">8.22321701049805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8059401512146</t>
+    <t xml:space="preserve">8.0145788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80594158172607</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299383163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10091209411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98580121994019</t>
+    <t xml:space="preserve">7.99299430847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10091114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98580074310303</t>
   </si>
   <si>
     <t xml:space="preserve">7.8850793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7339973449707</t>
+    <t xml:space="preserve">7.73399591445923</t>
   </si>
   <si>
     <t xml:space="preserve">7.41024732589722</t>
@@ -1145,79 +1145,79 @@
     <t xml:space="preserve">7.54694032669067</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47499799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535820007324</t>
+    <t xml:space="preserve">7.47499704360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535724639893</t>
   </si>
   <si>
     <t xml:space="preserve">7.38866424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23760509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84191179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702314376831</t>
+    <t xml:space="preserve">8.23760414123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84191226959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702266693115</t>
   </si>
   <si>
     <t xml:space="preserve">7.84910678863525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824554443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630178451538</t>
+    <t xml:space="preserve">8.04335594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824506759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85630226135254</t>
   </si>
   <si>
     <t xml:space="preserve">7.74838542938232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57571792602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463636398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19441509246826</t>
+    <t xml:space="preserve">7.57571840286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.424635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441556930542</t>
   </si>
   <si>
     <t xml:space="preserve">6.96419382095337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21599769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2088041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20160961151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485811233521</t>
+    <t xml:space="preserve">7.21599721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498512268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20161008834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55413436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485668182373</t>
   </si>
   <si>
     <t xml:space="preserve">7.2519702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24477577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722057342529</t>
+    <t xml:space="preserve">7.24477529525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722105026245</t>
   </si>
   <si>
     <t xml:space="preserve">7.10448408126831</t>
@@ -1226,151 +1226,151 @@
     <t xml:space="preserve">7.00736045837402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89944458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340156555176</t>
+    <t xml:space="preserve">6.89944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340204238892</t>
   </si>
   <si>
     <t xml:space="preserve">7.15844297409058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91742992401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85627698898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.892249584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78793048858643</t>
+    <t xml:space="preserve">6.91742944717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85627746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89224815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78792953491211</t>
   </si>
   <si>
     <t xml:space="preserve">6.95699977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93541622161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98218011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16204023361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217490196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82752323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25918674468994</t>
+    <t xml:space="preserve">6.93541574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98218059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203927993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.140456199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02174854278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33830213546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82752466201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25918769836426</t>
   </si>
   <si>
     <t xml:space="preserve">8.15846633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91385555267334</t>
+    <t xml:space="preserve">7.9138560295105</t>
   </si>
   <si>
     <t xml:space="preserve">7.8994665145874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924571990967</t>
+    <t xml:space="preserve">7.81313467025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924715042114</t>
   </si>
   <si>
     <t xml:space="preserve">7.76996755599976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64046812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435707092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48219060897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79152679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64044523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48936319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6260552406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5613055229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791904449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19439077377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02172565460205</t>
+    <t xml:space="preserve">7.64046859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48219156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79152727127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836158752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850147247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6404447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48936223983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325119018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56130599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411195755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791856765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19439125061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02172517776489</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619512557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4677791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641592025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51814079284668</t>
+    <t xml:space="preserve">5.86344718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914144515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619560241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46777820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51813983917236</t>
   </si>
   <si>
     <t xml:space="preserve">6.46058416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29511308670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10086250305176</t>
+    <t xml:space="preserve">6.2951135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10086345672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.13683557510376</t>
@@ -1385,34 +1385,34 @@
     <t xml:space="preserve">5.89222526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79869842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97136449813843</t>
+    <t xml:space="preserve">5.79869890213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97136497497559</t>
   </si>
   <si>
     <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99294757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17280864715576</t>
+    <t xml:space="preserve">5.99294710159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1728081703186</t>
   </si>
   <si>
     <t xml:space="preserve">6.18719720840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25194549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22316884994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12244749069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27353000640869</t>
+    <t xml:space="preserve">6.25194692611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12244701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27352952957153</t>
   </si>
   <si>
     <t xml:space="preserve">6.30950260162354</t>
@@ -1421,34 +1421,34 @@
     <t xml:space="preserve">6.30230808258057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33827972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58551645278931</t>
+    <t xml:space="preserve">6.33827924728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58551692962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.38323211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46564340591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326242446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3083119392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59300947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41320085525513</t>
+    <t xml:space="preserve">6.46564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59300899505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41320037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.17345428466797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09853363037109</t>
+    <t xml:space="preserve">6.09853410720825</t>
   </si>
   <si>
     <t xml:space="preserve">5.90374040603638</t>
@@ -1457,16 +1457,16 @@
     <t xml:space="preserve">5.95618486404419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94120025634766</t>
+    <t xml:space="preserve">5.94120073318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.86628007888794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94869232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84380388259888</t>
+    <t xml:space="preserve">5.9486927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84380435943604</t>
   </si>
   <si>
     <t xml:space="preserve">5.59656572341919</t>
@@ -1478,13 +1478,13 @@
     <t xml:space="preserve">5.60405826568604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55910491943359</t>
+    <t xml:space="preserve">5.55910539627075</t>
   </si>
   <si>
     <t xml:space="preserve">5.888756275177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80634355545044</t>
+    <t xml:space="preserve">5.80634307861328</t>
   </si>
   <si>
     <t xml:space="preserve">5.64151811599731</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">6.33078765869141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55554914474487</t>
+    <t xml:space="preserve">6.55554962158203</t>
   </si>
   <si>
     <t xml:space="preserve">6.45815277099609</t>
@@ -1514,22 +1514,22 @@
     <t xml:space="preserve">6.3008189201355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.128502368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06107378005981</t>
+    <t xml:space="preserve">6.12850189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0610728263855</t>
   </si>
   <si>
     <t xml:space="preserve">5.77637529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.768883228302</t>
+    <t xml:space="preserve">5.76888275146484</t>
   </si>
   <si>
     <t xml:space="preserve">5.70145463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66399431228638</t>
+    <t xml:space="preserve">5.66399478912354</t>
   </si>
   <si>
     <t xml:space="preserve">5.57409000396729</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">5.75389909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78386783599854</t>
+    <t xml:space="preserve">5.78386735916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.67897844314575</t>
@@ -1547,70 +1547,70 @@
     <t xml:space="preserve">5.62653398513794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61904191970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65650272369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54412221908569</t>
+    <t xml:space="preserve">5.61904239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65650320053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54412174224854</t>
   </si>
   <si>
     <t xml:space="preserve">5.58158159255981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50666046142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53662872314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43174028396606</t>
+    <t xml:space="preserve">5.50666093826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53662967681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43174076080322</t>
   </si>
   <si>
     <t xml:space="preserve">5.4692006111145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31936025619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28189945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424869537354</t>
+    <t xml:space="preserve">5.31935977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28189897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424917221069</t>
   </si>
   <si>
     <t xml:space="preserve">5.49167680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51415348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36431217193604</t>
+    <t xml:space="preserve">5.51415300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36431169509888</t>
   </si>
   <si>
     <t xml:space="preserve">5.27440738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18450260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20697927474976</t>
+    <t xml:space="preserve">5.18450212478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2069787979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.58907413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74640703201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47669363021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21447086334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13955068588257</t>
+    <t xml:space="preserve">5.74640655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47669315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21447134017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13955020904541</t>
   </si>
   <si>
     <t xml:space="preserve">5.09459781646729</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">5.10958242416382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07212257385254</t>
+    <t xml:space="preserve">5.07212162017822</t>
   </si>
   <si>
     <t xml:space="preserve">5.05713796615601</t>
@@ -1628,13 +1628,13 @@
     <t xml:space="preserve">5.01967763900757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03466129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732887268066</t>
+    <t xml:space="preserve">5.03466176986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732839584351</t>
   </si>
   <si>
     <t xml:space="preserve">4.86983680725098</t>
@@ -1643,19 +1643,19 @@
     <t xml:space="preserve">4.73498010635376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77243947982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82488441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88482093811035</t>
+    <t xml:space="preserve">4.77243995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82488393783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
     <t xml:space="preserve">4.75745534896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86234378814697</t>
+    <t xml:space="preserve">4.86234426498413</t>
   </si>
   <si>
     <t xml:space="preserve">4.9147891998291</t>
@@ -1664,22 +1664,22 @@
     <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8548526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95224905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16951894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710622787476</t>
+    <t xml:space="preserve">4.85485219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95224952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16951847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0871057510376</t>
   </si>
   <si>
     <t xml:space="preserve">5.13205862045288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21840667724609</t>
+    <t xml:space="preserve">6.21840763092041</t>
   </si>
   <si>
     <t xml:space="preserve">6.25586652755737</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">5.99364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04215383529663</t>
+    <t xml:space="preserve">5.04215335845947</t>
   </si>
   <si>
     <t xml:space="preserve">4.98221731185913</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">4.99720144271851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0271692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89231300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964542388916</t>
+    <t xml:space="preserve">5.02716970443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89231252670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964590072632</t>
   </si>
   <si>
     <t xml:space="preserve">4.95974111557007</t>
@@ -1736,34 +1736,34 @@
     <t xml:space="preserve">4.90729665756226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76494789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4727578163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38285350799561</t>
+    <t xml:space="preserve">4.76494741439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47275686264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047252655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38285255432129</t>
   </si>
   <si>
     <t xml:space="preserve">4.32291650772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18056678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558265686035</t>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
   </si>
   <si>
     <t xml:space="preserve">4.30043983459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31542444229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46526479721069</t>
+    <t xml:space="preserve">4.31542491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46526527404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.45777320861816</t>
@@ -1775,25 +1775,25 @@
     <t xml:space="preserve">5.10208988189697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07961416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726539611816</t>
+    <t xml:space="preserve">5.07961463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726491928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.01218605041504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24443960189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196340560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19948720932007</t>
+    <t xml:space="preserve">5.24444007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25942373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19948673248291</t>
   </si>
   <si>
     <t xml:space="preserve">5.11707401275635</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">5.16202640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31186819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41675662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180376052856</t>
+    <t xml:space="preserve">5.31186866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41675615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180423736572</t>
   </si>
   <si>
     <t xml:space="preserve">5.44672441482544</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39427995681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421743392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.409264087677</t>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40926456451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.89624834060669</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">6.12100982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22589874267578</t>
+    <t xml:space="preserve">6.22589826583862</t>
   </si>
   <si>
     <t xml:space="preserve">5.81383514404297</t>
@@ -1844,28 +1844,28 @@
     <t xml:space="preserve">6.00113725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79885149002075</t>
+    <t xml:space="preserve">5.79885101318359</t>
   </si>
   <si>
     <t xml:space="preserve">5.82132768630981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91123199462891</t>
+    <t xml:space="preserve">5.91123247146606</t>
   </si>
   <si>
     <t xml:space="preserve">6.03110551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.008629322052</t>
+    <t xml:space="preserve">6.00862979888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.91872453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83631181716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377166748047</t>
+    <t xml:space="preserve">5.83631134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377214431763</t>
   </si>
   <si>
     <t xml:space="preserve">5.97116804122925</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">6.21091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09104204177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348554611206</t>
+    <t xml:space="preserve">6.09104156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097761154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1434850692749</t>
   </si>
   <si>
     <t xml:space="preserve">6.04608869552612</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">6.03859758377075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73142337799072</t>
+    <t xml:space="preserve">5.73142242431641</t>
   </si>
   <si>
     <t xml:space="preserve">5.97866010665894</t>
@@ -1901,52 +1901,52 @@
     <t xml:space="preserve">5.69396209716797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72393083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70894718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170854568481</t>
+    <t xml:space="preserve">5.72393035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916887283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170806884766</t>
   </si>
   <si>
     <t xml:space="preserve">5.73891448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55161380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47268533706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33155584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484422683716</t>
+    <t xml:space="preserve">5.55161333084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47268581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33155632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484518051147</t>
   </si>
   <si>
     <t xml:space="preserve">5.35507726669312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30803489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37860012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24531078338623</t>
+    <t xml:space="preserve">5.30803442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859964370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531030654907</t>
   </si>
   <si>
     <t xml:space="preserve">5.26883172988892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28451299667358</t>
+    <t xml:space="preserve">5.28451251983643</t>
   </si>
   <si>
     <t xml:space="preserve">5.25315093994141</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">5.14338350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06497812271118</t>
+    <t xml:space="preserve">5.06497859954834</t>
   </si>
   <si>
     <t xml:space="preserve">5.00225448608398</t>
@@ -1967,37 +1967,37 @@
     <t xml:space="preserve">5.20610809326172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33939695358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235315322876</t>
+    <t xml:space="preserve">5.33939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235410690308</t>
   </si>
   <si>
     <t xml:space="preserve">5.11986207962036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13554286956787</t>
+    <t xml:space="preserve">5.13554334640503</t>
   </si>
   <si>
     <t xml:space="preserve">5.09634065628052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11202144622803</t>
+    <t xml:space="preserve">5.11202096939087</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44916439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45700407028198</t>
+    <t xml:space="preserve">5.44916391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45700454711914</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70790147781372</t>
+    <t xml:space="preserve">5.70790195465088</t>
   </si>
   <si>
     <t xml:space="preserve">5.67653942108154</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">5.63733673095703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55893135070801</t>
+    <t xml:space="preserve">5.55893182754517</t>
   </si>
   <si>
     <t xml:space="preserve">5.51188802719116</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48052644729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36291790008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31587505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32371616363525</t>
+    <t xml:space="preserve">5.48052549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36291837692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31587553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3237156867981</t>
   </si>
   <si>
     <t xml:space="preserve">5.19826745986938</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">4.71999502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51614189147949</t>
+    <t xml:space="preserve">4.51614236831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.97089195251465</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">4.71215534210205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67295217514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63374948501587</t>
+    <t xml:space="preserve">4.67295265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63374900817871</t>
   </si>
   <si>
     <t xml:space="preserve">4.64943075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59454679489136</t>
+    <t xml:space="preserve">4.59454727172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.62590885162354</t>
@@ -2072,34 +2072,34 @@
     <t xml:space="preserve">4.68079233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90032768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2296290397644</t>
+    <t xml:space="preserve">4.90032720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22962951660156</t>
   </si>
   <si>
     <t xml:space="preserve">5.02577543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0414571762085</t>
+    <t xml:space="preserve">5.04145622253418</t>
   </si>
   <si>
     <t xml:space="preserve">5.15122413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21394872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15906476974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08065938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1277027130127</t>
+    <t xml:space="preserve">5.22178888320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21394824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15906429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08065986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12770318984985</t>
   </si>
   <si>
     <t xml:space="preserve">5.01793527603149</t>
@@ -2114,19 +2114,19 @@
     <t xml:space="preserve">5.19042634963989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18258666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52756881713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5197286605835</t>
+    <t xml:space="preserve">5.18258619308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52756929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51972818374634</t>
   </si>
   <si>
     <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5667724609375</t>
+    <t xml:space="preserve">5.56677198410034</t>
   </si>
   <si>
     <t xml:space="preserve">5.43348264694214</t>
@@ -2135,31 +2135,31 @@
     <t xml:space="preserve">5.50404787063599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53541040420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41780138015747</t>
+    <t xml:space="preserve">5.53540992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41780185699463</t>
   </si>
   <si>
     <t xml:space="preserve">5.42564249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84118986129761</t>
+    <t xml:space="preserve">5.84119033813477</t>
   </si>
   <si>
     <t xml:space="preserve">5.76278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64517736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44132423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40996170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38643980026245</t>
+    <t xml:space="preserve">5.64517688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44132328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40996122360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38644027709961</t>
   </si>
   <si>
     <t xml:space="preserve">5.34723711013794</t>
@@ -2168,19 +2168,19 @@
     <t xml:space="preserve">5.37075901031494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23746967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97873210906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8376030921936</t>
+    <t xml:space="preserve">5.23746919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97873258590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83760356903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.89248704910278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86896467208862</t>
+    <t xml:space="preserve">4.86896514892578</t>
   </si>
   <si>
     <t xml:space="preserve">4.92384910583496</t>
@@ -2192,28 +2192,28 @@
     <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750442504883</t>
+    <t xml:space="preserve">4.57102584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750394821167</t>
   </si>
   <si>
     <t xml:space="preserve">4.57886648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39069366455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15547800064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22604274749756</t>
+    <t xml:space="preserve">4.39069271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15547752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2260422706604</t>
   </si>
   <si>
     <t xml:space="preserve">4.1162748336792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84185695648193</t>
+    <t xml:space="preserve">3.84185671806335</t>
   </si>
   <si>
     <t xml:space="preserve">3.63800263404846</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">3.29301977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32438158988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099406242371</t>
+    <t xml:space="preserve">3.32438182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099382400513</t>
   </si>
   <si>
     <t xml:space="preserve">3.09700679779053</t>
@@ -2240,22 +2240,22 @@
     <t xml:space="preserve">2.94803690910339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00292038917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13620972633362</t>
+    <t xml:space="preserve">3.00292062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13620948791504</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21461486816406</t>
+    <t xml:space="preserve">3.21461462974548</t>
   </si>
   <si>
     <t xml:space="preserve">3.25381779670715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22245526313782</t>
+    <t xml:space="preserve">3.22245502471924</t>
   </si>
   <si>
     <t xml:space="preserve">3.24205660820007</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">3.36750507354736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34006309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45767116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59880042076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37142539024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52039527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54391646385193</t>
+    <t xml:space="preserve">3.34006333351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59880089759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37142562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52039504051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54391694068909</t>
   </si>
   <si>
     <t xml:space="preserve">3.7242488861084</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">3.81049418449402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9202618598938</t>
+    <t xml:space="preserve">3.92026209831238</t>
   </si>
   <si>
     <t xml:space="preserve">4.33581018447876</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">4.32796907424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32012891769409</t>
+    <t xml:space="preserve">4.32012796401978</t>
   </si>
   <si>
     <t xml:space="preserve">4.23388242721558</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">4.16331815719604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07707166671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21820211410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036100387573</t>
+    <t xml:space="preserve">4.07707214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21820163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036148071289</t>
   </si>
   <si>
     <t xml:space="preserve">4.25740432739258</t>
@@ -2327,13 +2327,13 @@
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208975791931</t>
+    <t xml:space="preserve">3.73208951950073</t>
   </si>
   <si>
     <t xml:space="preserve">3.79481387138367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83401608467102</t>
+    <t xml:space="preserve">3.83401584625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.84577703475952</t>
@@ -2342,31 +2342,31 @@
     <t xml:space="preserve">3.7007269859314</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83009648323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265402793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225513458252</t>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225561141968</t>
   </si>
   <si>
     <t xml:space="preserve">3.86145853996277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75169038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74385023117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660701751709</t>
+    <t xml:space="preserve">3.75169014930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385046958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298621177673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660749435425</t>
   </si>
   <si>
     <t xml:space="preserve">4.10059404373169</t>
@@ -2378,100 +2378,100 @@
     <t xml:space="preserve">3.95946478843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03786945343018</t>
+    <t xml:space="preserve">4.03787040710449</t>
   </si>
   <si>
     <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763689041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01434850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95162391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9437837600708</t>
+    <t xml:space="preserve">4.14763641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01434803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95162415504456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94378328323364</t>
   </si>
   <si>
     <t xml:space="preserve">3.8889000415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.053551197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923198699951</t>
+    <t xml:space="preserve">4.05355024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923151016235</t>
   </si>
   <si>
     <t xml:space="preserve">4.030029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89282011985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810225486755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8575382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8653781414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617545127869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105869293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90850114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913284301758</t>
+    <t xml:space="preserve">3.89281988143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810201644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242146492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753750801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86537837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105893135071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458059310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085009098053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913236618042</t>
   </si>
   <si>
     <t xml:space="preserve">3.755610704422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74777030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96730470657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02218866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594264984131</t>
+    <t xml:space="preserve">3.74777054786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657410621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96730518341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02218914031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594312667847</t>
   </si>
   <si>
     <t xml:space="preserve">3.76345133781433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75953102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64584302902222</t>
+    <t xml:space="preserve">3.75953078269958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64584374427795</t>
   </si>
   <si>
     <t xml:space="preserve">3.66936540603638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66544556617737</t>
+    <t xml:space="preserve">3.66544485092163</t>
   </si>
   <si>
     <t xml:space="preserve">3.63016247749329</t>
@@ -2480,28 +2480,28 @@
     <t xml:space="preserve">3.56351804733276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56743836402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59096002578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119235038757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44198942184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38710641860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654191017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33222270011902</t>
+    <t xml:space="preserve">3.56743812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5909595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903298377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119306564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44198966026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38710618019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33222246170044</t>
   </si>
   <si>
     <t xml:space="preserve">3.40278744697571</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">3.43807005882263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46551156044006</t>
+    <t xml:space="preserve">3.46551132202148</t>
   </si>
   <si>
     <t xml:space="preserve">3.49295353889465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55175757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55567789077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50079441070557</t>
+    <t xml:space="preserve">3.55175733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55567765235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50079393386841</t>
   </si>
   <si>
     <t xml:space="preserve">3.51255440711975</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">3.37926578521729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43414974212646</t>
+    <t xml:space="preserve">3.43414950370789</t>
   </si>
   <si>
     <t xml:space="preserve">3.42630887031555</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">3.4498302936554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15189051628113</t>
+    <t xml:space="preserve">3.15189027786255</t>
   </si>
   <si>
     <t xml:space="preserve">3.20677423477173</t>
@@ -2555,28 +2555,28 @@
     <t xml:space="preserve">3.17541241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52823567390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607654571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10843420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866700172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2025203704834</t>
+    <t xml:space="preserve">3.528235912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215622901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607630729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10843467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252132415771</t>
   </si>
   <si>
     <t xml:space="preserve">4.13195610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09275341033936</t>
+    <t xml:space="preserve">4.09275388717651</t>
   </si>
   <si>
     <t xml:space="preserve">4.06139135360718</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">4.28876638412476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2495641708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24172258377075</t>
+    <t xml:space="preserve">4.24956369400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.39853382110596</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">4.35933065414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69647359848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919771194458</t>
+    <t xml:space="preserve">4.69647312164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75919818878174</t>
   </si>
   <si>
     <t xml:space="preserve">4.82976293563843</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">4.7278356552124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74351739883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76703882217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487993240356</t>
+    <t xml:space="preserve">4.74351692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76703834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487897872925</t>
   </si>
   <si>
     <t xml:space="preserve">4.73567628860474</t>
@@ -2630,40 +2630,40 @@
     <t xml:space="preserve">5.01009464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99441337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9473705291748</t>
+    <t xml:space="preserve">4.99441385269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94737005233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.86112451553345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84544372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91600799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93953037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04929733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245229721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68437957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59813404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62949562072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71574211120605</t>
+    <t xml:space="preserve">4.84544324874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91600847244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93952989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04929780960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59813356399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6294960975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7157416343689</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222068786621</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">5.66869878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66085815429688</t>
+    <t xml:space="preserve">5.66085767745972</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358226776123</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">5.78630638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08424663543701</t>
+    <t xml:space="preserve">6.08424711227417</t>
   </si>
   <si>
     <t xml:space="preserve">6.17833280563354</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">6.14697074890137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05288410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97447872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720331192017</t>
+    <t xml:space="preserve">6.05288457870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97447919845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720235824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">6.11834812164307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49161577224731</t>
+    <t xml:space="preserve">6.49161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">6.45915842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42670059204102</t>
+    <t xml:space="preserve">6.4266996383667</t>
   </si>
   <si>
     <t xml:space="preserve">6.26440954208374</t>
@@ -2726,91 +2726,91 @@
     <t xml:space="preserve">6.39424228668213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44292974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96225833892822</t>
+    <t xml:space="preserve">6.44292879104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96225786209106</t>
   </si>
   <si>
     <t xml:space="preserve">7.14077806472778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43289995193481</t>
+    <t xml:space="preserve">7.43290090560913</t>
   </si>
   <si>
     <t xml:space="preserve">8.00091743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83862638473511</t>
+    <t xml:space="preserve">7.83862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">7.87108421325684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78993988037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977214813232</t>
+    <t xml:space="preserve">7.78993892669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977167129517</t>
   </si>
   <si>
     <t xml:space="preserve">7.95222997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90354251861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60139274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6419620513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56081962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43910121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19566631317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01714515686035</t>
+    <t xml:space="preserve">7.90354299545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60139179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64196395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56081867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43910026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19566535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23623847961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01714706420898</t>
   </si>
   <si>
     <t xml:space="preserve">8.06583309173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96845960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4004430770874</t>
+    <t xml:space="preserve">7.96845865249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40044212341309</t>
   </si>
   <si>
     <t xml:space="preserve">7.25438070297241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4815878868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64387798309326</t>
+    <t xml:space="preserve">7.48158884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64387941360474</t>
   </si>
   <si>
     <t xml:space="preserve">7.5627326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69256448745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502374649048</t>
+    <t xml:space="preserve">7.69256496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502422332764</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62764930725098</t>
+    <t xml:space="preserve">7.6276478767395</t>
   </si>
   <si>
     <t xml:space="preserve">7.4653582572937</t>
@@ -2819,79 +2819,79 @@
     <t xml:space="preserve">7.3030686378479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22192287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81619691848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15700721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23815202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38421392440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70879507064819</t>
+    <t xml:space="preserve">7.22192335128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81619644165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15700674057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23815250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3842134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70879364013672</t>
   </si>
   <si>
     <t xml:space="preserve">7.61141967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66010761260986</t>
+    <t xml:space="preserve">7.66010713577271</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74125289916992</t>
+    <t xml:space="preserve">7.74125194549561</t>
   </si>
   <si>
     <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15509414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96654605865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84482765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5202465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39852905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47967433929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31738376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08206367492676</t>
+    <t xml:space="preserve">8.1550931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96654510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368141174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52024745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39852809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47967338562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31738471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08206272125244</t>
   </si>
   <si>
     <t xml:space="preserve">8.11452007293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03337478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04960441589355</t>
+    <t xml:space="preserve">8.03337574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04960536956787</t>
   </si>
   <si>
     <t xml:space="preserve">9.04768943786621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41284370422363</t>
+    <t xml:space="preserve">9.41284465789795</t>
   </si>
   <si>
     <t xml:space="preserve">9.16940784454346</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">9.7795877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61241436004639</t>
+    <t xml:space="preserve">9.6124153137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.57062244415283</t>
@@ -2924,16 +2924,16 @@
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420818328857</t>
+    <t xml:space="preserve">9.73779392242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420913696289</t>
   </si>
   <si>
     <t xml:space="preserve">9.90496635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31986331939697</t>
+    <t xml:space="preserve">9.31986236572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
@@ -2942,22 +2942,22 @@
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15269088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013889312744</t>
+    <t xml:space="preserve">9.15268993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.7765531539917</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35862159729004</t>
+    <t xml:space="preserve">8.35862064361572</t>
   </si>
   <si>
     <t xml:space="preserve">8.6093807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19448280334473</t>
+    <t xml:space="preserve">9.19448375701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">9.11089706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36165523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06910610198975</t>
+    <t xml:space="preserve">9.36165618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06910514831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.94372463226318</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">8.90193176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81834697723389</t>
+    <t xml:space="preserve">8.81834602355957</t>
   </si>
   <si>
     <t xml:space="preserve">8.56758785247803</t>
@@ -2987,49 +2987,49 @@
     <t xml:space="preserve">8.52579307556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73476028442383</t>
+    <t xml:space="preserve">8.73475933074951</t>
   </si>
   <si>
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32518768310547</t>
+    <t xml:space="preserve">8.30846881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32518672943115</t>
   </si>
   <si>
     <t xml:space="preserve">7.65649747848511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82366943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321538925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154626846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0713939666748</t>
+    <t xml:space="preserve">7.82366991043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321443557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07139444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.10482835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68993186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589017868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053916931152</t>
+    <t xml:space="preserve">7.68993139266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053869247437</t>
   </si>
   <si>
     <t xml:space="preserve">7.80695247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62306308746338</t>
+    <t xml:space="preserve">7.62306261062622</t>
   </si>
   <si>
     <t xml:space="preserve">7.99084281921387</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">8.40041542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1078634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48400115966797</t>
+    <t xml:space="preserve">8.10786247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48400020599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.30011177062988</t>
@@ -3059,31 +3059,31 @@
     <t xml:space="preserve">8.35026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24995994567871</t>
+    <t xml:space="preserve">8.24996089935303</t>
   </si>
   <si>
     <t xml:space="preserve">7.8738226890564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69828987121582</t>
+    <t xml:space="preserve">7.69829034805298</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531190872192</t>
+    <t xml:space="preserve">7.81531095504761</t>
   </si>
   <si>
     <t xml:space="preserve">7.77351856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91561603546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78187656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60634660720825</t>
+    <t xml:space="preserve">7.91561508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7818775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60634565353394</t>
   </si>
   <si>
     <t xml:space="preserve">7.89889764785767</t>
@@ -3092,19 +3092,19 @@
     <t xml:space="preserve">7.79859447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79023504257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41302871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64850187301636</t>
+    <t xml:space="preserve">7.79023551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978052139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41302824020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64850234985352</t>
   </si>
   <si>
     <t xml:space="preserve">8.24154376983643</t>
@@ -3113,16 +3113,16 @@
     <t xml:space="preserve">8.21538066864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28514862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32003498077393</t>
+    <t xml:space="preserve">8.28514957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32003402709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19793796539307</t>
+    <t xml:space="preserve">8.19793701171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.49445819854736</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678535461426</t>
+    <t xml:space="preserve">8.54678630828857</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
@@ -3155,19 +3155,19 @@
     <t xml:space="preserve">8.45957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177486419678</t>
+    <t xml:space="preserve">8.17177391052246</t>
   </si>
   <si>
     <t xml:space="preserve">8.1281681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93630123138428</t>
+    <t xml:space="preserve">7.93630218505859</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827125549316</t>
+    <t xml:space="preserve">7.71827077865601</t>
   </si>
   <si>
     <t xml:space="preserve">7.77931928634644</t>
@@ -3176,43 +3176,43 @@
     <t xml:space="preserve">7.95374345779419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14561080932617</t>
+    <t xml:space="preserve">8.14560985565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86653232574463</t>
+    <t xml:space="preserve">7.86653184890747</t>
   </si>
   <si>
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804016113281</t>
+    <t xml:space="preserve">7.78804063796997</t>
   </si>
   <si>
     <t xml:space="preserve">7.65722274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76187658309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69210767745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70082855224609</t>
+    <t xml:space="preserve">7.76187705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6921067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70082807540894</t>
   </si>
   <si>
     <t xml:space="preserve">7.5961742401123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46535634994507</t>
+    <t xml:space="preserve">7.46535587310791</t>
   </si>
   <si>
     <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571300506592</t>
+    <t xml:space="preserve">7.73571395874023</t>
   </si>
   <si>
     <t xml:space="preserve">7.50024080276489</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256843566895</t>
+    <t xml:space="preserve">7.55256748199463</t>
   </si>
   <si>
     <t xml:space="preserve">7.447913646698</t>
@@ -3236,19 +3236,19 @@
     <t xml:space="preserve">7.50896167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57001066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80548286437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74443483352661</t>
+    <t xml:space="preserve">7.57001113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80548334121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74443435668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77353763580322</t>
+    <t xml:space="preserve">8.77353858947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.72121047973633</t>
@@ -3257,16 +3257,16 @@
     <t xml:space="preserve">8.48573684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50318050384521</t>
+    <t xml:space="preserve">8.5031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3461971282959</t>
+    <t xml:space="preserve">8.41596794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34619808197021</t>
   </si>
   <si>
     <t xml:space="preserve">8.02351379394531</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83164596557617</t>
+    <t xml:space="preserve">7.83164644241333</t>
   </si>
   <si>
     <t xml:space="preserve">7.66594362258911</t>
@@ -3287,31 +3287,31 @@
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97118711471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68338632583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16883516311646</t>
+    <t xml:space="preserve">7.9711856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33453750610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1688346862793</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418037414551</t>
+    <t xml:space="preserve">7.06418085098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13395023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12522888183594</t>
+    <t xml:space="preserve">7.13395071029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12522840499878</t>
   </si>
   <si>
     <t xml:space="preserve">6.78510189056396</t>
@@ -3323,46 +3323,46 @@
     <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63684129714966</t>
+    <t xml:space="preserve">6.6368408203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75315570831299</t>
+    <t xml:space="preserve">7.75315618515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.4391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43047189712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49151992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27348899841309</t>
+    <t xml:space="preserve">7.43047142028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49152040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2734899520874</t>
   </si>
   <si>
     <t xml:space="preserve">7.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38686513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35198068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31709575653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47407722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.290931224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581615447998</t>
+    <t xml:space="preserve">7.38686466217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3519811630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31709623336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47407674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29093170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581663131714</t>
   </si>
   <si>
     <t xml:space="preserve">7.30837440490723</t>
@@ -3371,28 +3371,28 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663547515869</t>
+    <t xml:space="preserve">7.45663499832153</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03223514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1020040512085</t>
+    <t xml:space="preserve">7.85781002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03223419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10200500488281</t>
   </si>
   <si>
     <t xml:space="preserve">8.15433216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09328365325928</t>
+    <t xml:space="preserve">8.05839729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09328269958496</t>
   </si>
   <si>
     <t xml:space="preserve">8.00607109069824</t>
@@ -3401,31 +3401,31 @@
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584095001221</t>
+    <t xml:space="preserve">8.11072540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584190368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990703582764</t>
+    <t xml:space="preserve">7.97990751266479</t>
   </si>
   <si>
     <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90141677856445</t>
+    <t xml:space="preserve">7.90141725540161</t>
   </si>
   <si>
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82292556762695</t>
+    <t xml:space="preserve">7.91885900497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82292652130127</t>
   </si>
   <si>
     <t xml:space="preserve">8.11944675445557</t>
@@ -3440,16 +3440,16 @@
     <t xml:space="preserve">8.337477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52934265136719</t>
+    <t xml:space="preserve">8.5293436050415</t>
   </si>
   <si>
     <t xml:space="preserve">8.94796180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87819194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563465118408</t>
+    <t xml:space="preserve">8.87819290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563369750977</t>
   </si>
   <si>
     <t xml:space="preserve">8.65144062042236</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">8.71248912811279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86074924468994</t>
+    <t xml:space="preserve">8.86075019836426</t>
   </si>
   <si>
     <t xml:space="preserve">8.93051910400391</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">8.6863260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15727138519287</t>
+    <t xml:space="preserve">9.15727043151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">8.91307735443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00028800964355</t>
+    <t xml:space="preserve">8.96540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00028896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3512,22 +3512,22 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842304229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66888332366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91124629974365</t>
+    <t xml:space="preserve">8.80842208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66888236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91124534606934</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85674285888672</t>
+    <t xml:space="preserve">8.82040786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8567419052124</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422660827637</t>
+    <t xml:space="preserve">8.58422756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498722076416</t>
+    <t xml:space="preserve">8.77498817443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49339008331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3843822479248</t>
+    <t xml:space="preserve">8.49338912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38438320159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453884124756</t>
+    <t xml:space="preserve">8.18453788757324</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896446228027</t>
+    <t xml:space="preserve">8.33896350860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09369945526123</t>
+    <t xml:space="preserve">8.09370040893555</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04827976226807</t>
+    <t xml:space="preserve">8.04828071594238</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644916534424</t>
+    <t xml:space="preserve">8.06644821166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3653,40 +3653,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919792175293</t>
+    <t xml:space="preserve">8.03919696807861</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9483585357666</t>
+    <t xml:space="preserve">8.00286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94835901260376</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744276046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90293884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385557174683</t>
+    <t xml:space="preserve">7.95744228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9029393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385461807251</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85751962661743</t>
+    <t xml:space="preserve">7.85752010345459</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210088729858</t>
+    <t xml:space="preserve">7.81210136413574</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126293182373</t>
+    <t xml:space="preserve">7.72126245498657</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568855285645</t>
+    <t xml:space="preserve">7.87568807601929</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950824737549</t>
+    <t xml:space="preserve">7.63950777053833</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4941668510437</t>
+    <t xml:space="preserve">7.49416637420654</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4124116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44874715805054</t>
+    <t xml:space="preserve">7.41241216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4487476348877</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112392425537</t>
+    <t xml:space="preserve">6.73112440109253</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72204065322876</t>
+    <t xml:space="preserve">6.7220401763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486722946167</t>
+    <t xml:space="preserve">6.59486675262451</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3800,22 +3800,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272296905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767621994019</t>
+    <t xml:space="preserve">7.01272344589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699247360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31248998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790967941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767669677734</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393291473389</t>
+    <t xml:space="preserve">7.79393339157104</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3836,31 +3836,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9665265083313</t>
+    <t xml:space="preserve">7.76668214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96652698516846</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47599840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607669830322</t>
+    <t xml:space="preserve">7.63042449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.475998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607717514038</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523874282837</t>
+    <t xml:space="preserve">7.28523921966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264514923096</t>
+    <t xml:space="preserve">7.11264562606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225700378418</t>
+    <t xml:space="preserve">7.61225652694702</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890327453613</t>
+    <t xml:space="preserve">7.24890279769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -71001,7 +71001,7 @@
     </row>
     <row r="2553">
       <c r="A2553" s="1" t="n">
-        <v>46041.6909953704</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2553" t="n">
         <v>26656</v>
@@ -71022,6 +71022,32 @@
         <v>1432</v>
       </c>
       <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46042.6909953704</v>
+      </c>
+      <c r="B2554" t="n">
+        <v>12290</v>
+      </c>
+      <c r="C2554" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H2554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355509757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546660900116</t>
+    <t xml:space="preserve">1.21355521678925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546637058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.20654845237732</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">1.23177242279053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24998998641968</t>
+    <t xml:space="preserve">1.2499897480011</t>
   </si>
   <si>
     <t xml:space="preserve">1.26330232620239</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">1.27311182022095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26120042800903</t>
+    <t xml:space="preserve">1.26120054721832</t>
   </si>
   <si>
     <t xml:space="preserve">1.24718701839447</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">1.20794975757599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19323563575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17501842975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814050197601</t>
+    <t xml:space="preserve">1.19323575496674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17501854896545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1981406211853</t>
   </si>
   <si>
     <t xml:space="preserve">1.24578595161438</t>
@@ -89,64 +89,64 @@
     <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495652198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18272566795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17992317676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641949653625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12457048892975</t>
+    <t xml:space="preserve">1.21495628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18272578716278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17992293834686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641985416412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12457025051117</t>
   </si>
   <si>
     <t xml:space="preserve">1.12807381153107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10284960269928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08603358268738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01596713066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0250757932663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02017116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297377586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.04329311847687</t>
+    <t xml:space="preserve">1.10284984111786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08603370189667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01596701145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02507567405701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02017104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195372104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297365665436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04329299926758</t>
   </si>
   <si>
     <t xml:space="preserve">1.09654366970062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11335980892181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1105569601059</t>
+    <t xml:space="preserve">1.11335968971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11055707931519</t>
   </si>
   <si>
     <t xml:space="preserve">1.0930403470993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12106728553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017582893372</t>
+    <t xml:space="preserve">1.12106704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017594814301</t>
   </si>
   <si>
     <t xml:space="preserve">1.15610027313232</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">1.14909374713898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17852199077606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1701135635376</t>
+    <t xml:space="preserve">1.17852163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17011368274689</t>
   </si>
   <si>
     <t xml:space="preserve">1.18412709236145</t>
@@ -182,37 +182,37 @@
     <t xml:space="preserve">1.17081451416016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16310715675354</t>
+    <t xml:space="preserve">1.16310703754425</t>
   </si>
   <si>
     <t xml:space="preserve">1.22616708278656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24508512020111</t>
+    <t xml:space="preserve">1.2450852394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.24088108539581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20514714717865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19113385677338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22686779499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22196316719055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24438440799713</t>
+    <t xml:space="preserve">1.20514702796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113373756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22686767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22196304798126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24438428878784</t>
   </si>
   <si>
     <t xml:space="preserve">1.17221570014954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19183444976807</t>
+    <t xml:space="preserve">1.19183433055878</t>
   </si>
   <si>
     <t xml:space="preserve">1.19743978977203</t>
@@ -221,31 +221,31 @@
     <t xml:space="preserve">1.20374572277069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.203045129776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23807847499847</t>
+    <t xml:space="preserve">1.20304501056671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23807859420776</t>
   </si>
   <si>
     <t xml:space="preserve">1.23317384719849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19954180717468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2247656583786</t>
+    <t xml:space="preserve">1.19954168796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22476577758789</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845972537994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21916043758392</t>
+    <t xml:space="preserve">1.21916031837463</t>
   </si>
   <si>
     <t xml:space="preserve">1.22896981239319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.212153673172</t>
+    <t xml:space="preserve">1.21215379238129</t>
   </si>
   <si>
     <t xml:space="preserve">1.22266376018524</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">1.29202973842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29623377323151</t>
+    <t xml:space="preserve">1.29623365402222</t>
   </si>
   <si>
     <t xml:space="preserve">1.2752138376236</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">1.28712522983551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28151977062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788773059845</t>
+    <t xml:space="preserve">1.28151988983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788784980774</t>
   </si>
   <si>
     <t xml:space="preserve">1.23737788200378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20865035057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469908714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138627052307</t>
+    <t xml:space="preserve">1.20865046977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469920635223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138638973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.11896502971649</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13648176193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14629113674164</t>
+    <t xml:space="preserve">1.13648164272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14629101753235</t>
   </si>
   <si>
     <t xml:space="preserve">1.14208710193634</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">1.084632396698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501352787018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07061910629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08253026008606</t>
+    <t xml:space="preserve">1.06501376628876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07061898708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08253037929535</t>
   </si>
   <si>
     <t xml:space="preserve">1.07902693748474</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05800688266754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1014484167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355031490326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09514224529266</t>
+    <t xml:space="preserve">1.05800712108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10144829750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355043411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09514236450195</t>
   </si>
   <si>
     <t xml:space="preserve">1.11966574192047</t>
@@ -332,16 +332,16 @@
     <t xml:space="preserve">1.09934628009796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11265921592712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15680122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528040885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681533336639</t>
+    <t xml:space="preserve">1.11265909671783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1568009853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528028964996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48681509494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.48821663856506</t>
@@ -350,142 +350,142 @@
     <t xml:space="preserve">1.45178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4153470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45738708972931</t>
+    <t xml:space="preserve">1.41534698009491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4573872089386</t>
   </si>
   <si>
     <t xml:space="preserve">1.40133380889893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4699991941452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375528812408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43636727333069</t>
+    <t xml:space="preserve">1.46999931335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776857852936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375516891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4363671541214</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936050891876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41674864292145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42235374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814970970154</t>
+    <t xml:space="preserve">1.41674852371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42235386371613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814982891083</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42795932292938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48120999336243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69421243667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338312625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071377754211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84555697441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7923059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268743515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064732551575</t>
+    <t xml:space="preserve">1.42795920372009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48121011257172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6942126750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8007138967514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84555649757385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79230606555939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090464115143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268731594086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064720630646</t>
   </si>
   <si>
     <t xml:space="preserve">1.71663403511047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670084476471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8427540063858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593786716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313525676727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8399510383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83854997158051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84415531158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8301420211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472718715668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874059677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192481517792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294439315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835922718048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937928199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99549925327301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07257294654846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02913117408752</t>
+    <t xml:space="preserve">1.78670048713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8259379863739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313513755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995127677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83855020999908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8441549539566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014190196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472754478455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874035835266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192445755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835958480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937892436981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549913406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07257270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0291314125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.08798742294312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04034233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830186367035</t>
+    <t xml:space="preserve">2.04034209251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830210208893</t>
   </si>
   <si>
     <t xml:space="preserve">2.03053259849548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01932191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970364570618</t>
+    <t xml:space="preserve">2.01932215690613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9997034072876</t>
   </si>
   <si>
     <t xml:space="preserve">2.01231551170349</t>
@@ -494,118 +494,118 @@
     <t xml:space="preserve">2.09359288215637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066621780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15945553779602</t>
+    <t xml:space="preserve">2.17066597938538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15945529937744</t>
   </si>
   <si>
     <t xml:space="preserve">1.98989403247833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88339269161224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167646884918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345962047577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01651954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250649452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97868359088898</t>
+    <t xml:space="preserve">1.88339304924011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167670726776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345938205719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01651930809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428857326508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97868323326111</t>
   </si>
   <si>
     <t xml:space="preserve">1.93944585323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91982746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377394199371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86797797679901</t>
+    <t xml:space="preserve">1.91982710361481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377418041229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8679780960083</t>
   </si>
   <si>
     <t xml:space="preserve">1.87918841838837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85676729679108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78950333595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631935596466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301144123077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89880728721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91001772880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690067768097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849284648895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224858283997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766317844391</t>
+    <t xml:space="preserve">1.85676753520966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78950321674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89880764484406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690079689026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849296569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98568987846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224894046783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766365528107</t>
   </si>
   <si>
     <t xml:space="preserve">1.96186721324921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96326839923859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97027504444122</t>
+    <t xml:space="preserve">1.96326851844788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027516365051</t>
   </si>
   <si>
     <t xml:space="preserve">1.96607136726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00390720367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18888354301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16506052017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13283014297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06416463851929</t>
+    <t xml:space="preserve">2.0039074420929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18888378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1650607585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13282990455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06416511535645</t>
   </si>
   <si>
     <t xml:space="preserve">2.09639525413513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11601376533508</t>
+    <t xml:space="preserve">2.11601424217224</t>
   </si>
   <si>
     <t xml:space="preserve">2.09499430656433</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">2.14404082298279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13002705574036</t>
+    <t xml:space="preserve">2.13002753257751</t>
   </si>
   <si>
     <t xml:space="preserve">2.14824461936951</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">2.13423156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14123821258545</t>
+    <t xml:space="preserve">2.14123797416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.1524486541748</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">2.09779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11881709098816</t>
+    <t xml:space="preserve">2.11881685256958</t>
   </si>
   <si>
     <t xml:space="preserve">2.10200071334839</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">2.11741542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24213457107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48876881599426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4873673915863</t>
+    <t xml:space="preserve">2.24213409423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48876857757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48736763000488</t>
   </si>
   <si>
     <t xml:space="preserve">2.49297285079956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48316359519958</t>
+    <t xml:space="preserve">2.48316335678101</t>
   </si>
   <si>
     <t xml:space="preserve">2.46494603157043</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">2.46634769439697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4439263343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43972229957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47615694999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45513677597046</t>
+    <t xml:space="preserve">2.44392609596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43972206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47615718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45513653755188</t>
   </si>
   <si>
     <t xml:space="preserve">2.49437403678894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47335410118103</t>
+    <t xml:space="preserve">2.47335386276245</t>
   </si>
   <si>
     <t xml:space="preserve">2.65552759170532</t>
@@ -704,100 +704,100 @@
     <t xml:space="preserve">2.71858763694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70457434654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751057624817</t>
+    <t xml:space="preserve">2.70457410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751033782959</t>
   </si>
   <si>
     <t xml:space="preserve">2.78865432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11096096038818</t>
+    <t xml:space="preserve">3.11096143722534</t>
   </si>
   <si>
     <t xml:space="preserve">3.23988389968872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129465103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003127098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5804078578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66098427772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601774215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7836012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19349193572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16896772384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11291456222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03233814239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30910062789917</t>
+    <t xml:space="preserve">3.38422107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129441261292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251489639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66098475456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601798057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78360104560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95176100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386804580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19349145889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16896820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03233766555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30910205841064</t>
   </si>
   <si>
     <t xml:space="preserve">4.30559825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69797134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50023460388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256200790405</t>
+    <t xml:space="preserve">4.55433464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69797229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50023508071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256248474121</t>
   </si>
   <si>
     <t xml:space="preserve">5.10085535049438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01677465438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44768571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44418239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77349519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39708852767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143455505371</t>
+    <t xml:space="preserve">5.01677513122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44768524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44418144226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7734956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3970890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143646240234</t>
   </si>
   <si>
     <t xml:space="preserve">6.49518251419067</t>
@@ -806,55 +806,55 @@
     <t xml:space="preserve">6.71238946914673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09369325637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858190536499</t>
+    <t xml:space="preserve">7.09369373321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858238220215</t>
   </si>
   <si>
     <t xml:space="preserve">6.78433418273926</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35626602172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5325288772583</t>
+    <t xml:space="preserve">6.35626554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53252792358398</t>
   </si>
   <si>
     <t xml:space="preserve">6.35266828536987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07208585739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32389068603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900156021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094484329224</t>
+    <t xml:space="preserve">6.0720853805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32389116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094532012939</t>
   </si>
   <si>
     <t xml:space="preserve">6.40302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15841913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37425088882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47137641906738</t>
+    <t xml:space="preserve">6.15841865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37425231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47137594223022</t>
   </si>
   <si>
     <t xml:space="preserve">6.32748794555664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1512246131897</t>
+    <t xml:space="preserve">6.15122556686401</t>
   </si>
   <si>
     <t xml:space="preserve">6.11165523529053</t>
@@ -866,25 +866,25 @@
     <t xml:space="preserve">5.96057271957397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85265684127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90661525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89582300186157</t>
+    <t xml:space="preserve">5.85265636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90661478042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89582252502441</t>
   </si>
   <si>
     <t xml:space="preserve">5.75193452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69437980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70157384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3670334815979</t>
+    <t xml:space="preserve">5.6943793296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70157432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36703395843506</t>
   </si>
   <si>
     <t xml:space="preserve">4.87421560287476</t>
@@ -893,43 +893,43 @@
     <t xml:space="preserve">5.17997884750366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97853565216064</t>
+    <t xml:space="preserve">4.97853469848633</t>
   </si>
   <si>
     <t xml:space="preserve">4.96414613723755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84543895721436</t>
+    <t xml:space="preserve">4.8454384803772</t>
   </si>
   <si>
     <t xml:space="preserve">4.87781381607056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9101881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92457723617554</t>
+    <t xml:space="preserve">4.91018772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92457628250122</t>
   </si>
   <si>
     <t xml:space="preserve">4.7698974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69075870513916</t>
+    <t xml:space="preserve">4.690758228302</t>
   </si>
   <si>
     <t xml:space="preserve">4.6583833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68716096878052</t>
+    <t xml:space="preserve">4.68716049194336</t>
   </si>
   <si>
     <t xml:space="preserve">4.82385492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55046701431274</t>
+    <t xml:space="preserve">4.5504674911499</t>
   </si>
   <si>
     <t xml:space="preserve">4.51089763641357</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">4.49291229248047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43895387649536</t>
+    <t xml:space="preserve">4.43895435333252</t>
   </si>
   <si>
     <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38499546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46413469314575</t>
+    <t xml:space="preserve">4.38499593734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46413421630859</t>
   </si>
   <si>
     <t xml:space="preserve">5.03609085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85622978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80946588516235</t>
+    <t xml:space="preserve">4.85622930526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80946636199951</t>
   </si>
   <si>
     <t xml:space="preserve">4.76629972457886</t>
@@ -965,43 +965,43 @@
     <t xml:space="preserve">4.68356418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67636966705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60442590713501</t>
+    <t xml:space="preserve">4.67637014389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60442543029785</t>
   </si>
   <si>
     <t xml:space="preserve">4.59003686904907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62960624694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66198110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67277240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74831342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75910472869873</t>
+    <t xml:space="preserve">4.62960577011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66198062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6727728843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74831390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75910520553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.95335483551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83104944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14400672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11522817611694</t>
+    <t xml:space="preserve">4.83104991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486797332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14400720596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11522960662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.19436740875244</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">4.7555079460144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99652147293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90659093856812</t>
+    <t xml:space="preserve">4.99652099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90659141540527</t>
   </si>
   <si>
     <t xml:space="preserve">4.92097997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82025814056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89220237731934</t>
+    <t xml:space="preserve">4.82025718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89220190048218</t>
   </si>
   <si>
     <t xml:space="preserve">5.05407667160034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07925701141357</t>
+    <t xml:space="preserve">5.07925605773926</t>
   </si>
   <si>
     <t xml:space="preserve">5.0181040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95695209503174</t>
+    <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.94616031646729</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">5.60804605484009</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89942026138306</t>
+    <t xml:space="preserve">5.8994197845459</t>
   </si>
   <si>
     <t xml:space="preserve">5.77711486816406</t>
@@ -1064,37 +1064,37 @@
     <t xml:space="preserve">6.03611469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94978141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18000221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20878076553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52533388137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03613805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89584684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13685894012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802474975586</t>
+    <t xml:space="preserve">5.94978094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18000268936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20878028869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52533435821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03613710403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89584636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527585983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13685941696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802379608154</t>
   </si>
   <si>
     <t xml:space="preserve">8.12968921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43904781341553</t>
+    <t xml:space="preserve">8.43904876708984</t>
   </si>
   <si>
     <t xml:space="preserve">8.95704650878906</t>
@@ -1109,52 +1109,52 @@
     <t xml:space="preserve">8.42465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61890888214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01457691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80594110488892</t>
+    <t xml:space="preserve">8.6189079284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321701049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0145788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80593919754028</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299478530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10091114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98580121994019</t>
+    <t xml:space="preserve">7.99299430847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10091209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98580026626587</t>
   </si>
   <si>
     <t xml:space="preserve">7.88507843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73399639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41024780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54694175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499704360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38866376876831</t>
+    <t xml:space="preserve">7.73399496078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41024684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54694223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4749960899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535772323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38866472244263</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760509490967</t>
@@ -1163,199 +1163,199 @@
     <t xml:space="preserve">7.84191274642944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702314376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910583496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824554443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630083084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74838638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19441509246826</t>
+    <t xml:space="preserve">7.95702266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8491063117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04335784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85629987716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74838495254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571792602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42463636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1944146156311</t>
   </si>
   <si>
     <t xml:space="preserve">6.96419382095337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21599769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498512268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2088041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20160865783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485715866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25196933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448551177979</t>
+    <t xml:space="preserve">7.21599817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498464584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880460739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20160961151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25196981430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477529525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18721914291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448360443115</t>
   </si>
   <si>
     <t xml:space="preserve">7.00735950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89944410324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91743040084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85627794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.892249584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78792953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95699977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98218011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1620397567749</t>
+    <t xml:space="preserve">6.89944314956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91742944717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85627746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89224910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78793001174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95699882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217916488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16204023361206</t>
   </si>
   <si>
     <t xml:space="preserve">7.14045667648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02174949645996</t>
+    <t xml:space="preserve">7.02174997329712</t>
   </si>
   <si>
     <t xml:space="preserve">7.33830308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82752323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25918674468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15846633911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91385650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89946842193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76996850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435707092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48219108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79152727127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7483606338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6404447555542</t>
+    <t xml:space="preserve">7.82752418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25918769836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15846729278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91385698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89946699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313514709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76996803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046764373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435659408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48219060897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79152774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64044523239136</t>
   </si>
   <si>
     <t xml:space="preserve">6.48936319351196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62605571746826</t>
+    <t xml:space="preserve">6.63325119018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605667114258</t>
   </si>
   <si>
     <t xml:space="preserve">6.56130647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60447359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791904449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19439172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02172565460205</t>
+    <t xml:space="preserve">6.60447263717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791856765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19439077377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02172517776489</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344861984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25914001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633596420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4677791595459</t>
+    <t xml:space="preserve">5.86344766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46777868270874</t>
   </si>
   <si>
     <t xml:space="preserve">6.67641639709473</t>
@@ -1367,40 +1367,40 @@
     <t xml:space="preserve">6.46058416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29511260986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10086297988892</t>
+    <t xml:space="preserve">6.29511308670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10086345672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.13683557510376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92819690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9353928565979</t>
+    <t xml:space="preserve">5.92819786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93539190292358</t>
   </si>
   <si>
     <t xml:space="preserve">5.89222526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79869937896729</t>
+    <t xml:space="preserve">5.79869890213013</t>
   </si>
   <si>
     <t xml:space="preserve">5.97136449813843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01453113555908</t>
+    <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
     <t xml:space="preserve">5.99294757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17280769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18719673156738</t>
+    <t xml:space="preserve">6.17280721664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18719720840454</t>
   </si>
   <si>
     <t xml:space="preserve">6.25194692611694</t>
@@ -1415,46 +1415,46 @@
     <t xml:space="preserve">6.27353048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30950164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30230808258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33828020095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58551740646362</t>
+    <t xml:space="preserve">6.30950260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30230760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33827924728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58551788330078</t>
   </si>
   <si>
     <t xml:space="preserve">6.38323211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46564531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326290130615</t>
+    <t xml:space="preserve">6.46564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326242446899</t>
   </si>
   <si>
     <t xml:space="preserve">6.30831146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59300899505615</t>
+    <t xml:space="preserve">6.59300994873047</t>
   </si>
   <si>
     <t xml:space="preserve">6.41319990158081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17345333099365</t>
+    <t xml:space="preserve">6.17345428466797</t>
   </si>
   <si>
     <t xml:space="preserve">6.09853410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90374040603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618391036987</t>
+    <t xml:space="preserve">5.90374088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
   </si>
   <si>
     <t xml:space="preserve">5.94120025634766</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">5.59656620025635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48418521881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60405826568604</t>
+    <t xml:space="preserve">5.48418569564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60405778884888</t>
   </si>
   <si>
     <t xml:space="preserve">5.55910539627075</t>
@@ -1484,43 +1484,43 @@
     <t xml:space="preserve">5.888756275177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80634355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64151859283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79135894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139068603516</t>
+    <t xml:space="preserve">5.8063440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64151811599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.88126373291016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92621612548828</t>
+    <t xml:space="preserve">5.92621660232544</t>
   </si>
   <si>
     <t xml:space="preserve">6.33078718185425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55554866790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815229415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33827924728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30081987380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.128502368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06107378005981</t>
+    <t xml:space="preserve">6.55554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815277099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33827877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30081844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12850189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0610728263855</t>
   </si>
   <si>
     <t xml:space="preserve">5.77637529373169</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">5.76888275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70145416259766</t>
+    <t xml:space="preserve">5.70145511627197</t>
   </si>
   <si>
     <t xml:space="preserve">5.66399431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57409000396729</t>
+    <t xml:space="preserve">5.57408952713013</t>
   </si>
   <si>
     <t xml:space="preserve">5.75389909744263</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62653398513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61904191970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65650224685669</t>
+    <t xml:space="preserve">5.6265344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61904239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.54412174224854</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">5.58158206939697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50666093826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53662872314453</t>
+    <t xml:space="preserve">5.5066614151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53662919998169</t>
   </si>
   <si>
     <t xml:space="preserve">5.43174076080322</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">5.31935977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189897537231</t>
+    <t xml:space="preserve">5.28189945220947</t>
   </si>
   <si>
     <t xml:space="preserve">5.42424869537354</t>
@@ -1586,37 +1586,37 @@
     <t xml:space="preserve">5.49167680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51415348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36431264877319</t>
+    <t xml:space="preserve">5.5141544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36431217193604</t>
   </si>
   <si>
     <t xml:space="preserve">5.27440738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18450307846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2069787979126</t>
+    <t xml:space="preserve">5.18450260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20697927474976</t>
   </si>
   <si>
     <t xml:space="preserve">5.58907413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74640655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47669315338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21447086334229</t>
+    <t xml:space="preserve">5.74640703201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47669363021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21447038650513</t>
   </si>
   <si>
     <t xml:space="preserve">5.13955020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09459829330444</t>
+    <t xml:space="preserve">5.09459781646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.10958194732666</t>
@@ -1625,31 +1625,31 @@
     <t xml:space="preserve">5.07212162017822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05713796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01967763900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466176986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732839584351</t>
+    <t xml:space="preserve">5.05713701248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732887268066</t>
   </si>
   <si>
     <t xml:space="preserve">4.86983633041382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7349796295166</t>
+    <t xml:space="preserve">4.73498010635376</t>
   </si>
   <si>
     <t xml:space="preserve">4.77243947982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82488489151001</t>
+    <t xml:space="preserve">4.82488393783569</t>
   </si>
   <si>
     <t xml:space="preserve">4.88482046127319</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8548526763916</t>
+    <t xml:space="preserve">4.85485219955444</t>
   </si>
   <si>
     <t xml:space="preserve">4.95224905014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16951894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0871057510376</t>
+    <t xml:space="preserve">5.16951847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08710622787476</t>
   </si>
   <si>
     <t xml:space="preserve">5.13205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21840667724609</t>
+    <t xml:space="preserve">6.21840620040894</t>
   </si>
   <si>
     <t xml:space="preserve">6.25586748123169</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">6.01612091064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10602569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99364471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04215335845947</t>
+    <t xml:space="preserve">6.10602474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99364423751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04215383529663</t>
   </si>
   <si>
     <t xml:space="preserve">4.98221731185913</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">5.02716970443726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89231300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964590072632</t>
+    <t xml:space="preserve">4.89231252670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964542388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95974111557007</t>
@@ -1724,19 +1724,19 @@
     <t xml:space="preserve">4.81739187240601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79491567611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78742408752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83237552642822</t>
+    <t xml:space="preserve">4.7949161529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78742361068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83237600326538</t>
   </si>
   <si>
     <t xml:space="preserve">4.97472524642944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90729665756226</t>
+    <t xml:space="preserve">4.90729713439941</t>
   </si>
   <si>
     <t xml:space="preserve">4.76494789123535</t>
@@ -1745,49 +1745,49 @@
     <t xml:space="preserve">4.47275733947754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27047204971313</t>
+    <t xml:space="preserve">4.27047252655029</t>
   </si>
   <si>
     <t xml:space="preserve">4.38285303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32291603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30043983459473</t>
+    <t xml:space="preserve">4.32291650772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30044078826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.31542444229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46526527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777273178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7125039100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10209035873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07961416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218557357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443960189819</t>
+    <t xml:space="preserve">4.46526575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777368545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71250295639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10208988189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07961463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726491928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443912506104</t>
   </si>
   <si>
     <t xml:space="preserve">5.22196292877197</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">5.19948720932007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11707401275635</t>
+    <t xml:space="preserve">5.11707448959351</t>
   </si>
   <si>
     <t xml:space="preserve">5.28939151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16202688217163</t>
+    <t xml:space="preserve">5.16202640533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.31186771392822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41675615310669</t>
+    <t xml:space="preserve">5.41675662994385</t>
   </si>
   <si>
     <t xml:space="preserve">5.37180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44672441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39427995681763</t>
+    <t xml:space="preserve">5.4467248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39428043365479</t>
   </si>
   <si>
     <t xml:space="preserve">5.45421695709229</t>
@@ -1829,40 +1829,40 @@
     <t xml:space="preserve">5.40926456451416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89624738693237</t>
+    <t xml:space="preserve">5.89624786376953</t>
   </si>
   <si>
     <t xml:space="preserve">5.85878801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12100982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589921951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.001136302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885149002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82132816314697</t>
+    <t xml:space="preserve">6.12101030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00113725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82132720947266</t>
   </si>
   <si>
     <t xml:space="preserve">5.91123199462891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03110551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.008629322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872453689575</t>
+    <t xml:space="preserve">6.03110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00862979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872406005859</t>
   </si>
   <si>
     <t xml:space="preserve">5.83631134033203</t>
@@ -1871,40 +1871,40 @@
     <t xml:space="preserve">5.87377214431763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97116804122925</t>
+    <t xml:space="preserve">5.97116899490356</t>
   </si>
   <si>
     <t xml:space="preserve">6.21091413497925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09104156494141</t>
+    <t xml:space="preserve">6.09104204177856</t>
   </si>
   <si>
     <t xml:space="preserve">6.15097856521606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14348602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361345291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866010665894</t>
+    <t xml:space="preserve">6.1434850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608869552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859758377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866106033325</t>
   </si>
   <si>
     <t xml:space="preserve">5.69396257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72393035888672</t>
+    <t xml:space="preserve">5.72393083572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.70894718170166</t>
@@ -1916,16 +1916,16 @@
     <t xml:space="preserve">5.46170902252197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73891448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161285400391</t>
+    <t xml:space="preserve">5.73891496658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161380767822</t>
   </si>
   <si>
     <t xml:space="preserve">5.47268533706665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30019474029541</t>
+    <t xml:space="preserve">5.30019426345825</t>
   </si>
   <si>
     <t xml:space="preserve">5.33155584335327</t>
@@ -1934,28 +1934,25 @@
     <t xml:space="preserve">5.46484470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35507726669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30803489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39428043365479</t>
+    <t xml:space="preserve">5.35507774353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30803442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859916687012</t>
   </si>
   <si>
     <t xml:space="preserve">5.24531078338623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26883125305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315093994141</t>
+    <t xml:space="preserve">5.26883172988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315046310425</t>
   </si>
   <si>
     <t xml:space="preserve">5.14338350296021</t>
@@ -1964,7 +1961,7 @@
     <t xml:space="preserve">5.06497859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00225448608398</t>
+    <t xml:space="preserve">5.00225400924683</t>
   </si>
   <si>
     <t xml:space="preserve">5.16690492630005</t>
@@ -1976,10 +1973,10 @@
     <t xml:space="preserve">5.33939647674561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11986255645752</t>
+    <t xml:space="preserve">5.2923526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11986207962036</t>
   </si>
   <si>
     <t xml:space="preserve">5.13554334640503</t>
@@ -1988,7 +1985,10 @@
     <t xml:space="preserve">5.09634017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11202096939087</t>
+    <t xml:space="preserve">5.05713748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11202144622803</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474555969238</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733625411987</t>
+    <t xml:space="preserve">5.63733673095703</t>
   </si>
   <si>
     <t xml:space="preserve">5.55893135070801</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">5.48052644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36291837692261</t>
+    <t xml:space="preserve">5.36291885375977</t>
   </si>
   <si>
     <t xml:space="preserve">5.31587553024292</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">4.79840040206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70431470870972</t>
+    <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
     <t xml:space="preserve">4.71999549865723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51614141464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97089147567749</t>
+    <t xml:space="preserve">4.51614189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97089195251465</t>
   </si>
   <si>
     <t xml:space="preserve">4.82192182540894</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">4.71215486526489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67295217514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63374948501587</t>
+    <t xml:space="preserve">4.67295265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63374996185303</t>
   </si>
   <si>
     <t xml:space="preserve">4.64943075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59454679489136</t>
+    <t xml:space="preserve">4.59454727172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.62590885162354</t>
@@ -2084,25 +2084,25 @@
     <t xml:space="preserve">5.22962951660156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04145622253418</t>
+    <t xml:space="preserve">5.02577590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04145669937134</t>
   </si>
   <si>
     <t xml:space="preserve">5.15122413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22178888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21394872665405</t>
+    <t xml:space="preserve">5.22178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21394824981689</t>
   </si>
   <si>
     <t xml:space="preserve">5.15906476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08065891265869</t>
+    <t xml:space="preserve">5.08065938949585</t>
   </si>
   <si>
     <t xml:space="preserve">5.12770223617554</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">5.01793527603149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07281875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08849954605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19042730331421</t>
+    <t xml:space="preserve">5.07281923294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08849906921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19042682647705</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
@@ -2132,37 +2132,37 @@
     <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56677150726318</t>
+    <t xml:space="preserve">5.56677198410034</t>
   </si>
   <si>
     <t xml:space="preserve">5.43348264694214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50404787063599</t>
+    <t xml:space="preserve">5.50404739379883</t>
   </si>
   <si>
     <t xml:space="preserve">5.53540992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41780185699463</t>
+    <t xml:space="preserve">5.41780138015747</t>
   </si>
   <si>
     <t xml:space="preserve">5.42564249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84118938446045</t>
+    <t xml:space="preserve">5.84119033813477</t>
   </si>
   <si>
     <t xml:space="preserve">5.76278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64517688751221</t>
+    <t xml:space="preserve">5.64517736434937</t>
   </si>
   <si>
     <t xml:space="preserve">5.44132375717163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40996170043945</t>
+    <t xml:space="preserve">5.40996122360229</t>
   </si>
   <si>
     <t xml:space="preserve">5.38643980026245</t>
@@ -2186,22 +2186,22 @@
     <t xml:space="preserve">4.89248657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86896514892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92384958267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87680530548096</t>
+    <t xml:space="preserve">4.86896562576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92384910583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87680578231812</t>
   </si>
   <si>
     <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54750394821167</t>
+    <t xml:space="preserve">4.57102489471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54750442504883</t>
   </si>
   <si>
     <t xml:space="preserve">4.57886600494385</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">4.39069318771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15547800064087</t>
+    <t xml:space="preserve">4.15547752380371</t>
   </si>
   <si>
     <t xml:space="preserve">4.2260422706604</t>
@@ -2219,19 +2219,19 @@
     <t xml:space="preserve">4.11627435684204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84185695648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63800287246704</t>
+    <t xml:space="preserve">3.84185671806335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63800311088562</t>
   </si>
   <si>
     <t xml:space="preserve">3.26165771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29301977157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32438182830811</t>
+    <t xml:space="preserve">3.29302000999451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32438158988953</t>
   </si>
   <si>
     <t xml:space="preserve">2.90099382400513</t>
@@ -2240,46 +2240,46 @@
     <t xml:space="preserve">3.09700679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05780434608459</t>
+    <t xml:space="preserve">3.05780458450317</t>
   </si>
   <si>
     <t xml:space="preserve">2.94803690910339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00292038917542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13620948791504</t>
+    <t xml:space="preserve">3.00292062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13620924949646</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036260604858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21461486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25381755828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2224555015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24205660820007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24597668647766</t>
+    <t xml:space="preserve">3.2146143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25381708145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22245526313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24205684661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24597692489624</t>
   </si>
   <si>
     <t xml:space="preserve">3.23813629150391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36750531196594</t>
+    <t xml:space="preserve">3.36750483512878</t>
   </si>
   <si>
     <t xml:space="preserve">3.34006333351135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45767068862915</t>
+    <t xml:space="preserve">3.45767092704773</t>
   </si>
   <si>
     <t xml:space="preserve">3.59880042076111</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">3.37142562866211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52039504051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54391670227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7242488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8104944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9202618598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3358097076416</t>
+    <t xml:space="preserve">3.52039480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54391694068909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72424912452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81049418449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92026209831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33580923080444</t>
   </si>
   <si>
     <t xml:space="preserve">4.32796907424927</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">4.23388290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1633186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07707214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21820211410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036052703857</t>
+    <t xml:space="preserve">4.16331768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07707166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21820163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036148071289</t>
   </si>
   <si>
     <t xml:space="preserve">4.25740432739258</t>
@@ -2333,70 +2333,70 @@
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208951950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401560783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84577751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009600639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145853996277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169014930725</t>
+    <t xml:space="preserve">3.73208928108215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481387138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401608467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577679634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70072722434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009552955627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265402793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225584983826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145830154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169038772583</t>
   </si>
   <si>
     <t xml:space="preserve">3.74385046958923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98298597335815</t>
+    <t xml:space="preserve">3.98298573493958</t>
   </si>
   <si>
     <t xml:space="preserve">4.29660701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10059404373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91634130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946526527405</t>
+    <t xml:space="preserve">4.10059356689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91634106636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946455001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13979625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14763736724854</t>
+    <t xml:space="preserve">4.13979721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14763689041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.01434803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95162391662598</t>
+    <t xml:space="preserve">3.9516236782074</t>
   </si>
   <si>
     <t xml:space="preserve">3.9437837600708</t>
@@ -2405,31 +2405,31 @@
     <t xml:space="preserve">3.8889000415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05355072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03002882003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89282011985779</t>
+    <t xml:space="preserve">4.053551197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923151016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89281988143921</t>
   </si>
   <si>
     <t xml:space="preserve">3.92810273170471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91242122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85753798484802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8653781414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617545127869</t>
+    <t xml:space="preserve">3.91242074966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753774642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86537766456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617568969727</t>
   </si>
   <si>
     <t xml:space="preserve">3.88105869293213</t>
@@ -2438,73 +2438,73 @@
     <t xml:space="preserve">3.90458106994629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90850162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913308143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75560998916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777007102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657410621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497877120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96730494499207</t>
+    <t xml:space="preserve">3.90850138664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.755610704422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497948646545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96730470657349</t>
   </si>
   <si>
     <t xml:space="preserve">4.02218866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75953102111816</t>
+    <t xml:space="preserve">3.93594312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345181465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75953078269958</t>
   </si>
   <si>
     <t xml:space="preserve">3.64584350585938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66936540603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544485092163</t>
+    <t xml:space="preserve">3.66936492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544508934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.63016247749329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56351780891418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56743836402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59095978736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119282722473</t>
+    <t xml:space="preserve">3.56351828575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56743860244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59096002578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903298377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119258880615</t>
   </si>
   <si>
     <t xml:space="preserve">3.44198966026306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38710641860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654191017151</t>
+    <t xml:space="preserve">3.38710689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654119491577</t>
   </si>
   <si>
     <t xml:space="preserve">3.33222270011902</t>
@@ -2519,40 +2519,40 @@
     <t xml:space="preserve">3.43807005882263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46551132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49295353889465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55175733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55567789077759</t>
+    <t xml:space="preserve">3.46551203727722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49295377731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55175757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55567717552185</t>
   </si>
   <si>
     <t xml:space="preserve">3.50079393386841</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51255440711975</t>
+    <t xml:space="preserve">3.51255488395691</t>
   </si>
   <si>
     <t xml:space="preserve">3.37926602363586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43414950370789</t>
+    <t xml:space="preserve">3.43414926528931</t>
   </si>
   <si>
     <t xml:space="preserve">3.42630887031555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4615912437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4498302936554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189051628113</t>
+    <t xml:space="preserve">3.46159100532532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44983077049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189027786255</t>
   </si>
   <si>
     <t xml:space="preserve">3.20677423477173</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">3.52823567390442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53215622901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607630729675</t>
+    <t xml:space="preserve">3.53215646743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607678413391</t>
   </si>
   <si>
     <t xml:space="preserve">4.10843420028687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99866700172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252084732056</t>
+    <t xml:space="preserve">3.99866676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2025203704834</t>
   </si>
   <si>
     <t xml:space="preserve">4.13195562362671</t>
@@ -2585,67 +2585,67 @@
     <t xml:space="preserve">4.09275341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28876638412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2495641708374</t>
+    <t xml:space="preserve">4.06139135360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2887659072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24956369400024</t>
   </si>
   <si>
     <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39853382110596</t>
+    <t xml:space="preserve">4.39853429794312</t>
   </si>
   <si>
     <t xml:space="preserve">4.35933113098145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69647359848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976341247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7278356552124</t>
+    <t xml:space="preserve">4.69647312164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7591986656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976245880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72783613204956</t>
   </si>
   <si>
     <t xml:space="preserve">4.74351692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703882217407</t>
+    <t xml:space="preserve">4.76703834533691</t>
   </si>
   <si>
     <t xml:space="preserve">4.77487945556641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73567628860474</t>
+    <t xml:space="preserve">4.73567676544189</t>
   </si>
   <si>
     <t xml:space="preserve">4.68863344192505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80624055862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01009511947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99441385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9473705291748</t>
+    <t xml:space="preserve">4.80624103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01009464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99441337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94737005233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.86112451553345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84544324874878</t>
+    <t xml:space="preserve">4.84544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">4.91600847244263</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">4.93953037261963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04929685592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245229721069</t>
+    <t xml:space="preserve">5.04929733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245277404785</t>
   </si>
   <si>
     <t xml:space="preserve">5.68438005447388</t>
@@ -2666,25 +2666,25 @@
     <t xml:space="preserve">5.59813404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62949657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7157416343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69222068786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66869926452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66085863113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72358226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78630638122559</t>
+    <t xml:space="preserve">5.6294960975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71574211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69222021102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66869878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66085815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72358274459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78630685806274</t>
   </si>
   <si>
     <t xml:space="preserve">6.08424663543701</t>
@@ -2693,16 +2693,16 @@
     <t xml:space="preserve">6.1783332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14697122573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288457870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97447919845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720235824585</t>
+    <t xml:space="preserve">6.14697074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97447967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">6.00474500656128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11834812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49161624908447</t>
+    <t xml:space="preserve">6.11834859848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49161577224731</t>
   </si>
   <si>
     <t xml:space="preserve">6.45915842056274</t>
@@ -2723,10 +2723,10 @@
     <t xml:space="preserve">6.42670011520386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26440906524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41047143936157</t>
+    <t xml:space="preserve">6.26440954208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41047096252441</t>
   </si>
   <si>
     <t xml:space="preserve">6.39424228668213</t>
@@ -2735,28 +2735,28 @@
     <t xml:space="preserve">6.4429292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96225786209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43290042877197</t>
+    <t xml:space="preserve">6.96225833892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43290090560913</t>
   </si>
   <si>
     <t xml:space="preserve">8.00091648101807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83862733840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87108421325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78993988037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977119445801</t>
+    <t xml:space="preserve">7.83862686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87108469009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78994035720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">7.95222997665405</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">8.60139179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64196395874023</t>
+    <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.56081867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43910121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19566535949707</t>
+    <t xml:space="preserve">8.43910026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19566631317139</t>
   </si>
   <si>
     <t xml:space="preserve">8.23623752593994</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">8.01714611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06583309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96845865249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40044212341309</t>
+    <t xml:space="preserve">8.06583213806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96845960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40044260025024</t>
   </si>
   <si>
     <t xml:space="preserve">7.25438117980957</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">7.64387798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56273174285889</t>
+    <t xml:space="preserve">7.5627326965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.69256448745728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72502279281616</t>
+    <t xml:space="preserve">7.72502326965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">7.62764835357666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46535873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192239761353</t>
+    <t xml:space="preserve">7.4653582572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3030686378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192287445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.81619691848755</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">7.61142015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66010665893555</t>
+    <t xml:space="preserve">7.66010713577271</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74125194549561</t>
+    <t xml:space="preserve">7.74125289916992</t>
   </si>
   <si>
     <t xml:space="preserve">8.35795593261719</t>
@@ -2861,25 +2861,25 @@
     <t xml:space="preserve">8.1550931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96654605865479</t>
+    <t xml:space="preserve">8.96654510498047</t>
   </si>
   <si>
     <t xml:space="preserve">8.84482765197754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76368141174316</t>
+    <t xml:space="preserve">8.76368236541748</t>
   </si>
   <si>
     <t xml:space="preserve">8.52024555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39852809906006</t>
+    <t xml:space="preserve">8.39852905273438</t>
   </si>
   <si>
     <t xml:space="preserve">8.47967338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31738376617432</t>
+    <t xml:space="preserve">8.3173828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.08206272125244</t>
@@ -2894,13 +2894,13 @@
     <t xml:space="preserve">8.04960441589355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04768943786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41284370422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16940784454346</t>
+    <t xml:space="preserve">9.04769039154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41284465789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16940975189209</t>
   </si>
   <si>
     <t xml:space="preserve">9.4452428817749</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">9.48703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77958679199219</t>
+    <t xml:space="preserve">9.7795877456665</t>
   </si>
   <si>
     <t xml:space="preserve">9.6124153137207</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">9.57062149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52882766723633</t>
+    <t xml:space="preserve">9.52882862091064</t>
   </si>
   <si>
     <t xml:space="preserve">9.69600105285645</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">9.73779392242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65420913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90496730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31986331939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2780704498291</t>
+    <t xml:space="preserve">9.65420818328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90496635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31986236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27807140350342</t>
   </si>
   <si>
     <t xml:space="preserve">9.02731132507324</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">9.36165618896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06910514831543</t>
+    <t xml:space="preserve">9.06910419464111</t>
   </si>
   <si>
     <t xml:space="preserve">8.94372463226318</t>
@@ -2984,22 +2984,22 @@
     <t xml:space="preserve">8.90193176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81834602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758785247803</t>
+    <t xml:space="preserve">8.81834506988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758689880371</t>
   </si>
   <si>
     <t xml:space="preserve">8.52579402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73476028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20816707611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30846881866455</t>
+    <t xml:space="preserve">8.73475933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20816612243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30846977233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.32518672943115</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">7.82366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67321443557739</t>
+    <t xml:space="preserve">7.67321395874023</t>
   </si>
   <si>
     <t xml:space="preserve">7.12154626846313</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">7.10482835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68993186950684</t>
+    <t xml:space="preserve">7.68993234634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.45589017868042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89053821563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80695247650146</t>
+    <t xml:space="preserve">7.89053773880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80695295333862</t>
   </si>
   <si>
     <t xml:space="preserve">7.62306261062622</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">7.99084281921387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09114551544189</t>
+    <t xml:space="preserve">8.09114646911621</t>
   </si>
   <si>
     <t xml:space="preserve">8.04099369049072</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">8.10786247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48400115966797</t>
+    <t xml:space="preserve">8.48400020599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.30011177062988</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87382173538208</t>
+    <t xml:space="preserve">7.87382125854492</t>
   </si>
   <si>
     <t xml:space="preserve">7.69829082489014</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">7.81531095504761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77351760864258</t>
+    <t xml:space="preserve">7.77351808547974</t>
   </si>
   <si>
     <t xml:space="preserve">7.91561508178711</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">7.79859447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79023408889771</t>
+    <t xml:space="preserve">7.79023456573486</t>
   </si>
   <si>
     <t xml:space="preserve">7.83202838897705</t>
@@ -27036,7 +27036,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G861" t="s">
-        <v>643</v>
+        <v>602</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27062,7 +27062,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G862" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27088,7 +27088,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G863" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27114,7 +27114,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G864" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27140,7 +27140,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G865" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27166,7 +27166,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G866" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27192,7 +27192,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G867" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27218,7 +27218,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27244,7 +27244,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G869" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27270,7 +27270,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G870" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27296,7 +27296,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G871" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27322,7 +27322,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G872" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27348,7 +27348,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27400,7 +27400,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G875" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27426,7 +27426,7 @@
         <v>6.75</v>
       </c>
       <c r="G876" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27452,7 +27452,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G877" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27478,7 +27478,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G878" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27504,7 +27504,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G879" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27530,7 +27530,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G880" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27556,7 +27556,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G881" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27582,7 +27582,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G882" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27608,7 +27608,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G883" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27634,7 +27634,7 @@
         <v>6.5</v>
       </c>
       <c r="G884" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27660,7 +27660,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G885" t="s">
-        <v>537</v>
+        <v>657</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27712,7 +27712,7 @@
         <v>6.5</v>
       </c>
       <c r="G887" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28128,7 +28128,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G903" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28206,7 +28206,7 @@
         <v>6.75</v>
       </c>
       <c r="G906" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28310,7 +28310,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28388,7 +28388,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G913" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28414,7 +28414,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G914" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29142,7 +29142,7 @@
         <v>6.75</v>
       </c>
       <c r="G942" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29194,7 +29194,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G944" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29376,7 +29376,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G951" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -29402,7 +29402,7 @@
         <v>6.5</v>
       </c>
       <c r="G952" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -29610,7 +29610,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G960" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29688,7 +29688,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G963" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -29740,7 +29740,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G965" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30780,7 +30780,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1005" t="s">
-        <v>643</v>
+        <v>602</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30936,7 +30936,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1011" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30962,7 +30962,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31144,7 +31144,7 @@
         <v>6.75</v>
       </c>
       <c r="G1019" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31170,7 +31170,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31196,7 +31196,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1021" t="s">
-        <v>643</v>
+        <v>602</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31300,7 +31300,7 @@
         <v>6.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31326,7 +31326,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1026" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31352,7 +31352,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1027" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31378,7 +31378,7 @@
         <v>6.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31456,7 +31456,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1031" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31482,7 +31482,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1032" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31560,7 +31560,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1035" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31872,7 +31872,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31976,7 +31976,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1051" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -38424,7 +38424,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1299" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38450,7 +38450,7 @@
         <v>6.5</v>
       </c>
       <c r="G1300" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38476,7 +38476,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1301" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38502,7 +38502,7 @@
         <v>6.5</v>
       </c>
       <c r="G1302" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38970,7 +38970,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1320" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38996,7 +38996,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1321" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -71062,7 +71062,7 @@
     </row>
     <row r="2555">
       <c r="A2555" s="1" t="n">
-        <v>46043.6910648148</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B2555" t="n">
         <v>9234</v>
@@ -71083,6 +71083,32 @@
         <v>1394</v>
       </c>
       <c r="H2555" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" s="1" t="n">
+        <v>46044.6911458333</v>
+      </c>
+      <c r="B2556" t="n">
+        <v>5224</v>
+      </c>
+      <c r="C2556" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="D2556" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="E2556" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F2556" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G2556" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H2556" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19253504276276</t>
+    <t xml:space="preserve">1.19253516197205</t>
   </si>
   <si>
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355497837067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546648979187</t>
+    <t xml:space="preserve">1.21355509757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546637058258</t>
   </si>
   <si>
     <t xml:space="preserve">1.20654857158661</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">1.23177230358124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24998986721039</t>
+    <t xml:space="preserve">1.2499897480011</t>
   </si>
   <si>
     <t xml:space="preserve">1.26330256462097</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">1.26120042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24718713760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2079496383667</t>
+    <t xml:space="preserve">1.24718725681305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20794975757599</t>
   </si>
   <si>
     <t xml:space="preserve">1.19323575496674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814038276672</t>
+    <t xml:space="preserve">1.17501866817474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19814050197601</t>
   </si>
   <si>
     <t xml:space="preserve">1.24578583240509</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495628356934</t>
+    <t xml:space="preserve">1.21495640277863</t>
   </si>
   <si>
     <t xml:space="preserve">1.18272578716278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17992305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641961574554</t>
+    <t xml:space="preserve">1.17992317676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641985416412</t>
   </si>
   <si>
     <t xml:space="preserve">1.12457036972046</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">1.10284972190857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08603358268738</t>
+    <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
     <t xml:space="preserve">1.01596701145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02017116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195372104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297365665436</t>
+    <t xml:space="preserve">1.02507567405701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02017092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195384025574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297389507294</t>
   </si>
   <si>
     <t xml:space="preserve">1.04329311847687</t>
@@ -137,31 +137,31 @@
     <t xml:space="preserve">1.11335968971252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11055707931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09304022789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106716632843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017582893372</t>
+    <t xml:space="preserve">1.11055719852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0930403470993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106728553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017570972443</t>
   </si>
   <si>
     <t xml:space="preserve">1.15610039234161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10004723072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13157689571381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705387592316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227772712708</t>
+    <t xml:space="preserve">1.10004711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1315770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705351829529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227784633636</t>
   </si>
   <si>
     <t xml:space="preserve">1.11826431751251</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">1.14909386634827</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17852175235748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17011380195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412697315216</t>
+    <t xml:space="preserve">1.17852187156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1701135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412733078003</t>
   </si>
   <si>
     <t xml:space="preserve">1.17081439495087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16310703754425</t>
+    <t xml:space="preserve">1.16310715675354</t>
   </si>
   <si>
     <t xml:space="preserve">1.22616708278656</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">1.19113373756409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22686767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22196316719055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24438464641571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17221581935883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183444976807</t>
+    <t xml:space="preserve">1.22686779499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22196304798126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24438452720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17221558094025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183433055878</t>
   </si>
   <si>
     <t xml:space="preserve">1.19743978977203</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">1.20374584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.203045129776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2380782365799</t>
+    <t xml:space="preserve">1.20304524898529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23807847499847</t>
   </si>
   <si>
     <t xml:space="preserve">1.2331737279892</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">1.22476589679718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845972537994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916031837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21215379238129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22266376018524</t>
+    <t xml:space="preserve">1.21845984458923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916055679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2289696931839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.212153673172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22266387939453</t>
   </si>
   <si>
     <t xml:space="preserve">1.2920298576355</t>
@@ -260,70 +260,70 @@
     <t xml:space="preserve">1.27521371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28712522983551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28151965141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788773059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737764358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469908714294</t>
+    <t xml:space="preserve">1.28712511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28151977062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788784980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737776279449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865046977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469920635223</t>
   </si>
   <si>
     <t xml:space="preserve">1.14138650894165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11896502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036657333374</t>
+    <t xml:space="preserve">1.11896514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
     <t xml:space="preserve">1.13648152351379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14629113674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14208710193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07202041149139</t>
+    <t xml:space="preserve">1.14629101753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14208698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0720202922821</t>
   </si>
   <si>
     <t xml:space="preserve">1.08463227748871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.06501376628876</t>
+    <t xml:space="preserve">1.06501364707947</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253049850464</t>
+    <t xml:space="preserve">1.08253037929535</t>
   </si>
   <si>
     <t xml:space="preserve">1.07902705669403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05800700187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1014484167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09514224529266</t>
+    <t xml:space="preserve">1.05800712108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10144829750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355031490326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09514236450195</t>
   </si>
   <si>
     <t xml:space="preserve">1.11966586112976</t>
@@ -335,88 +335,88 @@
     <t xml:space="preserve">1.11265897750854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15680110454559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528064727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681509494781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48821663856506</t>
+    <t xml:space="preserve">1.1568009853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528052806854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4868152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48821651935577</t>
   </si>
   <si>
     <t xml:space="preserve">1.45178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41534698009491</t>
+    <t xml:space="preserve">1.41534721851349</t>
   </si>
   <si>
     <t xml:space="preserve">1.45738708972931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40133380889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4699991941452</t>
+    <t xml:space="preserve">1.40133392810822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46999943256378</t>
   </si>
   <si>
     <t xml:space="preserve">1.43776845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42375516891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43636703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936050891876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42235398292542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814970970154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114330291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42795932292938</t>
+    <t xml:space="preserve">1.42375528812408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4363671541214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936062812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674840450287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42235362529755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814982891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114294528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4279590845108</t>
   </si>
   <si>
     <t xml:space="preserve">1.48120987415314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69421243667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338312625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071377754211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84555637836456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79230606555939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090464115143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268731594086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064732551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71663403511047</t>
+    <t xml:space="preserve">1.69421255588531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80071413516998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84555649757385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79230570793152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090476036072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064756393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71663379669189</t>
   </si>
   <si>
     <t xml:space="preserve">1.78670048713684</t>
@@ -425,43 +425,43 @@
     <t xml:space="preserve">1.8427540063858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82593810558319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313525676727</t>
+    <t xml:space="preserve">1.82593774795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313513755798</t>
   </si>
   <si>
     <t xml:space="preserve">1.83995127677917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83854985237122</t>
+    <t xml:space="preserve">1.83855009078979</t>
   </si>
   <si>
     <t xml:space="preserve">1.84415531158447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83014178276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472706794739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874071598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192469596863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294463157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937928199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99549901485443</t>
+    <t xml:space="preserve">1.83014214038849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472718715668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192457675934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294451236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835946559906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8693790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549913406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.0725724697113</t>
@@ -473,109 +473,109 @@
     <t xml:space="preserve">2.08798766136169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04034233093262</t>
+    <t xml:space="preserve">2.04034185409546</t>
   </si>
   <si>
     <t xml:space="preserve">1.99830210208893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03053259849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01932191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970328807831</t>
+    <t xml:space="preserve">2.03053283691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01932168006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9997034072876</t>
   </si>
   <si>
     <t xml:space="preserve">2.01231527328491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09359288215637</t>
+    <t xml:space="preserve">2.09359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066597938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15945529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989403247833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339269161224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167658805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345962047577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01651978492737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00250625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428893089294</t>
+    <t xml:space="preserve">2.15945553779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989391326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339257240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167670726776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345914363861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01651954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00250601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428869247437</t>
   </si>
   <si>
     <t xml:space="preserve">1.97868323326111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93944621086121</t>
+    <t xml:space="preserve">1.93944585323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.91982710361481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377394199371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8679780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918889522552</t>
+    <t xml:space="preserve">1.86377418041229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86797773838043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918829917908</t>
   </si>
   <si>
     <t xml:space="preserve">1.85676729679108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78950357437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631947517395</t>
+    <t xml:space="preserve">1.78950321674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631935596466</t>
   </si>
   <si>
     <t xml:space="preserve">1.90301132202148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89880740642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9100182056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690067768097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849260807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9856903553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766317844391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186721324921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326887607574</t>
+    <t xml:space="preserve">1.89880752563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001784801483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849272727966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98569011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224870204926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766341686249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186745166779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326875686646</t>
   </si>
   <si>
     <t xml:space="preserve">1.97027540206909</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">1.96607136726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0039074420929</t>
+    <t xml:space="preserve">2.00390768051147</t>
   </si>
   <si>
     <t xml:space="preserve">2.07397413253784</t>
@@ -593,31 +593,31 @@
     <t xml:space="preserve">2.18888354301453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16506099700928</t>
+    <t xml:space="preserve">2.1650607585907</t>
   </si>
   <si>
     <t xml:space="preserve">2.13282990455627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06416487693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09639573097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601400375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499382972717</t>
+    <t xml:space="preserve">2.06416511535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09639525413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601424217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499406814575</t>
   </si>
   <si>
     <t xml:space="preserve">2.11321139335632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14404082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002753257751</t>
+    <t xml:space="preserve">2.14404058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002729415894</t>
   </si>
   <si>
     <t xml:space="preserve">2.14824461936951</t>
@@ -629,37 +629,37 @@
     <t xml:space="preserve">2.14123797416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13703417778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11180996894836</t>
+    <t xml:space="preserve">2.15244913101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13703346252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11181020736694</t>
   </si>
   <si>
     <t xml:space="preserve">2.09779691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11881685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10200047492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1174156665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24213433265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48876929283142</t>
+    <t xml:space="preserve">2.118816614151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10200071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11741542816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213457107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48876905441284</t>
   </si>
   <si>
     <t xml:space="preserve">2.48736763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297308921814</t>
+    <t xml:space="preserve">2.49297332763672</t>
   </si>
   <si>
     <t xml:space="preserve">2.48316359519958</t>
@@ -668,163 +668,163 @@
     <t xml:space="preserve">2.46494603157043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40328764915466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099967002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48036074638367</t>
+    <t xml:space="preserve">2.40328741073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52099943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48036098480225</t>
   </si>
   <si>
     <t xml:space="preserve">2.46634745597839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4439263343811</t>
+    <t xml:space="preserve">2.44392609596252</t>
   </si>
   <si>
     <t xml:space="preserve">2.43972229957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47615647315979</t>
+    <t xml:space="preserve">2.47615694999695</t>
   </si>
   <si>
     <t xml:space="preserve">2.45513677597046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49437427520752</t>
+    <t xml:space="preserve">2.4943745136261</t>
   </si>
   <si>
     <t xml:space="preserve">2.47335410118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65552735328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71858787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70457434654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751033782959</t>
+    <t xml:space="preserve">2.6555278301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71858739852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70457410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751057624817</t>
   </si>
   <si>
     <t xml:space="preserve">2.788654088974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11096119880676</t>
+    <t xml:space="preserve">3.11096096038818</t>
   </si>
   <si>
     <t xml:space="preserve">3.23988389968872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129465103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003103256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040833473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251465797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66098380088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601774215698</t>
+    <t xml:space="preserve">3.38422155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129512786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66098499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601821899414</t>
   </si>
   <si>
     <t xml:space="preserve">3.78360104560852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95176124572754</t>
+    <t xml:space="preserve">3.95176148414612</t>
   </si>
   <si>
     <t xml:space="preserve">4.06386804580688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19349193572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16896820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11291456222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03233861923218</t>
+    <t xml:space="preserve">4.19349241256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16896772384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03233814239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.30910158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30559825897217</t>
+    <t xml:space="preserve">4.30559873580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.55433464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6979718208313</t>
+    <t xml:space="preserve">4.69797134399414</t>
   </si>
   <si>
     <t xml:space="preserve">5.50023508071899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79256153106689</t>
+    <t xml:space="preserve">4.79256200790405</t>
   </si>
   <si>
     <t xml:space="preserve">5.10085487365723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0167760848999</t>
+    <t xml:space="preserve">5.01677465438843</t>
   </si>
   <si>
     <t xml:space="preserve">5.44768524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44418239593506</t>
+    <t xml:space="preserve">5.4441819190979</t>
   </si>
   <si>
     <t xml:space="preserve">5.77349519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39708948135376</t>
+    <t xml:space="preserve">6.3970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">6.76143503189087</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49518251419067</t>
+    <t xml:space="preserve">6.49518203735352</t>
   </si>
   <si>
     <t xml:space="preserve">6.71238899230957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09369230270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858285903931</t>
+    <t xml:space="preserve">7.09369325637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858238220215</t>
   </si>
   <si>
     <t xml:space="preserve">6.78433322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3562650680542</t>
+    <t xml:space="preserve">6.35626602172852</t>
   </si>
   <si>
     <t xml:space="preserve">6.53252935409546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35266828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0720853805542</t>
+    <t xml:space="preserve">6.35266780853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07208633422852</t>
   </si>
   <si>
     <t xml:space="preserve">6.323890209198</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">6.43900108337402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51094484329224</t>
+    <t xml:space="preserve">6.51094627380371</t>
   </si>
   <si>
     <t xml:space="preserve">6.40302896499634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15841865539551</t>
+    <t xml:space="preserve">6.15841960906982</t>
   </si>
   <si>
     <t xml:space="preserve">6.19798803329468</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">6.37425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47137498855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3274884223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15122509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11165475845337</t>
+    <t xml:space="preserve">6.47137594223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32748746871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1512246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11165523529053</t>
   </si>
   <si>
     <t xml:space="preserve">5.93898916244507</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">5.75193452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6943793296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70157384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36703300476074</t>
+    <t xml:space="preserve">5.69437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70157337188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36703395843506</t>
   </si>
   <si>
     <t xml:space="preserve">4.87421607971191</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">4.97853517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96414709091187</t>
+    <t xml:space="preserve">4.96414613723755</t>
   </si>
   <si>
     <t xml:space="preserve">4.8454384803772</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">4.8778133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91018724441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155000686646</t>
+    <t xml:space="preserve">4.9101881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155096054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.92457675933838</t>
@@ -917,34 +917,34 @@
     <t xml:space="preserve">4.76989698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69075870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65838384628296</t>
+    <t xml:space="preserve">4.690758228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6583833694458</t>
   </si>
   <si>
     <t xml:space="preserve">4.68716144561768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82385540008545</t>
+    <t xml:space="preserve">4.82385492324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.5504674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51089811325073</t>
+    <t xml:space="preserve">4.51089859008789</t>
   </si>
   <si>
     <t xml:space="preserve">4.49291229248047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4389533996582</t>
+    <t xml:space="preserve">4.43895387649536</t>
   </si>
   <si>
     <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38499641418457</t>
+    <t xml:space="preserve">4.38499593734741</t>
   </si>
   <si>
     <t xml:space="preserve">4.46413421630859</t>
@@ -953,25 +953,25 @@
     <t xml:space="preserve">5.03609037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85623025894165</t>
+    <t xml:space="preserve">4.85623073577881</t>
   </si>
   <si>
     <t xml:space="preserve">4.80946636199951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76629972457886</t>
+    <t xml:space="preserve">4.76630020141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.68356418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67637014389038</t>
+    <t xml:space="preserve">4.67636966705322</t>
   </si>
   <si>
     <t xml:space="preserve">4.60442590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59003639221191</t>
+    <t xml:space="preserve">4.59003686904907</t>
   </si>
   <si>
     <t xml:space="preserve">4.62960624694824</t>
@@ -980,19 +980,19 @@
     <t xml:space="preserve">4.66198110580444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6727728843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74831390380859</t>
+    <t xml:space="preserve">4.67277240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74831342697144</t>
   </si>
   <si>
     <t xml:space="preserve">4.75910568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95335531234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104991912842</t>
+    <t xml:space="preserve">4.95335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104944229126</t>
   </si>
   <si>
     <t xml:space="preserve">5.06486845016479</t>
@@ -1001,58 +1001,58 @@
     <t xml:space="preserve">5.14400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11522960662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19436740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10803461074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93536853790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550842285156</t>
+    <t xml:space="preserve">5.11522912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19436693191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10803413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93536901473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7555079460144</t>
   </si>
   <si>
     <t xml:space="preserve">4.99652147293091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90659093856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097949981689</t>
+    <t xml:space="preserve">4.90659141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92098045349121</t>
   </si>
   <si>
     <t xml:space="preserve">4.82025766372681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89220237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05407619476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925748825073</t>
+    <t xml:space="preserve">4.89220190048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05407667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925653457642</t>
   </si>
   <si>
     <t xml:space="preserve">5.0181040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95695209503174</t>
+    <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.94616031646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15839529037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23393630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60804605484009</t>
+    <t xml:space="preserve">5.15839576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23393678665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60804653167725</t>
   </si>
   <si>
     <t xml:space="preserve">5.89942026138306</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">5.77711486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03611469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978094100952</t>
+    <t xml:space="preserve">6.03611421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978141784668</t>
   </si>
   <si>
     <t xml:space="preserve">6.18000268936157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20877981185913</t>
+    <t xml:space="preserve">6.20878028869629</t>
   </si>
   <si>
     <t xml:space="preserve">6.52533435821533</t>
@@ -1079,19 +1079,19 @@
     <t xml:space="preserve">7.03613710403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8958477973938</t>
+    <t xml:space="preserve">6.89584684371948</t>
   </si>
   <si>
     <t xml:space="preserve">7.11527633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980242729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969017028809</t>
+    <t xml:space="preserve">7.13685989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12968921661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.43904781341553</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">9.29518413543701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160692214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42465972900391</t>
+    <t xml:space="preserve">10.2160682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42466068267822</t>
   </si>
   <si>
     <t xml:space="preserve">8.61890888214111</t>
@@ -1115,19 +1115,19 @@
     <t xml:space="preserve">8.22321605682373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0145788192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80593919754028</t>
+    <t xml:space="preserve">8.01457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80594110488892</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393741607666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299478530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10091114044189</t>
+    <t xml:space="preserve">7.992995262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10091209411621</t>
   </si>
   <si>
     <t xml:space="preserve">7.98580121994019</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">7.88507843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73399639129639</t>
+    <t xml:space="preserve">7.73399591445923</t>
   </si>
   <si>
     <t xml:space="preserve">7.41024732589722</t>
@@ -1145,58 +1145,58 @@
     <t xml:space="preserve">7.54694128036499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47499704360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535676956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38866519927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84191274642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702314376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910774230957</t>
+    <t xml:space="preserve">7.47499656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535772323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38866376876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910726547241</t>
   </si>
   <si>
     <t xml:space="preserve">8.04335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92824602127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74838495254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571983337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.424635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1944146156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419382095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498512268066</t>
+    <t xml:space="preserve">7.92824554443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85630178451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74838447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571935653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42463636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498416900635</t>
   </si>
   <si>
     <t xml:space="preserve">7.2088041305542</t>
@@ -1205,37 +1205,37 @@
     <t xml:space="preserve">7.20160961151123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5541353225708</t>
+    <t xml:space="preserve">7.55413627624512</t>
   </si>
   <si>
     <t xml:space="preserve">7.65485763549805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25197124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722105026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00735998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340156555176</t>
+    <t xml:space="preserve">7.25197076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448598861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00735950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944458007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340204238892</t>
   </si>
   <si>
     <t xml:space="preserve">7.15844249725342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91742992401123</t>
+    <t xml:space="preserve">6.91742944717407</t>
   </si>
   <si>
     <t xml:space="preserve">6.85627698898315</t>
@@ -1244,130 +1244,130 @@
     <t xml:space="preserve">6.89225006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78793096542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95699977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98217964172363</t>
+    <t xml:space="preserve">6.78793048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95699882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217916488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.16203927993774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14045667648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02174949645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33830165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82752323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25918769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15846824645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91385650634766</t>
+    <t xml:space="preserve">7.14045715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0217490196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33830261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82752227783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25918865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15846729278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9138560295105</t>
   </si>
   <si>
     <t xml:space="preserve">7.89946794509888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313371658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924715042114</t>
+    <t xml:space="preserve">7.81313419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924619674683</t>
   </si>
   <si>
     <t xml:space="preserve">7.76996803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64046955108643</t>
+    <t xml:space="preserve">7.64046859741211</t>
   </si>
   <si>
     <t xml:space="preserve">7.78435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48219060897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79152774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850147247314</t>
+    <t xml:space="preserve">7.48219108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79152822494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836111068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850099563599</t>
   </si>
   <si>
     <t xml:space="preserve">6.6404447555542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4893627166748</t>
+    <t xml:space="preserve">6.48936367034912</t>
   </si>
   <si>
     <t xml:space="preserve">6.63325119018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62605571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56130695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447263717651</t>
+    <t xml:space="preserve">6.62605619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56130647659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447359085083</t>
   </si>
   <si>
     <t xml:space="preserve">6.55411148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28791809082031</t>
+    <t xml:space="preserve">6.28791761398315</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02172565460205</t>
+    <t xml:space="preserve">6.02172470092773</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344861984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25914001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633548736572</t>
+    <t xml:space="preserve">5.86344766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914144515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633596420288</t>
   </si>
   <si>
     <t xml:space="preserve">6.44619607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46777868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51814031600952</t>
+    <t xml:space="preserve">6.46777820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641687393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51814079284668</t>
   </si>
   <si>
     <t xml:space="preserve">6.46058416366577</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29511308670044</t>
+    <t xml:space="preserve">6.29511213302612</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086345672607</t>
@@ -1382,43 +1382,43 @@
     <t xml:space="preserve">5.93539190292358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89222526550293</t>
+    <t xml:space="preserve">5.89222574234009</t>
   </si>
   <si>
     <t xml:space="preserve">5.79869890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97136402130127</t>
+    <t xml:space="preserve">5.97136449813843</t>
   </si>
   <si>
     <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99294757843018</t>
+    <t xml:space="preserve">5.99294710159302</t>
   </si>
   <si>
     <t xml:space="preserve">6.17280769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18719673156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25194549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22316884994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12244749069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27352905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30230712890625</t>
+    <t xml:space="preserve">6.18719720840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25194644927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1224479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27353000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30230760574341</t>
   </si>
   <si>
     <t xml:space="preserve">6.33827972412109</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">6.58551692962646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38323259353638</t>
+    <t xml:space="preserve">6.38323211669922</t>
   </si>
   <si>
     <t xml:space="preserve">6.46564435958862</t>
@@ -1442,22 +1442,22 @@
     <t xml:space="preserve">6.59300947189331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41319990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17345428466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09853410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90373992919922</t>
+    <t xml:space="preserve">6.41320037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09853363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90374040603638</t>
   </si>
   <si>
     <t xml:space="preserve">5.95618486404419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94120025634766</t>
+    <t xml:space="preserve">5.94120073318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.86628007888794</t>
@@ -1466,7 +1466,7 @@
     <t xml:space="preserve">5.94869232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84380340576172</t>
+    <t xml:space="preserve">5.84380435943604</t>
   </si>
   <si>
     <t xml:space="preserve">5.59656572341919</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">5.55910539627075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.888756275177</t>
+    <t xml:space="preserve">5.88875579833984</t>
   </si>
   <si>
     <t xml:space="preserve">5.80634355545044</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">5.64151811599731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79135894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139163970947</t>
+    <t xml:space="preserve">5.79135942459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139116287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.88126420974731</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">5.92621612548828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33078670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55554914474487</t>
+    <t xml:space="preserve">6.33078765869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55554866790771</t>
   </si>
   <si>
     <t xml:space="preserve">6.45815229415894</t>
@@ -1514,25 +1514,25 @@
     <t xml:space="preserve">6.30081939697266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.128502368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06107330322266</t>
+    <t xml:space="preserve">6.12850189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06107378005981</t>
   </si>
   <si>
     <t xml:space="preserve">5.77637529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76888275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70145463943481</t>
+    <t xml:space="preserve">5.768883228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70145511627197</t>
   </si>
   <si>
     <t xml:space="preserve">5.66399431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57409000396729</t>
+    <t xml:space="preserve">5.57408952713013</t>
   </si>
   <si>
     <t xml:space="preserve">5.75389909744263</t>
@@ -1544,43 +1544,43 @@
     <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6265344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61904239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65650320053101</t>
+    <t xml:space="preserve">5.62653398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61904191970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.54412126541138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58158111572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50666093826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53662919998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43174076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46920108795166</t>
+    <t xml:space="preserve">5.58158206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5066614151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53662872314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43174123764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4692006111145</t>
   </si>
   <si>
     <t xml:space="preserve">5.31935930252075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189897537231</t>
+    <t xml:space="preserve">5.28189945220947</t>
   </si>
   <si>
     <t xml:space="preserve">5.42424869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49167680740356</t>
+    <t xml:space="preserve">5.49167728424072</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415348052979</t>
@@ -1595,19 +1595,19 @@
     <t xml:space="preserve">5.18450260162354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20697927474976</t>
+    <t xml:space="preserve">5.2069787979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.58907413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7464075088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47669267654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21447086334229</t>
+    <t xml:space="preserve">5.74640703201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47669315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21447134017944</t>
   </si>
   <si>
     <t xml:space="preserve">5.13955020904541</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">5.07212209701538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05713796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01967668533325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466176986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977285385132</t>
+    <t xml:space="preserve">5.05713844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967763900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977237701416</t>
   </si>
   <si>
     <t xml:space="preserve">4.87732887268066</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">4.86983633041382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7349796295166</t>
+    <t xml:space="preserve">4.73497915267944</t>
   </si>
   <si>
     <t xml:space="preserve">4.77243947982788</t>
@@ -1649,55 +1649,55 @@
     <t xml:space="preserve">4.82488393783569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88482093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75745534896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234378814697</t>
+    <t xml:space="preserve">4.88482046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75745582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234426498413</t>
   </si>
   <si>
     <t xml:space="preserve">4.91478872299194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89980411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8548526763916</t>
+    <t xml:space="preserve">4.89980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85485219955444</t>
   </si>
   <si>
     <t xml:space="preserve">4.95224905014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16951894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710622787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13205909729004</t>
+    <t xml:space="preserve">5.16951847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0871057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13205862045288</t>
   </si>
   <si>
     <t xml:space="preserve">6.21840667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25586652755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01612043380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602617263794</t>
+    <t xml:space="preserve">6.25586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01612091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602521896362</t>
   </si>
   <si>
     <t xml:space="preserve">5.99364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04215335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221731185913</t>
+    <t xml:space="preserve">5.04215383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221778869629</t>
   </si>
   <si>
     <t xml:space="preserve">4.94475698471069</t>
@@ -1706,34 +1706,34 @@
     <t xml:space="preserve">4.99720096588135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02717018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89231300354004</t>
+    <t xml:space="preserve">5.0271692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89231252670288</t>
   </si>
   <si>
     <t xml:space="preserve">5.04964590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95974063873291</t>
+    <t xml:space="preserve">4.95974111557007</t>
   </si>
   <si>
     <t xml:space="preserve">4.81739234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79491567611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78742361068726</t>
+    <t xml:space="preserve">4.79491662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7874231338501</t>
   </si>
   <si>
     <t xml:space="preserve">4.83237600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97472524642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729808807373</t>
+    <t xml:space="preserve">4.9747257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729713439941</t>
   </si>
   <si>
     <t xml:space="preserve">4.76494789123535</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">4.47275733947754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38285255432129</t>
+    <t xml:space="preserve">4.27047204971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38285303115845</t>
   </si>
   <si>
     <t xml:space="preserve">4.32291650772095</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">4.18056678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16558313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30043983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3154239654541</t>
+    <t xml:space="preserve">4.16558361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30044031143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31542444229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.46526527404785</t>
@@ -1769,25 +1769,25 @@
     <t xml:space="preserve">4.45777320861816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10209035873413</t>
+    <t xml:space="preserve">4.71250247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10208988189697</t>
   </si>
   <si>
     <t xml:space="preserve">5.07961416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93726491928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218605041504</t>
+    <t xml:space="preserve">4.93726539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218557357788</t>
   </si>
   <si>
     <t xml:space="preserve">5.24443912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22196245193481</t>
+    <t xml:space="preserve">5.22196340560913</t>
   </si>
   <si>
     <t xml:space="preserve">5.25942325592041</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">5.11707448959351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28939199447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202640533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31186819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41675615310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44672441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39428091049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421695709229</t>
+    <t xml:space="preserve">5.28939151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202688217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31186771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41675662994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180471420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4467248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421648025513</t>
   </si>
   <si>
     <t xml:space="preserve">5.40926456451416</t>
@@ -1829,43 +1829,43 @@
     <t xml:space="preserve">5.89624834060669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85878753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.121009349823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589874267578</t>
+    <t xml:space="preserve">5.85878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12101030349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589921951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.81383562088013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82132768630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91123199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03110504150391</t>
+    <t xml:space="preserve">6.00113725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885149002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82132720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91123151779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03110456466675</t>
   </si>
   <si>
     <t xml:space="preserve">6.008629322052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91872406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377166748047</t>
+    <t xml:space="preserve">5.91872453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631181716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377214431763</t>
   </si>
   <si>
     <t xml:space="preserve">5.97116851806641</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">6.21091461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09104156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348649978638</t>
+    <t xml:space="preserve">6.09104108810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097856521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
   </si>
   <si>
     <t xml:space="preserve">6.04608917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02361345291138</t>
+    <t xml:space="preserve">6.02361297607422</t>
   </si>
   <si>
     <t xml:space="preserve">6.03859758377075</t>
@@ -1895,40 +1895,40 @@
     <t xml:space="preserve">5.73142290115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396305084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70894622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170902252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73891448974609</t>
+    <t xml:space="preserve">5.97866106033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396257400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916887283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170806884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73891496658325</t>
   </si>
   <si>
     <t xml:space="preserve">5.55161380767822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47268629074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33155632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484422683716</t>
+    <t xml:space="preserve">5.47268581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33155584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484518051147</t>
   </si>
   <si>
     <t xml:space="preserve">5.35507774353027</t>
@@ -1943,16 +1943,16 @@
     <t xml:space="preserve">5.39428043365479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24531078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26883220672607</t>
+    <t xml:space="preserve">5.24531030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26883172988892</t>
   </si>
   <si>
     <t xml:space="preserve">5.28451299667358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25315046310425</t>
+    <t xml:space="preserve">5.25315093994141</t>
   </si>
   <si>
     <t xml:space="preserve">5.14338350296021</t>
@@ -1961,25 +1961,25 @@
     <t xml:space="preserve">5.06497859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00225400924683</t>
+    <t xml:space="preserve">5.00225448608398</t>
   </si>
   <si>
     <t xml:space="preserve">5.16690540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20610761642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33939695358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235363006592</t>
+    <t xml:space="preserve">5.20610809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235410690308</t>
   </si>
   <si>
     <t xml:space="preserve">5.11986207962036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13554430007935</t>
+    <t xml:space="preserve">5.13554334640503</t>
   </si>
   <si>
     <t xml:space="preserve">5.09634017944336</t>
@@ -1988,55 +1988,55 @@
     <t xml:space="preserve">5.05713748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11202192306519</t>
+    <t xml:space="preserve">5.11202144622803</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44916439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45700454711914</t>
+    <t xml:space="preserve">5.44916391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4570050239563</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70790147781372</t>
+    <t xml:space="preserve">5.70790100097656</t>
   </si>
   <si>
     <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55893182754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51188898086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48836612701416</t>
+    <t xml:space="preserve">5.63733673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55893135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51188850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
     <t xml:space="preserve">5.48052597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36291790008545</t>
+    <t xml:space="preserve">5.36291885375977</t>
   </si>
   <si>
     <t xml:space="preserve">5.31587505340576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3237156867981</t>
+    <t xml:space="preserve">5.32371520996094</t>
   </si>
   <si>
     <t xml:space="preserve">5.19826745986938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79840087890625</t>
+    <t xml:space="preserve">4.79840040206909</t>
   </si>
   <si>
     <t xml:space="preserve">4.70431423187256</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">4.71999502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51614141464233</t>
+    <t xml:space="preserve">4.51614189147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.97089242935181</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">4.82192230224609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64159059524536</t>
+    <t xml:space="preserve">4.6415901184082</t>
   </si>
   <si>
     <t xml:space="preserve">4.71215486526489</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">4.67295217514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63374996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64942979812622</t>
+    <t xml:space="preserve">4.63374948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64943027496338</t>
   </si>
   <si>
     <t xml:space="preserve">4.59454727172852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62590932846069</t>
+    <t xml:space="preserve">4.62590885162354</t>
   </si>
   <si>
     <t xml:space="preserve">4.68079233169556</t>
@@ -2081,55 +2081,55 @@
     <t xml:space="preserve">4.90032768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22962856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02577495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04145669937134</t>
+    <t xml:space="preserve">5.2296290397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02577543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0414571762085</t>
   </si>
   <si>
     <t xml:space="preserve">5.15122413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22178936004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21394824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15906476974487</t>
+    <t xml:space="preserve">5.22178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21394872665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15906429290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.08065938949585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12770223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01793527603149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07281923294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08849906921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19042634963989</t>
+    <t xml:space="preserve">5.12770318984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01793575286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07281875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08850002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19042682647705</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52756881713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5197286605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40212059020996</t>
+    <t xml:space="preserve">5.52756929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51972913742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40212106704712</t>
   </si>
   <si>
     <t xml:space="preserve">5.56677150726318</t>
@@ -2144,28 +2144,28 @@
     <t xml:space="preserve">5.53540992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41780185699463</t>
+    <t xml:space="preserve">5.41780138015747</t>
   </si>
   <si>
     <t xml:space="preserve">5.42564249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84118938446045</t>
+    <t xml:space="preserve">5.84119033813477</t>
   </si>
   <si>
     <t xml:space="preserve">5.76278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64517736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44132375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40996170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38643932342529</t>
+    <t xml:space="preserve">5.64517688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44132328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40996122360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38643980026245</t>
   </si>
   <si>
     <t xml:space="preserve">5.3472375869751</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">5.23746967315674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97873258590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83760356903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89248609542847</t>
+    <t xml:space="preserve">4.97873306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8376030921936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89248704910278</t>
   </si>
   <si>
     <t xml:space="preserve">4.86896514892578</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">4.57102537155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54750394821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57886552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39069318771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15547752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2260422706604</t>
+    <t xml:space="preserve">4.54750347137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57886648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39069271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15547800064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22604179382324</t>
   </si>
   <si>
     <t xml:space="preserve">4.11627531051636</t>
@@ -2222,25 +2222,25 @@
     <t xml:space="preserve">3.84185671806335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63800287246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26165795326233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29302000999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32438158988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099382400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09700679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05780434608459</t>
+    <t xml:space="preserve">3.63800311088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26165771484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29301953315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32438182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099358558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09700703620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05780458450317</t>
   </si>
   <si>
     <t xml:space="preserve">2.94803690910339</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">3.00292062759399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13620924949646</t>
+    <t xml:space="preserve">3.13620948791504</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036236763</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">3.21461486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25381731987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22245502471924</t>
+    <t xml:space="preserve">3.25381755828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2224555015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.24205660820007</t>
@@ -2276,31 +2276,31 @@
     <t xml:space="preserve">3.36750507354736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34006357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45767045021057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59880042076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37142539024353</t>
+    <t xml:space="preserve">3.34006333351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45767092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59880089759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37142515182495</t>
   </si>
   <si>
     <t xml:space="preserve">3.52039480209351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54391694068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7242488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8104944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92026209831238</t>
+    <t xml:space="preserve">3.54391670227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72424912452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81049466133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9202618598938</t>
   </si>
   <si>
     <t xml:space="preserve">4.3358097076416</t>
@@ -2315,70 +2315,70 @@
     <t xml:space="preserve">4.23388290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16331815719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07707214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21820163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740480422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19468021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208904266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401560783386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84577679634094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70072674751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321853637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265402793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169014930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74385023117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298668861389</t>
+    <t xml:space="preserve">4.16331768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07707166671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21820211410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19468069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208928108215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481339454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401584625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577703475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70072746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321925163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265378952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8222553730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145806312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169062614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74384999275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298597335815</t>
   </si>
   <si>
     <t xml:space="preserve">4.29660701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10059404373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91634130477905</t>
+    <t xml:space="preserve">4.10059356689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91634154319763</t>
   </si>
   <si>
     <t xml:space="preserve">3.95946455001831</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763689041138</t>
+    <t xml:space="preserve">4.14763736724854</t>
   </si>
   <si>
     <t xml:space="preserve">4.01434803009033</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">3.8889000415802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05355167388916</t>
+    <t xml:space="preserve">4.053551197052</t>
   </si>
   <si>
     <t xml:space="preserve">4.06923151016235</t>
@@ -2420,40 +2420,40 @@
     <t xml:space="preserve">3.92810273170471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91242122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85753726959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8653781414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617616653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105916976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458059310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90850138664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913308143616</t>
+    <t xml:space="preserve">3.91242051124573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753774642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86537861824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105893135071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458083152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.779132604599</t>
   </si>
   <si>
     <t xml:space="preserve">3.75561118125916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7477707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657434463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497948646545</t>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657410621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497972488403</t>
   </si>
   <si>
     <t xml:space="preserve">3.96730518341064</t>
@@ -2462,46 +2462,46 @@
     <t xml:space="preserve">4.02218866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93594264984131</t>
+    <t xml:space="preserve">3.93594288825989</t>
   </si>
   <si>
     <t xml:space="preserve">3.76345181465149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75953102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6458432674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6693651676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016223907471</t>
+    <t xml:space="preserve">3.75953149795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64584374427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66936469078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544461250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016247749329</t>
   </si>
   <si>
     <t xml:space="preserve">3.56351804733276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56743884086609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59096026420593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119235038757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44199013710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38710641860962</t>
+    <t xml:space="preserve">3.56743836402893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59095978736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903298377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44198966026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3871066570282</t>
   </si>
   <si>
     <t xml:space="preserve">3.31654167175293</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">3.33222270011902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40278768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238855361938</t>
+    <t xml:space="preserve">3.40278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238831520081</t>
   </si>
   <si>
     <t xml:space="preserve">3.43806958198547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46551203727722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49295330047607</t>
+    <t xml:space="preserve">3.46551156044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49295353889465</t>
   </si>
   <si>
     <t xml:space="preserve">3.55175757408142</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">3.37926578521729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43414950370789</t>
+    <t xml:space="preserve">3.43414926528931</t>
   </si>
   <si>
     <t xml:space="preserve">3.42630863189697</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">3.4615912437439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44983077049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189075469971</t>
+    <t xml:space="preserve">3.44983053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189051628113</t>
   </si>
   <si>
     <t xml:space="preserve">3.20677423477173</t>
@@ -2561,97 +2561,97 @@
     <t xml:space="preserve">3.17541241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.528235912323</t>
+    <t xml:space="preserve">3.52823543548584</t>
   </si>
   <si>
     <t xml:space="preserve">3.53215599060059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53607654571533</t>
+    <t xml:space="preserve">3.53607678413391</t>
   </si>
   <si>
     <t xml:space="preserve">4.10843420028687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99866676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252132415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13195562362671</t>
+    <t xml:space="preserve">3.99866652488708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13195610046387</t>
   </si>
   <si>
     <t xml:space="preserve">4.09275341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28876638412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24956369400024</t>
+    <t xml:space="preserve">4.06139135360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2887659072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2495641708374</t>
   </si>
   <si>
     <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39853382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35933113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69647407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976245880127</t>
+    <t xml:space="preserve">4.3985333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3593316078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69647359848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75919771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976293563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.72783613204956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74351692199707</t>
+    <t xml:space="preserve">4.74351739883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.76703834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77487945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73567628860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80624103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01009464263916</t>
+    <t xml:space="preserve">4.77487897872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73567676544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68863344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80624151229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.010094165802</t>
   </si>
   <si>
     <t xml:space="preserve">4.99441337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9473705291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86112499237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84544372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91600799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93952941894531</t>
+    <t xml:space="preserve">4.94736957550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86112451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84544277191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91600894927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93952989578247</t>
   </si>
   <si>
     <t xml:space="preserve">5.04929733276367</t>
@@ -2660,25 +2660,25 @@
     <t xml:space="preserve">5.58245325088501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68438005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59813356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6294960975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71574211120605</t>
+    <t xml:space="preserve">5.68438053131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59813404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62949562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71574115753174</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66869831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66085767745972</t>
+    <t xml:space="preserve">5.66869878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66085815429688</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358226776123</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">6.05288457870483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97447872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720283508301</t>
+    <t xml:space="preserve">5.97447919845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720331192017</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080690383911</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">6.00474500656128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11834859848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49161577224731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45915794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42670011520386</t>
+    <t xml:space="preserve">6.11834812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49161624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4591588973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4266996383667</t>
   </si>
   <si>
     <t xml:space="preserve">6.2644100189209</t>
@@ -2729,37 +2729,37 @@
     <t xml:space="preserve">6.41047096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39424180984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44292974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96225881576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43290138244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00091743469238</t>
+    <t xml:space="preserve">6.39424228668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4429292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96225833892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43290090560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0009183883667</t>
   </si>
   <si>
     <t xml:space="preserve">7.83862686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87108469009399</t>
+    <t xml:space="preserve">7.87108421325684</t>
   </si>
   <si>
     <t xml:space="preserve">7.78994035720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91977310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95223093032837</t>
+    <t xml:space="preserve">7.91977214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95222997665405</t>
   </si>
   <si>
     <t xml:space="preserve">7.90354251861572</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">8.60139274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64196300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56081867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43910217285156</t>
+    <t xml:space="preserve">8.64196395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56081962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43910026550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.19566631317139</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">8.23623752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01714611053467</t>
+    <t xml:space="preserve">8.01714706420898</t>
   </si>
   <si>
     <t xml:space="preserve">8.06583213806152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96845960617065</t>
+    <t xml:space="preserve">7.96845865249634</t>
   </si>
   <si>
     <t xml:space="preserve">7.40044260025024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25438165664673</t>
+    <t xml:space="preserve">7.25438070297241</t>
   </si>
   <si>
     <t xml:space="preserve">7.48158836364746</t>
@@ -2807,55 +2807,55 @@
     <t xml:space="preserve">7.56273317337036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69256448745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75748157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62764835357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3030686378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192335128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81619739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15700578689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23815155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38421440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70879411697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61142015457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010665893555</t>
+    <t xml:space="preserve">7.69256496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502374649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75748109817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62764883041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4653582572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30306768417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192239761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81619596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15700674057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23815298080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3842134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70879459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61141967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010808944702</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74125289916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3579568862915</t>
+    <t xml:space="preserve">7.74125242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
     <t xml:space="preserve">8.1550931930542</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">8.96654605865479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84482765197754</t>
+    <t xml:space="preserve">8.84482669830322</t>
   </si>
   <si>
     <t xml:space="preserve">8.76368236541748</t>
@@ -2876,52 +2876,52 @@
     <t xml:space="preserve">8.39852905273438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47967338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31738376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08206272125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11452102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03337574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04960346221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04769039154053</t>
+    <t xml:space="preserve">8.47967433929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08206176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11452007293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03337478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04960441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04768943786621</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940784454346</t>
+    <t xml:space="preserve">9.16940879821777</t>
   </si>
   <si>
     <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4034481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23627662658691</t>
+    <t xml:space="preserve">9.40345001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23627758026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.48703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77958679199219</t>
+    <t xml:space="preserve">9.7795877456665</t>
   </si>
   <si>
     <t xml:space="preserve">9.6124153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57062149047852</t>
+    <t xml:space="preserve">9.57062244415283</t>
   </si>
   <si>
     <t xml:space="preserve">9.52882862091064</t>
@@ -2933,25 +2933,25 @@
     <t xml:space="preserve">9.73779392242432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65420818328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90496730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31986331939697</t>
+    <t xml:space="preserve">9.65420913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90496635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31986236572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02731037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15269088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013889312744</t>
+    <t xml:space="preserve">9.02731132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15268993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.7765531539917</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">8.35862159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60937976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19448280334473</t>
+    <t xml:space="preserve">8.6093807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19448375701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">9.11089706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36165618896484</t>
+    <t xml:space="preserve">9.36165523529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.06910514831543</t>
@@ -2984,34 +2984,34 @@
     <t xml:space="preserve">8.90193176269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81834506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758785247803</t>
+    <t xml:space="preserve">8.81834602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758689880371</t>
   </si>
   <si>
     <t xml:space="preserve">8.52579307556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73475933074951</t>
+    <t xml:space="preserve">8.73476028442383</t>
   </si>
   <si>
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32518768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65649700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82366943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321491241455</t>
+    <t xml:space="preserve">8.30846881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32518672943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65649747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82366895675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321538925171</t>
   </si>
   <si>
     <t xml:space="preserve">7.12154579162598</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">7.10482835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68993234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589065551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053773880005</t>
+    <t xml:space="preserve">7.68993139266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589113235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053964614868</t>
   </si>
   <si>
     <t xml:space="preserve">7.80695295333862</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">7.99084186553955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09114646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04099369049072</t>
+    <t xml:space="preserve">8.09114551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04099464416504</t>
   </si>
   <si>
     <t xml:space="preserve">8.27503490447998</t>
@@ -3059,28 +3059,28 @@
     <t xml:space="preserve">8.48400020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30011177062988</t>
+    <t xml:space="preserve">8.30011081695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.35026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24995994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87382221221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69828987121582</t>
+    <t xml:space="preserve">8.24996089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87382173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69829034805298</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531190872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77351808547974</t>
+    <t xml:space="preserve">7.81531095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77351856231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.91561508178711</t>
@@ -3089,40 +3089,40 @@
     <t xml:space="preserve">7.7818775177002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60634613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89889764785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79859352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023456573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978004455566</t>
+    <t xml:space="preserve">7.60634565353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89889812469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79859447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63977956771851</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64850187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24154376983643</t>
+    <t xml:space="preserve">7.64850234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24154472351074</t>
   </si>
   <si>
     <t xml:space="preserve">8.21538066864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28514957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32003498077393</t>
+    <t xml:space="preserve">8.2851505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32003402709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
@@ -3131,22 +3131,22 @@
     <t xml:space="preserve">8.19793701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49445915222168</t>
+    <t xml:space="preserve">8.49445819854736</t>
   </si>
   <si>
     <t xml:space="preserve">8.69504642486572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67760372161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54678726196289</t>
+    <t xml:space="preserve">8.67760467529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54678630828857</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59039211273193</t>
+    <t xml:space="preserve">8.59039306640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.64271926879883</t>
@@ -3164,25 +3164,25 @@
     <t xml:space="preserve">8.17177391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12816715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93630170822144</t>
+    <t xml:space="preserve">8.1281681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93630123138428</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827077865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77931976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95374393463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14561080932617</t>
+    <t xml:space="preserve">7.71827173233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77931928634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95374345779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14560985565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
@@ -3194,31 +3194,31 @@
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65722274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76187658309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6921067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70082855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5961742401123</t>
+    <t xml:space="preserve">7.78804063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65722179412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76187705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69210767745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70082807540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59617376327515</t>
   </si>
   <si>
     <t xml:space="preserve">7.46535634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54384660720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73571348190308</t>
+    <t xml:space="preserve">7.54384613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73571395874023</t>
   </si>
   <si>
     <t xml:space="preserve">7.50024127960205</t>
@@ -3227,22 +3227,22 @@
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.447913646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53512620925903</t>
+    <t xml:space="preserve">7.55256748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44791316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53512668609619</t>
   </si>
   <si>
     <t xml:space="preserve">7.51768350601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50896167755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57001113891602</t>
+    <t xml:space="preserve">7.50896120071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57001066207886</t>
   </si>
   <si>
     <t xml:space="preserve">7.80548334121704</t>
@@ -3263,46 +3263,46 @@
     <t xml:space="preserve">8.48573684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5031795501709</t>
+    <t xml:space="preserve">8.50318050384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596698760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02351379394531</t>
+    <t xml:space="preserve">8.41596794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3461971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.023512840271</t>
   </si>
   <si>
     <t xml:space="preserve">8.37236213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89269542694092</t>
+    <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
     <t xml:space="preserve">7.83164644241333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66594314575195</t>
+    <t xml:space="preserve">7.66594457626343</t>
   </si>
   <si>
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97118616104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68338632583618</t>
+    <t xml:space="preserve">7.97118663787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338584899902</t>
   </si>
   <si>
     <t xml:space="preserve">7.33453750610352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1688346862793</t>
+    <t xml:space="preserve">7.16883516311646</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
@@ -3311,16 +3311,16 @@
     <t xml:space="preserve">7.06418085098267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28221082687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13395023345947</t>
+    <t xml:space="preserve">7.28221130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13395071029663</t>
   </si>
   <si>
     <t xml:space="preserve">7.12522888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78510189056396</t>
+    <t xml:space="preserve">6.78510141372681</t>
   </si>
   <si>
     <t xml:space="preserve">6.61939907073975</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63684129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87231349945068</t>
+    <t xml:space="preserve">6.6368408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
     <t xml:space="preserve">7.75315618515015</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">7.43047142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49151992797852</t>
+    <t xml:space="preserve">7.49151945114136</t>
   </si>
   <si>
     <t xml:space="preserve">7.27348947525024</t>
@@ -3353,25 +3353,25 @@
     <t xml:space="preserve">7.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38686513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3519811630249</t>
+    <t xml:space="preserve">7.38686561584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35198068618774</t>
   </si>
   <si>
     <t xml:space="preserve">7.31709575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47407674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29093170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581663131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30837392807007</t>
+    <t xml:space="preserve">7.47407722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.290931224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30837440490723</t>
   </si>
   <si>
     <t xml:space="preserve">7.42175006866455</t>
@@ -3383,10 +3383,10 @@
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03223419189453</t>
+    <t xml:space="preserve">7.85781097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03223514556885</t>
   </si>
   <si>
     <t xml:space="preserve">8.10200500488281</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">8.15433216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839729309082</t>
+    <t xml:space="preserve">8.05839824676514</t>
   </si>
   <si>
     <t xml:space="preserve">8.09328269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00607109069824</t>
+    <t xml:space="preserve">8.00607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">8.11072540283203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07584190368652</t>
+    <t xml:space="preserve">8.07584095001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">7.97990655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98862838745117</t>
+    <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.90141725540161</t>
@@ -3428,28 +3428,28 @@
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82292652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11944770812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2589864730835</t>
+    <t xml:space="preserve">7.91885900497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82292556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11944675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25898551940918</t>
   </si>
   <si>
     <t xml:space="preserve">8.27642822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52934265136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94796085357666</t>
+    <t xml:space="preserve">8.337477684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5293436050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94796180725098</t>
   </si>
   <si>
     <t xml:space="preserve">8.87819194793701</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">8.89563369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65144062042236</t>
+    <t xml:space="preserve">8.65144157409668</t>
   </si>
   <si>
     <t xml:space="preserve">8.6601619720459</t>
@@ -3467,31 +3467,31 @@
     <t xml:space="preserve">8.79098033905029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70376682281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71248912811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86075019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93051910400391</t>
+    <t xml:space="preserve">8.70376777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71248817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86074924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93052005767822</t>
   </si>
   <si>
     <t xml:space="preserve">8.62527656555176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56422805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46829605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6863260269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15727138519287</t>
+    <t xml:space="preserve">8.56422901153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46829509735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68632507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15727043151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">8.91307735443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96540451049805</t>
+    <t xml:space="preserve">8.96540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">9.00028896331787</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">8.82586479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84330749511719</t>
+    <t xml:space="preserve">8.8433084487915</t>
   </si>
   <si>
     <t xml:space="preserve">8.80842208862305</t>
@@ -71137,7 +71137,7 @@
     </row>
     <row r="2558">
       <c r="A2558" s="1" t="n">
-        <v>46048.6910069444</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2558" t="n">
         <v>2114</v>
@@ -71158,6 +71158,32 @@
         <v>1399</v>
       </c>
       <c r="H2558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46049.691099537</v>
+      </c>
+      <c r="B2559" t="n">
+        <v>6351</v>
+      </c>
+      <c r="C2559" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H2559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19253492355347</t>
+    <t xml:space="preserve">1.19253528118134</t>
   </si>
   <si>
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355497837067</t>
+    <t xml:space="preserve">1.21355509757996</t>
   </si>
   <si>
     <t xml:space="preserve">1.22546637058258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20654833316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23177242279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24998962879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26330244541168</t>
+    <t xml:space="preserve">1.20654845237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23177254199982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2499897480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26330232620239</t>
   </si>
   <si>
     <t xml:space="preserve">1.27311182022095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26120018959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718737602234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2079496383667</t>
+    <t xml:space="preserve">1.26120030879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718689918518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20794975757599</t>
   </si>
   <si>
     <t xml:space="preserve">1.19323575496674</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">1.17501842975616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19814026355743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24578583240509</t>
+    <t xml:space="preserve">1.19814038276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2457857131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.23457515239716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495640277863</t>
+    <t xml:space="preserve">1.21495628356934</t>
   </si>
   <si>
     <t xml:space="preserve">1.18272578716278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17992293834686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641973495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12457048892975</t>
+    <t xml:space="preserve">1.17992317676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641985416412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12457036972046</t>
   </si>
   <si>
     <t xml:space="preserve">1.12807381153107</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">1.10284960269928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08603370189667</t>
+    <t xml:space="preserve">1.08603358268738</t>
   </si>
   <si>
     <t xml:space="preserve">1.01596713066101</t>
@@ -119,37 +119,37 @@
     <t xml:space="preserve">1.0250757932663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02017104625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195384025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297377586365</t>
+    <t xml:space="preserve">1.02017092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297365665436</t>
   </si>
   <si>
     <t xml:space="preserve">1.04329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09654366970062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11335968971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11055707931519</t>
+    <t xml:space="preserve">1.09654378890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11335980892181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1105569601059</t>
   </si>
   <si>
     <t xml:space="preserve">1.09304022789001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12106716632843</t>
+    <t xml:space="preserve">1.12106704711914</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017582893372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15610015392303</t>
+    <t xml:space="preserve">1.15610039234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.10004711151123</t>
@@ -158,43 +158,43 @@
     <t xml:space="preserve">1.1315770149231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10705363750458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227772712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11826419830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14909362792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17852187156677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17011380195618</t>
+    <t xml:space="preserve">1.10705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227784633636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11826431751251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14909374713898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1701135635376</t>
   </si>
   <si>
     <t xml:space="preserve">1.18412709236145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17081439495087</t>
+    <t xml:space="preserve">1.17081427574158</t>
   </si>
   <si>
     <t xml:space="preserve">1.16310703754425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22616708278656</t>
+    <t xml:space="preserve">1.22616720199585</t>
   </si>
   <si>
     <t xml:space="preserve">1.24508500099182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24088108539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20514714717865</t>
+    <t xml:space="preserve">1.2408812046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20514726638794</t>
   </si>
   <si>
     <t xml:space="preserve">1.19113373756409</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">1.22686791419983</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22196316719055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24438428878784</t>
+    <t xml:space="preserve">1.22196304798126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
     <t xml:space="preserve">1.17221570014954</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">1.19743978977203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20374584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20304489135742</t>
+    <t xml:space="preserve">1.20374572277069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20304501056671</t>
   </si>
   <si>
     <t xml:space="preserve">1.23807835578918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2331737279892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19954180717468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22476577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845984458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916031837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2289696931839</t>
+    <t xml:space="preserve">1.23317384719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19954168796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845972537994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916043758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22896981239319</t>
   </si>
   <si>
     <t xml:space="preserve">1.21215379238129</t>
@@ -251,40 +251,40 @@
     <t xml:space="preserve">1.22266376018524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29202961921692</t>
+    <t xml:space="preserve">1.2920298576355</t>
   </si>
   <si>
     <t xml:space="preserve">1.2962338924408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2752138376236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28712522983551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28151965141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788773059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737788200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865035057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469884872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138627052307</t>
+    <t xml:space="preserve">1.27521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28712511062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28151953220367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737764358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865046977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469896793365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138638973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.11896502971649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12036657333374</t>
+    <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
     <t xml:space="preserve">1.13648164272308</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07202041149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08463227748871</t>
+    <t xml:space="preserve">1.07202005386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084632396698</t>
   </si>
   <si>
     <t xml:space="preserve">1.06501364707947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07061910629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08253037929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902705669403</t>
+    <t xml:space="preserve">1.07061898708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08253049850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902717590332</t>
   </si>
   <si>
     <t xml:space="preserve">1.05800712108612</t>
@@ -326,22 +326,22 @@
     <t xml:space="preserve">1.09514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11966562271118</t>
+    <t xml:space="preserve">1.11966574192047</t>
   </si>
   <si>
     <t xml:space="preserve">1.09934639930725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11265897750854</t>
+    <t xml:space="preserve">1.11265921592712</t>
   </si>
   <si>
     <t xml:space="preserve">1.15680110454559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34528040885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681533336639</t>
+    <t xml:space="preserve">1.34528028964996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48681509494781</t>
   </si>
   <si>
     <t xml:space="preserve">1.48821651935577</t>
@@ -350,253 +350,253 @@
     <t xml:space="preserve">1.45178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41534721851349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4573872089386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40133380889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46999931335449</t>
+    <t xml:space="preserve">1.4153470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45738708972931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40133392810822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46999907493591</t>
   </si>
   <si>
     <t xml:space="preserve">1.43776845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42375528812408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43636703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936027050018</t>
+    <t xml:space="preserve">1.42375516891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4363671541214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936050891876</t>
   </si>
   <si>
     <t xml:space="preserve">1.41674852371216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42235386371613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814959049225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4111430644989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42795944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48120987415314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69421255588531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338336467743</t>
+    <t xml:space="preserve">1.42235374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814982891083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114294528961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42795932292938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48120999336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69421279430389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338324546814</t>
   </si>
   <si>
     <t xml:space="preserve">1.80071401596069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84555661678314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7923059463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090464115143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268731594086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064744472504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71663391590118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78670060634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84275376796722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593786716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313513755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995091915131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83855032920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84415543079376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83014178276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472742557526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874047756195</t>
+    <t xml:space="preserve">1.84555649757385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79230582714081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090440273285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268719673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064696788788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71663403511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78670072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8399510383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854997158051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84415555000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014190196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472718715668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874059677124</t>
   </si>
   <si>
     <t xml:space="preserve">1.81192469596863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83294427394867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835946559906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937940120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9954993724823</t>
+    <t xml:space="preserve">1.83294451236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835922718048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937928199768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549925327301</t>
   </si>
   <si>
     <t xml:space="preserve">2.07257270812988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02913188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798766136169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04034209251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830198287964</t>
+    <t xml:space="preserve">2.0291314125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798742294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04034185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830210208893</t>
   </si>
   <si>
     <t xml:space="preserve">2.03053283691406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01932168006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970352649689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359240531921</t>
+    <t xml:space="preserve">2.01932191848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9997034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231551170349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066621780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15945553779602</t>
+    <t xml:space="preserve">2.15945529937744</t>
   </si>
   <si>
     <t xml:space="preserve">1.98989379405975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88339293003082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9716762304306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345914363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01651930809021</t>
+    <t xml:space="preserve">1.88339281082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167646884918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345938205719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01651906967163</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250601768494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9786833524704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944561481476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9198272228241</t>
+    <t xml:space="preserve">1.98428845405579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97868311405182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944585323334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91982746124268</t>
   </si>
   <si>
     <t xml:space="preserve">1.86377394199371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86797773838043</t>
+    <t xml:space="preserve">1.86797797679901</t>
   </si>
   <si>
     <t xml:space="preserve">1.87918865680695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85676729679108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78950333595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301120281219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89880728721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91001784801483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690067768097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849272727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98568999767303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224870204926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766341686249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186697483063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326875686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97027540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00390768051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397413253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18888330459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1650607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13282990455627</t>
+    <t xml:space="preserve">1.85676717758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78950321674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631947517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301144123077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89880752563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001808643341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690043926239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849260807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98569011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224882125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9576632976532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186745166779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326863765717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027552127838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00390720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397389411926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18888378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16506099700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13283014297485</t>
   </si>
   <si>
     <t xml:space="preserve">2.06416511535645</t>
@@ -608,37 +608,37 @@
     <t xml:space="preserve">2.11601424217224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09499406814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1132116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14404082298279</t>
+    <t xml:space="preserve">2.09499430656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11321139335632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14404010772705</t>
   </si>
   <si>
     <t xml:space="preserve">2.13002729415894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14824485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13423156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14123821258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13703417778015</t>
+    <t xml:space="preserve">2.14824461936951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13423109054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14123797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15244841575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13703393936157</t>
   </si>
   <si>
     <t xml:space="preserve">2.11181020736694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09779691696167</t>
+    <t xml:space="preserve">2.09779667854309</t>
   </si>
   <si>
     <t xml:space="preserve">2.11881685256958</t>
@@ -647,70 +647,70 @@
     <t xml:space="preserve">2.10200095176697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11741542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24213433265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48876857757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48736763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297261238098</t>
+    <t xml:space="preserve">2.1174156665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213409423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48876881599426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4873673915863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297285079956</t>
   </si>
   <si>
     <t xml:space="preserve">2.48316359519958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46494626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40328741073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099967002869</t>
+    <t xml:space="preserve">2.46494603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40328764915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52099943161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.48036074638367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46634745597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4439263343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43972206115723</t>
+    <t xml:space="preserve">2.46634769439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44392609596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43972253799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.47615671157837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45513653755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437475204468</t>
+    <t xml:space="preserve">2.45513677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437379837036</t>
   </si>
   <si>
     <t xml:space="preserve">2.47335433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65552735328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71858787536621</t>
+    <t xml:space="preserve">2.65552759170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71858739852905</t>
   </si>
   <si>
     <t xml:space="preserve">2.70457410812378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84751057624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.788654088974</t>
+    <t xml:space="preserve">2.84751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865456581116</t>
   </si>
   <si>
     <t xml:space="preserve">3.11096119880676</t>
@@ -719,130 +719,130 @@
     <t xml:space="preserve">3.2398841381073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129488945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003127098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040809631348</t>
+    <t xml:space="preserve">3.38422083854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129393577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040833473206</t>
   </si>
   <si>
     <t xml:space="preserve">3.69251418113708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66098475456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78360152244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176100730896</t>
+    <t xml:space="preserve">3.6609845161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601798057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7836012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95176124572754</t>
   </si>
   <si>
     <t xml:space="preserve">4.06386852264404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19349098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16896772384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11291408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03233766555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30910110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30559921264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55433511734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69797134399414</t>
+    <t xml:space="preserve">4.19349193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16896867752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03233814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30910158157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30559825897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55433559417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6979718208313</t>
   </si>
   <si>
     <t xml:space="preserve">5.50023555755615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79256105422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10085535049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01677560806274</t>
+    <t xml:space="preserve">4.79256153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10085582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01677513122559</t>
   </si>
   <si>
     <t xml:space="preserve">5.44768524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44418239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77349519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39708852767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143503189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369230270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858285903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626602172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53252840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35266780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07208633422852</t>
+    <t xml:space="preserve">5.4441819190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77349472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3970890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518251419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238851547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369277954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78433322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5325288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35266828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0720853805542</t>
   </si>
   <si>
     <t xml:space="preserve">6.32389068603516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43900108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40302896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798851013184</t>
+    <t xml:space="preserve">6.43900203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40302848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15842008590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798755645752</t>
   </si>
   <si>
     <t xml:space="preserve">6.37425088882446</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">6.32748699188232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15122509002686</t>
+    <t xml:space="preserve">6.15122556686401</t>
   </si>
   <si>
     <t xml:space="preserve">6.11165475845337</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">5.93898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85265684127808</t>
+    <t xml:space="preserve">5.96057271957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85265588760376</t>
   </si>
   <si>
     <t xml:space="preserve">5.90661478042603</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">5.70157384872437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3670334815979</t>
+    <t xml:space="preserve">5.36703395843506</t>
   </si>
   <si>
     <t xml:space="preserve">4.87421560287476</t>
@@ -896,40 +896,40 @@
     <t xml:space="preserve">4.97853517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96414566040039</t>
+    <t xml:space="preserve">4.96414661407471</t>
   </si>
   <si>
     <t xml:space="preserve">4.8454384803772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87781381607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9101881980896</t>
+    <t xml:space="preserve">4.8778133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018724441528</t>
   </si>
   <si>
     <t xml:space="preserve">4.70155000686646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92457723617554</t>
+    <t xml:space="preserve">4.92457628250122</t>
   </si>
   <si>
     <t xml:space="preserve">4.76989698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69075775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65838384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68716096878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82385587692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55046796798706</t>
+    <t xml:space="preserve">4.690758228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6583833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68716144561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82385540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5504674911499</t>
   </si>
   <si>
     <t xml:space="preserve">4.51089811325073</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">4.49291181564331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4389533996582</t>
+    <t xml:space="preserve">4.43895387649536</t>
   </si>
   <si>
     <t xml:space="preserve">4.38139915466309</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">4.38499593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46413373947144</t>
+    <t xml:space="preserve">4.46413421630859</t>
   </si>
   <si>
     <t xml:space="preserve">5.03609085083008</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">4.76629972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68356418609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67636919021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60442638397217</t>
+    <t xml:space="preserve">4.68356513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67637014389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60442543029785</t>
   </si>
   <si>
     <t xml:space="preserve">4.59003686904907</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198062896729</t>
+    <t xml:space="preserve">4.66198015213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.67277240753174</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">4.74831390380859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75910568237305</t>
+    <t xml:space="preserve">4.75910520553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.95335483551025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83105039596558</t>
+    <t xml:space="preserve">4.83104991912842</t>
   </si>
   <si>
     <t xml:space="preserve">5.06486797332764</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">5.14400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152286529541</t>
+    <t xml:space="preserve">5.11522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.19436740875244</t>
@@ -1022,37 +1022,37 @@
     <t xml:space="preserve">4.90659093856812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92097997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82025766372681</t>
+    <t xml:space="preserve">4.92097949981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82025814056396</t>
   </si>
   <si>
     <t xml:space="preserve">4.89220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05407667160034</t>
+    <t xml:space="preserve">5.05407619476318</t>
   </si>
   <si>
     <t xml:space="preserve">5.07925748825073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0181040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95695209503174</t>
+    <t xml:space="preserve">5.01810359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.94616031646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15839576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23393678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60804605484009</t>
+    <t xml:space="preserve">5.15839529037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23393726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60804653167725</t>
   </si>
   <si>
     <t xml:space="preserve">5.89942026138306</t>
@@ -1061,58 +1061,58 @@
     <t xml:space="preserve">5.77711486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03611421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978141784668</t>
+    <t xml:space="preserve">6.03611373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978189468384</t>
   </si>
   <si>
     <t xml:space="preserve">6.18000268936157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20878028869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52533388137817</t>
+    <t xml:space="preserve">6.20877981185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52533435821533</t>
   </si>
   <si>
     <t xml:space="preserve">7.03613758087158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89584589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527681350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802474975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12968921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43904876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2951831817627</t>
+    <t xml:space="preserve">6.89584684371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13685989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802331924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12968826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43904781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29518413543701</t>
   </si>
   <si>
     <t xml:space="preserve">10.2160692214966</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42465972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61890888214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321605682373</t>
+    <t xml:space="preserve">8.42466068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6189079284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.0145788192749</t>
@@ -1121,118 +1121,118 @@
     <t xml:space="preserve">7.80594062805176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32393741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.992995262146</t>
+    <t xml:space="preserve">8.32393836975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99299383163452</t>
   </si>
   <si>
     <t xml:space="preserve">8.10091114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98580169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88507795333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73399591445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41024684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54694175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5253586769104</t>
+    <t xml:space="preserve">7.98580026626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8850793838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73399543762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41024732589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54694128036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535772323608</t>
   </si>
   <si>
     <t xml:space="preserve">7.38866376876831</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23760414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84191131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910678863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824506759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630035400391</t>
+    <t xml:space="preserve">8.23760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910726547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04335689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824602127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85630178451538</t>
   </si>
   <si>
     <t xml:space="preserve">7.74838542938232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57571887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19441366195679</t>
+    <t xml:space="preserve">7.57571935653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42463493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.96419382095337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21599817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498416900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2088041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20160865783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25196981430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448551177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00735998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844249725342</t>
+    <t xml:space="preserve">7.21599721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20160913467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25197076797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2447772026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18721961975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00735950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844202041626</t>
   </si>
   <si>
     <t xml:space="preserve">6.91742992401123</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">6.85627746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.892249584198</t>
+    <t xml:space="preserve">6.89224910736084</t>
   </si>
   <si>
     <t xml:space="preserve">6.78793048858643</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95699977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98218011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203927993774</t>
+    <t xml:space="preserve">6.95699882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541669845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217964172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16204023361206</t>
   </si>
   <si>
     <t xml:space="preserve">7.14045667648315</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">7.338303565979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82752275466919</t>
+    <t xml:space="preserve">7.82752323150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.25918769836426</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">8.15846633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91385698318481</t>
+    <t xml:space="preserve">7.91385507583618</t>
   </si>
   <si>
     <t xml:space="preserve">7.89946746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313467025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76996850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046764373779</t>
+    <t xml:space="preserve">7.81313419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76996755599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046907424927</t>
   </si>
   <si>
     <t xml:space="preserve">7.78435659408569</t>
@@ -1304,103 +1304,103 @@
     <t xml:space="preserve">6.79152727127075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74836158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6404447555542</t>
+    <t xml:space="preserve">6.74836111068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64044523239136</t>
   </si>
   <si>
     <t xml:space="preserve">6.48936223983765</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63325023651123</t>
+    <t xml:space="preserve">6.63325071334839</t>
   </si>
   <si>
     <t xml:space="preserve">6.62605667114258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56130647659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791904449463</t>
+    <t xml:space="preserve">6.56130599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791856765747</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02172517776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87783670425415</t>
+    <t xml:space="preserve">6.02172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
     <t xml:space="preserve">5.86344766616821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25914096832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4677791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641639709473</t>
+    <t xml:space="preserve">6.25914192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619655609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46777868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641735076904</t>
   </si>
   <si>
     <t xml:space="preserve">6.51814031600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46058464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2951135635376</t>
+    <t xml:space="preserve">6.46058416366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29511260986328</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086297988892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13683557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92819786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93539237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89222478866577</t>
+    <t xml:space="preserve">6.1368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92819738388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93539142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89222574234009</t>
   </si>
   <si>
     <t xml:space="preserve">5.79869890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97136449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01453018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99294757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17280769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18719673156738</t>
+    <t xml:space="preserve">5.97136354446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01453113555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99294805526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17280721664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18719720840454</t>
   </si>
   <si>
     <t xml:space="preserve">6.25194644927979</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">6.12244701385498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27353048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950212478638</t>
+    <t xml:space="preserve">6.27353000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950307846069</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230760574341</t>
@@ -1430,121 +1430,121 @@
     <t xml:space="preserve">6.38323211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46564483642578</t>
+    <t xml:space="preserve">6.46564435958862</t>
   </si>
   <si>
     <t xml:space="preserve">6.35326242446899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30831146240234</t>
+    <t xml:space="preserve">6.3083119392395</t>
   </si>
   <si>
     <t xml:space="preserve">6.59300899505615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41319942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17345428466797</t>
+    <t xml:space="preserve">6.41320085525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17345380783081</t>
   </si>
   <si>
     <t xml:space="preserve">6.09853410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90374040603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618391036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94120073318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86627960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9486927986145</t>
+    <t xml:space="preserve">5.90373992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94120025634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8662805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94869232177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.84380435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59656620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48418569564819</t>
+    <t xml:space="preserve">5.59656572341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48418474197388</t>
   </si>
   <si>
     <t xml:space="preserve">5.60405778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55910539627075</t>
+    <t xml:space="preserve">5.55910587310791</t>
   </si>
   <si>
     <t xml:space="preserve">5.888756275177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80634355545044</t>
+    <t xml:space="preserve">5.80634307861328</t>
   </si>
   <si>
     <t xml:space="preserve">5.64151811599731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79135990142822</t>
+    <t xml:space="preserve">5.79135894775391</t>
   </si>
   <si>
     <t xml:space="preserve">5.76139116287231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88126373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621660232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078622817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55554914474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815229415894</t>
+    <t xml:space="preserve">5.88126420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621612548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078718185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55554866790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815277099609</t>
   </si>
   <si>
     <t xml:space="preserve">6.33827924728394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12850189208984</t>
+    <t xml:space="preserve">6.3008189201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.128502368927</t>
   </si>
   <si>
     <t xml:space="preserve">6.06107330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77637481689453</t>
+    <t xml:space="preserve">5.77637529373169</t>
   </si>
   <si>
     <t xml:space="preserve">5.76888275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70145511627197</t>
+    <t xml:space="preserve">5.70145416259766</t>
   </si>
   <si>
     <t xml:space="preserve">5.66399431228638</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57409048080444</t>
+    <t xml:space="preserve">5.57409000396729</t>
   </si>
   <si>
     <t xml:space="preserve">5.75389862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78386735916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67897891998291</t>
+    <t xml:space="preserve">5.78386688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
     <t xml:space="preserve">5.62653398513794</t>
@@ -1553,37 +1553,37 @@
     <t xml:space="preserve">5.61904191970825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65650272369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54412126541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58158206939697</t>
+    <t xml:space="preserve">5.65650224685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54412174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58158159255981</t>
   </si>
   <si>
     <t xml:space="preserve">5.50666093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53662919998169</t>
+    <t xml:space="preserve">5.53662872314453</t>
   </si>
   <si>
     <t xml:space="preserve">5.43174076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46920156478882</t>
+    <t xml:space="preserve">5.4692006111145</t>
   </si>
   <si>
     <t xml:space="preserve">5.31935977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189945220947</t>
+    <t xml:space="preserve">5.28189992904663</t>
   </si>
   <si>
     <t xml:space="preserve">5.42424869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49167728424072</t>
+    <t xml:space="preserve">5.49167680740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415348052979</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">5.27440738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18450260162354</t>
+    <t xml:space="preserve">5.18450307846069</t>
   </si>
   <si>
     <t xml:space="preserve">5.2069787979126</t>
@@ -1607,46 +1607,46 @@
     <t xml:space="preserve">5.74640703201294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47669315338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21447134017944</t>
+    <t xml:space="preserve">5.47669363021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21447086334229</t>
   </si>
   <si>
     <t xml:space="preserve">5.13955068588257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0945987701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10958194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07212209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01967716217041</t>
+    <t xml:space="preserve">5.09459829330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10958242416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07212162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05713796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967763900757</t>
   </si>
   <si>
     <t xml:space="preserve">5.03466176986694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92977333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86983633041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73497915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77243995666504</t>
+    <t xml:space="preserve">4.92977285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732934951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86983680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7349796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77243947982788</t>
   </si>
   <si>
     <t xml:space="preserve">4.82488441467285</t>
@@ -1655,34 +1655,34 @@
     <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75745487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234426498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89980506896973</t>
+    <t xml:space="preserve">4.75745534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234378814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9147891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
     <t xml:space="preserve">4.85485172271729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95224952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16951847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710527420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13205814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840667724609</t>
+    <t xml:space="preserve">4.95224905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16951894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08710622787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13205862045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840572357178</t>
   </si>
   <si>
     <t xml:space="preserve">6.25586700439453</t>
@@ -1691,31 +1691,31 @@
     <t xml:space="preserve">6.01612091064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10602569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99364471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04215431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221778869629</t>
+    <t xml:space="preserve">6.10602521896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99364519119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04215383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221731185913</t>
   </si>
   <si>
     <t xml:space="preserve">4.94475698471069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99720096588135</t>
+    <t xml:space="preserve">4.99720144271851</t>
   </si>
   <si>
     <t xml:space="preserve">5.02716970443726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89231252670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964637756348</t>
+    <t xml:space="preserve">4.89231300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964542388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.95974111557007</t>
@@ -1724,52 +1724,52 @@
     <t xml:space="preserve">4.81739187240601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7949161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78742408752441</t>
+    <t xml:space="preserve">4.79491567611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78742361068726</t>
   </si>
   <si>
     <t xml:space="preserve">4.83237600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97472476959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76494741439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47275733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047204971313</t>
+    <t xml:space="preserve">4.97472524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76494789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4727578163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047157287598</t>
   </si>
   <si>
     <t xml:space="preserve">4.38285255432129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32291603088379</t>
+    <t xml:space="preserve">4.32291650772095</t>
   </si>
   <si>
     <t xml:space="preserve">4.18056726455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16558313369751</t>
+    <t xml:space="preserve">4.16558265686035</t>
   </si>
   <si>
     <t xml:space="preserve">4.30043983459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31542444229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46526575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777320861816</t>
+    <t xml:space="preserve">4.3154239654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46526527404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777368545532</t>
   </si>
   <si>
     <t xml:space="preserve">4.71250343322754</t>
@@ -1778,34 +1778,34 @@
     <t xml:space="preserve">5.10208988189697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07961368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726491928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218557357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443912506104</t>
+    <t xml:space="preserve">5.07961416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443960189819</t>
   </si>
   <si>
     <t xml:space="preserve">5.22196340560913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25942325592041</t>
+    <t xml:space="preserve">5.25942277908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.19948673248291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11707401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.289391040802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202688217163</t>
+    <t xml:space="preserve">5.11707353591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28939199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202640533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.31186819076538</t>
@@ -1820,16 +1820,16 @@
     <t xml:space="preserve">5.4467248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39427947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421648025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40926504135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89624738693237</t>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421743392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89624834060669</t>
   </si>
   <si>
     <t xml:space="preserve">5.85878801345825</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">6.12100982666016</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22589921951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383562088013</t>
+    <t xml:space="preserve">6.22589874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383514404297</t>
   </si>
   <si>
     <t xml:space="preserve">6.00113725662231</t>
@@ -1853,22 +1853,22 @@
     <t xml:space="preserve">5.82132768630981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91123247146606</t>
+    <t xml:space="preserve">5.91123199462891</t>
   </si>
   <si>
     <t xml:space="preserve">6.03110551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00862979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631181716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377166748047</t>
+    <t xml:space="preserve">6.008629322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872406005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377214431763</t>
   </si>
   <si>
     <t xml:space="preserve">5.97116851806641</t>
@@ -1880,46 +1880,46 @@
     <t xml:space="preserve">6.09104156494141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15097761154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859710693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866010665894</t>
+    <t xml:space="preserve">6.15097808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608869552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859758377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866106033325</t>
   </si>
   <si>
     <t xml:space="preserve">5.69396257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72393035888672</t>
+    <t xml:space="preserve">5.72393083572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.7089467048645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49916887283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73891496658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161333084106</t>
+    <t xml:space="preserve">5.49916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170902252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73891448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161380767822</t>
   </si>
   <si>
     <t xml:space="preserve">5.47268533706665</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">5.33155632019043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46484518051147</t>
+    <t xml:space="preserve">5.46484470367432</t>
   </si>
   <si>
     <t xml:space="preserve">5.35507726669312</t>
@@ -1943,16 +1943,16 @@
     <t xml:space="preserve">5.37859964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39427995681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24531030654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26883125305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451251983643</t>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26883172988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451299667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.25315093994141</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">5.06497812271118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00225400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690492630005</t>
+    <t xml:space="preserve">5.00225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690540313721</t>
   </si>
   <si>
     <t xml:space="preserve">5.20610761642456</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">5.29235315322876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11986255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13554382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09634017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11202144622803</t>
+    <t xml:space="preserve">5.11986207962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13554286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09634065628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11202096939087</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474555969238</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">5.44916391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45700407028198</t>
+    <t xml:space="preserve">5.45700454711914</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">5.70790147781372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67653894424438</t>
+    <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733673095703</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">5.51188802719116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48836612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48052597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36291885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31587553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3237156867981</t>
+    <t xml:space="preserve">5.48836660385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48052644729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36291790008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31587505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">5.19826745986938</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">4.71999549865723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51614236831665</t>
+    <t xml:space="preserve">4.51614141464233</t>
   </si>
   <si>
     <t xml:space="preserve">4.97089195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82192277908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64159059524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71215534210205</t>
+    <t xml:space="preserve">4.82192230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64158964157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71215486526489</t>
   </si>
   <si>
     <t xml:space="preserve">4.67295217514038</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">4.62590885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68079280853271</t>
+    <t xml:space="preserve">4.68079233169556</t>
   </si>
   <si>
     <t xml:space="preserve">4.90032720565796</t>
@@ -2087,28 +2087,28 @@
     <t xml:space="preserve">5.02577543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04145622253418</t>
+    <t xml:space="preserve">5.04145669937134</t>
   </si>
   <si>
     <t xml:space="preserve">5.15122413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22178888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21394824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15906429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08065938949585</t>
+    <t xml:space="preserve">5.22178840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21394872665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15906476974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08065891265869</t>
   </si>
   <si>
     <t xml:space="preserve">5.1277027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01793575286865</t>
+    <t xml:space="preserve">5.01793527603149</t>
   </si>
   <si>
     <t xml:space="preserve">5.07281875610352</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">5.08850002288818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19042682647705</t>
+    <t xml:space="preserve">5.19042634963989</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
@@ -2132,37 +2132,37 @@
     <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5667724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4334831237793</t>
+    <t xml:space="preserve">5.56677198410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43348264694214</t>
   </si>
   <si>
     <t xml:space="preserve">5.50404787063599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53540992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41780185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42564296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84119033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76278448104858</t>
+    <t xml:space="preserve">5.53541040420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41780138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42564249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84118986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7627854347229</t>
   </si>
   <si>
     <t xml:space="preserve">5.64517736434937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44132423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40996122360229</t>
+    <t xml:space="preserve">5.44132375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40996170043945</t>
   </si>
   <si>
     <t xml:space="preserve">5.38643980026245</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">5.34723711013794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37075853347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2374701499939</t>
+    <t xml:space="preserve">5.37075901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23746967315674</t>
   </si>
   <si>
     <t xml:space="preserve">4.97873210906982</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">4.8376030921936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89248609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896514892578</t>
+    <t xml:space="preserve">4.89248704910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896467208862</t>
   </si>
   <si>
     <t xml:space="preserve">4.92384910583496</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">4.87680578231812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98657369613647</t>
+    <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
     <t xml:space="preserve">4.57102537155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54750394821167</t>
+    <t xml:space="preserve">4.54750442504883</t>
   </si>
   <si>
     <t xml:space="preserve">4.57886648178101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39069318771362</t>
+    <t xml:space="preserve">4.39069366455078</t>
   </si>
   <si>
     <t xml:space="preserve">4.15547752380371</t>
@@ -2219,91 +2219,91 @@
     <t xml:space="preserve">4.1162748336792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84185671806335</t>
+    <t xml:space="preserve">3.84185695648193</t>
   </si>
   <si>
     <t xml:space="preserve">3.63800311088562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26165747642517</t>
+    <t xml:space="preserve">3.26165771484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.29301977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32438182830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099382400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09700679779053</t>
+    <t xml:space="preserve">3.32438158988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099406242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09700655937195</t>
   </si>
   <si>
     <t xml:space="preserve">3.05780458450317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94803690910339</t>
+    <t xml:space="preserve">2.94803667068481</t>
   </si>
   <si>
     <t xml:space="preserve">3.00292038917542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13620948791504</t>
+    <t xml:space="preserve">3.13620972633362</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036236763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21461462974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25381755828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2224555015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24205636978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23813652992249</t>
+    <t xml:space="preserve">3.21461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25381731987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22245526313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24205684661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24597668647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23813629150391</t>
   </si>
   <si>
     <t xml:space="preserve">3.36750507354736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34006333351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45767045021057</t>
+    <t xml:space="preserve">3.34006309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45767116546631</t>
   </si>
   <si>
     <t xml:space="preserve">3.59880042076111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37142562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52039527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54391694068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72424912452698</t>
+    <t xml:space="preserve">3.37142539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52039480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54391646385193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7242488861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.81049466133118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92026257514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3358097076416</t>
+    <t xml:space="preserve">3.9202618598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33581018447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.32796907424927</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">4.32012891769409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23388242721558</t>
+    <t xml:space="preserve">4.23388290405273</t>
   </si>
   <si>
     <t xml:space="preserve">4.16331815719604</t>
@@ -2324,55 +2324,55 @@
     <t xml:space="preserve">4.21820211410522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21036148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740385055542</t>
+    <t xml:space="preserve">4.21036100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740432739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208975791931</t>
+    <t xml:space="preserve">3.73208928108215</t>
   </si>
   <si>
     <t xml:space="preserve">3.79481387138367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83401584625244</t>
+    <t xml:space="preserve">3.83401608467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.84577703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70072722434998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009600639343</t>
+    <t xml:space="preserve">3.7007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009648323059</t>
   </si>
   <si>
     <t xml:space="preserve">3.87321853637695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80265402793884</t>
+    <t xml:space="preserve">3.80265355110168</t>
   </si>
   <si>
     <t xml:space="preserve">3.82225513458252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86145853996277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169014930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74385046958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298621177673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660654067993</t>
+    <t xml:space="preserve">3.86145806312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385023117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660749435425</t>
   </si>
   <si>
     <t xml:space="preserve">4.10059404373169</t>
@@ -2384,121 +2384,121 @@
     <t xml:space="preserve">3.95946478843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03786993026733</t>
+    <t xml:space="preserve">4.03786945343018</t>
   </si>
   <si>
     <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763736724854</t>
+    <t xml:space="preserve">4.14763689041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.01434803009033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95162415504456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94378328323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88889956474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05355072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03002882003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89281964302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242146492004</t>
+    <t xml:space="preserve">3.95162391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9437837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8889000415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.053551197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89282011985779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810225486755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242122650146</t>
   </si>
   <si>
     <t xml:space="preserve">3.85753798484802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86537790298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617592811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105893135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458059310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90850186347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913212776184</t>
+    <t xml:space="preserve">3.8653781414032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617545127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913331985474</t>
   </si>
   <si>
     <t xml:space="preserve">3.755610704422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74777054786682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657434463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497924804688</t>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657410621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497972488403</t>
   </si>
   <si>
     <t xml:space="preserve">3.96730470657349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02218914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345133781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75953125953674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64584374427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6693651676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544508934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016223907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56351757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56743836402893</t>
+    <t xml:space="preserve">4.02218866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594288825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345181465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64584302902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66936540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544556617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016247749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56351804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56743860244751</t>
   </si>
   <si>
     <t xml:space="preserve">3.5909595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48903322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44198966026306</t>
+    <t xml:space="preserve">3.48903274536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119282722473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44198989868164</t>
   </si>
   <si>
     <t xml:space="preserve">3.38710641860962</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">3.31654167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33222246170044</t>
+    <t xml:space="preserve">3.33222270011902</t>
   </si>
   <si>
     <t xml:space="preserve">3.40278744697571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42238879203796</t>
+    <t xml:space="preserve">3.42238855361938</t>
   </si>
   <si>
     <t xml:space="preserve">3.43807005882263</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">3.46551156044006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49295330047607</t>
+    <t xml:space="preserve">3.49295353889465</t>
   </si>
   <si>
     <t xml:space="preserve">3.55175757408142</t>
@@ -2531,55 +2531,55 @@
     <t xml:space="preserve">3.55567765235901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50079417228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51255464553833</t>
+    <t xml:space="preserve">3.50079393386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51255488395691</t>
   </si>
   <si>
     <t xml:space="preserve">3.37926578521729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43414974212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630863189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46159076690674</t>
+    <t xml:space="preserve">3.43414926528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630887031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4615912437439</t>
   </si>
   <si>
     <t xml:space="preserve">3.4498302936554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15189027786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20677447319031</t>
+    <t xml:space="preserve">3.15189051628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20677423477173</t>
   </si>
   <si>
     <t xml:space="preserve">3.17541241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52823543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215622901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607678413391</t>
+    <t xml:space="preserve">3.52823567390442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607654571533</t>
   </si>
   <si>
     <t xml:space="preserve">4.10843420028687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99866676330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252084732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13195562362671</t>
+    <t xml:space="preserve">3.99866700172424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2025203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13195610046387</t>
   </si>
   <si>
     <t xml:space="preserve">4.09275341033936</t>
@@ -2603,49 +2603,49 @@
     <t xml:space="preserve">4.35933065414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69647312164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976245880127</t>
+    <t xml:space="preserve">4.69647359848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75919771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976293563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.7278356552124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74351739883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76703834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487897872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73567628860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80624103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01009464263916</t>
+    <t xml:space="preserve">4.74351692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76703882217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487993240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73567676544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68863344192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80624151229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.010094165802</t>
   </si>
   <si>
     <t xml:space="preserve">4.99441337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94737100601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86112451553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84544372558594</t>
+    <t xml:space="preserve">4.9473705291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86112499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8454442024231</t>
   </si>
   <si>
     <t xml:space="preserve">4.91600847244263</t>
@@ -2654,73 +2654,73 @@
     <t xml:space="preserve">4.93952989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04929780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68438005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59813356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6294960975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7157416343689</t>
+    <t xml:space="preserve">5.04929733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245229721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68437957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59813451766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62949562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71574211120605</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222068786621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66869926452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66085767745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72358179092407</t>
+    <t xml:space="preserve">5.66869831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66085863113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72358226776123</t>
   </si>
   <si>
     <t xml:space="preserve">5.78630638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08424663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17833280563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14697122573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97447919845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720331192017</t>
+    <t xml:space="preserve">6.08424711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17833232879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14697074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288362503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97447872161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00474452972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11834859848022</t>
+    <t xml:space="preserve">6.00474500656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11834812164307</t>
   </si>
   <si>
     <t xml:space="preserve">6.49161577224731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45915794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4266996383667</t>
+    <t xml:space="preserve">6.45915842056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42670059204102</t>
   </si>
   <si>
     <t xml:space="preserve">6.26440954208374</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">6.39424228668213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4429292678833</t>
+    <t xml:space="preserve">6.44292974472046</t>
   </si>
   <si>
     <t xml:space="preserve">6.96225833892822</t>
@@ -2741,112 +2741,112 @@
     <t xml:space="preserve">7.14077806472778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43290090560913</t>
+    <t xml:space="preserve">7.43289995193481</t>
   </si>
   <si>
     <t xml:space="preserve">8.00091743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83862686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87108516693115</t>
+    <t xml:space="preserve">7.83862638473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87108421325684</t>
   </si>
   <si>
     <t xml:space="preserve">7.78993988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91977262496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95223093032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90354204177856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60139179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64196300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56081771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43910026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19566535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23623847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01714611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06583213806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96845865249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40044260025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25438165664673</t>
+    <t xml:space="preserve">7.91977214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95222997665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90354251861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60139274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6419620513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56081962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43910121917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19566631317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01714515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06583309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96845960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4004430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25438070297241</t>
   </si>
   <si>
     <t xml:space="preserve">7.4815878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6438775062561</t>
+    <t xml:space="preserve">7.64387798309326</t>
   </si>
   <si>
     <t xml:space="preserve">7.5627326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69256496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502326965332</t>
+    <t xml:space="preserve">7.69256448745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502374649048</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6276478767395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306911468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192335128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81619739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15700578689575</t>
+    <t xml:space="preserve">7.62764930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4653582572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3030686378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192287445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81619691848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15700721740723</t>
   </si>
   <si>
     <t xml:space="preserve">7.23815202713013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38421440124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70879459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61142063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010713577271</t>
+    <t xml:space="preserve">7.38421392440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70879507064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61141967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010761260986</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
@@ -2858,43 +2858,43 @@
     <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1550931930542</t>
+    <t xml:space="preserve">8.15509414672852</t>
   </si>
   <si>
     <t xml:space="preserve">8.96654605865479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84482669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368141174316</t>
+    <t xml:space="preserve">8.84482765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368236541748</t>
   </si>
   <si>
     <t xml:space="preserve">8.5202465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39853000640869</t>
+    <t xml:space="preserve">8.39852905273438</t>
   </si>
   <si>
     <t xml:space="preserve">8.47967433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31738471984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08206272125244</t>
+    <t xml:space="preserve">8.31738376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08206367492676</t>
   </si>
   <si>
     <t xml:space="preserve">8.11452007293701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03337574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04960536956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04769039154053</t>
+    <t xml:space="preserve">8.03337478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04960441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04768943786621</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40344905853271</t>
+    <t xml:space="preserve">9.40345001220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.23627758026123</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">9.48703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77958679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6124153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57062149047852</t>
+    <t xml:space="preserve">9.7795877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61241436004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57062244415283</t>
   </si>
   <si>
     <t xml:space="preserve">9.52882766723633</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420913696289</t>
+    <t xml:space="preserve">9.73779487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420818328857</t>
   </si>
   <si>
     <t xml:space="preserve">9.90496635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31986236572266</t>
+    <t xml:space="preserve">9.31986331939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15268993377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013984680176</t>
+    <t xml:space="preserve">9.15269088745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013889312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.7765531539917</t>
@@ -2963,28 +2963,28 @@
     <t xml:space="preserve">8.6093807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19448375701904</t>
+    <t xml:space="preserve">9.19448280334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11089611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06910514831543</t>
+    <t xml:space="preserve">9.11089706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36165523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06910610198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.94372463226318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.901930809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81834602355957</t>
+    <t xml:space="preserve">8.90193176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81834697723389</t>
   </si>
   <si>
     <t xml:space="preserve">8.56758785247803</t>
@@ -2993,13 +2993,13 @@
     <t xml:space="preserve">8.52579307556152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7347583770752</t>
+    <t xml:space="preserve">8.73476028442383</t>
   </si>
   <si>
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846881866455</t>
+    <t xml:space="preserve">8.30846977233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.32518768310547</t>
@@ -3008,43 +3008,43 @@
     <t xml:space="preserve">7.65649747848511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82366991043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321443557739</t>
+    <t xml:space="preserve">7.82366943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321538925171</t>
   </si>
   <si>
     <t xml:space="preserve">7.12154626846313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07139444351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10482788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68993234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589065551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053869247437</t>
+    <t xml:space="preserve">7.0713939666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10482835769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68993186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053916931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.80695247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62306261062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99084186553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04099369049072</t>
+    <t xml:space="preserve">7.62306308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99084281921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09114646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04099464416504</t>
   </si>
   <si>
     <t xml:space="preserve">8.27503490447998</t>
@@ -3053,25 +3053,25 @@
     <t xml:space="preserve">8.40041542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10786247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48400020599365</t>
+    <t xml:space="preserve">8.1078634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48400115966797</t>
   </si>
   <si>
     <t xml:space="preserve">8.30011177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35026359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24996089935303</t>
+    <t xml:space="preserve">8.35026264190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.8738226890564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69829034805298</t>
+    <t xml:space="preserve">7.69828987121582</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">7.77351856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91561412811279</t>
+    <t xml:space="preserve">7.91561603546143</t>
   </si>
   <si>
     <t xml:space="preserve">7.78187656402588</t>
@@ -3098,19 +3098,19 @@
     <t xml:space="preserve">7.79859447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79023551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978052139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41302824020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64850234985352</t>
+    <t xml:space="preserve">7.79023504257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41302871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64850187301636</t>
   </si>
   <si>
     <t xml:space="preserve">8.24154376983643</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">8.21538066864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28514957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32003402709961</t>
+    <t xml:space="preserve">8.28514862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32003498077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19793701171875</t>
+    <t xml:space="preserve">8.19793796539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.49445819854736</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678630828857</t>
+    <t xml:space="preserve">8.54678535461426</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">8.45957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177391052246</t>
+    <t xml:space="preserve">8.17177486419678</t>
   </si>
   <si>
     <t xml:space="preserve">8.1281681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93630218505859</t>
+    <t xml:space="preserve">7.93630123138428</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827077865601</t>
+    <t xml:space="preserve">7.71827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">7.77931928634644</t>
@@ -3182,43 +3182,43 @@
     <t xml:space="preserve">7.95374345779419</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14560985565186</t>
+    <t xml:space="preserve">8.14561080932617</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86653184890747</t>
+    <t xml:space="preserve">7.86653232574463</t>
   </si>
   <si>
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804063796997</t>
+    <t xml:space="preserve">7.78804016113281</t>
   </si>
   <si>
     <t xml:space="preserve">7.65722274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76187705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6921067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70082807540894</t>
+    <t xml:space="preserve">7.76187658309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69210767745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70082855224609</t>
   </si>
   <si>
     <t xml:space="preserve">7.5961742401123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46535587310791</t>
+    <t xml:space="preserve">7.46535634994507</t>
   </si>
   <si>
     <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571395874023</t>
+    <t xml:space="preserve">7.73571300506592</t>
   </si>
   <si>
     <t xml:space="preserve">7.50024080276489</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256748199463</t>
+    <t xml:space="preserve">7.55256843566895</t>
   </si>
   <si>
     <t xml:space="preserve">7.447913646698</t>
@@ -3242,19 +3242,19 @@
     <t xml:space="preserve">7.50896167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57001113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80548334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74443435668945</t>
+    <t xml:space="preserve">7.57001066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80548286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74443483352661</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77353858947754</t>
+    <t xml:space="preserve">8.77353763580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.72121047973633</t>
@@ -3263,16 +3263,16 @@
     <t xml:space="preserve">8.48573684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5031795501709</t>
+    <t xml:space="preserve">8.50318050384521</t>
   </si>
   <si>
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34619808197021</t>
+    <t xml:space="preserve">8.41596698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3461971282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.02351379394531</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83164644241333</t>
+    <t xml:space="preserve">7.83164596557617</t>
   </si>
   <si>
     <t xml:space="preserve">7.66594362258911</t>
@@ -3293,31 +3293,31 @@
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9711856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68338680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33453750610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1688346862793</t>
+    <t xml:space="preserve">7.97118711471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33453798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16883516311646</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418085098267</t>
+    <t xml:space="preserve">7.06418037414551</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13395071029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12522840499878</t>
+    <t xml:space="preserve">7.13395023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12522888183594</t>
   </si>
   <si>
     <t xml:space="preserve">6.78510189056396</t>
@@ -3329,46 +3329,46 @@
     <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6368408203125</t>
+    <t xml:space="preserve">6.63684129714966</t>
   </si>
   <si>
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75315618515015</t>
+    <t xml:space="preserve">7.75315570831299</t>
   </si>
   <si>
     <t xml:space="preserve">7.4391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43047142028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49152040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2734899520874</t>
+    <t xml:space="preserve">7.43047189712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49151992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27348899841309</t>
   </si>
   <si>
     <t xml:space="preserve">7.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38686466217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3519811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31709623336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47407674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29093170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581663131714</t>
+    <t xml:space="preserve">7.38686513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35198068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31709575653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47407722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.290931224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581615447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.30837440490723</t>
@@ -3377,28 +3377,28 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663499832153</t>
+    <t xml:space="preserve">7.45663547515869</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03223419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10200500488281</t>
+    <t xml:space="preserve">7.85781049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03223514556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">8.15433216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09328269958496</t>
+    <t xml:space="preserve">8.05839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09328365325928</t>
   </si>
   <si>
     <t xml:space="preserve">8.00607109069824</t>
@@ -3407,31 +3407,31 @@
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072540283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584190368652</t>
+    <t xml:space="preserve">8.11072635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584095001221</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990751266479</t>
+    <t xml:space="preserve">7.97990703582764</t>
   </si>
   <si>
     <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90141725540161</t>
+    <t xml:space="preserve">7.90141677856445</t>
   </si>
   <si>
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885900497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82292652130127</t>
+    <t xml:space="preserve">7.91885852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82292556762695</t>
   </si>
   <si>
     <t xml:space="preserve">8.11944675445557</t>
@@ -3446,16 +3446,16 @@
     <t xml:space="preserve">8.337477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5293436050415</t>
+    <t xml:space="preserve">8.52934265136719</t>
   </si>
   <si>
     <t xml:space="preserve">8.94796180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87819290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89563369750977</t>
+    <t xml:space="preserve">8.87819194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89563465118408</t>
   </si>
   <si>
     <t xml:space="preserve">8.65144062042236</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">8.71248912811279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86075019836426</t>
+    <t xml:space="preserve">8.86074924468994</t>
   </si>
   <si>
     <t xml:space="preserve">8.93051910400391</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">8.6863260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15727043151855</t>
+    <t xml:space="preserve">9.15727138519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">8.91307735443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96540451049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00028896331787</t>
+    <t xml:space="preserve">8.96540355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00028800964355</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3518,22 +3518,22 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66888236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91124534606934</t>
+    <t xml:space="preserve">8.80842304229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66888332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91124629974365</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8567419052124</t>
+    <t xml:space="preserve">8.82040691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85674285888672</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422756195068</t>
+    <t xml:space="preserve">8.58422660827637</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498817443848</t>
+    <t xml:space="preserve">8.77498722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38438320159912</t>
+    <t xml:space="preserve">8.49339008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3843822479248</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453788757324</t>
+    <t xml:space="preserve">8.18453884124756</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896350860596</t>
+    <t xml:space="preserve">8.33896446228027</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09370040893555</t>
+    <t xml:space="preserve">8.09369945526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04828071594238</t>
+    <t xml:space="preserve">8.04827976226807</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644821166992</t>
+    <t xml:space="preserve">8.06644916534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3659,40 +3659,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919696807861</t>
+    <t xml:space="preserve">8.03919792175293</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94835901260376</t>
+    <t xml:space="preserve">8.00286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9483585357666</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9029393196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385461807251</t>
+    <t xml:space="preserve">7.95744276046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90293884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385557174683</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85752010345459</t>
+    <t xml:space="preserve">7.85751962661743</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210136413574</t>
+    <t xml:space="preserve">7.81210088729858</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126245498657</t>
+    <t xml:space="preserve">7.72126293182373</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568807601929</t>
+    <t xml:space="preserve">7.87568855285645</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950777053833</t>
+    <t xml:space="preserve">7.63950824737549</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49416637420654</t>
+    <t xml:space="preserve">7.4941668510437</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41241216659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4487476348877</t>
+    <t xml:space="preserve">7.4124116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44874715805054</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112440109253</t>
+    <t xml:space="preserve">6.73112392425537</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3779,13 +3779,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7220401763916</t>
+    <t xml:space="preserve">6.72204065322876</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486675262451</t>
+    <t xml:space="preserve">6.59486722946167</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3806,22 +3806,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272344589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699247360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31248998641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790967941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775308609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767669677734</t>
+    <t xml:space="preserve">7.01272296905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699295043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31249046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767621994019</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393339157104</t>
+    <t xml:space="preserve">7.79393291473389</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3842,31 +3842,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96652698516846</t>
+    <t xml:space="preserve">7.76668262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9665265083313</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.475998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607717514038</t>
+    <t xml:space="preserve">7.63042402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47599840164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607669830322</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523921966553</t>
+    <t xml:space="preserve">7.28523874282837</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264562606812</t>
+    <t xml:space="preserve">7.11264514923096</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225652694702</t>
+    <t xml:space="preserve">7.61225700378418</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890279769897</t>
+    <t xml:space="preserve">7.24890327453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -71215,7 +71215,7 @@
     </row>
     <row r="2561">
       <c r="A2561" s="1" t="n">
-        <v>46051.6910532407</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B2561" t="n">
         <v>9138</v>
@@ -71236,6 +71236,32 @@
         <v>1393</v>
       </c>
       <c r="H2561" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" s="1" t="n">
+        <v>46052.6385763889</v>
+      </c>
+      <c r="B2562" t="n">
+        <v>10264</v>
+      </c>
+      <c r="C2562" t="n">
+        <v>10.6499996185303</v>
+      </c>
+      <c r="D2562" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E2562" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="F2562" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="G2562" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H2562" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19253504276276</t>
+    <t xml:space="preserve">1.19253516197205</t>
   </si>
   <si>
     <t xml:space="preserve">GE.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.21355509757996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22546637058258</t>
+    <t xml:space="preserve">1.22546648979187</t>
   </si>
   <si>
     <t xml:space="preserve">1.20654833316803</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">1.2499897480011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26330256462097</t>
+    <t xml:space="preserve">1.26330244541168</t>
   </si>
   <si>
     <t xml:space="preserve">1.27311170101166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26120042800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718701839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20794975757599</t>
+    <t xml:space="preserve">1.26120030879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718713760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2079496383667</t>
   </si>
   <si>
     <t xml:space="preserve">1.19323575496674</t>
@@ -83,28 +83,28 @@
     <t xml:space="preserve">1.19814050197601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2457857131958</t>
+    <t xml:space="preserve">1.24578583240509</t>
   </si>
   <si>
     <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495652198792</t>
+    <t xml:space="preserve">1.21495640277863</t>
   </si>
   <si>
     <t xml:space="preserve">1.18272566795349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17992293834686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641985416412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12457048892975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12807369232178</t>
+    <t xml:space="preserve">1.17992317676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12457036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12807381153107</t>
   </si>
   <si>
     <t xml:space="preserve">1.10284960269928</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">1.01596701145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02507567405701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02017104625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195384025574</t>
+    <t xml:space="preserve">1.0250757932663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02017092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195348262787</t>
   </si>
   <si>
     <t xml:space="preserve">1.02297377586365</t>
@@ -131,34 +131,34 @@
     <t xml:space="preserve">1.04329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09654378890991</t>
+    <t xml:space="preserve">1.09654366970062</t>
   </si>
   <si>
     <t xml:space="preserve">1.11335980892181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11055707931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0930403470993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106692790985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15610015392303</t>
+    <t xml:space="preserve">1.1105569601059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09304046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106716632843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017582893372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15610027313232</t>
   </si>
   <si>
     <t xml:space="preserve">1.10004723072052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13157713413239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705363750458</t>
+    <t xml:space="preserve">1.1315770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705375671387</t>
   </si>
   <si>
     <t xml:space="preserve">1.13227784633636</t>
@@ -167,52 +167,52 @@
     <t xml:space="preserve">1.11826431751251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14909398555756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17852175235748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17011380195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412709236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081451416016</t>
+    <t xml:space="preserve">1.14909362792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852187156677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1701135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412721157074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081439495087</t>
   </si>
   <si>
     <t xml:space="preserve">1.16310703754425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22616708278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2450852394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24088108539581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20514690876007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19113385677338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22686767578125</t>
+    <t xml:space="preserve">1.22616696357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508512020111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2408812046051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20514714717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113373756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22686791419983</t>
   </si>
   <si>
     <t xml:space="preserve">1.22196304798126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24438440799713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17221581935883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183433055878</t>
+    <t xml:space="preserve">1.24438452720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17221558094025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183444976807</t>
   </si>
   <si>
     <t xml:space="preserve">1.19743978977203</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">1.20374584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.203045129776</t>
+    <t xml:space="preserve">1.20304501056671</t>
   </si>
   <si>
     <t xml:space="preserve">1.23807847499847</t>
@@ -233,61 +233,61 @@
     <t xml:space="preserve">1.19954180717468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2247656583786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845996379852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916055679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2289696931839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21215379238129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22266387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2920298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29623377323151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521395683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2871253490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28151988983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788784980774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737776279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865035057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469920635223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138638973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11896526813507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036633491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13648164272308</t>
+    <t xml:space="preserve">1.22476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916043758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22896981239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21215391159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22266364097595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29202973842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29623365402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2752138376236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28712499141693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28151977062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788773059845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737788200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865046977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469908714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138627052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11896514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036645412445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13648176193237</t>
   </si>
   <si>
     <t xml:space="preserve">1.14629113674164</t>
@@ -296,40 +296,40 @@
     <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07202041149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08463227748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501364707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07061922550201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08253037929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902705669403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05800700187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10144829750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355019569397</t>
+    <t xml:space="preserve">1.0720202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.084632396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501352787018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07061898708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08253014087677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902693748474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05800712108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1014484167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355055332184</t>
   </si>
   <si>
     <t xml:space="preserve">1.09514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11966574192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934651851654</t>
+    <t xml:space="preserve">1.11966586112976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934639930725</t>
   </si>
   <si>
     <t xml:space="preserve">1.11265909671783</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">1.1568009853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34528040885925</t>
+    <t xml:space="preserve">1.34528052806854</t>
   </si>
   <si>
     <t xml:space="preserve">1.48681509494781</t>
@@ -347,40 +347,40 @@
     <t xml:space="preserve">1.48821651935577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45178186893463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4153470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45738697052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40133392810822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46999931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776857852936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375528812408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4363671541214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936062812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42235386371613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814994812012</t>
+    <t xml:space="preserve">1.45178198814392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41534721851349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45738708972931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40133380889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46999907493591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375516891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43636727333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936050891876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674840450287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42235374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">1.42795920372009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48120987415314</t>
+    <t xml:space="preserve">1.48120999336243</t>
   </si>
   <si>
     <t xml:space="preserve">1.6942126750946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338312625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071413516998</t>
+    <t xml:space="preserve">1.66338324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8007138967514</t>
   </si>
   <si>
     <t xml:space="preserve">1.84555649757385</t>
@@ -407,157 +407,157 @@
     <t xml:space="preserve">1.7923059463501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79090452194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268707752228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064744472504</t>
+    <t xml:space="preserve">1.79090464115143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268731594086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064720630646</t>
   </si>
   <si>
     <t xml:space="preserve">1.71663391590118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670048713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8427540063858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593774795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313513755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995127677917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83855009078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8441549539566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83014225959778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472718715668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874059677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192457675934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294451236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8693790435791</t>
+    <t xml:space="preserve">1.78670072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275388717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593786716461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313549518585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8399510383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854997158051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84415519237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014190196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472706794739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874071598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835934638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937940120697</t>
   </si>
   <si>
     <t xml:space="preserve">1.99549949169159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07257270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02913165092468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798718452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04034209251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830210208893</t>
+    <t xml:space="preserve">2.07257294654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0291314125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798742294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04034185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830222129822</t>
   </si>
   <si>
     <t xml:space="preserve">2.03053283691406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01932215690613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9997034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359288215637</t>
+    <t xml:space="preserve">2.01932191848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970316886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231551170349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066597938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15945529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989415168762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339245319366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167658805847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345973968506</t>
+    <t xml:space="preserve">2.1594557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989427089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339257240295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9716762304306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345938205719</t>
   </si>
   <si>
     <t xml:space="preserve">2.01651930809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428857326508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97868323326111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944573402405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91982734203339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377441883087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86797773838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918865680695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85676729679108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78950309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631959438324</t>
+    <t xml:space="preserve">2.00250601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9786833524704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944609165192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91982746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377394199371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86797785758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918841838837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85676753520966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78950333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631923675537</t>
   </si>
   <si>
     <t xml:space="preserve">1.90301144123077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89880764484406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91001772880554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690079689026</t>
+    <t xml:space="preserve">1.89880740642548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001749038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690043926239</t>
   </si>
   <si>
     <t xml:space="preserve">1.98849260807037</t>
@@ -566,58 +566,58 @@
     <t xml:space="preserve">1.98569011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94224882125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766377449036</t>
+    <t xml:space="preserve">1.94224834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766317844391</t>
   </si>
   <si>
     <t xml:space="preserve">1.96186709403992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96326887607574</t>
+    <t xml:space="preserve">1.96326863765717</t>
   </si>
   <si>
     <t xml:space="preserve">1.97027552127838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9660712480545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00390768051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397389411926</t>
+    <t xml:space="preserve">1.96607160568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00390696525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397413253784</t>
   </si>
   <si>
     <t xml:space="preserve">2.18888354301453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1650607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13283014297485</t>
+    <t xml:space="preserve">2.16506028175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13282990455627</t>
   </si>
   <si>
     <t xml:space="preserve">2.06416463851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09639525413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601400375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499406814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11321115493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14404082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002729415894</t>
+    <t xml:space="preserve">2.09639549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601424217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499430656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11321139335632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14404058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002705574036</t>
   </si>
   <si>
     <t xml:space="preserve">2.14824485778809</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">2.13423156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14123845100403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15244889259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13703393936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11180996894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09779691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11881685256958</t>
+    <t xml:space="preserve">2.14123797416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13703417778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11181020736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09779620170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11881637573242</t>
   </si>
   <si>
     <t xml:space="preserve">2.10200095176697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11741542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2421338558197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48876881599426</t>
+    <t xml:space="preserve">2.11741590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213433265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48876905441284</t>
   </si>
   <si>
     <t xml:space="preserve">2.4873673915863</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">2.49297285079956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48316311836243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46494579315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40328764915466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48036074638367</t>
+    <t xml:space="preserve">2.48316359519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46494626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4032871723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52099967002869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48036050796509</t>
   </si>
   <si>
     <t xml:space="preserve">2.46634745597839</t>
@@ -683,64 +683,64 @@
     <t xml:space="preserve">2.44392609596252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43972229957581</t>
+    <t xml:space="preserve">2.43972253799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.47615694999695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45513677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437403678894</t>
+    <t xml:space="preserve">2.45513653755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437427520752</t>
   </si>
   <si>
     <t xml:space="preserve">2.47335433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65552759170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71858787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70457434654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751057624817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865456581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11096143722534</t>
+    <t xml:space="preserve">2.6555278301239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71858763694763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70457458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78865432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11096096038818</t>
   </si>
   <si>
     <t xml:space="preserve">3.23988389968872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129488945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003127098083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66098475456238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601798057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78360080718994</t>
+    <t xml:space="preserve">3.38422107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129441261292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5804078578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251489639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6609845161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6960175037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7836012840271</t>
   </si>
   <si>
     <t xml:space="preserve">3.95176124572754</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">4.16896772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1129150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30910205841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30559825897217</t>
+    <t xml:space="preserve">4.11291456222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03233766555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30910158157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30559778213501</t>
   </si>
   <si>
     <t xml:space="preserve">4.55433511734009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6979718208313</t>
+    <t xml:space="preserve">4.69797086715698</t>
   </si>
   <si>
     <t xml:space="preserve">5.50023508071899</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.79256200790405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10085582733154</t>
+    <t xml:space="preserve">5.10085535049438</t>
   </si>
   <si>
     <t xml:space="preserve">5.01677513122559</t>
@@ -794,52 +794,52 @@
     <t xml:space="preserve">5.77349519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3970890045166</t>
+    <t xml:space="preserve">6.39708948135376</t>
   </si>
   <si>
     <t xml:space="preserve">6.76143550872803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49518203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858285903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78433418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626602172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5325288772583</t>
+    <t xml:space="preserve">6.49518251419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369325637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78433465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626649856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53252983093262</t>
   </si>
   <si>
     <t xml:space="preserve">6.35266876220703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07208633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.323890209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900060653687</t>
+    <t xml:space="preserve">6.07208585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32389068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900108337402</t>
   </si>
   <si>
     <t xml:space="preserve">6.51094579696655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4030294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841913223267</t>
+    <t xml:space="preserve">6.40302896499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15841865539551</t>
   </si>
   <si>
     <t xml:space="preserve">6.19798898696899</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">6.1512246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11165571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93899011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96057224273682</t>
+    <t xml:space="preserve">6.11165523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96057271957397</t>
   </si>
   <si>
     <t xml:space="preserve">5.85265636444092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90661430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89582300186157</t>
+    <t xml:space="preserve">5.90661478042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89582252502441</t>
   </si>
   <si>
     <t xml:space="preserve">5.75193452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6943793296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70157384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3670334815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87421655654907</t>
+    <t xml:space="preserve">5.69437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70157337188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36703300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87421560287476</t>
   </si>
   <si>
     <t xml:space="preserve">5.17997884750366</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">4.96414613723755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84543800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8778133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018772125244</t>
+    <t xml:space="preserve">4.84543895721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87781381607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9101881980896</t>
   </si>
   <si>
     <t xml:space="preserve">4.70155000686646</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">4.92457723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76989698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69075870513916</t>
+    <t xml:space="preserve">4.7698974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.690758228302</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838384628296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68716096878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82385540008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5504674911499</t>
+    <t xml:space="preserve">4.68716144561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82385492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55046701431274</t>
   </si>
   <si>
     <t xml:space="preserve">4.51089811325073</t>
@@ -941,16 +941,16 @@
     <t xml:space="preserve">4.43895387649536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38139915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38499546051025</t>
+    <t xml:space="preserve">4.38139867782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38499593734741</t>
   </si>
   <si>
     <t xml:space="preserve">4.46413421630859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03609085083008</t>
+    <t xml:space="preserve">5.03609037399292</t>
   </si>
   <si>
     <t xml:space="preserve">4.85622978210449</t>
@@ -962,28 +962,28 @@
     <t xml:space="preserve">4.76629972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68356370925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67636919021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59003686904907</t>
+    <t xml:space="preserve">4.68356418609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67636966705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60442590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59003591537476</t>
   </si>
   <si>
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67277240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74831342697144</t>
+    <t xml:space="preserve">4.66198110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74831295013428</t>
   </si>
   <si>
     <t xml:space="preserve">4.75910520553589</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">4.9533543586731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83104944229126</t>
+    <t xml:space="preserve">4.8310489654541</t>
   </si>
   <si>
     <t xml:space="preserve">5.06486845016479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14400672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11522960662842</t>
+    <t xml:space="preserve">5.14400625228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1152286529541</t>
   </si>
   <si>
     <t xml:space="preserve">5.19436740875244</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">5.10803413391113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93536949157715</t>
+    <t xml:space="preserve">4.93536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">4.7555079460144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99652194976807</t>
+    <t xml:space="preserve">4.99652147293091</t>
   </si>
   <si>
     <t xml:space="preserve">4.90659093856812</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">4.92097997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82025766372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89220237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05407619476318</t>
+    <t xml:space="preserve">4.82025814056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89220142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0540771484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.07925701141357</t>
@@ -1040,28 +1040,28 @@
     <t xml:space="preserve">5.0181040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95695209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94616031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839576721191</t>
+    <t xml:space="preserve">4.95695161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94616079330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839529037476</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60804653167725</t>
+    <t xml:space="preserve">5.60804605484009</t>
   </si>
   <si>
     <t xml:space="preserve">5.89942026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77711534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611373901367</t>
+    <t xml:space="preserve">5.77711486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611421585083</t>
   </si>
   <si>
     <t xml:space="preserve">5.94978189468384</t>
@@ -1076,31 +1076,31 @@
     <t xml:space="preserve">6.52533435821533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03613662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89584636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980242729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12968921661377</t>
+    <t xml:space="preserve">7.03613805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89584589004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13686037063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12968826293945</t>
   </si>
   <si>
     <t xml:space="preserve">8.43904876708984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95704555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29518508911133</t>
+    <t xml:space="preserve">8.95704650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29518413543701</t>
   </si>
   <si>
     <t xml:space="preserve">10.2160682678223</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">8.61890888214111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22321605682373</t>
+    <t xml:space="preserve">8.22321701049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.0145788192749</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">8.32393741607666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.992995262146</t>
+    <t xml:space="preserve">7.99299383163452</t>
   </si>
   <si>
     <t xml:space="preserve">8.10091209411621</t>
@@ -1133,142 +1133,142 @@
     <t xml:space="preserve">7.98580121994019</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88507843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73399543762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41024827957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54694032669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499656677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38866472244263</t>
+    <t xml:space="preserve">7.8850793838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73399639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41024780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54694080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535820007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38866519927979</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84191226959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8491063117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04335594177246</t>
+    <t xml:space="preserve">7.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702409744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910678863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04335498809814</t>
   </si>
   <si>
     <t xml:space="preserve">7.92824554443359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85630083084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74838542938232</t>
+    <t xml:space="preserve">7.85630178451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74838447570801</t>
   </si>
   <si>
     <t xml:space="preserve">7.57571887969971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42463493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599864959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20880508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20160913467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485906600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25196981430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448408126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00736045837402</t>
+    <t xml:space="preserve">7.424635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498512268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880365371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20160865783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485811233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477529525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00735950469971</t>
   </si>
   <si>
     <t xml:space="preserve">6.89944410324097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91742944717407</t>
+    <t xml:space="preserve">6.95340204238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844297409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91742992401123</t>
   </si>
   <si>
     <t xml:space="preserve">6.85627698898315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89224863052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7879319190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9569993019104</t>
+    <t xml:space="preserve">6.89224815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78793144226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95699834823608</t>
   </si>
   <si>
     <t xml:space="preserve">6.93541622161865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98217964172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16204023361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02174997329712</t>
+    <t xml:space="preserve">6.98218011856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1620397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045667648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0217490196228</t>
   </si>
   <si>
     <t xml:space="preserve">7.33830261230469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82752466201782</t>
+    <t xml:space="preserve">7.82752323150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.25918865203857</t>
@@ -1277,61 +1277,61 @@
     <t xml:space="preserve">8.15846633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91385650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89946603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313562393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435564041138</t>
+    <t xml:space="preserve">7.91385555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76996850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435611724854</t>
   </si>
   <si>
     <t xml:space="preserve">7.48219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79152727127075</t>
+    <t xml:space="preserve">6.79152679443359</t>
   </si>
   <si>
     <t xml:space="preserve">6.74836111068726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56850099563599</t>
+    <t xml:space="preserve">6.56850051879883</t>
   </si>
   <si>
     <t xml:space="preserve">6.64044523239136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4893627166748</t>
+    <t xml:space="preserve">6.48936367034912</t>
   </si>
   <si>
     <t xml:space="preserve">6.63325071334839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62605571746826</t>
+    <t xml:space="preserve">6.6260552406311</t>
   </si>
   <si>
     <t xml:space="preserve">6.56130599975586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60447311401367</t>
+    <t xml:space="preserve">6.60447263717651</t>
   </si>
   <si>
     <t xml:space="preserve">6.55411195755005</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28791856765747</t>
+    <t xml:space="preserve">6.28791809082031</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439125061035</t>
@@ -1343,31 +1343,31 @@
     <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344766616821</t>
+    <t xml:space="preserve">5.86344861984253</t>
   </si>
   <si>
     <t xml:space="preserve">6.25914096832275</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26633548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46777820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51814079284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46058368682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29511260986328</t>
+    <t xml:space="preserve">6.26633501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619512557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46777868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641687393188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51813983917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46058320999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29511308670044</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086345672607</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">5.92819738388062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93539237976074</t>
+    <t xml:space="preserve">5.93539142608643</t>
   </si>
   <si>
     <t xml:space="preserve">5.89222526550293</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">5.79869890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97136449813843</t>
+    <t xml:space="preserve">5.97136497497559</t>
   </si>
   <si>
     <t xml:space="preserve">6.01453018188477</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">5.99294757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17280769348145</t>
+    <t xml:space="preserve">6.1728081703186</t>
   </si>
   <si>
     <t xml:space="preserve">6.18719673156738</t>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">6.25194597244263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22316884994507</t>
+    <t xml:space="preserve">6.22316837310791</t>
   </si>
   <si>
     <t xml:space="preserve">6.12244749069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27353000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950260162354</t>
+    <t xml:space="preserve">6.27353048324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950164794922</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230712890625</t>
@@ -1424,61 +1424,61 @@
     <t xml:space="preserve">6.33827972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58551645278931</t>
+    <t xml:space="preserve">6.58551740646362</t>
   </si>
   <si>
     <t xml:space="preserve">6.38323211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46564483642578</t>
+    <t xml:space="preserve">6.46564435958862</t>
   </si>
   <si>
     <t xml:space="preserve">6.35326385498047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59300947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41319942474365</t>
+    <t xml:space="preserve">6.3083119392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59300899505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41320037841797</t>
   </si>
   <si>
     <t xml:space="preserve">6.17345380783081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09853363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90373992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618486404419</t>
+    <t xml:space="preserve">6.09853410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90374040603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
   </si>
   <si>
     <t xml:space="preserve">5.9411997795105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86627960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94869232177734</t>
+    <t xml:space="preserve">5.86628007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9486927986145</t>
   </si>
   <si>
     <t xml:space="preserve">5.84380388259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59656572341919</t>
+    <t xml:space="preserve">5.59656620025635</t>
   </si>
   <si>
     <t xml:space="preserve">5.48418474197388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60405731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55910539627075</t>
+    <t xml:space="preserve">5.60405778884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55910587310791</t>
   </si>
   <si>
     <t xml:space="preserve">5.888756275177</t>
@@ -1490,64 +1490,64 @@
     <t xml:space="preserve">5.64151859283447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79135942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88126468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621660232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078718185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55554819107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815229415894</t>
+    <t xml:space="preserve">5.79135894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88126373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621612548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078765869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55554866790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815277099609</t>
   </si>
   <si>
     <t xml:space="preserve">6.30081939697266</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12850189208984</t>
+    <t xml:space="preserve">6.128502368927</t>
   </si>
   <si>
     <t xml:space="preserve">6.06107378005981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77637529373169</t>
+    <t xml:space="preserve">5.77637577056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.76888275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70145463943481</t>
+    <t xml:space="preserve">5.70145416259766</t>
   </si>
   <si>
     <t xml:space="preserve">5.66399478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57408905029297</t>
+    <t xml:space="preserve">5.57409000396729</t>
   </si>
   <si>
     <t xml:space="preserve">5.75389909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78386688232422</t>
+    <t xml:space="preserve">5.78386735916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6265344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61904191970825</t>
+    <t xml:space="preserve">5.62653398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61904239654541</t>
   </si>
   <si>
     <t xml:space="preserve">5.65650272369385</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">5.54412174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58158206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5066614151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53662967681885</t>
+    <t xml:space="preserve">5.58158111572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50666093826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53662919998169</t>
   </si>
   <si>
     <t xml:space="preserve">5.43174076080322</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">5.49167680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51415300369263</t>
+    <t xml:space="preserve">5.51415395736694</t>
   </si>
   <si>
     <t xml:space="preserve">5.36431169509888</t>
@@ -1592,403 +1592,403 @@
     <t xml:space="preserve">5.27440786361694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18450307846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2069787979126</t>
+    <t xml:space="preserve">5.18450260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20697927474976</t>
   </si>
   <si>
     <t xml:space="preserve">5.58907413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74640703201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47669219970703</t>
+    <t xml:space="preserve">5.74640655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47669315338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.21447134017944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13955068588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09459829330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10958242416382</t>
+    <t xml:space="preserve">5.13955020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09459781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10958194732666</t>
   </si>
   <si>
     <t xml:space="preserve">5.07212209701538</t>
   </si>
   <si>
+    <t xml:space="preserve">5.05713796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466176986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86983633041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7349796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77243947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82488441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88481998443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75745534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234426498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91478872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89980459213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85485219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95224905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16951894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08710622787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13205862045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01612091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99364519119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04215335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94475698471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99720144271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02716970443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89231204986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95974111557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81739234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79491567611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78742361068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83237600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97472524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76494789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47275733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38285350799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32291603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30044031143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31542444229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46526575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777368545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71250295639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10209035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07961463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218557357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196340560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25942325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19948720932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11707401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28939199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31186819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41675615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44672441482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.409264087677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89624834060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85878753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12100982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00113677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885149002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91123199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.008629322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377214431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97116899490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21091413497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09104204177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0236120223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859758377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142337799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866010665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72392988204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170806884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73891496658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161333084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47268581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33155584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35507726669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30803489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26883125305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315046310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14338350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06497859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00225400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20610809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33939695358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11986207962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13554286956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09634065628052</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.05713748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01967763900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466176986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732839584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86983680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73497915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77243995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82488441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88482046127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75745582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9147891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89980554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8548526763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95224905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16951942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0871057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13205814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25586700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01612043380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99364471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04215383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221731185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94475698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99720191955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02717018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89231252670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964590072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95974063873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81739187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79491567611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78742361068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83237600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97472524642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76494789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4727578163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38285303115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32291603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30043983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31542444229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46526527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777368545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71250295639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10208988189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07961416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218557357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443960189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25942277908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19948768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11707401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28939199447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202640533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31186819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41675662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4467248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39427995681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.409264087677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89624786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85878801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12100982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383562088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82132768630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91123247146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03110504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.008629322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631229400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97116899490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21091413497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09104156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859758377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7089467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916887283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73891496658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47268581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33155632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35507726669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30803442001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39428091049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24531078338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26883220672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14338397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06497859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00225448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20610761642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33939647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11986207962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13554334640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09634065628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713701248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11202192306519</t>
+    <t xml:space="preserve">5.11202096939087</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474555969238</t>
@@ -1997,52 +1997,52 @@
     <t xml:space="preserve">5.44916391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4570050239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61381435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70790147781372</t>
+    <t xml:space="preserve">5.45700454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61381483078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70790100097656</t>
   </si>
   <si>
     <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55893182754517</t>
+    <t xml:space="preserve">5.63733673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55893135070801</t>
   </si>
   <si>
     <t xml:space="preserve">5.51188802719116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48836660385132</t>
+    <t xml:space="preserve">5.48836612701416</t>
   </si>
   <si>
     <t xml:space="preserve">5.48052597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36291885375977</t>
+    <t xml:space="preserve">5.36291837692261</t>
   </si>
   <si>
     <t xml:space="preserve">5.31587553024292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32371520996094</t>
+    <t xml:space="preserve">5.3237156867981</t>
   </si>
   <si>
     <t xml:space="preserve">5.19826698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79840040206909</t>
+    <t xml:space="preserve">4.79840087890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71999502182007</t>
+    <t xml:space="preserve">4.71999549865723</t>
   </si>
   <si>
     <t xml:space="preserve">4.51614189147949</t>
@@ -2054,31 +2054,31 @@
     <t xml:space="preserve">4.82192230224609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64158964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71215534210205</t>
+    <t xml:space="preserve">4.6415901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71215486526489</t>
   </si>
   <si>
     <t xml:space="preserve">4.67295217514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63374948501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64943075180054</t>
+    <t xml:space="preserve">4.63374900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64943027496338</t>
   </si>
   <si>
     <t xml:space="preserve">4.59454679489136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62590837478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68079280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90032720565796</t>
+    <t xml:space="preserve">4.62590885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68079233169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90032768249512</t>
   </si>
   <si>
     <t xml:space="preserve">5.22962951660156</t>
@@ -2090,19 +2090,19 @@
     <t xml:space="preserve">5.04145669937134</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15122413635254</t>
+    <t xml:space="preserve">5.1512246131897</t>
   </si>
   <si>
     <t xml:space="preserve">5.22178888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21394872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15906429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08065938949585</t>
+    <t xml:space="preserve">5.21394824981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15906476974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08065891265869</t>
   </si>
   <si>
     <t xml:space="preserve">5.12770318984985</t>
@@ -2111,34 +2111,34 @@
     <t xml:space="preserve">5.01793527603149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07281827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08849954605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19042634963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18258571624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52756977081299</t>
+    <t xml:space="preserve">5.07281875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08850002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19042682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18258619308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52756929397583</t>
   </si>
   <si>
     <t xml:space="preserve">5.51972913742065</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40212059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56677150726318</t>
+    <t xml:space="preserve">5.40212106704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5667724609375</t>
   </si>
   <si>
     <t xml:space="preserve">5.43348264694214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50404739379883</t>
+    <t xml:space="preserve">5.50404787063599</t>
   </si>
   <si>
     <t xml:space="preserve">5.53540992736816</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">5.41780185699463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42564296722412</t>
+    <t xml:space="preserve">5.42564249038696</t>
   </si>
   <si>
     <t xml:space="preserve">5.84119033813477</t>
@@ -2156,16 +2156,16 @@
     <t xml:space="preserve">5.76278495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64517688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44132375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40996170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38643932342529</t>
+    <t xml:space="preserve">5.64517736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44132423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40996122360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38643980026245</t>
   </si>
   <si>
     <t xml:space="preserve">5.3472375869751</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">4.97873258590698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8376030921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89248657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896467208862</t>
+    <t xml:space="preserve">4.83760356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89248704910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896514892578</t>
   </si>
   <si>
     <t xml:space="preserve">4.92384910583496</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">4.87680530548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98657369613647</t>
+    <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
     <t xml:space="preserve">4.57102584838867</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">4.54750394821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57886600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39069271087646</t>
+    <t xml:space="preserve">4.57886648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39069366455078</t>
   </si>
   <si>
     <t xml:space="preserve">4.15547752380371</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">4.11627531051636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84185671806335</t>
+    <t xml:space="preserve">3.84185695648193</t>
   </si>
   <si>
     <t xml:space="preserve">3.63800287246704</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">3.26165771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29301977157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32438206672668</t>
+    <t xml:space="preserve">3.29301953315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32438182830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.90099382400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09700679779053</t>
+    <t xml:space="preserve">3.09700703620911</t>
   </si>
   <si>
     <t xml:space="preserve">3.05780434608459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94803667068481</t>
+    <t xml:space="preserve">2.94803714752197</t>
   </si>
   <si>
     <t xml:space="preserve">3.00292062759399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13620948791504</t>
+    <t xml:space="preserve">3.13620972633362</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036236763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2146143913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25381755828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22245526313782</t>
+    <t xml:space="preserve">3.21461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25381731987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2224555015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.24205684661865</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">3.34006333351135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45767140388489</t>
+    <t xml:space="preserve">3.45767116546631</t>
   </si>
   <si>
     <t xml:space="preserve">3.59880042076111</t>
@@ -2291,22 +2291,22 @@
     <t xml:space="preserve">3.52039480209351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54391694068909</t>
+    <t xml:space="preserve">3.54391670227051</t>
   </si>
   <si>
     <t xml:space="preserve">3.7242488861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81049466133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92026209831238</t>
+    <t xml:space="preserve">3.81049513816833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9202618598938</t>
   </si>
   <si>
     <t xml:space="preserve">4.33581018447876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32796907424927</t>
+    <t xml:space="preserve">4.32796955108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.32012844085693</t>
@@ -2315,73 +2315,73 @@
     <t xml:space="preserve">4.23388290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16331768035889</t>
+    <t xml:space="preserve">4.16331815719604</t>
   </si>
   <si>
     <t xml:space="preserve">4.07707166671753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21820163726807</t>
+    <t xml:space="preserve">4.21820211410522</t>
   </si>
   <si>
     <t xml:space="preserve">4.21036100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25740480422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19467973709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208928108215</t>
+    <t xml:space="preserve">4.25740385055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19468021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208999633789</t>
   </si>
   <si>
     <t xml:space="preserve">3.79481363296509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83401584625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84577631950378</t>
+    <t xml:space="preserve">3.83401608467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577751159668</t>
   </si>
   <si>
     <t xml:space="preserve">3.70072722434998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83009552955627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321925163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8222553730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169062614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74384999275208</t>
+    <t xml:space="preserve">3.83009648323059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265355110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145806312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385023117065</t>
   </si>
   <si>
     <t xml:space="preserve">3.98298597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29660654067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10059452056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91634202003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946455001831</t>
+    <t xml:space="preserve">4.29660701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10059404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91634082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946478843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763736724854</t>
+    <t xml:space="preserve">4.14763689041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.01434803009033</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">3.95162439346313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94378352165222</t>
+    <t xml:space="preserve">3.9437837600708</t>
   </si>
   <si>
     <t xml:space="preserve">3.8889000415802</t>
@@ -2408,19 +2408,19 @@
     <t xml:space="preserve">4.05355072021484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06923151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03002882003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89282011985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242098808289</t>
+    <t xml:space="preserve">4.06923198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89281964302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9281017780304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242122650146</t>
   </si>
   <si>
     <t xml:space="preserve">3.8575382232666</t>
@@ -2429,76 +2429,76 @@
     <t xml:space="preserve">3.8653781414032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82617592811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105916976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458106994629</t>
+    <t xml:space="preserve">3.82617545127869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458059310913</t>
   </si>
   <si>
     <t xml:space="preserve">3.90850114822388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.779132604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75561046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777007102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657434463501</t>
+    <t xml:space="preserve">3.77913284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.755610704422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657386779785</t>
   </si>
   <si>
     <t xml:space="preserve">3.88497972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96730542182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02218914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594312667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345109939575</t>
+    <t xml:space="preserve">3.96730494499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02218866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594336509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345133781433</t>
   </si>
   <si>
     <t xml:space="preserve">3.75953102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6458432674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66936492919922</t>
+    <t xml:space="preserve">3.64584374427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66936469078064</t>
   </si>
   <si>
     <t xml:space="preserve">3.66544485092163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63016247749329</t>
+    <t xml:space="preserve">3.63016223907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.56351804733276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56743836402893</t>
+    <t xml:space="preserve">3.56743860244751</t>
   </si>
   <si>
     <t xml:space="preserve">3.59095978736877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48903322219849</t>
+    <t xml:space="preserve">3.48903298377991</t>
   </si>
   <si>
     <t xml:space="preserve">3.48119282722473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44198966026306</t>
+    <t xml:space="preserve">3.44198989868164</t>
   </si>
   <si>
     <t xml:space="preserve">3.3871066570282</t>
@@ -2507,85 +2507,85 @@
     <t xml:space="preserve">3.31654167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33222270011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278768539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238831520081</t>
+    <t xml:space="preserve">3.33222246170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238855361938</t>
   </si>
   <si>
     <t xml:space="preserve">3.43806958198547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46551203727722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49295330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55175757408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55567765235901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50079369544983</t>
+    <t xml:space="preserve">3.46551179885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49295353889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55175733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55567789077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50079393386841</t>
   </si>
   <si>
     <t xml:space="preserve">3.51255440711975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37926578521729</t>
+    <t xml:space="preserve">3.37926602363586</t>
   </si>
   <si>
     <t xml:space="preserve">3.43414950370789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42630863189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46159148216248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44983053207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189051628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20677423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17541217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52823543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215599060059</t>
+    <t xml:space="preserve">3.42630887031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4615912437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4498302936554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20677447319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17541241645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52823519706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215551376343</t>
   </si>
   <si>
     <t xml:space="preserve">3.53607678413391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10843420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866700172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252084732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13195657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0927529335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06139039993286</t>
+    <t xml:space="preserve">4.10843467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2025203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13195610046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09275341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06139135360718</t>
   </si>
   <si>
     <t xml:space="preserve">4.28876638412476</t>
@@ -2594,19 +2594,19 @@
     <t xml:space="preserve">4.2495641708374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24172306060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39853382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35933113098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69647407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919818878174</t>
+    <t xml:space="preserve">4.24172258377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3985333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3593316078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69647359848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75919771194458</t>
   </si>
   <si>
     <t xml:space="preserve">4.82976245880127</t>
@@ -2615,16 +2615,16 @@
     <t xml:space="preserve">4.7278356552124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74351692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76703834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77487897872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73567628860474</t>
+    <t xml:space="preserve">4.74351739883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76703882217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77487945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73567676544189</t>
   </si>
   <si>
     <t xml:space="preserve">4.68863344192505</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">4.94737005233765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86112499237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84544372558594</t>
+    <t xml:space="preserve">4.86112403869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84544324874878</t>
   </si>
   <si>
     <t xml:space="preserve">4.91600847244263</t>
@@ -2660,25 +2660,25 @@
     <t xml:space="preserve">5.58245277404785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68438005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59813404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62949562072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71574115753174</t>
+    <t xml:space="preserve">5.68437957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59813451766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6294960975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7157416343689</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222068786621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66869831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66085767745972</t>
+    <t xml:space="preserve">5.66869878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66085815429688</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358226776123</t>
@@ -2693,22 +2693,22 @@
     <t xml:space="preserve">6.17833280563354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14697027206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288410186768</t>
+    <t xml:space="preserve">6.14697074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288457870483</t>
   </si>
   <si>
     <t xml:space="preserve">5.97447919845581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03720331192017</t>
+    <t xml:space="preserve">6.03720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00474500656128</t>
+    <t xml:space="preserve">6.00474548339844</t>
   </si>
   <si>
     <t xml:space="preserve">6.11834812164307</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">6.49161624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4591588973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42670011520386</t>
+    <t xml:space="preserve">6.45915842056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4266996383667</t>
   </si>
   <si>
     <t xml:space="preserve">6.26440954208374</t>
@@ -2729,10 +2729,10 @@
     <t xml:space="preserve">6.41047096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39424180984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4429292678833</t>
+    <t xml:space="preserve">6.39424228668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44292879104614</t>
   </si>
   <si>
     <t xml:space="preserve">6.96225786209106</t>
@@ -2741,31 +2741,31 @@
     <t xml:space="preserve">7.14077806472778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43290090560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00091648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83862686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87108516693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78993892669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977262496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95222949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90354347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60139179229736</t>
+    <t xml:space="preserve">7.43289995193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00091743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83862733840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87108421325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78993988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95222997665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90354251861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60139274597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.64196395874023</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">8.56081962585449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43910026550293</t>
+    <t xml:space="preserve">8.43910121917725</t>
   </si>
   <si>
     <t xml:space="preserve">8.19566535949707</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">8.23623752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01714706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06583213806152</t>
+    <t xml:space="preserve">8.01714515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06583309173584</t>
   </si>
   <si>
     <t xml:space="preserve">7.96845865249634</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">7.40044260025024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25438022613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4815878868103</t>
+    <t xml:space="preserve">7.25438070297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48158884048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.64387893676758</t>
@@ -2807,7 +2807,7 @@
     <t xml:space="preserve">7.5627326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69256544113159</t>
+    <t xml:space="preserve">7.69256448745728</t>
   </si>
   <si>
     <t xml:space="preserve">7.72502374649048</t>
@@ -2819,43 +2819,43 @@
     <t xml:space="preserve">7.62764930725098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46535873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306768417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192335128784</t>
+    <t xml:space="preserve">7.46535778045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30306816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192287445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.81619644165039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15700721740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23815155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3842134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70879459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61142015457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010713577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53027486801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74125194549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3579568862915</t>
+    <t xml:space="preserve">7.15700626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23815250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38421392440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70879507064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61141967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010761260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53027534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74125289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
     <t xml:space="preserve">8.1550931930542</t>
@@ -2864,28 +2864,28 @@
     <t xml:space="preserve">8.96654605865479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84482669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368236541748</t>
+    <t xml:space="preserve">8.84482765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368141174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.52024745941162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39852905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47967338562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31738471984863</t>
+    <t xml:space="preserve">8.39852809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47967433929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31738376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.08206272125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11452007293701</t>
+    <t xml:space="preserve">8.1145191192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.03337478637695</t>
@@ -2897,16 +2897,16 @@
     <t xml:space="preserve">9.04768943786621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41284465789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16940879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4452428817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40344905853271</t>
+    <t xml:space="preserve">9.41284370422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16940784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44524192810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40345001220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.23627758026123</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">9.48703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7795877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61241436004639</t>
+    <t xml:space="preserve">9.77958679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6124153137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.57062244415283</t>
@@ -2939,16 +2939,16 @@
     <t xml:space="preserve">9.90496635437012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31986331939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27807140350342</t>
+    <t xml:space="preserve">9.31986236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2780704498291</t>
   </si>
   <si>
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15268993377686</t>
+    <t xml:space="preserve">9.15269088745117</t>
   </si>
   <si>
     <t xml:space="preserve">8.86013889312744</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">8.35862159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6093807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19448375701904</t>
+    <t xml:space="preserve">8.60937976837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19448280334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
@@ -2975,13 +2975,13 @@
     <t xml:space="preserve">9.36165523529053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06910610198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94372463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90193176269531</t>
+    <t xml:space="preserve">9.06910514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9437255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90193271636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.81834697723389</t>
@@ -2990,43 +2990,43 @@
     <t xml:space="preserve">8.56758785247803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52579402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73475933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20816516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30846977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32518672943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65649747848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82366991043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154626846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0713939666748</t>
+    <t xml:space="preserve">8.52579307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73476028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20816612243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30846881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32518768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65649652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82366943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321538925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07139444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.10482835769653</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68993234634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589017868042</t>
+    <t xml:space="preserve">7.68993091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589113235474</t>
   </si>
   <si>
     <t xml:space="preserve">7.89053916931152</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">7.62306308746338</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99084234237671</t>
+    <t xml:space="preserve">7.99084186553955</t>
   </si>
   <si>
     <t xml:space="preserve">8.09114551544189</t>
@@ -3050,22 +3050,22 @@
     <t xml:space="preserve">8.27503490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40041446685791</t>
+    <t xml:space="preserve">8.40041542053223</t>
   </si>
   <si>
     <t xml:space="preserve">8.1078634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48400020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30011177062988</t>
+    <t xml:space="preserve">8.48400115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30011081695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.35026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24995899200439</t>
+    <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
     <t xml:space="preserve">7.87382173538208</t>
@@ -3077,16 +3077,16 @@
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531143188477</t>
+    <t xml:space="preserve">7.81531095504761</t>
   </si>
   <si>
     <t xml:space="preserve">7.77351856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91561555862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78187704086304</t>
+    <t xml:space="preserve">7.91561508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78187656402588</t>
   </si>
   <si>
     <t xml:space="preserve">7.60634613037109</t>
@@ -3095,28 +3095,28 @@
     <t xml:space="preserve">7.89889764785767</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79859399795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023456573486</t>
+    <t xml:space="preserve">7.79859447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023504257202</t>
   </si>
   <si>
     <t xml:space="preserve">7.83202838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63978052139282</t>
+    <t xml:space="preserve">7.63978004455566</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6485013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24154281616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21538066864014</t>
+    <t xml:space="preserve">7.64850187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24154376983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21537971496582</t>
   </si>
   <si>
     <t xml:space="preserve">8.28514957427979</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">8.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59039211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64271926879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63399696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47701740264893</t>
+    <t xml:space="preserve">8.59039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64271831512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63399791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47701644897461</t>
   </si>
   <si>
     <t xml:space="preserve">8.45957374572754</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">8.12816715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93630170822144</t>
+    <t xml:space="preserve">7.93630123138428</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77931976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95374298095703</t>
+    <t xml:space="preserve">7.71827125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77931928634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95374345779419</t>
   </si>
   <si>
     <t xml:space="preserve">8.14561080932617</t>
@@ -3188,67 +3188,67 @@
     <t xml:space="preserve">8.0496768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86653184890747</t>
+    <t xml:space="preserve">7.86653232574463</t>
   </si>
   <si>
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65722274780273</t>
+    <t xml:space="preserve">7.78804016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65722179412842</t>
   </si>
   <si>
     <t xml:space="preserve">7.76187658309937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6921067237854</t>
+    <t xml:space="preserve">7.69210767745972</t>
   </si>
   <si>
     <t xml:space="preserve">7.70082855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5961742401123</t>
+    <t xml:space="preserve">7.59617376327515</t>
   </si>
   <si>
     <t xml:space="preserve">7.46535634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54384613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73571348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50024080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63105869293213</t>
+    <t xml:space="preserve">7.54384660720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73571395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50024127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
     <t xml:space="preserve">7.55256795883179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.447913646698</t>
+    <t xml:space="preserve">7.44791316986084</t>
   </si>
   <si>
     <t xml:space="preserve">7.53512620925903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51768350601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50896167755127</t>
+    <t xml:space="preserve">7.5176830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50896120071411</t>
   </si>
   <si>
     <t xml:space="preserve">7.57001066207886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80548334121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74443531036377</t>
+    <t xml:space="preserve">7.80548286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74443483352661</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">8.72121047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48573684692383</t>
+    <t xml:space="preserve">8.48573780059814</t>
   </si>
   <si>
     <t xml:space="preserve">8.50318050384521</t>
@@ -3275,19 +3275,19 @@
     <t xml:space="preserve">8.3461971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.023512840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37236213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89269542694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83164644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66594314575195</t>
+    <t xml:space="preserve">8.02351379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37236309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89269495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83164596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66594362258911</t>
   </si>
   <si>
     <t xml:space="preserve">7.88397407531738</t>
@@ -3296,19 +3296,19 @@
     <t xml:space="preserve">7.97118711471558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6833872795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1688346862793</t>
+    <t xml:space="preserve">7.68338632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33453750610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16883516311646</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418037414551</t>
+    <t xml:space="preserve">7.06418085098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">7.13395023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1252293586731</t>
+    <t xml:space="preserve">7.12522888183594</t>
   </si>
   <si>
     <t xml:space="preserve">6.78510189056396</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">6.61939907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41008901596069</t>
+    <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
     <t xml:space="preserve">6.63684129714966</t>
@@ -3335,40 +3335,40 @@
     <t xml:space="preserve">6.87231397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75315618515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4391918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43047142028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49151992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27348947525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39558601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38686513900757</t>
+    <t xml:space="preserve">7.7531566619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43919229507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43047189712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49151945114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27348899841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39558553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">7.35198068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31709575653076</t>
+    <t xml:space="preserve">7.3170952796936</t>
   </si>
   <si>
     <t xml:space="preserve">7.47407722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.290931224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581615447998</t>
+    <t xml:space="preserve">7.29093170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581663131714</t>
   </si>
   <si>
     <t xml:space="preserve">7.30837440490723</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663547515869</t>
+    <t xml:space="preserve">7.45663499832153</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781097412109</t>
+    <t xml:space="preserve">7.85781145095825</t>
   </si>
   <si>
     <t xml:space="preserve">8.03223514556885</t>
@@ -3392,37 +3392,37 @@
     <t xml:space="preserve">8.1020040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15433311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05839729309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09328269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00607204437256</t>
+    <t xml:space="preserve">8.15433120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09328365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584095001221</t>
+    <t xml:space="preserve">8.11072540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584190368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98862838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90141725540161</t>
+    <t xml:space="preserve">7.97990703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98862886428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90141677856445</t>
   </si>
   <si>
     <t xml:space="preserve">7.84908962249756</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">7.91885852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82292652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11944770812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25898742675781</t>
+    <t xml:space="preserve">7.82292556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11944675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2589864730835</t>
   </si>
   <si>
     <t xml:space="preserve">8.27642822265625</t>
@@ -3452,34 +3452,34 @@
     <t xml:space="preserve">8.94796180725098</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87819194793701</t>
+    <t xml:space="preserve">8.87819290161133</t>
   </si>
   <si>
     <t xml:space="preserve">8.89563465118408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65144062042236</t>
+    <t xml:space="preserve">8.65144157409668</t>
   </si>
   <si>
     <t xml:space="preserve">8.6601619720459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79098033905029</t>
+    <t xml:space="preserve">8.79097938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.70376777648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71248817443848</t>
+    <t xml:space="preserve">8.71248912811279</t>
   </si>
   <si>
     <t xml:space="preserve">8.86074924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93051910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62527751922607</t>
+    <t xml:space="preserve">8.93052005767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62527656555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.56422805786133</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">8.46829509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6863260269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15727138519287</t>
+    <t xml:space="preserve">8.68632507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15727043151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">8.96540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00028800964355</t>
+    <t xml:space="preserve">9.00028896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842304229736</t>
+    <t xml:space="preserve">8.80842208862305</t>
   </si>
   <si>
     <t xml:space="preserve">8.66888236999512</t>
@@ -71293,7 +71293,7 @@
     </row>
     <row r="2564">
       <c r="A2564" s="1" t="n">
-        <v>46056.6911226852</v>
+        <v>46056.3333333333</v>
       </c>
       <c r="B2564" t="n">
         <v>5148</v>
@@ -71314,6 +71314,32 @@
         <v>1397</v>
       </c>
       <c r="H2564" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" s="1" t="n">
+        <v>46057.691099537</v>
+      </c>
+      <c r="B2565" t="n">
+        <v>21223</v>
+      </c>
+      <c r="C2565" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="D2565" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E2565" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="F2565" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="G2565" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H2565" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355509757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546637058258</t>
+    <t xml:space="preserve">1.21355497837067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546625137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.20654857158661</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">1.26330256462097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27311182022095</t>
+    <t xml:space="preserve">1.27311170101166</t>
   </si>
   <si>
     <t xml:space="preserve">1.26120042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24718701839447</t>
+    <t xml:space="preserve">1.24718713760376</t>
   </si>
   <si>
     <t xml:space="preserve">1.20794975757599</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">1.19323563575745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501842975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814038276672</t>
+    <t xml:space="preserve">1.17501831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1981406211853</t>
   </si>
   <si>
     <t xml:space="preserve">1.24578583240509</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495652198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18272566795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17992317676544</t>
+    <t xml:space="preserve">1.21495640277863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1827255487442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17992305755615</t>
   </si>
   <si>
     <t xml:space="preserve">1.17641973495483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12457036972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12807381153107</t>
+    <t xml:space="preserve">1.12457060813904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12807369232178</t>
   </si>
   <si>
     <t xml:space="preserve">1.10284972190857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08603358268738</t>
+    <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
     <t xml:space="preserve">1.01596701145172</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">1.02507567405701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02017092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195372104645</t>
+    <t xml:space="preserve">1.02017104625702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195348262787</t>
   </si>
   <si>
     <t xml:space="preserve">1.02297377586365</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">1.04329311847687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09654378890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11335980892181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11055707931519</t>
+    <t xml:space="preserve">1.0965439081192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1133599281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1105569601059</t>
   </si>
   <si>
     <t xml:space="preserve">1.09304022789001</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12106692790985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13017570972443</t>
+    <t xml:space="preserve">1.12106704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13017582893372</t>
   </si>
   <si>
     <t xml:space="preserve">1.15610039234161</t>
@@ -161,22 +161,22 @@
     <t xml:space="preserve">1.10705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13227796554565</t>
+    <t xml:space="preserve">1.13227760791779</t>
   </si>
   <si>
     <t xml:space="preserve">1.11826431751251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1490935087204</t>
+    <t xml:space="preserve">1.14909374713898</t>
   </si>
   <si>
     <t xml:space="preserve">1.17852187156677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1701135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412697315216</t>
+    <t xml:space="preserve">1.17011380195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412709236145</t>
   </si>
   <si>
     <t xml:space="preserve">1.17081439495087</t>
@@ -185,34 +185,34 @@
     <t xml:space="preserve">1.16310703754425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22616696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2450852394104</t>
+    <t xml:space="preserve">1.22616708278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508500099182</t>
   </si>
   <si>
     <t xml:space="preserve">1.2408812046051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20514702796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1911336183548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22686791419983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22196292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24438452720642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17221581935883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183444976807</t>
+    <t xml:space="preserve">1.20514690876007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113373756409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22686779499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22196316719055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24438440799713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17221570014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183433055878</t>
   </si>
   <si>
     <t xml:space="preserve">1.19743967056274</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">1.20374572277069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.203045129776</t>
+    <t xml:space="preserve">1.20304501056671</t>
   </si>
   <si>
     <t xml:space="preserve">1.23807835578918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23317384719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19954180717468</t>
+    <t xml:space="preserve">1.2331737279892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19954168796539</t>
   </si>
   <si>
     <t xml:space="preserve">1.22476577758789</t>
@@ -239,55 +239,55 @@
     <t xml:space="preserve">1.21845972537994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21916031837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896993160248</t>
+    <t xml:space="preserve">1.21916043758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2289696931839</t>
   </si>
   <si>
     <t xml:space="preserve">1.21215379238129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22266387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29202973842621</t>
+    <t xml:space="preserve">1.22266364097595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29202997684479</t>
   </si>
   <si>
     <t xml:space="preserve">1.2962338924408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27521371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28712511062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28151977062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24788761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23737788200378</t>
+    <t xml:space="preserve">1.27521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28712522983551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28151965141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24788784980774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23737776279449</t>
   </si>
   <si>
     <t xml:space="preserve">1.20865035057068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15469896793365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138627052307</t>
+    <t xml:space="preserve">1.15469908714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138650894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.11896502971649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12036645412445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13648176193237</t>
+    <t xml:space="preserve">1.12036657333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13648164272308</t>
   </si>
   <si>
     <t xml:space="preserve">1.14629113674164</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0720202922821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08463215827942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501364707947</t>
+    <t xml:space="preserve">1.07202017307281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08463227748871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501376628876</t>
   </si>
   <si>
     <t xml:space="preserve">1.07061898708344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253037929535</t>
+    <t xml:space="preserve">1.08253026008606</t>
   </si>
   <si>
     <t xml:space="preserve">1.07902705669403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05800700187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1014484167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10355031490326</t>
+    <t xml:space="preserve">1.05800712108612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10144829750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10355043411255</t>
   </si>
   <si>
     <t xml:space="preserve">1.09514236450195</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">1.11966574192047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09934639930725</t>
+    <t xml:space="preserve">1.09934628009796</t>
   </si>
   <si>
     <t xml:space="preserve">1.11265909671783</t>
@@ -347,55 +347,55 @@
     <t xml:space="preserve">1.48821651935577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45178186893463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41534698009491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45738708972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40133368968964</t>
+    <t xml:space="preserve">1.45178174972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4153470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45738697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40133380889893</t>
   </si>
   <si>
     <t xml:space="preserve">1.4699991941452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43776845932007</t>
+    <t xml:space="preserve">1.43776857852936</t>
   </si>
   <si>
     <t xml:space="preserve">1.42375516891479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43636703491211</t>
+    <t xml:space="preserve">1.4363671541214</t>
   </si>
   <si>
     <t xml:space="preserve">1.42936050891876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41674864292145</t>
+    <t xml:space="preserve">1.41674852371216</t>
   </si>
   <si>
     <t xml:space="preserve">1.42235374450684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41814982891083</t>
+    <t xml:space="preserve">1.41814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42795920372009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48121011257172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69421243667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338324546814</t>
+    <t xml:space="preserve">1.4279590845108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48120999336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69421255588531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338312625885</t>
   </si>
   <si>
     <t xml:space="preserve">1.8007138967514</t>
@@ -407,43 +407,43 @@
     <t xml:space="preserve">1.7923059463501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79090440273285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268707752228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064744472504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71663391590118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78670072555542</t>
+    <t xml:space="preserve">1.79090487957001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268719673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064732551575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71663403511047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78670048713684</t>
   </si>
   <si>
     <t xml:space="preserve">1.8427540063858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82593786716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313549518585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995139598846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83854997158051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84415543079376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83014190196991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472754478455</t>
+    <t xml:space="preserve">1.82593810558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313525676727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995127677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83855009078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84415519237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014225959778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472718715668</t>
   </si>
   <si>
     <t xml:space="preserve">1.82874047756195</t>
@@ -452,130 +452,130 @@
     <t xml:space="preserve">1.81192457675934</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83294451236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84835958480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86937928199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99549973011017</t>
+    <t xml:space="preserve">1.83294463157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84835922718048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86937940120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549949169159</t>
   </si>
   <si>
     <t xml:space="preserve">2.07257270812988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0291314125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798742294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04034185409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830234050751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03053307533264</t>
+    <t xml:space="preserve">2.02913165092468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798718452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04034209251404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830210208893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03053283691406</t>
   </si>
   <si>
     <t xml:space="preserve">2.01932215690613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9997034072876</t>
+    <t xml:space="preserve">1.99970316886902</t>
   </si>
   <si>
     <t xml:space="preserve">2.01231551170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066597938538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15945553779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989403247833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339257240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167694568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345914363861</t>
+    <t xml:space="preserve">2.09359240531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066621780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15945529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989427089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339281082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167646884918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345938205719</t>
   </si>
   <si>
     <t xml:space="preserve">2.01651930809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250601768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97868311405182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944597244263</t>
+    <t xml:space="preserve">2.00250625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428893089294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9786833524704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944585323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.9198272228241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377418041229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86797773838043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918865680695</t>
+    <t xml:space="preserve">1.86377382278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86797785758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918853759766</t>
   </si>
   <si>
     <t xml:space="preserve">1.85676729679108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78950321674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631947517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89880704879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91001796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690043926239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849284648895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224858283997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766353607178</t>
+    <t xml:space="preserve">1.78950309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631935596466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301120281219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89880740642548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91001784801483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690091609955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849260807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9856903553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224882125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9576632976532</t>
   </si>
   <si>
     <t xml:space="preserve">1.96186721324921</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96326863765717</t>
+    <t xml:space="preserve">1.96326887607574</t>
   </si>
   <si>
     <t xml:space="preserve">1.9702752828598</t>
@@ -584,40 +584,40 @@
     <t xml:space="preserve">1.96607136726379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0039074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397389411926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18888354301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1650607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13283038139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06416487693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09639549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601400375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499430656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11321139335632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14404058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002729415894</t>
+    <t xml:space="preserve">2.00390696525574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18888330459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16506052017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13282990455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06416511535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09639573097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601424217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499406814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1132116317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14404034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002753257751</t>
   </si>
   <si>
     <t xml:space="preserve">2.14824485778809</t>
@@ -632,37 +632,37 @@
     <t xml:space="preserve">2.1524486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13703370094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11181044578552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09779667854309</t>
+    <t xml:space="preserve">2.13703417778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11180973052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09779691696167</t>
   </si>
   <si>
     <t xml:space="preserve">2.11881685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10200071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2421338558197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48876905441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4873673915863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297285079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316383361816</t>
+    <t xml:space="preserve">2.10200047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11741518974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213409423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48876881599426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48736763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297308921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316359519958</t>
   </si>
   <si>
     <t xml:space="preserve">2.46494626998901</t>
@@ -677,10 +677,10 @@
     <t xml:space="preserve">2.48036074638367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46634769439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44392585754395</t>
+    <t xml:space="preserve">2.46634745597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4439263343811</t>
   </si>
   <si>
     <t xml:space="preserve">2.43972229957581</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">2.45513677597046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49437403678894</t>
+    <t xml:space="preserve">2.49437427520752</t>
   </si>
   <si>
     <t xml:space="preserve">2.47335433959961</t>
@@ -710,40 +710,40 @@
     <t xml:space="preserve">2.84751033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.788654088974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11096119880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23988366127014</t>
+    <t xml:space="preserve">2.78865456581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11096143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23988342285156</t>
   </si>
   <si>
     <t xml:space="preserve">3.38422083854675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46129488945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040833473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6609845161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601798057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78360176086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176124572754</t>
+    <t xml:space="preserve">3.46129465103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003127098083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040738105774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251418113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66098475456238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601845741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7836012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9517617225647</t>
   </si>
   <si>
     <t xml:space="preserve">4.06386804580688</t>
@@ -755,37 +755,37 @@
     <t xml:space="preserve">4.16896820068359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11291408538818</t>
+    <t xml:space="preserve">4.11291456222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.03233861923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30910158157349</t>
+    <t xml:space="preserve">4.30910205841064</t>
   </si>
   <si>
     <t xml:space="preserve">4.30559825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55433464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6979718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50023508071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79256153106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10085487365723</t>
+    <t xml:space="preserve">4.55433511734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69797134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50023555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79256248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10085582733154</t>
   </si>
   <si>
     <t xml:space="preserve">5.01677465438843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44768571853638</t>
+    <t xml:space="preserve">5.44768524169922</t>
   </si>
   <si>
     <t xml:space="preserve">5.44418144226074</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">5.77349472045898</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143598556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518251419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369230270386</t>
+    <t xml:space="preserve">6.39708852767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369277954102</t>
   </si>
   <si>
     <t xml:space="preserve">6.97858238220215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78433275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626554489136</t>
+    <t xml:space="preserve">6.78433322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626459121704</t>
   </si>
   <si>
     <t xml:space="preserve">6.5325288772583</t>
@@ -824,28 +824,28 @@
     <t xml:space="preserve">6.35266828536987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07208490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32389068603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900156021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094484329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4030294418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798898696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37425136566162</t>
+    <t xml:space="preserve">6.07208585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32388973236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40302896499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15841913223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37425231933594</t>
   </si>
   <si>
     <t xml:space="preserve">6.47137594223022</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">6.11165523529053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93898916244507</t>
+    <t xml:space="preserve">5.93898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">5.96057271957397</t>
@@ -872,43 +872,43 @@
     <t xml:space="preserve">5.90661478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89582252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75193405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69437980651855</t>
+    <t xml:space="preserve">5.89582300186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75193452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6943793296814</t>
   </si>
   <si>
     <t xml:space="preserve">5.70157337188721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36703443527222</t>
+    <t xml:space="preserve">5.36703395843506</t>
   </si>
   <si>
     <t xml:space="preserve">4.87421607971191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1799783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97853565216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96414613723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8454384803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87781381607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155048370361</t>
+    <t xml:space="preserve">5.17997884750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97853517532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96414661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84543800354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8778133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9101881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155000686646</t>
   </si>
   <si>
     <t xml:space="preserve">4.92457675933838</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">4.76989698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69075870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65838384628296</t>
+    <t xml:space="preserve">4.690758228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6583833694458</t>
   </si>
   <si>
     <t xml:space="preserve">4.68716096878052</t>
@@ -929,37 +929,37 @@
     <t xml:space="preserve">4.82385492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55046701431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51089763641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49291181564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4389533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38139820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38499641418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46413469314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03609085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85622978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80946683883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76630020141602</t>
+    <t xml:space="preserve">4.5504674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51089811325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49291229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43895387649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38139867782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38499546051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46413421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03609037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85622930526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80946636199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76629972457886</t>
   </si>
   <si>
     <t xml:space="preserve">4.68356418609619</t>
@@ -974,28 +974,28 @@
     <t xml:space="preserve">4.59003686904907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62960577011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66198062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67277240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74831342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75910520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95335483551025</t>
+    <t xml:space="preserve">4.62960529327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66198110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74831390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75910568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9533543586731</t>
   </si>
   <si>
     <t xml:space="preserve">4.83104991912842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06486749649048</t>
+    <t xml:space="preserve">5.06486797332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.14400672912598</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">5.19436740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10803413391113</t>
+    <t xml:space="preserve">5.10803508758545</t>
   </si>
   <si>
     <t xml:space="preserve">4.93536901473999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75550842285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99652099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90659093856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097997665405</t>
+    <t xml:space="preserve">4.75550889968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99652147293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90659046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92098045349121</t>
   </si>
   <si>
     <t xml:space="preserve">4.82025814056396</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">4.89220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0540771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925701141357</t>
+    <t xml:space="preserve">5.05407619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925748825073</t>
   </si>
   <si>
     <t xml:space="preserve">5.0181040763855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95695114135742</t>
+    <t xml:space="preserve">4.95695161819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.94615983963013</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">5.23393678665161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60804605484009</t>
+    <t xml:space="preserve">5.60804653167725</t>
   </si>
   <si>
     <t xml:space="preserve">5.89942026138306</t>
@@ -1061,40 +1061,40 @@
     <t xml:space="preserve">5.77711486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03611469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978189468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18000268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20877981185913</t>
+    <t xml:space="preserve">6.03611421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978094100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18000221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20877933502197</t>
   </si>
   <si>
     <t xml:space="preserve">6.52533483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03613758087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89584732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1152777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980242729187</t>
+    <t xml:space="preserve">7.03613805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89584636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13685894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802331924438</t>
   </si>
   <si>
     <t xml:space="preserve">8.12969017028809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43904781341553</t>
+    <t xml:space="preserve">8.43904685974121</t>
   </si>
   <si>
     <t xml:space="preserve">8.95704650878906</t>
@@ -1103,22 +1103,22 @@
     <t xml:space="preserve">9.29518413543701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42465972900391</t>
+    <t xml:space="preserve">10.2160701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42466068267822</t>
   </si>
   <si>
     <t xml:space="preserve">8.61890888214111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2232141494751</t>
+    <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.01457786560059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80594062805176</t>
+    <t xml:space="preserve">7.80593967437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
@@ -1127,16 +1127,16 @@
     <t xml:space="preserve">7.99299383163452</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10091114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98579931259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8850793838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73399543762207</t>
+    <t xml:space="preserve">8.10091209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98580121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88507843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7339973449707</t>
   </si>
   <si>
     <t xml:space="preserve">7.41024732589722</t>
@@ -1145,22 +1145,22 @@
     <t xml:space="preserve">7.54694080352783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47499656677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341396331787</t>
+    <t xml:space="preserve">7.47499704360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341300964355</t>
   </si>
   <si>
     <t xml:space="preserve">7.52535772323608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38866472244263</t>
+    <t xml:space="preserve">7.38866424560547</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760509490967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84191179275513</t>
+    <t xml:space="preserve">7.84191274642944</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702362060547</t>
@@ -1169,124 +1169,124 @@
     <t xml:space="preserve">7.8491063117981</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04335689544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824506759644</t>
+    <t xml:space="preserve">8.04335594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824602127075</t>
   </si>
   <si>
     <t xml:space="preserve">7.85630083084106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74838447570801</t>
+    <t xml:space="preserve">7.74838542938232</t>
   </si>
   <si>
     <t xml:space="preserve">7.57571840286255</t>
   </si>
   <si>
-    <t xml:space="preserve">7.424635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419429779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97498464584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2088041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20161008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485811233521</t>
+    <t xml:space="preserve">7.42463731765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97498559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20161056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55413579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485715866089</t>
   </si>
   <si>
     <t xml:space="preserve">7.2519702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24477624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18721961975098</t>
+    <t xml:space="preserve">7.24477577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722009658813</t>
   </si>
   <si>
     <t xml:space="preserve">7.10448503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00735950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340299606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844202041626</t>
+    <t xml:space="preserve">7.00736045837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944362640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844345092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.91742992401123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85627698898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89225006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78793001174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95699977874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98218059539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16203927993774</t>
+    <t xml:space="preserve">6.85627794265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89224910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78793048858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95699834823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541479110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98218011856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1620397567749</t>
   </si>
   <si>
     <t xml:space="preserve">7.14045667648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02174806594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.338303565979</t>
+    <t xml:space="preserve">7.02174949645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33830261230469</t>
   </si>
   <si>
     <t xml:space="preserve">7.82752323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25918769836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15846538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91385507583618</t>
+    <t xml:space="preserve">8.25918674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15846633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9138560295105</t>
   </si>
   <si>
     <t xml:space="preserve">7.89946746826172</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924667358398</t>
+    <t xml:space="preserve">7.81313323974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">7.76996755599976</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">6.79152727127075</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74836158752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850099563599</t>
+    <t xml:space="preserve">6.7483606338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850051879883</t>
   </si>
   <si>
     <t xml:space="preserve">6.64044523239136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48936367034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62605619430542</t>
+    <t xml:space="preserve">6.4893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325166702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605667114258</t>
   </si>
   <si>
     <t xml:space="preserve">6.5613055229187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60447359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411243438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791904449463</t>
+    <t xml:space="preserve">6.60447263717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791809082031</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439125061035</t>
@@ -1340,34 +1340,34 @@
     <t xml:space="preserve">6.02172517776489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87783718109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86344718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633548736572</t>
+    <t xml:space="preserve">5.87783670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86344814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633501052856</t>
   </si>
   <si>
     <t xml:space="preserve">6.44619560241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4677791595459</t>
+    <t xml:space="preserve">6.46777868270874</t>
   </si>
   <si>
     <t xml:space="preserve">6.67641687393188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51813983917236</t>
+    <t xml:space="preserve">6.51814031600952</t>
   </si>
   <si>
     <t xml:space="preserve">6.46058464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29511260986328</t>
+    <t xml:space="preserve">6.2951135635376</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086345672607</t>
@@ -1376,100 +1376,100 @@
     <t xml:space="preserve">6.1368350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92819786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93539237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89222526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79869937896729</t>
+    <t xml:space="preserve">5.92819738388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9353928565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89222574234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79869842529297</t>
   </si>
   <si>
     <t xml:space="preserve">5.97136449813843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01453113555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99294757843018</t>
+    <t xml:space="preserve">6.01453065872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99294662475586</t>
   </si>
   <si>
     <t xml:space="preserve">6.17280769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18719673156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25194644927979</t>
+    <t xml:space="preserve">6.1871976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25194597244263</t>
   </si>
   <si>
     <t xml:space="preserve">6.22316837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12244701385498</t>
+    <t xml:space="preserve">6.12244749069214</t>
   </si>
   <si>
     <t xml:space="preserve">6.27353000640869</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30950164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30230760574341</t>
+    <t xml:space="preserve">6.30950260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30230808258057</t>
   </si>
   <si>
     <t xml:space="preserve">6.33828020095825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58551740646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38323259353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46564435958862</t>
+    <t xml:space="preserve">6.58551645278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38323163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46564388275146</t>
   </si>
   <si>
     <t xml:space="preserve">6.35326337814331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30831098556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17345428466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09853410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90373992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618391036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94120073318481</t>
+    <t xml:space="preserve">6.30831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59300899505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41319990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17345380783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09853363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90374040603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9411997795105</t>
   </si>
   <si>
     <t xml:space="preserve">5.86627960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94869232177734</t>
+    <t xml:space="preserve">5.9486927986145</t>
   </si>
   <si>
     <t xml:space="preserve">5.84380388259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59656572341919</t>
+    <t xml:space="preserve">5.59656620025635</t>
   </si>
   <si>
     <t xml:space="preserve">5.48418521881104</t>
@@ -1478,49 +1478,49 @@
     <t xml:space="preserve">5.60405778884888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55910587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.888756275177</t>
+    <t xml:space="preserve">5.55910539627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88875675201416</t>
   </si>
   <si>
     <t xml:space="preserve">5.80634355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64151859283447</t>
+    <t xml:space="preserve">5.64151811599731</t>
   </si>
   <si>
     <t xml:space="preserve">5.79135942459106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76139116287231</t>
+    <t xml:space="preserve">5.76139163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.88126420974731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92621660232544</t>
+    <t xml:space="preserve">5.92621612548828</t>
   </si>
   <si>
     <t xml:space="preserve">6.33078765869141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55554866790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815277099609</t>
+    <t xml:space="preserve">6.55554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815229415894</t>
   </si>
   <si>
     <t xml:space="preserve">6.33827924728394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30081987380981</t>
+    <t xml:space="preserve">6.30081939697266</t>
   </si>
   <si>
     <t xml:space="preserve">6.128502368927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0610728263855</t>
+    <t xml:space="preserve">6.06107378005981</t>
   </si>
   <si>
     <t xml:space="preserve">5.77637529373169</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">5.70145463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57408952713013</t>
+    <t xml:space="preserve">5.66399478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57409000396729</t>
   </si>
   <si>
     <t xml:space="preserve">5.75389909744263</t>
@@ -1544,16 +1544,16 @@
     <t xml:space="preserve">5.78386735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67897891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6265344619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61904144287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65650224685669</t>
+    <t xml:space="preserve">5.67897844314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62653398513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61904191970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
     <t xml:space="preserve">5.54412174224854</t>
@@ -1565,25 +1565,25 @@
     <t xml:space="preserve">5.50666093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53662919998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43174123764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4692006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31935930252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28189945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49167680740356</t>
+    <t xml:space="preserve">5.53662967681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43174076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46920108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31936025619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28189992904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49167728424072</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415348052979</t>
@@ -1592,19 +1592,19 @@
     <t xml:space="preserve">5.36431169509888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27440690994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450355529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20697832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58907461166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74640703201294</t>
+    <t xml:space="preserve">5.27440738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450307846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2069787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58907413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74640655517578</t>
   </si>
   <si>
     <t xml:space="preserve">5.47669315338135</t>
@@ -1619,378 +1619,378 @@
     <t xml:space="preserve">5.09459829330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10958242416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07212162017822</t>
+    <t xml:space="preserve">5.10958194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07212209701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05713701248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967763900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977285385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732839584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86983633041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7349796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77243947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82488441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88482046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75745534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234426498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91478872299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8548526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95224952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16951894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0871057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13205766677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25586748123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01612091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99364471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04215383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94475698471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99720191955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02717018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89231252670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95974063873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81739187240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79491567611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78742408752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83237600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97472524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76494789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47275733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047204971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38285255432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32291603088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30043935775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31542491912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46526479721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71250295639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10209035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07961416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218509674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25942325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19948768615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11707448959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28939199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31186819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41675710678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44672441482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89624786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85878801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.121009349823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589874267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00113677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82132720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91123199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00862979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872406005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377214431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97116899490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21091461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09104156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859710693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142290115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170854568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73891448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161333084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47268533706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33155632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35507774353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30803442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859964370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26883125305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14338350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06497859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00225400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20610761642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11986207962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13554382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09634017944336</t>
   </si>
   <si>
     <t xml:space="preserve">5.05713748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01967763900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466176986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732839584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86983633041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7349796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77243995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82488393783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88482093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75745534896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89980459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85485219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95224905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16951847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710622787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13205862045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25586700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01612091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602474212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99364471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04215383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221731185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94475650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99720144271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02716875076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8923134803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95974111557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81739187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79491567611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78742361068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83237600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97472524642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729665756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76494741439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47275733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047157287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38285303115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32291603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30043983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3154239654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46526479721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71250295639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10208988189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07961463928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218557357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443960189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196340560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19948720932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11707353591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28939151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202592849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31186819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41675615310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4467248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39427995681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.409264087677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89624834060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85878753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12100982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82132768630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91123199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03110551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00862979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872406005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631181716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377214431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97116899490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21091413497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09104156494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608869552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396257400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7089467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73891496658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161333084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47268629074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019330978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33155584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35507726669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30803489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39428043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24531030654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26883172988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14338302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06497859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00225496292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20610761642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33939647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11986255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13554286956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09634065628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713796615601</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.11202192306519</t>
   </si>
   <si>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">5.44916391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45700407028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61381483078003</t>
+    <t xml:space="preserve">5.45700454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61381435394287</t>
   </si>
   <si>
     <t xml:space="preserve">5.70790147781372</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">5.67653894424438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55893087387085</t>
+    <t xml:space="preserve">5.63733625411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55893182754517</t>
   </si>
   <si>
     <t xml:space="preserve">5.51188802719116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48836660385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48052644729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36291790008545</t>
+    <t xml:space="preserve">5.48836612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36291837692261</t>
   </si>
   <si>
     <t xml:space="preserve">5.31587553024292</t>
@@ -2036,40 +2036,40 @@
     <t xml:space="preserve">5.3237156867981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19826698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79840040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70431470870972</t>
+    <t xml:space="preserve">5.19826745986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79839992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
     <t xml:space="preserve">4.71999502182007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51614141464233</t>
+    <t xml:space="preserve">4.51614236831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.97089195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82192182540894</t>
+    <t xml:space="preserve">4.82192230224609</t>
   </si>
   <si>
     <t xml:space="preserve">4.64159059524536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71215486526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67295217514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63374948501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64943075180054</t>
+    <t xml:space="preserve">4.71215534210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67295169830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63374996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64943027496338</t>
   </si>
   <si>
     <t xml:space="preserve">4.59454727172852</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">4.62590885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68079233169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90032768249512</t>
+    <t xml:space="preserve">4.68079280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90032720565796</t>
   </si>
   <si>
     <t xml:space="preserve">5.22962951660156</t>
@@ -2090,19 +2090,19 @@
     <t xml:space="preserve">5.02577543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04145622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1512246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22178888320923</t>
+    <t xml:space="preserve">5.04145669937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15122413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22178840637207</t>
   </si>
   <si>
     <t xml:space="preserve">5.21394872665405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15906524658203</t>
+    <t xml:space="preserve">5.15906429290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.08065938949585</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">5.07281875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08849954605103</t>
+    <t xml:space="preserve">5.08850002288818</t>
   </si>
   <si>
     <t xml:space="preserve">5.19042682647705</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">5.18258619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52756929397583</t>
+    <t xml:space="preserve">5.52756977081299</t>
   </si>
   <si>
     <t xml:space="preserve">5.5197286605835</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">5.53540992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41780233383179</t>
+    <t xml:space="preserve">5.41780185699463</t>
   </si>
   <si>
     <t xml:space="preserve">5.42564296722412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84119033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76278495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517688751221</t>
+    <t xml:space="preserve">5.84118986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76278448104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517736434937</t>
   </si>
   <si>
     <t xml:space="preserve">5.44132375717163</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">5.40996122360229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38644027709961</t>
+    <t xml:space="preserve">5.38643980026245</t>
   </si>
   <si>
     <t xml:space="preserve">5.34723711013794</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">5.37075853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23746967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97873258590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8376030921936</t>
+    <t xml:space="preserve">5.2374701499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97873210906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83760356903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.89248657226562</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">4.87680530548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98657321929932</t>
+    <t xml:space="preserve">4.98657369613647</t>
   </si>
   <si>
     <t xml:space="preserve">4.57102537155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54750394821167</t>
+    <t xml:space="preserve">4.54750347137451</t>
   </si>
   <si>
     <t xml:space="preserve">4.57886600494385</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">4.1162748336792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84185647964478</t>
+    <t xml:space="preserve">3.84185671806335</t>
   </si>
   <si>
     <t xml:space="preserve">3.63800287246704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26165771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29302000999451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32438206672668</t>
+    <t xml:space="preserve">3.26165747642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29301977157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32438182830811</t>
   </si>
   <si>
     <t xml:space="preserve">2.90099382400513</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">3.05780434608459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94803714752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00292062759399</t>
+    <t xml:space="preserve">2.94803690910339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00292038917542</t>
   </si>
   <si>
     <t xml:space="preserve">3.13620948791504</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">3.21461462974548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25381708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22245526313782</t>
+    <t xml:space="preserve">3.25381755828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2224555015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.24205660820007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24597668647766</t>
+    <t xml:space="preserve">3.24597692489624</t>
   </si>
   <si>
     <t xml:space="preserve">3.23813652992249</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">3.36750507354736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34006357192993</t>
+    <t xml:space="preserve">3.34006309509277</t>
   </si>
   <si>
     <t xml:space="preserve">3.45767068862915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59880089759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37142539024353</t>
+    <t xml:space="preserve">3.59880042076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37142562866211</t>
   </si>
   <si>
     <t xml:space="preserve">3.52039527893066</t>
@@ -2297,25 +2297,25 @@
     <t xml:space="preserve">3.54391694068909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72424864768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81049466133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9202618598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33581018447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32796907424927</t>
+    <t xml:space="preserve">3.72424912452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92026257514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3358097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32796955108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.32012891769409</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23388338088989</t>
+    <t xml:space="preserve">4.23388242721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.16331815719604</t>
@@ -2324,76 +2324,76 @@
     <t xml:space="preserve">4.07707214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21820259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19468021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208951950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481363296509</t>
+    <t xml:space="preserve">4.21820211410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740385055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19467973709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208975791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481387138367</t>
   </si>
   <si>
     <t xml:space="preserve">3.83401608467102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84577703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70072746276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009648323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145758628845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74385023117065</t>
+    <t xml:space="preserve">3.8457772731781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70072722434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321877479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265402793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145830154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169014930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385046958923</t>
   </si>
   <si>
     <t xml:space="preserve">3.98298597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29660701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10059356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91634082794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946526527405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03786945343018</t>
+    <t xml:space="preserve">4.29660654067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10059404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91634154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946455001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
     <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763641357422</t>
+    <t xml:space="preserve">4.14763736724854</t>
   </si>
   <si>
     <t xml:space="preserve">4.01434803009033</t>
@@ -2402,58 +2402,58 @@
     <t xml:space="preserve">3.95162391662598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94378328323364</t>
+    <t xml:space="preserve">3.94378352165222</t>
   </si>
   <si>
     <t xml:space="preserve">3.88889956474304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05355024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.030029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89282011985779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810273170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85753798484802</t>
+    <t xml:space="preserve">4.05355072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923151016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03002882003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89281964302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810201644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753774642944</t>
   </si>
   <si>
     <t xml:space="preserve">3.8653781414032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82617545127869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105916976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90850114822388</t>
+    <t xml:space="preserve">3.82617592811584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458059310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850162506104</t>
   </si>
   <si>
     <t xml:space="preserve">3.77913212776184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75561118125916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777054786682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657410621643</t>
+    <t xml:space="preserve">3.755610704422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74777030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657458305359</t>
   </si>
   <si>
     <t xml:space="preserve">3.88497924804688</t>
@@ -2462,13 +2462,13 @@
     <t xml:space="preserve">3.96730494499207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02218866348267</t>
+    <t xml:space="preserve">4.02218961715698</t>
   </si>
   <si>
     <t xml:space="preserve">3.93594264984131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76345157623291</t>
+    <t xml:space="preserve">3.76345133781433</t>
   </si>
   <si>
     <t xml:space="preserve">3.75953102111816</t>
@@ -2477,52 +2477,52 @@
     <t xml:space="preserve">3.64584374427795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66936469078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544485092163</t>
+    <t xml:space="preserve">3.6693651676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544508934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.63016223907471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56351852416992</t>
+    <t xml:space="preserve">3.56351757049561</t>
   </si>
   <si>
     <t xml:space="preserve">3.56743836402893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59096002578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119282722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44198989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38710618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3322229385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278744697571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43806934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551108360291</t>
+    <t xml:space="preserve">3.5909595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903298377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44198966026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38710641860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654143333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33222246170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238879203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43806982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551132202148</t>
   </si>
   <si>
     <t xml:space="preserve">3.49295330047607</t>
@@ -2534,43 +2534,43 @@
     <t xml:space="preserve">3.55567765235901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50079393386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51255440711975</t>
+    <t xml:space="preserve">3.50079417228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51255464553833</t>
   </si>
   <si>
     <t xml:space="preserve">3.37926578521729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43414926528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630887031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4615912437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44983053207397</t>
+    <t xml:space="preserve">3.43414974212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630863189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46159100532532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4498302936554</t>
   </si>
   <si>
     <t xml:space="preserve">3.15189051628113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20677423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17541193962097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52823615074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215599060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607678413391</t>
+    <t xml:space="preserve">3.20677447319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17541265487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52823543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215622901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607654571533</t>
   </si>
   <si>
     <t xml:space="preserve">4.10843420028687</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">4.0927529335022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06139183044434</t>
+    <t xml:space="preserve">4.06139087677002</t>
   </si>
   <si>
     <t xml:space="preserve">4.28876638412476</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39853382110596</t>
+    <t xml:space="preserve">4.3985333442688</t>
   </si>
   <si>
     <t xml:space="preserve">4.35933065414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69647359848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75919771194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976198196411</t>
+    <t xml:space="preserve">4.69647312164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7591986656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976245880127</t>
   </si>
   <si>
     <t xml:space="preserve">4.7278356552124</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">4.74351739883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76703834533691</t>
+    <t xml:space="preserve">4.76703882217407</t>
   </si>
   <si>
     <t xml:space="preserve">4.77487897872925</t>
@@ -2630,43 +2630,43 @@
     <t xml:space="preserve">4.73567676544189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68863391876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80624151229858</t>
+    <t xml:space="preserve">4.68863296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80624103546143</t>
   </si>
   <si>
     <t xml:space="preserve">5.01009464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99441432952881</t>
+    <t xml:space="preserve">4.99441337585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.9473705291748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86112451553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84544372558594</t>
+    <t xml:space="preserve">4.86112499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84544324874878</t>
   </si>
   <si>
     <t xml:space="preserve">4.91600847244263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93952941894531</t>
+    <t xml:space="preserve">4.93953037261963</t>
   </si>
   <si>
     <t xml:space="preserve">5.04929733276367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58245325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68437957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59813404083252</t>
+    <t xml:space="preserve">5.58245277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59813356399536</t>
   </si>
   <si>
     <t xml:space="preserve">5.62949657440186</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">5.69222068786621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66869831085205</t>
+    <t xml:space="preserve">5.66869878768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.66085815429688</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">5.72358226776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78630685806274</t>
+    <t xml:space="preserve">5.78630638122559</t>
   </si>
   <si>
     <t xml:space="preserve">6.08424663543701</t>
@@ -2702,19 +2702,19 @@
     <t xml:space="preserve">6.05288457870483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97447872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720283508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15080690383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00474500656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11834812164307</t>
+    <t xml:space="preserve">5.97447919845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720331192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15080642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00474452972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11834859848022</t>
   </si>
   <si>
     <t xml:space="preserve">6.49161577224731</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">6.45915842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42670059204102</t>
+    <t xml:space="preserve">6.42670011520386</t>
   </si>
   <si>
     <t xml:space="preserve">6.2644100189209</t>
@@ -2732,25 +2732,25 @@
     <t xml:space="preserve">6.41047096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39424228668213</t>
+    <t xml:space="preserve">6.39424180984497</t>
   </si>
   <si>
     <t xml:space="preserve">6.4429292678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96225833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077806472778</t>
+    <t xml:space="preserve">6.96225881576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077854156494</t>
   </si>
   <si>
     <t xml:space="preserve">7.43290090560913</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00091648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83862543106079</t>
+    <t xml:space="preserve">8.00091743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83862638473511</t>
   </si>
   <si>
     <t xml:space="preserve">7.87108516693115</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">7.78993988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91977119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95222902297974</t>
+    <t xml:space="preserve">7.91977262496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95223140716553</t>
   </si>
   <si>
     <t xml:space="preserve">7.90354251861572</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">8.60139179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6419620513916</t>
+    <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.56081867218018</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">8.43910121917725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1956672668457</t>
+    <t xml:space="preserve">8.19566440582275</t>
   </si>
   <si>
     <t xml:space="preserve">8.23623752593994</t>
@@ -2789,22 +2789,22 @@
     <t xml:space="preserve">8.01714611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06583309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96845960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40044212341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25438070297241</t>
+    <t xml:space="preserve">8.06583213806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96845865249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4004430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25438117980957</t>
   </si>
   <si>
     <t xml:space="preserve">7.4815878868103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64387893676758</t>
+    <t xml:space="preserve">7.64387798309326</t>
   </si>
   <si>
     <t xml:space="preserve">7.5627326965332</t>
@@ -2813,61 +2813,61 @@
     <t xml:space="preserve">7.69256544113159</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72502374649048</t>
+    <t xml:space="preserve">7.72502279281616</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62764930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535921096802</t>
+    <t xml:space="preserve">7.62764883041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4653582572937</t>
   </si>
   <si>
     <t xml:space="preserve">7.30306911468506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22192287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81619691848755</t>
+    <t xml:space="preserve">7.22192335128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81619739532471</t>
   </si>
   <si>
     <t xml:space="preserve">7.15700626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23815250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38421392440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70879411697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61141967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010761260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53027486801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74125194549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35795593261719</t>
+    <t xml:space="preserve">7.23815202713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38421440124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70879459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61142110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010713577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53027534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74125242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3579568862915</t>
   </si>
   <si>
     <t xml:space="preserve">8.1550931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96654415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84482765197754</t>
+    <t xml:space="preserve">8.96654510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84482669830322</t>
   </si>
   <si>
     <t xml:space="preserve">8.76368236541748</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">8.5202465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39852809906006</t>
+    <t xml:space="preserve">8.39853000640869</t>
   </si>
   <si>
     <t xml:space="preserve">8.47967433929443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3173828125</t>
+    <t xml:space="preserve">8.31738471984863</t>
   </si>
   <si>
     <t xml:space="preserve">8.08206272125244</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">8.03337478637695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04960346221924</t>
+    <t xml:space="preserve">8.04960536956787</t>
   </si>
   <si>
     <t xml:space="preserve">9.04769039154053</t>
@@ -2903,31 +2903,31 @@
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940879821777</t>
+    <t xml:space="preserve">9.16940689086914</t>
   </si>
   <si>
     <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40345001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23627662658691</t>
+    <t xml:space="preserve">9.40344905853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23627758026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.48703575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7795877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61241436004639</t>
+    <t xml:space="preserve">9.77958679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6124153137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.57062149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52882766723633</t>
+    <t xml:space="preserve">9.52882862091064</t>
   </si>
   <si>
     <t xml:space="preserve">9.69600105285645</t>
@@ -2945,64 +2945,64 @@
     <t xml:space="preserve">9.31986331939697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27806949615479</t>
+    <t xml:space="preserve">9.2780704498291</t>
   </si>
   <si>
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15269088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86013793945312</t>
+    <t xml:space="preserve">9.15268993377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86013984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.7765531539917</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35862159729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60937976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19448280334473</t>
+    <t xml:space="preserve">8.35862255096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6093807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19448375701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1108980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06910514831543</t>
+    <t xml:space="preserve">9.11089706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36165523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06910610198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.94372463226318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90193176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81834697723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56758689880371</t>
+    <t xml:space="preserve">8.901930809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81834602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56758785247803</t>
   </si>
   <si>
     <t xml:space="preserve">8.52579402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73476028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20816707611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30846977233887</t>
+    <t xml:space="preserve">8.7347583770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20816612243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30846881866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.32518768310547</t>
@@ -3011,40 +3011,40 @@
     <t xml:space="preserve">7.65649747848511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82366943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321538925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154626846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07139348983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10482835769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68993186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45589113235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053821563721</t>
+    <t xml:space="preserve">7.82366991043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321443557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154674530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07139444351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10482788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68993234634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45589065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053916931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.80695247650146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62306213378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99084329605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09114646911621</t>
+    <t xml:space="preserve">7.62306308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99084234237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09114456176758</t>
   </si>
   <si>
     <t xml:space="preserve">8.04099369049072</t>
@@ -3053,25 +3053,25 @@
     <t xml:space="preserve">8.27503490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40041542053223</t>
+    <t xml:space="preserve">8.40041446685791</t>
   </si>
   <si>
     <t xml:space="preserve">8.1078634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48400211334229</t>
+    <t xml:space="preserve">8.48400020599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.30011177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35026264190674</t>
+    <t xml:space="preserve">8.35026359558105</t>
   </si>
   <si>
     <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8738226890564</t>
+    <t xml:space="preserve">7.87382173538208</t>
   </si>
   <si>
     <t xml:space="preserve">7.69829082489014</t>
@@ -3080,34 +3080,34 @@
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531190872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77351856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91561603546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78187656402588</t>
+    <t xml:space="preserve">7.81531238555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77351760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91561460494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78187704086304</t>
   </si>
   <si>
     <t xml:space="preserve">7.60634660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89889669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79859447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023504257202</t>
+    <t xml:space="preserve">7.89889764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79859399795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023551940918</t>
   </si>
   <si>
     <t xml:space="preserve">7.83202838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63978099822998</t>
+    <t xml:space="preserve">7.63978004455566</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">8.21538066864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28514862060547</t>
+    <t xml:space="preserve">8.28514957427979</t>
   </si>
   <si>
     <t xml:space="preserve">8.32003498077393</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">8.38108253479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19793796539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49445819854736</t>
+    <t xml:space="preserve">8.19793701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49445915222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.69504642486572</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678535461426</t>
+    <t xml:space="preserve">8.54678726196289</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
@@ -3164,25 +3164,25 @@
     <t xml:space="preserve">8.45957374572754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1281681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93630123138428</t>
+    <t xml:space="preserve">8.17177391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12816715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93630170822144</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77931928634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95374345779419</t>
+    <t xml:space="preserve">7.71827077865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77931976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95374393463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.14561080932617</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">8.0496768951416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86653232574463</t>
+    <t xml:space="preserve">7.86653184890747</t>
   </si>
   <si>
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804016113281</t>
+    <t xml:space="preserve">7.78804111480713</t>
   </si>
   <si>
     <t xml:space="preserve">7.65722274780273</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">7.76187658309937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69210767745972</t>
+    <t xml:space="preserve">7.6921067237854</t>
   </si>
   <si>
     <t xml:space="preserve">7.70082855224609</t>
@@ -3221,16 +3221,16 @@
     <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50024080276489</t>
+    <t xml:space="preserve">7.73571348190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50024127960205</t>
   </si>
   <si>
     <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55256843566895</t>
+    <t xml:space="preserve">7.55256795883179</t>
   </si>
   <si>
     <t xml:space="preserve">7.447913646698</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">7.50896167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57001066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80548286437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74443483352661</t>
+    <t xml:space="preserve">7.57001113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80548334121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74443435668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">8.48573684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50318050384521</t>
+    <t xml:space="preserve">8.5031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.607834815979</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">8.41596698760986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3461971282959</t>
+    <t xml:space="preserve">8.34619808197021</t>
   </si>
   <si>
     <t xml:space="preserve">8.02351379394531</t>
@@ -3284,34 +3284,34 @@
     <t xml:space="preserve">8.37236213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89269495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83164596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66594362258911</t>
+    <t xml:space="preserve">7.89269542694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83164644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66594314575195</t>
   </si>
   <si>
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97118711471558</t>
+    <t xml:space="preserve">7.97118616104126</t>
   </si>
   <si>
     <t xml:space="preserve">7.68338632583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16883516311646</t>
+    <t xml:space="preserve">7.33453750610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1688346862793</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418037414551</t>
+    <t xml:space="preserve">7.06418085098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
@@ -3335,22 +3335,22 @@
     <t xml:space="preserve">6.63684129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87231397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75315570831299</t>
+    <t xml:space="preserve">6.87231349945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75315618515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.4391918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43047189712524</t>
+    <t xml:space="preserve">7.43047142028809</t>
   </si>
   <si>
     <t xml:space="preserve">7.49151992797852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27348899841309</t>
+    <t xml:space="preserve">7.27348947525024</t>
   </si>
   <si>
     <t xml:space="preserve">7.39558601379395</t>
@@ -3359,49 +3359,49 @@
     <t xml:space="preserve">7.38686513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35198068618774</t>
+    <t xml:space="preserve">7.3519811630249</t>
   </si>
   <si>
     <t xml:space="preserve">7.31709575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47407722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.290931224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30837440490723</t>
+    <t xml:space="preserve">7.47407674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29093170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581663131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30837392807007</t>
   </si>
   <si>
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663547515869</t>
+    <t xml:space="preserve">7.45663499832153</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781049728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03223514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1020040512085</t>
+    <t xml:space="preserve">7.85781002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03223419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10200500488281</t>
   </si>
   <si>
     <t xml:space="preserve">8.15433216094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05839824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09328365325928</t>
+    <t xml:space="preserve">8.05839729309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09328269958496</t>
   </si>
   <si>
     <t xml:space="preserve">8.00607109069824</t>
@@ -3410,22 +3410,22 @@
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584095001221</t>
+    <t xml:space="preserve">8.11072540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584190368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97990703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98862886428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90141677856445</t>
+    <t xml:space="preserve">7.97990655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98862838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90141725540161</t>
   </si>
   <si>
     <t xml:space="preserve">7.84908962249756</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">7.91885852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82292556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11944675445557</t>
+    <t xml:space="preserve">7.82292652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11944770812988</t>
   </si>
   <si>
     <t xml:space="preserve">8.2589864730835</t>
@@ -3446,19 +3446,19 @@
     <t xml:space="preserve">8.27642822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.337477684021</t>
+    <t xml:space="preserve">8.33747673034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.52934265136719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94796180725098</t>
+    <t xml:space="preserve">8.94796085357666</t>
   </si>
   <si>
     <t xml:space="preserve">8.87819194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563465118408</t>
+    <t xml:space="preserve">8.89563369750977</t>
   </si>
   <si>
     <t xml:space="preserve">8.65144062042236</t>
@@ -3470,25 +3470,25 @@
     <t xml:space="preserve">8.79098033905029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70376777648926</t>
+    <t xml:space="preserve">8.70376682281494</t>
   </si>
   <si>
     <t xml:space="preserve">8.71248912811279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86074924468994</t>
+    <t xml:space="preserve">8.86075019836426</t>
   </si>
   <si>
     <t xml:space="preserve">8.93051910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62527751922607</t>
+    <t xml:space="preserve">8.62527656555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.56422805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46829509735107</t>
+    <t xml:space="preserve">8.46829605102539</t>
   </si>
   <si>
     <t xml:space="preserve">8.6863260269165</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">8.91307735443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00028800964355</t>
+    <t xml:space="preserve">8.96540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00028896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3521,22 +3521,22 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842304229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66888332366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91124629974365</t>
+    <t xml:space="preserve">8.80842208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66888236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91124534606934</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85674285888672</t>
+    <t xml:space="preserve">8.82040786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8567419052124</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422660827637</t>
+    <t xml:space="preserve">8.58422756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498722076416</t>
+    <t xml:space="preserve">8.77498817443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3584,19 +3584,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49339008331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3843822479248</t>
+    <t xml:space="preserve">8.49338912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38438320159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453884124756</t>
+    <t xml:space="preserve">8.18453788757324</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896446228027</t>
+    <t xml:space="preserve">8.33896350860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09369945526123</t>
+    <t xml:space="preserve">8.09370040893555</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04827976226807</t>
+    <t xml:space="preserve">8.04828071594238</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644916534424</t>
+    <t xml:space="preserve">8.06644821166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3662,40 +3662,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919792175293</t>
+    <t xml:space="preserve">8.03919696807861</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9483585357666</t>
+    <t xml:space="preserve">8.00286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94835901260376</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744276046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90293884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385557174683</t>
+    <t xml:space="preserve">7.95744228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9029393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385461807251</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85751962661743</t>
+    <t xml:space="preserve">7.85752010345459</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210088729858</t>
+    <t xml:space="preserve">7.81210136413574</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126293182373</t>
+    <t xml:space="preserve">7.72126245498657</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568855285645</t>
+    <t xml:space="preserve">7.87568807601929</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950824737549</t>
+    <t xml:space="preserve">7.63950777053833</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4941668510437</t>
+    <t xml:space="preserve">7.49416637420654</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4124116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44874715805054</t>
+    <t xml:space="preserve">7.41241216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4487476348877</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112392425537</t>
+    <t xml:space="preserve">6.73112440109253</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72204065322876</t>
+    <t xml:space="preserve">6.7220401763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486722946167</t>
+    <t xml:space="preserve">6.59486675262451</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272296905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767621994019</t>
+    <t xml:space="preserve">7.01272344589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699247360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31248998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790967941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767669677734</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393291473389</t>
+    <t xml:space="preserve">7.79393339157104</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3845,31 +3845,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9665265083313</t>
+    <t xml:space="preserve">7.76668214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96652698516846</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47599840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607669830322</t>
+    <t xml:space="preserve">7.63042449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.475998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607717514038</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523874282837</t>
+    <t xml:space="preserve">7.28523921966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264514923096</t>
+    <t xml:space="preserve">7.11264562606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225700378418</t>
+    <t xml:space="preserve">7.61225652694702</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890327453613</t>
+    <t xml:space="preserve">7.24890279769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -71348,7 +71348,7 @@
     </row>
     <row r="2566">
       <c r="A2566" s="1" t="n">
-        <v>46058.6912384259</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B2566" t="n">
         <v>7639</v>
@@ -71369,6 +71369,32 @@
         <v>1391</v>
       </c>
       <c r="H2566" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" s="1" t="n">
+        <v>46059.691099537</v>
+      </c>
+      <c r="B2567" t="n">
+        <v>988</v>
+      </c>
+      <c r="C2567" t="n">
+        <v>10.5500001907349</v>
+      </c>
+      <c r="D2567" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="E2567" t="n">
+        <v>10.3500003814697</v>
+      </c>
+      <c r="F2567" t="n">
+        <v>10.4499998092651</v>
+      </c>
+      <c r="G2567" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H2567" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">1.21355497837067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22546648979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20654845237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23177254199982</t>
+    <t xml:space="preserve">1.22546637058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20654857158661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23177242279053</t>
   </si>
   <si>
     <t xml:space="preserve">1.2499897480011</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">1.26330244541168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27311158180237</t>
+    <t xml:space="preserve">1.27311182022095</t>
   </si>
   <si>
     <t xml:space="preserve">1.26120042800903</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24718701839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20794975757599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19323563575745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17501854896545</t>
+    <t xml:space="preserve">1.24718713760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2079496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19323551654816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17501831054688</t>
   </si>
   <si>
     <t xml:space="preserve">1.19814038276672</t>
@@ -86,43 +86,43 @@
     <t xml:space="preserve">1.24578583240509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23457491397858</t>
+    <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
     <t xml:space="preserve">1.21495640277863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18272566795349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17992305755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641949653625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12457025051117</t>
+    <t xml:space="preserve">1.1827255487442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17992317676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12457036972046</t>
   </si>
   <si>
     <t xml:space="preserve">1.12807369232178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10284972190857</t>
+    <t xml:space="preserve">1.10284948348999</t>
   </si>
   <si>
     <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01596701145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0250757932663</t>
+    <t xml:space="preserve">1.01596713066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02507567405701</t>
   </si>
   <si>
     <t xml:space="preserve">1.02017104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00195372104645</t>
+    <t xml:space="preserve">1.00195360183716</t>
   </si>
   <si>
     <t xml:space="preserve">1.02297365665436</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">1.04329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0965439081192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11335980892181</t>
+    <t xml:space="preserve">1.09654378890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11335968971252</t>
   </si>
   <si>
     <t xml:space="preserve">1.1105569601059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09304010868073</t>
+    <t xml:space="preserve">1.0930403470993</t>
   </si>
   <si>
     <t xml:space="preserve">1.12106716632843</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">1.13017582893372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15610027313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10004711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1315770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10705363750458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13227772712708</t>
+    <t xml:space="preserve">1.15610039234161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10004699230194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13157713413239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10705387592316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13227784633636</t>
   </si>
   <si>
     <t xml:space="preserve">1.11826431751251</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">1.18412709236145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17081427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16310703754425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22616696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508500099182</t>
+    <t xml:space="preserve">1.17081451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16310715675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22616708278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508512020111</t>
   </si>
   <si>
     <t xml:space="preserve">1.24088108539581</t>
@@ -197,31 +197,31 @@
     <t xml:space="preserve">1.20514726638794</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19113397598267</t>
+    <t xml:space="preserve">1.19113373756409</t>
   </si>
   <si>
     <t xml:space="preserve">1.22686779499054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22196304798126</t>
+    <t xml:space="preserve">1.22196292877197</t>
   </si>
   <si>
     <t xml:space="preserve">1.24438452720642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17221558094025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183444976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19743990898132</t>
+    <t xml:space="preserve">1.17221570014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183433055878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19743967056274</t>
   </si>
   <si>
     <t xml:space="preserve">1.20374584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20304489135742</t>
+    <t xml:space="preserve">1.203045129776</t>
   </si>
   <si>
     <t xml:space="preserve">1.23807847499847</t>
@@ -230,19 +230,19 @@
     <t xml:space="preserve">1.2331737279892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19954180717468</t>
+    <t xml:space="preserve">1.1995415687561</t>
   </si>
   <si>
     <t xml:space="preserve">1.22476577758789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21845948696136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916043758392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896981239319</t>
+    <t xml:space="preserve">1.21845972537994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916031837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2289696931839</t>
   </si>
   <si>
     <t xml:space="preserve">1.21215379238129</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">1.29202961921692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29623365402222</t>
+    <t xml:space="preserve">1.29623377323151</t>
   </si>
   <si>
     <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28712511062622</t>
+    <t xml:space="preserve">1.28712499141693</t>
   </si>
   <si>
     <t xml:space="preserve">1.28151977062225</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">1.24788773059845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23737800121307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865035057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15469920635223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14138638973236</t>
+    <t xml:space="preserve">1.23737788200378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865046977997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15469908714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14138627052307</t>
   </si>
   <si>
     <t xml:space="preserve">1.11896502971649</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13648176193237</t>
+    <t xml:space="preserve">1.13648164272308</t>
   </si>
   <si>
     <t xml:space="preserve">1.14629113674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14208710193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07202053070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084632396698</t>
+    <t xml:space="preserve">1.14208698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0720202922821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08463227748871</t>
   </si>
   <si>
     <t xml:space="preserve">1.06501364707947</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">1.07061910629272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253037929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902681827545</t>
+    <t xml:space="preserve">1.08253026008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902705669403</t>
   </si>
   <si>
     <t xml:space="preserve">1.05800712108612</t>
@@ -320,31 +320,31 @@
     <t xml:space="preserve">1.1014484167099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10355031490326</t>
+    <t xml:space="preserve">1.10355043411255</t>
   </si>
   <si>
     <t xml:space="preserve">1.09514224529266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11966574192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934628009796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11265909671783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1568009853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528052806854</t>
+    <t xml:space="preserve">1.11966562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934639930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11265921592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15680110454559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528040885925</t>
   </si>
   <si>
     <t xml:space="preserve">1.4868152141571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48821651935577</t>
+    <t xml:space="preserve">1.48821663856506</t>
   </si>
   <si>
     <t xml:space="preserve">1.45178186893463</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">1.40133380889893</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4699991941452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776857852936</t>
+    <t xml:space="preserve">1.46999907493591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776845932007</t>
   </si>
   <si>
     <t xml:space="preserve">1.42375528812408</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">1.41674852371216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42235398292542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814982891083</t>
+    <t xml:space="preserve">1.42235374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
@@ -395,40 +395,40 @@
     <t xml:space="preserve">1.69421243667603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338336467743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8007138967514</t>
+    <t xml:space="preserve">1.66338312625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80071365833282</t>
   </si>
   <si>
     <t xml:space="preserve">1.84555673599243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7923059463501</t>
+    <t xml:space="preserve">1.79230606555939</t>
   </si>
   <si>
     <t xml:space="preserve">1.79090476036072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7726868391037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064744472504</t>
+    <t xml:space="preserve">1.77268743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064720630646</t>
   </si>
   <si>
     <t xml:space="preserve">1.71663391590118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670060634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84275424480438</t>
+    <t xml:space="preserve">1.78670048713684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8427540063858</t>
   </si>
   <si>
     <t xml:space="preserve">1.82593786716461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82313549518585</t>
+    <t xml:space="preserve">1.82313525676727</t>
   </si>
   <si>
     <t xml:space="preserve">1.83995127677917</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">1.83854997158051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84415531158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8301420211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472718715668</t>
+    <t xml:space="preserve">1.84415507316589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014178276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472730636597</t>
   </si>
   <si>
     <t xml:space="preserve">1.82874059677124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81192481517792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83294486999512</t>
+    <t xml:space="preserve">1.81192445755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83294463157654</t>
   </si>
   <si>
     <t xml:space="preserve">1.84835922718048</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.86937952041626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99549949169159</t>
+    <t xml:space="preserve">1.99549925327301</t>
   </si>
   <si>
     <t xml:space="preserve">2.0725724697113</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">2.0291314125061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08798766136169</t>
+    <t xml:space="preserve">2.08798742294312</t>
   </si>
   <si>
     <t xml:space="preserve">2.04034209251404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99830222129822</t>
+    <t xml:space="preserve">1.99830186367035</t>
   </si>
   <si>
     <t xml:space="preserve">2.0305323600769</t>
@@ -485,22 +485,22 @@
     <t xml:space="preserve">2.01932215690613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9997034072876</t>
+    <t xml:space="preserve">1.99970364570618</t>
   </si>
   <si>
     <t xml:space="preserve">2.01231551170349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09359240531921</t>
+    <t xml:space="preserve">2.09359288215637</t>
   </si>
   <si>
     <t xml:space="preserve">2.17066597938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15945529937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989379405975</t>
+    <t xml:space="preserve">2.15945553779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989403247833</t>
   </si>
   <si>
     <t xml:space="preserve">1.88339245319366</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">2.01651930809021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00250577926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98428869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9786833524704</t>
+    <t xml:space="preserve">2.00250649452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98428893089294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97868311405182</t>
   </si>
   <si>
     <t xml:space="preserve">1.93944585323334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9198272228241</t>
+    <t xml:space="preserve">1.91982746124268</t>
   </si>
   <si>
     <t xml:space="preserve">1.86377394199371</t>
@@ -536,40 +536,40 @@
     <t xml:space="preserve">1.86797797679901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87918829917908</t>
+    <t xml:space="preserve">1.87918865680695</t>
   </si>
   <si>
     <t xml:space="preserve">1.85676753520966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78950345516205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301120281219</t>
+    <t xml:space="preserve">1.78950321674347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631959438324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301144123077</t>
   </si>
   <si>
     <t xml:space="preserve">1.89880728721619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91001796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99690067768097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849284648895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224882125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9576632976532</t>
+    <t xml:space="preserve">1.91001772880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99690091609955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849260807037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9856903553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224858283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766317844391</t>
   </si>
   <si>
     <t xml:space="preserve">1.96186721324921</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">1.9702752828598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96607112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0039074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397413253784</t>
+    <t xml:space="preserve">1.96607136726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00390720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397389411926</t>
   </si>
   <si>
     <t xml:space="preserve">2.18888354301453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1650607585907</t>
+    <t xml:space="preserve">2.16506052017212</t>
   </si>
   <si>
     <t xml:space="preserve">2.13283014297485</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">2.11321139335632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14404106140137</t>
+    <t xml:space="preserve">2.14404058456421</t>
   </si>
   <si>
     <t xml:space="preserve">2.13002729415894</t>
@@ -623,31 +623,31 @@
     <t xml:space="preserve">2.14824461936951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13423132896423</t>
+    <t xml:space="preserve">2.13423156738281</t>
   </si>
   <si>
     <t xml:space="preserve">2.14123821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15244889259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13703417778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11181020736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09779644012451</t>
+    <t xml:space="preserve">2.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13703393936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11180996894836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09779691696167</t>
   </si>
   <si>
     <t xml:space="preserve">2.11881685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10200095176697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741542816162</t>
+    <t xml:space="preserve">2.10200071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1174156665802</t>
   </si>
   <si>
     <t xml:space="preserve">2.24213433265686</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">2.4873673915863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316335678101</t>
+    <t xml:space="preserve">2.49297285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316359519958</t>
   </si>
   <si>
     <t xml:space="preserve">2.46494626998901</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">2.46634745597839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44392609596252</t>
+    <t xml:space="preserve">2.44392585754395</t>
   </si>
   <si>
     <t xml:space="preserve">2.43972253799438</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">2.47615694999695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45513653755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437403678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47335410118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65552759170532</t>
+    <t xml:space="preserve">2.45513677597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47335433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65552735328674</t>
   </si>
   <si>
     <t xml:space="preserve">2.71858787536621</t>
@@ -710,43 +710,43 @@
     <t xml:space="preserve">2.84751057624817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78865432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1109607219696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23988366127014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38422131538391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129488945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003174781799</t>
+    <t xml:space="preserve">2.78865456581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11096143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23988342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38422155380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129441261292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003127098083</t>
   </si>
   <si>
     <t xml:space="preserve">3.58040809631348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69251394271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66098380088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69601821899414</t>
+    <t xml:space="preserve">3.69251441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66098523139954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601774215698</t>
   </si>
   <si>
     <t xml:space="preserve">3.78360080718994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95176124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386804580688</t>
+    <t xml:space="preserve">3.95176029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386852264404</t>
   </si>
   <si>
     <t xml:space="preserve">4.19349193572998</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">4.16896820068359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1129150390625</t>
+    <t xml:space="preserve">4.11291408538818</t>
   </si>
   <si>
     <t xml:space="preserve">4.03233861923218</t>
@@ -770,10 +770,10 @@
     <t xml:space="preserve">4.55433511734009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6979718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50023508071899</t>
+    <t xml:space="preserve">4.69797229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50023555755615</t>
   </si>
   <si>
     <t xml:space="preserve">4.79256153106689</t>
@@ -785,76 +785,76 @@
     <t xml:space="preserve">5.01677513122559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44768524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44418239593506</t>
+    <t xml:space="preserve">5.44768571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4441819190979</t>
   </si>
   <si>
     <t xml:space="preserve">5.77349519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39708995819092</t>
+    <t xml:space="preserve">6.39708805084229</t>
   </si>
   <si>
     <t xml:space="preserve">6.76143598556519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49518251419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238946914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369230270386</t>
+    <t xml:space="preserve">6.49518203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238851547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369325637817</t>
   </si>
   <si>
     <t xml:space="preserve">6.97858285903931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7843337059021</t>
+    <t xml:space="preserve">6.78433275222778</t>
   </si>
   <si>
     <t xml:space="preserve">6.35626602172852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53252840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35266828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07208585739136</t>
+    <t xml:space="preserve">6.53252935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35266780853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07208633422852</t>
   </si>
   <si>
     <t xml:space="preserve">6.32389068603516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43900156021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40302848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19798803329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37425184249878</t>
+    <t xml:space="preserve">6.43900060653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4030294418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15841960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19798898696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37425136566162</t>
   </si>
   <si>
     <t xml:space="preserve">6.47137594223022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1512246131897</t>
+    <t xml:space="preserve">6.32748699188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15122413635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.11165523529053</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">5.93898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85265684127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90661478042603</t>
+    <t xml:space="preserve">5.96057319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85265636444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90661525726318</t>
   </si>
   <si>
     <t xml:space="preserve">5.89582300186157</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">5.69437980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70157384872437</t>
+    <t xml:space="preserve">5.70157432556152</t>
   </si>
   <si>
     <t xml:space="preserve">5.3670334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87421560287476</t>
+    <t xml:space="preserve">4.87421607971191</t>
   </si>
   <si>
     <t xml:space="preserve">5.17997884750366</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">4.97853565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96414566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84543895721436</t>
+    <t xml:space="preserve">4.96414613723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8454384803772</t>
   </si>
   <si>
     <t xml:space="preserve">4.87781381607056</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">4.9101881980896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70155048370361</t>
+    <t xml:space="preserve">4.70155000686646</t>
   </si>
   <si>
     <t xml:space="preserve">4.92457723617554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69075918197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6583833694458</t>
+    <t xml:space="preserve">4.76989793777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.690758228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65838384628296</t>
   </si>
   <si>
     <t xml:space="preserve">4.68716096878052</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">4.82385587692261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55046701431274</t>
+    <t xml:space="preserve">4.5504674911499</t>
   </si>
   <si>
     <t xml:space="preserve">4.51089859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49291181564331</t>
+    <t xml:space="preserve">4.49291276931763</t>
   </si>
   <si>
     <t xml:space="preserve">4.43895435333252</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38499593734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46413421630859</t>
+    <t xml:space="preserve">4.38499641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46413469314575</t>
   </si>
   <si>
     <t xml:space="preserve">5.03609085083008</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.80946588516235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76629972457886</t>
+    <t xml:space="preserve">4.76630020141602</t>
   </si>
   <si>
     <t xml:space="preserve">4.68356418609619</t>
@@ -977,52 +977,52 @@
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6727728843689</t>
+    <t xml:space="preserve">4.6619815826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277193069458</t>
   </si>
   <si>
     <t xml:space="preserve">4.74831342697144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75910472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9533543586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8310489654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14400720596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1152286529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19436740875244</t>
+    <t xml:space="preserve">4.75910568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14400672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11522912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19436693191528</t>
   </si>
   <si>
     <t xml:space="preserve">5.10803461074829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93536901473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7555079460144</t>
+    <t xml:space="preserve">4.93536806106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550746917725</t>
   </si>
   <si>
     <t xml:space="preserve">4.99652147293091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90659093856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92098045349121</t>
+    <t xml:space="preserve">4.90659141540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92097997665405</t>
   </si>
   <si>
     <t xml:space="preserve">4.82025766372681</t>
@@ -1031,58 +1031,58 @@
     <t xml:space="preserve">4.89220190048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0540771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01810455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95695161819458</t>
+    <t xml:space="preserve">5.05407667160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0181040763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95695114135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.94615983963013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15839576721191</t>
+    <t xml:space="preserve">5.15839529037476</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393678665161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60804653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8994197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7771143913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18000221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20878028869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52533388137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03613662719727</t>
+    <t xml:space="preserve">5.60804605484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89942026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77711486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18000268936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20877981185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52533435821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03613758087158</t>
   </si>
   <si>
     <t xml:space="preserve">6.89584636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11527585983276</t>
+    <t xml:space="preserve">7.11527633666992</t>
   </si>
   <si>
     <t xml:space="preserve">7.13685941696167</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">8.12968921661377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43904781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704650878906</t>
+    <t xml:space="preserve">8.43904876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.29518413543701</t>
@@ -1109,31 +1109,31 @@
     <t xml:space="preserve">8.42465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6189079284668</t>
+    <t xml:space="preserve">8.61890983581543</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321605682373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01457691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8059401512146</t>
+    <t xml:space="preserve">8.01457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80593919754028</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393836975098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299383163452</t>
+    <t xml:space="preserve">7.99299478530884</t>
   </si>
   <si>
     <t xml:space="preserve">8.10091114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98580121994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8850793838501</t>
+    <t xml:space="preserve">7.9858021736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88507843017578</t>
   </si>
   <si>
     <t xml:space="preserve">7.73399639129639</t>
@@ -1145,94 +1145,94 @@
     <t xml:space="preserve">7.54694032669067</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47499799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341491699219</t>
+    <t xml:space="preserve">7.47499704360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341396331787</t>
   </si>
   <si>
     <t xml:space="preserve">7.52535820007324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38866376876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23760509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84191274642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702219009399</t>
+    <t xml:space="preserve">7.38866472244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23760604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84191179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702314376831</t>
   </si>
   <si>
     <t xml:space="preserve">7.84910583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04335594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824411392212</t>
+    <t xml:space="preserve">8.04335498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824459075928</t>
   </si>
   <si>
     <t xml:space="preserve">7.85630178451538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74838638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463636398315</t>
+    <t xml:space="preserve">7.74838542938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571983337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42463541030884</t>
   </si>
   <si>
     <t xml:space="preserve">7.19441509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96419382095337</t>
+    <t xml:space="preserve">6.96419477462769</t>
   </si>
   <si>
     <t xml:space="preserve">7.21599769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97498512268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2088041305542</t>
+    <t xml:space="preserve">6.97498416900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20880317687988</t>
   </si>
   <si>
     <t xml:space="preserve">7.20160913467407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55413484573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485811233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2519702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722009658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00736045837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89944458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95340204238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844297409058</t>
+    <t xml:space="preserve">7.55413579940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485715866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25196981430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477529525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722057342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448360443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00735998153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89944410324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95340251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844249725342</t>
   </si>
   <si>
     <t xml:space="preserve">6.91742992401123</t>
@@ -1244,208 +1244,208 @@
     <t xml:space="preserve">6.89224910736084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78793001174927</t>
+    <t xml:space="preserve">6.78793048858643</t>
   </si>
   <si>
     <t xml:space="preserve">6.95699977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93541526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98218011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16204071044922</t>
+    <t xml:space="preserve">6.93541622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98218059539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1620397567749</t>
   </si>
   <si>
     <t xml:space="preserve">7.14045715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02174806594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82752323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25918579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15846538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91385746002197</t>
+    <t xml:space="preserve">7.02174949645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33830213546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82752418518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25918674468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15846729278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91385555267334</t>
   </si>
   <si>
     <t xml:space="preserve">7.89946842193604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81313323974609</t>
+    <t xml:space="preserve">7.81313419342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.66924571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76996850967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48219108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79152679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836206436157</t>
+    <t xml:space="preserve">7.76996755599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48219203948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79152727127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74836254119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.56850051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64044523239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48936319351196</t>
+    <t xml:space="preserve">6.64044570922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4893627166748</t>
   </si>
   <si>
     <t xml:space="preserve">6.63325119018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62605619430542</t>
+    <t xml:space="preserve">6.62605571746826</t>
   </si>
   <si>
     <t xml:space="preserve">6.56130599975586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60447263717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791904449463</t>
+    <t xml:space="preserve">6.60447359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791809082031</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87783670425415</t>
+    <t xml:space="preserve">6.02172470092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
     <t xml:space="preserve">5.86344766616821</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633548736572</t>
+    <t xml:space="preserve">6.25914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633501052856</t>
   </si>
   <si>
     <t xml:space="preserve">6.44619607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46777820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51814031600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46058320999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29511308670044</t>
+    <t xml:space="preserve">6.46777868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51813983917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46058368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2951135635376</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086297988892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13683605194092</t>
+    <t xml:space="preserve">6.13683557510376</t>
   </si>
   <si>
     <t xml:space="preserve">5.92819738388062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93539190292358</t>
+    <t xml:space="preserve">5.93539237976074</t>
   </si>
   <si>
     <t xml:space="preserve">5.89222478866577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79869890213013</t>
+    <t xml:space="preserve">5.79869842529297</t>
   </si>
   <si>
     <t xml:space="preserve">5.97136497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01453065872192</t>
+    <t xml:space="preserve">6.01453113555908</t>
   </si>
   <si>
     <t xml:space="preserve">5.99294757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17280769348145</t>
+    <t xml:space="preserve">6.1728081703186</t>
   </si>
   <si>
     <t xml:space="preserve">6.18719720840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25194644927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22316837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12244749069214</t>
+    <t xml:space="preserve">6.25194597244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22316789627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12244701385498</t>
   </si>
   <si>
     <t xml:space="preserve">6.27353048324585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30950260162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30230712890625</t>
+    <t xml:space="preserve">6.30950307846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30230808258057</t>
   </si>
   <si>
     <t xml:space="preserve">6.33828020095825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58551740646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38323259353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46564483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326290130615</t>
+    <t xml:space="preserve">6.58551692962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38323163986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326337814331</t>
   </si>
   <si>
     <t xml:space="preserve">6.30831146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41319990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17345428466797</t>
+    <t xml:space="preserve">6.59300851821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41320037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17345380783081</t>
   </si>
   <si>
     <t xml:space="preserve">6.09853410720825</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">5.95618438720703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9411997795105</t>
+    <t xml:space="preserve">5.94120025634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.86627960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9486927986145</t>
+    <t xml:space="preserve">5.94869232177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.84380435943604</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">5.59656572341919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48418521881104</t>
+    <t xml:space="preserve">5.48418474197388</t>
   </si>
   <si>
     <t xml:space="preserve">5.60405826568604</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">5.888756275177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80634355545044</t>
+    <t xml:space="preserve">5.80634307861328</t>
   </si>
   <si>
     <t xml:space="preserve">5.64151859283447</t>
@@ -1493,13 +1493,13 @@
     <t xml:space="preserve">5.79135894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76139116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88126373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621660232544</t>
+    <t xml:space="preserve">5.76139068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88126420974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621612548828</t>
   </si>
   <si>
     <t xml:space="preserve">6.33078765869141</t>
@@ -1508,22 +1508,19 @@
     <t xml:space="preserve">6.55554962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45815229415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33827972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12850284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06107330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77637529373169</t>
+    <t xml:space="preserve">6.45815277099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30081939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.128502368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06107378005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77637577056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.76888275146484</t>
@@ -1532,7 +1529,7 @@
     <t xml:space="preserve">5.70145463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66399383544922</t>
+    <t xml:space="preserve">5.66399478912354</t>
   </si>
   <si>
     <t xml:space="preserve">5.57408952713013</t>
@@ -1541,7 +1538,7 @@
     <t xml:space="preserve">5.75389909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78386688232422</t>
+    <t xml:space="preserve">5.78386735916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.67897844314575</t>
@@ -1556,10 +1553,10 @@
     <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54412126541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58158159255981</t>
+    <t xml:space="preserve">5.54412221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58158111572266</t>
   </si>
   <si>
     <t xml:space="preserve">5.5066614151001</t>
@@ -1577,13 +1574,13 @@
     <t xml:space="preserve">5.31935977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189897537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49167633056641</t>
+    <t xml:space="preserve">5.28189945220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49167680740356</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415348052979</t>
@@ -1595,7 +1592,7 @@
     <t xml:space="preserve">5.27440738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18450307846069</t>
+    <t xml:space="preserve">5.18450260162354</t>
   </si>
   <si>
     <t xml:space="preserve">5.2069787979126</t>
@@ -1604,7 +1601,7 @@
     <t xml:space="preserve">5.5890736579895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74640703201294</t>
+    <t xml:space="preserve">5.74640655517578</t>
   </si>
   <si>
     <t xml:space="preserve">5.47669315338135</t>
@@ -1613,406 +1610,409 @@
     <t xml:space="preserve">5.21447086334229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13955068588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09459829330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10958194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07212114334106</t>
+    <t xml:space="preserve">5.13954973220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09459781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10958242416382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07212162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05713844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87732887268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86983633041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7349796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77243947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82488441467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88482046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75745582580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234378814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9147891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8548526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95224905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16951894760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08710622787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13205862045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25586700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01612091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99364471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04215335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94475698471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99720144271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0271692276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8923134803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95974111557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81739139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79491567611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78742456436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83237600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97472476959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76494741439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47275733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047252655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38285255432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32291698455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30043983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31542444229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46526527404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777273178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71250343322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10209035873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07961416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726491928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25942325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19948720932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11707401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28939199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16202640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31186771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41675615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44672441482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421743392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89624786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85878753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12100982666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22589826583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00113677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885149002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91123199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00862979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872453689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631134033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377214431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97116804122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21091413497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09104156494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15097808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14348602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608869552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859710693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142290115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70894718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170854568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73891448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55161333084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47268533706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019426345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33155584335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35507726669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30803489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26883125305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14338350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06497812271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00225448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20610761642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33939647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235363006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11986255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13554334640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09634017944336</t>
   </si>
   <si>
     <t xml:space="preserve">5.05713796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01967763900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466176986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977285385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87732887268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86983680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73497915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77243947982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82488489151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88482093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75745582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9147891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89980459213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85485219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95224905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16951894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710622787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13205814361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21840667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25586700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01612043380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602474212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99364566802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04215383529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221731185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94475698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99720144271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0271692276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89231300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95974111557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81739187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7949161529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78742361068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83237600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97472524642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729665756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76494741439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4727578163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047204971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38285255432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32291650772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30043935775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31542444229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46526527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10209035873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07961416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726444244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01218557357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19948720932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11707401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28939199447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16202640533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31186819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41675615310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4467248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39427995681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40926456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89624786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85878801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12100982666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22589874267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383562088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00113725662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82132816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91123199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03110504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.008629322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97116851806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21091413497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09104108810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15097808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14348602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859758377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142337799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393035888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70894622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916887283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170854568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73891448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55161333084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47268533706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019426345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33155632019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35507726669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30803442001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39428043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24531030654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26883172988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14338350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06497859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00225448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20610761642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33939647674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11986255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13554286956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09634065628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11202144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17474603652954</t>
+    <t xml:space="preserve">5.11202096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17474555969238</t>
   </si>
   <si>
     <t xml:space="preserve">5.44916391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45700454711914</t>
+    <t xml:space="preserve">5.45700407028198</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70790147781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67653894424438</t>
+    <t xml:space="preserve">5.70790195465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733673095703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55893182754517</t>
+    <t xml:space="preserve">5.55893135070801</t>
   </si>
   <si>
     <t xml:space="preserve">5.51188850402832</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48052597045898</t>
+    <t xml:space="preserve">5.48052644729614</t>
   </si>
   <si>
     <t xml:space="preserve">5.36291837692261</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">5.3237156867981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19826745986938</t>
+    <t xml:space="preserve">5.19826793670654</t>
   </si>
   <si>
     <t xml:space="preserve">4.79840040206909</t>
@@ -2057,55 +2057,55 @@
     <t xml:space="preserve">4.6415901184082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71215534210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67295217514038</t>
+    <t xml:space="preserve">4.71215486526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67295265197754</t>
   </si>
   <si>
     <t xml:space="preserve">4.63374948501587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64943075180054</t>
+    <t xml:space="preserve">4.64943027496338</t>
   </si>
   <si>
     <t xml:space="preserve">4.59454679489136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62590837478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68079280853271</t>
+    <t xml:space="preserve">4.62590885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68079233169556</t>
   </si>
   <si>
     <t xml:space="preserve">4.90032768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22962951660156</t>
+    <t xml:space="preserve">5.2296290397644</t>
   </si>
   <si>
     <t xml:space="preserve">5.02577590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04145669937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1512246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22178936004639</t>
+    <t xml:space="preserve">5.04145622253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15122413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22178888320923</t>
   </si>
   <si>
     <t xml:space="preserve">5.21394824981689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15906476974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08065891265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12770223617554</t>
+    <t xml:space="preserve">5.15906429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08065938949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1277027130127</t>
   </si>
   <si>
     <t xml:space="preserve">5.01793527603149</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">5.08849954605103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19042682647705</t>
+    <t xml:space="preserve">5.19042730331421</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52756881713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5197286605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40212106704712</t>
+    <t xml:space="preserve">5.52756929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51972818374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
     <t xml:space="preserve">5.56677198410034</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">5.53540992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41780138015747</t>
+    <t xml:space="preserve">5.41780233383179</t>
   </si>
   <si>
     <t xml:space="preserve">5.42564249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84118986129761</t>
+    <t xml:space="preserve">5.84118938446045</t>
   </si>
   <si>
     <t xml:space="preserve">5.76278495788574</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">5.44132375717163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40996122360229</t>
+    <t xml:space="preserve">5.40996170043945</t>
   </si>
   <si>
     <t xml:space="preserve">5.38643980026245</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">4.97873258590698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8376030921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89248704910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86896514892578</t>
+    <t xml:space="preserve">4.83760356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89248657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86896467208862</t>
   </si>
   <si>
     <t xml:space="preserve">4.92384910583496</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57102537155151</t>
+    <t xml:space="preserve">4.57102584838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750394821167</t>
@@ -2210,19 +2210,19 @@
     <t xml:space="preserve">4.39069318771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15547752380371</t>
+    <t xml:space="preserve">4.15547800064087</t>
   </si>
   <si>
     <t xml:space="preserve">4.2260422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11627435684204</t>
+    <t xml:space="preserve">4.1162748336792</t>
   </si>
   <si>
     <t xml:space="preserve">3.84185695648193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63800311088562</t>
+    <t xml:space="preserve">3.63800263404846</t>
   </si>
   <si>
     <t xml:space="preserve">3.26165771484375</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">3.32438182830811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90099382400513</t>
+    <t xml:space="preserve">2.90099406242371</t>
   </si>
   <si>
     <t xml:space="preserve">3.09700703620911</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">3.00292015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13620972633362</t>
+    <t xml:space="preserve">3.13620948791504</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036236763</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">3.22245526313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24205684661865</t>
+    <t xml:space="preserve">3.24205660820007</t>
   </si>
   <si>
     <t xml:space="preserve">3.24597668647766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23813629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36750483512878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34006333351135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45767092704773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59880018234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37142539024353</t>
+    <t xml:space="preserve">3.23813652992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36750507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34006309509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59880065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37142562866211</t>
   </si>
   <si>
     <t xml:space="preserve">3.52039480209351</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">3.9202618598938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33580923080444</t>
+    <t xml:space="preserve">4.3358097076416</t>
   </si>
   <si>
     <t xml:space="preserve">4.32796907424927</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">4.23388290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16331768035889</t>
+    <t xml:space="preserve">4.1633186340332</t>
   </si>
   <si>
     <t xml:space="preserve">4.07707214355469</t>
@@ -2324,31 +2324,31 @@
     <t xml:space="preserve">4.21820211410522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21036052703857</t>
+    <t xml:space="preserve">4.21036100387573</t>
   </si>
   <si>
     <t xml:space="preserve">4.25740432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19468021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208904266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481363296509</t>
+    <t xml:space="preserve">4.19467973709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208951950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481410980225</t>
   </si>
   <si>
     <t xml:space="preserve">3.83401560783386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84577703475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70072650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009600639343</t>
+    <t xml:space="preserve">3.84577751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009648323059</t>
   </si>
   <si>
     <t xml:space="preserve">3.87321901321411</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">3.80265426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82225561141968</t>
+    <t xml:space="preserve">3.82225513458252</t>
   </si>
   <si>
     <t xml:space="preserve">3.86145853996277</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">3.75169014930725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74385046958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298573493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29660749435425</t>
+    <t xml:space="preserve">3.74385023117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29660701751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.10059404373169</t>
@@ -2381,19 +2381,19 @@
     <t xml:space="preserve">3.91634130477905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95946478843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03786945343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1397967338562</t>
+    <t xml:space="preserve">3.95946526527405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03786993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13979625701904</t>
   </si>
   <si>
     <t xml:space="preserve">4.14763689041138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01434850692749</t>
+    <t xml:space="preserve">4.01434803009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.95162391662598</t>
@@ -2411,25 +2411,25 @@
     <t xml:space="preserve">4.06923198699951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.030029296875</t>
+    <t xml:space="preserve">4.03002882003784</t>
   </si>
   <si>
     <t xml:space="preserve">3.89282011985779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92810273170471</t>
+    <t xml:space="preserve">3.92810225486755</t>
   </si>
   <si>
     <t xml:space="preserve">3.91242122650146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85753798484802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86537766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617545127869</t>
+    <t xml:space="preserve">3.85753750801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8653781414032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617592811584</t>
   </si>
   <si>
     <t xml:space="preserve">3.88105869293213</t>
@@ -2438,16 +2438,16 @@
     <t xml:space="preserve">3.90458106994629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90850114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913236618042</t>
+    <t xml:space="preserve">3.90850162506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.779132604599</t>
   </si>
   <si>
     <t xml:space="preserve">3.75561046600342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74777054786682</t>
+    <t xml:space="preserve">3.74777007102966</t>
   </si>
   <si>
     <t xml:space="preserve">3.80657410621643</t>
@@ -2456,31 +2456,31 @@
     <t xml:space="preserve">3.88497924804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96730542182922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02218866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594288825989</t>
+    <t xml:space="preserve">3.96730494499207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02218818664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594264984131</t>
   </si>
   <si>
     <t xml:space="preserve">3.76345157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75953149795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64584350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66936492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016295433044</t>
+    <t xml:space="preserve">3.75953102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6458432674408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66936540603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016223907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.56351804733276</t>
@@ -2492,34 +2492,34 @@
     <t xml:space="preserve">3.59096002578735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48903274536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119235038757</t>
+    <t xml:space="preserve">3.48903322219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119282722473</t>
   </si>
   <si>
     <t xml:space="preserve">3.44198966026306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3871066570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3322229385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278720855713</t>
+    <t xml:space="preserve">3.38710641860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654191017151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33222270011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278744697571</t>
   </si>
   <si>
     <t xml:space="preserve">3.42238855361938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43806982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551156044006</t>
+    <t xml:space="preserve">3.43807005882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551132202148</t>
   </si>
   <si>
     <t xml:space="preserve">3.49295353889465</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">3.55175733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55567741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50079369544983</t>
+    <t xml:space="preserve">3.55567765235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50079417228699</t>
   </si>
   <si>
     <t xml:space="preserve">3.51255464553833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37926578521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43414926528931</t>
+    <t xml:space="preserve">3.37926602363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43414974212646</t>
   </si>
   <si>
     <t xml:space="preserve">3.42630887031555</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">3.44983005523682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15189075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20677447319031</t>
+    <t xml:space="preserve">3.15189051628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20677423477173</t>
   </si>
   <si>
     <t xml:space="preserve">3.17541241645813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52823567390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215646743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53607654571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10843372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866700172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20252132415771</t>
+    <t xml:space="preserve">3.52823543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215599060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53607630729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10843420028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252084732056</t>
   </si>
   <si>
     <t xml:space="preserve">4.13195610046387</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">4.06139135360718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2887659072876</t>
+    <t xml:space="preserve">4.28876638412476</t>
   </si>
   <si>
     <t xml:space="preserve">4.2495641708374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24172258377075</t>
+    <t xml:space="preserve">4.24172306060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.39853382110596</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">4.69647359848022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75919818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976245880127</t>
+    <t xml:space="preserve">4.75919771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976293563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.7278356552124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74351692199707</t>
+    <t xml:space="preserve">4.74351739883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.76703882217407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77487945556641</t>
+    <t xml:space="preserve">4.77487897872925</t>
   </si>
   <si>
     <t xml:space="preserve">4.73567676544189</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">4.80624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.010094165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99441385269165</t>
+    <t xml:space="preserve">5.01009511947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99441337585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.9473705291748</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">4.91600847244263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93953037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04929733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245229721069</t>
+    <t xml:space="preserve">4.93952989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04929685592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245277404785</t>
   </si>
   <si>
     <t xml:space="preserve">5.68438005447388</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">5.62949657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7157416343689</t>
+    <t xml:space="preserve">5.71574115753174</t>
   </si>
   <si>
     <t xml:space="preserve">5.69222068786621</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">5.66869878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66085863113403</t>
+    <t xml:space="preserve">5.66085815429688</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358226776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78630685806274</t>
+    <t xml:space="preserve">5.78630638122559</t>
   </si>
   <si>
     <t xml:space="preserve">6.08424663543701</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">6.1783332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14697170257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288362503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97447872161865</t>
+    <t xml:space="preserve">6.14697122573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288410186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97447919845581</t>
   </si>
   <si>
     <t xml:space="preserve">6.03720283508301</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">6.15080642700195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00474500656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11834812164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49161624908447</t>
+    <t xml:space="preserve">6.00474548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11834859848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49161577224731</t>
   </si>
   <si>
     <t xml:space="preserve">6.45915842056274</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">6.42670011520386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26440906524658</t>
+    <t xml:space="preserve">6.26440954208374</t>
   </si>
   <si>
     <t xml:space="preserve">6.41047143936157</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">6.39424228668213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4429292678833</t>
+    <t xml:space="preserve">6.44292879104614</t>
   </si>
   <si>
     <t xml:space="preserve">6.96225786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14077758789062</t>
+    <t xml:space="preserve">7.14077806472778</t>
   </si>
   <si>
     <t xml:space="preserve">7.43290042877197</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">7.78993988037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91977119445801</t>
+    <t xml:space="preserve">7.91977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">7.95222997665405</t>
@@ -2765,16 +2765,16 @@
     <t xml:space="preserve">7.90354251861572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60139179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64196395874023</t>
+    <t xml:space="preserve">8.60139083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.56081867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43910121917725</t>
+    <t xml:space="preserve">8.43910026550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.19566535949707</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">7.96845865249634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40044212341309</t>
+    <t xml:space="preserve">7.4004430770874</t>
   </si>
   <si>
     <t xml:space="preserve">7.25438117980957</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">7.64387798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56273174285889</t>
+    <t xml:space="preserve">7.5627326965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.69256448745728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72502279281616</t>
+    <t xml:space="preserve">7.72502374649048</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">7.30306816101074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22192239761353</t>
+    <t xml:space="preserve">7.22192287445068</t>
   </si>
   <si>
     <t xml:space="preserve">6.81619691848755</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">7.15700674057007</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23815202713013</t>
+    <t xml:space="preserve">7.23815250396729</t>
   </si>
   <si>
     <t xml:space="preserve">7.38421392440796</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">7.61142015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66010665893555</t>
+    <t xml:space="preserve">7.66010761260986</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">8.1550931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96654605865479</t>
+    <t xml:space="preserve">8.96654510498047</t>
   </si>
   <si>
     <t xml:space="preserve">8.84482765197754</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">8.08206272125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11452102661133</t>
+    <t xml:space="preserve">8.11452007293701</t>
   </si>
   <si>
     <t xml:space="preserve">8.03337478637695</t>
@@ -2894,13 +2894,13 @@
     <t xml:space="preserve">8.04960441589355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04768943786621</t>
+    <t xml:space="preserve">9.04769039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940784454346</t>
+    <t xml:space="preserve">9.16940879821777</t>
   </si>
   <si>
     <t xml:space="preserve">9.4452428817749</t>
@@ -21004,7 +21004,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21030,7 +21030,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G630" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21056,7 +21056,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G631" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21082,7 +21082,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G632" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21108,7 +21108,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21134,7 +21134,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G634" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21160,7 +21160,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G635" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21212,7 +21212,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G637" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21238,7 +21238,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G638" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21264,7 +21264,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G639" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21290,7 +21290,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G640" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21316,7 +21316,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G641" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21342,7 +21342,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21368,7 +21368,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G643" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21394,7 +21394,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G644" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21420,7 +21420,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G645" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21446,7 +21446,7 @@
         <v>7.5</v>
       </c>
       <c r="G646" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21472,7 +21472,7 @@
         <v>7.5</v>
       </c>
       <c r="G647" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21498,7 +21498,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G648" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21524,7 +21524,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G649" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21550,7 +21550,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G650" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21576,7 +21576,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G651" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21602,7 +21602,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G652" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21628,7 +21628,7 @@
         <v>7.25</v>
       </c>
       <c r="G653" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21654,7 +21654,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21680,7 +21680,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21706,7 +21706,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21732,7 +21732,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G657" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -21758,7 +21758,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G658" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21784,7 +21784,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G659" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21836,7 +21836,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G661" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21862,7 +21862,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G662" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21888,7 +21888,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G663" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21914,7 +21914,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G664" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21940,7 +21940,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21966,7 +21966,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G666" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21992,7 +21992,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G667" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22018,7 +22018,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G668" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22044,7 +22044,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G669" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22070,7 +22070,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22096,7 +22096,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G671" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22122,7 +22122,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G672" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22148,7 +22148,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G673" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22174,7 +22174,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G674" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22200,7 +22200,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G675" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22226,7 +22226,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22252,7 +22252,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22278,7 +22278,7 @@
         <v>6.75</v>
       </c>
       <c r="G678" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22304,7 +22304,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G679" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22330,7 +22330,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G680" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22356,7 +22356,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22382,7 +22382,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G682" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22408,7 +22408,7 @@
         <v>6.5</v>
       </c>
       <c r="G683" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22434,7 +22434,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G684" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22460,7 +22460,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G685" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22486,7 +22486,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G686" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22512,7 +22512,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22538,7 +22538,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G688" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22564,7 +22564,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G689" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22590,7 +22590,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G690" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22616,7 +22616,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G691" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22642,7 +22642,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22668,7 +22668,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22694,7 +22694,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G694" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22720,7 +22720,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G695" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -22746,7 +22746,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22772,7 +22772,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G697" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22798,7 +22798,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G698" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22824,7 +22824,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G699" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22850,7 +22850,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G700" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22876,7 +22876,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G701" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22902,7 +22902,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G702" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22928,7 +22928,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G703" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22954,7 +22954,7 @@
         <v>8</v>
       </c>
       <c r="G704" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23006,7 +23006,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G706" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23032,7 +23032,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G707" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23058,7 +23058,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G708" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23084,7 +23084,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23110,7 +23110,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G710" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23136,7 +23136,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G711" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23162,7 +23162,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23188,7 +23188,7 @@
         <v>6.75</v>
       </c>
       <c r="G713" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23214,7 +23214,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G714" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23240,7 +23240,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G715" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23266,7 +23266,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G716" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23292,7 +23292,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G717" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23318,7 +23318,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G718" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23344,7 +23344,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G719" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23370,7 +23370,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G720" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23396,7 +23396,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G721" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23422,7 +23422,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G722" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23448,7 +23448,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G723" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23474,7 +23474,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G724" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23500,7 +23500,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G725" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23526,7 +23526,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G726" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23552,7 +23552,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G727" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23578,7 +23578,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23604,7 +23604,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G729" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23630,7 +23630,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G730" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23656,7 +23656,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23682,7 +23682,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G732" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23708,7 +23708,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G733" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23734,7 +23734,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G734" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23760,7 +23760,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G735" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23786,7 +23786,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G736" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23812,7 +23812,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G737" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23838,7 +23838,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G738" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23864,7 +23864,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G739" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23890,7 +23890,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G740" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23916,7 +23916,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G741" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23942,7 +23942,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23968,7 +23968,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G743" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23994,7 +23994,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24020,7 +24020,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24046,7 +24046,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G746" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24072,7 +24072,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24098,7 +24098,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G748" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24124,7 +24124,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G749" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24150,7 +24150,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G750" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24176,7 +24176,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G751" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24202,7 +24202,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G752" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24228,7 +24228,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G753" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24254,7 +24254,7 @@
         <v>7</v>
       </c>
       <c r="G754" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24280,7 +24280,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G755" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24306,7 +24306,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G756" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24332,7 +24332,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G757" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24358,7 +24358,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24384,7 +24384,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G759" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24410,7 +24410,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G760" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24436,7 +24436,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G761" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24462,7 +24462,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24488,7 +24488,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24514,7 +24514,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24540,7 +24540,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G765" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24566,7 +24566,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24592,7 +24592,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G767" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24618,7 +24618,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G768" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24644,7 +24644,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24670,7 +24670,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G770" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24696,7 +24696,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G771" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24722,7 +24722,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24748,7 +24748,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24774,7 +24774,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G774" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24800,7 +24800,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G775" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24826,7 +24826,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G776" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24852,7 +24852,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G777" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24878,7 +24878,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G778" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24904,7 +24904,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24930,7 +24930,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G780" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25034,7 +25034,7 @@
         <v>8</v>
       </c>
       <c r="G784" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25086,7 +25086,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G786" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25112,7 +25112,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G787" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25138,7 +25138,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25164,7 +25164,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G789" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25216,7 +25216,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G791" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25242,7 +25242,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G792" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25268,7 +25268,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G793" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25320,7 +25320,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G795" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25346,7 +25346,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G796" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25372,7 +25372,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G797" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25424,7 +25424,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G799" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25502,7 +25502,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G802" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25528,7 +25528,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G803" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25580,7 +25580,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25606,7 +25606,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G806" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25632,7 +25632,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G807" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25658,7 +25658,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G808" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25710,7 +25710,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25736,7 +25736,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G811" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25762,7 +25762,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25788,7 +25788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G813" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25814,7 +25814,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G814" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25866,7 +25866,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G816" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25892,7 +25892,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G817" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25918,7 +25918,7 @@
         <v>8</v>
       </c>
       <c r="G818" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25944,7 +25944,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G819" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26048,7 +26048,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G823" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26074,7 +26074,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26100,7 +26100,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G825" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26126,7 +26126,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G826" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26204,7 +26204,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26256,7 +26256,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G831" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26282,7 +26282,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26308,7 +26308,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G833" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26334,7 +26334,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G834" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26360,7 +26360,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G835" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26412,7 +26412,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26438,7 +26438,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26464,7 +26464,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G839" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26490,7 +26490,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G840" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26516,7 +26516,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26542,7 +26542,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G842" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26568,7 +26568,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G843" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26594,7 +26594,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G844" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26620,7 +26620,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G845" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26646,7 +26646,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G846" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26672,7 +26672,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G847" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26698,7 +26698,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G848" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26724,7 +26724,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G849" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26750,7 +26750,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G850" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26776,7 +26776,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G851" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26802,7 +26802,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26828,7 +26828,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G853" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26854,7 +26854,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G854" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26880,7 +26880,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G855" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26906,7 +26906,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G856" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26932,7 +26932,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G857" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26958,7 +26958,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G858" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26984,7 +26984,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G859" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27010,7 +27010,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G860" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27036,7 +27036,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G861" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27062,7 +27062,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G862" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27088,7 +27088,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G863" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27114,7 +27114,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G864" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27140,7 +27140,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G865" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27166,7 +27166,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G866" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27192,7 +27192,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G867" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27218,7 +27218,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27244,7 +27244,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G869" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27270,7 +27270,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G870" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27296,7 +27296,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G871" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27322,7 +27322,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G872" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27348,7 +27348,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27374,7 +27374,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G874" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27400,7 +27400,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G875" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27426,7 +27426,7 @@
         <v>6.75</v>
       </c>
       <c r="G876" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27452,7 +27452,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G877" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27478,7 +27478,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G878" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27504,7 +27504,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G879" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27530,7 +27530,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G880" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27556,7 +27556,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G881" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27582,7 +27582,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G882" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27608,7 +27608,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G883" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27634,7 +27634,7 @@
         <v>6.5</v>
       </c>
       <c r="G884" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27660,7 +27660,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G885" t="s">
-        <v>537</v>
+        <v>657</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27712,7 +27712,7 @@
         <v>6.5</v>
       </c>
       <c r="G887" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27764,7 +27764,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G889" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28050,7 +28050,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28128,7 +28128,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G903" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28154,7 +28154,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G904" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28206,7 +28206,7 @@
         <v>6.75</v>
       </c>
       <c r="G906" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28284,7 +28284,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G909" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -28310,7 +28310,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28362,7 +28362,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G912" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -28388,7 +28388,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G913" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28414,7 +28414,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G914" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29142,7 +29142,7 @@
         <v>6.75</v>
       </c>
       <c r="G942" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29194,7 +29194,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G944" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29376,7 +29376,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G951" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -29402,7 +29402,7 @@
         <v>6.5</v>
       </c>
       <c r="G952" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -29610,7 +29610,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G960" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29688,7 +29688,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G963" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -29740,7 +29740,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G965" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30780,7 +30780,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1005" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30858,7 +30858,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1008" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30936,7 +30936,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1011" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30962,7 +30962,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31092,7 +31092,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1017" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31144,7 +31144,7 @@
         <v>6.75</v>
       </c>
       <c r="G1019" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31170,7 +31170,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31196,7 +31196,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1021" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31248,7 +31248,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1023" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31274,7 +31274,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1024" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31300,7 +31300,7 @@
         <v>6.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31326,7 +31326,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1026" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31352,7 +31352,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1027" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31378,7 +31378,7 @@
         <v>6.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31456,7 +31456,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1031" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31482,7 +31482,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1032" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31560,7 +31560,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1035" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31872,7 +31872,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31976,7 +31976,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1051" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -38424,7 +38424,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1299" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38450,7 +38450,7 @@
         <v>6.5</v>
       </c>
       <c r="G1300" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38476,7 +38476,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1301" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38502,7 +38502,7 @@
         <v>6.5</v>
       </c>
       <c r="G1302" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38970,7 +38970,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1320" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -38996,7 +38996,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1321" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -39620,7 +39620,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1345" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -71842,7 +71842,7 @@
     </row>
     <row r="2585">
       <c r="A2585" s="1" t="n">
-        <v>46085.6912268518</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B2585" t="n">
         <v>5719</v>
@@ -71863,6 +71863,32 @@
         <v>1395</v>
       </c>
       <c r="H2585" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" s="1" t="n">
+        <v>46086.691099537</v>
+      </c>
+      <c r="B2586" t="n">
+        <v>2835</v>
+      </c>
+      <c r="C2586" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="D2586" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="E2586" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="F2586" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="G2586" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H2586" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19253516197205</t>
+    <t xml:space="preserve">1.19253504276276</t>
   </si>
   <si>
     <t xml:space="preserve">GE.MI</t>
@@ -50,79 +50,79 @@
     <t xml:space="preserve">1.22546637058258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20654845237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23177230358124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24998962879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26330256462097</t>
+    <t xml:space="preserve">1.20654833316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23177242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24998998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26330244541168</t>
   </si>
   <si>
     <t xml:space="preserve">1.27311170101166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26120042800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718713760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2079496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19323575496674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17501842975616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19814050197601</t>
+    <t xml:space="preserve">1.26120030879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718701839447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20794975757599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19323563575745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17501854896545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1981406211853</t>
   </si>
   <si>
     <t xml:space="preserve">1.24578583240509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23457503318787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21495628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18272578716278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17992317676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641985416412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12457048892975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12807357311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10284972190857</t>
+    <t xml:space="preserve">1.23457515239716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21495640277863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1827255487442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17992305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641973495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12457036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12807369232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10284960269928</t>
   </si>
   <si>
     <t xml:space="preserve">1.08603370189667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.01596689224243</t>
+    <t xml:space="preserve">1.01596701145172</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507567405701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.02017104625702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00195372104645</t>
+    <t xml:space="preserve">1.02017092704773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00195360183716</t>
   </si>
   <si>
     <t xml:space="preserve">1.02297389507294</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">1.04329311847687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09654378890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11335968971252</t>
+    <t xml:space="preserve">1.0965439081192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1133599281311</t>
   </si>
   <si>
     <t xml:space="preserve">1.11055707931519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0930403470993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106716632843</t>
+    <t xml:space="preserve">1.09304046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106704711914</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017570972443</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">1.15610039234161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10004687309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13157713413239</t>
+    <t xml:space="preserve">1.10004723072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13157689571381</t>
   </si>
   <si>
     <t xml:space="preserve">1.10705363750458</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">1.13227784633636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11826419830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14909386634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17852199077606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1701135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18412721157074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17081427574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16310715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22616708278656</t>
+    <t xml:space="preserve">1.11826431751251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1490935087204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17852175235748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17011368274689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18412709236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17081451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16310703754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22616684436798</t>
   </si>
   <si>
     <t xml:space="preserve">1.24508512020111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24088108539581</t>
+    <t xml:space="preserve">1.24088132381439</t>
   </si>
   <si>
     <t xml:space="preserve">1.20514714717865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19113385677338</t>
+    <t xml:space="preserve">1.19113373756409</t>
   </si>
   <si>
     <t xml:space="preserve">1.22686779499054</t>
@@ -209,13 +209,13 @@
     <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17221570014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183444976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19743978977203</t>
+    <t xml:space="preserve">1.17221581935883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183433055878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19743967056274</t>
   </si>
   <si>
     <t xml:space="preserve">1.20374572277069</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">1.203045129776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23807859420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23317360877991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19954180717468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22476577758789</t>
+    <t xml:space="preserve">1.23807847499847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23317384719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19954168796539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22476589679718</t>
   </si>
   <si>
     <t xml:space="preserve">1.21845972537994</t>
@@ -242,25 +242,25 @@
     <t xml:space="preserve">1.21916043758392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22896957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21215355396271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22266387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29202973842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2962338924408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2752138376236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28712511062622</t>
+    <t xml:space="preserve">1.2289696931839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21215379238129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22266364097595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29202961921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29623377323151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28712522983551</t>
   </si>
   <si>
     <t xml:space="preserve">1.28151977062225</t>
@@ -269,31 +269,31 @@
     <t xml:space="preserve">1.24788773059845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23737788200378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20865046977997</t>
+    <t xml:space="preserve">1.23737800121307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20865035057068</t>
   </si>
   <si>
     <t xml:space="preserve">1.15469920635223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14138627052307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11896502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036645412445</t>
+    <t xml:space="preserve">1.14138638973236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1189649105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036633491516</t>
   </si>
   <si>
     <t xml:space="preserve">1.13648164272308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14629101753235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14208686351776</t>
+    <t xml:space="preserve">1.14629113674164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
     <t xml:space="preserve">1.0720202922821</t>
@@ -311,46 +311,46 @@
     <t xml:space="preserve">1.08253037929535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07902717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05800700187683</t>
+    <t xml:space="preserve">1.07902705669403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05800712108612</t>
   </si>
   <si>
     <t xml:space="preserve">1.1014484167099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10355043411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09514224529266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11966574192047</t>
+    <t xml:space="preserve">1.10355031490326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09514236450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11966586112976</t>
   </si>
   <si>
     <t xml:space="preserve">1.09934628009796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11265897750854</t>
+    <t xml:space="preserve">1.11265909671783</t>
   </si>
   <si>
     <t xml:space="preserve">1.1568009853363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34528040885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4868152141571</t>
+    <t xml:space="preserve">1.34528028964996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48681533336639</t>
   </si>
   <si>
     <t xml:space="preserve">1.48821663856506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45178163051605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41534721851349</t>
+    <t xml:space="preserve">1.45178174972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4153470993042</t>
   </si>
   <si>
     <t xml:space="preserve">1.45738697052002</t>
@@ -359,34 +359,34 @@
     <t xml:space="preserve">1.40133392810822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4699991941452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43776857852936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375528812408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4363671541214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936062812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674852371216</t>
+    <t xml:space="preserve">1.46999907493591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43776845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375516891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43636703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936050891876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674864292145</t>
   </si>
   <si>
     <t xml:space="preserve">1.42235386371613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41814982891083</t>
+    <t xml:space="preserve">1.41814970970154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42795920372009</t>
+    <t xml:space="preserve">1.42795944213867</t>
   </si>
   <si>
     <t xml:space="preserve">1.48120999336243</t>
@@ -395,37 +395,37 @@
     <t xml:space="preserve">1.6942126750946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66338312625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071377754211</t>
+    <t xml:space="preserve">1.66338324546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80071365833282</t>
   </si>
   <si>
     <t xml:space="preserve">1.84555661678314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79230618476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090464115143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268731594086</t>
+    <t xml:space="preserve">1.79230606555939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090452194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268719673157</t>
   </si>
   <si>
     <t xml:space="preserve">1.73064732551575</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71663403511047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78670072555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8427540063858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593786716461</t>
+    <t xml:space="preserve">1.71663415431976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78670060634613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275424480438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8259379863739</t>
   </si>
   <si>
     <t xml:space="preserve">1.82313525676727</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">1.83854985237122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84415531158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83014214038849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81472730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874083518982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192469596863</t>
+    <t xml:space="preserve">1.84415555000305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8301420211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81472718715668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874047756195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192457675934</t>
   </si>
   <si>
     <t xml:space="preserve">1.83294451236725</t>
@@ -458,25 +458,25 @@
     <t xml:space="preserve">1.84835922718048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9954993724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07257270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02913117408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798742294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04034209251404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99830186367035</t>
+    <t xml:space="preserve">1.86937940120697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549925327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07257318496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02913188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798766136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04034185409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99830234050751</t>
   </si>
   <si>
     <t xml:space="preserve">2.03053283691406</t>
@@ -488,58 +488,58 @@
     <t xml:space="preserve">1.9997034072876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01231503486633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066621780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15945553779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989391326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339257240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9716762304306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345938205719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01651954650879</t>
+    <t xml:space="preserve">2.01231551170349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359240531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066597938538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15945529937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989427089691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339281082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167646884918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345914363861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01651930809021</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250601768494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98428857326508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97868299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93944609165192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91982734203339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86377418041229</t>
+    <t xml:space="preserve">1.98428869247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97868311405182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93944585323334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9198272228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86377382278442</t>
   </si>
   <si>
     <t xml:space="preserve">1.86797797679901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87918829917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85676729679108</t>
+    <t xml:space="preserve">1.87918865680695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85676741600037</t>
   </si>
   <si>
     <t xml:space="preserve">1.78950321674347</t>
@@ -548,46 +548,46 @@
     <t xml:space="preserve">1.80631947517395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90301156044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89880740642548</t>
+    <t xml:space="preserve">1.90301132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8988071680069</t>
   </si>
   <si>
     <t xml:space="preserve">1.91001796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99690079689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849272727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9856903553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224870204926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766365528107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186745166779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326899528503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97027492523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0039074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397413253784</t>
+    <t xml:space="preserve">1.99690091609955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849284648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98568987846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96186721324921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326863765717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027504444122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607136726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00390720367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397389411926</t>
   </si>
   <si>
     <t xml:space="preserve">2.18888330459595</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">2.09639525413513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11601400375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499382972717</t>
+    <t xml:space="preserve">2.11601424217224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499430656433</t>
   </si>
   <si>
     <t xml:space="preserve">2.11321139335632</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">2.13002753257751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14824461936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13423156738281</t>
+    <t xml:space="preserve">2.14824485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13423109054565</t>
   </si>
   <si>
     <t xml:space="preserve">2.14123797416687</t>
@@ -635,34 +635,34 @@
     <t xml:space="preserve">2.13703393936157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11180996894836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09779667854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11881685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10200071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24213433265686</t>
+    <t xml:space="preserve">2.11181020736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09779691696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.118816614151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10200047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11741518974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213409423828</t>
   </si>
   <si>
     <t xml:space="preserve">2.48876881599426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48736786842346</t>
+    <t xml:space="preserve">2.4873673915863</t>
   </si>
   <si>
     <t xml:space="preserve">2.49297308921814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48316335678101</t>
+    <t xml:space="preserve">2.48316359519958</t>
   </si>
   <si>
     <t xml:space="preserve">2.46494626998901</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">2.40328764915466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52099990844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48036098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46634721755981</t>
+    <t xml:space="preserve">2.52099943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48036074638367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46634769439697</t>
   </si>
   <si>
     <t xml:space="preserve">2.44392585754395</t>
@@ -686,76 +686,76 @@
     <t xml:space="preserve">2.43972229957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47615718841553</t>
+    <t xml:space="preserve">2.47615694999695</t>
   </si>
   <si>
     <t xml:space="preserve">2.45513653755188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49437427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47335410118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65552735328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71858739852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70457410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751057624817</t>
+    <t xml:space="preserve">2.49437403678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47335433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65552759170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71858763694763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70457434654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751033782959</t>
   </si>
   <si>
     <t xml:space="preserve">2.78865432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11096096038818</t>
+    <t xml:space="preserve">3.11096119880676</t>
   </si>
   <si>
     <t xml:space="preserve">3.23988366127014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38422155380249</t>
+    <t xml:space="preserve">3.38422107696533</t>
   </si>
   <si>
     <t xml:space="preserve">3.46129465103149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71003174781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251441955566</t>
+    <t xml:space="preserve">3.71003150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5804078578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251418113708</t>
   </si>
   <si>
     <t xml:space="preserve">3.66098475456238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69601774215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78360152244568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9517605304718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386756896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19349193572998</t>
+    <t xml:space="preserve">3.69601798057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78360176086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9517617225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386804580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19349241256714</t>
   </si>
   <si>
     <t xml:space="preserve">4.16896820068359</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11291456222534</t>
+    <t xml:space="preserve">4.11291408538818</t>
   </si>
   <si>
     <t xml:space="preserve">4.03233861923218</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">4.30910158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30559873580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55433511734009</t>
+    <t xml:space="preserve">4.30559825897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55433464050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.6979718208313</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">5.50023555755615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79256200790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10085535049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01677465438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44768524169922</t>
+    <t xml:space="preserve">4.79256248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10085582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01677560806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44768571853638</t>
   </si>
   <si>
     <t xml:space="preserve">5.4441819190979</t>
@@ -794,67 +794,67 @@
     <t xml:space="preserve">5.77349519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39708948135376</t>
+    <t xml:space="preserve">6.3970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">6.76143550872803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49518156051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369230270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78433275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626602172852</t>
+    <t xml:space="preserve">6.49518346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369325637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7843337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35626554489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.5325288772583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35266780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07208633422852</t>
+    <t xml:space="preserve">6.35266828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07208585739136</t>
   </si>
   <si>
     <t xml:space="preserve">6.323890209198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43900108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094675064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40302896499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15841960906982</t>
+    <t xml:space="preserve">6.43900156021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094484329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40302848815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15842008590698</t>
   </si>
   <si>
     <t xml:space="preserve">6.19798851013184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37425136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47137546539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15122556686401</t>
+    <t xml:space="preserve">6.37425184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47137594223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3274884223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15122509002686</t>
   </si>
   <si>
     <t xml:space="preserve">6.11165523529053</t>
@@ -863,34 +863,34 @@
     <t xml:space="preserve">5.93898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85265636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90661430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89582300186157</t>
+    <t xml:space="preserve">5.96057224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85265684127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90661478042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89582347869873</t>
   </si>
   <si>
     <t xml:space="preserve">5.75193452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69437885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70157384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36703395843506</t>
+    <t xml:space="preserve">5.6943793296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70157337188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3670334815979</t>
   </si>
   <si>
     <t xml:space="preserve">4.87421560287476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1799783706665</t>
+    <t xml:space="preserve">5.17997884750366</t>
   </si>
   <si>
     <t xml:space="preserve">4.97853469848633</t>
@@ -902,46 +902,46 @@
     <t xml:space="preserve">4.8454384803772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87781429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70155048370361</t>
+    <t xml:space="preserve">4.8778133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9101881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7015495300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.92457675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76989698410034</t>
+    <t xml:space="preserve">4.7698974609375</t>
   </si>
   <si>
     <t xml:space="preserve">4.690758228302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65838384628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68716144561768</t>
+    <t xml:space="preserve">4.6583833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68716096878052</t>
   </si>
   <si>
     <t xml:space="preserve">4.82385540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5504674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51089763641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49291181564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43895435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38139915466309</t>
+    <t xml:space="preserve">4.55046701431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51089859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49291276931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4389533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
     <t xml:space="preserve">4.38499593734741</t>
@@ -950,37 +950,37 @@
     <t xml:space="preserve">4.46413469314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03609037399292</t>
+    <t xml:space="preserve">5.03609085083008</t>
   </si>
   <si>
     <t xml:space="preserve">4.85623025894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80946636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76630020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68356370925903</t>
+    <t xml:space="preserve">4.80946683883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7662992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68356466293335</t>
   </si>
   <si>
     <t xml:space="preserve">4.67636966705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60442543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59003639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62960577011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66198110580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6727728843689</t>
+    <t xml:space="preserve">4.60442590713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59003734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62960624694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66198062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67277240753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.74831390380859</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">4.83104991912842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06486797332764</t>
+    <t xml:space="preserve">5.06486749649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.14400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11522912979126</t>
+    <t xml:space="preserve">5.11522960662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.19436740875244</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.10803461074829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93536901473999</t>
+    <t xml:space="preserve">4.93536853790283</t>
   </si>
   <si>
     <t xml:space="preserve">4.75550842285156</t>
@@ -1019,76 +1019,76 @@
     <t xml:space="preserve">4.99652147293091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90659141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92098045349121</t>
+    <t xml:space="preserve">4.90659093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92097997665405</t>
   </si>
   <si>
     <t xml:space="preserve">4.82025814056396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89220237731934</t>
+    <t xml:space="preserve">4.89220190048218</t>
   </si>
   <si>
     <t xml:space="preserve">5.05407667160034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07925653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0181040763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95695161819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94615936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839576721191</t>
+    <t xml:space="preserve">5.07925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01810359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95695209503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94616031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839529037476</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393678665161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6080470085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8994197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77711534500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03611469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978094100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18000268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20878028869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52533483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03613758087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89584589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527585983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802474975586</t>
+    <t xml:space="preserve">5.60804605484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89942026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77711486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03611421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18000221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20877981185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52533388137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03613805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89584684371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527729034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13685989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6980242729187</t>
   </si>
   <si>
     <t xml:space="preserve">8.12968826293945</t>
@@ -1109,25 +1109,25 @@
     <t xml:space="preserve">8.42465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61890697479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321701049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01457691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8059401512146</t>
+    <t xml:space="preserve">8.61890888214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80593967437744</t>
   </si>
   <si>
     <t xml:space="preserve">8.32393741607666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99299430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10091114044189</t>
+    <t xml:space="preserve">7.99299383163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10091209411621</t>
   </si>
   <si>
     <t xml:space="preserve">7.98580026626587</t>
@@ -1136,22 +1136,22 @@
     <t xml:space="preserve">7.88507843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73399591445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41024780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54694128036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499847412109</t>
+    <t xml:space="preserve">7.73399639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4102463722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54694080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499704360962</t>
   </si>
   <si>
     <t xml:space="preserve">7.45341348648071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52535772323608</t>
+    <t xml:space="preserve">7.52535820007324</t>
   </si>
   <si>
     <t xml:space="preserve">7.38866376876831</t>
@@ -1163,34 +1163,34 @@
     <t xml:space="preserve">7.84191274642944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95702362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84910821914673</t>
+    <t xml:space="preserve">7.95702266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84910726547241</t>
   </si>
   <si>
     <t xml:space="preserve">8.04335594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92824554443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85630178451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74838447570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571744918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.424635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1944146156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419525146484</t>
+    <t xml:space="preserve">7.92824506759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85630083084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74838638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571983337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42463445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419477462769</t>
   </si>
   <si>
     <t xml:space="preserve">7.21599817276001</t>
@@ -1199,25 +1199,25 @@
     <t xml:space="preserve">6.97498464584351</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20880317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20161008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413484573364</t>
+    <t xml:space="preserve">7.2088041305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20160913467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55413579940796</t>
   </si>
   <si>
     <t xml:space="preserve">7.65485763549805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25196981430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722057342529</t>
+    <t xml:space="preserve">7.2519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477529525757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722009658813</t>
   </si>
   <si>
     <t xml:space="preserve">7.10448503494263</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">6.89944458007812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91742944717407</t>
+    <t xml:space="preserve">6.95340251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1584415435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91743087768555</t>
   </si>
   <si>
     <t xml:space="preserve">6.85627746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.892249584198</t>
+    <t xml:space="preserve">6.89225006103516</t>
   </si>
   <si>
     <t xml:space="preserve">6.78793048858643</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">6.95699977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93541669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98217964172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16204023361206</t>
+    <t xml:space="preserve">6.93541574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217916488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203927993774</t>
   </si>
   <si>
     <t xml:space="preserve">7.140456199646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02174854278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.338303565979</t>
+    <t xml:space="preserve">7.0217490196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33830261230469</t>
   </si>
   <si>
     <t xml:space="preserve">7.82752418518066</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">8.25918769836426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15846729278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9138560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89946603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313514709473</t>
+    <t xml:space="preserve">8.15846633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91385698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8994665145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313323974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.66924619674683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76996803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64046955108643</t>
+    <t xml:space="preserve">7.76996850967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046859741211</t>
   </si>
   <si>
     <t xml:space="preserve">7.78435659408569</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">7.48219108581543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79152774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74836206436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56850147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64044427871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325023651123</t>
+    <t xml:space="preserve">6.79152679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7483606338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56850099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64044523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48936319351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325071334839</t>
   </si>
   <si>
     <t xml:space="preserve">6.62605571746826</t>
@@ -1325,61 +1325,61 @@
     <t xml:space="preserve">6.56130647659302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60447406768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55411148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28791809082031</t>
+    <t xml:space="preserve">6.60447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55411195755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28791952133179</t>
   </si>
   <si>
     <t xml:space="preserve">6.19439125061035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02172517776489</t>
+    <t xml:space="preserve">6.02172613143921</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783718109131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633548736572</t>
+    <t xml:space="preserve">5.86344814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633596420288</t>
   </si>
   <si>
     <t xml:space="preserve">6.44619607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46777963638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641639709473</t>
+    <t xml:space="preserve">6.4677791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641687393188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51814031600952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46058368682861</t>
+    <t xml:space="preserve">6.46058464050293</t>
   </si>
   <si>
     <t xml:space="preserve">6.29511308670044</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10086297988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13683557510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92819738388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93539237976074</t>
+    <t xml:space="preserve">6.10086393356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92819786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93539190292358</t>
   </si>
   <si>
     <t xml:space="preserve">5.89222574234009</t>
@@ -1394,37 +1394,37 @@
     <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99294662475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1728081703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18719816207886</t>
+    <t xml:space="preserve">5.99294710159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17280721664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18719720840454</t>
   </si>
   <si>
     <t xml:space="preserve">6.25194597244263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22316837310791</t>
+    <t xml:space="preserve">6.22316884994507</t>
   </si>
   <si>
     <t xml:space="preserve">6.12244749069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27352952957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950260162354</t>
+    <t xml:space="preserve">6.27353000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950212478638</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230760574341</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33828020095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58551740646362</t>
+    <t xml:space="preserve">6.33827972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58551692962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.38323211669922</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">6.46564435958862</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35326290130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30831146240234</t>
+    <t xml:space="preserve">6.35326385498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3083119392395</t>
   </si>
   <si>
     <t xml:space="preserve">6.59300947189331</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">6.41320085525513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17345380783081</t>
+    <t xml:space="preserve">6.17345428466797</t>
   </si>
   <si>
     <t xml:space="preserve">6.09853410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90374040603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618486404419</t>
+    <t xml:space="preserve">5.90373992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
   </si>
   <si>
     <t xml:space="preserve">5.94120025634766</t>
@@ -1466,25 +1466,25 @@
     <t xml:space="preserve">5.94869232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84380435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48418474197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60405826568604</t>
+    <t xml:space="preserve">5.84380388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656572341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48418521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60405778884888</t>
   </si>
   <si>
     <t xml:space="preserve">5.55910539627075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88875579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80634307861328</t>
+    <t xml:space="preserve">5.888756275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80634355545044</t>
   </si>
   <si>
     <t xml:space="preserve">5.64151811599731</t>
@@ -1493,16 +1493,16 @@
     <t xml:space="preserve">5.79135942459106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76139163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88126420974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621612548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078765869141</t>
+    <t xml:space="preserve">5.76139116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88126373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621660232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078670501709</t>
   </si>
   <si>
     <t xml:space="preserve">6.55554914474487</t>
@@ -1511,25 +1511,28 @@
     <t xml:space="preserve">6.45815229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3008189201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12850189208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06107378005981</t>
+    <t xml:space="preserve">6.33827924728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30081939697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.128502368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0610728263855</t>
   </si>
   <si>
     <t xml:space="preserve">5.77637529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.768883228302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70145416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66399431228638</t>
+    <t xml:space="preserve">5.76888275146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70145463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66399478912354</t>
   </si>
   <si>
     <t xml:space="preserve">5.57409000396729</t>
@@ -1538,61 +1541,61 @@
     <t xml:space="preserve">5.75389909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78386640548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67897844314575</t>
+    <t xml:space="preserve">5.78386688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67897891998291</t>
   </si>
   <si>
     <t xml:space="preserve">5.62653398513794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61904144287109</t>
+    <t xml:space="preserve">5.61904239654541</t>
   </si>
   <si>
     <t xml:space="preserve">5.65650320053101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54412174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58158159255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50666093826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53662872314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43174028396606</t>
+    <t xml:space="preserve">5.54412126541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58158206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50666046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53662919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43174076080322</t>
   </si>
   <si>
     <t xml:space="preserve">5.46920108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31935930252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28189945220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42424774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49167776107788</t>
+    <t xml:space="preserve">5.31935977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28189897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42424821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49167728424072</t>
   </si>
   <si>
     <t xml:space="preserve">5.51415348052979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36431217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27440738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450307846069</t>
+    <t xml:space="preserve">5.36431169509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27440690994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450260162354</t>
   </si>
   <si>
     <t xml:space="preserve">5.2069787979126</t>
@@ -1601,16 +1604,16 @@
     <t xml:space="preserve">5.5890736579895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74640655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47669315338135</t>
+    <t xml:space="preserve">5.74640703201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47669363021851</t>
   </si>
   <si>
     <t xml:space="preserve">5.21447086334229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13955068588257</t>
+    <t xml:space="preserve">5.13955020904541</t>
   </si>
   <si>
     <t xml:space="preserve">5.09459781646729</t>
@@ -1625,16 +1628,16 @@
     <t xml:space="preserve">5.05713796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01967811584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466081619263</t>
+    <t xml:space="preserve">5.01967763900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466176986694</t>
   </si>
   <si>
     <t xml:space="preserve">4.92977237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87732839584351</t>
+    <t xml:space="preserve">4.87732887268066</t>
   </si>
   <si>
     <t xml:space="preserve">4.86983633041382</t>
@@ -1643,7 +1646,7 @@
     <t xml:space="preserve">4.7349796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77243947982788</t>
+    <t xml:space="preserve">4.77243995666504</t>
   </si>
   <si>
     <t xml:space="preserve">4.82488393783569</t>
@@ -1652,28 +1655,28 @@
     <t xml:space="preserve">4.88482046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75745582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478872299194</t>
+    <t xml:space="preserve">4.75745487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234426498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9147891998291</t>
   </si>
   <si>
     <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8548526763916</t>
+    <t xml:space="preserve">4.85485219955444</t>
   </si>
   <si>
     <t xml:space="preserve">4.95224905014038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16951894760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08710670471191</t>
+    <t xml:space="preserve">5.16951847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0871057510376</t>
   </si>
   <si>
     <t xml:space="preserve">5.13205862045288</t>
@@ -1682,46 +1685,46 @@
     <t xml:space="preserve">6.21840667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25586748123169</t>
+    <t xml:space="preserve">6.25586652755737</t>
   </si>
   <si>
     <t xml:space="preserve">6.01612091064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10602521896362</t>
+    <t xml:space="preserve">6.10602569580078</t>
   </si>
   <si>
     <t xml:space="preserve">5.99364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04215335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221731185913</t>
+    <t xml:space="preserve">5.04215431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221778869629</t>
   </si>
   <si>
     <t xml:space="preserve">4.94475698471069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99720096588135</t>
+    <t xml:space="preserve">4.99720144271851</t>
   </si>
   <si>
     <t xml:space="preserve">5.02716970443726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89231300354004</t>
+    <t xml:space="preserve">4.89231204986572</t>
   </si>
   <si>
     <t xml:space="preserve">5.04964590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95974063873291</t>
+    <t xml:space="preserve">4.95974159240723</t>
   </si>
   <si>
     <t xml:space="preserve">4.81739187240601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79491662979126</t>
+    <t xml:space="preserve">4.7949161529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.78742361068726</t>
@@ -1730,31 +1733,31 @@
     <t xml:space="preserve">4.83237600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9747257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729713439941</t>
+    <t xml:space="preserve">4.97472524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729665756226</t>
   </si>
   <si>
     <t xml:space="preserve">4.76494741439819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4727578163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27047252655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38285255432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32291603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056631088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558361053467</t>
+    <t xml:space="preserve">4.47275733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27047204971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38285303115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32291650772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558313369751</t>
   </si>
   <si>
     <t xml:space="preserve">4.30043983459473</t>
@@ -1763,13 +1766,13 @@
     <t xml:space="preserve">4.31542444229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46526527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777273178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71250295639038</t>
+    <t xml:space="preserve">4.46526575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7125039100647</t>
   </si>
   <si>
     <t xml:space="preserve">5.10209035873413</t>
@@ -1778,16 +1781,16 @@
     <t xml:space="preserve">5.07961416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93726539611816</t>
+    <t xml:space="preserve">4.93726491928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.01218557357788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24444007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196340560913</t>
+    <t xml:space="preserve">5.24443960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196292877197</t>
   </si>
   <si>
     <t xml:space="preserve">5.25942325592041</t>
@@ -1799,16 +1802,16 @@
     <t xml:space="preserve">5.11707401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">5.289391040802</t>
+    <t xml:space="preserve">5.28939151763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.16202688217163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31186771392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41675662994385</t>
+    <t xml:space="preserve">5.31186819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41675615310669</t>
   </si>
   <si>
     <t xml:space="preserve">5.37180423736572</t>
@@ -1817,22 +1820,22 @@
     <t xml:space="preserve">5.4467248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39427947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421648025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40926504135132</t>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40926456451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.89624786376953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85878753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12101030349731</t>
+    <t xml:space="preserve">5.85878849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12100982666016</t>
   </si>
   <si>
     <t xml:space="preserve">6.22589874267578</t>
@@ -1841,19 +1844,19 @@
     <t xml:space="preserve">5.81383562088013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00113677978516</t>
+    <t xml:space="preserve">6.00113725662231</t>
   </si>
   <si>
     <t xml:space="preserve">5.79885149002075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82132720947266</t>
+    <t xml:space="preserve">5.82132768630981</t>
   </si>
   <si>
     <t xml:space="preserve">5.91123199462891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03110504150391</t>
+    <t xml:space="preserve">6.03110599517822</t>
   </si>
   <si>
     <t xml:space="preserve">6.00862979888916</t>
@@ -1862,43 +1865,43 @@
     <t xml:space="preserve">5.91872406005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83631181716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87377214431763</t>
+    <t xml:space="preserve">5.83631086349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87377166748047</t>
   </si>
   <si>
     <t xml:space="preserve">5.97116804122925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21091413497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09104156494141</t>
+    <t xml:space="preserve">6.21091461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09104204177856</t>
   </si>
   <si>
     <t xml:space="preserve">6.15097808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14348554611206</t>
+    <t xml:space="preserve">6.14348602294922</t>
   </si>
   <si>
     <t xml:space="preserve">6.04608917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02361297607422</t>
+    <t xml:space="preserve">6.02361345291138</t>
   </si>
   <si>
     <t xml:space="preserve">6.03859758377075</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73142290115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69396257400513</t>
+    <t xml:space="preserve">5.73142242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97866010665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69396209716797</t>
   </si>
   <si>
     <t xml:space="preserve">5.72393083572388</t>
@@ -1910,22 +1913,22 @@
     <t xml:space="preserve">5.49916887283325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46170902252197</t>
+    <t xml:space="preserve">5.46170854568481</t>
   </si>
   <si>
     <t xml:space="preserve">5.73891496658325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55161380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47268533706665</t>
+    <t xml:space="preserve">5.55161333084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47268581390381</t>
   </si>
   <si>
     <t xml:space="preserve">5.30019426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33155584335327</t>
+    <t xml:space="preserve">5.33155679702759</t>
   </si>
   <si>
     <t xml:space="preserve">5.46484518051147</t>
@@ -1937,10 +1940,10 @@
     <t xml:space="preserve">5.30803442001343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37859964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39427995681763</t>
+    <t xml:space="preserve">5.37859916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39428091049194</t>
   </si>
   <si>
     <t xml:space="preserve">5.24531030654907</t>
@@ -1949,10 +1952,10 @@
     <t xml:space="preserve">5.26883125305176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28451299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315141677856</t>
+    <t xml:space="preserve">5.28451251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315093994141</t>
   </si>
   <si>
     <t xml:space="preserve">5.14338350296021</t>
@@ -1967,46 +1970,43 @@
     <t xml:space="preserve">5.16690540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20610809326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33939695358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29235363006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11986255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13554334640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09634017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713748931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11202144622803</t>
+    <t xml:space="preserve">5.20610761642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33939599990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29235410690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11986207962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13554382324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09634065628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11202096939087</t>
   </si>
   <si>
     <t xml:space="preserve">5.17474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44916391372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45700454711914</t>
+    <t xml:space="preserve">5.44916439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45700407028198</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70790100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67653846740723</t>
+    <t xml:space="preserve">5.70790147781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67653894424438</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733673095703</t>
@@ -2015,19 +2015,19 @@
     <t xml:space="preserve">5.55893135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51188850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48836755752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48052549362183</t>
+    <t xml:space="preserve">5.51188802719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48836708068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48052597045898</t>
   </si>
   <si>
     <t xml:space="preserve">5.36291837692261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31587505340576</t>
+    <t xml:space="preserve">5.31587553024292</t>
   </si>
   <si>
     <t xml:space="preserve">5.32371616363525</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">5.19826745986938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79840040206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70431470870972</t>
+    <t xml:space="preserve">4.79839992523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7043137550354</t>
   </si>
   <si>
     <t xml:space="preserve">4.71999502182007</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">4.51614189147949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97089195251465</t>
+    <t xml:space="preserve">4.97089242935181</t>
   </si>
   <si>
     <t xml:space="preserve">4.82192230224609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64159059524536</t>
+    <t xml:space="preserve">4.6415901184082</t>
   </si>
   <si>
     <t xml:space="preserve">4.71215534210205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67295217514038</t>
+    <t xml:space="preserve">4.67295265197754</t>
   </si>
   <si>
     <t xml:space="preserve">4.63374948501587</t>
@@ -2069,25 +2069,25 @@
     <t xml:space="preserve">4.64943075180054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59454774856567</t>
+    <t xml:space="preserve">4.59454727172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.62590885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68079280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90032720565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2296290397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02577543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04145669937134</t>
+    <t xml:space="preserve">4.68079233169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90032768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22962951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02577590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04145622253418</t>
   </si>
   <si>
     <t xml:space="preserve">5.15122413635254</t>
@@ -2096,22 +2096,22 @@
     <t xml:space="preserve">5.22178888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21394824981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15906429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08065986633301</t>
+    <t xml:space="preserve">5.21394872665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15906476974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08065938949585</t>
   </si>
   <si>
     <t xml:space="preserve">5.1277027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01793575286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07281827926636</t>
+    <t xml:space="preserve">5.01793527603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07281875610352</t>
   </si>
   <si>
     <t xml:space="preserve">5.08849954605103</t>
@@ -2120,43 +2120,43 @@
     <t xml:space="preserve">5.19042634963989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18258619308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52756929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5197286605835</t>
+    <t xml:space="preserve">5.18258571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52756977081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51972818374634</t>
   </si>
   <si>
     <t xml:space="preserve">5.40212106704712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56677150726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4334831237793</t>
+    <t xml:space="preserve">5.5667724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43348264694214</t>
   </si>
   <si>
     <t xml:space="preserve">5.50404739379883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53540945053101</t>
+    <t xml:space="preserve">5.53540992736816</t>
   </si>
   <si>
     <t xml:space="preserve">5.41780138015747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42564296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84118986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76278448104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517641067505</t>
+    <t xml:space="preserve">5.42564249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84119033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76278495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517736434937</t>
   </si>
   <si>
     <t xml:space="preserve">5.44132328033447</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">5.40996170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38643980026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3472375869751</t>
+    <t xml:space="preserve">5.38643932342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34723663330078</t>
   </si>
   <si>
     <t xml:space="preserve">5.37075901031494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23746967315674</t>
+    <t xml:space="preserve">5.2374701499939</t>
   </si>
   <si>
     <t xml:space="preserve">4.97873258590698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83760356903076</t>
+    <t xml:space="preserve">4.83760261535645</t>
   </si>
   <si>
     <t xml:space="preserve">4.89248704910278</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">4.92384910583496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87680578231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98657274246216</t>
+    <t xml:space="preserve">4.87680530548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98657369613647</t>
   </si>
   <si>
     <t xml:space="preserve">4.57102537155151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54750347137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57886552810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39069366455078</t>
+    <t xml:space="preserve">4.54750394821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57886648178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39069318771362</t>
   </si>
   <si>
     <t xml:space="preserve">4.15547752380371</t>
@@ -2219,19 +2219,19 @@
     <t xml:space="preserve">4.1162748336792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84185647964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63800287246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26165747642517</t>
+    <t xml:space="preserve">3.84185695648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6380033493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26165771484375</t>
   </si>
   <si>
     <t xml:space="preserve">3.29301977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32438182830811</t>
+    <t xml:space="preserve">3.32438206672668</t>
   </si>
   <si>
     <t xml:space="preserve">2.90099382400513</t>
@@ -2240,37 +2240,37 @@
     <t xml:space="preserve">3.09700679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05780458450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94803714752197</t>
+    <t xml:space="preserve">3.05780434608459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94803690910339</t>
   </si>
   <si>
     <t xml:space="preserve">3.00292062759399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13620948791504</t>
+    <t xml:space="preserve">3.13620924949646</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036236763</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21461462974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25381755828857</t>
+    <t xml:space="preserve">3.2146143913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25381708145142</t>
   </si>
   <si>
     <t xml:space="preserve">3.22245526313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24205660820007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23813652992249</t>
+    <t xml:space="preserve">3.24205684661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24597716331482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23813629150391</t>
   </si>
   <si>
     <t xml:space="preserve">3.36750507354736</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">3.45767092704773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59880065917969</t>
+    <t xml:space="preserve">3.59880018234253</t>
   </si>
   <si>
     <t xml:space="preserve">3.37142539024353</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">3.52039480209351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54391694068909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72424864768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81049418449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9202618598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3358097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32796907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32012891769409</t>
+    <t xml:space="preserve">3.54391646385193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72424936294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81049466133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92026209831238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33581018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32796859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32012844085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.23388290405273</t>
@@ -2321,55 +2321,55 @@
     <t xml:space="preserve">4.07707214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21820211410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21036100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740385055542</t>
+    <t xml:space="preserve">4.21820163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21036148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740432739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208928108215</t>
+    <t xml:space="preserve">3.73208951950073</t>
   </si>
   <si>
     <t xml:space="preserve">3.79481363296509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83401608467102</t>
+    <t xml:space="preserve">3.83401584625244</t>
   </si>
   <si>
     <t xml:space="preserve">3.84577703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321877479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265402793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82225489616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145830154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75169062614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74384999275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298597335815</t>
+    <t xml:space="preserve">3.70072650909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009600639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82225561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145853996277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75169014930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385046958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298573493958</t>
   </si>
   <si>
     <t xml:space="preserve">4.29660701751709</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">4.10059404373169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91634249687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946502685547</t>
+    <t xml:space="preserve">3.91634178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946478843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
@@ -2390,160 +2390,160 @@
     <t xml:space="preserve">4.1397967338562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14763736724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01434803009033</t>
+    <t xml:space="preserve">4.14763641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01434850692749</t>
   </si>
   <si>
     <t xml:space="preserve">3.9516236782074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9437837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88889956474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05355024337769</t>
+    <t xml:space="preserve">3.94378328323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8889000415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.053551197052</t>
   </si>
   <si>
     <t xml:space="preserve">4.06923151016235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.030029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89282035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810273170471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242146492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8575382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86537837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617592811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105869293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90850067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75561046600342</t>
+    <t xml:space="preserve">4.03002882003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89281988143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242098808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85753750801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86537790298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105940818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458059310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850138664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75561094284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.74777054786682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80657434463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96730470657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02218914031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93594288825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345133781433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75953102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64584350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66936469078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016247749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56351804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56743860244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59095978736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48903322219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48119282722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44198942184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38710618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31654191017151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33222246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278744697571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238855361938</t>
+    <t xml:space="preserve">3.80657410621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96730518341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02218866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93594312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345181465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75953125953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64584374427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6693651676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016271591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56351780891418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56743812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59096026420593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48903298377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48119258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44198966026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38710641860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31654143333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33222270011902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238831520081</t>
   </si>
   <si>
     <t xml:space="preserve">3.43807005882263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46551132202148</t>
+    <t xml:space="preserve">3.46551156044006</t>
   </si>
   <si>
     <t xml:space="preserve">3.49295330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55175733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55567741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50079417228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51255464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37926578521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43414950370789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630910873413</t>
+    <t xml:space="preserve">3.55175757408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55567765235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50079393386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51255488395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37926554679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43414902687073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630887031555</t>
   </si>
   <si>
     <t xml:space="preserve">3.4615912437439</t>
@@ -2555,40 +2555,40 @@
     <t xml:space="preserve">3.15189051628113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20677423477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17541241645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52823543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215599060059</t>
+    <t xml:space="preserve">3.20677447319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17541217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52823519706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215646743774</t>
   </si>
   <si>
     <t xml:space="preserve">3.53607654571533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10843467712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866700172424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2025203704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0927529335022</t>
+    <t xml:space="preserve">4.10843372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866724014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20252084732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13195657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09275388717651</t>
   </si>
   <si>
     <t xml:space="preserve">4.06139135360718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2887659072876</t>
+    <t xml:space="preserve">4.28876638412476</t>
   </si>
   <si>
     <t xml:space="preserve">4.24956369400024</t>
@@ -2600,31 +2600,31 @@
     <t xml:space="preserve">4.39853382110596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3593316078186</t>
+    <t xml:space="preserve">4.35933065414429</t>
   </si>
   <si>
     <t xml:space="preserve">4.69647312164307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75919818878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976245880127</t>
+    <t xml:space="preserve">4.75919771194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976293563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.72783613204956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74351692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76703882217407</t>
+    <t xml:space="preserve">4.74351739883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76703786849976</t>
   </si>
   <si>
     <t xml:space="preserve">4.77487897872925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73567628860474</t>
+    <t xml:space="preserve">4.73567676544189</t>
   </si>
   <si>
     <t xml:space="preserve">4.68863296508789</t>
@@ -2633,37 +2633,37 @@
     <t xml:space="preserve">4.80624103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01009464263916</t>
+    <t xml:space="preserve">5.010094165802</t>
   </si>
   <si>
     <t xml:space="preserve">4.99441337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94737005233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86112403869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84544324874878</t>
+    <t xml:space="preserve">4.9473705291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86112451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">4.91600847244263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93953037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04929733276367</t>
+    <t xml:space="preserve">4.93952989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04929780960083</t>
   </si>
   <si>
     <t xml:space="preserve">5.58245277404785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68437957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59813404083252</t>
+    <t xml:space="preserve">5.68438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59813356399536</t>
   </si>
   <si>
     <t xml:space="preserve">5.6294960975647</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">5.71574211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69222116470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66869878768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66085863113403</t>
+    <t xml:space="preserve">5.69222021102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66869831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66085815429688</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358274459839</t>
@@ -2693,16 +2693,16 @@
     <t xml:space="preserve">6.17833280563354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14697074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288362503052</t>
+    <t xml:space="preserve">6.14697122573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288410186768</t>
   </si>
   <si>
     <t xml:space="preserve">5.97447919845581</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03720331192017</t>
+    <t xml:space="preserve">6.03720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.15080642700195</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">6.00474500656128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11834812164307</t>
+    <t xml:space="preserve">6.11834859848022</t>
   </si>
   <si>
     <t xml:space="preserve">6.49161624908447</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">6.45915842056274</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42670011520386</t>
+    <t xml:space="preserve">6.4266996383667</t>
   </si>
   <si>
     <t xml:space="preserve">6.26440954208374</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">6.41047096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39424228668213</t>
+    <t xml:space="preserve">6.39424180984497</t>
   </si>
   <si>
     <t xml:space="preserve">6.4429292678833</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">6.96225833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14077854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43290042877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00091648101807</t>
+    <t xml:space="preserve">7.14077758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43290138244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00091743469238</t>
   </si>
   <si>
     <t xml:space="preserve">7.83862590789795</t>
@@ -2753,16 +2753,16 @@
     <t xml:space="preserve">7.87108421325684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78993940353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95222997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90354251861572</t>
+    <t xml:space="preserve">7.78993988037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977262496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95223093032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90354299545288</t>
   </si>
   <si>
     <t xml:space="preserve">8.60139179229736</t>
@@ -2771,16 +2771,16 @@
     <t xml:space="preserve">8.64196300506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56081962585449</t>
+    <t xml:space="preserve">8.56081867218018</t>
   </si>
   <si>
     <t xml:space="preserve">8.43910026550293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19566631317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23623752593994</t>
+    <t xml:space="preserve">8.19566535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23623847961426</t>
   </si>
   <si>
     <t xml:space="preserve">8.01714706420898</t>
@@ -2792,70 +2792,70 @@
     <t xml:space="preserve">7.96845865249634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40044164657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25438022613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48158836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64387893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56273221969604</t>
+    <t xml:space="preserve">7.40044260025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25438165664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4815878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6438775062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5627326965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.69256496429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72502374649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75748205184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62764883041382</t>
+    <t xml:space="preserve">7.72502326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75748157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6276478767395</t>
   </si>
   <si>
     <t xml:space="preserve">7.4653582572937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3030686378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22192239761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81619644165039</t>
+    <t xml:space="preserve">7.30306816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22192287445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81619691848755</t>
   </si>
   <si>
     <t xml:space="preserve">7.15700626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23815250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38421392440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70879411697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61142015457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66010618209839</t>
+    <t xml:space="preserve">7.23815298080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3842134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70879459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61142063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66010713577271</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74125289916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35795497894287</t>
+    <t xml:space="preserve">7.74125194549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
     <t xml:space="preserve">8.1550931930542</t>
@@ -2867,55 +2867,55 @@
     <t xml:space="preserve">8.84482669830322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76368236541748</t>
+    <t xml:space="preserve">8.76368141174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.5202465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39852905273438</t>
+    <t xml:space="preserve">8.39852809906006</t>
   </si>
   <si>
     <t xml:space="preserve">8.47967338562012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3173828125</t>
+    <t xml:space="preserve">8.31738376617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.08206272125244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11452007293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03337383270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04960441589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04768943786621</t>
+    <t xml:space="preserve">8.11452102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03337574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04960536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04769039154053</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284465789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940879821777</t>
+    <t xml:space="preserve">9.16940784454346</t>
   </si>
   <si>
     <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40344905853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23627662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48703670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77958679199219</t>
+    <t xml:space="preserve">9.40345001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23627758026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48703575134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7795877456665</t>
   </si>
   <si>
     <t xml:space="preserve">9.61241436004639</t>
@@ -2927,19 +2927,19 @@
     <t xml:space="preserve">9.52882862091064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69600200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73779392242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420818328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90496730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31986236572266</t>
+    <t xml:space="preserve">9.69600105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90496635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31986331939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">9.15269088745117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86013889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7765531539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35862159729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60937976837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19448280334473</t>
+    <t xml:space="preserve">8.86013984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77655220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35862255096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6093807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19448471069336</t>
   </si>
   <si>
     <t xml:space="preserve">8.98551845550537</t>
@@ -2999,25 +2999,25 @@
     <t xml:space="preserve">8.20816612243652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30846977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32518768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65649700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82366895675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07139348983765</t>
+    <t xml:space="preserve">8.30846881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32518672943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65649843215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82366991043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321443557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154626846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0713939666748</t>
   </si>
   <si>
     <t xml:space="preserve">7.10482835769653</t>
@@ -3026,28 +3026,28 @@
     <t xml:space="preserve">7.68993139266968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45589065551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89053773880005</t>
+    <t xml:space="preserve">7.45589113235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89053869247437</t>
   </si>
   <si>
     <t xml:space="preserve">7.80695295333862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62306213378906</t>
+    <t xml:space="preserve">7.62306308746338</t>
   </si>
   <si>
     <t xml:space="preserve">7.99084281921387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09114742279053</t>
+    <t xml:space="preserve">8.09114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.04099369049072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27503395080566</t>
+    <t xml:space="preserve">8.27503490447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.40041542053223</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">8.48400020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30011177062988</t>
+    <t xml:space="preserve">8.30011081695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.35026264190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24995994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87382221221924</t>
+    <t xml:space="preserve">8.24996089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87382078170776</t>
   </si>
   <si>
     <t xml:space="preserve">7.69829082489014</t>
@@ -3077,52 +3077,52 @@
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77351903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91561603546143</t>
+    <t xml:space="preserve">7.81531095504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77351856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91561508178711</t>
   </si>
   <si>
     <t xml:space="preserve">7.7818775177002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60634613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89889669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79859352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79023456573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83202838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978099822998</t>
+    <t xml:space="preserve">7.60634565353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89889812469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79859447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79023551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83202791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63978052139282</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6485013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24154281616211</t>
+    <t xml:space="preserve">7.64850234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24154472351074</t>
   </si>
   <si>
     <t xml:space="preserve">8.21538066864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28514957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32003498077393</t>
+    <t xml:space="preserve">8.2851505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32003402709961</t>
   </si>
   <si>
     <t xml:space="preserve">8.38108253479004</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">8.69504642486572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67760372161865</t>
+    <t xml:space="preserve">8.67760467529297</t>
   </si>
   <si>
     <t xml:space="preserve">8.54678630828857</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">8.7386531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59039211273193</t>
+    <t xml:space="preserve">8.59039306640625</t>
   </si>
   <si>
     <t xml:space="preserve">8.64271926879883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63399696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47701740264893</t>
+    <t xml:space="preserve">8.63399791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47701644897461</t>
   </si>
   <si>
     <t xml:space="preserve">8.45957374572754</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">8.17177391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12816715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93630170822144</t>
+    <t xml:space="preserve">8.1281681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93630123138428</t>
   </si>
   <si>
     <t xml:space="preserve">7.61361598968506</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">7.71827173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77931976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95374298095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14561080932617</t>
+    <t xml:space="preserve">7.77931928634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95374345779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14560985565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.0496768951416</t>
@@ -3194,25 +3194,25 @@
     <t xml:space="preserve">7.99734973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78804111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65722274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76187658309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63978052139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6921067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70082855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5961742401123</t>
+    <t xml:space="preserve">7.78804063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65722179412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76187705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63977956771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69210767745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70082807540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59617376327515</t>
   </si>
   <si>
     <t xml:space="preserve">7.46535634994507</t>
@@ -3221,28 +3221,28 @@
     <t xml:space="preserve">7.54384613037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73571348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50024080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63105869293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55256795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.447913646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53512620925903</t>
+    <t xml:space="preserve">7.73571395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50024127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63105916976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55256748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44791316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53512668609619</t>
   </si>
   <si>
     <t xml:space="preserve">7.51768350601196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50896167755127</t>
+    <t xml:space="preserve">7.50896120071411</t>
   </si>
   <si>
     <t xml:space="preserve">7.57001066207886</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">7.80548334121704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74443531036377</t>
+    <t xml:space="preserve">7.74443435668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">8.607834815979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41596698760986</t>
+    <t xml:space="preserve">8.41596794128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.3461971282959</t>
@@ -3284,55 +3284,55 @@
     <t xml:space="preserve">8.37236213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89269542694092</t>
+    <t xml:space="preserve">7.89269495010376</t>
   </si>
   <si>
     <t xml:space="preserve">7.83164644241333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66594314575195</t>
+    <t xml:space="preserve">7.66594457626343</t>
   </si>
   <si>
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97118711471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6833872795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33453798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1688346862793</t>
+    <t xml:space="preserve">7.97118663787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33453750610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16883516311646</t>
   </si>
   <si>
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418037414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28221082687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13395023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1252293586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78510189056396</t>
+    <t xml:space="preserve">7.06418085098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28221130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13395071029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12522888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78510141372681</t>
   </si>
   <si>
     <t xml:space="preserve">6.61939907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41008901596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63684129714966</t>
+    <t xml:space="preserve">6.41008949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6368408203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.87231397628784</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">7.43047142028809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49151992797852</t>
+    <t xml:space="preserve">7.49151945114136</t>
   </si>
   <si>
     <t xml:space="preserve">7.27348947525024</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">7.39558601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38686513900757</t>
+    <t xml:space="preserve">7.38686561584473</t>
   </si>
   <si>
     <t xml:space="preserve">7.35198068618774</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663547515869</t>
+    <t xml:space="preserve">7.45663499832153</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
@@ -3392,25 +3392,25 @@
     <t xml:space="preserve">8.03223514556885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1020040512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15433311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05839729309082</t>
+    <t xml:space="preserve">8.10200500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15433216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05839824676514</t>
   </si>
   <si>
     <t xml:space="preserve">8.09328269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00607204437256</t>
+    <t xml:space="preserve">8.00607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072635650635</t>
+    <t xml:space="preserve">8.11072540283203</t>
   </si>
   <si>
     <t xml:space="preserve">8.07584095001221</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">7.97990655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98862838745117</t>
+    <t xml:space="preserve">7.98862886428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.90141725540161</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">7.84908962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91885852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82292652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11944770812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25898742675781</t>
+    <t xml:space="preserve">7.91885900497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82292556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11944675445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25898551940918</t>
   </si>
   <si>
     <t xml:space="preserve">8.27642822265625</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">8.337477684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52934265136719</t>
+    <t xml:space="preserve">8.5293436050415</t>
   </si>
   <si>
     <t xml:space="preserve">8.94796180725098</t>
@@ -3458,10 +3458,10 @@
     <t xml:space="preserve">8.87819194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65144062042236</t>
+    <t xml:space="preserve">8.89563369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65144157409668</t>
   </si>
   <si>
     <t xml:space="preserve">8.6601619720459</t>
@@ -3479,22 +3479,22 @@
     <t xml:space="preserve">8.86074924468994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93051910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62527751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56422805786133</t>
+    <t xml:space="preserve">8.93052005767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62527656555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56422901153564</t>
   </si>
   <si>
     <t xml:space="preserve">8.46829509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6863260269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15727138519287</t>
+    <t xml:space="preserve">8.68632507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15727043151855</t>
   </si>
   <si>
     <t xml:space="preserve">8.9828462600708</t>
@@ -3512,31 +3512,31 @@
     <t xml:space="preserve">8.96540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00028800964355</t>
+    <t xml:space="preserve">9.00028896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84330749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80842304229736</t>
+    <t xml:space="preserve">8.8433084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80842208862305</t>
   </si>
   <si>
     <t xml:space="preserve">8.66888236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91124629974365</t>
+    <t xml:space="preserve">8.91124534606934</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85674285888672</t>
+    <t xml:space="preserve">8.82040786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8567419052124</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422660827637</t>
+    <t xml:space="preserve">8.58422756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498722076416</t>
+    <t xml:space="preserve">8.77498817443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3584,19 +3584,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49339008331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3843822479248</t>
+    <t xml:space="preserve">8.49338912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38438320159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453884124756</t>
+    <t xml:space="preserve">8.18453788757324</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896446228027</t>
+    <t xml:space="preserve">8.33896350860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09369945526123</t>
+    <t xml:space="preserve">8.09370040893555</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04827976226807</t>
+    <t xml:space="preserve">8.04828071594238</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644916534424</t>
+    <t xml:space="preserve">8.06644821166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3662,40 +3662,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919792175293</t>
+    <t xml:space="preserve">8.03919696807861</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9483585357666</t>
+    <t xml:space="preserve">8.00286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94835901260376</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744276046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90293884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385557174683</t>
+    <t xml:space="preserve">7.95744228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9029393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385461807251</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85751962661743</t>
+    <t xml:space="preserve">7.85752010345459</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210088729858</t>
+    <t xml:space="preserve">7.81210136413574</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126293182373</t>
+    <t xml:space="preserve">7.72126245498657</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568855285645</t>
+    <t xml:space="preserve">7.87568807601929</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950824737549</t>
+    <t xml:space="preserve">7.63950777053833</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4941668510437</t>
+    <t xml:space="preserve">7.49416637420654</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4124116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44874715805054</t>
+    <t xml:space="preserve">7.41241216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4487476348877</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112392425537</t>
+    <t xml:space="preserve">6.73112440109253</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72204065322876</t>
+    <t xml:space="preserve">6.7220401763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486722946167</t>
+    <t xml:space="preserve">6.59486675262451</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272296905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767621994019</t>
+    <t xml:space="preserve">7.01272344589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699247360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31248998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790967941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767669677734</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393291473389</t>
+    <t xml:space="preserve">7.79393339157104</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3845,31 +3845,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9665265083313</t>
+    <t xml:space="preserve">7.76668214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96652698516846</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47599840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607669830322</t>
+    <t xml:space="preserve">7.63042449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.475998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607717514038</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523874282837</t>
+    <t xml:space="preserve">7.28523921966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264514923096</t>
+    <t xml:space="preserve">7.11264562606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225700378418</t>
+    <t xml:space="preserve">7.61225652694702</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890327453613</t>
+    <t xml:space="preserve">7.24890279769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -21010,7 +21010,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21036,7 +21036,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G630" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21062,7 +21062,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G631" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21088,7 +21088,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G632" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21114,7 +21114,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21140,7 +21140,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G634" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21166,7 +21166,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G635" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21218,7 +21218,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G637" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21244,7 +21244,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G638" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21270,7 +21270,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G639" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21296,7 +21296,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G640" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21322,7 +21322,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G641" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21348,7 +21348,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G642" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21374,7 +21374,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G643" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21400,7 +21400,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G644" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21426,7 +21426,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G645" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21452,7 +21452,7 @@
         <v>7.5</v>
       </c>
       <c r="G646" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21478,7 +21478,7 @@
         <v>7.5</v>
       </c>
       <c r="G647" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21504,7 +21504,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G648" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21530,7 +21530,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G649" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21556,7 +21556,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G650" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21582,7 +21582,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G651" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -21608,7 +21608,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G652" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -21634,7 +21634,7 @@
         <v>7.25</v>
       </c>
       <c r="G653" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -21660,7 +21660,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -21686,7 +21686,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G655" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -21712,7 +21712,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -21738,7 +21738,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G657" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -21764,7 +21764,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G658" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -21790,7 +21790,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G659" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -21842,7 +21842,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G661" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -21868,7 +21868,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G662" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21894,7 +21894,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G663" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21920,7 +21920,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G664" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21946,7 +21946,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21972,7 +21972,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G666" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21998,7 +21998,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G667" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22024,7 +22024,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G668" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22050,7 +22050,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G669" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22076,7 +22076,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22102,7 +22102,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G671" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22128,7 +22128,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G672" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22154,7 +22154,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G673" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22180,7 +22180,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G674" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22206,7 +22206,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G675" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22232,7 +22232,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22258,7 +22258,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G677" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22284,7 +22284,7 @@
         <v>6.75</v>
       </c>
       <c r="G678" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22310,7 +22310,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G679" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22336,7 +22336,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G680" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22362,7 +22362,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G682" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22414,7 +22414,7 @@
         <v>6.5</v>
       </c>
       <c r="G683" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22440,7 +22440,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G684" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22466,7 +22466,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G685" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22492,7 +22492,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G686" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22518,7 +22518,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22544,7 +22544,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G688" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22570,7 +22570,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G689" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -22596,7 +22596,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G690" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -22622,7 +22622,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G691" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -22648,7 +22648,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G692" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -22674,7 +22674,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -22700,7 +22700,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G694" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -22726,7 +22726,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G695" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -22752,7 +22752,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -22778,7 +22778,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G697" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -22804,7 +22804,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G698" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -22830,7 +22830,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G699" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -22856,7 +22856,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G700" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -22882,7 +22882,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G701" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22908,7 +22908,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G702" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22934,7 +22934,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G703" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22960,7 +22960,7 @@
         <v>8</v>
       </c>
       <c r="G704" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23012,7 +23012,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G706" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23038,7 +23038,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G707" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23064,7 +23064,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G708" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23090,7 +23090,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G709" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23116,7 +23116,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G710" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23142,7 +23142,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G711" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23168,7 +23168,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23194,7 +23194,7 @@
         <v>6.75</v>
       </c>
       <c r="G713" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23220,7 +23220,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G714" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23246,7 +23246,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G715" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23272,7 +23272,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G716" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23298,7 +23298,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G717" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23324,7 +23324,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G718" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23350,7 +23350,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G719" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23376,7 +23376,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G720" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23402,7 +23402,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G721" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23428,7 +23428,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G722" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23454,7 +23454,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G723" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23480,7 +23480,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G724" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23506,7 +23506,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G725" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23532,7 +23532,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G726" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23558,7 +23558,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G727" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23584,7 +23584,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -23610,7 +23610,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G729" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -23636,7 +23636,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G730" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -23662,7 +23662,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -23688,7 +23688,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G732" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -23714,7 +23714,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G733" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -23740,7 +23740,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G734" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -23766,7 +23766,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G735" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -23792,7 +23792,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G736" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -23818,7 +23818,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G737" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -23844,7 +23844,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G738" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -23870,7 +23870,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G739" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23896,7 +23896,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G740" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23922,7 +23922,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G741" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23948,7 +23948,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23974,7 +23974,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G743" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24000,7 +24000,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24026,7 +24026,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G745" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24052,7 +24052,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G746" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24078,7 +24078,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24104,7 +24104,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G748" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24130,7 +24130,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G749" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24156,7 +24156,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G750" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24182,7 +24182,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G751" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G752" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24234,7 +24234,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G753" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24260,7 +24260,7 @@
         <v>7</v>
       </c>
       <c r="G754" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24286,7 +24286,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G755" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24312,7 +24312,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G756" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24338,7 +24338,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G757" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24364,7 +24364,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G758" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24390,7 +24390,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G759" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24416,7 +24416,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G760" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24442,7 +24442,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G761" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24468,7 +24468,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24494,7 +24494,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G763" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24520,7 +24520,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24546,7 +24546,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G765" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24572,7 +24572,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -24598,7 +24598,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G767" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -24624,7 +24624,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G768" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -24650,7 +24650,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -24676,7 +24676,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G770" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -24702,7 +24702,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G771" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -24728,7 +24728,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -24754,7 +24754,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -24780,7 +24780,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G774" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -24806,7 +24806,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G775" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -24832,7 +24832,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G776" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -24858,7 +24858,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G777" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -24884,7 +24884,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G778" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24910,7 +24910,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G779" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G780" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25040,7 +25040,7 @@
         <v>8</v>
       </c>
       <c r="G784" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25092,7 +25092,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G786" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25118,7 +25118,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G787" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25144,7 +25144,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25170,7 +25170,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G789" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G791" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25248,7 +25248,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G792" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25274,7 +25274,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G793" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25326,7 +25326,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G795" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25352,7 +25352,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G796" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25378,7 +25378,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G797" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25430,7 +25430,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G799" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25508,7 +25508,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G802" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25534,7 +25534,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G803" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25586,7 +25586,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G805" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -25612,7 +25612,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G806" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -25638,7 +25638,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G807" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G808" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -25716,7 +25716,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -25742,7 +25742,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G811" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -25768,7 +25768,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -25794,7 +25794,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G813" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -25820,7 +25820,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G814" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -25872,7 +25872,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G816" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -25898,7 +25898,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G817" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25924,7 +25924,7 @@
         <v>8</v>
       </c>
       <c r="G818" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25950,7 +25950,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G819" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26054,7 +26054,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G823" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26080,7 +26080,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G824" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26106,7 +26106,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G825" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26132,7 +26132,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G826" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26210,7 +26210,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26262,7 +26262,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G831" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26288,7 +26288,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26314,7 +26314,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G833" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26340,7 +26340,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G834" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26366,7 +26366,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G835" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26418,7 +26418,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G837" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26444,7 +26444,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G838" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26470,7 +26470,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G839" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26496,7 +26496,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G840" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26522,7 +26522,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26548,7 +26548,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G842" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26574,7 +26574,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G843" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -26600,7 +26600,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G844" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -26626,7 +26626,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G845" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -26652,7 +26652,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G846" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -26678,7 +26678,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G847" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -26704,7 +26704,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G848" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -26730,7 +26730,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G849" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G850" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -26782,7 +26782,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G851" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -26808,7 +26808,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G852" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -26834,7 +26834,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G853" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -26860,7 +26860,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G854" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -26886,7 +26886,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G855" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26912,7 +26912,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G856" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26938,7 +26938,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G857" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26964,7 +26964,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G858" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26990,7 +26990,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G859" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -27016,7 +27016,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G860" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -27042,7 +27042,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G861" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -27068,7 +27068,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G862" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -27094,7 +27094,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G863" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -27120,7 +27120,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G864" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -27146,7 +27146,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G865" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -27172,7 +27172,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G866" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -27198,7 +27198,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G867" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -27224,7 +27224,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -27250,7 +27250,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G869" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -27276,7 +27276,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G870" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -27302,7 +27302,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G871" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27328,7 +27328,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G872" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27354,7 +27354,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G873" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -27380,7 +27380,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G874" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -27406,7 +27406,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G875" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -27432,7 +27432,7 @@
         <v>6.75</v>
       </c>
       <c r="G876" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -27458,7 +27458,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G877" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -27484,7 +27484,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G878" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -27510,7 +27510,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G879" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -27536,7 +27536,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G880" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -27562,7 +27562,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G881" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -27588,7 +27588,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G882" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -27614,7 +27614,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G883" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -27640,7 +27640,7 @@
         <v>6.5</v>
       </c>
       <c r="G884" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -27666,7 +27666,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G885" t="s">
-        <v>657</v>
+        <v>537</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -27718,7 +27718,7 @@
         <v>6.5</v>
       </c>
       <c r="G887" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -27770,7 +27770,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G889" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28056,7 +28056,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28134,7 +28134,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G903" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28160,7 +28160,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G904" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28212,7 +28212,7 @@
         <v>6.75</v>
       </c>
       <c r="G906" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28290,7 +28290,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G909" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -28316,7 +28316,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G910" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28368,7 +28368,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G912" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -28394,7 +28394,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G913" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -28420,7 +28420,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G914" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29148,7 +29148,7 @@
         <v>6.75</v>
       </c>
       <c r="G942" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29200,7 +29200,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G944" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29382,7 +29382,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G951" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -29408,7 +29408,7 @@
         <v>6.5</v>
       </c>
       <c r="G952" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -29616,7 +29616,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G960" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -29694,7 +29694,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G963" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -29746,7 +29746,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G965" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30786,7 +30786,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1005" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -30864,7 +30864,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1008" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -30942,7 +30942,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1011" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -30968,7 +30968,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31098,7 +31098,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1017" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31150,7 +31150,7 @@
         <v>6.75</v>
       </c>
       <c r="G1019" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31176,7 +31176,7 @@
         <v>6.75</v>
       </c>
       <c r="G1020" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31202,7 +31202,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1021" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31254,7 +31254,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1023" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31280,7 +31280,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1024" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31306,7 +31306,7 @@
         <v>6.75</v>
       </c>
       <c r="G1025" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31332,7 +31332,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1026" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31358,7 +31358,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1027" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -31384,7 +31384,7 @@
         <v>6.75</v>
       </c>
       <c r="G1028" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -31462,7 +31462,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1031" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -31488,7 +31488,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1032" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -31566,7 +31566,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1035" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -31878,7 +31878,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -31982,7 +31982,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1051" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -38430,7 +38430,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1299" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -38456,7 +38456,7 @@
         <v>6.5</v>
       </c>
       <c r="G1300" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -38482,7 +38482,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1301" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -38508,7 +38508,7 @@
         <v>6.5</v>
       </c>
       <c r="G1302" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -38976,7 +38976,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1320" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -39002,7 +39002,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1321" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -39626,7 +39626,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1345" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -72070,9 +72070,11 @@
       <c r="E2593" t="n">
         <v>10.3000001907349</v>
       </c>
-      <c r="F2593"/>
+      <c r="F2593" t="n">
+        <v>10.1000003814697</v>
+      </c>
       <c r="G2593" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="H2593" t="s">
         <v>9</v>
@@ -72080,27 +72082,51 @@
     </row>
     <row r="2594">
       <c r="A2594" s="1" t="n">
-        <v>46097.6911458333</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B2594" t="n">
-        <v>20336</v>
+        <v>4633</v>
       </c>
       <c r="C2594" t="n">
         <v>10.3000001907349</v>
       </c>
       <c r="D2594" t="n">
-        <v>9.89999961853027</v>
+        <v>10.1000003814697</v>
       </c>
       <c r="E2594" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="F2594"/>
+      <c r="G2594" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H2594" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46098.6911574074</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>4633</v>
+      </c>
+      <c r="C2595" t="n">
         <v>10.3000001907349</v>
       </c>
-      <c r="F2594" t="n">
+      <c r="D2595" t="n">
         <v>10.1000003814697</v>
       </c>
-      <c r="G2594" t="s">
-        <v>1435</v>
-      </c>
-      <c r="H2594" t="s">
+      <c r="E2595" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>10.1499996185303</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H2595" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="1439">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,25 +44,25 @@
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355521678925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546637058258</t>
+    <t xml:space="preserve">1.21355497837067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546625137329</t>
   </si>
   <si>
     <t xml:space="preserve">1.20654845237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23177254199982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24998962879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26330232620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27311170101166</t>
+    <t xml:space="preserve">1.23177242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2499897480011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26330256462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27311193943024</t>
   </si>
   <si>
     <t xml:space="preserve">1.26120042800903</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">1.24718713760376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20794975757599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19323575496674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17501842975616</t>
+    <t xml:space="preserve">1.2079496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19323587417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17501854896545</t>
   </si>
   <si>
     <t xml:space="preserve">1.19814050197601</t>
@@ -86,19 +86,19 @@
     <t xml:space="preserve">1.24578583240509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23457515239716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21495640277863</t>
+    <t xml:space="preserve">1.23457503318787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21495628356934</t>
   </si>
   <si>
     <t xml:space="preserve">1.18272578716278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17992317676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17641985416412</t>
+    <t xml:space="preserve">1.17992305755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17641961574554</t>
   </si>
   <si>
     <t xml:space="preserve">1.12457048892975</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">1.10284984111786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08603382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01596713066101</t>
+    <t xml:space="preserve">1.08603370189667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01596701145172</t>
   </si>
   <si>
     <t xml:space="preserve">1.02507567405701</t>
@@ -122,58 +122,58 @@
     <t xml:space="preserve">1.02017104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00195372104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297377586365</t>
+    <t xml:space="preserve">1.00195360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297365665436</t>
   </si>
   <si>
     <t xml:space="preserve">1.04329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09654378890991</t>
+    <t xml:space="preserve">1.09654366970062</t>
   </si>
   <si>
     <t xml:space="preserve">1.11335980892181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1105569601059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09304022789001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12106704711914</t>
+    <t xml:space="preserve">1.11055707931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0930403470993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12106716632843</t>
   </si>
   <si>
     <t xml:space="preserve">1.13017570972443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1561005115509</t>
+    <t xml:space="preserve">1.15610039234161</t>
   </si>
   <si>
     <t xml:space="preserve">1.10004699230194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13157689571381</t>
+    <t xml:space="preserve">1.13157713413239</t>
   </si>
   <si>
     <t xml:space="preserve">1.10705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13227772712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11826431751251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14909374713898</t>
+    <t xml:space="preserve">1.13227796554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1182644367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14909362792969</t>
   </si>
   <si>
     <t xml:space="preserve">1.17852163314819</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17011368274689</t>
+    <t xml:space="preserve">1.17011380195618</t>
   </si>
   <si>
     <t xml:space="preserve">1.18412709236145</t>
@@ -182,70 +182,70 @@
     <t xml:space="preserve">1.17081439495087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16310703754425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22616708278656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508512020111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24088096618652</t>
+    <t xml:space="preserve">1.16310715675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22616696357727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508500099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2408812046051</t>
   </si>
   <si>
     <t xml:space="preserve">1.20514702796936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19113373756409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22686767578125</t>
+    <t xml:space="preserve">1.19113385677338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22686779499054</t>
   </si>
   <si>
     <t xml:space="preserve">1.22196304798126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24438452720642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17221570014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19183421134949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19743978977203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20374572277069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20304524898529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23807835578918</t>
+    <t xml:space="preserve">1.24438440799713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17221593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19183433055878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19743955135345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20374584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.203045129776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2380782365799</t>
   </si>
   <si>
     <t xml:space="preserve">1.2331737279892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19954180717468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22476577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845984458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916031837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896981239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21215379238129</t>
+    <t xml:space="preserve">1.1995415687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845960617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916043758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2289696931839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.212153673172</t>
   </si>
   <si>
     <t xml:space="preserve">1.22266376018524</t>
@@ -254,13 +254,13 @@
     <t xml:space="preserve">1.29202973842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29623365402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27521407604218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28712499141693</t>
+    <t xml:space="preserve">1.29623377323151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27521395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28712511062622</t>
   </si>
   <si>
     <t xml:space="preserve">1.28151977062225</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">1.20865046977997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15469896793365</t>
+    <t xml:space="preserve">1.15469908714294</t>
   </si>
   <si>
     <t xml:space="preserve">1.14138638973236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11896502971649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12036621570587</t>
+    <t xml:space="preserve">1.11896514892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12036645412445</t>
   </si>
   <si>
     <t xml:space="preserve">1.13648164272308</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">1.14208710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.07202041149139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08463227748871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06501364707947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07061898708344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08253037929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902693748474</t>
+    <t xml:space="preserve">1.07202053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08463251590729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.06501376628876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07061910629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08253049850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902705669403</t>
   </si>
   <si>
     <t xml:space="preserve">1.05800712108612</t>
@@ -320,31 +320,31 @@
     <t xml:space="preserve">1.1014484167099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10355031490326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09514248371124</t>
+    <t xml:space="preserve">1.10355043411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09514236450195</t>
   </si>
   <si>
     <t xml:space="preserve">1.11966574192047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.09934639930725</t>
+    <t xml:space="preserve">1.09934651851654</t>
   </si>
   <si>
     <t xml:space="preserve">1.11265909671783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15680110454559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528052806854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681533336639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48821651935577</t>
+    <t xml:space="preserve">1.1568009853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528040885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4868152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48821663856506</t>
   </si>
   <si>
     <t xml:space="preserve">1.45178186893463</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">1.4153470993042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45738708972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40133392810822</t>
+    <t xml:space="preserve">1.4573872089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40133380889893</t>
   </si>
   <si>
     <t xml:space="preserve">1.4699991941452</t>
@@ -365,76 +365,76 @@
     <t xml:space="preserve">1.43776845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42375528812408</t>
+    <t xml:space="preserve">1.42375504970551</t>
   </si>
   <si>
     <t xml:space="preserve">1.4363671541214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42936062812805</t>
+    <t xml:space="preserve">1.42936038970947</t>
   </si>
   <si>
     <t xml:space="preserve">1.41674852371216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42235362529755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814970970154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41114318370819</t>
+    <t xml:space="preserve">1.42235386371613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814959049225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41114294528961</t>
   </si>
   <si>
     <t xml:space="preserve">1.42795932292938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48120987415314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6942126750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66338324546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80071377754211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84555697441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79230606555939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79090476036072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77268707752228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064708709717</t>
+    <t xml:space="preserve">1.48120999336243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69421243667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66338312625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8007138967514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84555673599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7923059463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79090452194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77268743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064732551575</t>
   </si>
   <si>
     <t xml:space="preserve">1.71663403511047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670060634613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8427540063858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593786716461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313513755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995115756989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83855009078979</t>
+    <t xml:space="preserve">1.78670072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593810558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995139598846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83854973316193</t>
   </si>
   <si>
     <t xml:space="preserve">1.84415531158447</t>
@@ -443,133 +443,133 @@
     <t xml:space="preserve">1.83014214038849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81472730636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82874035835266</t>
+    <t xml:space="preserve">1.81472718715668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82874047756195</t>
   </si>
   <si>
     <t xml:space="preserve">1.81192469596863</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83294451236725</t>
+    <t xml:space="preserve">1.83294463157654</t>
   </si>
   <si>
     <t xml:space="preserve">1.84835922718048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86937940120697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99549901485443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07257270812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0291314125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08798742294312</t>
+    <t xml:space="preserve">1.8693790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99549925327301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07257294654846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02913093566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08798718452454</t>
   </si>
   <si>
     <t xml:space="preserve">2.04034209251404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99830210208893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03053307533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01932191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9997034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231527328491</t>
+    <t xml:space="preserve">1.99830198287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03053283691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01932168006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970304965973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231551170349</t>
   </si>
   <si>
     <t xml:space="preserve">2.09359264373779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17066597938538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15945553779602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98989391326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88339257240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167670726776</t>
+    <t xml:space="preserve">2.17066645622253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1594557762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98989379405975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88339245319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167646884918</t>
   </si>
   <si>
     <t xml:space="preserve">1.95345962047577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01651930809021</t>
+    <t xml:space="preserve">2.01651978492737</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250625610352</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98428869247437</t>
+    <t xml:space="preserve">1.98428893089294</t>
   </si>
   <si>
     <t xml:space="preserve">1.9786833524704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9394463300705</t>
+    <t xml:space="preserve">1.93944585323334</t>
   </si>
   <si>
     <t xml:space="preserve">1.91982734203339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377394199371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86797785758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918877601624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85676729679108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78950321674347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80631935596466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301096439362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89880752563477</t>
+    <t xml:space="preserve">1.863774061203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8679780960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918865680695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85676753520966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78950333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80631923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89880728721619</t>
   </si>
   <si>
     <t xml:space="preserve">1.91001796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99690055847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98849248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98569011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224846363068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95766294002533</t>
+    <t xml:space="preserve">1.99690079689026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98849284648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98568999767303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224882125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766317844391</t>
   </si>
   <si>
     <t xml:space="preserve">1.96186721324921</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">1.96326875686646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97027540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0039074420929</t>
+    <t xml:space="preserve">1.97027516365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00390720367432</t>
   </si>
   <si>
     <t xml:space="preserve">2.07397413253784</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">2.18888354301453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1650607585907</t>
+    <t xml:space="preserve">2.16506099700928</t>
   </si>
   <si>
     <t xml:space="preserve">2.13282990455627</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">2.06416487693787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09639596939087</t>
+    <t xml:space="preserve">2.09639549255371</t>
   </si>
   <si>
     <t xml:space="preserve">2.11601424217224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09499430656433</t>
+    <t xml:space="preserve">2.09499382972717</t>
   </si>
   <si>
     <t xml:space="preserve">2.11321139335632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14404082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13002729415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14824461936951</t>
+    <t xml:space="preserve">2.14404106140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13002753257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14824485778809</t>
   </si>
   <si>
     <t xml:space="preserve">2.13423156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14123797416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1524486541748</t>
+    <t xml:space="preserve">2.14123821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15244889259338</t>
   </si>
   <si>
     <t xml:space="preserve">2.13703393936157</t>
@@ -638,34 +638,34 @@
     <t xml:space="preserve">2.11180996894836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09779691696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11881637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10200071334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11741542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24213409423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48876905441284</t>
+    <t xml:space="preserve">2.09779644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.118816614151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10200047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1174156665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24213433265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48876881599426</t>
   </si>
   <si>
     <t xml:space="preserve">2.4873673915863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49297308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316359519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46494626998901</t>
+    <t xml:space="preserve">2.49297285079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316335678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46494603157043</t>
   </si>
   <si>
     <t xml:space="preserve">2.40328741073608</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">2.43972229957581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47615671157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45513677597046</t>
+    <t xml:space="preserve">2.47615647315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45513653755188</t>
   </si>
   <si>
     <t xml:space="preserve">2.49437427520752</t>
@@ -698,34 +698,34 @@
     <t xml:space="preserve">2.47335410118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65552735328674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71858763694763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70457410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751057624817</t>
+    <t xml:space="preserve">2.65552759170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71858739852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70457434654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751009941101</t>
   </si>
   <si>
     <t xml:space="preserve">2.78865432739258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11096143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2398841381073</t>
+    <t xml:space="preserve">3.11096096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23988389968872</t>
   </si>
   <si>
     <t xml:space="preserve">3.38422107696533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46129417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7100305557251</t>
+    <t xml:space="preserve">3.46129465103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003103256226</t>
   </si>
   <si>
     <t xml:space="preserve">3.58040809631348</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">3.69251441955566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66098475456238</t>
+    <t xml:space="preserve">3.6609845161438</t>
   </si>
   <si>
     <t xml:space="preserve">3.69601798057556</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">3.7836012840271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95176148414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19349241256714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16896772384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11291456222534</t>
+    <t xml:space="preserve">3.95176100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386804580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19349193572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16896820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1129150390625</t>
   </si>
   <si>
     <t xml:space="preserve">4.03233814239502</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">4.30910158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30559825897217</t>
+    <t xml:space="preserve">4.30559778213501</t>
   </si>
   <si>
     <t xml:space="preserve">4.55433511734009</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">4.6979718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50023460388184</t>
+    <t xml:space="preserve">5.50023508071899</t>
   </si>
   <si>
     <t xml:space="preserve">4.79256200790405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1008563041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01677465438843</t>
+    <t xml:space="preserve">5.10085582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01677560806274</t>
   </si>
   <si>
     <t xml:space="preserve">5.44768524169922</t>
@@ -791,85 +791,85 @@
     <t xml:space="preserve">5.4441819190979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77349519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238851547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369230270386</t>
+    <t xml:space="preserve">5.7734956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39708948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143503189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369373321533</t>
   </si>
   <si>
     <t xml:space="preserve">6.97858238220215</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78433275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35626554489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5325288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35266780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07208633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32389068603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900156021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40302896499634</t>
+    <t xml:space="preserve">6.78433322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3562650680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53252792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35266828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0720853805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.323890209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40302848815918</t>
   </si>
   <si>
     <t xml:space="preserve">6.15841913223267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19798851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37425184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47137641906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32748794555664</t>
+    <t xml:space="preserve">6.19798803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37425088882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47137498855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3274884223938</t>
   </si>
   <si>
     <t xml:space="preserve">6.15122509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11165571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93899011611938</t>
+    <t xml:space="preserve">6.11165475845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">5.96057271957397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85265636444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90661478042603</t>
+    <t xml:space="preserve">5.85265684127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90661430358887</t>
   </si>
   <si>
     <t xml:space="preserve">5.89582300186157</t>
@@ -881,25 +881,25 @@
     <t xml:space="preserve">5.69437980651855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70157337188721</t>
+    <t xml:space="preserve">5.70157432556152</t>
   </si>
   <si>
     <t xml:space="preserve">5.36703395843506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87421607971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17997884750366</t>
+    <t xml:space="preserve">4.87421655654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1799783706665</t>
   </si>
   <si>
     <t xml:space="preserve">4.97853517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96414613723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8454384803772</t>
+    <t xml:space="preserve">4.96414661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84543895721436</t>
   </si>
   <si>
     <t xml:space="preserve">4.8778133392334</t>
@@ -908,25 +908,25 @@
     <t xml:space="preserve">4.9101881980896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70155048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92457675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.690758228302</t>
+    <t xml:space="preserve">4.70155000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92457628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76989698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69075870513916</t>
   </si>
   <si>
     <t xml:space="preserve">4.6583833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68716049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82385540008545</t>
+    <t xml:space="preserve">4.68716144561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82385587692261</t>
   </si>
   <si>
     <t xml:space="preserve">4.5504674911499</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">4.51089811325073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49291229248047</t>
+    <t xml:space="preserve">4.49291181564331</t>
   </si>
   <si>
     <t xml:space="preserve">4.43895387649536</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">4.38139867782593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38499546051025</t>
+    <t xml:space="preserve">4.38499593734741</t>
   </si>
   <si>
     <t xml:space="preserve">4.46413469314575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03609085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85623025894165</t>
+    <t xml:space="preserve">5.03608989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85622978210449</t>
   </si>
   <si>
     <t xml:space="preserve">4.80946588516235</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">4.68356418609619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67636919021606</t>
+    <t xml:space="preserve">4.67636966705322</t>
   </si>
   <si>
     <t xml:space="preserve">4.60442590713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59003686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62960577011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66198110580444</t>
+    <t xml:space="preserve">4.59003639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62960624694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66198062896729</t>
   </si>
   <si>
     <t xml:space="preserve">4.6727728843689</t>
@@ -989,49 +989,49 @@
     <t xml:space="preserve">4.75910568237305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95335483551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104991912842</t>
+    <t xml:space="preserve">4.95335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104944229126</t>
   </si>
   <si>
     <t xml:space="preserve">5.06486797332764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14400672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11522912979126</t>
+    <t xml:space="preserve">5.14400625228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1152286529541</t>
   </si>
   <si>
     <t xml:space="preserve">5.1943678855896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10803413391113</t>
+    <t xml:space="preserve">5.10803461074829</t>
   </si>
   <si>
     <t xml:space="preserve">4.93536853790283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7555079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99652147293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90659141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82025766372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89220237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05407667160034</t>
+    <t xml:space="preserve">4.75550889968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99652099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90659093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92098045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82025718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89220285415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05407619476318</t>
   </si>
   <si>
     <t xml:space="preserve">5.07925701141357</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">4.95695114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839529037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23393774032593</t>
+    <t xml:space="preserve">4.94615983963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23393726348877</t>
   </si>
   <si>
     <t xml:space="preserve">5.60804653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8994197845459</t>
+    <t xml:space="preserve">5.89942026138306</t>
   </si>
   <si>
     <t xml:space="preserve">5.77711486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03611516952515</t>
+    <t xml:space="preserve">6.03611469268799</t>
   </si>
   <si>
     <t xml:space="preserve">5.94978141784668</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">6.18000268936157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20878028869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52533388137817</t>
+    <t xml:space="preserve">6.20877981185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52533435821533</t>
   </si>
   <si>
     <t xml:space="preserve">7.03613758087158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89584684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11527729034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13686084747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69802284240723</t>
+    <t xml:space="preserve">6.89584732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11527633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13685894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802474975586</t>
   </si>
   <si>
     <t xml:space="preserve">8.12968921661377</t>
@@ -1097,40 +1097,40 @@
     <t xml:space="preserve">8.43904781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95704555511475</t>
+    <t xml:space="preserve">8.95704650878906</t>
   </si>
   <si>
     <t xml:space="preserve">9.29518508911133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160682678223</t>
+    <t xml:space="preserve">10.2160692214966</t>
   </si>
   <si>
     <t xml:space="preserve">8.42465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6189079284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321605682373</t>
+    <t xml:space="preserve">8.61890983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321701049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.01457786560059</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8059401512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32393741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99299621582031</t>
+    <t xml:space="preserve">7.80593967437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32393836975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99299383163452</t>
   </si>
   <si>
     <t xml:space="preserve">8.10091114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98580121994019</t>
+    <t xml:space="preserve">7.98580074310303</t>
   </si>
   <si>
     <t xml:space="preserve">7.88507843017578</t>
@@ -1139,34 +1139,34 @@
     <t xml:space="preserve">7.73399591445923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41024684906006</t>
+    <t xml:space="preserve">7.41024732589722</t>
   </si>
   <si>
     <t xml:space="preserve">7.54694032669067</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47499752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535772323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38866424560547</t>
+    <t xml:space="preserve">7.47499656677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52535724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38866376876831</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760509490967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84191274642944</t>
+    <t xml:space="preserve">7.84191036224365</t>
   </si>
   <si>
     <t xml:space="preserve">7.95702266693115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8491063117981</t>
+    <t xml:space="preserve">7.84910678863525</t>
   </si>
   <si>
     <t xml:space="preserve">8.04335689544678</t>
@@ -1178,70 +1178,70 @@
     <t xml:space="preserve">7.85630083084106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74838495254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571935653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463636398315</t>
+    <t xml:space="preserve">7.74838447570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571840286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.424635887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.19441509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96419429779053</t>
+    <t xml:space="preserve">6.96419382095337</t>
   </si>
   <si>
     <t xml:space="preserve">7.21599817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97498512268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20880365371704</t>
+    <t xml:space="preserve">6.97498559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2088041305542</t>
   </si>
   <si>
     <t xml:space="preserve">7.20160961151123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55413579940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65485858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25197076797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24477529525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18722057342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448408126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00735950469971</t>
+    <t xml:space="preserve">7.55413627624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65485763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25196981430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24477577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18722009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00736045837402</t>
   </si>
   <si>
     <t xml:space="preserve">6.89944410324097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9534010887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91742897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.856276512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89224863052368</t>
+    <t xml:space="preserve">6.95340204238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15844297409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91742992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85627698898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.892249584198</t>
   </si>
   <si>
     <t xml:space="preserve">6.78793096542358</t>
@@ -1250,25 +1250,25 @@
     <t xml:space="preserve">6.95699977874756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93541622161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98218011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1620397567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217490196228</t>
+    <t xml:space="preserve">6.93541717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98217916488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16203927993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045667648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02174949645996</t>
   </si>
   <si>
     <t xml:space="preserve">7.338303565979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82752323150635</t>
+    <t xml:space="preserve">7.82752418518066</t>
   </si>
   <si>
     <t xml:space="preserve">8.25918865203857</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">7.9138560295105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89946699142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81313419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66924619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7699670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64047002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78435659408569</t>
+    <t xml:space="preserve">7.89946746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81313467025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66924476623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76996803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64046955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78435611724854</t>
   </si>
   <si>
     <t xml:space="preserve">7.48219108581543</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">6.56850147247314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64044427871704</t>
+    <t xml:space="preserve">6.64044523239136</t>
   </si>
   <si>
     <t xml:space="preserve">6.48936223983765</t>
@@ -1319,64 +1319,64 @@
     <t xml:space="preserve">6.63325119018555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62605667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56130599975586</t>
+    <t xml:space="preserve">6.62605619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56130647659302</t>
   </si>
   <si>
     <t xml:space="preserve">6.60447311401367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55411052703857</t>
+    <t xml:space="preserve">6.55411148071289</t>
   </si>
   <si>
     <t xml:space="preserve">6.28791856765747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19439125061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02172565460205</t>
+    <t xml:space="preserve">6.19439077377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02172517776489</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783670425415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86344861984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2591404914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26633501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619560241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46777868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67641687393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51813983917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46058464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29511308670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10086297988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13683605194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92819738388062</t>
+    <t xml:space="preserve">5.86344814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25914096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26633548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4677791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67641735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51814031600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46058368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2951135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10086345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1368350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92819786071777</t>
   </si>
   <si>
     <t xml:space="preserve">5.93539190292358</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">6.01453065872192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99294710159302</t>
+    <t xml:space="preserve">5.99294757843018</t>
   </si>
   <si>
     <t xml:space="preserve">6.1728081703186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1871976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25194692611694</t>
+    <t xml:space="preserve">6.18719673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25194549560547</t>
   </si>
   <si>
     <t xml:space="preserve">6.22316837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12244749069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27353000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950260162354</t>
+    <t xml:space="preserve">6.1224479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27352952957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950212478638</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230760574341</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">6.33828020095825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58551836013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38323163986206</t>
+    <t xml:space="preserve">6.58551645278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38323259353638</t>
   </si>
   <si>
     <t xml:space="preserve">6.46564388275146</t>
@@ -1442,34 +1442,34 @@
     <t xml:space="preserve">6.59300899505615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17345380783081</t>
+    <t xml:space="preserve">6.41319990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17345428466797</t>
   </si>
   <si>
     <t xml:space="preserve">6.09853410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90373992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618391036987</t>
+    <t xml:space="preserve">5.90374040603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
   </si>
   <si>
     <t xml:space="preserve">5.94120025634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8662805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94869327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84380388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656524658203</t>
+    <t xml:space="preserve">5.86628007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9486927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84380340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656620025635</t>
   </si>
   <si>
     <t xml:space="preserve">5.48418521881104</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">5.80634355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64151859283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139163970947</t>
+    <t xml:space="preserve">5.64151811599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79135942459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139116287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.88126373291016</t>
@@ -1505,58 +1505,58 @@
     <t xml:space="preserve">6.33078718185425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55554866790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815181732178</t>
+    <t xml:space="preserve">6.55554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815229415894</t>
   </si>
   <si>
     <t xml:space="preserve">6.33827972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30081939697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.128502368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06107330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77637529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76888275146484</t>
+    <t xml:space="preserve">6.30081844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12850189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06107378005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77637577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76888370513916</t>
   </si>
   <si>
     <t xml:space="preserve">5.70145463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57408905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75389909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78386688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67897891998291</t>
+    <t xml:space="preserve">5.66399478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57408952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75389862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78386783599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67897844314575</t>
   </si>
   <si>
     <t xml:space="preserve">5.6265344619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61904239654541</t>
+    <t xml:space="preserve">5.61904191970825</t>
   </si>
   <si>
     <t xml:space="preserve">5.65650272369385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54412221908569</t>
+    <t xml:space="preserve">5.54412126541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.58158159255981</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">5.5066614151001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53662872314453</t>
+    <t xml:space="preserve">5.53662919998169</t>
   </si>
   <si>
     <t xml:space="preserve">5.43174028396606</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">5.31935977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28189945220947</t>
+    <t xml:space="preserve">5.28189992904663</t>
   </si>
   <si>
     <t xml:space="preserve">5.42424821853638</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49167728424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51415348052979</t>
+    <t xml:space="preserve">5.49167776107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51415300369263</t>
   </si>
   <si>
     <t xml:space="preserve">5.36431217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27440738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450307846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20697832107544</t>
+    <t xml:space="preserve">5.27440786361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450260162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2069787979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.58907413482666</t>
@@ -1610,31 +1610,31 @@
     <t xml:space="preserve">5.47669315338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21447134017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13955068588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09459781646729</t>
+    <t xml:space="preserve">5.21447086334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13954973220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09459829330444</t>
   </si>
   <si>
     <t xml:space="preserve">5.10958242416382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07212162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05713796615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01967763900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03466129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92977237701416</t>
+    <t xml:space="preserve">5.07212209701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05713748931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01967716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03466176986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92977285385132</t>
   </si>
   <si>
     <t xml:space="preserve">4.87732839584351</t>
@@ -1646,34 +1646,34 @@
     <t xml:space="preserve">4.73498010635376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77243995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82488441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88482046127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75745582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86234378814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91478872299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89980411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85485219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95224905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16951847076416</t>
+    <t xml:space="preserve">4.77243947982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82488393783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88482093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75745534896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86234426498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91478824615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89980506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8548526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95224952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16951894760132</t>
   </si>
   <si>
     <t xml:space="preserve">5.08710622787476</t>
@@ -1682,19 +1682,19 @@
     <t xml:space="preserve">5.13205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21840667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25586748123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01612091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10602521896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99364423751831</t>
+    <t xml:space="preserve">6.21840620040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25586652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01612043380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10602617263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99364519119263</t>
   </si>
   <si>
     <t xml:space="preserve">5.04215383529663</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">4.98221731185913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94475698471069</t>
+    <t xml:space="preserve">4.94475746154785</t>
   </si>
   <si>
     <t xml:space="preserve">4.99720144271851</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">5.02716970443726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89231252670288</t>
+    <t xml:space="preserve">4.89231300354004</t>
   </si>
   <si>
     <t xml:space="preserve">5.04964542388916</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">4.78742408752441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83237648010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97472476959229</t>
+    <t xml:space="preserve">4.83237600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97472524642944</t>
   </si>
   <si>
     <t xml:space="preserve">4.90729665756226</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">4.47275686264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27047252655029</t>
+    <t xml:space="preserve">4.27047204971313</t>
   </si>
   <si>
     <t xml:space="preserve">4.38285303115845</t>
@@ -1754,124 +1754,124 @@
     <t xml:space="preserve">4.32291650772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18056678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30044031143188</t>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30043935775757</t>
   </si>
   <si>
     <t xml:space="preserve">4.31542444229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46526527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45777368545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71250343322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10209035873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07961463928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93726444244385</t>
+    <t xml:space="preserve">4.46526479721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45777320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71250295639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10208988189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07961416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93726539611816</t>
   </si>
   <si>
     <t xml:space="preserve">5.01218509674072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24443912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196340560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25942373275757</t>
+    <t xml:space="preserve">5.24443864822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196245193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25942277908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.19948673248291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11707448959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28939199447632</t>
+    <t xml:space="preserve">5.11707401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28939151763916</t>
   </si>
   <si>
     <t xml:space="preserve">5.16202640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31186771392822</t>
+    <t xml:space="preserve">5.31186819076538</t>
   </si>
   <si>
     <t xml:space="preserve">5.41675615310669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37180471420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44672441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39427947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40926456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89624786376953</t>
+    <t xml:space="preserve">5.37180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44672536849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39428043365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421743392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.409264087677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89624834060669</t>
   </si>
   <si>
     <t xml:space="preserve">5.85878801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12100982666016</t>
+    <t xml:space="preserve">6.121009349823</t>
   </si>
   <si>
     <t xml:space="preserve">6.22589874267578</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81383609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79885196685791</t>
+    <t xml:space="preserve">5.81383562088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00113725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79885101318359</t>
   </si>
   <si>
     <t xml:space="preserve">5.82132720947266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91123247146606</t>
+    <t xml:space="preserve">5.91123199462891</t>
   </si>
   <si>
     <t xml:space="preserve">6.03110504150391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.008629322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91872358322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83631229400635</t>
+    <t xml:space="preserve">6.00862979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91872406005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83631134033203</t>
   </si>
   <si>
     <t xml:space="preserve">5.87377214431763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97116851806641</t>
+    <t xml:space="preserve">5.97116804122925</t>
   </si>
   <si>
     <t xml:space="preserve">6.21091461181641</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">6.15097808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14348554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361345291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03859710693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73142290115356</t>
+    <t xml:space="preserve">6.14348649978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608869552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03859758377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73142385482788</t>
   </si>
   <si>
     <t xml:space="preserve">5.97866058349609</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">5.69396257400513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72393131256104</t>
+    <t xml:space="preserve">5.72393083572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.70894622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49916839599609</t>
+    <t xml:space="preserve">5.49916934967041</t>
   </si>
   <si>
     <t xml:space="preserve">5.46170854568481</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">5.73891448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55161333084106</t>
+    <t xml:space="preserve">5.55161380767822</t>
   </si>
   <si>
     <t xml:space="preserve">5.47268533706665</t>
@@ -1928,31 +1928,31 @@
     <t xml:space="preserve">5.30019426345825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33155584335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46484565734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35507774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30803442001343</t>
+    <t xml:space="preserve">5.33155632019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46484422683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30803489685059</t>
   </si>
   <si>
     <t xml:space="preserve">5.37859964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39428043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24530982971191</t>
+    <t xml:space="preserve">5.39428091049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24531030654907</t>
   </si>
   <si>
     <t xml:space="preserve">5.26883172988892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28451251983643</t>
+    <t xml:space="preserve">5.28451299667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.25315093994141</t>
@@ -1961,16 +1961,16 @@
     <t xml:space="preserve">5.14338350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06497859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00225448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16690444946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2061071395874</t>
+    <t xml:space="preserve">5.06497812271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00225400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16690492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20610761642456</t>
   </si>
   <si>
     <t xml:space="preserve">5.33939695358276</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">5.11986207962036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13554286956787</t>
+    <t xml:space="preserve">5.13554334640503</t>
   </si>
   <si>
     <t xml:space="preserve">5.09634065628052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11202144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17474555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44916343688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4570050239563</t>
+    <t xml:space="preserve">5.11202192306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17474603652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44916391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45700454711914</t>
   </si>
   <si>
     <t xml:space="preserve">5.61381483078003</t>
@@ -2006,25 +2006,25 @@
     <t xml:space="preserve">5.70790147781372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67653894424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733625411987</t>
+    <t xml:space="preserve">5.6765398979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733720779419</t>
   </si>
   <si>
     <t xml:space="preserve">5.55893135070801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51188850402832</t>
+    <t xml:space="preserve">5.51188802719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48052597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36291790008545</t>
+    <t xml:space="preserve">5.48052549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36291837692261</t>
   </si>
   <si>
     <t xml:space="preserve">5.31587553024292</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">5.19826745986938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79839992523193</t>
+    <t xml:space="preserve">4.79840087890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.70431423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71999502182007</t>
+    <t xml:space="preserve">4.71999549865723</t>
   </si>
   <si>
     <t xml:space="preserve">4.51614189147949</t>
@@ -2054,31 +2054,31 @@
     <t xml:space="preserve">4.82192182540894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64158964157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71215486526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67295217514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63374900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64943027496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59454679489136</t>
+    <t xml:space="preserve">4.64159059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71215438842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67295169830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63374948501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64943075180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59454727172852</t>
   </si>
   <si>
     <t xml:space="preserve">4.62590932846069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6807918548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90032720565796</t>
+    <t xml:space="preserve">4.68079233169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9003267288208</t>
   </si>
   <si>
     <t xml:space="preserve">5.22962951660156</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">5.02577543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04145669937134</t>
+    <t xml:space="preserve">5.04145622253418</t>
   </si>
   <si>
     <t xml:space="preserve">5.1512246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22178840637207</t>
+    <t xml:space="preserve">5.22178888320923</t>
   </si>
   <si>
     <t xml:space="preserve">5.21394824981689</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">5.15906429290771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08065938949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12770175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01793527603149</t>
+    <t xml:space="preserve">5.08065891265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12770223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01793575286865</t>
   </si>
   <si>
     <t xml:space="preserve">5.07281923294067</t>
@@ -2132,31 +2132,31 @@
     <t xml:space="preserve">5.40212059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56677198410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4334831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50404787063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53541040420532</t>
+    <t xml:space="preserve">5.56677150726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43348264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50404739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53540992736816</t>
   </si>
   <si>
     <t xml:space="preserve">5.41780185699463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42564296722412</t>
+    <t xml:space="preserve">5.4256420135498</t>
   </si>
   <si>
     <t xml:space="preserve">5.84118986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76278495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64517641067505</t>
+    <t xml:space="preserve">5.7627854347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64517688751221</t>
   </si>
   <si>
     <t xml:space="preserve">5.44132328033447</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">5.38643980026245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3472375869751</t>
+    <t xml:space="preserve">5.34723711013794</t>
   </si>
   <si>
     <t xml:space="preserve">5.37075853347778</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">4.8376030921936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89248704910278</t>
+    <t xml:space="preserve">4.89248657226562</t>
   </si>
   <si>
     <t xml:space="preserve">4.86896562576294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92384910583496</t>
+    <t xml:space="preserve">4.9238486289978</t>
   </si>
   <si>
     <t xml:space="preserve">4.87680578231812</t>
@@ -2198,28 +2198,28 @@
     <t xml:space="preserve">4.98657321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57102489471436</t>
+    <t xml:space="preserve">4.57102584838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750394821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57886600494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39069366455078</t>
+    <t xml:space="preserve">4.57886552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39069271087646</t>
   </si>
   <si>
     <t xml:space="preserve">4.15547752380371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2260422706604</t>
+    <t xml:space="preserve">4.22604274749756</t>
   </si>
   <si>
     <t xml:space="preserve">4.1162748336792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84185671806335</t>
+    <t xml:space="preserve">3.84185695648193</t>
   </si>
   <si>
     <t xml:space="preserve">3.63800311088562</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">3.29301977157593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32438206672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099406242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09700655937195</t>
+    <t xml:space="preserve">3.32438182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099358558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09700679779053</t>
   </si>
   <si>
     <t xml:space="preserve">3.05780434608459</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">3.00292038917542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13620924949646</t>
+    <t xml:space="preserve">3.13620948791504</t>
   </si>
   <si>
     <t xml:space="preserve">3.03036260604858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21461462974548</t>
+    <t xml:space="preserve">3.21461486816406</t>
   </si>
   <si>
     <t xml:space="preserve">3.25381755828857</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">3.22245526313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24205660820007</t>
+    <t xml:space="preserve">3.24205684661865</t>
   </si>
   <si>
     <t xml:space="preserve">3.24597692489624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23813629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34006309509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45767068862915</t>
+    <t xml:space="preserve">3.23813652992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36750531196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34006333351135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45767092704773</t>
   </si>
   <si>
     <t xml:space="preserve">3.59880065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37142539024353</t>
+    <t xml:space="preserve">3.37142515182495</t>
   </si>
   <si>
     <t xml:space="preserve">3.52039504051208</t>
@@ -2294,25 +2294,25 @@
     <t xml:space="preserve">3.54391670227051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72424864768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81049489974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92026209831238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3358097076416</t>
+    <t xml:space="preserve">3.7242488861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92026138305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33580923080444</t>
   </si>
   <si>
     <t xml:space="preserve">4.32796907424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32012844085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23388290405273</t>
+    <t xml:space="preserve">4.32012891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23388242721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.16331815719604</t>
@@ -2321,40 +2321,40 @@
     <t xml:space="preserve">4.07707214355469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21820163726807</t>
+    <t xml:space="preserve">4.21820211410522</t>
   </si>
   <si>
     <t xml:space="preserve">4.21036100387573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25740385055542</t>
+    <t xml:space="preserve">4.25740432739258</t>
   </si>
   <si>
     <t xml:space="preserve">4.19468021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73208928108215</t>
+    <t xml:space="preserve">3.73208904266357</t>
   </si>
   <si>
     <t xml:space="preserve">3.79481363296509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83401584625244</t>
+    <t xml:space="preserve">3.83401608467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.84577703475952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7007269859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009576797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321877479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80265355110168</t>
+    <t xml:space="preserve">3.70072674751282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321925163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80265426635742</t>
   </si>
   <si>
     <t xml:space="preserve">3.8222553730011</t>
@@ -2363,37 +2363,37 @@
     <t xml:space="preserve">3.86145806312561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75169038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74384999275208</t>
+    <t xml:space="preserve">3.75169062614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74385046958923</t>
   </si>
   <si>
     <t xml:space="preserve">3.98298645019531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29660701751709</t>
+    <t xml:space="preserve">4.29660654067993</t>
   </si>
   <si>
     <t xml:space="preserve">4.10059404373169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91634130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946478843689</t>
+    <t xml:space="preserve">3.91634178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946383476257</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13979625701904</t>
+    <t xml:space="preserve">4.13979721069336</t>
   </si>
   <si>
     <t xml:space="preserve">4.14763689041138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01434803009033</t>
+    <t xml:space="preserve">4.01434755325317</t>
   </si>
   <si>
     <t xml:space="preserve">3.95162415504456</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">3.88889980316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05355024337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03002882003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89281988143921</t>
+    <t xml:space="preserve">4.05355072021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89282083511353</t>
   </si>
   <si>
     <t xml:space="preserve">3.92810249328613</t>
@@ -2426,49 +2426,49 @@
     <t xml:space="preserve">3.85753750801086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86537837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617616653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88105964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90458154678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9085009098053</t>
+    <t xml:space="preserve">3.86537790298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617592811584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88105916976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90458106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90850138664246</t>
   </si>
   <si>
     <t xml:space="preserve">3.779132604599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75561046600342</t>
+    <t xml:space="preserve">3.75561094284058</t>
   </si>
   <si>
     <t xml:space="preserve">3.74777030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80657386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8849790096283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96730518341064</t>
+    <t xml:space="preserve">3.80657482147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497948646545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96730470657349</t>
   </si>
   <si>
     <t xml:space="preserve">4.02218866348267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93594336509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76345181465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75953102111816</t>
+    <t xml:space="preserve">3.93594241142273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76345205307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75953125953674</t>
   </si>
   <si>
     <t xml:space="preserve">3.6458432674408</t>
@@ -2477,43 +2477,43 @@
     <t xml:space="preserve">3.6693651676178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66544508934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56351804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56743836402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59095978736877</t>
+    <t xml:space="preserve">3.66544485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016295433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56351828575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56743860244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59096002578735</t>
   </si>
   <si>
     <t xml:space="preserve">3.48903274536133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48119282722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44198989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38710641860962</t>
+    <t xml:space="preserve">3.48119235038757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44199013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3871066570282</t>
   </si>
   <si>
     <t xml:space="preserve">3.31654167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33222270011902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40278744697571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42238831520081</t>
+    <t xml:space="preserve">3.33222222328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40278768539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42238855361938</t>
   </si>
   <si>
     <t xml:space="preserve">3.43807005882263</t>
@@ -2528,28 +2528,28 @@
     <t xml:space="preserve">3.55175757408142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55567717552185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50079369544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51255488395691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37926554679871</t>
+    <t xml:space="preserve">3.55567741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50079393386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51255440711975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37926578521729</t>
   </si>
   <si>
     <t xml:space="preserve">3.43414926528931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42630887031555</t>
+    <t xml:space="preserve">3.42630910873413</t>
   </si>
   <si>
     <t xml:space="preserve">3.4615912437439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4498302936554</t>
+    <t xml:space="preserve">3.44983053207397</t>
   </si>
   <si>
     <t xml:space="preserve">3.15189075469971</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">3.17541217803955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52823567390442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53215622901917</t>
+    <t xml:space="preserve">3.528235912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53215551376343</t>
   </si>
   <si>
     <t xml:space="preserve">3.53607630729675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10843420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99866700172424</t>
+    <t xml:space="preserve">4.10843467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99866652488708</t>
   </si>
   <si>
     <t xml:space="preserve">4.20252084732056</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">4.13195610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0927529335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06139087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2887659072876</t>
+    <t xml:space="preserve">4.09275341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06139135360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28876638412476</t>
   </si>
   <si>
     <t xml:space="preserve">4.2495641708374</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">4.69647359848022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75919771194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82976245880127</t>
+    <t xml:space="preserve">4.75919818878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82976293563843</t>
   </si>
   <si>
     <t xml:space="preserve">4.72783613204956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74351692199707</t>
+    <t xml:space="preserve">4.74351644515991</t>
   </si>
   <si>
     <t xml:space="preserve">4.76703834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77487945556641</t>
+    <t xml:space="preserve">4.77487897872925</t>
   </si>
   <si>
     <t xml:space="preserve">4.73567628860474</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">4.86112451553345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84544324874878</t>
+    <t xml:space="preserve">4.84544372558594</t>
   </si>
   <si>
     <t xml:space="preserve">4.91600847244263</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">4.93952989578247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04929780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58245325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68437957763672</t>
+    <t xml:space="preserve">5.04929685592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58245277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68438005447388</t>
   </si>
   <si>
     <t xml:space="preserve">5.59813404083252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6294960975647</t>
+    <t xml:space="preserve">5.62949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">5.7157416343689</t>
@@ -2681,40 +2681,40 @@
     <t xml:space="preserve">5.66085815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72358226776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78630638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08424711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17833232879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14697074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05288410186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97447872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03720283508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15080690383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00474548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11834859848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49161577224731</t>
+    <t xml:space="preserve">5.72358274459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78630685806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08424663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17833185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14697122573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05288457870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97447919845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03720331192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15080642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00474452972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11834812164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49161624908447</t>
   </si>
   <si>
     <t xml:space="preserve">6.45915794372559</t>
@@ -2723,43 +2723,43 @@
     <t xml:space="preserve">6.42670011520386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26440954208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41047048568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39424180984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44292974472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96225833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14077758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43290042877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00091743469238</t>
+    <t xml:space="preserve">6.2644100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41047096252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39424133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4429292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96225881576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14077806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43290090560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00091648101807</t>
   </si>
   <si>
     <t xml:space="preserve">7.83862686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87108373641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78994035720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91977310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95222997665405</t>
+    <t xml:space="preserve">7.87108516693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78994083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91977262496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95223045349121</t>
   </si>
   <si>
     <t xml:space="preserve">7.90354347229004</t>
@@ -2768,37 +2768,37 @@
     <t xml:space="preserve">8.60139179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64196300506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56081962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43910121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19566631317139</t>
+    <t xml:space="preserve">8.64196395874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56081867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43910026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19566440582275</t>
   </si>
   <si>
     <t xml:space="preserve">8.23623752593994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01714611053467</t>
+    <t xml:space="preserve">8.01714706420898</t>
   </si>
   <si>
     <t xml:space="preserve">8.06583309173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96845960617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40044164657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25438070297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48158740997314</t>
+    <t xml:space="preserve">7.96845865249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4004430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25438117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4815878868103</t>
   </si>
   <si>
     <t xml:space="preserve">7.64387845993042</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">7.56273221969604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69256448745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72502326965332</t>
+    <t xml:space="preserve">7.69256544113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72502279281616</t>
   </si>
   <si>
     <t xml:space="preserve">7.75748157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62764835357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46535778045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30306816101074</t>
+    <t xml:space="preserve">7.62764883041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46535873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3030686378479</t>
   </si>
   <si>
     <t xml:space="preserve">7.22192239761353</t>
@@ -2831,43 +2831,43 @@
     <t xml:space="preserve">6.81619691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15700626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23815202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3842134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70879411697388</t>
+    <t xml:space="preserve">7.15700674057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23815250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38421392440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70879459381104</t>
   </si>
   <si>
     <t xml:space="preserve">7.61142015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66010665893555</t>
+    <t xml:space="preserve">7.66010618209839</t>
   </si>
   <si>
     <t xml:space="preserve">7.53027486801147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74125289916992</t>
+    <t xml:space="preserve">7.74125242233276</t>
   </si>
   <si>
     <t xml:space="preserve">8.35795593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1550931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96654510498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84482765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76368236541748</t>
+    <t xml:space="preserve">8.15509223937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96654415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76368141174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.5202465057373</t>
@@ -2876,49 +2876,49 @@
     <t xml:space="preserve">8.39852905273438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47967433929443</t>
+    <t xml:space="preserve">8.47967338562012</t>
   </si>
   <si>
     <t xml:space="preserve">8.31738376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08206367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11452102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03337574005127</t>
+    <t xml:space="preserve">8.08206272125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1145191192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03337478637695</t>
   </si>
   <si>
     <t xml:space="preserve">8.04960441589355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04768848419189</t>
+    <t xml:space="preserve">9.04768943786621</t>
   </si>
   <si>
     <t xml:space="preserve">9.41284370422363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16940879821777</t>
+    <t xml:space="preserve">9.16940784454346</t>
   </si>
   <si>
     <t xml:space="preserve">9.4452428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40344905853271</t>
+    <t xml:space="preserve">9.4034481048584</t>
   </si>
   <si>
     <t xml:space="preserve">9.23627662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48703670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77958679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61241436004639</t>
+    <t xml:space="preserve">9.48703575134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7795877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6124153137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.57062149047852</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">9.52882862091064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69600200653076</t>
+    <t xml:space="preserve">9.69600105285645</t>
   </si>
   <si>
     <t xml:space="preserve">9.73779392242432</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">9.90496730804443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31986236572266</t>
+    <t xml:space="preserve">9.31986331939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.2780704498291</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">9.02731132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15269088745117</t>
+    <t xml:space="preserve">9.15268993377686</t>
   </si>
   <si>
     <t xml:space="preserve">8.86013889312744</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">8.35862159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60937976837158</t>
+    <t xml:space="preserve">8.6093807220459</t>
   </si>
   <si>
     <t xml:space="preserve">9.19448280334473</t>
@@ -2972,25 +2972,25 @@
     <t xml:space="preserve">9.11089706420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36165618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06910514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94372463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.901930809021</t>
+    <t xml:space="preserve">9.36165523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06910610198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9437255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90193176269531</t>
   </si>
   <si>
     <t xml:space="preserve">8.81834602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56758689880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52579402923584</t>
+    <t xml:space="preserve">8.56758785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52579307556152</t>
   </si>
   <si>
     <t xml:space="preserve">8.73475933074951</t>
@@ -3005,97 +3005,97 @@
     <t xml:space="preserve">8.32518768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65649700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82366895675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67321586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12154579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07139348983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10482835769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68993139266968</t>
+    <t xml:space="preserve">7.65649747848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82366991043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67321443557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12154626846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07139444351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10482788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68993234634399</t>
   </si>
   <si>
     <t xml:space="preserve">7.45589065551758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89053773880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80695295333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62306213378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99084281921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09114742279053</t>
+    <t xml:space="preserve">7.89053821563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80695247650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62306356430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99084234237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09114551544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.04099369049072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27503395080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40041542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10786247253418</t>
+    <t xml:space="preserve">8.2750358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40041446685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1078634262085</t>
   </si>
   <si>
     <t xml:space="preserve">8.48400020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30011177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35026264190674</t>
+    <t xml:space="preserve">8.3001127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35026359558105</t>
   </si>
   <si>
     <t xml:space="preserve">8.24995994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87382221221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69829082489014</t>
+    <t xml:space="preserve">7.87382173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69828987121582</t>
   </si>
   <si>
     <t xml:space="preserve">7.96576595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81531286239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77351903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91561603546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7818775177002</t>
+    <t xml:space="preserve">7.81531143188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77351760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91561460494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78187704086304</t>
   </si>
   <si>
     <t xml:space="preserve">7.60634613037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89889669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79859352111816</t>
+    <t xml:space="preserve">7.89889764785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79859304428101</t>
   </si>
   <si>
     <t xml:space="preserve">7.79023456573486</t>
@@ -3104,16 +3104,16 @@
     <t xml:space="preserve">7.83202838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63978099822998</t>
+    <t xml:space="preserve">7.63978052139282</t>
   </si>
   <si>
     <t xml:space="preserve">7.41302871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6485013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24154281616211</t>
+    <t xml:space="preserve">7.64850187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24154376983643</t>
   </si>
   <si>
     <t xml:space="preserve">8.21538066864014</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">8.19793701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49445819854736</t>
+    <t xml:space="preserve">8.49445915222168</t>
   </si>
   <si>
     <t xml:space="preserve">8.69504642486572</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">8.67760372161865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54678630828857</t>
+    <t xml:space="preserve">8.54678726196289</t>
   </si>
   <si>
     <t xml:space="preserve">8.7386531829834</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">8.64271926879883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63399696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47701740264893</t>
+    <t xml:space="preserve">8.63399791717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47701644897461</t>
   </si>
   <si>
     <t xml:space="preserve">8.45957374572754</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">7.61361598968506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71827173233032</t>
+    <t xml:space="preserve">7.71827077865601</t>
   </si>
   <si>
     <t xml:space="preserve">7.77931976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95374298095703</t>
+    <t xml:space="preserve">7.95374393463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.14561080932617</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">7.76187658309937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63978052139282</t>
+    <t xml:space="preserve">7.63978004455566</t>
   </si>
   <si>
     <t xml:space="preserve">7.6921067237854</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">7.46535634994507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54384613037109</t>
+    <t xml:space="preserve">7.54384660720825</t>
   </si>
   <si>
     <t xml:space="preserve">7.73571348190308</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50024080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63105869293213</t>
+    <t xml:space="preserve">7.50024127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63105916976929</t>
   </si>
   <si>
     <t xml:space="preserve">7.55256795883179</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">7.50896167755127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57001066207886</t>
+    <t xml:space="preserve">7.57001113891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.80548334121704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74443531036377</t>
+    <t xml:space="preserve">7.74443435668945</t>
   </si>
   <si>
     <t xml:space="preserve">8.61655616760254</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">8.48573684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50318050384521</t>
+    <t xml:space="preserve">8.5031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.607834815979</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">8.41596698760986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3461971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.023512840271</t>
+    <t xml:space="preserve">8.34619808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02351379394531</t>
   </si>
   <si>
     <t xml:space="preserve">8.37236213684082</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">7.88397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97118711471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6833872795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33453798294067</t>
+    <t xml:space="preserve">7.97118616104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68338632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33453750610352</t>
   </si>
   <si>
     <t xml:space="preserve">7.1688346862793</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">7.09906530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06418037414551</t>
+    <t xml:space="preserve">7.06418085098267</t>
   </si>
   <si>
     <t xml:space="preserve">7.28221082687378</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">7.13395023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1252293586731</t>
+    <t xml:space="preserve">7.12522888183594</t>
   </si>
   <si>
     <t xml:space="preserve">6.78510189056396</t>
@@ -3329,13 +3329,13 @@
     <t xml:space="preserve">6.61939907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41008901596069</t>
+    <t xml:space="preserve">6.41008949279785</t>
   </si>
   <si>
     <t xml:space="preserve">6.63684129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87231397628784</t>
+    <t xml:space="preserve">6.87231349945068</t>
   </si>
   <si>
     <t xml:space="preserve">7.75315618515015</t>
@@ -3359,43 +3359,43 @@
     <t xml:space="preserve">7.38686513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35198068618774</t>
+    <t xml:space="preserve">7.3519811630249</t>
   </si>
   <si>
     <t xml:space="preserve">7.31709575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47407722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.290931224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32581615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30837440490723</t>
+    <t xml:space="preserve">7.47407674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29093170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32581663131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30837392807007</t>
   </si>
   <si>
     <t xml:space="preserve">7.42175006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45663547515869</t>
+    <t xml:space="preserve">7.45663499832153</t>
   </si>
   <si>
     <t xml:space="preserve">7.3694224357605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85781097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03223514556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1020040512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15433311462402</t>
+    <t xml:space="preserve">7.85781002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03223419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10200500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15433216094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.05839729309082</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">8.09328269958496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00607204437256</t>
+    <t xml:space="preserve">8.00607109069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.08456230163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11072635650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07584095001221</t>
+    <t xml:space="preserve">8.11072540283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07584190368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.04095649719238</t>
@@ -3440,25 +3440,25 @@
     <t xml:space="preserve">8.11944770812988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25898742675781</t>
+    <t xml:space="preserve">8.2589864730835</t>
   </si>
   <si>
     <t xml:space="preserve">8.27642822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.337477684021</t>
+    <t xml:space="preserve">8.33747673034668</t>
   </si>
   <si>
     <t xml:space="preserve">8.52934265136719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94796180725098</t>
+    <t xml:space="preserve">8.94796085357666</t>
   </si>
   <si>
     <t xml:space="preserve">8.87819194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89563465118408</t>
+    <t xml:space="preserve">8.89563369750977</t>
   </si>
   <si>
     <t xml:space="preserve">8.65144062042236</t>
@@ -3470,25 +3470,25 @@
     <t xml:space="preserve">8.79098033905029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70376777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71248817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86074924468994</t>
+    <t xml:space="preserve">8.70376682281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71248912811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86075019836426</t>
   </si>
   <si>
     <t xml:space="preserve">8.93051910400391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62527751922607</t>
+    <t xml:space="preserve">8.62527656555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.56422805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46829509735107</t>
+    <t xml:space="preserve">8.46829605102539</t>
   </si>
   <si>
     <t xml:space="preserve">8.6863260269165</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">8.91307735443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00028800964355</t>
+    <t xml:space="preserve">8.96540451049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00028896331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.82586479187012</t>
@@ -3521,22 +3521,22 @@
     <t xml:space="preserve">8.84330749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80842304229736</t>
+    <t xml:space="preserve">8.80842208862305</t>
   </si>
   <si>
     <t xml:space="preserve">8.66888236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91124629974365</t>
+    <t xml:space="preserve">8.91124534606934</t>
   </si>
   <si>
     <t xml:space="preserve">8.95666408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82040691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85674285888672</t>
+    <t xml:space="preserve">8.82040786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8567419052124</t>
   </si>
   <si>
     <t xml:space="preserve">8.75682067871094</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">8.5751428604126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58422660827637</t>
+    <t xml:space="preserve">8.58422756195068</t>
   </si>
   <si>
     <t xml:space="preserve">8.6750659942627</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">8.702317237854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77498722076416</t>
+    <t xml:space="preserve">8.77498817443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.62056255340576</t>
@@ -3584,19 +3584,19 @@
     <t xml:space="preserve">8.51155662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49339008331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3843822479248</t>
+    <t xml:space="preserve">8.49338912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38438320159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.23904132843018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18453884124756</t>
+    <t xml:space="preserve">8.18453788757324</t>
   </si>
   <si>
     <t xml:space="preserve">8.08461570739746</t>
@@ -3608,13 +3608,13 @@
     <t xml:space="preserve">8.14820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33896446228027</t>
+    <t xml:space="preserve">8.33896350860596</t>
   </si>
   <si>
     <t xml:space="preserve">8.17545509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09369945526123</t>
+    <t xml:space="preserve">8.09370040893555</t>
   </si>
   <si>
     <t xml:space="preserve">8.13003540039062</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">7.77576589584351</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04827976226807</t>
+    <t xml:space="preserve">8.04828071594238</t>
   </si>
   <si>
     <t xml:space="preserve">8.01194477081299</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">8.13911914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06644916534424</t>
+    <t xml:space="preserve">8.06644821166992</t>
   </si>
   <si>
     <t xml:space="preserve">8.21179008483887</t>
@@ -3662,40 +3662,40 @@
     <t xml:space="preserve">8.15728664398193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03919792175293</t>
+    <t xml:space="preserve">8.03919696807861</t>
   </si>
   <si>
     <t xml:space="preserve">7.93927478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00286293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9483585357666</t>
+    <t xml:space="preserve">8.00286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94835901260376</t>
   </si>
   <si>
     <t xml:space="preserve">7.97561025619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95744276046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90293884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89385557174683</t>
+    <t xml:space="preserve">7.95744228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9029393196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89385461807251</t>
   </si>
   <si>
     <t xml:space="preserve">7.84843683242798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85751962661743</t>
+    <t xml:space="preserve">7.85752010345459</t>
   </si>
   <si>
     <t xml:space="preserve">7.91202354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81210088729858</t>
+    <t xml:space="preserve">7.81210136413574</t>
   </si>
   <si>
     <t xml:space="preserve">7.86660385131836</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">7.7121787071228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72126293182373</t>
+    <t xml:space="preserve">7.72126245498657</t>
   </si>
   <si>
     <t xml:space="preserve">7.98469352722168</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">7.83026885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87568855285645</t>
+    <t xml:space="preserve">7.87568807601929</t>
   </si>
   <si>
     <t xml:space="preserve">7.75759792327881</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">7.58500528335571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63950824737549</t>
+    <t xml:space="preserve">7.63950777053833</t>
   </si>
   <si>
     <t xml:space="preserve">7.57592153549194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4941668510437</t>
+    <t xml:space="preserve">7.49416637420654</t>
   </si>
   <si>
     <t xml:space="preserve">7.53958606719971</t>
@@ -3752,10 +3752,10 @@
     <t xml:space="preserve">7.5123348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4124116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44874715805054</t>
+    <t xml:space="preserve">7.41241216659546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4487476348877</t>
   </si>
   <si>
     <t xml:space="preserve">7.32157421112061</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">6.77654361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73112392425537</t>
+    <t xml:space="preserve">6.73112440109253</t>
   </si>
   <si>
     <t xml:space="preserve">6.52219581604004</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">6.38593864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72204065322876</t>
+    <t xml:space="preserve">6.7220401763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.46769285202026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59486722946167</t>
+    <t xml:space="preserve">6.59486675262451</t>
   </si>
   <si>
     <t xml:space="preserve">6.85829830169678</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">6.71295642852783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01272296905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36699295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31249046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35790920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55775356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65767621994019</t>
+    <t xml:space="preserve">7.01272344589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36699247360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31248998641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35790967941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55775308609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65767669677734</t>
   </si>
   <si>
     <t xml:space="preserve">7.73943090438843</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">7.83935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79393291473389</t>
+    <t xml:space="preserve">7.79393339157104</t>
   </si>
   <si>
     <t xml:space="preserve">7.62134075164795</t>
@@ -3845,31 +3845,31 @@
     <t xml:space="preserve">7.82118463516235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76668262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9665265083313</t>
+    <t xml:space="preserve">7.76668214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96652698516846</t>
   </si>
   <si>
     <t xml:space="preserve">7.56683731079102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63042402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53050184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47599840164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37607669830322</t>
+    <t xml:space="preserve">7.63042449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53050231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.475998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37607717514038</t>
   </si>
   <si>
     <t xml:space="preserve">7.39424467086792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28523874282837</t>
+    <t xml:space="preserve">7.28523921966553</t>
   </si>
   <si>
     <t xml:space="preserve">7.26707077026367</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">7.14898061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11264514923096</t>
+    <t xml:space="preserve">7.11264562606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.23073530197144</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">7.30340623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61225700378418</t>
+    <t xml:space="preserve">7.61225652694702</t>
   </si>
   <si>
     <t xml:space="preserve">7.43058013916016</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">7.19440031051636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24890327453613</t>
+    <t xml:space="preserve">7.24890279769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.83328247070312</t>
@@ -4326,6 +4326,9 @@
   </si>
   <si>
     <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88000011444092</t>
   </si>
 </sst>
 </file>
@@ -72200,9 +72203,11 @@
       <c r="E2598" t="n">
         <v>10.1499996185303</v>
       </c>
-      <c r="F2598"/>
+      <c r="F2598" t="n">
+        <v>10.1999998092651</v>
+      </c>
       <c r="G2598" t="s">
-        <v>1437</v>
+        <v>1400</v>
       </c>
       <c r="H2598" t="s">
         <v>9</v>
@@ -72210,27 +72215,51 @@
     </row>
     <row r="2599">
       <c r="A2599" s="1" t="n">
-        <v>46104.6912384259</v>
+        <v>46105.3333333333</v>
       </c>
       <c r="B2599" t="n">
-        <v>12787</v>
+        <v>5514</v>
       </c>
       <c r="C2599" t="n">
-        <v>10.3500003814697</v>
+        <v>10.1000003814697</v>
       </c>
       <c r="D2599" t="n">
-        <v>9.85999965667725</v>
+        <v>9.9399995803833</v>
       </c>
       <c r="E2599" t="n">
-        <v>10.1499996185303</v>
-      </c>
-      <c r="F2599" t="n">
-        <v>10.1999998092651</v>
-      </c>
+        <v>10.0500001907349</v>
+      </c>
+      <c r="F2599"/>
       <c r="G2599" t="s">
-        <v>1400</v>
+        <v>1437</v>
       </c>
       <c r="H2599" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" s="1" t="n">
+        <v>46105.6912384259</v>
+      </c>
+      <c r="B2600" t="n">
+        <v>5514</v>
+      </c>
+      <c r="C2600" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="D2600" t="n">
+        <v>9.9399995803833</v>
+      </c>
+      <c r="E2600" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="F2600" t="n">
+        <v>9.88000011444092</v>
+      </c>
+      <c r="G2600" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H2600" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GE.MI.xlsx
+++ b/data/GE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="1440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="1439">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,88 +44,88 @@
     <t xml:space="preserve">GE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21355497837067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22546625137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20654857158661</t>
+    <t xml:space="preserve">1.21355509757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22546637058258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20654845237732</t>
   </si>
   <si>
     <t xml:space="preserve">1.23177242279053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24998962879181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26330244541168</t>
+    <t xml:space="preserve">1.24998986721039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26330256462097</t>
   </si>
   <si>
     <t xml:space="preserve">1.27311170101166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26120042800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24718689918518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20794975757599</t>
+    <t xml:space="preserve">1.26120030879974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24718701839447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2079496383667</t>
   </si>
   <si>
     <t xml:space="preserve">1.19323575496674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17501842975616</t>
+    <t xml:space="preserve">1.17501819133759</t>
   </si>
   <si>
     <t xml:space="preserve">1.19814050197601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24578583240509</t>
+    <t xml:space="preserve">1.2457857131958</t>
   </si>
   <si>
     <t xml:space="preserve">1.23457503318787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21495652198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1827255487442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17992281913757</t>
+    <t xml:space="preserve">1.21495628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18272566795349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17992305755615</t>
   </si>
   <si>
     <t xml:space="preserve">1.17641985416412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.12457036972046</t>
+    <t xml:space="preserve">1.12457048892975</t>
   </si>
   <si>
     <t xml:space="preserve">1.12807369232178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10284972190857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08603358268738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01596701145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0250757932663</t>
+    <t xml:space="preserve">1.10284960269928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08603370189667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01596689224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02507591247559</t>
   </si>
   <si>
     <t xml:space="preserve">1.02017104625702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.00195372104645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02297389507294</t>
+    <t xml:space="preserve">1.00195384025574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02297353744507</t>
   </si>
   <si>
     <t xml:space="preserve">1.04329299926758</t>
@@ -140,40 +140,40 @@
     <t xml:space="preserve">1.11055707931519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0930403470993</t>
+    <t xml:space="preserve">1.09304022789001</t>
   </si>
   <si>
     <t xml:space="preserve">1.12106704711914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13017582893372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15610063076019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10004711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13157713413239</t>
+    <t xml:space="preserve">1.13017594814301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15610039234161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10004699230194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13157725334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.10705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.13227772712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11826431751251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14909374713898</t>
+    <t xml:space="preserve">1.13227796554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1182644367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14909362792969</t>
   </si>
   <si>
     <t xml:space="preserve">1.17852175235748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17011368274689</t>
+    <t xml:space="preserve">1.17011392116547</t>
   </si>
   <si>
     <t xml:space="preserve">1.18412709236145</t>
@@ -185,64 +185,64 @@
     <t xml:space="preserve">1.16310703754425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22616696357727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24508512020111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24088132381439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20514702796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1911336183548</t>
+    <t xml:space="preserve">1.22616708278656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24508500099182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24088108539581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20514714717865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19113385677338</t>
   </si>
   <si>
     <t xml:space="preserve">1.22686779499054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22196292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24438428878784</t>
+    <t xml:space="preserve">1.22196304798126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24438440799713</t>
   </si>
   <si>
     <t xml:space="preserve">1.17221581935883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19183433055878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19743978977203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20374572277069</t>
+    <t xml:space="preserve">1.19183421134949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19743955135345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20374584197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.203045129776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23807835578918</t>
+    <t xml:space="preserve">1.2380782365799</t>
   </si>
   <si>
     <t xml:space="preserve">1.2331737279892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19954168796539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22476577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21845984458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21916055679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22896981239319</t>
+    <t xml:space="preserve">1.19954180717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22476589679718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21845972537994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21916043758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2289696931839</t>
   </si>
   <si>
     <t xml:space="preserve">1.21215379238129</t>
@@ -254,34 +254,34 @@
     <t xml:space="preserve">1.29202973842621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2962338924408</t>
+    <t xml:space="preserve">1.29623365402222</t>
   </si>
   <si>
     <t xml:space="preserve">1.2752138376236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28712511062622</t>
+    <t xml:space="preserve">1.28712522983551</t>
   </si>
   <si>
     <t xml:space="preserve">1.28151977062225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24788784980774</t>
+    <t xml:space="preserve">1.24788761138916</t>
   </si>
   <si>
     <t xml:space="preserve">1.23737788200378</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20865035057068</t>
+    <t xml:space="preserve">1.20865046977997</t>
   </si>
   <si>
     <t xml:space="preserve">1.15469908714294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14138638973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11896502971649</t>
+    <t xml:space="preserve">1.14138627052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11896514892578</t>
   </si>
   <si>
     <t xml:space="preserve">1.12036633491516</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">1.14629113674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14208710193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07202017307281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.084632396698</t>
+    <t xml:space="preserve">1.14208722114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07202053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08463251590729</t>
   </si>
   <si>
     <t xml:space="preserve">1.06501388549805</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">1.07061910629272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.08253037929535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07902717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05800700187683</t>
+    <t xml:space="preserve">1.08253026008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.07902705669403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05800724029541</t>
   </si>
   <si>
     <t xml:space="preserve">1.1014484167099</t>
@@ -326,61 +326,61 @@
     <t xml:space="preserve">1.09514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.11966574192047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09934639930725</t>
+    <t xml:space="preserve">1.11966562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09934628009796</t>
   </si>
   <si>
     <t xml:space="preserve">1.11265909671783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1568009853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34528028964996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48681497573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48821651935577</t>
+    <t xml:space="preserve">1.15680110454559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34528040885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4868152141571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48821663856506</t>
   </si>
   <si>
     <t xml:space="preserve">1.45178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41534721851349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45738708972931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40133380889893</t>
+    <t xml:space="preserve">1.4153470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4573872089386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40133368968964</t>
   </si>
   <si>
     <t xml:space="preserve">1.4699991941452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43776857852936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42375540733337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43636691570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42936062812805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41674852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42235374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41814970970154</t>
+    <t xml:space="preserve">1.43776845932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42375516891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4363671541214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42936050891876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41674864292145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42235398292542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41814982891083</t>
   </si>
   <si>
     <t xml:space="preserve">1.4111430644989</t>
@@ -410,52 +410,52 @@
     <t xml:space="preserve">1.79090476036072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77268719673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73064744472504</t>
+    <t xml:space="preserve">1.77268731594086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73064732551575</t>
   </si>
   <si>
     <t xml:space="preserve">1.71663403511047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78670048713684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8427540063858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82593762874603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82313525676727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83995115756989</t>
+    <t xml:space="preserve">1.78670036792755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84275412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82593810558319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82313513755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83995139598846</t>
   </si>
   <si>
     <t xml:space="preserve">1.83855020999908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84415531158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83014214038849</t>
+    <t xml:space="preserve">1.84415519237518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83014190196991</t>
   </si>
   <si>
     <t xml:space="preserve">1.81472718715668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82874047756195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81192457675934</t>
+    <t xml:space="preserve">1.82874059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81192481517792</t>
   </si>
   <si>
     <t xml:space="preserve">1.83294463157654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84835934638977</t>
+    <t xml:space="preserve">1.84835922718048</t>
   </si>
   <si>
     <t xml:space="preserve">1.86937916278839</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">2.07257270812988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02913165092468</t>
+    <t xml:space="preserve">2.0291314125061</t>
   </si>
   <si>
     <t xml:space="preserve">2.08798742294312</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">2.04034209251404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99830186367035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03053283691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01932191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970316886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01231575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09359240531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17066621780396</t>
+    <t xml:space="preserve">1.99830198287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03053259849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01932168006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9997034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01231527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17066597938538</t>
   </si>
   <si>
     <t xml:space="preserve">2.15945529937744</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">1.98989403247833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88339257240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97167694568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345914363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01651930809021</t>
+    <t xml:space="preserve">1.88339245319366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97167658805847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345950126648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01651954650879</t>
   </si>
   <si>
     <t xml:space="preserve">2.00250601768494</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1.98428869247437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9786833524704</t>
+    <t xml:space="preserve">1.97868323326111</t>
   </si>
   <si>
     <t xml:space="preserve">1.93944585323334</t>
@@ -530,100 +530,100 @@
     <t xml:space="preserve">1.9198272228241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86377382278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8679780960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87918889522552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85676753520966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78950333595276</t>
+    <t xml:space="preserve">1.86377394199371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86797797679901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87918865680695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85676729679108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78950309753418</t>
   </si>
   <si>
     <t xml:space="preserve">1.80631947517395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90301120281219</t>
+    <t xml:space="preserve">1.90301144123077</t>
   </si>
   <si>
     <t xml:space="preserve">1.89880740642548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91001784801483</t>
+    <t xml:space="preserve">1.91001808643341</t>
   </si>
   <si>
     <t xml:space="preserve">1.99690067768097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98849260807037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98568987846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94224834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9576632976532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96186721324921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96326887607574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9702752828598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607136726379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0039074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07397437095642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18888354301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1650607585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13282990455627</t>
+    <t xml:space="preserve">1.98849284648895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98569011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94224870204926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95766341686249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9618673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96326851844788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97027540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9660712480545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00390768051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07397389411926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18888378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16506052017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13283038139343</t>
   </si>
   <si>
     <t xml:space="preserve">2.06416487693787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09639573097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11601400375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09499382972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1132116317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14404034614563</t>
+    <t xml:space="preserve">2.09639549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11601448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09499406814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11321115493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14404106140137</t>
   </si>
   <si>
     <t xml:space="preserve">2.13002777099609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14824461936951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13423109054565</t>
+    <t xml:space="preserve">2.14824485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13423132896423</t>
   </si>
   <si>
     <t xml:space="preserve">2.14123821258545</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">2.1524486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13703393936157</t>
+    <t xml:space="preserve">2.13703441619873</t>
   </si>
   <si>
     <t xml:space="preserve">2.11180996894836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09779691696167</t>
+    <t xml:space="preserve">2.09779667854309</t>
   </si>
   <si>
     <t xml:space="preserve">2.11881685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10200071334839</t>
+    <t xml:space="preserve">2.10200095176697</t>
   </si>
   <si>
     <t xml:space="preserve">2.11741542816162</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">2.24213409423828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48876857757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48736786842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49297308921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48316359519958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46494626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40328741073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52099967002869</t>
+    <t xml:space="preserve">2.48876881599426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4873673915863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49297332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48316311836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46494603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40328764915466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52099943161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.48036098480225</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">2.46634745597839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44392585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43972206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47615671157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45513677597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49437379837036</t>
+    <t xml:space="preserve">2.44392609596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43972229957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47615647315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45513653755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49437403678894</t>
   </si>
   <si>
     <t xml:space="preserve">2.47335433959961</t>
@@ -704,52 +704,52 @@
     <t xml:space="preserve">2.71858763694763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70457434654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84751081466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78865456581116</t>
+    <t xml:space="preserve">2.70457410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84751033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.788654088974</t>
   </si>
   <si>
     <t xml:space="preserve">3.11096096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23988366127014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38422155380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46129488945007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71003174781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58040761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69251418113708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66098427772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6960175037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7836012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95176076889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06386804580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19349145889282</t>
+    <t xml:space="preserve">3.23988389968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38422083854675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46129465103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71003103256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58040809631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69251441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6609845161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69601774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78360104560852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9517617225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06386756896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19349193572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.16896820068359</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">4.03233814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30910110473633</t>
+    <t xml:space="preserve">4.30910158157349</t>
   </si>
   <si>
     <t xml:space="preserve">4.30559825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55433511734009</t>
+    <t xml:space="preserve">4.55433559417725</t>
   </si>
   <si>
     <t xml:space="preserve">4.6979718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50023555755615</t>
+    <t xml:space="preserve">5.50023508071899</t>
   </si>
   <si>
     <t xml:space="preserve">4.79256200790405</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">5.10085535049438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01677465438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44768476486206</t>
+    <t xml:space="preserve">5.01677513122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44768524169922</t>
   </si>
   <si>
     <t xml:space="preserve">5.44418144226074</t>
@@ -794,91 +794,91 @@
     <t xml:space="preserve">5.77349519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39708852767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76143646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49518251419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71238803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09369325637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97858285903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7843337059021</t>
+    <t xml:space="preserve">6.3970890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76143503189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49518203735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71238946914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09369421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97858238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78433275222778</t>
   </si>
   <si>
     <t xml:space="preserve">6.35626602172852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5325288772583</t>
+    <t xml:space="preserve">6.53252840042114</t>
   </si>
   <si>
     <t xml:space="preserve">6.35266828536987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07208633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32389068603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43900060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51094627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4030294418335</t>
+    <t xml:space="preserve">6.07208585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.323890209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43900156021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51094532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40302991867065</t>
   </si>
   <si>
     <t xml:space="preserve">6.15841913223267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19798851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37425136566162</t>
+    <t xml:space="preserve">6.19798803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37425088882446</t>
   </si>
   <si>
     <t xml:space="preserve">6.47137594223022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32748651504517</t>
+    <t xml:space="preserve">6.32748794555664</t>
   </si>
   <si>
     <t xml:space="preserve">6.15122509002686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11165475845337</t>
+    <t xml:space="preserve">6.11165523529053</t>
   </si>
   <si>
     <t xml:space="preserve">5.93898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96057271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85265636444092</t>
+    <t xml:space="preserve">5.96057224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85265731811523</t>
   </si>
   <si>
     <t xml:space="preserve">5.90661478042603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89582252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75193405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6943793296814</t>
+    <t xml:space="preserve">5.89582300186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75193452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69437885284424</t>
   </si>
   <si>
     <t xml:space="preserve">5.70157384872437</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">5.3670334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87421560287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17997884750366</t>
+    <t xml:space="preserve">4.87421607971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1799783706665</t>
   </si>
   <si>
     <t xml:space="preserve">4.97853517532349</t>
@@ -905,61 +905,61 @@
     <t xml:space="preserve">4.87781381607056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91018772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7015495300293</t>
+    <t xml:space="preserve">4.9101881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70155048370361</t>
   </si>
   <si>
     <t xml:space="preserve">4.92457675933838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69075870513916</t>
+    <t xml:space="preserve">4.76989698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.690758228302</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838384628296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68716096878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82385540008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5504674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51089859008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49291229248047</t>
+    <t xml:space="preserve">4.68716144561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82385492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55046701431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51089811325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49291133880615</t>
   </si>
   <si>
     <t xml:space="preserve">4.43895387649536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38139867782593</t>
+    <t xml:space="preserve">4.38139915466309</t>
   </si>
   <si>
     <t xml:space="preserve">4.38499593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46413469314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03609085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85623025894165</t>
+    <t xml:space="preserve">4.46413421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03609037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85622978210449</t>
   </si>
   <si>
     <t xml:space="preserve">4.80946636199951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76629972457886</t>
+    <t xml:space="preserve">4.76629877090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.68356418609619</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">4.67637014389038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60442543029785</t>
+    <t xml:space="preserve">4.60442590713501</t>
   </si>
   <si>
     <t xml:space="preserve">4.59003686904907</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">4.62960624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66198062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67277240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74831390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75910568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9533543586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83104991912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06486749649048</t>
+    <t xml:space="preserve">4.66198110580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6727728843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74831342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75910472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95335578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83104944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06486797332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.14400672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11522960662842</t>
+    <t xml:space="preserve">5.11522912979126</t>
   </si>
   <si>
     <t xml:space="preserve">5.19436740875244</t>
@@ -1010,49 +1010,49 @@
     <t xml:space="preserve">5.10803413391113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93536901473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75550889968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99652194976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90659046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92097997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82025814056396</t>
+    <t xml:space="preserve">4.93536853790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75550842285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99652099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90659093856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92097949981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82025718688965</t>
   </si>
   <si>
     <t xml:space="preserve">4.89220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05407667160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07925748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0181040763855</t>
+    <t xml:space="preserve">5.05407619476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07925701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01810455322266</t>
   </si>
   <si>
     <t xml:space="preserve">4.95695209503174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94615983963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15839576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23393630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6080470085144</t>
+    <t xml:space="preserve">4.94616031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15839529037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23393678665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60804653167725</t>
   </si>
   <si>
     <t xml:space="preserve">5.89942026138306</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">5.77711486816406</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03611373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94978189468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18000268936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20877933502197</t>
+    <t xml:space="preserve">6.03611469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94978141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18000316619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20877981185913</t>
   </si>
   <si>
     <t xml:space="preserve">6.52533435821533</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">7.03613710403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89584684371948</t>
+    <t xml:space="preserve">6.89584636688232</t>
   </si>
   <si>
     <t xml:space="preserve">7.11527633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13685941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980242729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969017028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43904876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95704650878906</t>
+    <t xml:space="preserve">7.13685894012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69802474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12968921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43904685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95704555511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.29518413543701</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">10.2160682678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42466163635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61890983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321605682373</t>
+    <t xml:space="preserve">8.42465877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61890888214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321701049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.0145788192749</t>
@@ -1130,82 +1130,82 @@
     <t xml:space="preserve">8.10091209411621</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98580121994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8850793838501</t>
+    <t xml:space="preserve">7.98580026626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88507795333862</t>
   </si>
   <si>
     <t xml:space="preserve">7.73399543762207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41024780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54694080352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47499656677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45341444015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52535820007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38866519927979</t>
+    <t xml:space="preserve">7.41024732589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54694128036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47499704360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45341300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5253586769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38866376876831</t>
   </si>
   <si>
     <t xml:space="preserve">8.23760414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84191179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95702362060547</t>
+    <t xml:space="preserve">7.84191083908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95702266693115</t>
   </si>
   <si>
     <t xml:space="preserve">7.8491063117981</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04335498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92824506759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8563027381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74838542938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57571887969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42463541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1944146156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96419477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21599721908569</t>
+    <t xml:space="preserve">8.04335689544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92824554443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85630083084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74838590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57571840286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.424635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96419382095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21599864959717</t>
   </si>
   <si>
     <t xml:space="preserve">6.97498512268066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20880365371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20161008834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55413389205933</t>
+    <t xml:space="preserve">7.20880460739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20161056518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55413627624512</t>
   </si>
   <si>
     <t xml:space="preserve">7.65485763549805</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">7.24477624893188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18722105026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10448503494263</t>
+    <t xml:space="preserve">7.18722009658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10448360443115</t>
   </si>
   <si>
     <t xml:space="preserve">7.00735950469971</t>
@@ -1229,46 +1229,46 @@
     <t xml:space="preserve">6.89944410324097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15844249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91742992401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85627794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89224863052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78793048858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9569993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93541717529297</t>
+    <t xml:space="preserve">6.95340204238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1584415435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91743040084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.856276512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.892249584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78793096542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95700025558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93541574478149</t>
   </si>
   <si>
     <t xml:space="preserve">6.98218011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16204023361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14045715332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0217490196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82752418518066</t>
+    <t xml:space="preserve">7.16203880310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14045763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02174949645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33830261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82752323150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.25918865203857</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">8.15846633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9138560295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89946746826172</t>
+    <t xml:space="preserve">7.91385650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89946794509888</t>
   </si>
   <si>
     <t xml:space="preserve">7.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66924524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76996755599976</t>
+    <t xml:space="preserve">7.66924667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76996850967407</t>
   </si>
   <si>
     <t xml:space="preserve">7.64046859741211</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">7.78435659408569</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48219203948975</t>
+    <t xml:space="preserve">7.48219108581543</t>
   </si>
   <si>
     <t xml:space="preserve">6.79152727127075</t>
@@ -1313,31 +1313,31 @@
     <t xml:space="preserve">6.64044523239136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63325119018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62605571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56130647659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60447311401367</t>
+    <t xml:space="preserve">6.48936223983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63325071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62605619430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56130599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60447359085083</t>
   </si>
   <si>
     <t xml:space="preserve">6.55411148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28791856765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19439125061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02172517776489</t>
+    <t xml:space="preserve">6.28791904449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19439077377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02172470092773</t>
   </si>
   <si>
     <t xml:space="preserve">5.87783670425415</t>
@@ -1349,46 +1349,46 @@
     <t xml:space="preserve">6.2591404914856</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26633548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44619560241699</t>
+    <t xml:space="preserve">6.26633501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44619607925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.4677791595459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67641687393188</t>
+    <t xml:space="preserve">6.67641735076904</t>
   </si>
   <si>
     <t xml:space="preserve">6.51814079284668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46058368682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2951135635376</t>
+    <t xml:space="preserve">6.46058464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29511308670044</t>
   </si>
   <si>
     <t xml:space="preserve">6.10086297988892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1368350982666</t>
+    <t xml:space="preserve">6.13683557510376</t>
   </si>
   <si>
     <t xml:space="preserve">5.92819786071777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93539237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89222526550293</t>
+    <t xml:space="preserve">5.93539190292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89222574234009</t>
   </si>
   <si>
     <t xml:space="preserve">5.79869890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97136497497559</t>
+    <t xml:space="preserve">5.97136402130127</t>
   </si>
   <si>
     <t xml:space="preserve">6.01453065872192</t>
@@ -1400,130 +1400,130 @@
     <t xml:space="preserve">6.1728081703186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1871976852417</t>
+    <t xml:space="preserve">6.18719720840454</t>
   </si>
   <si>
     <t xml:space="preserve">6.25194597244263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22316789627075</t>
+    <t xml:space="preserve">6.22316837310791</t>
   </si>
   <si>
     <t xml:space="preserve">6.12244749069214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27353048324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30950307846069</t>
+    <t xml:space="preserve">6.27352952957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30950260162354</t>
   </si>
   <si>
     <t xml:space="preserve">6.30230760574341</t>
   </si>
   <si>
+    <t xml:space="preserve">6.33828020095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58551692962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38323259353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46564435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35326290130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59300947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41320037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17345476150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09853363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90373992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95618438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94120073318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86627960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9486927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84380388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59656572341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48418474197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60405826568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55910539627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88875579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8063440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64151859283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76139068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.881263256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92621612548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33078718185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55554914474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45815181732178</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.33827972412109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58551740646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38323211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46564388275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35326290130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30831098556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59300899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41319990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17345428466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09853363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90374040603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95618438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94120025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86627912521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94869232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84380340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59656572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48418474197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60405826568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55910587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88875579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80634355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64151859283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79135942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76139116287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88126420974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92621612548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33078718185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55554962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45815277099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33828020095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30081939697266</t>
+    <t xml:space="preserve">6.3008189201355</t>
   </si>
   <si>
     <t xml:space="preserve">6.128502368927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06107378005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77637577056885</t>
+    <t xml:space="preserve">6.0610728263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77637481689453</t>
   </si>
   <si>
     <t xml:space="preserve">5.768883228302</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">5.70145463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57408952713013</t>
+    <t xml:space="preserve">5.66399478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57409048080444</t>
   </si>
   <si>
     <t xml:space="preserve">5.75389862060547</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">5.78386735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67897748947144</t>
+    <t xml:space="preserve">5.67897891998291</t>
   </si>
   <si>
     <t xml:space="preserve">5.6265344619751</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">5.65650224685669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54412174224854</t>
+    <t xml:space="preserve">5.54412126541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.58158159255981</t>
@@ -1565,37 +1565,37 @@
     <t xml:space="preserve">5.50666093826294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53662967681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43174123764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4692006111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31935930252075</t>
+    <t xml:space="preserve">5.53662919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43174076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46920156478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31935977935791</t>
   </si>
   <si>
     <t xml:space="preserve">5.28189945220947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42424821853638</t>
+    <t xml:space="preserve">5.42424917221069</t>
   </si>
   <si>
     <t xml:space="preserve">5.49167728424072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51415395736694</t>
+    <t xml:space="preserve">5.51415300369263</t>
   </si>
   <si>
     <t xml:space="preserve">5.36431217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27440690994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18450307846069</t>
+    <t xml:space="preserve">5.27440786361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18450260162354</t>
   </si>
   <si>
     <t xml:space="preserve">5.2069787979126</t>
@@ -1607,28 +1607,28 @@
     <t xml:space="preserve">5.74640703201294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47669267654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21446990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13955068588257</t>
+    <t xml:space="preserve">5.47669315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21447134017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13954973220825</t>
   </si>
   <si>
     <t xml:space="preserve">5.09459829330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10958194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07212209701538</t>
+    <t xml:space="preserve">5.10958290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07212162017822</t>
   </si>
   <si>
     <t xml:space="preserve">5.05713796615601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01967763900757</t>
+    <t xml:space="preserve">5.01967716217041</t>
   </si>
   <si>
     <t xml:space="preserve">5.03466129302979</t>
@@ -1637,52 +1637,52 @@
     <t xml:space="preserve">4.92977285385132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87732839584351</t>
+    <t xml:space="preserve">4.87732887268066</t>
   </si>
   <si>
     <t xml:space="preserve">4.86983680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7349796295166</t>
+    <t xml:space="preserve">4.73497915267944</t>
   </si>
   <si>
     <t xml:space="preserve">4.77243900299072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82488441467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88482093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75745534896851</t>
+    <t xml:space="preserve">4.82488393783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88482046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75745487213135</t>
   </si>
   <si>
     <t xml:space="preserve">4.86234378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91478872299194</t>
+    <t xml:space="preserve">4.9147891998291</t>
   </si>
   <si>
     <t xml:space="preserve">4.89980459213257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85485219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95224952697754</t>
+    <t xml:space="preserve">4.8548526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95224905014038</t>
   </si>
   <si>
     <t xml:space="preserve">5.16951894760132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08710622787476</t>
+    <t xml:space="preserve">5.08710670471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.13205814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21840715408325</t>
+    <t xml:space="preserve">6.21840667724609</t>
   </si>
   <si>
     <t xml:space="preserve">6.25586700439453</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">5.99364471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04215335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98221683502197</t>
+    <t xml:space="preserve">5.04215383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98221731185913</t>
   </si>
   <si>
     <t xml:space="preserve">4.94475698471069</t>
@@ -1712,37 +1712,37 @@
     <t xml:space="preserve">5.02716970443726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8923134803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04964542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95974159240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81739187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79491567611694</t>
+    <t xml:space="preserve">4.89231300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04964637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95974063873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81739234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7949161529541</t>
   </si>
   <si>
     <t xml:space="preserve">4.78742408752441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83237552642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9747257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90729761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76494789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47275733947754</t>
+    <t xml:space="preserve">4.83237600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97472524642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90729665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76494741439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47275686264038</t>
   </si>
   <si>
     <t xml:space="preserve">4.27047157287598</t>
@@ -1751,46 +1751,46 @@
     <t xml:space="preserve">4.38285303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32291698455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18056678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16558265686035</t>
+    <t xml:space="preserve">4.32291650772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18056726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16558361053467</t>
   </si>
   <si>
     <t xml:space="preserve">4.30044031143188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31542444229126</t>
+    <t xml:space="preserve">4.31542491912842</t>
   </si>
   <si>
     <t xml:space="preserve">4.46526527404785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45777273178101</t>
+    <t xml:space="preserve">4.45777320861816</t>
   </si>
   <si>
     <t xml:space="preserve">4.71250343322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10209035873413</t>
+    <t xml:space="preserve">5.10208988189697</t>
   </si>
   <si>
     <t xml:space="preserve">5.07961463928223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93726444244385</t>
+    <t xml:space="preserve">4.93726491928101</t>
   </si>
   <si>
     <t xml:space="preserve">5.01218557357788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24443960189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22196292877197</t>
+    <t xml:space="preserve">5.24443912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22196245193481</t>
   </si>
   <si>
     <t xml:space="preserve">5.25942325592041</t>
@@ -1805,55 +1805,55 @@
     <t xml:space="preserve">5.28939199447632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16202688217163</t>
+    <t xml:space="preserve">5.16202640533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.31186819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41675662994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37180471420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44672441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39428043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45421695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.409264087677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89624834060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85878753662109</t>
+    <t xml:space="preserve">5.41675710678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37180376052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44672536849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39427995681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45421743392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40926456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89624738693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85878801345825</t>
   </si>
   <si>
     <t xml:space="preserve">6.121009349823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22589826583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81383562088013</t>
+    <t xml:space="preserve">6.22589921951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81383609771729</t>
   </si>
   <si>
     <t xml:space="preserve">6.00113725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79885149002075</t>
+    <t xml:space="preserve">5.79885101318359</t>
   </si>
   <si>
     <t xml:space="preserve">5.82132720947266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91123199462891</t>
+    <t xml:space="preserve">5.91123247146606</t>
   </si>
   <si>
     <t xml:space="preserve">6.03110504150391</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">5.91872453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83631181716919</t>
+    <t xml:space="preserve">5.83631229400635</t>
   </si>
   <si>
     <t xml:space="preserve">5.87377214431763</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">5.97116851806641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21091508865356</t>
+    <t xml:space="preserve">6.21091461181641</t>
   </si>
   <si>
     <t xml:space="preserve">6.09104156494141</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">6.15097808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14348602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04608869552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02361297607422</t>
+    <t xml:space="preserve">6.14348554611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04608964920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02361345291138</t>
   </si>
   <si>
     <t xml:space="preserve">6.03859758377075</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">5.97866106033325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69396257400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72393131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70894718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46170902252197</t>
+    <t xml:space="preserve">5.69396209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72393083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49916887283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46170854568481</t>
   </si>
   <si>
     <t xml:space="preserve">5.73891448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55161333084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47268533706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30019474029541</t>
+    <t xml:space="preserve">5.55161380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47268581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30019426345825</t>
   </si>
   <si>
     <t xml:space="preserve">5.33155632019043</t>
@@ -1937,31 +1937,31 @@
     <t xml:space="preserve">5.35507774353027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30803489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37859916687012</t>
+    <t xml:space="preserve">5.30803442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37859869003296</t>
   </si>
   <si>
     <t xml:space="preserve">5.24531030654907</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26883125305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28451251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25315141677856</t>
+    <t xml:space="preserve">5.26883172988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28451347351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25315046310425</t>
   </si>
   <si>
     <t xml:space="preserve">5.14338350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06497859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00225448608398</t>
+    <t xml:space="preserve">5.06497812271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00225400924683</t>
   </si>
   <si>
     <t xml:space="preserve">5.16690540313721</t>
@@ -1970,31 +1970,31 @@
     <t xml:space="preserve">5.20610761642456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33939647674561</t>
+    <t xml:space="preserve">5.33939695358276</t>
   </si>
   <si>
     <t xml:space="preserve">5.29235363006592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11986255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13554382324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09634017944336</t>
+    <t xml:space="preserve">5.11986207962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13554334640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09634065628052</t>
   </si>
   <si>
     <t xml:space="preserve">5.05713748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11202096939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17474508285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44916391372681</t>
+    <t xml:space="preserve">5.11202144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17474555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44916439056396</t>
   </si>
   <si>
     <t xml:space="preserve">5.45700454711914</t>
@@ -2003,40 +2003,40 @@
     <t xml:space="preserve">5.61381483078003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70790147781372</t>
+    <t xml:space="preserve">5.70790195465088</t>
   </si>
   <si>
     <t xml:space="preserve">5.67653942108154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55893135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51188850402832</t>
+    <t xml:space="preserve">5.63733673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55893182754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51188898086548</t>
   </si>
   <si>
     <t xml:space="preserve">5.48836660385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48052644729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36291885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31587505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3237156867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19826793670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79839992523193</t>
+    <t xml:space="preserve">5.48052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36291837692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31587553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32371616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19826745986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79840040206909</t>
   </si>
   <si>
     <t xml:space="preserve">4.70431423187256</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">4.71215486526489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67295217514038</t>
+    <t xml:space="preserve">4.67295169830322</t>
   </si>
   <si>
     <t xml:space="preserve">4.63374948501587</t>
@@ -2072,34 +2072,34 @@
     <t xml:space="preserve">4.59454679489136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62590932846069</t>
+    <t xml:space="preserve">4.62590885162354</t>
   </si>
   <si>
     <t xml:space="preserve">4.68079233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90032768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22962951660156</t>
+    <t xml:space="preserve">4.90032720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2296290397644</t>
   </si>
   <si>
     <t xml:space="preserve">5.02577543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04145622253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15122413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22178888320923</t>
+    <t xml:space="preserve">5.0414571762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1512246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22178840637207</t>
   </si>
   <si>
     <t xml:space="preserve">5.21394824981689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15906429290771</t>
+    <t xml:space="preserve">5.15906476974487</t>
   </si>
   <si>
     <t xml:space="preserve">5.08065938949585</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">5.1277027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01793622970581</t>
+    <t xml:space="preserve">5.01793575286865</t>
   </si>
   <si>
     <t xml:space="preserve">5.07281875610352</t>
@@ -2117,43 +2117,43 @@
     <t xml:space="preserve">5.08849954605103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19042730331421</t>
+    <t xml:space="preserve">5.19042634963989</t>
   </si>
   <si>
     <t xml:space="preserve">5.18258619308472</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52756977081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51972818374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40212059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56677198410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43348264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50404787063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53540992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41780185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42564296722412</t>
+    <t xml:space="preserve">5.52756881713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5197286605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40212106704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56677150726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4334831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50404739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53541040420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41780138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42564249038696</t>
   </si>
   <si>
     <t xml:space="preserve">5.84118986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7627854347229</t>
+    <t xml:space="preserve">5.76278448104858</t>
   </si>
   <si>
     <t xml:space="preserve">5.64517688751221</t>
@@ -2162,28 +2162,28 @@
     <t xml:space="preserve">5.44132328033447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40996122360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38643980026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34723711013794</t>
+    <t xml:space="preserve">5.40996170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38643932342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3472375869751</t>
   </si>
   <si>
     <t xml:space="preserve">5.37075853347778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23746967315674</t>
+    <t xml:space="preserve">5.2374701499939</t>
   </si>
   <si>
     <t xml:space="preserve">4.97873210906982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83760356903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89248657226562</t>
+    <t xml:space="preserve">4.83760261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89248704910278</t>
   </si>
   <si>
     <t xml:space="preserve">4.86896514892578</t>
@@ -2192,37 +2192,37 @@
     <t xml:space="preserve">4.92384910583496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87680530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98657321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57102537155151</t>
+    <t xml:space="preserve">4.87680578231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98657274246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57102584838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.54750394821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57886648178101</t>
+    <t xml:space="preserve">4.57886600494385</t>
   </si>
   <si>
     <t xml:space="preserve">4.39069318771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15547752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2260422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1162748336792</t>
+    <t xml:space="preserve">4.15547800064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22604179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11627531051636</t>
   </si>
   <si>
     <t xml:space="preserve">3.84185719490051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63800263404846</t>
+    <t xml:space="preserve">3.63800311088562</t>
   </si>
   <si>
     <t xml:space="preserve">3.26165771484375</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">3.29302000999451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32438158988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90099406242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09700679779053</t>
+    <t xml:space="preserve">3.32438182830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90099358558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09700703620911</t>
   </si>
   <si>
     <t xml:space="preserve">3.05780434608459</t>
@@ -2246,19 +2246,19 @@
     <t xml:space="preserve">2.94803690910339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00292062759399</t>
+    <t xml:space="preserve">3.00292038917542</t>
   </si>
   <si>
     <t xml:space="preserve">3.13620948791504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03036236763</t>
+    <t xml:space="preserve">3.03036260604858</t>
   </si>
   <si>
     <t xml:space="preserve">3.21461462974548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25381755828857</t>
+    <t xml:space="preserve">3.25381731987</t>
   </si>
   <si>
     <t xml:space="preserve">3.22245526313782</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">3.24205660820007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24597692489624</t>
+    <t xml:space="preserve">3.24597716331482</t>
   </si>
   <si>
     <t xml:space="preserve">3.23813652992249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34006309509277</t>
+    <t xml:space="preserve">3.36750531196594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34006333351135</t>
   </si>
   <si>
     <t xml:space="preserve">3.45767068862915</t>
@@ -2285,13 +2285,13 @@
     <t xml:space="preserve">3.59880065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37142562866211</t>
+    <t xml:space="preserve">3.37142515182495</t>
   </si>
   <si>
     <t xml:space="preserve">3.52039480209351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54391670227051</t>
+    <t xml:space="preserve">3.54391694068909</t>
   </si>
   <si>
     <t xml:space="preserve">3.7242488861084</t>
@@ -2300,100 +2300,100 @@
     <t xml:space="preserve">3.81049466133118</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92026162147522</t>
+    <t xml:space="preserve">3.92026233673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.3358097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32796907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32012844085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23388242721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16331815719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07707262039185</t>
+    <t xml:space="preserve">4.32796859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32012891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23388290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16331768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07707166671753</t>
   </si>
   <si>
     <t xml:space="preserve">4.21820163726807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21036148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25740432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19467973709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73208975791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79481434822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83401608467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8457772731781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70072674751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83009600639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87321853637695</t>
+    <t xml:space="preserve">4.21036052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25740480422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19468021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73208951950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79481339454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83401560783386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84577703475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7007269859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83009624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87321901321411</t>
   </si>
   <si>
     <t xml:space="preserve">3.80265378952026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8222553730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86145782470703</t>
+    <t xml:space="preserve">3.82225513458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86145758628845</t>
   </si>
   <si>
     <t xml:space="preserve">3.75169038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74385023117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98298621177673</t>
+    <t xml:space="preserve">3.74384999275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98298692703247</t>
   </si>
   <si>
     <t xml:space="preserve">4.29660701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10059356689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91634178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95946502685547</t>
+    <t xml:space="preserve">4.10059404373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91634154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95946455001831</t>
   </si>
   <si>
     <t xml:space="preserve">4.03786993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1397967338562</t>
+    <t xml:space="preserve">4.13979721069336</t>
   </si>
   <si>
     <t xml:space="preserve">4.14763736724854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01434803009033</t>
+    <t xml:space="preserve">4.01434755325317</t>
   </si>
   <si>
     <t xml:space="preserve">3.95162415504456</t>
@@ -2405,31 +2405,31 @@
     <t xml:space="preserve">3.88889956474304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05355072021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06923151016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03002882003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89281988143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92810225486755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91242122650146</t>
+    <t xml:space="preserve">4.05355024337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06923198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89282035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92810273170471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91242098808289</t>
   </si>
   <si>
     <t xml:space="preserve">3.85753726959229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8653781414032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82617592811584</t>
+    <t xml:space="preserve">3.86537861824036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82617568969727</t>
   </si>
   <si>
     <t xml:space="preserve">3.88105916976929</t>
@@ -2438,58 +2438,58 @@
     <t xml:space="preserve">3.90458106994629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90850138664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77913308143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75561046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74777007102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80657410621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497948646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96730470657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02218818664551</t>
+    <t xml:space="preserve">3.90850114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77913236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75561094284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74777054786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80657434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96730518341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02218866348267</t>
   </si>
   <si>
     <t xml:space="preserve">3.93594264984131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76345181465149</t>
+    <t xml:space="preserve">3.76345157623291</t>
   </si>
   <si>
     <t xml:space="preserve">3.75953102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6458432674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6693651676178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66544508934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63016200065613</t>
+    <t xml:space="preserve">3.64584374427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66936492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66544461250305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63016319274902</t>
   </si>
   <si>
     <t xml:space="preserve">3.56351804733276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56743836402893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59096002578735</t>
+    <t xml:space="preserve">3.56743860244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59095978736877</t>
   </si>
   <si>
     <t xml:space="preserve">3.48903322219849</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">3.48119258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44198966026306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3871066570282</t>
+    <t xml:space="preserve">3.44199013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38710641860962</t>
   </si>
   <si>
     <t xml:space="preserve">3.31654167175293</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">3.40278744697571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42238831520081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43807005882263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46551156044006</t>
+    <t xml:space="preserve">3.42238855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43807029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46551132202148</t>
   </si>
   <si>
     <t xml:space="preserve">3.49295353889465</t>
@@ -2531,40 +2531,40 @@
     <t xml:space="preserve">3.55567765235901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50079417228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51255464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37926602363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43414974212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42630887031555</t>
+    <t xml:space="preserve">3.50079393386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51255488395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37926554679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43414950370789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42630910873413</t>
   </si>
   <si>
     <t xml:space="preserve">3.4615912437439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4498302